--- a/dados/base/goias.xlsx
+++ b/dados/base/goias.xlsx
@@ -1795,7 +1795,11 @@
       <c r="L13" s="1" t="n">
         <v>46213</v>
       </c>
-      <c r="M13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr">
         <is>
           <t>06/2026</t>
@@ -1828,7 +1832,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr"/>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 08/07/2026 - Data Comentário: 06/07/2026 12:40</t>
+        </is>
+      </c>
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr"/>
       <c r="Y13" t="inlineStr"/>
@@ -83553,8 +83561,16 @@
       <c r="AA789" t="inlineStr"/>
       <c r="AB789" t="inlineStr"/>
       <c r="AC789" t="inlineStr"/>
-      <c r="AD789" t="inlineStr"/>
-      <c r="AE789" t="inlineStr"/>
+      <c r="AD789" t="inlineStr">
+        <is>
+          <t>Atraso da operação, as coordenadoras Erika Santana e Isabella Nascimento informaram que os fechamentos serão concluídos até o final desta semana. - Data Comentário: 06/07/2026 12:41</t>
+        </is>
+      </c>
+      <c r="AE789" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
       <c r="AF789" t="inlineStr">
         <is>
           <t>Tarefa</t>
@@ -83662,12 +83678,12 @@
       <c r="AC790" t="inlineStr"/>
       <c r="AD790" t="inlineStr">
         <is>
-          <t>Tarefa reaberta. A previsão de conclusão está prevista para 25/06/2026. - Data Comentário: 24/06/2026 12:06</t>
+          <t>Atraso da operação, as coordenadoras Erika Santana e Isabella Nascimento informaram que os fechamentos serão concluídos até o final desta semana. - Data Comentário: 06/07/2026 12:41</t>
         </is>
       </c>
       <c r="AE790" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
       <c r="AF790" t="inlineStr">
@@ -83777,12 +83793,12 @@
       <c r="AC791" t="inlineStr"/>
       <c r="AD791" t="inlineStr">
         <is>
-          <t>Tarefa reaberta. A previsão de conclusão está prevista para 03/07/2026. - Data Comentário: 02/07/2026 07:32</t>
+          <t>Tarefa reaberta. A previsão de conclusão está prevista para 06/07/2026. - Data Comentário: 06/07/2026 12:41</t>
         </is>
       </c>
       <c r="AE791" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="AF791" t="inlineStr">
@@ -83892,12 +83908,12 @@
       <c r="AC792" t="inlineStr"/>
       <c r="AD792" t="inlineStr">
         <is>
-          <t>Tarefa reaberta. A previsão de conclusão está prevista para 30/06/2026. - Data Comentário: 29/06/2026 09:26</t>
+          <t>Tarefa reaberta. A previsão de conclusão está prevista para 06/07/2026. - Data Comentário: 06/07/2026 12:41</t>
         </is>
       </c>
       <c r="AE792" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="AF792" t="inlineStr">
@@ -84007,12 +84023,12 @@
       <c r="AC793" t="inlineStr"/>
       <c r="AD793" t="inlineStr">
         <is>
-          <t>Tarefa reaberta. A previsão de conclusão está prevista para 30/06/2026. - Data Comentário: 29/06/2026 09:23</t>
+          <t>Tarefa reaberta. A previsão de conclusão está prevista para 06/07/2026. - Data Comentário: 06/07/2026 12:41</t>
         </is>
       </c>
       <c r="AE793" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="AF793" t="inlineStr">
@@ -84119,12 +84135,12 @@
       <c r="AC794" t="inlineStr"/>
       <c r="AD794" t="inlineStr">
         <is>
-          <t>Aguardando implantação do cliente para que seja possível a realização da tarefa - AI09 - Data Comentário: 25/06/2026 18:15</t>
+          <t>Aguardando implantação do cliente para que seja possível a realização da tarefa - AI09 - Data Comentário: 06/07/2026 12:41</t>
         </is>
       </c>
       <c r="AE794" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
       <c r="AF794" t="inlineStr">
@@ -84227,12 +84243,12 @@
       <c r="AC795" t="inlineStr"/>
       <c r="AD795" t="inlineStr">
         <is>
-          <t>Aguardando implantação do cliente para que seja possível a realização da tarefa - AI09 - Data Comentário: 25/06/2026 18:15</t>
+          <t>Aguardando implantação do cliente para que seja possível a realização da tarefa - AI09 - Data Comentário: 06/07/2026 12:41</t>
         </is>
       </c>
       <c r="AE795" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
       <c r="AF795" t="inlineStr">
@@ -84333,8 +84349,16 @@
       <c r="AA796" t="inlineStr"/>
       <c r="AB796" t="inlineStr"/>
       <c r="AC796" t="inlineStr"/>
-      <c r="AD796" t="inlineStr"/>
-      <c r="AE796" t="inlineStr"/>
+      <c r="AD796" t="inlineStr">
+        <is>
+          <t>Aguardando implantação do cliente para que seja possível a realização da tarefa - AI09 - Data Comentário: 06/07/2026 12:41</t>
+        </is>
+      </c>
+      <c r="AE796" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
       <c r="AF796" t="inlineStr">
         <is>
           <t>Tarefa</t>
@@ -84443,12 +84467,12 @@
       <c r="AC797" t="inlineStr"/>
       <c r="AD797" t="inlineStr">
         <is>
-          <t>Operação e GC validando as informações errôneas no sistema de análise - Data Comentário: 24/06/2026 14:39</t>
+          <t>A operação e o GC estão ajustando os créditos de meses anteriores para que o valor desse mês seja ajustado. A Gerente Priscila Volpe está em contato direto com o GC e informou que a tarefa deve ser concluída até o fim desta semana. - Data Comentário: 06/07/2026 12:41</t>
         </is>
       </c>
       <c r="AE797" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
       <c r="AF797" t="inlineStr">
@@ -84554,12 +84578,12 @@
       <c r="AC798" t="inlineStr"/>
       <c r="AD798" t="inlineStr">
         <is>
-          <t>Atraso por parte do cliente, GC e GM acionado - CA03 - Data Comentário: 25/06/2026 18:14</t>
+          <t>Atraso do cliente, o atraso do cliente já é recorrente e de ciência do Master e do Gerente de Contas. - Data Comentário: 06/07/2026 12:41</t>
         </is>
       </c>
       <c r="AE798" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
       <c r="AF798" t="inlineStr">
@@ -84669,12 +84693,12 @@
       <c r="AC799" t="inlineStr"/>
       <c r="AD799" t="inlineStr">
         <is>
-          <t>Atraso por parte do cliente, GC e GM acionados - Data Comentário: 25/06/2026 18:14</t>
+          <t>Atraso do cliente, o atraso do cliente já é recorrente e de ciência do Master e do Gerente de Contas. - Data Comentário: 06/07/2026 12:41</t>
         </is>
       </c>
       <c r="AE799" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
       <c r="AF799" t="inlineStr">
@@ -84778,8 +84802,16 @@
       <c r="AA800" t="inlineStr"/>
       <c r="AB800" t="inlineStr"/>
       <c r="AC800" t="inlineStr"/>
-      <c r="AD800" t="inlineStr"/>
-      <c r="AE800" t="inlineStr"/>
+      <c r="AD800" t="inlineStr">
+        <is>
+          <t>Claudineia cobrada a respeito das aplicações, ela informou que o atraso se deu ao fato de estar concluindo a distribuição da carteira de clientes do seu departamento, mas a tarefa será executada ainda hoje. - Data Comentário: 06/07/2026 12:41</t>
+        </is>
+      </c>
+      <c r="AE800" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
       <c r="AF800" t="inlineStr">
         <is>
           <t>Tarefa</t>
@@ -84888,12 +84920,12 @@
       <c r="AC801" t="inlineStr"/>
       <c r="AD801" t="inlineStr">
         <is>
-          <t>Tarefa reaberta. A previsão de conclusão está prevista para 01/07/2026. - Data Comentário: 30/06/2026 08:45</t>
+          <t>Os GC's estão respondendo as importações do Contábil conforme vão sendo realizadas, o GD Sérgio informou que a previsão é concluir na próxima semana - Data Comentário: 06/07/2026 12:42</t>
         </is>
       </c>
       <c r="AE801" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="AF801" t="inlineStr">
@@ -85004,12 +85036,12 @@
       <c r="AC802" t="inlineStr"/>
       <c r="AD802" t="inlineStr">
         <is>
-          <t>Tarefa reaberta e já passadas para o GO Sérgio que disse que as mesmas serão conclupidas até o fim da semana - Data Comentário: 22/06/2026 17:05</t>
+          <t>Os GC's estão respondendo as importações do Contábil conforme vão sendo realizadas, o GD Sérgio informou que a previsão é concluir na próxima semana - Data Comentário: 06/07/2026 12:42</t>
         </is>
       </c>
       <c r="AE802" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="AF802" t="inlineStr">
@@ -85111,12 +85143,12 @@
       <c r="AC803" t="inlineStr"/>
       <c r="AD803" t="inlineStr">
         <is>
-          <t>Tarefa reaberta. A previsão de conclusão está prevista para 04/07/2026. - Data Comentário: 03/07/2026 17:02</t>
+          <t>Os GC's estão respondendo as importações do Contábil conforme vão sendo realizadas, o GD Sérgio informou que a previsão é concluir na próxima semana - Data Comentário: 06/07/2026 12:42</t>
         </is>
       </c>
       <c r="AE803" t="inlineStr">
         <is>
-          <t>04/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="AF803" t="inlineStr">
@@ -85227,12 +85259,12 @@
       <c r="AC804" t="inlineStr"/>
       <c r="AD804" t="inlineStr">
         <is>
-          <t>Tarefa reaberta. A previsão de conclusão está prevista para 01/07/2026. - Data Comentário: 30/06/2026 08:50</t>
+          <t>Os GC's estão respondendo as importações do Contábil conforme vão sendo realizadas, o GD Sérgio informou que a previsão é concluir na próxima semana - Data Comentário: 06/07/2026 12:42</t>
         </is>
       </c>
       <c r="AE804" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="AF804" t="inlineStr">

--- a/dados/base/goias.xlsx
+++ b/dados/base/goias.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG804"/>
+  <dimension ref="A1:AG803"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85036,11 +85036,11 @@
     </row>
     <row r="801">
       <c r="A801" t="n">
-        <v>6981</v>
+        <v>6404</v>
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUIZ GOMES DA SILVA - O GOIANO </t>
+          <t>SOLAR INVESTIMENTOS LTDA</t>
         </is>
       </c>
       <c r="C801" t="inlineStr">
@@ -85050,7 +85050,7 @@
       </c>
       <c r="D801" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E801" t="inlineStr">
@@ -85060,41 +85060,45 @@
       </c>
       <c r="F801" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G801" t="n">
-        <v>9793</v>
+        <v>11001</v>
       </c>
       <c r="H801" t="n">
         <v>0</v>
       </c>
       <c r="I801" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="J801" t="inlineStr">
         <is>
-          <t>Aplicação de Modelo - Pendente - SP</t>
+          <t>Movimento - Analise de Balanço Lucro Presumido</t>
         </is>
       </c>
       <c r="K801" t="inlineStr"/>
       <c r="L801" s="1" t="n">
-        <v>46205</v>
-      </c>
-      <c r="M801" t="inlineStr"/>
+        <v>46202</v>
+      </c>
+      <c r="M801" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
+        </is>
+      </c>
       <c r="N801" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>05/2026</t>
         </is>
       </c>
       <c r="O801" t="n">
-        <v>18195069</v>
+        <v>16962451</v>
       </c>
       <c r="P801" t="inlineStr">
         <is>
-          <t>Claudineia Rodrigues</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="Q801" t="inlineStr">
@@ -85104,17 +85108,22 @@
       </c>
       <c r="R801" t="inlineStr"/>
       <c r="S801" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T801" t="inlineStr">
         <is>
-          <t>SUPERMERCADO AVENIDA</t>
-        </is>
-      </c>
-      <c r="U801" t="inlineStr"/>
+          <t>SOLAR INVESTIMENTOS</t>
+        </is>
+      </c>
+      <c r="U801" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V801" t="inlineStr">
         <is>
-          <t>Rotina de Cliente Sem Modelo - CodCliente: 6981; Tarefa Incluida: 9793; Vencimento: 02/07/2026 00:00:00; UsuarioResponsavel: Claudineia - Data Comentário: 01/07/2026 09:04</t>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 02/07/2026 
+Analisar até 02/07/2026 - Data Comentário: 01/07/2026 07:26</t>
         </is>
       </c>
       <c r="W801" t="inlineStr"/>
@@ -85126,12 +85135,12 @@
       <c r="AC801" t="inlineStr"/>
       <c r="AD801" t="inlineStr">
         <is>
-          <t>Claudineia cobrada a respeito das aplicações, ela informou que o atraso se deu ao fato de estar concluindo a distribuição da carteira de clientes do seu departamento, mas a tarefa será executada ainda hoje. - Data Comentário: 06/07/2026 12:41</t>
+          <t>Os GC's estão respondendo as importações do Contábil conforme vão sendo realizadas, o GD Sérgio informou que a previsão é concluir na próxima semana - Data Comentário: 06/07/2026 12:42</t>
         </is>
       </c>
       <c r="AE801" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="AF801" t="inlineStr">
@@ -85143,11 +85152,11 @@
     </row>
     <row r="802">
       <c r="A802" t="n">
-        <v>6404</v>
+        <v>6224</v>
       </c>
       <c r="B802" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C802" t="inlineStr">
@@ -85157,7 +85166,7 @@
       </c>
       <c r="D802" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E802" t="inlineStr">
@@ -85167,11 +85176,11 @@
       </c>
       <c r="F802" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G802" t="n">
-        <v>11001</v>
+        <v>7877</v>
       </c>
       <c r="H802" t="n">
         <v>0</v>
@@ -85183,25 +85192,25 @@
       </c>
       <c r="J802" t="inlineStr">
         <is>
-          <t>Movimento - Analise de Balanço Lucro Presumido</t>
+          <t>Movimento - Analise de Balanço Lucro Real</t>
         </is>
       </c>
       <c r="K802" t="inlineStr"/>
       <c r="L802" s="1" t="n">
-        <v>46202</v>
+        <v>46171</v>
       </c>
       <c r="M802" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="N802" t="inlineStr">
         <is>
-          <t>05/2026</t>
+          <t>04/2026</t>
         </is>
       </c>
       <c r="O802" t="n">
-        <v>16962451</v>
+        <v>18076566</v>
       </c>
       <c r="P802" t="inlineStr">
         <is>
@@ -85215,11 +85224,11 @@
       </c>
       <c r="R802" t="inlineStr"/>
       <c r="S802" t="n">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="T802" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U802" t="inlineStr">
@@ -85229,8 +85238,8 @@
       </c>
       <c r="V802" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 02/07/2026 
-Analisar até 02/07/2026 - Data Comentário: 01/07/2026 07:26</t>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 03/07/2026 
+Devido as ocorrências com Cbenef e atendimetnos a cliente precisamos reprogramar conclusão para 03/07/2026 - Data Comentário: 03/07/2026 08:15</t>
         </is>
       </c>
       <c r="W802" t="inlineStr"/>
@@ -85259,11 +85268,11 @@
     </row>
     <row r="803">
       <c r="A803" t="n">
-        <v>6224</v>
+        <v>6486</v>
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>PC GAMER GOIANIA LTDA</t>
         </is>
       </c>
       <c r="C803" t="inlineStr">
@@ -85283,11 +85292,11 @@
       </c>
       <c r="F803" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G803" t="n">
-        <v>7877</v>
+        <v>9774</v>
       </c>
       <c r="H803" t="n">
         <v>0</v>
@@ -85299,25 +85308,25 @@
       </c>
       <c r="J803" t="inlineStr">
         <is>
-          <t>Movimento - Analise de Balanço Lucro Real</t>
+          <t>Movimento - Analise de Balanço Simples Nacional</t>
         </is>
       </c>
       <c r="K803" t="inlineStr"/>
       <c r="L803" s="1" t="n">
-        <v>46171</v>
+        <v>46189</v>
       </c>
       <c r="M803" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="N803" t="inlineStr">
         <is>
-          <t>04/2026</t>
+          <t>05/2026</t>
         </is>
       </c>
       <c r="O803" t="n">
-        <v>18076566</v>
+        <v>16976318</v>
       </c>
       <c r="P803" t="inlineStr">
         <is>
@@ -85331,11 +85340,11 @@
       </c>
       <c r="R803" t="inlineStr"/>
       <c r="S803" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="T803" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>PC GAMER</t>
         </is>
       </c>
       <c r="U803" t="inlineStr">
@@ -85345,8 +85354,8 @@
       </c>
       <c r="V803" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 03/07/2026 
-Devido as ocorrências com Cbenef e atendimetnos a cliente precisamos reprogramar conclusão para 03/07/2026 - Data Comentário: 03/07/2026 08:15</t>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 02/07/2026 
+Priorização na análise - Data Comentário: 01/07/2026 08:13</t>
         </is>
       </c>
       <c r="W803" t="inlineStr"/>
@@ -85373,122 +85382,6 @@
       </c>
       <c r="AG803" t="inlineStr"/>
     </row>
-    <row r="804">
-      <c r="A804" t="n">
-        <v>6486</v>
-      </c>
-      <c r="B804" t="inlineStr">
-        <is>
-          <t>PC GAMER GOIANIA LTDA</t>
-        </is>
-      </c>
-      <c r="C804" t="inlineStr">
-        <is>
-          <t>GOIAS</t>
-        </is>
-      </c>
-      <c r="D804" t="inlineStr">
-        <is>
-          <t>Federal - L Real -Trimestral</t>
-        </is>
-      </c>
-      <c r="E804" t="inlineStr">
-        <is>
-          <t>Ricardo Ferreira</t>
-        </is>
-      </c>
-      <c r="F804" t="inlineStr">
-        <is>
-          <t>Edimir Santos</t>
-        </is>
-      </c>
-      <c r="G804" t="n">
-        <v>9774</v>
-      </c>
-      <c r="H804" t="n">
-        <v>0</v>
-      </c>
-      <c r="I804" t="inlineStr">
-        <is>
-          <t>GERENCIA DE CONTAS</t>
-        </is>
-      </c>
-      <c r="J804" t="inlineStr">
-        <is>
-          <t>Movimento - Analise de Balanço Simples Nacional</t>
-        </is>
-      </c>
-      <c r="K804" t="inlineStr"/>
-      <c r="L804" s="1" t="n">
-        <v>46189</v>
-      </c>
-      <c r="M804" t="inlineStr">
-        <is>
-          <t>02/07/2026</t>
-        </is>
-      </c>
-      <c r="N804" t="inlineStr">
-        <is>
-          <t>05/2026</t>
-        </is>
-      </c>
-      <c r="O804" t="n">
-        <v>16976318</v>
-      </c>
-      <c r="P804" t="inlineStr">
-        <is>
-          <t>Ricardo Ferreira</t>
-        </is>
-      </c>
-      <c r="Q804" t="inlineStr">
-        <is>
-          <t>Em Atraso</t>
-        </is>
-      </c>
-      <c r="R804" t="inlineStr"/>
-      <c r="S804" t="n">
-        <v>21</v>
-      </c>
-      <c r="T804" t="inlineStr">
-        <is>
-          <t>PC GAMER</t>
-        </is>
-      </c>
-      <c r="U804" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="V804" t="inlineStr">
-        <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 02/07/2026 
-Priorização na análise - Data Comentário: 01/07/2026 08:13</t>
-        </is>
-      </c>
-      <c r="W804" t="inlineStr"/>
-      <c r="X804" t="inlineStr"/>
-      <c r="Y804" t="inlineStr"/>
-      <c r="Z804" t="inlineStr"/>
-      <c r="AA804" t="inlineStr"/>
-      <c r="AB804" t="inlineStr"/>
-      <c r="AC804" t="inlineStr"/>
-      <c r="AD804" t="inlineStr">
-        <is>
-          <t>Os GC's estão respondendo as importações do Contábil conforme vão sendo realizadas, o GD Sérgio informou que a previsão é concluir na próxima semana - Data Comentário: 06/07/2026 12:42</t>
-        </is>
-      </c>
-      <c r="AE804" t="inlineStr">
-        <is>
-          <t>13/07/2026</t>
-        </is>
-      </c>
-      <c r="AF804" t="inlineStr">
-        <is>
-          <t>Tarefa</t>
-        </is>
-      </c>
-      <c r="AG804" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dados/base/goias.xlsx
+++ b/dados/base/goias.xlsx
@@ -2575,7 +2575,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2612,8 +2612,8 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 08/07/2026 
-Fechamento já enviado no e-social, em processo de validação, previsão de conclusão em 08/07/2026 - Data Comentário: 06/07/2026 11:19</t>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 07/07/2026 
+Previsão de conclusão 07/07/2026. - Data Comentário: 07/07/2026 10:22</t>
         </is>
       </c>
       <c r="W20" t="inlineStr"/>
@@ -2640,11 +2640,11 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>6779</v>
+        <v>6885</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CORDEIRO E CIA LTDA</t>
+          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2698,11 +2698,11 @@
         </is>
       </c>
       <c r="O21" t="n">
-        <v>18090248</v>
+        <v>18157325</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kaique Souza</t>
+          <t>Vitor Guedes</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -2716,14 +2716,14 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 10/07/2026 
-ESocial será baixado no vencimento para evitar retificações por solicitações do cliente. - Data Comentário: 03/07/2026 14:17</t>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 08/07/2026 
+PREVISÃO DE CONCLUSÃO: 08/07/2026 - Data Comentário: 06/07/2026 13:15</t>
         </is>
       </c>
       <c r="W21" t="inlineStr"/>
@@ -2744,17 +2744,17 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>David Bragança</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>6885</v>
+        <v>6945</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
+          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2797,22 +2797,18 @@
       <c r="L22" s="1" t="n">
         <v>46213</v>
       </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>08/07/2026</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O22" t="n">
-        <v>18157325</v>
+        <v>18179152</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Vitor Guedes</t>
+          <t>Santos Karina</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -2826,16 +2822,11 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>BRASIL DISTRIBUIDORA</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 08/07/2026 
-PREVISÃO DE CONCLUSÃO: 08/07/2026 - Data Comentário: 06/07/2026 13:15</t>
-        </is>
-      </c>
+      <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr"/>
@@ -2854,17 +2845,17 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Leandro Matos</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>6945</v>
+        <v>6279</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
+          <t>DIENNYFER DA S PEREIRA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2874,21 +2865,21 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>9746</v>
+        <v>10905</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -2900,25 +2891,29 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>eSocial – Fechamento Mensal</t>
+          <t>eSocial - Fechamento SM</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" s="1" t="n">
         <v>46213</v>
       </c>
-      <c r="M23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O23" t="n">
-        <v>18179152</v>
+        <v>18195935</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Santos Karina</t>
+          <t>Vitor Guedes</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -2932,11 +2927,20 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
+          <t>EMPORIO DOS FRIOS</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 08/07/2026 
+Previsão de conclusão: 08/07/2026 - Data Comentário: 06/07/2026 14:42</t>
+        </is>
+      </c>
       <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr"/>
@@ -2950,22 +2954,22 @@
       <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>Tarefa</t>
+          <t>Obrigação Acessória</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>Leandro Matos</t>
+          <t>David Bragança</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>6279</v>
+        <v>5617</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DIENNYFER DA S PEREIRA</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2975,7 +2979,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2985,14 +2989,14 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>10905</v>
+        <v>5853</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>5784</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -3001,29 +3005,25 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>eSocial - Fechamento SM</t>
+          <t>FOPAG Impressão PDF</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" s="1" t="n">
-        <v>46213</v>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>08/07/2026</t>
-        </is>
-      </c>
+        <v>46210</v>
+      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O24" t="n">
-        <v>18195935</v>
+        <v>17407635</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Vitor Guedes</t>
+          <t>Tania Luz</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -3033,11 +3033,11 @@
       </c>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3047,8 +3047,7 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 08/07/2026 
-Previsão de conclusão: 08/07/2026 - Data Comentário: 06/07/2026 14:42</t>
+          <t>8. Serviços Suspensos. - Data Comentário: 03/07/2026 08:40</t>
         </is>
       </c>
       <c r="W24" t="inlineStr"/>
@@ -3064,22 +3063,22 @@
       <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>Obrigação Acessória</t>
+          <t>Tarefa</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>5617</v>
+        <v>6224</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3099,7 +3098,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3129,7 +3128,7 @@
         </is>
       </c>
       <c r="O25" t="n">
-        <v>17407635</v>
+        <v>17688753</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
@@ -3157,7 +3156,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>8. Serviços Suspensos. - Data Comentário: 03/07/2026 08:40</t>
+          <t>8. Serviços Suspensos. - Data Comentário: 03/07/2026 08:39</t>
         </is>
       </c>
       <c r="W25" t="inlineStr"/>
@@ -3184,11 +3183,11 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>6224</v>
+        <v>5417</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3208,14 +3207,14 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>5853</v>
+        <v>5867</v>
       </c>
       <c r="H26" t="n">
-        <v>5784</v>
+        <v>5786</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -3224,12 +3223,12 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>FOPAG Impressão PDF</t>
+          <t>GFD - FGTS Digital Mensal</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" s="1" t="n">
-        <v>46210</v>
+        <v>46218</v>
       </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
@@ -3238,11 +3237,11 @@
         </is>
       </c>
       <c r="O26" t="n">
-        <v>17688753</v>
+        <v>17399054</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Tania Luz</t>
+          <t>Mikael Teixeira</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -3252,11 +3251,11 @@
       </c>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>NOSSO NOVO SUPERMERCADO</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3264,11 +3263,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>8. Serviços Suspensos. - Data Comentário: 03/07/2026 08:39</t>
-        </is>
-      </c>
+      <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr"/>
       <c r="X26" t="inlineStr"/>
       <c r="Y26" t="inlineStr"/>
@@ -3282,22 +3277,18 @@
       <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>Tarefa</t>
-        </is>
-      </c>
-      <c r="AG26" t="inlineStr">
-        <is>
-          <t>Sara Cavalheiro</t>
-        </is>
-      </c>
+          <t>Imposto</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>5417</v>
+        <v>5617</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3317,7 +3308,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3347,11 +3338,11 @@
         </is>
       </c>
       <c r="O27" t="n">
-        <v>17399054</v>
+        <v>17407645</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Mikael Teixeira</t>
+          <t>Tania Luz</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -3365,7 +3356,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3390,15 +3381,19 @@
           <t>Imposto</t>
         </is>
       </c>
-      <c r="AG27" t="inlineStr"/>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>Sara Cavalheiro</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>5617</v>
+        <v>6224</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3418,7 +3413,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3448,7 +3443,7 @@
         </is>
       </c>
       <c r="O28" t="n">
-        <v>17407645</v>
+        <v>17688773</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
@@ -3499,11 +3494,11 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>6224</v>
+        <v>6486</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>PC GAMER GOIANIA LTDA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3523,7 +3518,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3553,11 +3548,11 @@
         </is>
       </c>
       <c r="O29" t="n">
-        <v>17688773</v>
+        <v>16976054</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Tania Luz</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -3571,7 +3566,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>PC GAMER</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3598,17 +3593,17 @@
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>David Bragança</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>6486</v>
+        <v>6548</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>PC GAMER GOIANIA LTDA</t>
+          <t>GOIAS SILAGEM LTDA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3658,11 +3653,11 @@
         </is>
       </c>
       <c r="O30" t="n">
-        <v>16976054</v>
+        <v>17222615</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Evellin Bispo</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -3676,7 +3671,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>PC GAMER</t>
+          <t>GOIAS SILAGEM</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3703,17 +3698,17 @@
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Leandro Matos</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM LTDA</t>
+          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3728,7 +3723,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3763,11 +3758,11 @@
         </is>
       </c>
       <c r="O31" t="n">
-        <v>17222615</v>
+        <v>18068530</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Evellin Bispo</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -3781,7 +3776,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM</t>
+          <t xml:space="preserve">GTG </t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3808,17 +3803,17 @@
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>Leandro Matos</t>
+          <t>David Bragança</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3828,7 +3823,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3868,7 +3863,7 @@
         </is>
       </c>
       <c r="O32" t="n">
-        <v>18068530</v>
+        <v>18052449</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
@@ -3919,11 +3914,11 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>6628</v>
+        <v>6703</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3933,12 +3928,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3973,11 +3968,11 @@
         </is>
       </c>
       <c r="O33" t="n">
-        <v>18052449</v>
+        <v>18077099</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Elaine Assis</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -3991,7 +3986,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
+          <t>LIMA MOTA</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4024,11 +4019,11 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>6703</v>
+        <v>6779</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
+          <t>CORDEIRO E CIA LTDA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4038,7 +4033,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -4078,11 +4073,11 @@
         </is>
       </c>
       <c r="O34" t="n">
-        <v>18077099</v>
+        <v>18090176</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Elaine Assis</t>
+          <t>Kaique Souza</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -4096,14 +4091,10 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>LIMA MOTA</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>TECNO COM</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr"/>
       <c r="X34" t="inlineStr"/>
@@ -4123,17 +4114,17 @@
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>6779</v>
+        <v>6885</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CORDEIRO E CIA LTDA</t>
+          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4183,11 +4174,11 @@
         </is>
       </c>
       <c r="O35" t="n">
-        <v>18090176</v>
+        <v>18157267</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Kaique Souza</t>
+          <t>Vitor Guedes</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -4201,7 +4192,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U35" t="inlineStr"/>
@@ -4224,17 +4215,17 @@
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>David Bragança</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>6885</v>
+        <v>6945</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
+          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -4249,7 +4240,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4284,11 +4275,11 @@
         </is>
       </c>
       <c r="O36" t="n">
-        <v>18157267</v>
+        <v>18179101</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Vitor Guedes</t>
+          <t>Santos Karina</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -4302,7 +4293,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>BRASIL DISTRIBUIDORA</t>
         </is>
       </c>
       <c r="U36" t="inlineStr"/>
@@ -4325,17 +4316,17 @@
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Leandro Matos</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>6945</v>
+        <v>6486</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
+          <t>PC GAMER GOIANIA LTDA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -4345,12 +4336,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -4359,10 +4350,10 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>5867</v>
+        <v>6348</v>
       </c>
       <c r="H37" t="n">
-        <v>5786</v>
+        <v>0</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -4371,25 +4362,29 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>GFD - FGTS Digital Mensal</t>
+          <t>RESCISÃO - RESCISÃO</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" s="1" t="n">
-        <v>46218</v>
-      </c>
-      <c r="M37" t="inlineStr"/>
+        <v>46210</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>06/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
       <c r="O37" t="n">
-        <v>18179101</v>
+        <v>18167066</v>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Santos Karina</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -4399,15 +4394,24 @@
       </c>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
+          <t>PC GAMER</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 07/07/2026 
+PREVISÃO DE CONCLUSÃO: 07/07/2026 - Data Comentário: 06/07/2026 10:44</t>
+        </is>
+      </c>
       <c r="W37" t="inlineStr"/>
       <c r="X37" t="inlineStr"/>
       <c r="Y37" t="inlineStr"/>
@@ -4426,17 +4430,17 @@
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>Leandro Matos</t>
+          <t>David Bragança</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>6486</v>
+        <v>6949</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PC GAMER GOIANIA LTDA</t>
+          <t>TEC GRUA LOCAÇÃO E COMERCIO DE EQUIPAMENTOS PARA CONSTRUÇÃO LTDA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4456,7 +4460,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Reynaldo Santos</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4477,24 +4481,20 @@
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>07/07/2026</t>
-        </is>
-      </c>
+        <v>46211</v>
+      </c>
+      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
           <t>07/2026</t>
         </is>
       </c>
       <c r="O38" t="n">
-        <v>18167066</v>
+        <v>18199991</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Gabriela Peres</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -4504,22 +4504,17 @@
       </c>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>PC GAMER</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>TEC GRUA</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 07/07/2026 
-PREVISÃO DE CONCLUSÃO: 07/07/2026 - Data Comentário: 06/07/2026 10:44</t>
+          <t>Pedido de demissão - Desconto de Aviso em 02/07/2026 - Pgto 10/07/2026 - Data Comentário: 03/07/2026 13:51</t>
         </is>
       </c>
       <c r="W38" t="inlineStr"/>
@@ -4540,7 +4535,7 @@
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Leandro Matos</t>
         </is>
       </c>
     </row>
@@ -4574,37 +4569,41 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>6348</v>
+        <v>11617</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>RESCISÃO - RESCISÃO</t>
+          <t>Envio de ATA de Implantação - EF I</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" s="1" t="n">
-        <v>46211</v>
-      </c>
-      <c r="M39" t="inlineStr"/>
+        <v>46213</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
       <c r="O39" t="n">
-        <v>18199991</v>
+        <v>18166588</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Gabriela Peres</t>
+          <t>Priscila Volpe</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -4614,7 +4613,7 @@
       </c>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4624,7 +4623,8 @@
       <c r="U39" t="inlineStr"/>
       <c r="V39" t="inlineStr">
         <is>
-          <t>Pedido de demissão - Desconto de Aviso em 02/07/2026 - Pgto 10/07/2026 - Data Comentário: 03/07/2026 13:51</t>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 31/07/2026 
+ainda não foi realizado as implantações - Data Comentário: 01/07/2026 13:38</t>
         </is>
       </c>
       <c r="W39" t="inlineStr"/>
@@ -4640,22 +4640,22 @@
       <c r="AE39" t="inlineStr"/>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Tarefa</t>
         </is>
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>Leandro Matos</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>6949</v>
+        <v>6962</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>TEC GRUA LOCAÇÃO E COMERCIO DE EQUIPAMENTOS PARA CONSTRUÇÃO LTDA</t>
+          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="O40" t="n">
-        <v>18166588</v>
+        <v>18186565</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>TEC GRUA</t>
+          <t>PROMOTORAS GYN</t>
         </is>
       </c>
       <c r="U40" t="inlineStr"/>
@@ -4761,11 +4761,11 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
+          <t>PROMOTORAS GYN LTDA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -4819,7 +4819,7 @@
         </is>
       </c>
       <c r="O41" t="n">
-        <v>18186565</v>
+        <v>18186566</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
@@ -4871,11 +4871,11 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>6963</v>
+        <v>6628</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN LTDA</t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -4885,21 +4885,21 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>11617</v>
+        <v>1875</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -4911,29 +4911,25 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Envio de ATA de Implantação - EF I</t>
+          <t>Est - Sintegra Interestadual</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" s="1" t="n">
-        <v>46213</v>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>31/07/2026</t>
-        </is>
-      </c>
+        <v>46218</v>
+      </c>
+      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O42" t="n">
-        <v>18186566</v>
+        <v>17988660</v>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Priscila Volpe</t>
+          <t>Fernando Bastos</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -4943,20 +4939,19 @@
       </c>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="n">
-        <v>-3</v>
+        <v>-8</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 31/07/2026 
-ainda não foi realizado as implantações - Data Comentário: 01/07/2026 13:38</t>
-        </is>
-      </c>
+          <t xml:space="preserve">GTG </t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr"/>
       <c r="W42" t="inlineStr"/>
       <c r="X42" t="inlineStr"/>
       <c r="Y42" t="inlineStr"/>
@@ -4970,22 +4965,18 @@
       <c r="AE42" t="inlineStr"/>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>Tarefa</t>
-        </is>
-      </c>
-      <c r="AG42" t="inlineStr">
-        <is>
-          <t>Nayara Oliveira</t>
-        </is>
-      </c>
+          <t>Obrigação Acessória</t>
+        </is>
+      </c>
+      <c r="AG42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>6628</v>
+        <v>6548</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>GOIAS SILAGEM LTDA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4995,12 +4986,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -5009,7 +5000,7 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>1875</v>
+        <v>6805</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -5021,12 +5012,12 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Est - Sintegra Interestadual</t>
+          <t>Fed - EFD - REINF - Entrega e PDF</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" s="1" t="n">
-        <v>46218</v>
+        <v>46216</v>
       </c>
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
@@ -5035,11 +5026,11 @@
         </is>
       </c>
       <c r="O43" t="n">
-        <v>17988660</v>
+        <v>17222740</v>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Fernando Bastos</t>
+          <t>Cristiana Grizostomo</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
@@ -5049,11 +5040,11 @@
       </c>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
+          <t>GOIAS SILAGEM</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5078,15 +5069,19 @@
           <t>Obrigação Acessória</t>
         </is>
       </c>
-      <c r="AG43" t="inlineStr"/>
+      <c r="AG43" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM LTDA</t>
+          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -5101,7 +5096,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -5136,11 +5131,11 @@
         </is>
       </c>
       <c r="O44" t="n">
-        <v>17222740</v>
+        <v>18085517</v>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Cristiana Grizostomo</t>
+          <t>Denis Reis</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -5154,7 +5149,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM</t>
+          <t xml:space="preserve">GTG </t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5179,19 +5174,15 @@
           <t>Obrigação Acessória</t>
         </is>
       </c>
-      <c r="AG44" t="inlineStr">
-        <is>
-          <t>Nayara Oliveira</t>
-        </is>
-      </c>
+      <c r="AG44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -5201,7 +5192,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -5241,11 +5232,11 @@
         </is>
       </c>
       <c r="O45" t="n">
-        <v>18085517</v>
+        <v>17988707</v>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Denis Reis</t>
+          <t>Fernando Bastos</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -5288,11 +5279,11 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>6628</v>
+        <v>6962</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -5302,17 +5293,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Reynaldo Santos</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5342,11 +5333,11 @@
         </is>
       </c>
       <c r="O46" t="n">
-        <v>17988707</v>
+        <v>18186993</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Fernando Bastos</t>
+          <t>Denis Reis</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -5360,14 +5351,10 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>PROMOTORAS GYN</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr"/>
       <c r="V46" t="inlineStr"/>
       <c r="W46" t="inlineStr"/>
       <c r="X46" t="inlineStr"/>
@@ -5389,11 +5376,11 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
+          <t>PROMOTORAS GYN LTDA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -5443,7 +5430,7 @@
         </is>
       </c>
       <c r="O47" t="n">
-        <v>18186993</v>
+        <v>18187259</v>
       </c>
       <c r="P47" t="inlineStr">
         <is>
@@ -5486,11 +5473,11 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>6963</v>
+        <v>6962</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN LTDA</t>
+          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -5514,7 +5501,7 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>6805</v>
+        <v>1866</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -5526,21 +5513,25 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Fed - EFD - REINF - Entrega e PDF</t>
+          <t>Mun - ISS Serv. Prestados</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" s="1" t="n">
-        <v>46216</v>
-      </c>
-      <c r="M48" t="inlineStr"/>
+        <v>46212</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O48" t="n">
-        <v>18187259</v>
+        <v>18186944</v>
       </c>
       <c r="P48" t="inlineStr">
         <is>
@@ -5554,7 +5545,7 @@
       </c>
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="n">
-        <v>-6</v>
+        <v>-2</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5562,7 +5553,11 @@
         </is>
       </c>
       <c r="U48" t="inlineStr"/>
-      <c r="V48" t="inlineStr"/>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 06/07/2026 - Data Comentário: 06/07/2026 10:20</t>
+        </is>
+      </c>
       <c r="W48" t="inlineStr"/>
       <c r="X48" t="inlineStr"/>
       <c r="Y48" t="inlineStr"/>
@@ -5576,18 +5571,18 @@
       <c r="AE48" t="inlineStr"/>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>Obrigação Acessória</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="AG48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
+          <t>PROMOTORAS GYN LTDA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -5641,7 +5636,7 @@
         </is>
       </c>
       <c r="O49" t="n">
-        <v>18186944</v>
+        <v>18187210</v>
       </c>
       <c r="P49" t="inlineStr">
         <is>
@@ -5688,11 +5683,11 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>6963</v>
+        <v>6548</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN LTDA</t>
+          <t>GOIAS SILAGEM LTDA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -5712,11 +5707,11 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -5728,7 +5723,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Mun - ISS Serv. Prestados</t>
+          <t>Mun - ISS Serv. Tomados</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -5737,7 +5732,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -5746,11 +5741,11 @@
         </is>
       </c>
       <c r="O50" t="n">
-        <v>18187210</v>
+        <v>17988541</v>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Denis Reis</t>
+          <t>Cristiana Grizostomo</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
@@ -5764,13 +5759,18 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr"/>
+          <t>GOIAS SILAGEM</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 06/07/2026 - Data Comentário: 06/07/2026 10:20</t>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 08/07/2026 
+Colaborador de férias, volta amanhã 07/07 - Data Comentário: 06/07/2026 10:17</t>
         </is>
       </c>
       <c r="W50" t="inlineStr"/>
@@ -5789,15 +5789,19 @@
           <t>Imposto</t>
         </is>
       </c>
-      <c r="AG50" t="inlineStr"/>
+      <c r="AG50" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>6548</v>
+        <v>6962</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM LTDA</t>
+          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -5817,7 +5821,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Reynaldo Santos</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -5842,7 +5846,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -5851,11 +5855,11 @@
         </is>
       </c>
       <c r="O51" t="n">
-        <v>17988541</v>
+        <v>18186951</v>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Cristiana Grizostomo</t>
+          <t>Denis Reis</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
@@ -5869,18 +5873,13 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>PROMOTORAS GYN</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr"/>
       <c r="V51" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 08/07/2026 
-Colaborador de férias, volta amanhã 07/07 - Data Comentário: 06/07/2026 10:17</t>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 07/07/2026 - Data Comentário: 06/07/2026 10:20</t>
         </is>
       </c>
       <c r="W51" t="inlineStr"/>
@@ -5899,19 +5898,15 @@
           <t>Imposto</t>
         </is>
       </c>
-      <c r="AG51" t="inlineStr">
-        <is>
-          <t>Nayara Oliveira</t>
-        </is>
-      </c>
+      <c r="AG51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
+          <t>PROMOTORAS GYN LTDA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -5965,7 +5960,7 @@
         </is>
       </c>
       <c r="O52" t="n">
-        <v>18186951</v>
+        <v>18187217</v>
       </c>
       <c r="P52" t="inlineStr">
         <is>
@@ -6012,11 +6007,11 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>6963</v>
+        <v>6962</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN LTDA</t>
+          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -6040,10 +6035,10 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>1867</v>
+        <v>6886</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>1862</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -6052,25 +6047,21 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Mun - ISS Serv. Tomados</t>
+          <t>Recebimento de NF Serviços Tomados</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" s="1" t="n">
-        <v>46212</v>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>07/07/2026</t>
-        </is>
-      </c>
+        <v>46213</v>
+      </c>
+      <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O53" t="n">
-        <v>18187217</v>
+        <v>18187000</v>
       </c>
       <c r="P53" t="inlineStr">
         <is>
@@ -6084,7 +6075,7 @@
       </c>
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6092,11 +6083,7 @@
         </is>
       </c>
       <c r="U53" t="inlineStr"/>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 07/07/2026 - Data Comentário: 06/07/2026 10:20</t>
-        </is>
-      </c>
+      <c r="V53" t="inlineStr"/>
       <c r="W53" t="inlineStr"/>
       <c r="X53" t="inlineStr"/>
       <c r="Y53" t="inlineStr"/>
@@ -6110,18 +6097,18 @@
       <c r="AE53" t="inlineStr"/>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Tarefa</t>
         </is>
       </c>
       <c r="AG53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
+          <t>PROMOTORAS GYN LTDA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -6171,7 +6158,7 @@
         </is>
       </c>
       <c r="O54" t="n">
-        <v>18187000</v>
+        <v>18187266</v>
       </c>
       <c r="P54" t="inlineStr">
         <is>
@@ -6214,11 +6201,11 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>6963</v>
+        <v>6627</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN LTDA</t>
+          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -6233,19 +6220,19 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>6886</v>
+        <v>10674</v>
       </c>
       <c r="H55" t="n">
-        <v>1862</v>
+        <v>0</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -6254,12 +6241,12 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Recebimento de NF Serviços Tomados</t>
+          <t>Relatório de Entrada para Classificação</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" s="1" t="n">
-        <v>46213</v>
+        <v>46218</v>
       </c>
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
@@ -6268,7 +6255,7 @@
         </is>
       </c>
       <c r="O55" t="n">
-        <v>18187266</v>
+        <v>17968443</v>
       </c>
       <c r="P55" t="inlineStr">
         <is>
@@ -6282,14 +6269,18 @@
       </c>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="n">
-        <v>-3</v>
+        <v>-8</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN</t>
-        </is>
-      </c>
-      <c r="U55" t="inlineStr"/>
+          <t xml:space="preserve">GTG </t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V55" t="inlineStr"/>
       <c r="W55" t="inlineStr"/>
       <c r="X55" t="inlineStr"/>
@@ -6311,11 +6302,11 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>6627</v>
+        <v>6962</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
+          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -6330,12 +6321,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Reynaldo Santos</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -6365,7 +6356,7 @@
         </is>
       </c>
       <c r="O56" t="n">
-        <v>17968443</v>
+        <v>18187014</v>
       </c>
       <c r="P56" t="inlineStr">
         <is>
@@ -6383,14 +6374,10 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
-        </is>
-      </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>PROMOTORAS GYN</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr"/>
       <c r="V56" t="inlineStr"/>
       <c r="W56" t="inlineStr"/>
       <c r="X56" t="inlineStr"/>
@@ -6412,11 +6399,11 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
+          <t>PROMOTORAS GYN LTDA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -6466,7 +6453,7 @@
         </is>
       </c>
       <c r="O57" t="n">
-        <v>18187014</v>
+        <v>18187280</v>
       </c>
       <c r="P57" t="inlineStr">
         <is>
@@ -6509,11 +6496,11 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>6963</v>
+        <v>6779</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN LTDA</t>
+          <t>CORDEIRO E CIA LTDA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -6523,7 +6510,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -6533,41 +6520,45 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>10674</v>
+        <v>11636</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Relatório de Entrada para Classificação</t>
+          <t>Consulta - Movimento Serviços Prestados na Prefeitura</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" s="1" t="n">
-        <v>46218</v>
-      </c>
-      <c r="M58" t="inlineStr"/>
+        <v>46211</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O58" t="n">
-        <v>18187280</v>
+        <v>18085086</v>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Denis Reis</t>
+          <t>Cristina Leite</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
@@ -6577,15 +6568,19 @@
       </c>
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="n">
-        <v>-8</v>
+        <v>-1</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN</t>
+          <t>TECNO COM</t>
         </is>
       </c>
       <c r="U58" t="inlineStr"/>
-      <c r="V58" t="inlineStr"/>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 08/07/2026 - Data Comentário: 06/07/2026 17:18</t>
+        </is>
+      </c>
       <c r="W58" t="inlineStr"/>
       <c r="X58" t="inlineStr"/>
       <c r="Y58" t="inlineStr"/>
@@ -6602,15 +6597,19 @@
           <t>Tarefa</t>
         </is>
       </c>
-      <c r="AG58" t="inlineStr"/>
+      <c r="AG58" t="inlineStr">
+        <is>
+          <t>Ricardo Fischer</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>6779</v>
+        <v>6224</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CORDEIRO E CIA LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -6620,7 +6619,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -6630,11 +6629,11 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>11636</v>
+        <v>1802</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -6646,25 +6645,21 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Consulta - Movimento Serviços Prestados na Prefeitura</t>
+          <t>Est - ICMS RPA - CÓD. 046-2</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" s="1" t="n">
-        <v>46211</v>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>08/07/2026</t>
-        </is>
-      </c>
+        <v>46212</v>
+      </c>
+      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O59" t="n">
-        <v>18085086</v>
+        <v>17688681</v>
       </c>
       <c r="P59" t="inlineStr">
         <is>
@@ -6678,17 +6673,21 @@
       </c>
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
-        </is>
-      </c>
-      <c r="U59" t="inlineStr"/>
+          <t>SUPER MAIS DO GOIÁS</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 08/07/2026 - Data Comentário: 06/07/2026 17:18</t>
+          <t>Atraso do Cliente, cobrança ativa, GC e GM ciente do atraso - Data Comentário: 06/07/2026 15:17</t>
         </is>
       </c>
       <c r="W59" t="inlineStr"/>
@@ -6704,7 +6703,7 @@
       <c r="AE59" t="inlineStr"/>
       <c r="AF59" t="inlineStr">
         <is>
-          <t>Tarefa</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="AG59" t="inlineStr">
@@ -6715,11 +6714,11 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>6224</v>
+        <v>6705</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>NARCIZO ALVES CORDEIRO</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -6729,7 +6728,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -6739,11 +6738,11 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>1802</v>
+        <v>6298</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -6755,12 +6754,12 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Est - ICMS RPA - CÓD. 046-2</t>
+          <t>Est - Sintegra Interestadual</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" s="1" t="n">
-        <v>46212</v>
+        <v>46218</v>
       </c>
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
@@ -6769,7 +6768,7 @@
         </is>
       </c>
       <c r="O60" t="n">
-        <v>17688681</v>
+        <v>17949007</v>
       </c>
       <c r="P60" t="inlineStr">
         <is>
@@ -6783,11 +6782,11 @@
       </c>
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="n">
-        <v>-2</v>
+        <v>-8</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>TECNO COM</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6795,11 +6794,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>Atraso do Cliente, cobrança ativa, GC e GM ciente do atraso - Data Comentário: 06/07/2026 15:17</t>
-        </is>
-      </c>
+      <c r="V60" t="inlineStr"/>
       <c r="W60" t="inlineStr"/>
       <c r="X60" t="inlineStr"/>
       <c r="Y60" t="inlineStr"/>
@@ -6813,7 +6808,7 @@
       <c r="AE60" t="inlineStr"/>
       <c r="AF60" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Obrigação Acessória</t>
         </is>
       </c>
       <c r="AG60" t="inlineStr">
@@ -6824,11 +6819,11 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>6705</v>
+        <v>6885</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>NARCIZO ALVES CORDEIRO</t>
+          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -6878,7 +6873,7 @@
         </is>
       </c>
       <c r="O61" t="n">
-        <v>17949007</v>
+        <v>18134106</v>
       </c>
       <c r="P61" t="inlineStr">
         <is>
@@ -6896,14 +6891,10 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
-        </is>
-      </c>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>EMPORIO DOS FRIOS</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr"/>
       <c r="V61" t="inlineStr"/>
       <c r="W61" t="inlineStr"/>
       <c r="X61" t="inlineStr"/>
@@ -6929,11 +6920,11 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>6885</v>
+        <v>5417</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -6943,7 +6934,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -6953,11 +6944,11 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>6298</v>
+        <v>6806</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
@@ -6969,12 +6960,12 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Est - Sintegra Interestadual</t>
+          <t>Fed - EFD - REINF - Entrega e PDF</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" s="1" t="n">
-        <v>46218</v>
+        <v>46216</v>
       </c>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
@@ -6983,7 +6974,7 @@
         </is>
       </c>
       <c r="O62" t="n">
-        <v>18134106</v>
+        <v>17399228</v>
       </c>
       <c r="P62" t="inlineStr">
         <is>
@@ -6997,14 +6988,18 @@
       </c>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
-        </is>
-      </c>
-      <c r="U62" t="inlineStr"/>
+          <t>NOSSO NOVO SUPERMERCADO</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V62" t="inlineStr"/>
       <c r="W62" t="inlineStr"/>
       <c r="X62" t="inlineStr"/>
@@ -7030,11 +7025,11 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>5417</v>
+        <v>5617</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -7054,7 +7049,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7084,7 +7079,7 @@
         </is>
       </c>
       <c r="O63" t="n">
-        <v>17399228</v>
+        <v>17407789</v>
       </c>
       <c r="P63" t="inlineStr">
         <is>
@@ -7102,7 +7097,7 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7135,11 +7130,11 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>5617</v>
+        <v>6224</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -7159,7 +7154,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -7189,7 +7184,7 @@
         </is>
       </c>
       <c r="O64" t="n">
-        <v>17407789</v>
+        <v>17688917</v>
       </c>
       <c r="P64" t="inlineStr">
         <is>
@@ -7240,11 +7235,11 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>6224</v>
+        <v>6278</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>EMPORIO DOS FRIOS LTDA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -7254,7 +7249,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Real - Anual</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -7264,7 +7259,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -7294,7 +7289,7 @@
         </is>
       </c>
       <c r="O65" t="n">
-        <v>17688917</v>
+        <v>17148836</v>
       </c>
       <c r="P65" t="inlineStr">
         <is>
@@ -7312,7 +7307,7 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7345,11 +7340,11 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>6278</v>
+        <v>6279</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS LTDA</t>
+          <t>DIENNYFER DA S PEREIRA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -7359,7 +7354,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Federal - Lucro Real - Anual</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -7369,7 +7364,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -7399,7 +7394,7 @@
         </is>
       </c>
       <c r="O66" t="n">
-        <v>17148836</v>
+        <v>17071031</v>
       </c>
       <c r="P66" t="inlineStr">
         <is>
@@ -7450,11 +7445,11 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>6279</v>
+        <v>6404</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>DIENNYFER DA S PEREIRA</t>
+          <t>SOLAR INVESTIMENTOS LTDA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -7474,7 +7469,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -7504,7 +7499,7 @@
         </is>
       </c>
       <c r="O67" t="n">
-        <v>17071031</v>
+        <v>16962306</v>
       </c>
       <c r="P67" t="inlineStr">
         <is>
@@ -7522,7 +7517,7 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>SOLAR INVESTIMENTOS</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -7555,11 +7550,11 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>6404</v>
+        <v>6486</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS LTDA</t>
+          <t>PC GAMER GOIANIA LTDA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -7569,7 +7564,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -7609,7 +7604,7 @@
         </is>
       </c>
       <c r="O68" t="n">
-        <v>16962306</v>
+        <v>16976185</v>
       </c>
       <c r="P68" t="inlineStr">
         <is>
@@ -7627,7 +7622,7 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS</t>
+          <t>PC GAMER</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -7660,11 +7655,11 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>6486</v>
+        <v>6703</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PC GAMER GOIANIA LTDA</t>
+          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -7674,7 +7669,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -7714,7 +7709,7 @@
         </is>
       </c>
       <c r="O69" t="n">
-        <v>16976185</v>
+        <v>17948856</v>
       </c>
       <c r="P69" t="inlineStr">
         <is>
@@ -7732,7 +7727,7 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>PC GAMER</t>
+          <t>LIMA MOTA</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -7765,11 +7760,11 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>6703</v>
+        <v>6704</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
+          <t>TECNO COM INFORMATICA LTDA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -7779,7 +7774,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -7819,7 +7814,7 @@
         </is>
       </c>
       <c r="O70" t="n">
-        <v>17948856</v>
+        <v>18085295</v>
       </c>
       <c r="P70" t="inlineStr">
         <is>
@@ -7837,7 +7832,7 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>LIMA MOTA</t>
+          <t>TECNO COM</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -7870,11 +7865,11 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>6704</v>
+        <v>6705</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>TECNO COM INFORMATICA LTDA</t>
+          <t>NARCIZO ALVES CORDEIRO</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -7884,7 +7879,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -7924,7 +7919,7 @@
         </is>
       </c>
       <c r="O71" t="n">
-        <v>18085295</v>
+        <v>17949027</v>
       </c>
       <c r="P71" t="inlineStr">
         <is>
@@ -7975,11 +7970,11 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>6705</v>
+        <v>6779</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>NARCIZO ALVES CORDEIRO</t>
+          <t>CORDEIRO E CIA LTDA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -8029,7 +8024,7 @@
         </is>
       </c>
       <c r="O72" t="n">
-        <v>17949027</v>
+        <v>18085064</v>
       </c>
       <c r="P72" t="inlineStr">
         <is>
@@ -8050,11 +8045,7 @@
           <t>TECNO COM</t>
         </is>
       </c>
-      <c r="U72" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+      <c r="U72" t="inlineStr"/>
       <c r="V72" t="inlineStr"/>
       <c r="W72" t="inlineStr"/>
       <c r="X72" t="inlineStr"/>
@@ -8080,11 +8071,11 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>6779</v>
+        <v>6885</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CORDEIRO E CIA LTDA</t>
+          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -8134,7 +8125,7 @@
         </is>
       </c>
       <c r="O73" t="n">
-        <v>18085064</v>
+        <v>18134124</v>
       </c>
       <c r="P73" t="inlineStr">
         <is>
@@ -8152,7 +8143,7 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U73" t="inlineStr"/>
@@ -8181,11 +8172,11 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>6885</v>
+        <v>6224</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -8195,7 +8186,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -8205,11 +8196,11 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>6806</v>
+        <v>11665</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -8221,12 +8212,12 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Fed - EFD - REINF - Entrega e PDF</t>
+          <t>GIAM (TO)</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
       <c r="L74" s="1" t="n">
-        <v>46216</v>
+        <v>46212</v>
       </c>
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
@@ -8235,7 +8226,7 @@
         </is>
       </c>
       <c r="O74" t="n">
-        <v>18134124</v>
+        <v>18076580</v>
       </c>
       <c r="P74" t="inlineStr">
         <is>
@@ -8249,15 +8240,23 @@
       </c>
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="n">
-        <v>-6</v>
+        <v>-2</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
-        </is>
-      </c>
-      <c r="U74" t="inlineStr"/>
-      <c r="V74" t="inlineStr"/>
+          <t>SUPER MAIS DO GOIÁS</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Atraso do Cliente, cobrança ativa, GC e GM ciente do atraso - Data Comentário: 06/07/2026 15:55</t>
+        </is>
+      </c>
       <c r="W74" t="inlineStr"/>
       <c r="X74" t="inlineStr"/>
       <c r="Y74" t="inlineStr"/>
@@ -8271,7 +8270,7 @@
       <c r="AE74" t="inlineStr"/>
       <c r="AF74" t="inlineStr">
         <is>
-          <t>Obrigação Acessória</t>
+          <t>Tarefa</t>
         </is>
       </c>
       <c r="AG74" t="inlineStr">
@@ -8282,11 +8281,11 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>6224</v>
+        <v>5417</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -8306,14 +8305,14 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>11665</v>
+        <v>7884</v>
       </c>
       <c r="H75" t="n">
-        <v>0</v>
+        <v>9114</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -8322,12 +8321,12 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>GIAM (TO)</t>
+          <t>Log/Envio de Inconsistência (Mensal)</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
       <c r="L75" s="1" t="n">
-        <v>46212</v>
+        <v>46218</v>
       </c>
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr">
@@ -8336,7 +8335,7 @@
         </is>
       </c>
       <c r="O75" t="n">
-        <v>18076580</v>
+        <v>17399338</v>
       </c>
       <c r="P75" t="inlineStr">
         <is>
@@ -8350,11 +8349,11 @@
       </c>
       <c r="R75" t="inlineStr"/>
       <c r="S75" t="n">
-        <v>-2</v>
+        <v>-8</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>NOSSO NOVO SUPERMERCADO</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -8364,7 +8363,7 @@
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>Atraso do Cliente, cobrança ativa, GC e GM ciente do atraso - Data Comentário: 06/07/2026 15:55</t>
+          <t>Log de Inconsistências anexado via sistema - \\SRVMGC\DADOS\GOIAS\2026\5417 - COMERCIAL DE ALIMENTOS\EF - VAREJO\CONTROLE MENSAL\06 - JUNHO\ACESSÓRIA\INCONSISTENCIA\\5417-06-2026 Mensal 06-07-2026 141701.xlsx - Data Comentário: 06/07/2026 14:16</t>
         </is>
       </c>
       <c r="W75" t="inlineStr"/>
@@ -8391,11 +8390,11 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>5417</v>
+        <v>5617</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -8415,7 +8414,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -8445,7 +8444,7 @@
         </is>
       </c>
       <c r="O76" t="n">
-        <v>17399338</v>
+        <v>18120594</v>
       </c>
       <c r="P76" t="inlineStr">
         <is>
@@ -8463,7 +8462,7 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -8471,11 +8470,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V76" t="inlineStr">
-        <is>
-          <t>Log de Inconsistências anexado via sistema - \\SRVMGC\DADOS\GOIAS\2026\5417 - COMERCIAL DE ALIMENTOS\EF - VAREJO\CONTROLE MENSAL\06 - JUNHO\ACESSÓRIA\INCONSISTENCIA\\5417-06-2026 Mensal 06-07-2026 141701.xlsx - Data Comentário: 06/07/2026 14:16</t>
-        </is>
-      </c>
+      <c r="V76" t="inlineStr"/>
       <c r="W76" t="inlineStr"/>
       <c r="X76" t="inlineStr"/>
       <c r="Y76" t="inlineStr"/>
@@ -8528,10 +8523,10 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>7884</v>
+        <v>1793</v>
       </c>
       <c r="H77" t="n">
-        <v>9114</v>
+        <v>0</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -8540,21 +8535,25 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Log/Envio de Inconsistência (Mensal)</t>
+          <t>Mun - ISS Serv. Tomados</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
       <c r="L77" s="1" t="n">
-        <v>46218</v>
-      </c>
-      <c r="M77" t="inlineStr"/>
+        <v>46213</v>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
       <c r="N77" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O77" t="n">
-        <v>18120594</v>
+        <v>17407569</v>
       </c>
       <c r="P77" t="inlineStr">
         <is>
@@ -8568,7 +8567,7 @@
       </c>
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="n">
-        <v>-8</v>
+        <v>-3</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8580,7 +8579,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V77" t="inlineStr"/>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 08/07/2026 - Data Comentário: 06/07/2026 15:51</t>
+        </is>
+      </c>
       <c r="W77" t="inlineStr"/>
       <c r="X77" t="inlineStr"/>
       <c r="Y77" t="inlineStr"/>
@@ -8594,7 +8597,7 @@
       <c r="AE77" t="inlineStr"/>
       <c r="AF77" t="inlineStr">
         <is>
-          <t>Tarefa</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="AG77" t="inlineStr">
@@ -8605,11 +8608,11 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>5617</v>
+        <v>6224</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -8629,7 +8632,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -8663,7 +8666,7 @@
         </is>
       </c>
       <c r="O78" t="n">
-        <v>17407569</v>
+        <v>17688661</v>
       </c>
       <c r="P78" t="inlineStr">
         <is>
@@ -8718,11 +8721,11 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>6224</v>
+        <v>6278</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>EMPORIO DOS FRIOS LTDA</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -8732,7 +8735,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Real - Anual</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -8742,7 +8745,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -8776,7 +8779,7 @@
         </is>
       </c>
       <c r="O79" t="n">
-        <v>17688661</v>
+        <v>17148664</v>
       </c>
       <c r="P79" t="inlineStr">
         <is>
@@ -8794,7 +8797,7 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
@@ -8831,11 +8834,11 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>6278</v>
+        <v>6279</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS LTDA</t>
+          <t>DIENNYFER DA S PEREIRA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -8845,7 +8848,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Federal - Lucro Real - Anual</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -8855,7 +8858,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -8889,7 +8892,7 @@
         </is>
       </c>
       <c r="O80" t="n">
-        <v>17148664</v>
+        <v>17070843</v>
       </c>
       <c r="P80" t="inlineStr">
         <is>
@@ -8944,11 +8947,11 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>6279</v>
+        <v>6486</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>DIENNYFER DA S PEREIRA</t>
+          <t>PC GAMER GOIANIA LTDA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -8958,7 +8961,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -8968,7 +8971,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -9002,7 +9005,7 @@
         </is>
       </c>
       <c r="O81" t="n">
-        <v>17070843</v>
+        <v>16975950</v>
       </c>
       <c r="P81" t="inlineStr">
         <is>
@@ -9020,7 +9023,7 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>PC GAMER</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
@@ -9057,11 +9060,11 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>6486</v>
+        <v>6704</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>PC GAMER GOIANIA LTDA</t>
+          <t>TECNO COM INFORMATICA LTDA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -9115,7 +9118,7 @@
         </is>
       </c>
       <c r="O82" t="n">
-        <v>16975950</v>
+        <v>18085152</v>
       </c>
       <c r="P82" t="inlineStr">
         <is>
@@ -9133,7 +9136,7 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>PC GAMER</t>
+          <t>TECNO COM</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
@@ -9170,11 +9173,11 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>6704</v>
+        <v>6705</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>TECNO COM INFORMATICA LTDA</t>
+          <t>NARCIZO ALVES CORDEIRO</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -9184,7 +9187,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -9228,7 +9231,7 @@
         </is>
       </c>
       <c r="O83" t="n">
-        <v>18085152</v>
+        <v>17948926</v>
       </c>
       <c r="P83" t="inlineStr">
         <is>
@@ -9283,11 +9286,11 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>6705</v>
+        <v>6779</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>NARCIZO ALVES CORDEIRO</t>
+          <t>CORDEIRO E CIA LTDA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -9341,7 +9344,7 @@
         </is>
       </c>
       <c r="O84" t="n">
-        <v>17948926</v>
+        <v>18084953</v>
       </c>
       <c r="P84" t="inlineStr">
         <is>
@@ -9362,11 +9365,7 @@
           <t>TECNO COM</t>
         </is>
       </c>
-      <c r="U84" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+      <c r="U84" t="inlineStr"/>
       <c r="V84" t="inlineStr">
         <is>
           <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 08/07/2026 - Data Comentário: 06/07/2026 15:51</t>
@@ -9396,11 +9395,11 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>6779</v>
+        <v>6885</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>CORDEIRO E CIA LTDA</t>
+          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -9454,7 +9453,7 @@
         </is>
       </c>
       <c r="O85" t="n">
-        <v>18084953</v>
+        <v>18134033</v>
       </c>
       <c r="P85" t="inlineStr">
         <is>
@@ -9472,7 +9471,7 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U85" t="inlineStr"/>
@@ -9505,11 +9504,11 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>6885</v>
+        <v>6703</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
+          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -9519,7 +9518,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -9533,7 +9532,7 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>1793</v>
+        <v>1796</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -9545,12 +9544,12 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Mun - ISS Serv. Tomados</t>
+          <t>Produtor Rural</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
       <c r="L86" s="1" t="n">
-        <v>46213</v>
+        <v>46211</v>
       </c>
       <c r="M86" t="inlineStr">
         <is>
@@ -9563,7 +9562,7 @@
         </is>
       </c>
       <c r="O86" t="n">
-        <v>18134033</v>
+        <v>18073096</v>
       </c>
       <c r="P86" t="inlineStr">
         <is>
@@ -9577,17 +9576,21 @@
       </c>
       <c r="R86" t="inlineStr"/>
       <c r="S86" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
-        </is>
-      </c>
-      <c r="U86" t="inlineStr"/>
+          <t>LIMA MOTA</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V86" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 08/07/2026 - Data Comentário: 06/07/2026 15:51</t>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 08/07/2026 - Data Comentário: 06/07/2026 14:49</t>
         </is>
       </c>
       <c r="W86" t="inlineStr"/>
@@ -9603,7 +9606,7 @@
       <c r="AE86" t="inlineStr"/>
       <c r="AF86" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Tarefa</t>
         </is>
       </c>
       <c r="AG86" t="inlineStr">
@@ -9614,11 +9617,11 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>6703</v>
+        <v>6705</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
+          <t>NARCIZO ALVES CORDEIRO</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -9628,7 +9631,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -9642,10 +9645,10 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>1796</v>
+        <v>6884</v>
       </c>
       <c r="H87" t="n">
-        <v>0</v>
+        <v>1788</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -9654,7 +9657,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Produtor Rural</t>
+          <t>Recebimento de NF Serviços Tomados</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -9672,7 +9675,7 @@
         </is>
       </c>
       <c r="O87" t="n">
-        <v>18073096</v>
+        <v>17949037</v>
       </c>
       <c r="P87" t="inlineStr">
         <is>
@@ -9690,7 +9693,7 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>LIMA MOTA</t>
+          <t>TECNO COM</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
@@ -9700,7 +9703,7 @@
       </c>
       <c r="V87" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 08/07/2026 - Data Comentário: 06/07/2026 14:49</t>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 08/07/2026 - Data Comentário: 06/07/2026 15:52</t>
         </is>
       </c>
       <c r="W87" t="inlineStr"/>
@@ -9755,7 +9758,7 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>6884</v>
+        <v>6294</v>
       </c>
       <c r="H88" t="n">
         <v>1788</v>
@@ -9767,25 +9770,21 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Recebimento de NF Serviços Tomados</t>
+          <t>Recebimento NFCE</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
       <c r="L88" s="1" t="n">
-        <v>46211</v>
-      </c>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>08/07/2026</t>
-        </is>
-      </c>
+        <v>46216</v>
+      </c>
+      <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O88" t="n">
-        <v>17949037</v>
+        <v>17948997</v>
       </c>
       <c r="P88" t="inlineStr">
         <is>
@@ -9799,7 +9798,7 @@
       </c>
       <c r="R88" t="inlineStr"/>
       <c r="S88" t="n">
-        <v>-1</v>
+        <v>-6</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9811,11 +9810,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V88" t="inlineStr">
-        <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 08/07/2026 - Data Comentário: 06/07/2026 15:52</t>
-        </is>
-      </c>
+      <c r="V88" t="inlineStr"/>
       <c r="W88" t="inlineStr"/>
       <c r="X88" t="inlineStr"/>
       <c r="Y88" t="inlineStr"/>
@@ -9840,11 +9835,11 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>6705</v>
+        <v>5617</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>NARCIZO ALVES CORDEIRO</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -9854,7 +9849,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -9868,10 +9863,10 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>6294</v>
+        <v>11303</v>
       </c>
       <c r="H89" t="n">
-        <v>1788</v>
+        <v>0</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -9880,12 +9875,12 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Recebimento NFCE</t>
+          <t>Retorno do Check-List Fiscal</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
       <c r="L89" s="1" t="n">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr">
@@ -9894,7 +9889,7 @@
         </is>
       </c>
       <c r="O89" t="n">
-        <v>17948997</v>
+        <v>17407963</v>
       </c>
       <c r="P89" t="inlineStr">
         <is>
@@ -9908,11 +9903,11 @@
       </c>
       <c r="R89" t="inlineStr"/>
       <c r="S89" t="n">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
@@ -9945,11 +9940,11 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>5617</v>
+        <v>6885</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -9959,7 +9954,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -9999,7 +9994,7 @@
         </is>
       </c>
       <c r="O90" t="n">
-        <v>17407963</v>
+        <v>18134169</v>
       </c>
       <c r="P90" t="inlineStr">
         <is>
@@ -10017,14 +10012,10 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
-        </is>
-      </c>
-      <c r="U90" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>EMPORIO DOS FRIOS</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr"/>
       <c r="V90" t="inlineStr"/>
       <c r="W90" t="inlineStr"/>
       <c r="X90" t="inlineStr"/>
@@ -10050,11 +10041,11 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>6885</v>
+        <v>6703</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
+          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -10064,7 +10055,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -10078,24 +10069,24 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>11303</v>
+        <v>950</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Retorno do Check-List Fiscal</t>
+          <t>Confirm Rec - ISS Prestados</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
       <c r="L91" s="1" t="n">
-        <v>46218</v>
+        <v>46213</v>
       </c>
       <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr">
@@ -10104,11 +10095,11 @@
         </is>
       </c>
       <c r="O91" t="n">
-        <v>18134169</v>
+        <v>17941144</v>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Cristina Leite</t>
+          <t>Victoria Virgens</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
@@ -10118,15 +10109,23 @@
       </c>
       <c r="R91" t="inlineStr"/>
       <c r="S91" t="n">
-        <v>-8</v>
+        <v>-3</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
-        </is>
-      </c>
-      <c r="U91" t="inlineStr"/>
-      <c r="V91" t="inlineStr"/>
+          <t>LIMA MOTA</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1792] sendo a ultima baixa feita [1792]-06/07/2026 17:54:38.. - Data Comentário: 06/07/2026 17:53</t>
+        </is>
+      </c>
       <c r="W91" t="inlineStr"/>
       <c r="X91" t="inlineStr"/>
       <c r="Y91" t="inlineStr"/>
@@ -10140,22 +10139,18 @@
       <c r="AE91" t="inlineStr"/>
       <c r="AF91" t="inlineStr">
         <is>
-          <t>Tarefa</t>
-        </is>
-      </c>
-      <c r="AG91" t="inlineStr">
-        <is>
-          <t>Ricardo Fischer</t>
-        </is>
-      </c>
+          <t>Imposto</t>
+        </is>
+      </c>
+      <c r="AG91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>6703</v>
+        <v>6704</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
+          <t>TECNO COM INFORMATICA LTDA</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -10165,7 +10160,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -10205,7 +10200,7 @@
         </is>
       </c>
       <c r="O92" t="n">
-        <v>17941144</v>
+        <v>17952338</v>
       </c>
       <c r="P92" t="inlineStr">
         <is>
@@ -10223,7 +10218,7 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>LIMA MOTA</t>
+          <t>TECNO COM</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
@@ -10233,7 +10228,7 @@
       </c>
       <c r="V92" t="inlineStr">
         <is>
-          <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1792] sendo a ultima baixa feita [1792]-06/07/2026 17:54:38.. - Data Comentário: 06/07/2026 17:53</t>
+          <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1792] sendo a ultima baixa feita [1792]-06/07/2026 14:56:57.. - Data Comentário: 06/07/2026 14:56</t>
         </is>
       </c>
       <c r="W92" t="inlineStr"/>
@@ -10256,11 +10251,11 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>6704</v>
+        <v>6628</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>TECNO COM INFORMATICA LTDA</t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -10270,12 +10265,12 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -10284,7 +10279,7 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
@@ -10296,7 +10291,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Confirm Rec - ISS Prestados</t>
+          <t>Confirm Rec - ISS Tomados</t>
         </is>
       </c>
       <c r="K93" t="inlineStr"/>
@@ -10310,7 +10305,7 @@
         </is>
       </c>
       <c r="O93" t="n">
-        <v>17952338</v>
+        <v>16959948</v>
       </c>
       <c r="P93" t="inlineStr">
         <is>
@@ -10328,7 +10323,7 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t xml:space="preserve">GTG </t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
@@ -10336,11 +10331,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V93" t="inlineStr">
-        <is>
-          <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1792] sendo a ultima baixa feita [1792]-06/07/2026 14:56:57.. - Data Comentário: 06/07/2026 14:56</t>
-        </is>
-      </c>
+      <c r="V93" t="inlineStr"/>
       <c r="W93" t="inlineStr"/>
       <c r="X93" t="inlineStr"/>
       <c r="Y93" t="inlineStr"/>
@@ -10361,11 +10352,11 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>6628</v>
+        <v>6703</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -10375,12 +10366,12 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -10415,7 +10406,7 @@
         </is>
       </c>
       <c r="O94" t="n">
-        <v>16959948</v>
+        <v>17941154</v>
       </c>
       <c r="P94" t="inlineStr">
         <is>
@@ -10433,7 +10424,7 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
+          <t>LIMA MOTA</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
@@ -10441,7 +10432,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V94" t="inlineStr"/>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1793] sendo a ultima baixa feita [1793]-03/07/2026 12:03:31.. - Data Comentário: 03/07/2026 12:02</t>
+        </is>
+      </c>
       <c r="W94" t="inlineStr"/>
       <c r="X94" t="inlineStr"/>
       <c r="Y94" t="inlineStr"/>
@@ -10462,11 +10457,11 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>6703</v>
+        <v>6945</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
+          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -10476,12 +10471,12 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -10516,7 +10511,7 @@
         </is>
       </c>
       <c r="O95" t="n">
-        <v>17941154</v>
+        <v>18164499</v>
       </c>
       <c r="P95" t="inlineStr">
         <is>
@@ -10534,19 +10529,11 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>LIMA MOTA</t>
-        </is>
-      </c>
-      <c r="U95" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="V95" t="inlineStr">
-        <is>
-          <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1793] sendo a ultima baixa feita [1793]-03/07/2026 12:03:31.. - Data Comentário: 03/07/2026 12:02</t>
-        </is>
-      </c>
+          <t>BRASIL DISTRIBUIDORA</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr"/>
+      <c r="V95" t="inlineStr"/>
       <c r="W95" t="inlineStr"/>
       <c r="X95" t="inlineStr"/>
       <c r="Y95" t="inlineStr"/>
@@ -10567,11 +10554,11 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>6945</v>
+        <v>6278</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
+          <t>EMPORIO DOS FRIOS LTDA</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -10581,12 +10568,12 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - Lucro Real - Anual</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -10595,19 +10582,19 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>951</v>
+        <v>6017</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Confirm Rec - ISS Tomados</t>
+          <t>Cobrança de inventário SPED ICMS</t>
         </is>
       </c>
       <c r="K96" t="inlineStr"/>
@@ -10621,11 +10608,11 @@
         </is>
       </c>
       <c r="O96" t="n">
-        <v>18164499</v>
+        <v>17539760</v>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Victoria Virgens</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
@@ -10639,10 +10626,14 @@
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA</t>
-        </is>
-      </c>
-      <c r="U96" t="inlineStr"/>
+          <t>EMPORIO DOS FRIOS</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V96" t="inlineStr"/>
       <c r="W96" t="inlineStr"/>
       <c r="X96" t="inlineStr"/>
@@ -10657,18 +10648,18 @@
       <c r="AE96" t="inlineStr"/>
       <c r="AF96" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Tarefa</t>
         </is>
       </c>
       <c r="AG96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>6278</v>
+        <v>6404</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS LTDA</t>
+          <t>SOLAR INVESTIMENTOS LTDA</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -10678,7 +10669,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Federal - Lucro Real - Anual</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -10718,11 +10709,11 @@
         </is>
       </c>
       <c r="O97" t="n">
-        <v>17539760</v>
+        <v>16962256</v>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr">
@@ -10736,7 +10727,7 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>SOLAR INVESTIMENTOS</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
@@ -10765,11 +10756,11 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>6404</v>
+        <v>6627</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS LTDA</t>
+          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -10779,12 +10770,12 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -10819,11 +10810,11 @@
         </is>
       </c>
       <c r="O98" t="n">
-        <v>16962256</v>
+        <v>17042432</v>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
@@ -10837,7 +10828,7 @@
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS</t>
+          <t xml:space="preserve">GTG </t>
         </is>
       </c>
       <c r="U98" t="inlineStr">
@@ -10866,11 +10857,11 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>6627</v>
+        <v>6704</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
+          <t>TECNO COM INFORMATICA LTDA</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -10885,7 +10876,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -10920,7 +10911,7 @@
         </is>
       </c>
       <c r="O99" t="n">
-        <v>17042432</v>
+        <v>17952390</v>
       </c>
       <c r="P99" t="inlineStr">
         <is>
@@ -10938,7 +10929,7 @@
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
+          <t>TECNO COM</t>
         </is>
       </c>
       <c r="U99" t="inlineStr">
@@ -10967,11 +10958,11 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>6704</v>
+        <v>6885</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>TECNO COM INFORMATICA LTDA</t>
+          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -10981,7 +10972,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -11021,7 +11012,7 @@
         </is>
       </c>
       <c r="O100" t="n">
-        <v>17952390</v>
+        <v>18128767</v>
       </c>
       <c r="P100" t="inlineStr">
         <is>
@@ -11039,14 +11030,10 @@
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
-        </is>
-      </c>
-      <c r="U100" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>EMPORIO DOS FRIOS</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr"/>
       <c r="V100" t="inlineStr"/>
       <c r="W100" t="inlineStr"/>
       <c r="X100" t="inlineStr"/>
@@ -11068,11 +11055,11 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>6885</v>
+        <v>6949</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
+          <t>TEC GRUA LOCAÇÃO E COMERCIO DE EQUIPAMENTOS PARA CONSTRUÇÃO LTDA</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -11082,7 +11069,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -11092,11 +11079,11 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Reynaldo Santos</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>6017</v>
+        <v>6215</v>
       </c>
       <c r="H101" t="n">
         <v>0</v>
@@ -11108,21 +11095,21 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Cobrança de inventário SPED ICMS</t>
+          <t>DEC - Conferência 1º Quinzena</t>
         </is>
       </c>
       <c r="K101" t="inlineStr"/>
       <c r="L101" s="1" t="n">
-        <v>46213</v>
+        <v>46210</v>
       </c>
       <c r="M101" t="inlineStr"/>
       <c r="N101" t="inlineStr">
         <is>
-          <t>06/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
       <c r="O101" t="n">
-        <v>18128767</v>
+        <v>18178161</v>
       </c>
       <c r="P101" t="inlineStr">
         <is>
@@ -11136,11 +11123,11 @@
       </c>
       <c r="R101" t="inlineStr"/>
       <c r="S101" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>TEC GRUA</t>
         </is>
       </c>
       <c r="U101" t="inlineStr"/>
@@ -11158,18 +11145,18 @@
       <c r="AE101" t="inlineStr"/>
       <c r="AF101" t="inlineStr">
         <is>
-          <t>Tarefa</t>
+          <t>Obrigação Acessória</t>
         </is>
       </c>
       <c r="AG101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>6949</v>
+        <v>6962</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>TEC GRUA LOCAÇÃO E COMERCIO DE EQUIPAMENTOS PARA CONSTRUÇÃO LTDA</t>
+          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -11219,11 +11206,11 @@
         </is>
       </c>
       <c r="O102" t="n">
-        <v>18178161</v>
+        <v>18188744</v>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
@@ -11237,7 +11224,7 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>TEC GRUA</t>
+          <t>PROMOTORAS GYN</t>
         </is>
       </c>
       <c r="U102" t="inlineStr"/>
@@ -11262,11 +11249,11 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
+          <t>PROMOTORAS GYN LTDA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -11316,7 +11303,7 @@
         </is>
       </c>
       <c r="O103" t="n">
-        <v>18188744</v>
+        <v>18188650</v>
       </c>
       <c r="P103" t="inlineStr">
         <is>
@@ -11359,11 +11346,11 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>6963</v>
+        <v>5417</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN LTDA</t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -11383,11 +11370,11 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G104" t="n">
-        <v>6215</v>
+        <v>11746</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -11399,25 +11386,25 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>DEC - Conferência 1º Quinzena</t>
+          <t>Distribuição de Lucro Mensal</t>
         </is>
       </c>
       <c r="K104" t="inlineStr"/>
       <c r="L104" s="1" t="n">
-        <v>46210</v>
+        <v>46213</v>
       </c>
       <c r="M104" t="inlineStr"/>
       <c r="N104" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
       <c r="O104" t="n">
-        <v>18188650</v>
+        <v>17994309</v>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
@@ -11427,14 +11414,18 @@
       </c>
       <c r="R104" t="inlineStr"/>
       <c r="S104" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN</t>
-        </is>
-      </c>
-      <c r="U104" t="inlineStr"/>
+          <t>NOSSO NOVO SUPERMERCADO</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V104" t="inlineStr"/>
       <c r="W104" t="inlineStr"/>
       <c r="X104" t="inlineStr"/>
@@ -11449,18 +11440,18 @@
       <c r="AE104" t="inlineStr"/>
       <c r="AF104" t="inlineStr">
         <is>
-          <t>Obrigação Acessória</t>
+          <t>Tarefa</t>
         </is>
       </c>
       <c r="AG104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>5417</v>
+        <v>5617</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -11480,7 +11471,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -11510,7 +11501,7 @@
         </is>
       </c>
       <c r="O105" t="n">
-        <v>17994309</v>
+        <v>18001695</v>
       </c>
       <c r="P105" t="inlineStr">
         <is>
@@ -11528,7 +11519,7 @@
       </c>
       <c r="T105" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U105" t="inlineStr">
@@ -11557,11 +11548,11 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>5617</v>
+        <v>6224</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -11581,7 +11572,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -11611,11 +11602,11 @@
         </is>
       </c>
       <c r="O106" t="n">
-        <v>18001695</v>
+        <v>18004470</v>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
@@ -11658,11 +11649,11 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>6224</v>
+        <v>6278</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>EMPORIO DOS FRIOS LTDA</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -11672,7 +11663,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Real - Anual</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -11682,7 +11673,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -11712,11 +11703,11 @@
         </is>
       </c>
       <c r="O107" t="n">
-        <v>18004470</v>
+        <v>17994320</v>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="Q107" t="inlineStr">
@@ -11730,7 +11721,7 @@
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U107" t="inlineStr">
@@ -11759,11 +11750,11 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>6278</v>
+        <v>6279</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS LTDA</t>
+          <t>DIENNYFER DA S PEREIRA</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -11773,7 +11764,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Federal - Lucro Real - Anual</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -11783,7 +11774,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -11813,7 +11804,7 @@
         </is>
       </c>
       <c r="O108" t="n">
-        <v>17994320</v>
+        <v>17995240</v>
       </c>
       <c r="P108" t="inlineStr">
         <is>
@@ -11860,11 +11851,11 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>6279</v>
+        <v>6404</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>DIENNYFER DA S PEREIRA</t>
+          <t>SOLAR INVESTIMENTOS LTDA</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -11884,7 +11875,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -11914,11 +11905,11 @@
         </is>
       </c>
       <c r="O109" t="n">
-        <v>17995240</v>
+        <v>17994673</v>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="Q109" t="inlineStr">
@@ -11932,7 +11923,7 @@
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>SOLAR INVESTIMENTOS</t>
         </is>
       </c>
       <c r="U109" t="inlineStr">
@@ -11961,11 +11952,11 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>6404</v>
+        <v>6486</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS LTDA</t>
+          <t>PC GAMER GOIANIA LTDA</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -11975,7 +11966,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -12015,7 +12006,7 @@
         </is>
       </c>
       <c r="O110" t="n">
-        <v>17994673</v>
+        <v>17994807</v>
       </c>
       <c r="P110" t="inlineStr">
         <is>
@@ -12033,7 +12024,7 @@
       </c>
       <c r="T110" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS</t>
+          <t>PC GAMER</t>
         </is>
       </c>
       <c r="U110" t="inlineStr">
@@ -12062,11 +12053,11 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>6486</v>
+        <v>6548</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>PC GAMER GOIANIA LTDA</t>
+          <t>GOIAS SILAGEM LTDA</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -12116,11 +12107,11 @@
         </is>
       </c>
       <c r="O111" t="n">
-        <v>17994807</v>
+        <v>18006049</v>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr">
@@ -12134,7 +12125,7 @@
       </c>
       <c r="T111" t="inlineStr">
         <is>
-          <t>PC GAMER</t>
+          <t>GOIAS SILAGEM</t>
         </is>
       </c>
       <c r="U111" t="inlineStr">
@@ -12163,11 +12154,11 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>6548</v>
+        <v>6628</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM LTDA</t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -12177,12 +12168,12 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -12217,7 +12208,7 @@
         </is>
       </c>
       <c r="O112" t="n">
-        <v>18006049</v>
+        <v>18003254</v>
       </c>
       <c r="P112" t="inlineStr">
         <is>
@@ -12235,7 +12226,7 @@
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM</t>
+          <t xml:space="preserve">GTG </t>
         </is>
       </c>
       <c r="U112" t="inlineStr">
@@ -12264,11 +12255,11 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>6628</v>
+        <v>6703</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -12278,12 +12269,12 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -12318,7 +12309,7 @@
         </is>
       </c>
       <c r="O113" t="n">
-        <v>18003254</v>
+        <v>18004015</v>
       </c>
       <c r="P113" t="inlineStr">
         <is>
@@ -12336,7 +12327,7 @@
       </c>
       <c r="T113" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
+          <t>LIMA MOTA</t>
         </is>
       </c>
       <c r="U113" t="inlineStr">
@@ -12365,11 +12356,11 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>6703</v>
+        <v>6704</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
+          <t>TECNO COM INFORMATICA LTDA</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -12379,7 +12370,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -12419,7 +12410,7 @@
         </is>
       </c>
       <c r="O114" t="n">
-        <v>18004015</v>
+        <v>17995162</v>
       </c>
       <c r="P114" t="inlineStr">
         <is>
@@ -12437,7 +12428,7 @@
       </c>
       <c r="T114" t="inlineStr">
         <is>
-          <t>LIMA MOTA</t>
+          <t>TECNO COM</t>
         </is>
       </c>
       <c r="U114" t="inlineStr">
@@ -12466,11 +12457,11 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>6704</v>
+        <v>6705</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>TECNO COM INFORMATICA LTDA</t>
+          <t>NARCIZO ALVES CORDEIRO</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -12480,7 +12471,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -12520,7 +12511,7 @@
         </is>
       </c>
       <c r="O115" t="n">
-        <v>17995162</v>
+        <v>18004026</v>
       </c>
       <c r="P115" t="inlineStr">
         <is>
@@ -12567,11 +12558,11 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>6705</v>
+        <v>6949</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>NARCIZO ALVES CORDEIRO</t>
+          <t>TEC GRUA LOCAÇÃO E COMERCIO DE EQUIPAMENTOS PARA CONSTRUÇÃO LTDA</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -12581,7 +12572,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -12591,70 +12582,77 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Reynaldo Santos</t>
         </is>
       </c>
       <c r="G116" t="n">
-        <v>11746</v>
+        <v>11615</v>
       </c>
       <c r="H116" t="n">
         <v>0</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Distribuição de Lucro Mensal</t>
+          <t>Envio de ATA de Implantação - CTB I</t>
         </is>
       </c>
       <c r="K116" t="inlineStr"/>
       <c r="L116" s="1" t="n">
-        <v>46213</v>
-      </c>
-      <c r="M116" t="inlineStr"/>
+        <v>46206</v>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
       <c r="N116" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O116" t="n">
-        <v>18004026</v>
-      </c>
-      <c r="P116" t="inlineStr">
-        <is>
-          <t>Sergio Fernandes</t>
-        </is>
-      </c>
+        <v>18166586</v>
+      </c>
+      <c r="P116" t="inlineStr"/>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>Em Aberto</t>
-        </is>
-      </c>
-      <c r="R116" t="inlineStr"/>
+          <t>Baixado</t>
+        </is>
+      </c>
+      <c r="R116" s="1" t="n">
+        <v>46206.43215109954</v>
+      </c>
       <c r="S116" t="n">
-        <v>-3</v>
+        <v>4</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
-        </is>
-      </c>
-      <c r="U116" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="V116" t="inlineStr"/>
+          <t>TEC GRUA</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr"/>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 26/06/2026 
+Aguardando agendamento das implantações - Data Comentário: 18/06/2026 17:44</t>
+        </is>
+      </c>
       <c r="W116" t="inlineStr"/>
       <c r="X116" t="inlineStr"/>
       <c r="Y116" t="inlineStr"/>
       <c r="Z116" t="n">
         <v>0</v>
       </c>
-      <c r="AA116" t="inlineStr"/>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>Erika Santana</t>
+        </is>
+      </c>
       <c r="AB116" t="inlineStr"/>
       <c r="AC116" t="inlineStr"/>
       <c r="AD116" t="inlineStr"/>
@@ -12668,11 +12666,11 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>6949</v>
+        <v>6962</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>TEC GRUA LOCAÇÃO E COMERCIO DE EQUIPAMENTOS PARA CONSTRUÇÃO LTDA</t>
+          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -12715,18 +12713,14 @@
       <c r="L117" s="1" t="n">
         <v>46206</v>
       </c>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>26/06/2026</t>
-        </is>
-      </c>
+      <c r="M117" t="inlineStr"/>
       <c r="N117" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O117" t="n">
-        <v>18166586</v>
+        <v>18186559</v>
       </c>
       <c r="P117" t="inlineStr"/>
       <c r="Q117" t="inlineStr">
@@ -12735,21 +12729,20 @@
         </is>
       </c>
       <c r="R117" s="1" t="n">
-        <v>46206.43215109954</v>
+        <v>46206.43205978009</v>
       </c>
       <c r="S117" t="n">
         <v>4</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
-          <t>TEC GRUA</t>
+          <t>PROMOTORAS GYN</t>
         </is>
       </c>
       <c r="U117" t="inlineStr"/>
       <c r="V117" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 26/06/2026 
-Aguardando agendamento das implantações - Data Comentário: 18/06/2026 17:44</t>
+          <t>Rotina Para Criar Tarefas Dos Clientes Novos - CodCliente: 6962; Tarefa Incluida: 11615; Vencimento: 17/06/2026 00:00:00; UsuarioResponsavel: erikas - Data Comentário: 17/06/2026 11:09</t>
         </is>
       </c>
       <c r="W117" t="inlineStr"/>
@@ -12776,11 +12769,11 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
+          <t>PROMOTORAS GYN LTDA</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -12830,7 +12823,7 @@
         </is>
       </c>
       <c r="O118" t="n">
-        <v>18186559</v>
+        <v>18186560</v>
       </c>
       <c r="P118" t="inlineStr"/>
       <c r="Q118" t="inlineStr">
@@ -12839,7 +12832,7 @@
         </is>
       </c>
       <c r="R118" s="1" t="n">
-        <v>46206.43205978009</v>
+        <v>46206.43206049768</v>
       </c>
       <c r="S118" t="n">
         <v>4</v>
@@ -12852,7 +12845,7 @@
       <c r="U118" t="inlineStr"/>
       <c r="V118" t="inlineStr">
         <is>
-          <t>Rotina Para Criar Tarefas Dos Clientes Novos - CodCliente: 6962; Tarefa Incluida: 11615; Vencimento: 17/06/2026 00:00:00; UsuarioResponsavel: erikas - Data Comentário: 17/06/2026 11:09</t>
+          <t>Rotina Para Criar Tarefas Dos Clientes Novos - CodCliente: 6963; Tarefa Incluida: 11615; Vencimento: 17/06/2026 00:00:00; UsuarioResponsavel: erikas - Data Comentário: 17/06/2026 11:09</t>
         </is>
       </c>
       <c r="W118" t="inlineStr"/>
@@ -12879,11 +12872,11 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>6963</v>
+        <v>6548</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN LTDA</t>
+          <t>GOIAS SILAGEM LTDA</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -12903,11 +12896,11 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G119" t="n">
-        <v>11615</v>
+        <v>11299</v>
       </c>
       <c r="H119" t="n">
         <v>0</v>
@@ -12919,12 +12912,12 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Envio de ATA de Implantação - CTB I</t>
+          <t>Retorno do Check-List</t>
         </is>
       </c>
       <c r="K119" t="inlineStr"/>
       <c r="L119" s="1" t="n">
-        <v>46206</v>
+        <v>46218</v>
       </c>
       <c r="M119" t="inlineStr"/>
       <c r="N119" t="inlineStr">
@@ -12933,31 +12926,35 @@
         </is>
       </c>
       <c r="O119" t="n">
-        <v>18186560</v>
-      </c>
-      <c r="P119" t="inlineStr"/>
+        <v>17968039</v>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Thais Souza</t>
+        </is>
+      </c>
       <c r="Q119" t="inlineStr">
         <is>
           <t>Baixado</t>
         </is>
       </c>
       <c r="R119" s="1" t="n">
-        <v>46206.43206049768</v>
+        <v>46204.75352534722</v>
       </c>
       <c r="S119" t="n">
-        <v>4</v>
+        <v>-8</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN</t>
-        </is>
-      </c>
-      <c r="U119" t="inlineStr"/>
-      <c r="V119" t="inlineStr">
-        <is>
-          <t>Rotina Para Criar Tarefas Dos Clientes Novos - CodCliente: 6963; Tarefa Incluida: 11615; Vencimento: 17/06/2026 00:00:00; UsuarioResponsavel: erikas - Data Comentário: 17/06/2026 11:09</t>
-        </is>
-      </c>
+          <t>GOIAS SILAGEM</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr"/>
       <c r="W119" t="inlineStr"/>
       <c r="X119" t="inlineStr"/>
       <c r="Y119" t="inlineStr"/>
@@ -12966,7 +12963,7 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>Erika Santana</t>
+          <t>Juan Rodrigues</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr"/>
@@ -12978,15 +12975,19 @@
           <t>Tarefa</t>
         </is>
       </c>
-      <c r="AG119" t="inlineStr"/>
+      <c r="AG119" t="inlineStr">
+        <is>
+          <t>Erika Santana</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM LTDA</t>
+          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -13001,7 +13002,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -13036,11 +13037,11 @@
         </is>
       </c>
       <c r="O120" t="n">
-        <v>17968039</v>
+        <v>17042639</v>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Thais Souza</t>
+          <t>Nathalia Lourenco</t>
         </is>
       </c>
       <c r="Q120" t="inlineStr">
@@ -13049,14 +13050,14 @@
         </is>
       </c>
       <c r="R120" s="1" t="n">
-        <v>46204.75352534722</v>
+        <v>46204.75352809028</v>
       </c>
       <c r="S120" t="n">
         <v>-8</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM</t>
+          <t xml:space="preserve">GTG </t>
         </is>
       </c>
       <c r="U120" t="inlineStr">
@@ -13087,17 +13088,17 @@
       </c>
       <c r="AG120" t="inlineStr">
         <is>
-          <t>Erika Santana</t>
+          <t>Isabella Nascimento</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -13107,7 +13108,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -13147,7 +13148,7 @@
         </is>
       </c>
       <c r="O121" t="n">
-        <v>17042639</v>
+        <v>16960108</v>
       </c>
       <c r="P121" t="inlineStr">
         <is>
@@ -13160,7 +13161,7 @@
         </is>
       </c>
       <c r="R121" s="1" t="n">
-        <v>46204.75352809028</v>
+        <v>46204.7535284375</v>
       </c>
       <c r="S121" t="n">
         <v>-8</v>
@@ -13204,11 +13205,11 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>6628</v>
+        <v>6945</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -13258,11 +13259,11 @@
         </is>
       </c>
       <c r="O122" t="n">
-        <v>16960108</v>
+        <v>18163697</v>
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Nathalia Lourenco</t>
+          <t>Laisa Rocha</t>
         </is>
       </c>
       <c r="Q122" t="inlineStr">
@@ -13271,21 +13272,17 @@
         </is>
       </c>
       <c r="R122" s="1" t="n">
-        <v>46204.7535284375</v>
+        <v>46204.7535334838</v>
       </c>
       <c r="S122" t="n">
         <v>-8</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
-        </is>
-      </c>
-      <c r="U122" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>BRASIL DISTRIBUIDORA</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr"/>
       <c r="V122" t="inlineStr"/>
       <c r="W122" t="inlineStr"/>
       <c r="X122" t="inlineStr"/>
@@ -13315,11 +13312,11 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>6945</v>
+        <v>6962</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
+          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -13329,17 +13326,17 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Reynaldo Santos</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -13369,11 +13366,11 @@
         </is>
       </c>
       <c r="O123" t="n">
-        <v>18163697</v>
+        <v>18187976</v>
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Laisa Rocha</t>
+          <t>Mirian Lima</t>
         </is>
       </c>
       <c r="Q123" t="inlineStr">
@@ -13382,14 +13379,14 @@
         </is>
       </c>
       <c r="R123" s="1" t="n">
-        <v>46204.7535334838</v>
+        <v>46204.75353387732</v>
       </c>
       <c r="S123" t="n">
         <v>-8</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA</t>
+          <t>PROMOTORAS GYN</t>
         </is>
       </c>
       <c r="U123" t="inlineStr"/>
@@ -13422,11 +13419,11 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
+          <t>PROMOTORAS GYN LTDA</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -13476,7 +13473,7 @@
         </is>
       </c>
       <c r="O124" t="n">
-        <v>18187976</v>
+        <v>18187914</v>
       </c>
       <c r="P124" t="inlineStr">
         <is>
@@ -13489,7 +13486,7 @@
         </is>
       </c>
       <c r="R124" s="1" t="n">
-        <v>46204.75353387732</v>
+        <v>46204.75353515046</v>
       </c>
       <c r="S124" t="n">
         <v>-8</v>
@@ -13529,11 +13526,11 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>6963</v>
+        <v>5417</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN LTDA</t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -13553,18 +13550,18 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G125" t="n">
-        <v>11299</v>
+        <v>11297</v>
       </c>
       <c r="H125" t="n">
         <v>0</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL INDUSTRIA</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -13583,11 +13580,11 @@
         </is>
       </c>
       <c r="O125" t="n">
-        <v>18187914</v>
+        <v>17399442</v>
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Mirian Lima</t>
+          <t>Eveny Silva</t>
         </is>
       </c>
       <c r="Q125" t="inlineStr">
@@ -13596,17 +13593,21 @@
         </is>
       </c>
       <c r="R125" s="1" t="n">
-        <v>46204.75353515046</v>
+        <v>46204.75350494213</v>
       </c>
       <c r="S125" t="n">
         <v>-8</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN</t>
-        </is>
-      </c>
-      <c r="U125" t="inlineStr"/>
+          <t>NOSSO NOVO SUPERMERCADO</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V125" t="inlineStr"/>
       <c r="W125" t="inlineStr"/>
       <c r="X125" t="inlineStr"/>
@@ -13630,17 +13631,17 @@
       </c>
       <c r="AG125" t="inlineStr">
         <is>
-          <t>Isabella Nascimento</t>
+          <t>Karina Santos</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>5417</v>
+        <v>5617</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -13660,7 +13661,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -13690,11 +13691,11 @@
         </is>
       </c>
       <c r="O126" t="n">
-        <v>17399442</v>
+        <v>17407953</v>
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Eveny Silva</t>
+          <t>Jackson Silva</t>
         </is>
       </c>
       <c r="Q126" t="inlineStr">
@@ -13703,14 +13704,14 @@
         </is>
       </c>
       <c r="R126" s="1" t="n">
-        <v>46204.75350494213</v>
+        <v>46204.75351072917</v>
       </c>
       <c r="S126" t="n">
         <v>-8</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U126" t="inlineStr">
@@ -13741,17 +13742,17 @@
       </c>
       <c r="AG126" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>5617</v>
+        <v>6224</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -13771,7 +13772,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -13801,7 +13802,7 @@
         </is>
       </c>
       <c r="O127" t="n">
-        <v>17407953</v>
+        <v>17689061</v>
       </c>
       <c r="P127" t="inlineStr">
         <is>
@@ -13814,7 +13815,7 @@
         </is>
       </c>
       <c r="R127" s="1" t="n">
-        <v>46204.75351072917</v>
+        <v>46204.75352068287</v>
       </c>
       <c r="S127" t="n">
         <v>-8</v>
@@ -13858,11 +13859,11 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>6224</v>
+        <v>6278</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>EMPORIO DOS FRIOS LTDA</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -13872,7 +13873,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Real - Anual</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -13882,7 +13883,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -13912,11 +13913,11 @@
         </is>
       </c>
       <c r="O128" t="n">
-        <v>17689061</v>
+        <v>17539888</v>
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Jackson Silva</t>
+          <t>Isabela Lemos</t>
         </is>
       </c>
       <c r="Q128" t="inlineStr">
@@ -13925,14 +13926,14 @@
         </is>
       </c>
       <c r="R128" s="1" t="n">
-        <v>46204.75352068287</v>
+        <v>46204.75352175926</v>
       </c>
       <c r="S128" t="n">
         <v>-8</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U128" t="inlineStr">
@@ -13963,17 +13964,17 @@
       </c>
       <c r="AG128" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>6278</v>
+        <v>6704</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS LTDA</t>
+          <t>TECNO COM INFORMATICA LTDA</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -13983,7 +13984,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Federal - Lucro Real - Anual</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -14023,11 +14024,11 @@
         </is>
       </c>
       <c r="O129" t="n">
-        <v>17539888</v>
+        <v>17955432</v>
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Isabela Lemos</t>
+          <t>Paulo Silva</t>
         </is>
       </c>
       <c r="Q129" t="inlineStr">
@@ -14036,14 +14037,14 @@
         </is>
       </c>
       <c r="R129" s="1" t="n">
-        <v>46204.75352175926</v>
+        <v>46204.75353024306</v>
       </c>
       <c r="S129" t="n">
         <v>-8</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>TECNO COM</t>
         </is>
       </c>
       <c r="U129" t="inlineStr">
@@ -14080,11 +14081,11 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>6704</v>
+        <v>6705</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>TECNO COM INFORMATICA LTDA</t>
+          <t>NARCIZO ALVES CORDEIRO</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -14094,7 +14095,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -14134,7 +14135,7 @@
         </is>
       </c>
       <c r="O130" t="n">
-        <v>17955432</v>
+        <v>17955272</v>
       </c>
       <c r="P130" t="inlineStr">
         <is>
@@ -14147,7 +14148,7 @@
         </is>
       </c>
       <c r="R130" s="1" t="n">
-        <v>46204.75353024306</v>
+        <v>46204.7535309838</v>
       </c>
       <c r="S130" t="n">
         <v>-8</v>
@@ -14191,11 +14192,11 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>6705</v>
+        <v>6779</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>NARCIZO ALVES CORDEIRO</t>
+          <t>CORDEIRO E CIA LTDA</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -14245,7 +14246,7 @@
         </is>
       </c>
       <c r="O131" t="n">
-        <v>17955272</v>
+        <v>18056830</v>
       </c>
       <c r="P131" t="inlineStr">
         <is>
@@ -14258,7 +14259,7 @@
         </is>
       </c>
       <c r="R131" s="1" t="n">
-        <v>46204.7535309838</v>
+        <v>46204.75353240741</v>
       </c>
       <c r="S131" t="n">
         <v>-8</v>
@@ -14268,11 +14269,7 @@
           <t>TECNO COM</t>
         </is>
       </c>
-      <c r="U131" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+      <c r="U131" t="inlineStr"/>
       <c r="V131" t="inlineStr"/>
       <c r="W131" t="inlineStr"/>
       <c r="X131" t="inlineStr"/>
@@ -14302,11 +14299,11 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>6779</v>
+        <v>6885</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>CORDEIRO E CIA LTDA</t>
+          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -14356,11 +14353,11 @@
         </is>
       </c>
       <c r="O132" t="n">
-        <v>18056830</v>
+        <v>18128901</v>
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Paulo Silva</t>
+          <t>Isabela Lemos</t>
         </is>
       </c>
       <c r="Q132" t="inlineStr">
@@ -14369,14 +14366,14 @@
         </is>
       </c>
       <c r="R132" s="1" t="n">
-        <v>46204.75353240741</v>
+        <v>46204.75353278935</v>
       </c>
       <c r="S132" t="n">
         <v>-8</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U132" t="inlineStr"/>
@@ -14409,11 +14406,11 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>6885</v>
+        <v>6628</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -14428,7 +14425,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -14437,57 +14434,61 @@
         </is>
       </c>
       <c r="G133" t="n">
-        <v>11297</v>
+        <v>11817</v>
       </c>
       <c r="H133" t="n">
         <v>0</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>Retorno do Check-List</t>
+          <t>Alteração dados cadastrais</t>
         </is>
       </c>
       <c r="K133" t="inlineStr"/>
       <c r="L133" s="1" t="n">
-        <v>46218</v>
+        <v>46205</v>
       </c>
       <c r="M133" t="inlineStr"/>
       <c r="N133" t="inlineStr">
         <is>
-          <t>06/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
       <c r="O133" t="n">
-        <v>18128901</v>
-      </c>
-      <c r="P133" t="inlineStr">
-        <is>
-          <t>Isabela Lemos</t>
-        </is>
-      </c>
+        <v>18199226</v>
+      </c>
+      <c r="P133" t="inlineStr"/>
       <c r="Q133" t="inlineStr">
         <is>
           <t>Baixado</t>
         </is>
       </c>
       <c r="R133" s="1" t="n">
-        <v>46204.75353278935</v>
+        <v>46205.599529375</v>
       </c>
       <c r="S133" t="n">
-        <v>-8</v>
+        <v>5</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
-        </is>
-      </c>
-      <c r="U133" t="inlineStr"/>
-      <c r="V133" t="inlineStr"/>
+          <t xml:space="preserve">GTG </t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>Aplicação de promoção. - Data Comentário: 02/07/2026 11:13</t>
+        </is>
+      </c>
       <c r="W133" t="inlineStr"/>
       <c r="X133" t="inlineStr"/>
       <c r="Y133" t="inlineStr"/>
@@ -14496,7 +14497,7 @@
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>Juan Rodrigues</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr"/>
@@ -14508,19 +14509,15 @@
           <t>Tarefa</t>
         </is>
       </c>
-      <c r="AG133" t="inlineStr">
-        <is>
-          <t>Fernanda Araujo</t>
-        </is>
-      </c>
+      <c r="AG133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>6628</v>
+        <v>5417</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -14530,21 +14527,21 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G134" t="n">
-        <v>11817</v>
+        <v>11815</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -14556,12 +14553,12 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Alteração dados cadastrais</t>
+          <t>Cálculo de férias individuais</t>
         </is>
       </c>
       <c r="K134" t="inlineStr"/>
       <c r="L134" s="1" t="n">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="M134" t="inlineStr"/>
       <c r="N134" t="inlineStr">
@@ -14570,7 +14567,7 @@
         </is>
       </c>
       <c r="O134" t="n">
-        <v>18199226</v>
+        <v>18196299</v>
       </c>
       <c r="P134" t="inlineStr"/>
       <c r="Q134" t="inlineStr">
@@ -14579,14 +14576,14 @@
         </is>
       </c>
       <c r="R134" s="1" t="n">
-        <v>46205.599529375</v>
+        <v>46204.71542079861</v>
       </c>
       <c r="S134" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
+          <t>NOSSO NOVO SUPERMERCADO</t>
         </is>
       </c>
       <c r="U134" t="inlineStr">
@@ -14594,11 +14591,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V134" t="inlineStr">
-        <is>
-          <t>Aplicação de promoção. - Data Comentário: 02/07/2026 11:13</t>
-        </is>
-      </c>
+      <c r="V134" t="inlineStr"/>
       <c r="W134" t="inlineStr"/>
       <c r="X134" t="inlineStr"/>
       <c r="Y134" t="inlineStr"/>
@@ -14607,7 +14600,7 @@
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Mikael Teixeira</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr"/>
@@ -14677,7 +14670,7 @@
         </is>
       </c>
       <c r="O135" t="n">
-        <v>18196299</v>
+        <v>18196300</v>
       </c>
       <c r="P135" t="inlineStr"/>
       <c r="Q135" t="inlineStr">
@@ -14686,7 +14679,7 @@
         </is>
       </c>
       <c r="R135" s="1" t="n">
-        <v>46204.71542079861</v>
+        <v>46204.71542134259</v>
       </c>
       <c r="S135" t="n">
         <v>6</v>
@@ -14726,11 +14719,11 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>5417</v>
+        <v>6779</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>CORDEIRO E CIA LTDA</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -14740,7 +14733,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -14750,7 +14743,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -14780,7 +14773,7 @@
         </is>
       </c>
       <c r="O136" t="n">
-        <v>18196300</v>
+        <v>18195927</v>
       </c>
       <c r="P136" t="inlineStr"/>
       <c r="Q136" t="inlineStr">
@@ -14789,22 +14782,22 @@
         </is>
       </c>
       <c r="R136" s="1" t="n">
-        <v>46204.71542134259</v>
+        <v>46204.48446469908</v>
       </c>
       <c r="S136" t="n">
         <v>6</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
-        </is>
-      </c>
-      <c r="U136" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="V136" t="inlineStr"/>
+          <t>TECNO COM</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr"/>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>Férias de 02/07/2026 a 10/07/2026. - Data Comentário: 01/07/2026 11:26</t>
+        </is>
+      </c>
       <c r="W136" t="inlineStr"/>
       <c r="X136" t="inlineStr"/>
       <c r="Y136" t="inlineStr"/>
@@ -14813,7 +14806,7 @@
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>Mikael Teixeira</t>
+          <t>Kaique Souza</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr"/>
@@ -14829,11 +14822,11 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>6779</v>
+        <v>5417</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>CORDEIRO E CIA LTDA</t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -14843,7 +14836,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -14853,14 +14846,14 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G137" t="n">
-        <v>11815</v>
+        <v>5800</v>
       </c>
       <c r="H137" t="n">
-        <v>0</v>
+        <v>5776</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
@@ -14869,43 +14862,55 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>Cálculo de férias individuais</t>
+          <t>CCT Lançamento Sd.508</t>
         </is>
       </c>
       <c r="K137" t="inlineStr"/>
       <c r="L137" s="1" t="n">
-        <v>46204</v>
-      </c>
-      <c r="M137" t="inlineStr"/>
+        <v>46205</v>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
+        </is>
+      </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>00/2026</t>
         </is>
       </c>
       <c r="O137" t="n">
-        <v>18195927</v>
-      </c>
-      <c r="P137" t="inlineStr"/>
+        <v>17399013</v>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>Mikael Teixeira</t>
+        </is>
+      </c>
       <c r="Q137" t="inlineStr">
         <is>
           <t>Baixado</t>
         </is>
       </c>
       <c r="R137" s="1" t="n">
-        <v>46204.48446469908</v>
+        <v>46205.75412240741</v>
       </c>
       <c r="S137" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
-        </is>
-      </c>
-      <c r="U137" t="inlineStr"/>
+          <t>NOSSO NOVO SUPERMERCADO</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V137" t="inlineStr">
         <is>
-          <t>Férias de 02/07/2026 a 10/07/2026. - Data Comentário: 01/07/2026 11:26</t>
+          <t>2. Folha Processada aguardando OK do cliente para finalização   Previsão para conclusão dia 02/07/2026 - Data Comentário: 30/06/2026 15:03</t>
         </is>
       </c>
       <c r="W137" t="inlineStr"/>
@@ -14916,7 +14921,7 @@
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>Kaique Souza</t>
+          <t>Mikael Teixeira</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr"/>
@@ -14932,11 +14937,11 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>5417</v>
+        <v>6224</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -14956,14 +14961,14 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G138" t="n">
-        <v>5800</v>
+        <v>5859</v>
       </c>
       <c r="H138" t="n">
-        <v>5776</v>
+        <v>5786</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
@@ -14972,29 +14977,25 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>CCT Lançamento Sd.508</t>
+          <t>Contribuição Assistencial</t>
         </is>
       </c>
       <c r="K138" t="inlineStr"/>
       <c r="L138" s="1" t="n">
-        <v>46205</v>
-      </c>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>02/07/2026</t>
-        </is>
-      </c>
+        <v>46206</v>
+      </c>
+      <c r="M138" t="inlineStr"/>
       <c r="N138" t="inlineStr">
         <is>
-          <t>00/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
       <c r="O138" t="n">
-        <v>17399013</v>
+        <v>17688763</v>
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Mikael Teixeira</t>
+          <t>Tania Luz</t>
         </is>
       </c>
       <c r="Q138" t="inlineStr">
@@ -15003,14 +15004,14 @@
         </is>
       </c>
       <c r="R138" s="1" t="n">
-        <v>46205.75412240741</v>
+        <v>46205.75458568287</v>
       </c>
       <c r="S138" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U138" t="inlineStr">
@@ -15018,11 +15019,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V138" t="inlineStr">
-        <is>
-          <t>2. Folha Processada aguardando OK do cliente para finalização   Previsão para conclusão dia 02/07/2026 - Data Comentário: 30/06/2026 15:03</t>
-        </is>
-      </c>
+      <c r="V138" t="inlineStr"/>
       <c r="W138" t="inlineStr"/>
       <c r="X138" t="inlineStr"/>
       <c r="Y138" t="inlineStr"/>
@@ -15031,7 +15028,7 @@
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>Mikael Teixeira</t>
+          <t>Tania Luz</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr"/>
@@ -15040,18 +15037,22 @@
       <c r="AE138" t="inlineStr"/>
       <c r="AF138" t="inlineStr">
         <is>
-          <t>Tarefa</t>
-        </is>
-      </c>
-      <c r="AG138" t="inlineStr"/>
+          <t>Imposto</t>
+        </is>
+      </c>
+      <c r="AG138" t="inlineStr">
+        <is>
+          <t>Sara Cavalheiro</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>6224</v>
+        <v>6628</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -15061,17 +15062,17 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -15101,11 +15102,11 @@
         </is>
       </c>
       <c r="O139" t="n">
-        <v>17688763</v>
+        <v>18052438</v>
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Tania Luz</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="Q139" t="inlineStr">
@@ -15114,14 +15115,14 @@
         </is>
       </c>
       <c r="R139" s="1" t="n">
-        <v>46205.75458568287</v>
+        <v>46206.44903752315</v>
       </c>
       <c r="S139" t="n">
         <v>4</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t xml:space="preserve">GTG </t>
         </is>
       </c>
       <c r="U139" t="inlineStr">
@@ -15138,7 +15139,7 @@
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>Tania Luz</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr"/>
@@ -15152,17 +15153,17 @@
       </c>
       <c r="AG139" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>David Bragança</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>6628</v>
+        <v>6779</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>CORDEIRO E CIA LTDA</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -15177,7 +15178,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -15212,34 +15213,26 @@
         </is>
       </c>
       <c r="O140" t="n">
-        <v>18052438</v>
-      </c>
-      <c r="P140" t="inlineStr">
-        <is>
-          <t>Jakeline Silva</t>
-        </is>
-      </c>
+        <v>18090166</v>
+      </c>
+      <c r="P140" t="inlineStr"/>
       <c r="Q140" t="inlineStr">
         <is>
           <t>Baixado</t>
         </is>
       </c>
       <c r="R140" s="1" t="n">
-        <v>46206.44903752315</v>
+        <v>46199.48727971065</v>
       </c>
       <c r="S140" t="n">
         <v>4</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
-        </is>
-      </c>
-      <c r="U140" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>TECNO COM</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr"/>
       <c r="V140" t="inlineStr"/>
       <c r="W140" t="inlineStr"/>
       <c r="X140" t="inlineStr"/>
@@ -15249,7 +15242,7 @@
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Kaique Souza</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr"/>
@@ -15261,19 +15254,15 @@
           <t>Imposto</t>
         </is>
       </c>
-      <c r="AG140" t="inlineStr">
-        <is>
-          <t>David Bragança</t>
-        </is>
-      </c>
+      <c r="AG140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>6779</v>
+        <v>6885</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>CORDEIRO E CIA LTDA</t>
+          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -15323,23 +15312,27 @@
         </is>
       </c>
       <c r="O141" t="n">
-        <v>18090166</v>
-      </c>
-      <c r="P141" t="inlineStr"/>
+        <v>18157259</v>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>Vitor Guedes</t>
+        </is>
+      </c>
       <c r="Q141" t="inlineStr">
         <is>
           <t>Baixado</t>
         </is>
       </c>
       <c r="R141" s="1" t="n">
-        <v>46199.48727971065</v>
+        <v>46205.69236453703</v>
       </c>
       <c r="S141" t="n">
         <v>4</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U141" t="inlineStr"/>
@@ -15352,7 +15345,7 @@
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>Kaique Souza</t>
+          <t>Vitor Guedes</t>
         </is>
       </c>
       <c r="AB141" t="inlineStr"/>
@@ -15364,15 +15357,19 @@
           <t>Imposto</t>
         </is>
       </c>
-      <c r="AG141" t="inlineStr"/>
+      <c r="AG141" t="inlineStr">
+        <is>
+          <t>David Bragança</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>6885</v>
+        <v>6945</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
+          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -15387,7 +15384,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -15415,18 +15412,22 @@
       <c r="L142" s="1" t="n">
         <v>46206</v>
       </c>
-      <c r="M142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
       <c r="N142" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O142" t="n">
-        <v>18157259</v>
+        <v>18179094</v>
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Vitor Guedes</t>
+          <t>Santos Karina</t>
         </is>
       </c>
       <c r="Q142" t="inlineStr">
@@ -15435,18 +15436,23 @@
         </is>
       </c>
       <c r="R142" s="1" t="n">
-        <v>46205.69236453703</v>
+        <v>46209.43008613426</v>
       </c>
       <c r="S142" t="n">
         <v>4</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>BRASIL DISTRIBUIDORA</t>
         </is>
       </c>
       <c r="U142" t="inlineStr"/>
-      <c r="V142" t="inlineStr"/>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 07/07/2026 
+cliente em implantação, em andamento - Data Comentário: 03/07/2026 17:19</t>
+        </is>
+      </c>
       <c r="W142" t="inlineStr"/>
       <c r="X142" t="inlineStr"/>
       <c r="Y142" t="inlineStr"/>
@@ -15455,7 +15461,7 @@
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>Vitor Guedes</t>
+          <t>Santos Karina</t>
         </is>
       </c>
       <c r="AB142" t="inlineStr"/>
@@ -15469,17 +15475,17 @@
       </c>
       <c r="AG142" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Leandro Matos</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>6945</v>
+        <v>6486</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
+          <t>PC GAMER GOIANIA LTDA</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -15489,12 +15495,12 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -15503,10 +15509,10 @@
         </is>
       </c>
       <c r="G143" t="n">
-        <v>5859</v>
+        <v>11542</v>
       </c>
       <c r="H143" t="n">
-        <v>5786</v>
+        <v>0</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
@@ -15515,29 +15521,25 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Contribuição Assistencial</t>
+          <t>Envio Arq. eConsignado Cliente</t>
         </is>
       </c>
       <c r="K143" t="inlineStr"/>
       <c r="L143" s="1" t="n">
-        <v>46206</v>
-      </c>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>07/07/2026</t>
-        </is>
-      </c>
+        <v>46204</v>
+      </c>
+      <c r="M143" t="inlineStr"/>
       <c r="N143" t="inlineStr">
         <is>
-          <t>06/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
       <c r="O143" t="n">
-        <v>18179094</v>
+        <v>16976370</v>
       </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Santos Karina</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="Q143" t="inlineStr">
@@ -15546,23 +15548,22 @@
         </is>
       </c>
       <c r="R143" s="1" t="n">
-        <v>46209.43008613426</v>
+        <v>46204.5600265625</v>
       </c>
       <c r="S143" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA</t>
-        </is>
-      </c>
-      <c r="U143" t="inlineStr"/>
-      <c r="V143" t="inlineStr">
-        <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 07/07/2026 
-cliente em implantação, em andamento - Data Comentário: 03/07/2026 17:19</t>
-        </is>
-      </c>
+          <t>PC GAMER</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr"/>
       <c r="W143" t="inlineStr"/>
       <c r="X143" t="inlineStr"/>
       <c r="Y143" t="inlineStr"/>
@@ -15571,7 +15572,7 @@
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>Santos Karina</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="AB143" t="inlineStr"/>
@@ -15580,22 +15581,22 @@
       <c r="AE143" t="inlineStr"/>
       <c r="AF143" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Obrigação Acessória</t>
         </is>
       </c>
       <c r="AG143" t="inlineStr">
         <is>
-          <t>Leandro Matos</t>
+          <t>David Bragança</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>6486</v>
+        <v>6548</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>PC GAMER GOIANIA LTDA</t>
+          <t>GOIAS SILAGEM LTDA</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -15645,11 +15646,11 @@
         </is>
       </c>
       <c r="O144" t="n">
-        <v>16976370</v>
+        <v>17222966</v>
       </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Evellin Bispo</t>
         </is>
       </c>
       <c r="Q144" t="inlineStr">
@@ -15658,14 +15659,14 @@
         </is>
       </c>
       <c r="R144" s="1" t="n">
-        <v>46204.5600265625</v>
+        <v>46196.71390480324</v>
       </c>
       <c r="S144" t="n">
         <v>6</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
-          <t>PC GAMER</t>
+          <t>GOIAS SILAGEM</t>
         </is>
       </c>
       <c r="U144" t="inlineStr">
@@ -15682,7 +15683,7 @@
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Evellin Bispo</t>
         </is>
       </c>
       <c r="AB144" t="inlineStr"/>
@@ -15696,17 +15697,17 @@
       </c>
       <c r="AG144" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Leandro Matos</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>6548</v>
+        <v>6703</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM LTDA</t>
+          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -15716,7 +15717,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -15756,11 +15757,11 @@
         </is>
       </c>
       <c r="O145" t="n">
-        <v>17222966</v>
+        <v>18077183</v>
       </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Evellin Bispo</t>
+          <t>Elaine Assis</t>
         </is>
       </c>
       <c r="Q145" t="inlineStr">
@@ -15769,14 +15770,14 @@
         </is>
       </c>
       <c r="R145" s="1" t="n">
-        <v>46196.71390480324</v>
+        <v>46198.70825575232</v>
       </c>
       <c r="S145" t="n">
         <v>6</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM</t>
+          <t>LIMA MOTA</t>
         </is>
       </c>
       <c r="U145" t="inlineStr">
@@ -15793,7 +15794,7 @@
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>Evellin Bispo</t>
+          <t>Elaine Assis</t>
         </is>
       </c>
       <c r="AB145" t="inlineStr"/>
@@ -15807,17 +15808,17 @@
       </c>
       <c r="AG145" t="inlineStr">
         <is>
-          <t>Leandro Matos</t>
+          <t>David Bragança</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>6703</v>
+        <v>6779</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
+          <t>CORDEIRO E CIA LTDA</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -15827,7 +15828,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -15867,11 +15868,11 @@
         </is>
       </c>
       <c r="O146" t="n">
-        <v>18077183</v>
+        <v>18090270</v>
       </c>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Elaine Assis</t>
+          <t>Kaique Souza</t>
         </is>
       </c>
       <c r="Q146" t="inlineStr">
@@ -15880,21 +15881,17 @@
         </is>
       </c>
       <c r="R146" s="1" t="n">
-        <v>46198.70825575232</v>
+        <v>46196.59280127315</v>
       </c>
       <c r="S146" t="n">
         <v>6</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
-          <t>LIMA MOTA</t>
-        </is>
-      </c>
-      <c r="U146" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>TECNO COM</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr"/>
       <c r="V146" t="inlineStr"/>
       <c r="W146" t="inlineStr"/>
       <c r="X146" t="inlineStr"/>
@@ -15904,7 +15901,7 @@
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>Elaine Assis</t>
+          <t>Kaique Souza</t>
         </is>
       </c>
       <c r="AB146" t="inlineStr"/>
@@ -15918,17 +15915,17 @@
       </c>
       <c r="AG146" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>6779</v>
+        <v>6949</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>CORDEIRO E CIA LTDA</t>
+          <t>TEC GRUA LOCAÇÃO E COMERCIO DE EQUIPAMENTOS PARA CONSTRUÇÃO LTDA</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -15938,7 +15935,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -15948,7 +15945,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Reynaldo Santos</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -15978,11 +15975,11 @@
         </is>
       </c>
       <c r="O147" t="n">
-        <v>18090270</v>
+        <v>18190469</v>
       </c>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Kaique Souza</t>
+          <t>Gabriela Peres</t>
         </is>
       </c>
       <c r="Q147" t="inlineStr">
@@ -15991,14 +15988,14 @@
         </is>
       </c>
       <c r="R147" s="1" t="n">
-        <v>46196.59280127315</v>
+        <v>46204.41370118056</v>
       </c>
       <c r="S147" t="n">
         <v>6</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>TEC GRUA</t>
         </is>
       </c>
       <c r="U147" t="inlineStr"/>
@@ -16011,7 +16008,7 @@
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>Kaique Souza</t>
+          <t>Santos Karina</t>
         </is>
       </c>
       <c r="AB147" t="inlineStr"/>
@@ -16025,17 +16022,17 @@
       </c>
       <c r="AG147" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>Leandro Matos</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>6949</v>
+        <v>6404</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>TEC GRUA LOCAÇÃO E COMERCIO DE EQUIPAMENTOS PARA CONSTRUÇÃO LTDA</t>
+          <t>SOLAR INVESTIMENTOS LTDA</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -16045,7 +16042,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -16055,11 +16052,11 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G148" t="n">
-        <v>11542</v>
+        <v>9746</v>
       </c>
       <c r="H148" t="n">
         <v>0</v>
@@ -16071,25 +16068,29 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>Envio Arq. eConsignado Cliente</t>
+          <t>eSocial – Fechamento Mensal</t>
         </is>
       </c>
       <c r="K148" t="inlineStr"/>
       <c r="L148" s="1" t="n">
-        <v>46204</v>
-      </c>
-      <c r="M148" t="inlineStr"/>
+        <v>46213</v>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
       <c r="O148" t="n">
-        <v>18190469</v>
+        <v>16962422</v>
       </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Gabriela Peres</t>
+          <t>Jhenifer Tenorio</t>
         </is>
       </c>
       <c r="Q148" t="inlineStr">
@@ -16098,18 +16099,26 @@
         </is>
       </c>
       <c r="R148" s="1" t="n">
-        <v>46204.41370118056</v>
+        <v>46209.71247704861</v>
       </c>
       <c r="S148" t="n">
-        <v>6</v>
+        <v>-3</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
-          <t>TEC GRUA</t>
-        </is>
-      </c>
-      <c r="U148" t="inlineStr"/>
-      <c r="V148" t="inlineStr"/>
+          <t>SOLAR INVESTIMENTOS</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 08/07/2026 - Data Comentário: 06/07/2026 12:40</t>
+        </is>
+      </c>
       <c r="W148" t="inlineStr"/>
       <c r="X148" t="inlineStr"/>
       <c r="Y148" t="inlineStr"/>
@@ -16118,7 +16127,7 @@
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>Santos Karina</t>
+          <t>Jhenifer Tenorio</t>
         </is>
       </c>
       <c r="AB148" t="inlineStr"/>
@@ -16127,22 +16136,22 @@
       <c r="AE148" t="inlineStr"/>
       <c r="AF148" t="inlineStr">
         <is>
-          <t>Obrigação Acessória</t>
+          <t>Tarefa</t>
         </is>
       </c>
       <c r="AG148" t="inlineStr">
         <is>
-          <t>Leandro Matos</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>6404</v>
+        <v>6486</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS LTDA</t>
+          <t>PC GAMER GOIANIA LTDA</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -16152,7 +16161,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -16196,11 +16205,11 @@
         </is>
       </c>
       <c r="O149" t="n">
-        <v>16962422</v>
+        <v>16976298</v>
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Jhenifer Tenorio</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="Q149" t="inlineStr">
@@ -16209,14 +16218,14 @@
         </is>
       </c>
       <c r="R149" s="1" t="n">
-        <v>46209.71247704861</v>
+        <v>46209.71499087963</v>
       </c>
       <c r="S149" t="n">
         <v>-3</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS</t>
+          <t>PC GAMER</t>
         </is>
       </c>
       <c r="U149" t="inlineStr">
@@ -16226,7 +16235,8 @@
       </c>
       <c r="V149" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 08/07/2026 - Data Comentário: 06/07/2026 12:40</t>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 08/07/2026 
+PREVISÃO DE FINALIZAÇÃO: 08/07/2026 - Data Comentário: 06/07/2026 10:43</t>
         </is>
       </c>
       <c r="W149" t="inlineStr"/>
@@ -16237,7 +16247,7 @@
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>Jhenifer Tenorio</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="AB149" t="inlineStr"/>
@@ -16251,17 +16261,17 @@
       </c>
       <c r="AG149" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>David Bragança</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>6486</v>
+        <v>6779</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>PC GAMER GOIANIA LTDA</t>
+          <t>CORDEIRO E CIA LTDA</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -16271,7 +16281,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -16306,7 +16316,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -16315,11 +16325,11 @@
         </is>
       </c>
       <c r="O150" t="n">
-        <v>16976298</v>
+        <v>18090248</v>
       </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Kaique Souza</t>
         </is>
       </c>
       <c r="Q150" t="inlineStr">
@@ -16328,25 +16338,21 @@
         </is>
       </c>
       <c r="R150" s="1" t="n">
-        <v>46209.71499087963</v>
+        <v>46210.45896016204</v>
       </c>
       <c r="S150" t="n">
         <v>-3</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
-          <t>PC GAMER</t>
-        </is>
-      </c>
-      <c r="U150" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>TECNO COM</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr"/>
       <c r="V150" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 08/07/2026 
-PREVISÃO DE FINALIZAÇÃO: 08/07/2026 - Data Comentário: 06/07/2026 10:43</t>
+          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 10/07/2026 
+ESocial será baixado no vencimento para evitar retificações por solicitações do cliente. - Data Comentário: 03/07/2026 14:17</t>
         </is>
       </c>
       <c r="W150" t="inlineStr"/>
@@ -16357,7 +16363,7 @@
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Kaique Souza</t>
         </is>
       </c>
       <c r="AB150" t="inlineStr"/>
@@ -16371,7 +16377,7 @@
       </c>
       <c r="AG150" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
     </row>

--- a/dados/base/goias.xlsx
+++ b/dados/base/goias.xlsx
@@ -2244,7 +2244,11 @@
       <c r="L17" s="1" t="n">
         <v>46213</v>
       </c>
-      <c r="M17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr">
         <is>
           <t>06/2026</t>
@@ -2277,7 +2281,12 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr"/>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 08/07/2026 
+Previsão de conclusão em 08/07/2026. - Data Comentário: 07/07/2026 16:47</t>
+        </is>
+      </c>
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr"/>
@@ -2302,11 +2311,11 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>6885</v>
+        <v>6945</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
+          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2321,7 +2330,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2351,7 +2360,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2360,11 +2369,11 @@
         </is>
       </c>
       <c r="O18" t="n">
-        <v>18157325</v>
+        <v>18179152</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Vitor Guedes</t>
+          <t>Santos Karina</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -2378,14 +2387,14 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>BRASIL DISTRIBUIDORA</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 07/07/2026 
-PREVISÃO DE CONCLUSÃO: 07/07/2026 - Data Comentário: 07/07/2026 13:13</t>
+          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 10/07/2026 
+Empresa Implantação em processamento. - Data Comentário: 07/07/2026 15:25</t>
         </is>
       </c>
       <c r="W18" t="inlineStr"/>
@@ -2406,17 +2415,17 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Leandro Matos</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>6945</v>
+        <v>6279</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
+          <t>DIENNYFER DA S PEREIRA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2426,21 +2435,21 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>9746</v>
+        <v>10905</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -2452,7 +2461,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>eSocial – Fechamento Mensal</t>
+          <t>eSocial - Fechamento SM</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -2461,7 +2470,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2470,11 +2479,11 @@
         </is>
       </c>
       <c r="O19" t="n">
-        <v>18179152</v>
+        <v>18195935</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Santos Karina</t>
+          <t>Vitor Guedes</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -2488,14 +2497,18 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr"/>
+          <t>EMPORIO DOS FRIOS</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 10/07/2026 
-Empresa Implantação em processamento. - Data Comentário: 07/07/2026 15:25</t>
+          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 08/07/2026 
+Previsão de conclusão: 08/07/2026 - Data Comentário: 06/07/2026 14:42</t>
         </is>
       </c>
       <c r="W19" t="inlineStr"/>
@@ -2511,22 +2524,22 @@
       <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>Tarefa</t>
+          <t>Obrigação Acessória</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>Leandro Matos</t>
+          <t>David Bragança</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>6279</v>
+        <v>5617</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DIENNYFER DA S PEREIRA</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2536,7 +2549,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2546,14 +2559,14 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>10905</v>
+        <v>5853</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>5784</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2562,29 +2575,25 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>eSocial - Fechamento SM</t>
+          <t>FOPAG Impressão PDF</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" s="1" t="n">
-        <v>46213</v>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>08/07/2026</t>
-        </is>
-      </c>
+        <v>46210</v>
+      </c>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O20" t="n">
-        <v>18195935</v>
+        <v>17407635</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Vitor Guedes</t>
+          <t>Tania Luz</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -2594,11 +2603,11 @@
       </c>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2608,8 +2617,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 08/07/2026 
-Previsão de conclusão: 08/07/2026 - Data Comentário: 06/07/2026 14:42</t>
+          <t>8. Serviços Suspensos. - Data Comentário: 03/07/2026 08:40</t>
         </is>
       </c>
       <c r="W20" t="inlineStr"/>
@@ -2625,22 +2633,22 @@
       <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>Obrigação Acessória</t>
+          <t>Tarefa</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>5617</v>
+        <v>6224</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2660,7 +2668,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2690,7 +2698,7 @@
         </is>
       </c>
       <c r="O21" t="n">
-        <v>17407635</v>
+        <v>17688753</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
@@ -2718,7 +2726,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>8. Serviços Suspensos. - Data Comentário: 03/07/2026 08:40</t>
+          <t>8. Serviços Suspensos. - Data Comentário: 03/07/2026 08:39</t>
         </is>
       </c>
       <c r="W21" t="inlineStr"/>
@@ -2745,11 +2753,11 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>6224</v>
+        <v>5417</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2769,14 +2777,14 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>5853</v>
+        <v>5867</v>
       </c>
       <c r="H22" t="n">
-        <v>5784</v>
+        <v>5786</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2785,12 +2793,12 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>FOPAG Impressão PDF</t>
+          <t>GFD - FGTS Digital Mensal</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" s="1" t="n">
-        <v>46210</v>
+        <v>46218</v>
       </c>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
@@ -2799,11 +2807,11 @@
         </is>
       </c>
       <c r="O22" t="n">
-        <v>17688753</v>
+        <v>17399054</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Tania Luz</t>
+          <t>Mikael Teixeira</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -2813,11 +2821,11 @@
       </c>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>NOSSO NOVO SUPERMERCADO</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2825,11 +2833,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>8. Serviços Suspensos. - Data Comentário: 03/07/2026 08:39</t>
-        </is>
-      </c>
+      <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr"/>
@@ -2843,22 +2847,18 @@
       <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>Tarefa</t>
-        </is>
-      </c>
-      <c r="AG22" t="inlineStr">
-        <is>
-          <t>Sara Cavalheiro</t>
-        </is>
-      </c>
+          <t>Imposto</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>5417</v>
+        <v>5617</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -2908,11 +2908,11 @@
         </is>
       </c>
       <c r="O23" t="n">
-        <v>17399054</v>
+        <v>17407645</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mikael Teixeira</t>
+          <t>Tania Luz</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2951,15 +2951,19 @@
           <t>Imposto</t>
         </is>
       </c>
-      <c r="AG23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>Sara Cavalheiro</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>5617</v>
+        <v>6224</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2979,7 +2983,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3009,7 +3013,7 @@
         </is>
       </c>
       <c r="O24" t="n">
-        <v>17407645</v>
+        <v>17688773</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
@@ -3060,11 +3064,11 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>6224</v>
+        <v>6486</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>PC GAMER GOIANIA LTDA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3084,7 +3088,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3107,18 +3111,22 @@
       <c r="L25" s="1" t="n">
         <v>46218</v>
       </c>
-      <c r="M25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O25" t="n">
-        <v>17688773</v>
+        <v>16976054</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Tania Luz</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -3132,7 +3140,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>PC GAMER</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3140,7 +3148,12 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr"/>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 13/07/2026 
+PREVISÃO DE CONCLUSÃO: 13/07/2026 - Data Comentário: 07/07/2026 16:32</t>
+        </is>
+      </c>
       <c r="W25" t="inlineStr"/>
       <c r="X25" t="inlineStr"/>
       <c r="Y25" t="inlineStr"/>
@@ -3159,17 +3172,17 @@
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>David Bragança</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>6486</v>
+        <v>6548</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>PC GAMER GOIANIA LTDA</t>
+          <t>GOIAS SILAGEM LTDA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3212,22 +3225,18 @@
       <c r="L26" s="1" t="n">
         <v>46218</v>
       </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>13/07/2026</t>
-        </is>
-      </c>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O26" t="n">
-        <v>16976054</v>
+        <v>17222615</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Daniel Moraes</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -3241,7 +3250,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>PC GAMER</t>
+          <t>GOIAS SILAGEM</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3249,12 +3258,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 13/07/2026 
-PREVISÃO DE CONCLUSÃO: 13/07/2026 - Data Comentário: 07/07/2026 16:32</t>
-        </is>
-      </c>
+      <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr"/>
       <c r="X26" t="inlineStr"/>
       <c r="Y26" t="inlineStr"/>
@@ -3279,11 +3283,11 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM LTDA</t>
+          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3298,7 +3302,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3326,18 +3330,22 @@
       <c r="L27" s="1" t="n">
         <v>46218</v>
       </c>
-      <c r="M27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O27" t="n">
-        <v>17222615</v>
+        <v>18068530</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Daniel Moraes</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -3351,7 +3359,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM</t>
+          <t xml:space="preserve">GTG </t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3359,7 +3367,12 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr"/>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 13/07/2026 
+PREVISÃO DE CONCLUSÃO: 13/07/2026 - Data Comentário: 07/07/2026 16:32</t>
+        </is>
+      </c>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="inlineStr"/>
       <c r="Y27" t="inlineStr"/>
@@ -3384,11 +3397,11 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3398,7 +3411,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3442,7 +3455,7 @@
         </is>
       </c>
       <c r="O28" t="n">
-        <v>18068530</v>
+        <v>18052449</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
@@ -3498,11 +3511,11 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>6628</v>
+        <v>6703</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3512,12 +3525,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3545,22 +3558,18 @@
       <c r="L29" s="1" t="n">
         <v>46218</v>
       </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>13/07/2026</t>
-        </is>
-      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O29" t="n">
-        <v>18052449</v>
+        <v>18077099</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Elaine Assis</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -3574,7 +3583,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
+          <t>LIMA MOTA</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3582,12 +3591,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 13/07/2026 
-PREVISÃO DE CONCLUSÃO: 13/07/2026 - Data Comentário: 07/07/2026 16:32</t>
-        </is>
-      </c>
+      <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr"/>
       <c r="X29" t="inlineStr"/>
       <c r="Y29" t="inlineStr"/>
@@ -3612,11 +3616,11 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>6703</v>
+        <v>6779</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
+          <t>CORDEIRO E CIA LTDA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3626,7 +3630,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3666,11 +3670,11 @@
         </is>
       </c>
       <c r="O30" t="n">
-        <v>18077099</v>
+        <v>18090176</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Elaine Assis</t>
+          <t>Kaique Souza</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -3684,14 +3688,10 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>LIMA MOTA</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>TECNO COM</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr"/>
@@ -3711,17 +3711,17 @@
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>6779</v>
+        <v>6885</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CORDEIRO E CIA LTDA</t>
+          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3771,11 +3771,11 @@
         </is>
       </c>
       <c r="O31" t="n">
-        <v>18090176</v>
+        <v>18157267</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kaique Souza</t>
+          <t>Vitor Guedes</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -3789,7 +3789,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U31" t="inlineStr"/>
@@ -3812,17 +3812,17 @@
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>David Bragança</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>6885</v>
+        <v>6945</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
+          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3872,11 +3872,11 @@
         </is>
       </c>
       <c r="O32" t="n">
-        <v>18157267</v>
+        <v>18179101</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Vitor Guedes</t>
+          <t>Santos Karina</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -3890,7 +3890,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>BRASIL DISTRIBUIDORA</t>
         </is>
       </c>
       <c r="U32" t="inlineStr"/>
@@ -3913,17 +3913,17 @@
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Leandro Matos</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>6945</v>
+        <v>6949</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
+          <t>TEC GRUA LOCAÇÃO E COMERCIO DE EQUIPAMENTOS PARA CONSTRUÇÃO LTDA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3933,24 +3933,24 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Reynaldo Santos</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>5867</v>
+        <v>6348</v>
       </c>
       <c r="H33" t="n">
-        <v>5786</v>
+        <v>0</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -3959,25 +3959,29 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>GFD - FGTS Digital Mensal</t>
+          <t>RESCISÃO - RESCISÃO</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" s="1" t="n">
-        <v>46218</v>
-      </c>
-      <c r="M33" t="inlineStr"/>
+        <v>46211</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>06/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
       <c r="O33" t="n">
-        <v>18179101</v>
+        <v>18199991</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Santos Karina</t>
+          <t>Gabriela Peres</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -3987,15 +3991,20 @@
       </c>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="n">
-        <v>-8</v>
+        <v>-1</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA</t>
+          <t>TEC GRUA</t>
         </is>
       </c>
       <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 08/07/2026 
+Empresa em implantação, aguardando retorno do cliente para finalização. - Data Comentário: 07/07/2026 15:23</t>
+        </is>
+      </c>
       <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr"/>
       <c r="Y33" t="inlineStr"/>
@@ -4048,41 +4057,41 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>6348</v>
+        <v>11617</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>RESCISÃO - RESCISÃO</t>
+          <t>Envio de ATA de Implantação - EF I</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" s="1" t="n">
-        <v>46211</v>
+        <v>46213</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
       <c r="O34" t="n">
-        <v>18199991</v>
+        <v>18166588</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Gabriela Peres</t>
+          <t>Priscila Volpe</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -4092,7 +4101,7 @@
       </c>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4102,8 +4111,8 @@
       <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 08/07/2026 
-Empresa em implantação, aguardando retorno do cliente para finalização. - Data Comentário: 07/07/2026 15:23</t>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 31/07/2026 
+ainda não foi realizado as implantações - Data Comentário: 01/07/2026 13:38</t>
         </is>
       </c>
       <c r="W34" t="inlineStr"/>
@@ -4119,22 +4128,22 @@
       <c r="AE34" t="inlineStr"/>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Tarefa</t>
         </is>
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>Leandro Matos</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>6949</v>
+        <v>6962</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>TEC GRUA LOCAÇÃO E COMERCIO DE EQUIPAMENTOS PARA CONSTRUÇÃO LTDA</t>
+          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4188,7 +4197,7 @@
         </is>
       </c>
       <c r="O35" t="n">
-        <v>18166588</v>
+        <v>18186565</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
@@ -4206,7 +4215,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>TEC GRUA</t>
+          <t>PROMOTORAS GYN</t>
         </is>
       </c>
       <c r="U35" t="inlineStr"/>
@@ -4240,11 +4249,11 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
+          <t>PROMOTORAS GYN LTDA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -4298,7 +4307,7 @@
         </is>
       </c>
       <c r="O36" t="n">
-        <v>18186565</v>
+        <v>18186566</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
@@ -4350,11 +4359,11 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>6963</v>
+        <v>6628</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN LTDA</t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -4364,21 +4373,21 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>11617</v>
+        <v>1875</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -4390,29 +4399,25 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Envio de ATA de Implantação - EF I</t>
+          <t>Est - Sintegra Interestadual</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" s="1" t="n">
-        <v>46213</v>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>31/07/2026</t>
-        </is>
-      </c>
+        <v>46218</v>
+      </c>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O37" t="n">
-        <v>18186566</v>
+        <v>17988660</v>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Priscila Volpe</t>
+          <t>Fernando Bastos</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -4422,20 +4427,19 @@
       </c>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="n">
-        <v>-3</v>
+        <v>-8</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 31/07/2026 
-ainda não foi realizado as implantações - Data Comentário: 01/07/2026 13:38</t>
-        </is>
-      </c>
+          <t xml:space="preserve">GTG </t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr"/>
       <c r="X37" t="inlineStr"/>
       <c r="Y37" t="inlineStr"/>
@@ -4449,22 +4453,18 @@
       <c r="AE37" t="inlineStr"/>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>Tarefa</t>
-        </is>
-      </c>
-      <c r="AG37" t="inlineStr">
-        <is>
-          <t>Nayara Oliveira</t>
-        </is>
-      </c>
+          <t>Obrigação Acessória</t>
+        </is>
+      </c>
+      <c r="AG37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>6628</v>
+        <v>6548</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>GOIAS SILAGEM LTDA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4474,12 +4474,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4488,7 +4488,7 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>1875</v>
+        <v>6805</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -4500,12 +4500,12 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Est - Sintegra Interestadual</t>
+          <t>Fed - EFD - REINF - Entrega e PDF</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" s="1" t="n">
-        <v>46218</v>
+        <v>46216</v>
       </c>
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
@@ -4514,11 +4514,11 @@
         </is>
       </c>
       <c r="O38" t="n">
-        <v>17988660</v>
+        <v>17222740</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Fernando Bastos</t>
+          <t>Cristiana Grizostomo</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -4528,11 +4528,11 @@
       </c>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
+          <t>GOIAS SILAGEM</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4557,15 +4557,19 @@
           <t>Obrigação Acessória</t>
         </is>
       </c>
-      <c r="AG38" t="inlineStr"/>
+      <c r="AG38" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM LTDA</t>
+          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -4580,7 +4584,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4615,11 +4619,11 @@
         </is>
       </c>
       <c r="O39" t="n">
-        <v>17222740</v>
+        <v>18085517</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Cristiana Grizostomo</t>
+          <t>Denis Reis</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -4633,7 +4637,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM</t>
+          <t xml:space="preserve">GTG </t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4658,19 +4662,15 @@
           <t>Obrigação Acessória</t>
         </is>
       </c>
-      <c r="AG39" t="inlineStr">
-        <is>
-          <t>Nayara Oliveira</t>
-        </is>
-      </c>
+      <c r="AG39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4720,11 +4720,11 @@
         </is>
       </c>
       <c r="O40" t="n">
-        <v>18085517</v>
+        <v>17988707</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Denis Reis</t>
+          <t>Fernando Bastos</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -4767,11 +4767,11 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>6628</v>
+        <v>6962</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -4781,17 +4781,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Reynaldo Santos</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -4821,11 +4821,11 @@
         </is>
       </c>
       <c r="O41" t="n">
-        <v>17988707</v>
+        <v>18186993</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Fernando Bastos</t>
+          <t>Denis Reis</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -4839,14 +4839,10 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>PROMOTORAS GYN</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr"/>
       <c r="V41" t="inlineStr"/>
       <c r="W41" t="inlineStr"/>
       <c r="X41" t="inlineStr"/>
@@ -4868,11 +4864,11 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
+          <t>PROMOTORAS GYN LTDA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -4922,7 +4918,7 @@
         </is>
       </c>
       <c r="O42" t="n">
-        <v>18186993</v>
+        <v>18187259</v>
       </c>
       <c r="P42" t="inlineStr">
         <is>
@@ -4965,11 +4961,11 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>6963</v>
+        <v>6962</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN LTDA</t>
+          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4993,7 +4989,7 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>6805</v>
+        <v>1866</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -5005,21 +5001,25 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Fed - EFD - REINF - Entrega e PDF</t>
+          <t>Mun - ISS Serv. Prestados</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" s="1" t="n">
-        <v>46216</v>
-      </c>
-      <c r="M43" t="inlineStr"/>
+        <v>46212</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O43" t="n">
-        <v>18187259</v>
+        <v>18186944</v>
       </c>
       <c r="P43" t="inlineStr">
         <is>
@@ -5033,7 +5033,7 @@
       </c>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="n">
-        <v>-6</v>
+        <v>-2</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5041,7 +5041,11 @@
         </is>
       </c>
       <c r="U43" t="inlineStr"/>
-      <c r="V43" t="inlineStr"/>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 06/07/2026 - Data Comentário: 06/07/2026 10:20</t>
+        </is>
+      </c>
       <c r="W43" t="inlineStr"/>
       <c r="X43" t="inlineStr"/>
       <c r="Y43" t="inlineStr"/>
@@ -5055,18 +5059,18 @@
       <c r="AE43" t="inlineStr"/>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>Obrigação Acessória</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="AG43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
+          <t>PROMOTORAS GYN LTDA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -5120,7 +5124,7 @@
         </is>
       </c>
       <c r="O44" t="n">
-        <v>18186944</v>
+        <v>18187210</v>
       </c>
       <c r="P44" t="inlineStr">
         <is>
@@ -5167,11 +5171,11 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>6963</v>
+        <v>6962</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN LTDA</t>
+          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -5195,7 +5199,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -5207,7 +5211,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Mun - ISS Serv. Prestados</t>
+          <t>Mun - ISS Serv. Tomados</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -5216,7 +5220,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -5225,7 +5229,7 @@
         </is>
       </c>
       <c r="O45" t="n">
-        <v>18187210</v>
+        <v>18186951</v>
       </c>
       <c r="P45" t="inlineStr">
         <is>
@@ -5249,7 +5253,7 @@
       <c r="U45" t="inlineStr"/>
       <c r="V45" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 06/07/2026 - Data Comentário: 06/07/2026 10:20</t>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 07/07/2026 - Data Comentário: 06/07/2026 10:20</t>
         </is>
       </c>
       <c r="W45" t="inlineStr"/>
@@ -5272,11 +5276,11 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
+          <t>PROMOTORAS GYN LTDA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -5330,7 +5334,7 @@
         </is>
       </c>
       <c r="O46" t="n">
-        <v>18186951</v>
+        <v>18187217</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
@@ -5377,11 +5381,11 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>6963</v>
+        <v>6962</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN LTDA</t>
+          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -5405,10 +5409,10 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>1867</v>
+        <v>6886</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>1862</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -5417,25 +5421,21 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Mun - ISS Serv. Tomados</t>
+          <t>Recebimento de NF Serviços Tomados</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" s="1" t="n">
-        <v>46212</v>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>07/07/2026</t>
-        </is>
-      </c>
+        <v>46213</v>
+      </c>
+      <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O47" t="n">
-        <v>18187217</v>
+        <v>18187000</v>
       </c>
       <c r="P47" t="inlineStr">
         <is>
@@ -5449,7 +5449,7 @@
       </c>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5457,11 +5457,7 @@
         </is>
       </c>
       <c r="U47" t="inlineStr"/>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 07/07/2026 - Data Comentário: 06/07/2026 10:20</t>
-        </is>
-      </c>
+      <c r="V47" t="inlineStr"/>
       <c r="W47" t="inlineStr"/>
       <c r="X47" t="inlineStr"/>
       <c r="Y47" t="inlineStr"/>
@@ -5475,18 +5471,18 @@
       <c r="AE47" t="inlineStr"/>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Tarefa</t>
         </is>
       </c>
       <c r="AG47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
+          <t>PROMOTORAS GYN LTDA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -5536,7 +5532,7 @@
         </is>
       </c>
       <c r="O48" t="n">
-        <v>18187000</v>
+        <v>18187266</v>
       </c>
       <c r="P48" t="inlineStr">
         <is>
@@ -5579,11 +5575,11 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>6963</v>
+        <v>6627</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN LTDA</t>
+          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -5598,19 +5594,19 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>6886</v>
+        <v>10674</v>
       </c>
       <c r="H49" t="n">
-        <v>1862</v>
+        <v>0</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -5619,12 +5615,12 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Recebimento de NF Serviços Tomados</t>
+          <t>Relatório de Entrada para Classificação</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" s="1" t="n">
-        <v>46213</v>
+        <v>46218</v>
       </c>
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
@@ -5633,7 +5629,7 @@
         </is>
       </c>
       <c r="O49" t="n">
-        <v>18187266</v>
+        <v>17968443</v>
       </c>
       <c r="P49" t="inlineStr">
         <is>
@@ -5647,14 +5643,18 @@
       </c>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="n">
-        <v>-3</v>
+        <v>-8</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr"/>
+          <t xml:space="preserve">GTG </t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V49" t="inlineStr"/>
       <c r="W49" t="inlineStr"/>
       <c r="X49" t="inlineStr"/>
@@ -5676,11 +5676,11 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>6627</v>
+        <v>6962</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
+          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -5695,12 +5695,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Reynaldo Santos</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -5730,7 +5730,7 @@
         </is>
       </c>
       <c r="O50" t="n">
-        <v>17968443</v>
+        <v>18187014</v>
       </c>
       <c r="P50" t="inlineStr">
         <is>
@@ -5748,14 +5748,10 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>PROMOTORAS GYN</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr"/>
       <c r="V50" t="inlineStr"/>
       <c r="W50" t="inlineStr"/>
       <c r="X50" t="inlineStr"/>
@@ -5777,11 +5773,11 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
+          <t>PROMOTORAS GYN LTDA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -5831,7 +5827,7 @@
         </is>
       </c>
       <c r="O51" t="n">
-        <v>18187014</v>
+        <v>18187280</v>
       </c>
       <c r="P51" t="inlineStr">
         <is>
@@ -5874,11 +5870,11 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>6963</v>
+        <v>6779</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN LTDA</t>
+          <t>CORDEIRO E CIA LTDA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -5888,7 +5884,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -5898,41 +5894,45 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>10674</v>
+        <v>11636</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Relatório de Entrada para Classificação</t>
+          <t>Consulta - Movimento Serviços Prestados na Prefeitura</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" s="1" t="n">
-        <v>46218</v>
-      </c>
-      <c r="M52" t="inlineStr"/>
+        <v>46211</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O52" t="n">
-        <v>18187280</v>
+        <v>18085086</v>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Denis Reis</t>
+          <t>Cristina Leite</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
@@ -5942,15 +5942,19 @@
       </c>
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="n">
-        <v>-8</v>
+        <v>-1</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN</t>
+          <t>TECNO COM</t>
         </is>
       </c>
       <c r="U52" t="inlineStr"/>
-      <c r="V52" t="inlineStr"/>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 08/07/2026 - Data Comentário: 06/07/2026 17:18</t>
+        </is>
+      </c>
       <c r="W52" t="inlineStr"/>
       <c r="X52" t="inlineStr"/>
       <c r="Y52" t="inlineStr"/>
@@ -5967,15 +5971,19 @@
           <t>Tarefa</t>
         </is>
       </c>
-      <c r="AG52" t="inlineStr"/>
+      <c r="AG52" t="inlineStr">
+        <is>
+          <t>Ricardo Fischer</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>6779</v>
+        <v>6224</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CORDEIRO E CIA LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -5985,7 +5993,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -5995,11 +6003,11 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>11636</v>
+        <v>1802</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -6011,25 +6019,21 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Consulta - Movimento Serviços Prestados na Prefeitura</t>
+          <t>Est - ICMS RPA - CÓD. 046-2</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" s="1" t="n">
-        <v>46211</v>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>08/07/2026</t>
-        </is>
-      </c>
+        <v>46212</v>
+      </c>
+      <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O53" t="n">
-        <v>18085086</v>
+        <v>17688681</v>
       </c>
       <c r="P53" t="inlineStr">
         <is>
@@ -6043,17 +6047,21 @@
       </c>
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
-        </is>
-      </c>
-      <c r="U53" t="inlineStr"/>
+          <t>SUPER MAIS DO GOIÁS</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 08/07/2026 - Data Comentário: 06/07/2026 17:18</t>
+          <t>Atraso do Cliente, cobrança ativa, GC e GM ciente do atraso - Data Comentário: 06/07/2026 15:17</t>
         </is>
       </c>
       <c r="W53" t="inlineStr"/>
@@ -6069,7 +6077,7 @@
       <c r="AE53" t="inlineStr"/>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>Tarefa</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="AG53" t="inlineStr">
@@ -6080,11 +6088,11 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>6224</v>
+        <v>6705</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>NARCIZO ALVES CORDEIRO</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -6094,7 +6102,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -6104,11 +6112,11 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>1802</v>
+        <v>6298</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -6120,12 +6128,12 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Est - ICMS RPA - CÓD. 046-2</t>
+          <t>Est - Sintegra Interestadual</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" s="1" t="n">
-        <v>46212</v>
+        <v>46218</v>
       </c>
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
@@ -6134,7 +6142,7 @@
         </is>
       </c>
       <c r="O54" t="n">
-        <v>17688681</v>
+        <v>17949007</v>
       </c>
       <c r="P54" t="inlineStr">
         <is>
@@ -6148,11 +6156,11 @@
       </c>
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="n">
-        <v>-2</v>
+        <v>-8</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>TECNO COM</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6160,11 +6168,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>Atraso do Cliente, cobrança ativa, GC e GM ciente do atraso - Data Comentário: 06/07/2026 15:17</t>
-        </is>
-      </c>
+      <c r="V54" t="inlineStr"/>
       <c r="W54" t="inlineStr"/>
       <c r="X54" t="inlineStr"/>
       <c r="Y54" t="inlineStr"/>
@@ -6178,7 +6182,7 @@
       <c r="AE54" t="inlineStr"/>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Obrigação Acessória</t>
         </is>
       </c>
       <c r="AG54" t="inlineStr">
@@ -6189,11 +6193,11 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>6705</v>
+        <v>6885</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>NARCIZO ALVES CORDEIRO</t>
+          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -6243,7 +6247,7 @@
         </is>
       </c>
       <c r="O55" t="n">
-        <v>17949007</v>
+        <v>18134106</v>
       </c>
       <c r="P55" t="inlineStr">
         <is>
@@ -6261,14 +6265,10 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
-        </is>
-      </c>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>EMPORIO DOS FRIOS</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr"/>
       <c r="V55" t="inlineStr"/>
       <c r="W55" t="inlineStr"/>
       <c r="X55" t="inlineStr"/>
@@ -6294,11 +6294,11 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>6885</v>
+        <v>5417</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -6308,7 +6308,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -6318,11 +6318,11 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>6298</v>
+        <v>6806</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -6334,12 +6334,12 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Est - Sintegra Interestadual</t>
+          <t>Fed - EFD - REINF - Entrega e PDF</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" s="1" t="n">
-        <v>46218</v>
+        <v>46216</v>
       </c>
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
@@ -6348,7 +6348,7 @@
         </is>
       </c>
       <c r="O56" t="n">
-        <v>18134106</v>
+        <v>17399228</v>
       </c>
       <c r="P56" t="inlineStr">
         <is>
@@ -6362,14 +6362,18 @@
       </c>
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
-        </is>
-      </c>
-      <c r="U56" t="inlineStr"/>
+          <t>NOSSO NOVO SUPERMERCADO</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V56" t="inlineStr"/>
       <c r="W56" t="inlineStr"/>
       <c r="X56" t="inlineStr"/>
@@ -6395,11 +6399,11 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>5417</v>
+        <v>5617</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -6419,7 +6423,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -6449,7 +6453,7 @@
         </is>
       </c>
       <c r="O57" t="n">
-        <v>17399228</v>
+        <v>17407789</v>
       </c>
       <c r="P57" t="inlineStr">
         <is>
@@ -6467,7 +6471,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6500,11 +6504,11 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>5617</v>
+        <v>6224</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -6524,7 +6528,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -6554,7 +6558,7 @@
         </is>
       </c>
       <c r="O58" t="n">
-        <v>17407789</v>
+        <v>17688917</v>
       </c>
       <c r="P58" t="inlineStr">
         <is>
@@ -6605,11 +6609,11 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>6224</v>
+        <v>6278</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>EMPORIO DOS FRIOS LTDA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -6619,7 +6623,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Real - Anual</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -6629,7 +6633,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -6659,7 +6663,7 @@
         </is>
       </c>
       <c r="O59" t="n">
-        <v>17688917</v>
+        <v>17148836</v>
       </c>
       <c r="P59" t="inlineStr">
         <is>
@@ -6677,7 +6681,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6710,11 +6714,11 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>6278</v>
+        <v>6279</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS LTDA</t>
+          <t>DIENNYFER DA S PEREIRA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -6724,7 +6728,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Federal - Lucro Real - Anual</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -6734,7 +6738,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -6764,7 +6768,7 @@
         </is>
       </c>
       <c r="O60" t="n">
-        <v>17148836</v>
+        <v>17071031</v>
       </c>
       <c r="P60" t="inlineStr">
         <is>
@@ -6815,11 +6819,11 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>6279</v>
+        <v>6404</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>DIENNYFER DA S PEREIRA</t>
+          <t>SOLAR INVESTIMENTOS LTDA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -6839,7 +6843,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -6869,7 +6873,7 @@
         </is>
       </c>
       <c r="O61" t="n">
-        <v>17071031</v>
+        <v>16962306</v>
       </c>
       <c r="P61" t="inlineStr">
         <is>
@@ -6887,7 +6891,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>SOLAR INVESTIMENTOS</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -6920,11 +6924,11 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>6404</v>
+        <v>6486</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS LTDA</t>
+          <t>PC GAMER GOIANIA LTDA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -6934,7 +6938,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -6974,7 +6978,7 @@
         </is>
       </c>
       <c r="O62" t="n">
-        <v>16962306</v>
+        <v>16976185</v>
       </c>
       <c r="P62" t="inlineStr">
         <is>
@@ -6992,7 +6996,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS</t>
+          <t>PC GAMER</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7025,11 +7029,11 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>6486</v>
+        <v>6703</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>PC GAMER GOIANIA LTDA</t>
+          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -7039,7 +7043,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -7079,7 +7083,7 @@
         </is>
       </c>
       <c r="O63" t="n">
-        <v>16976185</v>
+        <v>17948856</v>
       </c>
       <c r="P63" t="inlineStr">
         <is>
@@ -7097,7 +7101,7 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>PC GAMER</t>
+          <t>LIMA MOTA</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7130,11 +7134,11 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>6703</v>
+        <v>6704</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
+          <t>TECNO COM INFORMATICA LTDA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -7144,7 +7148,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -7184,7 +7188,7 @@
         </is>
       </c>
       <c r="O64" t="n">
-        <v>17948856</v>
+        <v>18085295</v>
       </c>
       <c r="P64" t="inlineStr">
         <is>
@@ -7202,7 +7206,7 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>LIMA MOTA</t>
+          <t>TECNO COM</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7235,11 +7239,11 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>6704</v>
+        <v>6705</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>TECNO COM INFORMATICA LTDA</t>
+          <t>NARCIZO ALVES CORDEIRO</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -7249,7 +7253,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -7289,7 +7293,7 @@
         </is>
       </c>
       <c r="O65" t="n">
-        <v>18085295</v>
+        <v>17949027</v>
       </c>
       <c r="P65" t="inlineStr">
         <is>
@@ -7340,11 +7344,11 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>6705</v>
+        <v>6779</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NARCIZO ALVES CORDEIRO</t>
+          <t>CORDEIRO E CIA LTDA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -7394,7 +7398,7 @@
         </is>
       </c>
       <c r="O66" t="n">
-        <v>17949027</v>
+        <v>18085064</v>
       </c>
       <c r="P66" t="inlineStr">
         <is>
@@ -7415,11 +7419,7 @@
           <t>TECNO COM</t>
         </is>
       </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+      <c r="U66" t="inlineStr"/>
       <c r="V66" t="inlineStr"/>
       <c r="W66" t="inlineStr"/>
       <c r="X66" t="inlineStr"/>
@@ -7445,11 +7445,11 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>6779</v>
+        <v>6885</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CORDEIRO E CIA LTDA</t>
+          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -7499,7 +7499,7 @@
         </is>
       </c>
       <c r="O67" t="n">
-        <v>18085064</v>
+        <v>18134124</v>
       </c>
       <c r="P67" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U67" t="inlineStr"/>
@@ -7546,11 +7546,11 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>6885</v>
+        <v>6224</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -7560,7 +7560,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -7570,11 +7570,11 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>6806</v>
+        <v>11665</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -7586,12 +7586,12 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Fed - EFD - REINF - Entrega e PDF</t>
+          <t>GIAM (TO)</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
       <c r="L68" s="1" t="n">
-        <v>46216</v>
+        <v>46212</v>
       </c>
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
@@ -7600,7 +7600,7 @@
         </is>
       </c>
       <c r="O68" t="n">
-        <v>18134124</v>
+        <v>18076580</v>
       </c>
       <c r="P68" t="inlineStr">
         <is>
@@ -7614,15 +7614,23 @@
       </c>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="n">
-        <v>-6</v>
+        <v>-2</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
-        </is>
-      </c>
-      <c r="U68" t="inlineStr"/>
-      <c r="V68" t="inlineStr"/>
+          <t>SUPER MAIS DO GOIÁS</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Atraso do Cliente, cobrança ativa, GC e GM ciente do atraso - Data Comentário: 06/07/2026 15:55</t>
+        </is>
+      </c>
       <c r="W68" t="inlineStr"/>
       <c r="X68" t="inlineStr"/>
       <c r="Y68" t="inlineStr"/>
@@ -7636,7 +7644,7 @@
       <c r="AE68" t="inlineStr"/>
       <c r="AF68" t="inlineStr">
         <is>
-          <t>Obrigação Acessória</t>
+          <t>Tarefa</t>
         </is>
       </c>
       <c r="AG68" t="inlineStr">
@@ -7647,11 +7655,11 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>6224</v>
+        <v>5417</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -7671,14 +7679,14 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>11665</v>
+        <v>7884</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>9114</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -7687,12 +7695,12 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>GIAM (TO)</t>
+          <t>Log/Envio de Inconsistência (Mensal)</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" s="1" t="n">
-        <v>46212</v>
+        <v>46218</v>
       </c>
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
@@ -7701,7 +7709,7 @@
         </is>
       </c>
       <c r="O69" t="n">
-        <v>18076580</v>
+        <v>17399338</v>
       </c>
       <c r="P69" t="inlineStr">
         <is>
@@ -7715,11 +7723,11 @@
       </c>
       <c r="R69" t="inlineStr"/>
       <c r="S69" t="n">
-        <v>-2</v>
+        <v>-8</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>NOSSO NOVO SUPERMERCADO</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -7729,7 +7737,7 @@
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>Atraso do Cliente, cobrança ativa, GC e GM ciente do atraso - Data Comentário: 06/07/2026 15:55</t>
+          <t>Log de Inconsistências anexado via sistema - \\SRVMGC\DADOS\GOIAS\2026\5417 - COMERCIAL DE ALIMENTOS\EF - VAREJO\CONTROLE MENSAL\06 - JUNHO\ACESSÓRIA\INCONSISTENCIA\\5417-06-2026 Mensal 06-07-2026 141701.xlsx - Data Comentário: 06/07/2026 14:16</t>
         </is>
       </c>
       <c r="W69" t="inlineStr"/>
@@ -7756,11 +7764,11 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>5417</v>
+        <v>5617</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -7780,7 +7788,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -7810,7 +7818,7 @@
         </is>
       </c>
       <c r="O70" t="n">
-        <v>17399338</v>
+        <v>18120594</v>
       </c>
       <c r="P70" t="inlineStr">
         <is>
@@ -7828,7 +7836,7 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -7836,11 +7844,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>Log de Inconsistências anexado via sistema - \\SRVMGC\DADOS\GOIAS\2026\5417 - COMERCIAL DE ALIMENTOS\EF - VAREJO\CONTROLE MENSAL\06 - JUNHO\ACESSÓRIA\INCONSISTENCIA\\5417-06-2026 Mensal 06-07-2026 141701.xlsx - Data Comentário: 06/07/2026 14:16</t>
-        </is>
-      </c>
+      <c r="V70" t="inlineStr"/>
       <c r="W70" t="inlineStr"/>
       <c r="X70" t="inlineStr"/>
       <c r="Y70" t="inlineStr"/>
@@ -7893,10 +7897,10 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>7884</v>
+        <v>1793</v>
       </c>
       <c r="H71" t="n">
-        <v>9114</v>
+        <v>0</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -7905,21 +7909,25 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Log/Envio de Inconsistência (Mensal)</t>
+          <t>Mun - ISS Serv. Tomados</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
       <c r="L71" s="1" t="n">
-        <v>46218</v>
-      </c>
-      <c r="M71" t="inlineStr"/>
+        <v>46213</v>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
       <c r="N71" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O71" t="n">
-        <v>18120594</v>
+        <v>17407569</v>
       </c>
       <c r="P71" t="inlineStr">
         <is>
@@ -7933,7 +7941,7 @@
       </c>
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="n">
-        <v>-8</v>
+        <v>-3</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7945,7 +7953,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V71" t="inlineStr"/>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 08/07/2026 - Data Comentário: 06/07/2026 15:51</t>
+        </is>
+      </c>
       <c r="W71" t="inlineStr"/>
       <c r="X71" t="inlineStr"/>
       <c r="Y71" t="inlineStr"/>
@@ -7959,7 +7971,7 @@
       <c r="AE71" t="inlineStr"/>
       <c r="AF71" t="inlineStr">
         <is>
-          <t>Tarefa</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="AG71" t="inlineStr">
@@ -7970,11 +7982,11 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>5617</v>
+        <v>6224</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -7994,7 +8006,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8028,7 +8040,7 @@
         </is>
       </c>
       <c r="O72" t="n">
-        <v>17407569</v>
+        <v>17688661</v>
       </c>
       <c r="P72" t="inlineStr">
         <is>
@@ -8083,11 +8095,11 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>6224</v>
+        <v>6278</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>EMPORIO DOS FRIOS LTDA</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -8097,7 +8109,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Real - Anual</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -8107,7 +8119,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -8141,7 +8153,7 @@
         </is>
       </c>
       <c r="O73" t="n">
-        <v>17688661</v>
+        <v>17148664</v>
       </c>
       <c r="P73" t="inlineStr">
         <is>
@@ -8159,7 +8171,7 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -8196,11 +8208,11 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>6278</v>
+        <v>6279</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS LTDA</t>
+          <t>DIENNYFER DA S PEREIRA</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -8210,7 +8222,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Federal - Lucro Real - Anual</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -8220,7 +8232,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -8254,7 +8266,7 @@
         </is>
       </c>
       <c r="O74" t="n">
-        <v>17148664</v>
+        <v>17070843</v>
       </c>
       <c r="P74" t="inlineStr">
         <is>
@@ -8309,11 +8321,11 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>6279</v>
+        <v>6486</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>DIENNYFER DA S PEREIRA</t>
+          <t>PC GAMER GOIANIA LTDA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -8323,7 +8335,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -8333,7 +8345,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -8367,7 +8379,7 @@
         </is>
       </c>
       <c r="O75" t="n">
-        <v>17070843</v>
+        <v>16975950</v>
       </c>
       <c r="P75" t="inlineStr">
         <is>
@@ -8385,7 +8397,7 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>PC GAMER</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -8422,11 +8434,11 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>6486</v>
+        <v>6704</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>PC GAMER GOIANIA LTDA</t>
+          <t>TECNO COM INFORMATICA LTDA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -8480,7 +8492,7 @@
         </is>
       </c>
       <c r="O76" t="n">
-        <v>16975950</v>
+        <v>18085152</v>
       </c>
       <c r="P76" t="inlineStr">
         <is>
@@ -8498,7 +8510,7 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>PC GAMER</t>
+          <t>TECNO COM</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -8535,11 +8547,11 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>6704</v>
+        <v>6705</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>TECNO COM INFORMATICA LTDA</t>
+          <t>NARCIZO ALVES CORDEIRO</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -8549,7 +8561,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -8593,7 +8605,7 @@
         </is>
       </c>
       <c r="O77" t="n">
-        <v>18085152</v>
+        <v>17948926</v>
       </c>
       <c r="P77" t="inlineStr">
         <is>
@@ -8648,11 +8660,11 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>6705</v>
+        <v>6779</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>NARCIZO ALVES CORDEIRO</t>
+          <t>CORDEIRO E CIA LTDA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -8706,7 +8718,7 @@
         </is>
       </c>
       <c r="O78" t="n">
-        <v>17948926</v>
+        <v>18084953</v>
       </c>
       <c r="P78" t="inlineStr">
         <is>
@@ -8727,11 +8739,7 @@
           <t>TECNO COM</t>
         </is>
       </c>
-      <c r="U78" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+      <c r="U78" t="inlineStr"/>
       <c r="V78" t="inlineStr">
         <is>
           <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 08/07/2026 - Data Comentário: 06/07/2026 15:51</t>
@@ -8761,11 +8769,11 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>6779</v>
+        <v>6885</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CORDEIRO E CIA LTDA</t>
+          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -8819,7 +8827,7 @@
         </is>
       </c>
       <c r="O79" t="n">
-        <v>18084953</v>
+        <v>18134033</v>
       </c>
       <c r="P79" t="inlineStr">
         <is>
@@ -8837,7 +8845,7 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U79" t="inlineStr"/>
@@ -8870,11 +8878,11 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>6885</v>
+        <v>6703</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
+          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -8884,7 +8892,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -8898,7 +8906,7 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>1793</v>
+        <v>1796</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -8910,12 +8918,12 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Mun - ISS Serv. Tomados</t>
+          <t>Produtor Rural</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
       <c r="L80" s="1" t="n">
-        <v>46213</v>
+        <v>46211</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
@@ -8928,7 +8936,7 @@
         </is>
       </c>
       <c r="O80" t="n">
-        <v>18134033</v>
+        <v>18073096</v>
       </c>
       <c r="P80" t="inlineStr">
         <is>
@@ -8942,17 +8950,21 @@
       </c>
       <c r="R80" t="inlineStr"/>
       <c r="S80" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
-        </is>
-      </c>
-      <c r="U80" t="inlineStr"/>
+          <t>LIMA MOTA</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 08/07/2026 - Data Comentário: 06/07/2026 15:51</t>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 08/07/2026 - Data Comentário: 06/07/2026 14:49</t>
         </is>
       </c>
       <c r="W80" t="inlineStr"/>
@@ -8968,7 +8980,7 @@
       <c r="AE80" t="inlineStr"/>
       <c r="AF80" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Tarefa</t>
         </is>
       </c>
       <c r="AG80" t="inlineStr">
@@ -8979,11 +8991,11 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>6703</v>
+        <v>6705</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
+          <t>NARCIZO ALVES CORDEIRO</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -8993,7 +9005,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -9007,10 +9019,10 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>1796</v>
+        <v>6884</v>
       </c>
       <c r="H81" t="n">
-        <v>0</v>
+        <v>1788</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -9019,7 +9031,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Produtor Rural</t>
+          <t>Recebimento de NF Serviços Tomados</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -9037,7 +9049,7 @@
         </is>
       </c>
       <c r="O81" t="n">
-        <v>18073096</v>
+        <v>17949037</v>
       </c>
       <c r="P81" t="inlineStr">
         <is>
@@ -9055,7 +9067,7 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>LIMA MOTA</t>
+          <t>TECNO COM</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
@@ -9065,7 +9077,7 @@
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 08/07/2026 - Data Comentário: 06/07/2026 14:49</t>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 08/07/2026 - Data Comentário: 06/07/2026 15:52</t>
         </is>
       </c>
       <c r="W81" t="inlineStr"/>
@@ -9120,7 +9132,7 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>6884</v>
+        <v>6294</v>
       </c>
       <c r="H82" t="n">
         <v>1788</v>
@@ -9132,25 +9144,21 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Recebimento de NF Serviços Tomados</t>
+          <t>Recebimento NFCE</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
       <c r="L82" s="1" t="n">
-        <v>46211</v>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>08/07/2026</t>
-        </is>
-      </c>
+        <v>46216</v>
+      </c>
+      <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O82" t="n">
-        <v>17949037</v>
+        <v>17948997</v>
       </c>
       <c r="P82" t="inlineStr">
         <is>
@@ -9164,7 +9172,7 @@
       </c>
       <c r="R82" t="inlineStr"/>
       <c r="S82" t="n">
-        <v>-1</v>
+        <v>-6</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9176,11 +9184,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V82" t="inlineStr">
-        <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 08/07/2026 - Data Comentário: 06/07/2026 15:52</t>
-        </is>
-      </c>
+      <c r="V82" t="inlineStr"/>
       <c r="W82" t="inlineStr"/>
       <c r="X82" t="inlineStr"/>
       <c r="Y82" t="inlineStr"/>
@@ -9205,11 +9209,11 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>6705</v>
+        <v>5617</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>NARCIZO ALVES CORDEIRO</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -9219,7 +9223,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -9233,10 +9237,10 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>6294</v>
+        <v>11303</v>
       </c>
       <c r="H83" t="n">
-        <v>1788</v>
+        <v>0</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -9245,12 +9249,12 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Recebimento NFCE</t>
+          <t>Retorno do Check-List Fiscal</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
       <c r="L83" s="1" t="n">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr">
@@ -9259,7 +9263,7 @@
         </is>
       </c>
       <c r="O83" t="n">
-        <v>17948997</v>
+        <v>17407963</v>
       </c>
       <c r="P83" t="inlineStr">
         <is>
@@ -9273,11 +9277,11 @@
       </c>
       <c r="R83" t="inlineStr"/>
       <c r="S83" t="n">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
@@ -9310,11 +9314,11 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>5617</v>
+        <v>6885</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -9324,7 +9328,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -9364,7 +9368,7 @@
         </is>
       </c>
       <c r="O84" t="n">
-        <v>17407963</v>
+        <v>18134169</v>
       </c>
       <c r="P84" t="inlineStr">
         <is>
@@ -9382,14 +9386,10 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
-        </is>
-      </c>
-      <c r="U84" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>EMPORIO DOS FRIOS</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr"/>
       <c r="V84" t="inlineStr"/>
       <c r="W84" t="inlineStr"/>
       <c r="X84" t="inlineStr"/>
@@ -9415,11 +9415,11 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>6885</v>
+        <v>6548</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
+          <t>GOIAS SILAGEM LTDA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -9443,24 +9443,24 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>11303</v>
+        <v>951</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Retorno do Check-List Fiscal</t>
+          <t>Confirm Rec - ISS Tomados</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
       <c r="L85" s="1" t="n">
-        <v>46218</v>
+        <v>46213</v>
       </c>
       <c r="M85" t="inlineStr"/>
       <c r="N85" t="inlineStr">
@@ -9469,11 +9469,11 @@
         </is>
       </c>
       <c r="O85" t="n">
-        <v>18134169</v>
+        <v>17222400</v>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Cristina Leite</t>
+          <t>Victoria Virgens</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
@@ -9483,15 +9483,23 @@
       </c>
       <c r="R85" t="inlineStr"/>
       <c r="S85" t="n">
-        <v>-8</v>
+        <v>-3</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
-        </is>
-      </c>
-      <c r="U85" t="inlineStr"/>
-      <c r="V85" t="inlineStr"/>
+          <t>GOIAS SILAGEM</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1867] sendo a ultima baixa feita [1867]-07/07/2026 15:21:27.. - Data Comentário: 07/07/2026 15:20</t>
+        </is>
+      </c>
       <c r="W85" t="inlineStr"/>
       <c r="X85" t="inlineStr"/>
       <c r="Y85" t="inlineStr"/>
@@ -9505,22 +9513,18 @@
       <c r="AE85" t="inlineStr"/>
       <c r="AF85" t="inlineStr">
         <is>
-          <t>Tarefa</t>
-        </is>
-      </c>
-      <c r="AG85" t="inlineStr">
-        <is>
-          <t>Ricardo Fischer</t>
-        </is>
-      </c>
+          <t>Imposto</t>
+        </is>
+      </c>
+      <c r="AG85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>6548</v>
+        <v>6703</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM LTDA</t>
+          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -9530,7 +9534,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -9570,7 +9574,7 @@
         </is>
       </c>
       <c r="O86" t="n">
-        <v>17222400</v>
+        <v>17941154</v>
       </c>
       <c r="P86" t="inlineStr">
         <is>
@@ -9588,7 +9592,7 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM</t>
+          <t>LIMA MOTA</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
@@ -9598,7 +9602,7 @@
       </c>
       <c r="V86" t="inlineStr">
         <is>
-          <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1867] sendo a ultima baixa feita [1867]-07/07/2026 15:21:27.. - Data Comentário: 07/07/2026 15:20</t>
+          <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1793] sendo a ultima baixa feita [1793]-03/07/2026 12:03:31.. - Data Comentário: 03/07/2026 12:02</t>
         </is>
       </c>
       <c r="W86" t="inlineStr"/>
@@ -9621,11 +9625,11 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>6703</v>
+        <v>6278</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
+          <t>EMPORIO DOS FRIOS LTDA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -9635,7 +9639,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - Lucro Real - Anual</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -9649,19 +9653,19 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>951</v>
+        <v>6017</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Confirm Rec - ISS Tomados</t>
+          <t>Cobrança de inventário SPED ICMS</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -9675,11 +9679,11 @@
         </is>
       </c>
       <c r="O87" t="n">
-        <v>17941154</v>
+        <v>17539760</v>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Victoria Virgens</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
@@ -9693,7 +9697,7 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>LIMA MOTA</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
@@ -9701,11 +9705,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V87" t="inlineStr">
-        <is>
-          <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1793] sendo a ultima baixa feita [1793]-03/07/2026 12:03:31.. - Data Comentário: 03/07/2026 12:02</t>
-        </is>
-      </c>
+      <c r="V87" t="inlineStr"/>
       <c r="W87" t="inlineStr"/>
       <c r="X87" t="inlineStr"/>
       <c r="Y87" t="inlineStr"/>
@@ -9719,18 +9719,18 @@
       <c r="AE87" t="inlineStr"/>
       <c r="AF87" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Tarefa</t>
         </is>
       </c>
       <c r="AG87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>6278</v>
+        <v>6404</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS LTDA</t>
+          <t>SOLAR INVESTIMENTOS LTDA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -9740,7 +9740,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Federal - Lucro Real - Anual</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -9780,11 +9780,11 @@
         </is>
       </c>
       <c r="O88" t="n">
-        <v>17539760</v>
+        <v>16962256</v>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
@@ -9798,7 +9798,7 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>SOLAR INVESTIMENTOS</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
@@ -9827,11 +9827,11 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>6404</v>
+        <v>6627</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS LTDA</t>
+          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -9881,11 +9881,11 @@
         </is>
       </c>
       <c r="O89" t="n">
-        <v>16962256</v>
+        <v>17042432</v>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
@@ -9899,7 +9899,7 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS</t>
+          <t xml:space="preserve">GTG </t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
@@ -9928,11 +9928,11 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>6627</v>
+        <v>6704</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
+          <t>TECNO COM INFORMATICA LTDA</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -9947,7 +9947,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -9982,7 +9982,7 @@
         </is>
       </c>
       <c r="O90" t="n">
-        <v>17042432</v>
+        <v>17952390</v>
       </c>
       <c r="P90" t="inlineStr">
         <is>
@@ -10000,7 +10000,7 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
+          <t>TECNO COM</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
@@ -10029,11 +10029,11 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>6704</v>
+        <v>6885</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>TECNO COM INFORMATICA LTDA</t>
+          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -10043,7 +10043,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -10083,7 +10083,7 @@
         </is>
       </c>
       <c r="O91" t="n">
-        <v>17952390</v>
+        <v>18128767</v>
       </c>
       <c r="P91" t="inlineStr">
         <is>
@@ -10101,14 +10101,10 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
-        </is>
-      </c>
-      <c r="U91" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>EMPORIO DOS FRIOS</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr"/>
       <c r="V91" t="inlineStr"/>
       <c r="W91" t="inlineStr"/>
       <c r="X91" t="inlineStr"/>
@@ -10130,11 +10126,11 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>6885</v>
+        <v>6949</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
+          <t>TEC GRUA LOCAÇÃO E COMERCIO DE EQUIPAMENTOS PARA CONSTRUÇÃO LTDA</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -10144,7 +10140,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -10154,11 +10150,11 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Reynaldo Santos</t>
         </is>
       </c>
       <c r="G92" t="n">
-        <v>6017</v>
+        <v>6215</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
@@ -10170,21 +10166,21 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Cobrança de inventário SPED ICMS</t>
+          <t>DEC - Conferência 1º Quinzena</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
       <c r="L92" s="1" t="n">
-        <v>46213</v>
+        <v>46210</v>
       </c>
       <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr">
         <is>
-          <t>06/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
       <c r="O92" t="n">
-        <v>18128767</v>
+        <v>18178161</v>
       </c>
       <c r="P92" t="inlineStr">
         <is>
@@ -10198,11 +10194,11 @@
       </c>
       <c r="R92" t="inlineStr"/>
       <c r="S92" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>TEC GRUA</t>
         </is>
       </c>
       <c r="U92" t="inlineStr"/>
@@ -10220,18 +10216,18 @@
       <c r="AE92" t="inlineStr"/>
       <c r="AF92" t="inlineStr">
         <is>
-          <t>Tarefa</t>
+          <t>Obrigação Acessória</t>
         </is>
       </c>
       <c r="AG92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>6949</v>
+        <v>6962</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>TEC GRUA LOCAÇÃO E COMERCIO DE EQUIPAMENTOS PARA CONSTRUÇÃO LTDA</t>
+          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -10281,11 +10277,11 @@
         </is>
       </c>
       <c r="O93" t="n">
-        <v>18178161</v>
+        <v>18188744</v>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
@@ -10299,7 +10295,7 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>TEC GRUA</t>
+          <t>PROMOTORAS GYN</t>
         </is>
       </c>
       <c r="U93" t="inlineStr"/>
@@ -10324,11 +10320,11 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
+          <t>PROMOTORAS GYN LTDA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -10378,7 +10374,7 @@
         </is>
       </c>
       <c r="O94" t="n">
-        <v>18188744</v>
+        <v>18188650</v>
       </c>
       <c r="P94" t="inlineStr">
         <is>
@@ -10421,11 +10417,11 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>6963</v>
+        <v>5417</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN LTDA</t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -10445,11 +10441,11 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G95" t="n">
-        <v>6215</v>
+        <v>11746</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -10461,25 +10457,25 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>DEC - Conferência 1º Quinzena</t>
+          <t>Distribuição de Lucro Mensal</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
       <c r="L95" s="1" t="n">
-        <v>46210</v>
+        <v>46213</v>
       </c>
       <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
       <c r="O95" t="n">
-        <v>18188650</v>
+        <v>17994309</v>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
@@ -10489,14 +10485,18 @@
       </c>
       <c r="R95" t="inlineStr"/>
       <c r="S95" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN</t>
-        </is>
-      </c>
-      <c r="U95" t="inlineStr"/>
+          <t>NOSSO NOVO SUPERMERCADO</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V95" t="inlineStr"/>
       <c r="W95" t="inlineStr"/>
       <c r="X95" t="inlineStr"/>
@@ -10511,18 +10511,18 @@
       <c r="AE95" t="inlineStr"/>
       <c r="AF95" t="inlineStr">
         <is>
-          <t>Obrigação Acessória</t>
+          <t>Tarefa</t>
         </is>
       </c>
       <c r="AG95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>5417</v>
+        <v>5617</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -10542,7 +10542,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -10572,7 +10572,7 @@
         </is>
       </c>
       <c r="O96" t="n">
-        <v>17994309</v>
+        <v>18001695</v>
       </c>
       <c r="P96" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
@@ -10619,11 +10619,11 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>5617</v>
+        <v>6224</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -10643,7 +10643,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -10673,11 +10673,11 @@
         </is>
       </c>
       <c r="O97" t="n">
-        <v>18001695</v>
+        <v>18004470</v>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr">
@@ -10720,11 +10720,11 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>6224</v>
+        <v>6278</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>EMPORIO DOS FRIOS LTDA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -10734,7 +10734,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Real - Anual</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -10744,7 +10744,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -10774,11 +10774,11 @@
         </is>
       </c>
       <c r="O98" t="n">
-        <v>18004470</v>
+        <v>17994320</v>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U98" t="inlineStr">
@@ -10821,11 +10821,11 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>6278</v>
+        <v>6279</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS LTDA</t>
+          <t>DIENNYFER DA S PEREIRA</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -10835,7 +10835,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Federal - Lucro Real - Anual</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -10845,7 +10845,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -10875,7 +10875,7 @@
         </is>
       </c>
       <c r="O99" t="n">
-        <v>17994320</v>
+        <v>17995240</v>
       </c>
       <c r="P99" t="inlineStr">
         <is>
@@ -10922,11 +10922,11 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>6279</v>
+        <v>6404</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>DIENNYFER DA S PEREIRA</t>
+          <t>SOLAR INVESTIMENTOS LTDA</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -10946,7 +10946,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -10976,11 +10976,11 @@
         </is>
       </c>
       <c r="O100" t="n">
-        <v>17995240</v>
+        <v>17994673</v>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
@@ -10994,7 +10994,7 @@
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>SOLAR INVESTIMENTOS</t>
         </is>
       </c>
       <c r="U100" t="inlineStr">
@@ -11023,11 +11023,11 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>6404</v>
+        <v>6486</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS LTDA</t>
+          <t>PC GAMER GOIANIA LTDA</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -11037,7 +11037,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -11077,7 +11077,7 @@
         </is>
       </c>
       <c r="O101" t="n">
-        <v>17994673</v>
+        <v>17994807</v>
       </c>
       <c r="P101" t="inlineStr">
         <is>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS</t>
+          <t>PC GAMER</t>
         </is>
       </c>
       <c r="U101" t="inlineStr">
@@ -11124,11 +11124,11 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>6486</v>
+        <v>6548</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>PC GAMER GOIANIA LTDA</t>
+          <t>GOIAS SILAGEM LTDA</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -11178,11 +11178,11 @@
         </is>
       </c>
       <c r="O102" t="n">
-        <v>17994807</v>
+        <v>18006049</v>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
@@ -11196,7 +11196,7 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>PC GAMER</t>
+          <t>GOIAS SILAGEM</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
@@ -11225,11 +11225,11 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>6548</v>
+        <v>6628</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM LTDA</t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -11239,12 +11239,12 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -11279,7 +11279,7 @@
         </is>
       </c>
       <c r="O103" t="n">
-        <v>18006049</v>
+        <v>18003254</v>
       </c>
       <c r="P103" t="inlineStr">
         <is>
@@ -11297,7 +11297,7 @@
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM</t>
+          <t xml:space="preserve">GTG </t>
         </is>
       </c>
       <c r="U103" t="inlineStr">
@@ -11326,11 +11326,11 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>6628</v>
+        <v>6703</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -11340,12 +11340,12 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -11380,7 +11380,7 @@
         </is>
       </c>
       <c r="O104" t="n">
-        <v>18003254</v>
+        <v>18004015</v>
       </c>
       <c r="P104" t="inlineStr">
         <is>
@@ -11398,7 +11398,7 @@
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
+          <t>LIMA MOTA</t>
         </is>
       </c>
       <c r="U104" t="inlineStr">
@@ -11427,11 +11427,11 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>6703</v>
+        <v>6704</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
+          <t>TECNO COM INFORMATICA LTDA</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -11441,7 +11441,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -11481,7 +11481,7 @@
         </is>
       </c>
       <c r="O105" t="n">
-        <v>18004015</v>
+        <v>17995162</v>
       </c>
       <c r="P105" t="inlineStr">
         <is>
@@ -11499,7 +11499,7 @@
       </c>
       <c r="T105" t="inlineStr">
         <is>
-          <t>LIMA MOTA</t>
+          <t>TECNO COM</t>
         </is>
       </c>
       <c r="U105" t="inlineStr">
@@ -11528,11 +11528,11 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>6704</v>
+        <v>6705</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>TECNO COM INFORMATICA LTDA</t>
+          <t>NARCIZO ALVES CORDEIRO</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -11542,7 +11542,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -11582,7 +11582,7 @@
         </is>
       </c>
       <c r="O106" t="n">
-        <v>17995162</v>
+        <v>18004026</v>
       </c>
       <c r="P106" t="inlineStr">
         <is>
@@ -11629,11 +11629,11 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>6705</v>
+        <v>6949</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>NARCIZO ALVES CORDEIRO</t>
+          <t>TEC GRUA LOCAÇÃO E COMERCIO DE EQUIPAMENTOS PARA CONSTRUÇÃO LTDA</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -11643,7 +11643,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -11653,70 +11653,77 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Reynaldo Santos</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>11746</v>
+        <v>11615</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Distribuição de Lucro Mensal</t>
+          <t>Envio de ATA de Implantação - CTB I</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
       <c r="L107" s="1" t="n">
-        <v>46213</v>
-      </c>
-      <c r="M107" t="inlineStr"/>
+        <v>46206</v>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
       <c r="N107" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O107" t="n">
-        <v>18004026</v>
-      </c>
-      <c r="P107" t="inlineStr">
-        <is>
-          <t>Sergio Fernandes</t>
-        </is>
-      </c>
+        <v>18166586</v>
+      </c>
+      <c r="P107" t="inlineStr"/>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>Em Aberto</t>
-        </is>
-      </c>
-      <c r="R107" t="inlineStr"/>
+          <t>Baixado</t>
+        </is>
+      </c>
+      <c r="R107" s="1" t="n">
+        <v>46206.43215109954</v>
+      </c>
       <c r="S107" t="n">
-        <v>-3</v>
+        <v>4</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
-        </is>
-      </c>
-      <c r="U107" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="V107" t="inlineStr"/>
+          <t>TEC GRUA</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr"/>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 26/06/2026 
+Aguardando agendamento das implantações - Data Comentário: 18/06/2026 17:44</t>
+        </is>
+      </c>
       <c r="W107" t="inlineStr"/>
       <c r="X107" t="inlineStr"/>
       <c r="Y107" t="inlineStr"/>
       <c r="Z107" t="n">
         <v>0</v>
       </c>
-      <c r="AA107" t="inlineStr"/>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>Erika Santana</t>
+        </is>
+      </c>
       <c r="AB107" t="inlineStr"/>
       <c r="AC107" t="inlineStr"/>
       <c r="AD107" t="inlineStr"/>
@@ -11730,11 +11737,11 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>6949</v>
+        <v>6962</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>TEC GRUA LOCAÇÃO E COMERCIO DE EQUIPAMENTOS PARA CONSTRUÇÃO LTDA</t>
+          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -11777,18 +11784,14 @@
       <c r="L108" s="1" t="n">
         <v>46206</v>
       </c>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>26/06/2026</t>
-        </is>
-      </c>
+      <c r="M108" t="inlineStr"/>
       <c r="N108" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O108" t="n">
-        <v>18166586</v>
+        <v>18186559</v>
       </c>
       <c r="P108" t="inlineStr"/>
       <c r="Q108" t="inlineStr">
@@ -11797,21 +11800,20 @@
         </is>
       </c>
       <c r="R108" s="1" t="n">
-        <v>46206.43215109954</v>
+        <v>46206.43205978009</v>
       </c>
       <c r="S108" t="n">
         <v>4</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>TEC GRUA</t>
+          <t>PROMOTORAS GYN</t>
         </is>
       </c>
       <c r="U108" t="inlineStr"/>
       <c r="V108" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 26/06/2026 
-Aguardando agendamento das implantações - Data Comentário: 18/06/2026 17:44</t>
+          <t>Rotina Para Criar Tarefas Dos Clientes Novos - CodCliente: 6962; Tarefa Incluida: 11615; Vencimento: 17/06/2026 00:00:00; UsuarioResponsavel: erikas - Data Comentário: 17/06/2026 11:09</t>
         </is>
       </c>
       <c r="W108" t="inlineStr"/>
@@ -11838,11 +11840,11 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
+          <t>PROMOTORAS GYN LTDA</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -11892,7 +11894,7 @@
         </is>
       </c>
       <c r="O109" t="n">
-        <v>18186559</v>
+        <v>18186560</v>
       </c>
       <c r="P109" t="inlineStr"/>
       <c r="Q109" t="inlineStr">
@@ -11901,7 +11903,7 @@
         </is>
       </c>
       <c r="R109" s="1" t="n">
-        <v>46206.43205978009</v>
+        <v>46206.43206049768</v>
       </c>
       <c r="S109" t="n">
         <v>4</v>
@@ -11914,7 +11916,7 @@
       <c r="U109" t="inlineStr"/>
       <c r="V109" t="inlineStr">
         <is>
-          <t>Rotina Para Criar Tarefas Dos Clientes Novos - CodCliente: 6962; Tarefa Incluida: 11615; Vencimento: 17/06/2026 00:00:00; UsuarioResponsavel: erikas - Data Comentário: 17/06/2026 11:09</t>
+          <t>Rotina Para Criar Tarefas Dos Clientes Novos - CodCliente: 6963; Tarefa Incluida: 11615; Vencimento: 17/06/2026 00:00:00; UsuarioResponsavel: erikas - Data Comentário: 17/06/2026 11:09</t>
         </is>
       </c>
       <c r="W109" t="inlineStr"/>
@@ -11941,11 +11943,11 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>6963</v>
+        <v>6548</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN LTDA</t>
+          <t>GOIAS SILAGEM LTDA</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -11965,11 +11967,11 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G110" t="n">
-        <v>11615</v>
+        <v>11299</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -11981,12 +11983,12 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Envio de ATA de Implantação - CTB I</t>
+          <t>Retorno do Check-List</t>
         </is>
       </c>
       <c r="K110" t="inlineStr"/>
       <c r="L110" s="1" t="n">
-        <v>46206</v>
+        <v>46218</v>
       </c>
       <c r="M110" t="inlineStr"/>
       <c r="N110" t="inlineStr">
@@ -11995,31 +11997,35 @@
         </is>
       </c>
       <c r="O110" t="n">
-        <v>18186560</v>
-      </c>
-      <c r="P110" t="inlineStr"/>
+        <v>17968039</v>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Thais Souza</t>
+        </is>
+      </c>
       <c r="Q110" t="inlineStr">
         <is>
           <t>Baixado</t>
         </is>
       </c>
       <c r="R110" s="1" t="n">
-        <v>46206.43206049768</v>
+        <v>46204.75352534722</v>
       </c>
       <c r="S110" t="n">
-        <v>4</v>
+        <v>-8</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN</t>
-        </is>
-      </c>
-      <c r="U110" t="inlineStr"/>
-      <c r="V110" t="inlineStr">
-        <is>
-          <t>Rotina Para Criar Tarefas Dos Clientes Novos - CodCliente: 6963; Tarefa Incluida: 11615; Vencimento: 17/06/2026 00:00:00; UsuarioResponsavel: erikas - Data Comentário: 17/06/2026 11:09</t>
-        </is>
-      </c>
+          <t>GOIAS SILAGEM</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr"/>
       <c r="W110" t="inlineStr"/>
       <c r="X110" t="inlineStr"/>
       <c r="Y110" t="inlineStr"/>
@@ -12028,7 +12034,7 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>Erika Santana</t>
+          <t>Juan Rodrigues</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr"/>
@@ -12040,15 +12046,19 @@
           <t>Tarefa</t>
         </is>
       </c>
-      <c r="AG110" t="inlineStr"/>
+      <c r="AG110" t="inlineStr">
+        <is>
+          <t>Erika Santana</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM LTDA</t>
+          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -12063,7 +12073,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -12098,11 +12108,11 @@
         </is>
       </c>
       <c r="O111" t="n">
-        <v>17968039</v>
+        <v>17042639</v>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Thais Souza</t>
+          <t>Nathalia Lourenco</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr">
@@ -12111,14 +12121,14 @@
         </is>
       </c>
       <c r="R111" s="1" t="n">
-        <v>46204.75352534722</v>
+        <v>46204.75352809028</v>
       </c>
       <c r="S111" t="n">
         <v>-8</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM</t>
+          <t xml:space="preserve">GTG </t>
         </is>
       </c>
       <c r="U111" t="inlineStr">
@@ -12149,17 +12159,17 @@
       </c>
       <c r="AG111" t="inlineStr">
         <is>
-          <t>Erika Santana</t>
+          <t>Isabella Nascimento</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -12169,7 +12179,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -12209,7 +12219,7 @@
         </is>
       </c>
       <c r="O112" t="n">
-        <v>17042639</v>
+        <v>16960108</v>
       </c>
       <c r="P112" t="inlineStr">
         <is>
@@ -12222,7 +12232,7 @@
         </is>
       </c>
       <c r="R112" s="1" t="n">
-        <v>46204.75352809028</v>
+        <v>46204.7535284375</v>
       </c>
       <c r="S112" t="n">
         <v>-8</v>
@@ -12266,11 +12276,11 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>6628</v>
+        <v>6945</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -12320,11 +12330,11 @@
         </is>
       </c>
       <c r="O113" t="n">
-        <v>16960108</v>
+        <v>18163697</v>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Nathalia Lourenco</t>
+          <t>Laisa Rocha</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr">
@@ -12333,21 +12343,17 @@
         </is>
       </c>
       <c r="R113" s="1" t="n">
-        <v>46204.7535284375</v>
+        <v>46204.7535334838</v>
       </c>
       <c r="S113" t="n">
         <v>-8</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
-        </is>
-      </c>
-      <c r="U113" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>BRASIL DISTRIBUIDORA</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr"/>
       <c r="V113" t="inlineStr"/>
       <c r="W113" t="inlineStr"/>
       <c r="X113" t="inlineStr"/>
@@ -12377,11 +12383,11 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>6945</v>
+        <v>6962</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
+          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -12391,17 +12397,17 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Reynaldo Santos</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -12431,11 +12437,11 @@
         </is>
       </c>
       <c r="O114" t="n">
-        <v>18163697</v>
+        <v>18187976</v>
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Laisa Rocha</t>
+          <t>Mirian Lima</t>
         </is>
       </c>
       <c r="Q114" t="inlineStr">
@@ -12444,14 +12450,14 @@
         </is>
       </c>
       <c r="R114" s="1" t="n">
-        <v>46204.7535334838</v>
+        <v>46204.75353387732</v>
       </c>
       <c r="S114" t="n">
         <v>-8</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA</t>
+          <t>PROMOTORAS GYN</t>
         </is>
       </c>
       <c r="U114" t="inlineStr"/>
@@ -12484,11 +12490,11 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
+          <t>PROMOTORAS GYN LTDA</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -12538,7 +12544,7 @@
         </is>
       </c>
       <c r="O115" t="n">
-        <v>18187976</v>
+        <v>18187914</v>
       </c>
       <c r="P115" t="inlineStr">
         <is>
@@ -12551,7 +12557,7 @@
         </is>
       </c>
       <c r="R115" s="1" t="n">
-        <v>46204.75353387732</v>
+        <v>46204.75353515046</v>
       </c>
       <c r="S115" t="n">
         <v>-8</v>
@@ -12591,11 +12597,11 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>6963</v>
+        <v>5417</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN LTDA</t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -12615,18 +12621,18 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G116" t="n">
-        <v>11299</v>
+        <v>11297</v>
       </c>
       <c r="H116" t="n">
         <v>0</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL INDUSTRIA</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -12645,11 +12651,11 @@
         </is>
       </c>
       <c r="O116" t="n">
-        <v>18187914</v>
+        <v>17399442</v>
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Mirian Lima</t>
+          <t>Eveny Silva</t>
         </is>
       </c>
       <c r="Q116" t="inlineStr">
@@ -12658,17 +12664,21 @@
         </is>
       </c>
       <c r="R116" s="1" t="n">
-        <v>46204.75353515046</v>
+        <v>46204.75350494213</v>
       </c>
       <c r="S116" t="n">
         <v>-8</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN</t>
-        </is>
-      </c>
-      <c r="U116" t="inlineStr"/>
+          <t>NOSSO NOVO SUPERMERCADO</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V116" t="inlineStr"/>
       <c r="W116" t="inlineStr"/>
       <c r="X116" t="inlineStr"/>
@@ -12692,17 +12702,17 @@
       </c>
       <c r="AG116" t="inlineStr">
         <is>
-          <t>Isabella Nascimento</t>
+          <t>Karina Santos</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>5417</v>
+        <v>5617</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -12722,7 +12732,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -12752,11 +12762,11 @@
         </is>
       </c>
       <c r="O117" t="n">
-        <v>17399442</v>
+        <v>17407953</v>
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Eveny Silva</t>
+          <t>Jackson Silva</t>
         </is>
       </c>
       <c r="Q117" t="inlineStr">
@@ -12765,14 +12775,14 @@
         </is>
       </c>
       <c r="R117" s="1" t="n">
-        <v>46204.75350494213</v>
+        <v>46204.75351072917</v>
       </c>
       <c r="S117" t="n">
         <v>-8</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U117" t="inlineStr">
@@ -12803,17 +12813,17 @@
       </c>
       <c r="AG117" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>5617</v>
+        <v>6224</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -12833,7 +12843,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -12863,7 +12873,7 @@
         </is>
       </c>
       <c r="O118" t="n">
-        <v>17407953</v>
+        <v>17689061</v>
       </c>
       <c r="P118" t="inlineStr">
         <is>
@@ -12876,7 +12886,7 @@
         </is>
       </c>
       <c r="R118" s="1" t="n">
-        <v>46204.75351072917</v>
+        <v>46204.75352068287</v>
       </c>
       <c r="S118" t="n">
         <v>-8</v>
@@ -12920,11 +12930,11 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>6224</v>
+        <v>6278</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>EMPORIO DOS FRIOS LTDA</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -12934,7 +12944,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Real - Anual</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -12944,7 +12954,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -12974,11 +12984,11 @@
         </is>
       </c>
       <c r="O119" t="n">
-        <v>17689061</v>
+        <v>17539888</v>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Jackson Silva</t>
+          <t>Isabela Lemos</t>
         </is>
       </c>
       <c r="Q119" t="inlineStr">
@@ -12987,14 +12997,14 @@
         </is>
       </c>
       <c r="R119" s="1" t="n">
-        <v>46204.75352068287</v>
+        <v>46204.75352175926</v>
       </c>
       <c r="S119" t="n">
         <v>-8</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U119" t="inlineStr">
@@ -13025,17 +13035,17 @@
       </c>
       <c r="AG119" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>6278</v>
+        <v>6704</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS LTDA</t>
+          <t>TECNO COM INFORMATICA LTDA</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -13045,7 +13055,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Federal - Lucro Real - Anual</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -13085,11 +13095,11 @@
         </is>
       </c>
       <c r="O120" t="n">
-        <v>17539888</v>
+        <v>17955432</v>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Isabela Lemos</t>
+          <t>Paulo Silva</t>
         </is>
       </c>
       <c r="Q120" t="inlineStr">
@@ -13098,14 +13108,14 @@
         </is>
       </c>
       <c r="R120" s="1" t="n">
-        <v>46204.75352175926</v>
+        <v>46204.75353024306</v>
       </c>
       <c r="S120" t="n">
         <v>-8</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>TECNO COM</t>
         </is>
       </c>
       <c r="U120" t="inlineStr">
@@ -13142,11 +13152,11 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>6704</v>
+        <v>6705</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>TECNO COM INFORMATICA LTDA</t>
+          <t>NARCIZO ALVES CORDEIRO</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -13156,7 +13166,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -13196,7 +13206,7 @@
         </is>
       </c>
       <c r="O121" t="n">
-        <v>17955432</v>
+        <v>17955272</v>
       </c>
       <c r="P121" t="inlineStr">
         <is>
@@ -13209,7 +13219,7 @@
         </is>
       </c>
       <c r="R121" s="1" t="n">
-        <v>46204.75353024306</v>
+        <v>46204.7535309838</v>
       </c>
       <c r="S121" t="n">
         <v>-8</v>
@@ -13253,11 +13263,11 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>6705</v>
+        <v>6779</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>NARCIZO ALVES CORDEIRO</t>
+          <t>CORDEIRO E CIA LTDA</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -13307,7 +13317,7 @@
         </is>
       </c>
       <c r="O122" t="n">
-        <v>17955272</v>
+        <v>18056830</v>
       </c>
       <c r="P122" t="inlineStr">
         <is>
@@ -13320,7 +13330,7 @@
         </is>
       </c>
       <c r="R122" s="1" t="n">
-        <v>46204.7535309838</v>
+        <v>46204.75353240741</v>
       </c>
       <c r="S122" t="n">
         <v>-8</v>
@@ -13330,11 +13340,7 @@
           <t>TECNO COM</t>
         </is>
       </c>
-      <c r="U122" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+      <c r="U122" t="inlineStr"/>
       <c r="V122" t="inlineStr"/>
       <c r="W122" t="inlineStr"/>
       <c r="X122" t="inlineStr"/>
@@ -13364,11 +13370,11 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>6779</v>
+        <v>6885</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>CORDEIRO E CIA LTDA</t>
+          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -13418,11 +13424,11 @@
         </is>
       </c>
       <c r="O123" t="n">
-        <v>18056830</v>
+        <v>18128901</v>
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Paulo Silva</t>
+          <t>Isabela Lemos</t>
         </is>
       </c>
       <c r="Q123" t="inlineStr">
@@ -13431,14 +13437,14 @@
         </is>
       </c>
       <c r="R123" s="1" t="n">
-        <v>46204.75353240741</v>
+        <v>46204.75353278935</v>
       </c>
       <c r="S123" t="n">
         <v>-8</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U123" t="inlineStr"/>
@@ -13471,11 +13477,11 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>6885</v>
+        <v>6628</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -13490,7 +13496,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -13499,57 +13505,61 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>11297</v>
+        <v>11817</v>
       </c>
       <c r="H124" t="n">
         <v>0</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>Retorno do Check-List</t>
+          <t>Alteração dados cadastrais</t>
         </is>
       </c>
       <c r="K124" t="inlineStr"/>
       <c r="L124" s="1" t="n">
-        <v>46218</v>
+        <v>46205</v>
       </c>
       <c r="M124" t="inlineStr"/>
       <c r="N124" t="inlineStr">
         <is>
-          <t>06/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
       <c r="O124" t="n">
-        <v>18128901</v>
-      </c>
-      <c r="P124" t="inlineStr">
-        <is>
-          <t>Isabela Lemos</t>
-        </is>
-      </c>
+        <v>18199226</v>
+      </c>
+      <c r="P124" t="inlineStr"/>
       <c r="Q124" t="inlineStr">
         <is>
           <t>Baixado</t>
         </is>
       </c>
       <c r="R124" s="1" t="n">
-        <v>46204.75353278935</v>
+        <v>46205.599529375</v>
       </c>
       <c r="S124" t="n">
-        <v>-8</v>
+        <v>5</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
-        </is>
-      </c>
-      <c r="U124" t="inlineStr"/>
-      <c r="V124" t="inlineStr"/>
+          <t xml:space="preserve">GTG </t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Aplicação de promoção. - Data Comentário: 02/07/2026 11:13</t>
+        </is>
+      </c>
       <c r="W124" t="inlineStr"/>
       <c r="X124" t="inlineStr"/>
       <c r="Y124" t="inlineStr"/>
@@ -13558,7 +13568,7 @@
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>Juan Rodrigues</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr"/>
@@ -13570,19 +13580,15 @@
           <t>Tarefa</t>
         </is>
       </c>
-      <c r="AG124" t="inlineStr">
-        <is>
-          <t>Fernanda Araujo</t>
-        </is>
-      </c>
+      <c r="AG124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>6628</v>
+        <v>5417</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -13592,21 +13598,21 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G125" t="n">
-        <v>11817</v>
+        <v>11815</v>
       </c>
       <c r="H125" t="n">
         <v>0</v>
@@ -13618,12 +13624,12 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Alteração dados cadastrais</t>
+          <t>Cálculo de férias individuais</t>
         </is>
       </c>
       <c r="K125" t="inlineStr"/>
       <c r="L125" s="1" t="n">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="M125" t="inlineStr"/>
       <c r="N125" t="inlineStr">
@@ -13632,7 +13638,7 @@
         </is>
       </c>
       <c r="O125" t="n">
-        <v>18199226</v>
+        <v>18196299</v>
       </c>
       <c r="P125" t="inlineStr"/>
       <c r="Q125" t="inlineStr">
@@ -13641,14 +13647,14 @@
         </is>
       </c>
       <c r="R125" s="1" t="n">
-        <v>46205.599529375</v>
+        <v>46204.71542079861</v>
       </c>
       <c r="S125" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
+          <t>NOSSO NOVO SUPERMERCADO</t>
         </is>
       </c>
       <c r="U125" t="inlineStr">
@@ -13656,11 +13662,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V125" t="inlineStr">
-        <is>
-          <t>Aplicação de promoção. - Data Comentário: 02/07/2026 11:13</t>
-        </is>
-      </c>
+      <c r="V125" t="inlineStr"/>
       <c r="W125" t="inlineStr"/>
       <c r="X125" t="inlineStr"/>
       <c r="Y125" t="inlineStr"/>
@@ -13669,7 +13671,7 @@
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Mikael Teixeira</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr"/>
@@ -13739,7 +13741,7 @@
         </is>
       </c>
       <c r="O126" t="n">
-        <v>18196299</v>
+        <v>18196300</v>
       </c>
       <c r="P126" t="inlineStr"/>
       <c r="Q126" t="inlineStr">
@@ -13748,7 +13750,7 @@
         </is>
       </c>
       <c r="R126" s="1" t="n">
-        <v>46204.71542079861</v>
+        <v>46204.71542134259</v>
       </c>
       <c r="S126" t="n">
         <v>6</v>
@@ -13788,11 +13790,11 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>5417</v>
+        <v>6779</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>CORDEIRO E CIA LTDA</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -13802,7 +13804,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -13812,7 +13814,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -13842,7 +13844,7 @@
         </is>
       </c>
       <c r="O127" t="n">
-        <v>18196300</v>
+        <v>18195927</v>
       </c>
       <c r="P127" t="inlineStr"/>
       <c r="Q127" t="inlineStr">
@@ -13851,22 +13853,22 @@
         </is>
       </c>
       <c r="R127" s="1" t="n">
-        <v>46204.71542134259</v>
+        <v>46204.48446469908</v>
       </c>
       <c r="S127" t="n">
         <v>6</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
-        </is>
-      </c>
-      <c r="U127" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="V127" t="inlineStr"/>
+          <t>TECNO COM</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr"/>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Férias de 02/07/2026 a 10/07/2026. - Data Comentário: 01/07/2026 11:26</t>
+        </is>
+      </c>
       <c r="W127" t="inlineStr"/>
       <c r="X127" t="inlineStr"/>
       <c r="Y127" t="inlineStr"/>
@@ -13875,7 +13877,7 @@
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>Mikael Teixeira</t>
+          <t>Kaique Souza</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr"/>
@@ -13891,11 +13893,11 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>6779</v>
+        <v>5417</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>CORDEIRO E CIA LTDA</t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -13905,7 +13907,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -13915,14 +13917,14 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G128" t="n">
-        <v>11815</v>
+        <v>5800</v>
       </c>
       <c r="H128" t="n">
-        <v>0</v>
+        <v>5776</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
@@ -13931,43 +13933,55 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>Cálculo de férias individuais</t>
+          <t>CCT Lançamento Sd.508</t>
         </is>
       </c>
       <c r="K128" t="inlineStr"/>
       <c r="L128" s="1" t="n">
-        <v>46204</v>
-      </c>
-      <c r="M128" t="inlineStr"/>
+        <v>46205</v>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
+        </is>
+      </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>00/2026</t>
         </is>
       </c>
       <c r="O128" t="n">
-        <v>18195927</v>
-      </c>
-      <c r="P128" t="inlineStr"/>
+        <v>17399013</v>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Mikael Teixeira</t>
+        </is>
+      </c>
       <c r="Q128" t="inlineStr">
         <is>
           <t>Baixado</t>
         </is>
       </c>
       <c r="R128" s="1" t="n">
-        <v>46204.48446469908</v>
+        <v>46205.75412240741</v>
       </c>
       <c r="S128" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
-        </is>
-      </c>
-      <c r="U128" t="inlineStr"/>
+          <t>NOSSO NOVO SUPERMERCADO</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V128" t="inlineStr">
         <is>
-          <t>Férias de 02/07/2026 a 10/07/2026. - Data Comentário: 01/07/2026 11:26</t>
+          <t>2. Folha Processada aguardando OK do cliente para finalização   Previsão para conclusão dia 02/07/2026 - Data Comentário: 30/06/2026 15:03</t>
         </is>
       </c>
       <c r="W128" t="inlineStr"/>
@@ -13978,7 +13992,7 @@
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>Kaique Souza</t>
+          <t>Mikael Teixeira</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr"/>
@@ -13994,11 +14008,11 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>5417</v>
+        <v>6224</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -14018,14 +14032,14 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G129" t="n">
-        <v>5800</v>
+        <v>5859</v>
       </c>
       <c r="H129" t="n">
-        <v>5776</v>
+        <v>5786</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
@@ -14034,29 +14048,25 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>CCT Lançamento Sd.508</t>
+          <t>Contribuição Assistencial</t>
         </is>
       </c>
       <c r="K129" t="inlineStr"/>
       <c r="L129" s="1" t="n">
-        <v>46205</v>
-      </c>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>02/07/2026</t>
-        </is>
-      </c>
+        <v>46206</v>
+      </c>
+      <c r="M129" t="inlineStr"/>
       <c r="N129" t="inlineStr">
         <is>
-          <t>00/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
       <c r="O129" t="n">
-        <v>17399013</v>
+        <v>17688763</v>
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Mikael Teixeira</t>
+          <t>Tania Luz</t>
         </is>
       </c>
       <c r="Q129" t="inlineStr">
@@ -14065,14 +14075,14 @@
         </is>
       </c>
       <c r="R129" s="1" t="n">
-        <v>46205.75412240741</v>
+        <v>46205.75458568287</v>
       </c>
       <c r="S129" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U129" t="inlineStr">
@@ -14080,11 +14090,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V129" t="inlineStr">
-        <is>
-          <t>2. Folha Processada aguardando OK do cliente para finalização   Previsão para conclusão dia 02/07/2026 - Data Comentário: 30/06/2026 15:03</t>
-        </is>
-      </c>
+      <c r="V129" t="inlineStr"/>
       <c r="W129" t="inlineStr"/>
       <c r="X129" t="inlineStr"/>
       <c r="Y129" t="inlineStr"/>
@@ -14093,7 +14099,7 @@
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>Mikael Teixeira</t>
+          <t>Tania Luz</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr"/>
@@ -14102,18 +14108,22 @@
       <c r="AE129" t="inlineStr"/>
       <c r="AF129" t="inlineStr">
         <is>
-          <t>Tarefa</t>
-        </is>
-      </c>
-      <c r="AG129" t="inlineStr"/>
+          <t>Imposto</t>
+        </is>
+      </c>
+      <c r="AG129" t="inlineStr">
+        <is>
+          <t>Sara Cavalheiro</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>6224</v>
+        <v>6628</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -14123,17 +14133,17 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -14163,11 +14173,11 @@
         </is>
       </c>
       <c r="O130" t="n">
-        <v>17688763</v>
+        <v>18052438</v>
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Tania Luz</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="Q130" t="inlineStr">
@@ -14176,14 +14186,14 @@
         </is>
       </c>
       <c r="R130" s="1" t="n">
-        <v>46205.75458568287</v>
+        <v>46206.44903752315</v>
       </c>
       <c r="S130" t="n">
         <v>4</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t xml:space="preserve">GTG </t>
         </is>
       </c>
       <c r="U130" t="inlineStr">
@@ -14200,7 +14210,7 @@
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>Tania Luz</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr"/>
@@ -14214,17 +14224,17 @@
       </c>
       <c r="AG130" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>David Bragança</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>6628</v>
+        <v>6779</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>CORDEIRO E CIA LTDA</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -14239,7 +14249,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -14274,34 +14284,26 @@
         </is>
       </c>
       <c r="O131" t="n">
-        <v>18052438</v>
-      </c>
-      <c r="P131" t="inlineStr">
-        <is>
-          <t>Jakeline Silva</t>
-        </is>
-      </c>
+        <v>18090166</v>
+      </c>
+      <c r="P131" t="inlineStr"/>
       <c r="Q131" t="inlineStr">
         <is>
           <t>Baixado</t>
         </is>
       </c>
       <c r="R131" s="1" t="n">
-        <v>46206.44903752315</v>
+        <v>46199.48727971065</v>
       </c>
       <c r="S131" t="n">
         <v>4</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
-        </is>
-      </c>
-      <c r="U131" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>TECNO COM</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr"/>
       <c r="V131" t="inlineStr"/>
       <c r="W131" t="inlineStr"/>
       <c r="X131" t="inlineStr"/>
@@ -14311,7 +14313,7 @@
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Kaique Souza</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr"/>
@@ -14323,19 +14325,15 @@
           <t>Imposto</t>
         </is>
       </c>
-      <c r="AG131" t="inlineStr">
-        <is>
-          <t>David Bragança</t>
-        </is>
-      </c>
+      <c r="AG131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>6779</v>
+        <v>6885</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>CORDEIRO E CIA LTDA</t>
+          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -14385,23 +14383,27 @@
         </is>
       </c>
       <c r="O132" t="n">
-        <v>18090166</v>
-      </c>
-      <c r="P132" t="inlineStr"/>
+        <v>18157259</v>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>Vitor Guedes</t>
+        </is>
+      </c>
       <c r="Q132" t="inlineStr">
         <is>
           <t>Baixado</t>
         </is>
       </c>
       <c r="R132" s="1" t="n">
-        <v>46199.48727971065</v>
+        <v>46205.69236453703</v>
       </c>
       <c r="S132" t="n">
         <v>4</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U132" t="inlineStr"/>
@@ -14414,7 +14416,7 @@
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>Kaique Souza</t>
+          <t>Vitor Guedes</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr"/>
@@ -14426,15 +14428,19 @@
           <t>Imposto</t>
         </is>
       </c>
-      <c r="AG132" t="inlineStr"/>
+      <c r="AG132" t="inlineStr">
+        <is>
+          <t>David Bragança</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>6885</v>
+        <v>6945</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
+          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -14449,7 +14455,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -14477,18 +14483,22 @@
       <c r="L133" s="1" t="n">
         <v>46206</v>
       </c>
-      <c r="M133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
       <c r="N133" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O133" t="n">
-        <v>18157259</v>
+        <v>18179094</v>
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Vitor Guedes</t>
+          <t>Santos Karina</t>
         </is>
       </c>
       <c r="Q133" t="inlineStr">
@@ -14497,18 +14507,23 @@
         </is>
       </c>
       <c r="R133" s="1" t="n">
-        <v>46205.69236453703</v>
+        <v>46209.43008613426</v>
       </c>
       <c r="S133" t="n">
         <v>4</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>BRASIL DISTRIBUIDORA</t>
         </is>
       </c>
       <c r="U133" t="inlineStr"/>
-      <c r="V133" t="inlineStr"/>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 07/07/2026 
+cliente em implantação, em andamento - Data Comentário: 03/07/2026 17:19</t>
+        </is>
+      </c>
       <c r="W133" t="inlineStr"/>
       <c r="X133" t="inlineStr"/>
       <c r="Y133" t="inlineStr"/>
@@ -14517,7 +14532,7 @@
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>Vitor Guedes</t>
+          <t>Santos Karina</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr"/>
@@ -14531,17 +14546,17 @@
       </c>
       <c r="AG133" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Leandro Matos</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>6945</v>
+        <v>6486</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
+          <t>PC GAMER GOIANIA LTDA</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -14551,12 +14566,12 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -14565,10 +14580,10 @@
         </is>
       </c>
       <c r="G134" t="n">
-        <v>5859</v>
+        <v>11542</v>
       </c>
       <c r="H134" t="n">
-        <v>5786</v>
+        <v>0</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
@@ -14577,29 +14592,25 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Contribuição Assistencial</t>
+          <t>Envio Arq. eConsignado Cliente</t>
         </is>
       </c>
       <c r="K134" t="inlineStr"/>
       <c r="L134" s="1" t="n">
-        <v>46206</v>
-      </c>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>07/07/2026</t>
-        </is>
-      </c>
+        <v>46204</v>
+      </c>
+      <c r="M134" t="inlineStr"/>
       <c r="N134" t="inlineStr">
         <is>
-          <t>06/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
       <c r="O134" t="n">
-        <v>18179094</v>
+        <v>16976370</v>
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Santos Karina</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="Q134" t="inlineStr">
@@ -14608,23 +14619,22 @@
         </is>
       </c>
       <c r="R134" s="1" t="n">
-        <v>46209.43008613426</v>
+        <v>46204.5600265625</v>
       </c>
       <c r="S134" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA</t>
-        </is>
-      </c>
-      <c r="U134" t="inlineStr"/>
-      <c r="V134" t="inlineStr">
-        <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 07/07/2026 
-cliente em implantação, em andamento - Data Comentário: 03/07/2026 17:19</t>
-        </is>
-      </c>
+          <t>PC GAMER</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr"/>
       <c r="W134" t="inlineStr"/>
       <c r="X134" t="inlineStr"/>
       <c r="Y134" t="inlineStr"/>
@@ -14633,7 +14643,7 @@
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>Santos Karina</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr"/>
@@ -14642,22 +14652,22 @@
       <c r="AE134" t="inlineStr"/>
       <c r="AF134" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Obrigação Acessória</t>
         </is>
       </c>
       <c r="AG134" t="inlineStr">
         <is>
-          <t>Leandro Matos</t>
+          <t>David Bragança</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>6486</v>
+        <v>6548</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PC GAMER GOIANIA LTDA</t>
+          <t>GOIAS SILAGEM LTDA</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -14707,11 +14717,11 @@
         </is>
       </c>
       <c r="O135" t="n">
-        <v>16976370</v>
+        <v>17222966</v>
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Daniel Moraes</t>
         </is>
       </c>
       <c r="Q135" t="inlineStr">
@@ -14720,14 +14730,14 @@
         </is>
       </c>
       <c r="R135" s="1" t="n">
-        <v>46204.5600265625</v>
+        <v>46196.71390480324</v>
       </c>
       <c r="S135" t="n">
         <v>6</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
-          <t>PC GAMER</t>
+          <t>GOIAS SILAGEM</t>
         </is>
       </c>
       <c r="U135" t="inlineStr">
@@ -14744,7 +14754,7 @@
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Evellin Bispo</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr"/>
@@ -14764,11 +14774,11 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>6548</v>
+        <v>6703</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM LTDA</t>
+          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -14778,7 +14788,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -14818,11 +14828,11 @@
         </is>
       </c>
       <c r="O136" t="n">
-        <v>17222966</v>
+        <v>18077183</v>
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Daniel Moraes</t>
+          <t>Elaine Assis</t>
         </is>
       </c>
       <c r="Q136" t="inlineStr">
@@ -14831,14 +14841,14 @@
         </is>
       </c>
       <c r="R136" s="1" t="n">
-        <v>46196.71390480324</v>
+        <v>46198.70825575232</v>
       </c>
       <c r="S136" t="n">
         <v>6</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM</t>
+          <t>LIMA MOTA</t>
         </is>
       </c>
       <c r="U136" t="inlineStr">
@@ -14855,7 +14865,7 @@
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>Evellin Bispo</t>
+          <t>Elaine Assis</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr"/>
@@ -14875,11 +14885,11 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>6703</v>
+        <v>6779</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
+          <t>CORDEIRO E CIA LTDA</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -14889,7 +14899,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -14929,11 +14939,11 @@
         </is>
       </c>
       <c r="O137" t="n">
-        <v>18077183</v>
+        <v>18090270</v>
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Elaine Assis</t>
+          <t>Kaique Souza</t>
         </is>
       </c>
       <c r="Q137" t="inlineStr">
@@ -14942,21 +14952,17 @@
         </is>
       </c>
       <c r="R137" s="1" t="n">
-        <v>46198.70825575232</v>
+        <v>46196.59280127315</v>
       </c>
       <c r="S137" t="n">
         <v>6</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
-          <t>LIMA MOTA</t>
-        </is>
-      </c>
-      <c r="U137" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>TECNO COM</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr"/>
       <c r="V137" t="inlineStr"/>
       <c r="W137" t="inlineStr"/>
       <c r="X137" t="inlineStr"/>
@@ -14966,7 +14972,7 @@
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>Elaine Assis</t>
+          <t>Kaique Souza</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr"/>
@@ -14980,17 +14986,17 @@
       </c>
       <c r="AG137" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>6779</v>
+        <v>6949</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>CORDEIRO E CIA LTDA</t>
+          <t>TEC GRUA LOCAÇÃO E COMERCIO DE EQUIPAMENTOS PARA CONSTRUÇÃO LTDA</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -15000,7 +15006,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -15010,7 +15016,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Reynaldo Santos</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -15040,11 +15046,11 @@
         </is>
       </c>
       <c r="O138" t="n">
-        <v>18090270</v>
+        <v>18190469</v>
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Kaique Souza</t>
+          <t>Gabriela Peres</t>
         </is>
       </c>
       <c r="Q138" t="inlineStr">
@@ -15053,14 +15059,14 @@
         </is>
       </c>
       <c r="R138" s="1" t="n">
-        <v>46196.59280127315</v>
+        <v>46204.41370118056</v>
       </c>
       <c r="S138" t="n">
         <v>6</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>TEC GRUA</t>
         </is>
       </c>
       <c r="U138" t="inlineStr"/>
@@ -15073,7 +15079,7 @@
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>Kaique Souza</t>
+          <t>Santos Karina</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr"/>
@@ -15087,17 +15093,17 @@
       </c>
       <c r="AG138" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>Leandro Matos</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>6949</v>
+        <v>6404</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>TEC GRUA LOCAÇÃO E COMERCIO DE EQUIPAMENTOS PARA CONSTRUÇÃO LTDA</t>
+          <t>SOLAR INVESTIMENTOS LTDA</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -15107,7 +15113,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -15117,11 +15123,11 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G139" t="n">
-        <v>11542</v>
+        <v>9746</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
@@ -15133,25 +15139,29 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Envio Arq. eConsignado Cliente</t>
+          <t>eSocial – Fechamento Mensal</t>
         </is>
       </c>
       <c r="K139" t="inlineStr"/>
       <c r="L139" s="1" t="n">
-        <v>46204</v>
-      </c>
-      <c r="M139" t="inlineStr"/>
+        <v>46213</v>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
       <c r="O139" t="n">
-        <v>18190469</v>
+        <v>16962422</v>
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Gabriela Peres</t>
+          <t>Jhenifer Tenorio</t>
         </is>
       </c>
       <c r="Q139" t="inlineStr">
@@ -15160,18 +15170,26 @@
         </is>
       </c>
       <c r="R139" s="1" t="n">
-        <v>46204.41370118056</v>
+        <v>46209.71247704861</v>
       </c>
       <c r="S139" t="n">
-        <v>6</v>
+        <v>-3</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
-          <t>TEC GRUA</t>
-        </is>
-      </c>
-      <c r="U139" t="inlineStr"/>
-      <c r="V139" t="inlineStr"/>
+          <t>SOLAR INVESTIMENTOS</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 08/07/2026 - Data Comentário: 06/07/2026 12:40</t>
+        </is>
+      </c>
       <c r="W139" t="inlineStr"/>
       <c r="X139" t="inlineStr"/>
       <c r="Y139" t="inlineStr"/>
@@ -15180,7 +15198,7 @@
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>Santos Karina</t>
+          <t>Jhenifer Tenorio</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr"/>
@@ -15189,22 +15207,22 @@
       <c r="AE139" t="inlineStr"/>
       <c r="AF139" t="inlineStr">
         <is>
-          <t>Obrigação Acessória</t>
+          <t>Tarefa</t>
         </is>
       </c>
       <c r="AG139" t="inlineStr">
         <is>
-          <t>Leandro Matos</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>6404</v>
+        <v>6486</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS LTDA</t>
+          <t>PC GAMER GOIANIA LTDA</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -15214,7 +15232,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -15258,11 +15276,11 @@
         </is>
       </c>
       <c r="O140" t="n">
-        <v>16962422</v>
+        <v>16976298</v>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Jhenifer Tenorio</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="Q140" t="inlineStr">
@@ -15271,14 +15289,14 @@
         </is>
       </c>
       <c r="R140" s="1" t="n">
-        <v>46209.71247704861</v>
+        <v>46209.71499087963</v>
       </c>
       <c r="S140" t="n">
         <v>-3</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS</t>
+          <t>PC GAMER</t>
         </is>
       </c>
       <c r="U140" t="inlineStr">
@@ -15288,7 +15306,8 @@
       </c>
       <c r="V140" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 08/07/2026 - Data Comentário: 06/07/2026 12:40</t>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 08/07/2026 
+PREVISÃO DE FINALIZAÇÃO: 08/07/2026 - Data Comentário: 06/07/2026 10:43</t>
         </is>
       </c>
       <c r="W140" t="inlineStr"/>
@@ -15299,7 +15318,7 @@
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>Jhenifer Tenorio</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr"/>
@@ -15313,17 +15332,17 @@
       </c>
       <c r="AG140" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>David Bragança</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>6486</v>
+        <v>6627</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>PC GAMER GOIANIA LTDA</t>
+          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -15338,7 +15357,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -15377,7 +15396,7 @@
         </is>
       </c>
       <c r="O141" t="n">
-        <v>16976298</v>
+        <v>18068609</v>
       </c>
       <c r="P141" t="inlineStr">
         <is>
@@ -15390,14 +15409,14 @@
         </is>
       </c>
       <c r="R141" s="1" t="n">
-        <v>46209.71499087963</v>
+        <v>46210.47222041667</v>
       </c>
       <c r="S141" t="n">
         <v>-3</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
-          <t>PC GAMER</t>
+          <t xml:space="preserve">GTG </t>
         </is>
       </c>
       <c r="U141" t="inlineStr">
@@ -15439,11 +15458,11 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -15453,7 +15472,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -15497,7 +15516,7 @@
         </is>
       </c>
       <c r="O142" t="n">
-        <v>18068609</v>
+        <v>18052528</v>
       </c>
       <c r="P142" t="inlineStr">
         <is>
@@ -15510,7 +15529,7 @@
         </is>
       </c>
       <c r="R142" s="1" t="n">
-        <v>46210.47222041667</v>
+        <v>46210.48604510417</v>
       </c>
       <c r="S142" t="n">
         <v>-3</v>
@@ -15559,11 +15578,11 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>6628</v>
+        <v>6703</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -15573,12 +15592,12 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -15608,7 +15627,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -15617,11 +15636,11 @@
         </is>
       </c>
       <c r="O143" t="n">
-        <v>18052528</v>
+        <v>18077161</v>
       </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Elaine Assis</t>
         </is>
       </c>
       <c r="Q143" t="inlineStr">
@@ -15630,14 +15649,14 @@
         </is>
       </c>
       <c r="R143" s="1" t="n">
-        <v>46210.48604510417</v>
+        <v>46210.48132625</v>
       </c>
       <c r="S143" t="n">
         <v>-3</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
+          <t>LIMA MOTA</t>
         </is>
       </c>
       <c r="U143" t="inlineStr">
@@ -15647,8 +15666,8 @@
       </c>
       <c r="V143" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 08/07/2026 
-PREVISÃO DE FINALIZAÇÃO: 08/07/2026 - Data Comentário: 06/07/2026 10:43</t>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 07/07/2026 
+Previsão de conclusão 07/07/2026. - Data Comentário: 07/07/2026 10:22</t>
         </is>
       </c>
       <c r="W143" t="inlineStr"/>
@@ -15659,7 +15678,7 @@
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Elaine Assis</t>
         </is>
       </c>
       <c r="AB143" t="inlineStr"/>
@@ -15679,11 +15698,11 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>6703</v>
+        <v>6779</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
+          <t>CORDEIRO E CIA LTDA</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -15693,7 +15712,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -15728,7 +15747,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -15737,11 +15756,11 @@
         </is>
       </c>
       <c r="O144" t="n">
-        <v>18077161</v>
+        <v>18090248</v>
       </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Elaine Assis</t>
+          <t>Kaique Souza</t>
         </is>
       </c>
       <c r="Q144" t="inlineStr">
@@ -15750,25 +15769,21 @@
         </is>
       </c>
       <c r="R144" s="1" t="n">
-        <v>46210.48132625</v>
+        <v>46210.45896016204</v>
       </c>
       <c r="S144" t="n">
         <v>-3</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
-          <t>LIMA MOTA</t>
-        </is>
-      </c>
-      <c r="U144" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>TECNO COM</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr"/>
       <c r="V144" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 07/07/2026 
-Previsão de conclusão 07/07/2026. - Data Comentário: 07/07/2026 10:22</t>
+          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 10/07/2026 
+ESocial será baixado no vencimento para evitar retificações por solicitações do cliente. - Data Comentário: 03/07/2026 14:17</t>
         </is>
       </c>
       <c r="W144" t="inlineStr"/>
@@ -15779,7 +15794,7 @@
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>Elaine Assis</t>
+          <t>Kaique Souza</t>
         </is>
       </c>
       <c r="AB144" t="inlineStr"/>
@@ -15793,17 +15808,17 @@
       </c>
       <c r="AG144" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>6779</v>
+        <v>6885</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>CORDEIRO E CIA LTDA</t>
+          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -15848,7 +15863,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -15857,11 +15872,11 @@
         </is>
       </c>
       <c r="O145" t="n">
-        <v>18090248</v>
+        <v>18157325</v>
       </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Kaique Souza</t>
+          <t>Vitor Guedes</t>
         </is>
       </c>
       <c r="Q145" t="inlineStr">
@@ -15870,21 +15885,21 @@
         </is>
       </c>
       <c r="R145" s="1" t="n">
-        <v>46210.45896016204</v>
+        <v>46210.72289299768</v>
       </c>
       <c r="S145" t="n">
         <v>-3</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U145" t="inlineStr"/>
       <c r="V145" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 10/07/2026 
-ESocial será baixado no vencimento para evitar retificações por solicitações do cliente. - Data Comentário: 03/07/2026 14:17</t>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 07/07/2026 
+PREVISÃO DE CONCLUSÃO: 07/07/2026 - Data Comentário: 07/07/2026 13:13</t>
         </is>
       </c>
       <c r="W145" t="inlineStr"/>
@@ -15895,7 +15910,7 @@
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>Kaique Souza</t>
+          <t>Vitor Guedes</t>
         </is>
       </c>
       <c r="AB145" t="inlineStr"/>
@@ -15909,7 +15924,7 @@
       </c>
       <c r="AG145" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>David Bragança</t>
         </is>
       </c>
     </row>
@@ -53466,7 +53481,11 @@
       <c r="O496" t="n">
         <v>18201603</v>
       </c>
-      <c r="P496" t="inlineStr"/>
+      <c r="P496" t="inlineStr">
+        <is>
+          <t>Gabriela Peres</t>
+        </is>
+      </c>
       <c r="Q496" t="inlineStr">
         <is>
           <t>Em Aberto</t>
@@ -53499,7 +53518,11 @@
           <t>Imposto</t>
         </is>
       </c>
-      <c r="AG496" t="inlineStr"/>
+      <c r="AG496" t="inlineStr">
+        <is>
+          <t>Leandro Matos</t>
+        </is>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="n">

--- a/dados/base/goias.xlsx
+++ b/dados/base/goias.xlsx
@@ -2706,11 +2706,11 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>6548</v>
+        <v>6628</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM LTDA</t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2764,11 +2764,11 @@
         </is>
       </c>
       <c r="O22" t="n">
-        <v>17222913</v>
+        <v>18052528</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Daniel Moraes</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -2782,7 +2782,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM</t>
+          <t xml:space="preserve">GTG </t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2792,8 +2792,8 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 08/07/2026 
-Previsão de conclusão em 08/07/2026. - Data Comentário: 07/07/2026 16:47</t>
+          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 08/07/2026 
+EMPRESA SOLICITOU REABERTURA DA FOLHA PARA ALTERAÇÃO NO COLABORADOR TSN : Maycon Gomes da Silva. AGUARDANDO FECHAMENTO ESOCIAL PARA BAIXA. - Data Comentário: 08/07/2026 09:12</t>
         </is>
       </c>
       <c r="W22" t="inlineStr"/>
@@ -2820,11 +2820,11 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>6628</v>
+        <v>6945</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2878,11 +2878,11 @@
         </is>
       </c>
       <c r="O23" t="n">
-        <v>18052528</v>
+        <v>18179152</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Santos Karina</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -2896,18 +2896,14 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>BRASIL DISTRIBUIDORA</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 08/07/2026 
-EMPRESA SOLICITOU REABERTURA DA FOLHA PARA ALTERAÇÃO NO COLABORADOR TSN : Maycon Gomes da Silva. AGUARDANDO FECHAMENTO ESOCIAL PARA BAIXA. - Data Comentário: 08/07/2026 09:12</t>
+          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 10/07/2026 
+Empresa Implantação em processamento. - Data Comentário: 07/07/2026 15:25</t>
         </is>
       </c>
       <c r="W23" t="inlineStr"/>
@@ -2928,17 +2924,17 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Leandro Matos</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>6945</v>
+        <v>6279</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
+          <t>DIENNYFER DA S PEREIRA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2948,21 +2944,21 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>9746</v>
+        <v>10905</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -2974,7 +2970,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>eSocial – Fechamento Mensal</t>
+          <t>eSocial - Fechamento SM</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -2983,7 +2979,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2992,11 +2988,11 @@
         </is>
       </c>
       <c r="O24" t="n">
-        <v>18179152</v>
+        <v>18195935</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Santos Karina</t>
+          <t>Vitor Guedes</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -3010,14 +3006,18 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr"/>
+          <t>EMPORIO DOS FRIOS</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 10/07/2026 
-Empresa Implantação em processamento. - Data Comentário: 07/07/2026 15:25</t>
+          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 08/07/2026 
+Previsão de conclusão: 08/07/2026 - Data Comentário: 06/07/2026 14:42</t>
         </is>
       </c>
       <c r="W24" t="inlineStr"/>
@@ -3033,22 +3033,22 @@
       <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>Tarefa</t>
+          <t>Obrigação Acessória</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>Leandro Matos</t>
+          <t>David Bragança</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>6279</v>
+        <v>5417</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DIENNYFER DA S PEREIRA</t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -3068,14 +3068,14 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>10905</v>
+        <v>5867</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>5786</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -3084,29 +3084,25 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>eSocial - Fechamento SM</t>
+          <t>GFD - FGTS Digital Mensal</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" s="1" t="n">
-        <v>46213</v>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>08/07/2026</t>
-        </is>
-      </c>
+        <v>46218</v>
+      </c>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O25" t="n">
-        <v>18195935</v>
+        <v>17399054</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Vitor Guedes</t>
+          <t>Mikael Teixeira</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -3116,11 +3112,11 @@
       </c>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="n">
-        <v>-2</v>
+        <v>-7</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>NOSSO NOVO SUPERMERCADO</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3128,12 +3124,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 08/07/2026 
-Previsão de conclusão: 08/07/2026 - Data Comentário: 06/07/2026 14:42</t>
-        </is>
-      </c>
+      <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr"/>
       <c r="X25" t="inlineStr"/>
       <c r="Y25" t="inlineStr"/>
@@ -3147,22 +3138,18 @@
       <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>Obrigação Acessória</t>
-        </is>
-      </c>
-      <c r="AG25" t="inlineStr">
-        <is>
-          <t>David Bragança</t>
-        </is>
-      </c>
+          <t>Imposto</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>5417</v>
+        <v>5617</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3182,7 +3169,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3212,11 +3199,11 @@
         </is>
       </c>
       <c r="O26" t="n">
-        <v>17399054</v>
+        <v>17407645</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Mikael Teixeira</t>
+          <t>Tania Luz</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -3230,7 +3217,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3255,15 +3242,19 @@
           <t>Imposto</t>
         </is>
       </c>
-      <c r="AG26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>Edivaldo Veiga</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>5617</v>
+        <v>6224</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3283,7 +3274,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3313,7 +3304,7 @@
         </is>
       </c>
       <c r="O27" t="n">
-        <v>17407645</v>
+        <v>17688773</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
@@ -3364,11 +3355,11 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>6224</v>
+        <v>6486</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>PC GAMER GOIANIA LTDA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3388,7 +3379,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3411,18 +3402,22 @@
       <c r="L28" s="1" t="n">
         <v>46218</v>
       </c>
-      <c r="M28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O28" t="n">
-        <v>17688773</v>
+        <v>16976054</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Tania Luz</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -3436,7 +3431,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>PC GAMER</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3444,7 +3439,12 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr"/>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 13/07/2026 
+PREVISÃO DE CONCLUSÃO: 13/07/2026 - Data Comentário: 07/07/2026 16:32</t>
+        </is>
+      </c>
       <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr"/>
       <c r="Y28" t="inlineStr"/>
@@ -3463,17 +3463,17 @@
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>David Bragança</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>6486</v>
+        <v>6548</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PC GAMER GOIANIA LTDA</t>
+          <t>GOIAS SILAGEM LTDA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3516,22 +3516,18 @@
       <c r="L29" s="1" t="n">
         <v>46218</v>
       </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>13/07/2026</t>
-        </is>
-      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O29" t="n">
-        <v>16976054</v>
+        <v>17222615</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Daniel Moraes</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -3545,7 +3541,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>PC GAMER</t>
+          <t>GOIAS SILAGEM</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3553,12 +3549,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 13/07/2026 
-PREVISÃO DE CONCLUSÃO: 13/07/2026 - Data Comentário: 07/07/2026 16:32</t>
-        </is>
-      </c>
+      <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr"/>
       <c r="X29" t="inlineStr"/>
       <c r="Y29" t="inlineStr"/>
@@ -3583,11 +3574,11 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM LTDA</t>
+          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3602,7 +3593,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3630,18 +3621,22 @@
       <c r="L30" s="1" t="n">
         <v>46218</v>
       </c>
-      <c r="M30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O30" t="n">
-        <v>17222615</v>
+        <v>18068530</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Daniel Moraes</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -3655,7 +3650,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM</t>
+          <t xml:space="preserve">GTG </t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3663,7 +3658,12 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr"/>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 13/07/2026 
+PREVISÃO DE CONCLUSÃO: 13/07/2026 - Data Comentário: 07/07/2026 16:32</t>
+        </is>
+      </c>
       <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr"/>
       <c r="Y30" t="inlineStr"/>
@@ -3688,11 +3688,11 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3746,7 +3746,7 @@
         </is>
       </c>
       <c r="O31" t="n">
-        <v>18068530</v>
+        <v>18052449</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
@@ -3802,11 +3802,11 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>6628</v>
+        <v>6703</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3849,22 +3849,18 @@
       <c r="L32" s="1" t="n">
         <v>46218</v>
       </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>13/07/2026</t>
-        </is>
-      </c>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O32" t="n">
-        <v>18052449</v>
+        <v>18077099</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Ana Marcelino</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -3878,7 +3874,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
+          <t>LIMA MOTA</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3886,12 +3882,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 13/07/2026 
-PREVISÃO DE CONCLUSÃO: 13/07/2026 - Data Comentário: 07/07/2026 16:32</t>
-        </is>
-      </c>
+      <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr"/>
       <c r="Y32" t="inlineStr"/>
@@ -3910,17 +3901,17 @@
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>6703</v>
+        <v>6779</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
+          <t>CORDEIRO E CIA LTDA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3930,7 +3921,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3970,11 +3961,11 @@
         </is>
       </c>
       <c r="O33" t="n">
-        <v>18077099</v>
+        <v>18090176</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Ana Marcelino</t>
+          <t>Kaique Souza</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -3988,14 +3979,10 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>LIMA MOTA</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>TECNO COM</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr"/>
@@ -4021,11 +4008,11 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>6779</v>
+        <v>6885</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CORDEIRO E CIA LTDA</t>
+          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4075,11 +4062,11 @@
         </is>
       </c>
       <c r="O34" t="n">
-        <v>18090176</v>
+        <v>18157267</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Kaique Souza</t>
+          <t>Vitor Guedes</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -4093,7 +4080,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U34" t="inlineStr"/>
@@ -4116,17 +4103,17 @@
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>David Bragança</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>6885</v>
+        <v>6945</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
+          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4141,7 +4128,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4176,11 +4163,11 @@
         </is>
       </c>
       <c r="O35" t="n">
-        <v>18157267</v>
+        <v>18179101</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Vitor Guedes</t>
+          <t>Santos Karina</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -4194,7 +4181,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>BRASIL DISTRIBUIDORA</t>
         </is>
       </c>
       <c r="U35" t="inlineStr"/>
@@ -4217,17 +4204,17 @@
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Leandro Matos</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>6945</v>
+        <v>6949</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
+          <t>TEC GRUA LOCAÇÃO E COMERCIO DE EQUIPAMENTOS PARA CONSTRUÇÃO LTDA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -4237,24 +4224,24 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Reynaldo Santos</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>5867</v>
+        <v>6348</v>
       </c>
       <c r="H36" t="n">
-        <v>5786</v>
+        <v>0</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -4263,7 +4250,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>GFD - FGTS Digital Mensal</t>
+          <t>RESCISÃO - RESCISÃO</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -4273,15 +4260,15 @@
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
-          <t>06/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
       <c r="O36" t="n">
-        <v>18179101</v>
+        <v>18201961</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Santos Karina</t>
+          <t>Gabriela Peres</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -4295,11 +4282,15 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA</t>
+          <t>TEC GRUA</t>
         </is>
       </c>
       <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Pedido de demissão - Desconto de Aviso em 07/07/2026 - Pgto 17/07/2026 - Data Comentário: 08/07/2026 11:16</t>
+        </is>
+      </c>
       <c r="W36" t="inlineStr"/>
       <c r="X36" t="inlineStr"/>
       <c r="Y36" t="inlineStr"/>
@@ -4352,37 +4343,41 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>6348</v>
+        <v>11617</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>RESCISÃO - RESCISÃO</t>
+          <t>Envio de ATA de Implantação - EF I</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" s="1" t="n">
-        <v>46218</v>
-      </c>
-      <c r="M37" t="inlineStr"/>
+        <v>46213</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
       <c r="O37" t="n">
-        <v>18201961</v>
+        <v>18166588</v>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Gabriela Peres</t>
+          <t>Priscila Volpe</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -4392,7 +4387,7 @@
       </c>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="n">
-        <v>-7</v>
+        <v>-2</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4402,7 +4397,8 @@
       <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr">
         <is>
-          <t>Pedido de demissão - Desconto de Aviso em 07/07/2026 - Pgto 17/07/2026 - Data Comentário: 08/07/2026 11:16</t>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 31/07/2026 
+ainda não foi realizado as implantações - Data Comentário: 01/07/2026 13:38</t>
         </is>
       </c>
       <c r="W37" t="inlineStr"/>
@@ -4418,22 +4414,22 @@
       <c r="AE37" t="inlineStr"/>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Tarefa</t>
         </is>
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>Leandro Matos</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>6949</v>
+        <v>6962</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>TEC GRUA LOCAÇÃO E COMERCIO DE EQUIPAMENTOS PARA CONSTRUÇÃO LTDA</t>
+          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4487,7 +4483,7 @@
         </is>
       </c>
       <c r="O38" t="n">
-        <v>18166588</v>
+        <v>18186565</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
@@ -4505,7 +4501,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>TEC GRUA</t>
+          <t>PROMOTORAS GYN</t>
         </is>
       </c>
       <c r="U38" t="inlineStr"/>
@@ -4539,11 +4535,11 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
+          <t>PROMOTORAS GYN LTDA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -4597,7 +4593,7 @@
         </is>
       </c>
       <c r="O39" t="n">
-        <v>18186565</v>
+        <v>18186566</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
@@ -4649,11 +4645,11 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>6963</v>
+        <v>6628</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN LTDA</t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -4663,21 +4659,21 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>11617</v>
+        <v>1875</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -4689,29 +4685,25 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Envio de ATA de Implantação - EF I</t>
+          <t>Est - Sintegra Interestadual</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" s="1" t="n">
-        <v>46213</v>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>31/07/2026</t>
-        </is>
-      </c>
+        <v>46218</v>
+      </c>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O40" t="n">
-        <v>18186566</v>
+        <v>17988660</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Priscila Volpe</t>
+          <t>Fernando Bastos</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -4721,20 +4713,19 @@
       </c>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="n">
-        <v>-2</v>
+        <v>-7</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 31/07/2026 
-ainda não foi realizado as implantações - Data Comentário: 01/07/2026 13:38</t>
-        </is>
-      </c>
+          <t xml:space="preserve">GTG </t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr"/>
       <c r="W40" t="inlineStr"/>
       <c r="X40" t="inlineStr"/>
       <c r="Y40" t="inlineStr"/>
@@ -4748,7 +4739,7 @@
       <c r="AE40" t="inlineStr"/>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>Tarefa</t>
+          <t>Obrigação Acessória</t>
         </is>
       </c>
       <c r="AG40" t="inlineStr">
@@ -4759,11 +4750,11 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>6628</v>
+        <v>6548</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>GOIAS SILAGEM LTDA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -4773,12 +4764,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4787,7 +4778,7 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>1875</v>
+        <v>6805</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -4799,12 +4790,12 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Est - Sintegra Interestadual</t>
+          <t>Fed - EFD - REINF - Entrega e PDF</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" s="1" t="n">
-        <v>46218</v>
+        <v>46216</v>
       </c>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
@@ -4813,11 +4804,11 @@
         </is>
       </c>
       <c r="O41" t="n">
-        <v>17988660</v>
+        <v>17222740</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Fernando Bastos</t>
+          <t>Cristiana Grizostomo</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -4827,11 +4818,11 @@
       </c>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
+          <t>GOIAS SILAGEM</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4864,11 +4855,11 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM LTDA</t>
+          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -4883,7 +4874,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4918,11 +4909,11 @@
         </is>
       </c>
       <c r="O42" t="n">
-        <v>17222740</v>
+        <v>18085517</v>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Cristiana Grizostomo</t>
+          <t>Denis Reis</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -4936,7 +4927,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM</t>
+          <t xml:space="preserve">GTG </t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4969,11 +4960,11 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4983,7 +4974,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -5023,11 +5014,11 @@
         </is>
       </c>
       <c r="O43" t="n">
-        <v>18085517</v>
+        <v>17988707</v>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Denis Reis</t>
+          <t>Fernando Bastos</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
@@ -5074,11 +5065,11 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>6628</v>
+        <v>6962</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -5088,17 +5079,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Reynaldo Santos</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5128,11 +5119,11 @@
         </is>
       </c>
       <c r="O44" t="n">
-        <v>17988707</v>
+        <v>18186993</v>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Fernando Bastos</t>
+          <t>Denis Reis</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -5146,14 +5137,10 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>PROMOTORAS GYN</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr"/>
       <c r="V44" t="inlineStr"/>
       <c r="W44" t="inlineStr"/>
       <c r="X44" t="inlineStr"/>
@@ -5179,11 +5166,11 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
+          <t>PROMOTORAS GYN LTDA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -5233,7 +5220,7 @@
         </is>
       </c>
       <c r="O45" t="n">
-        <v>18186993</v>
+        <v>18187259</v>
       </c>
       <c r="P45" t="inlineStr">
         <is>
@@ -5280,11 +5267,11 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>6963</v>
+        <v>6962</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN LTDA</t>
+          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -5308,7 +5295,7 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>6805</v>
+        <v>1866</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -5320,21 +5307,25 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Fed - EFD - REINF - Entrega e PDF</t>
+          <t>Mun - ISS Serv. Prestados</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" s="1" t="n">
-        <v>46216</v>
-      </c>
-      <c r="M46" t="inlineStr"/>
+        <v>46212</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O46" t="n">
-        <v>18187259</v>
+        <v>18186944</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
@@ -5348,7 +5339,7 @@
       </c>
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="n">
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5356,7 +5347,11 @@
         </is>
       </c>
       <c r="U46" t="inlineStr"/>
-      <c r="V46" t="inlineStr"/>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 06/07/2026 - Data Comentário: 06/07/2026 10:20</t>
+        </is>
+      </c>
       <c r="W46" t="inlineStr"/>
       <c r="X46" t="inlineStr"/>
       <c r="Y46" t="inlineStr"/>
@@ -5370,7 +5365,7 @@
       <c r="AE46" t="inlineStr"/>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>Obrigação Acessória</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="AG46" t="inlineStr">
@@ -5381,11 +5376,11 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
+          <t>PROMOTORAS GYN LTDA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -5439,7 +5434,7 @@
         </is>
       </c>
       <c r="O47" t="n">
-        <v>18186944</v>
+        <v>18187210</v>
       </c>
       <c r="P47" t="inlineStr">
         <is>
@@ -5490,11 +5485,11 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>6963</v>
+        <v>6962</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN LTDA</t>
+          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -5518,7 +5513,7 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -5530,7 +5525,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Mun - ISS Serv. Prestados</t>
+          <t>Mun - ISS Serv. Tomados</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -5539,7 +5534,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -5548,7 +5543,7 @@
         </is>
       </c>
       <c r="O48" t="n">
-        <v>18187210</v>
+        <v>18186951</v>
       </c>
       <c r="P48" t="inlineStr">
         <is>
@@ -5572,7 +5567,7 @@
       <c r="U48" t="inlineStr"/>
       <c r="V48" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 06/07/2026 - Data Comentário: 06/07/2026 10:20</t>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 07/07/2026 - Data Comentário: 06/07/2026 10:20</t>
         </is>
       </c>
       <c r="W48" t="inlineStr"/>
@@ -5599,11 +5594,11 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
+          <t>PROMOTORAS GYN LTDA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -5657,7 +5652,7 @@
         </is>
       </c>
       <c r="O49" t="n">
-        <v>18186951</v>
+        <v>18187217</v>
       </c>
       <c r="P49" t="inlineStr">
         <is>
@@ -5708,11 +5703,11 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>6963</v>
+        <v>6962</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN LTDA</t>
+          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -5736,10 +5731,10 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>1867</v>
+        <v>6886</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>1862</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -5748,25 +5743,21 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Mun - ISS Serv. Tomados</t>
+          <t>Recebimento de NF Serviços Tomados</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" s="1" t="n">
-        <v>46212</v>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>07/07/2026</t>
-        </is>
-      </c>
+        <v>46213</v>
+      </c>
+      <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O50" t="n">
-        <v>18187217</v>
+        <v>18187000</v>
       </c>
       <c r="P50" t="inlineStr">
         <is>
@@ -5780,7 +5771,7 @@
       </c>
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5788,11 +5779,7 @@
         </is>
       </c>
       <c r="U50" t="inlineStr"/>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 07/07/2026 - Data Comentário: 06/07/2026 10:20</t>
-        </is>
-      </c>
+      <c r="V50" t="inlineStr"/>
       <c r="W50" t="inlineStr"/>
       <c r="X50" t="inlineStr"/>
       <c r="Y50" t="inlineStr"/>
@@ -5806,7 +5793,7 @@
       <c r="AE50" t="inlineStr"/>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Tarefa</t>
         </is>
       </c>
       <c r="AG50" t="inlineStr">
@@ -5817,11 +5804,11 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
+          <t>PROMOTORAS GYN LTDA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -5871,7 +5858,7 @@
         </is>
       </c>
       <c r="O51" t="n">
-        <v>18187000</v>
+        <v>18187266</v>
       </c>
       <c r="P51" t="inlineStr">
         <is>
@@ -5918,11 +5905,11 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>6963</v>
+        <v>6627</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN LTDA</t>
+          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -5937,19 +5924,19 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>6886</v>
+        <v>10674</v>
       </c>
       <c r="H52" t="n">
-        <v>1862</v>
+        <v>0</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -5958,12 +5945,12 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Recebimento de NF Serviços Tomados</t>
+          <t>Relatório de Entrada para Classificação</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" s="1" t="n">
-        <v>46213</v>
+        <v>46218</v>
       </c>
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
@@ -5972,7 +5959,7 @@
         </is>
       </c>
       <c r="O52" t="n">
-        <v>18187266</v>
+        <v>17968443</v>
       </c>
       <c r="P52" t="inlineStr">
         <is>
@@ -5986,14 +5973,18 @@
       </c>
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="n">
-        <v>-2</v>
+        <v>-7</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr"/>
+          <t xml:space="preserve">GTG </t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V52" t="inlineStr"/>
       <c r="W52" t="inlineStr"/>
       <c r="X52" t="inlineStr"/>
@@ -6019,11 +6010,11 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>6627</v>
+        <v>6962</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
+          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -6038,12 +6029,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Reynaldo Santos</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6073,7 +6064,7 @@
         </is>
       </c>
       <c r="O53" t="n">
-        <v>17968443</v>
+        <v>18187014</v>
       </c>
       <c r="P53" t="inlineStr">
         <is>
@@ -6091,14 +6082,10 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
-        </is>
-      </c>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>PROMOTORAS GYN</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr"/>
       <c r="V53" t="inlineStr"/>
       <c r="W53" t="inlineStr"/>
       <c r="X53" t="inlineStr"/>
@@ -6124,11 +6111,11 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
+          <t>PROMOTORAS GYN LTDA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -6178,7 +6165,7 @@
         </is>
       </c>
       <c r="O54" t="n">
-        <v>18187014</v>
+        <v>18187280</v>
       </c>
       <c r="P54" t="inlineStr">
         <is>
@@ -6225,11 +6212,11 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>6963</v>
+        <v>6224</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -6249,28 +6236,28 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>10674</v>
+        <v>1802</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Relatório de Entrada para Classificação</t>
+          <t>Est - ICMS RPA - CÓD. 046-2</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" s="1" t="n">
-        <v>46218</v>
+        <v>46212</v>
       </c>
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
@@ -6279,11 +6266,11 @@
         </is>
       </c>
       <c r="O55" t="n">
-        <v>18187280</v>
+        <v>17688681</v>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Denis Reis</t>
+          <t>Cristina Leite</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
@@ -6293,15 +6280,23 @@
       </c>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="n">
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN</t>
-        </is>
-      </c>
-      <c r="U55" t="inlineStr"/>
-      <c r="V55" t="inlineStr"/>
+          <t>SUPER MAIS DO GOIÁS</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Atraso do Cliente, cobrança ativa, GC e GM ciente do atraso - Data Comentário: 06/07/2026 15:17</t>
+        </is>
+      </c>
       <c r="W55" t="inlineStr"/>
       <c r="X55" t="inlineStr"/>
       <c r="Y55" t="inlineStr"/>
@@ -6315,22 +6310,22 @@
       <c r="AE55" t="inlineStr"/>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>Tarefa</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="AG55" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>6224</v>
+        <v>6705</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>NARCIZO ALVES CORDEIRO</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -6340,7 +6335,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -6350,11 +6345,11 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>1802</v>
+        <v>6298</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -6366,12 +6361,12 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Est - ICMS RPA - CÓD. 046-2</t>
+          <t>Est - Sintegra Interestadual</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" s="1" t="n">
-        <v>46212</v>
+        <v>46218</v>
       </c>
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
@@ -6380,7 +6375,7 @@
         </is>
       </c>
       <c r="O56" t="n">
-        <v>17688681</v>
+        <v>17949007</v>
       </c>
       <c r="P56" t="inlineStr">
         <is>
@@ -6394,11 +6389,11 @@
       </c>
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="n">
-        <v>-1</v>
+        <v>-7</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>TECNO COM</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6406,11 +6401,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>Atraso do Cliente, cobrança ativa, GC e GM ciente do atraso - Data Comentário: 06/07/2026 15:17</t>
-        </is>
-      </c>
+      <c r="V56" t="inlineStr"/>
       <c r="W56" t="inlineStr"/>
       <c r="X56" t="inlineStr"/>
       <c r="Y56" t="inlineStr"/>
@@ -6424,7 +6415,7 @@
       <c r="AE56" t="inlineStr"/>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Obrigação Acessória</t>
         </is>
       </c>
       <c r="AG56" t="inlineStr">
@@ -6435,11 +6426,11 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>6705</v>
+        <v>6885</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NARCIZO ALVES CORDEIRO</t>
+          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -6489,7 +6480,7 @@
         </is>
       </c>
       <c r="O57" t="n">
-        <v>17949007</v>
+        <v>18134106</v>
       </c>
       <c r="P57" t="inlineStr">
         <is>
@@ -6507,14 +6498,10 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
-        </is>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>EMPORIO DOS FRIOS</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr"/>
       <c r="V57" t="inlineStr"/>
       <c r="W57" t="inlineStr"/>
       <c r="X57" t="inlineStr"/>
@@ -6540,11 +6527,11 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>6885</v>
+        <v>5417</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -6554,7 +6541,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -6564,11 +6551,11 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>6298</v>
+        <v>6806</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -6580,12 +6567,12 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Est - Sintegra Interestadual</t>
+          <t>Fed - EFD - REINF - Entrega e PDF</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" s="1" t="n">
-        <v>46218</v>
+        <v>46216</v>
       </c>
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
@@ -6594,7 +6581,7 @@
         </is>
       </c>
       <c r="O58" t="n">
-        <v>18134106</v>
+        <v>17399228</v>
       </c>
       <c r="P58" t="inlineStr">
         <is>
@@ -6608,14 +6595,18 @@
       </c>
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr"/>
+          <t>NOSSO NOVO SUPERMERCADO</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V58" t="inlineStr"/>
       <c r="W58" t="inlineStr"/>
       <c r="X58" t="inlineStr"/>
@@ -6641,11 +6632,11 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>5417</v>
+        <v>5617</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -6665,7 +6656,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -6695,7 +6686,7 @@
         </is>
       </c>
       <c r="O59" t="n">
-        <v>17399228</v>
+        <v>17407789</v>
       </c>
       <c r="P59" t="inlineStr">
         <is>
@@ -6713,7 +6704,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6746,11 +6737,11 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>5617</v>
+        <v>6224</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -6770,7 +6761,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -6800,7 +6791,7 @@
         </is>
       </c>
       <c r="O60" t="n">
-        <v>17407789</v>
+        <v>17688917</v>
       </c>
       <c r="P60" t="inlineStr">
         <is>
@@ -6851,11 +6842,11 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>6224</v>
+        <v>6278</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>EMPORIO DOS FRIOS LTDA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -6865,7 +6856,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Real - Anual</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -6875,7 +6866,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -6905,7 +6896,7 @@
         </is>
       </c>
       <c r="O61" t="n">
-        <v>17688917</v>
+        <v>17148836</v>
       </c>
       <c r="P61" t="inlineStr">
         <is>
@@ -6923,7 +6914,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -6956,11 +6947,11 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>6278</v>
+        <v>6279</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS LTDA</t>
+          <t>DIENNYFER DA S PEREIRA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -6970,7 +6961,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Federal - Lucro Real - Anual</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -6980,7 +6971,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7010,7 +7001,7 @@
         </is>
       </c>
       <c r="O62" t="n">
-        <v>17148836</v>
+        <v>17071031</v>
       </c>
       <c r="P62" t="inlineStr">
         <is>
@@ -7061,11 +7052,11 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>6279</v>
+        <v>6404</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>DIENNYFER DA S PEREIRA</t>
+          <t>SOLAR INVESTIMENTOS LTDA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -7085,7 +7076,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7115,7 +7106,7 @@
         </is>
       </c>
       <c r="O63" t="n">
-        <v>17071031</v>
+        <v>16962306</v>
       </c>
       <c r="P63" t="inlineStr">
         <is>
@@ -7133,7 +7124,7 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>SOLAR INVESTIMENTOS</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7166,11 +7157,11 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>6404</v>
+        <v>6486</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS LTDA</t>
+          <t>PC GAMER GOIANIA LTDA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -7180,7 +7171,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -7220,7 +7211,7 @@
         </is>
       </c>
       <c r="O64" t="n">
-        <v>16962306</v>
+        <v>16976185</v>
       </c>
       <c r="P64" t="inlineStr">
         <is>
@@ -7238,7 +7229,7 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS</t>
+          <t>PC GAMER</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7271,11 +7262,11 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>6486</v>
+        <v>6703</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PC GAMER GOIANIA LTDA</t>
+          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -7285,7 +7276,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -7325,7 +7316,7 @@
         </is>
       </c>
       <c r="O65" t="n">
-        <v>16976185</v>
+        <v>17948856</v>
       </c>
       <c r="P65" t="inlineStr">
         <is>
@@ -7343,7 +7334,7 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>PC GAMER</t>
+          <t>LIMA MOTA</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7376,11 +7367,11 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>6703</v>
+        <v>6704</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
+          <t>TECNO COM INFORMATICA LTDA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -7390,7 +7381,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -7430,7 +7421,7 @@
         </is>
       </c>
       <c r="O66" t="n">
-        <v>17948856</v>
+        <v>18085295</v>
       </c>
       <c r="P66" t="inlineStr">
         <is>
@@ -7448,7 +7439,7 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>LIMA MOTA</t>
+          <t>TECNO COM</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -7481,11 +7472,11 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>6704</v>
+        <v>6705</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>TECNO COM INFORMATICA LTDA</t>
+          <t>NARCIZO ALVES CORDEIRO</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -7495,7 +7486,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -7535,7 +7526,7 @@
         </is>
       </c>
       <c r="O67" t="n">
-        <v>18085295</v>
+        <v>17949027</v>
       </c>
       <c r="P67" t="inlineStr">
         <is>
@@ -7586,11 +7577,11 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>6705</v>
+        <v>6779</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>NARCIZO ALVES CORDEIRO</t>
+          <t>CORDEIRO E CIA LTDA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -7640,7 +7631,7 @@
         </is>
       </c>
       <c r="O68" t="n">
-        <v>17949027</v>
+        <v>18085064</v>
       </c>
       <c r="P68" t="inlineStr">
         <is>
@@ -7661,11 +7652,7 @@
           <t>TECNO COM</t>
         </is>
       </c>
-      <c r="U68" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+      <c r="U68" t="inlineStr"/>
       <c r="V68" t="inlineStr"/>
       <c r="W68" t="inlineStr"/>
       <c r="X68" t="inlineStr"/>
@@ -7691,11 +7678,11 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>6779</v>
+        <v>6885</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CORDEIRO E CIA LTDA</t>
+          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -7745,7 +7732,7 @@
         </is>
       </c>
       <c r="O69" t="n">
-        <v>18085064</v>
+        <v>18134124</v>
       </c>
       <c r="P69" t="inlineStr">
         <is>
@@ -7763,7 +7750,7 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U69" t="inlineStr"/>
@@ -7792,11 +7779,11 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>6885</v>
+        <v>6224</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -7806,7 +7793,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -7816,11 +7803,11 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>6806</v>
+        <v>11665</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -7832,12 +7819,12 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Fed - EFD - REINF - Entrega e PDF</t>
+          <t>GIAM (TO)</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
       <c r="L70" s="1" t="n">
-        <v>46216</v>
+        <v>46212</v>
       </c>
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr">
@@ -7846,7 +7833,7 @@
         </is>
       </c>
       <c r="O70" t="n">
-        <v>18134124</v>
+        <v>18076580</v>
       </c>
       <c r="P70" t="inlineStr">
         <is>
@@ -7860,15 +7847,23 @@
       </c>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="n">
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
-        </is>
-      </c>
-      <c r="U70" t="inlineStr"/>
-      <c r="V70" t="inlineStr"/>
+          <t>SUPER MAIS DO GOIÁS</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Atraso do Cliente, cobrança ativa, GC e GM ciente do atraso - Data Comentário: 06/07/2026 15:55</t>
+        </is>
+      </c>
       <c r="W70" t="inlineStr"/>
       <c r="X70" t="inlineStr"/>
       <c r="Y70" t="inlineStr"/>
@@ -7882,7 +7877,7 @@
       <c r="AE70" t="inlineStr"/>
       <c r="AF70" t="inlineStr">
         <is>
-          <t>Obrigação Acessória</t>
+          <t>Tarefa</t>
         </is>
       </c>
       <c r="AG70" t="inlineStr">
@@ -7893,11 +7888,11 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>6224</v>
+        <v>5417</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -7917,14 +7912,14 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>11665</v>
+        <v>7884</v>
       </c>
       <c r="H71" t="n">
-        <v>0</v>
+        <v>9114</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -7933,12 +7928,12 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>GIAM (TO)</t>
+          <t>Log/Envio de Inconsistência (Mensal)</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
       <c r="L71" s="1" t="n">
-        <v>46212</v>
+        <v>46218</v>
       </c>
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr">
@@ -7947,7 +7942,7 @@
         </is>
       </c>
       <c r="O71" t="n">
-        <v>18076580</v>
+        <v>17399338</v>
       </c>
       <c r="P71" t="inlineStr">
         <is>
@@ -7961,11 +7956,11 @@
       </c>
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="n">
-        <v>-1</v>
+        <v>-7</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>NOSSO NOVO SUPERMERCADO</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -7975,7 +7970,7 @@
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>Atraso do Cliente, cobrança ativa, GC e GM ciente do atraso - Data Comentário: 06/07/2026 15:55</t>
+          <t>Log de Inconsistências anexado via sistema - \\SRVMGC\DADOS\GOIAS\2026\5417 - COMERCIAL DE ALIMENTOS\EF - VAREJO\CONTROLE MENSAL\06 - JUNHO\ACESSÓRIA\INCONSISTENCIA\\5417-06-2026 Mensal 06-07-2026 141701.xlsx - Data Comentário: 06/07/2026 14:16</t>
         </is>
       </c>
       <c r="W71" t="inlineStr"/>
@@ -8002,11 +7997,11 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>5417</v>
+        <v>5617</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -8026,7 +8021,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8056,7 +8051,7 @@
         </is>
       </c>
       <c r="O72" t="n">
-        <v>17399338</v>
+        <v>18120594</v>
       </c>
       <c r="P72" t="inlineStr">
         <is>
@@ -8074,7 +8069,7 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -8082,11 +8077,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V72" t="inlineStr">
-        <is>
-          <t>Log de Inconsistências anexado via sistema - \\SRVMGC\DADOS\GOIAS\2026\5417 - COMERCIAL DE ALIMENTOS\EF - VAREJO\CONTROLE MENSAL\06 - JUNHO\ACESSÓRIA\INCONSISTENCIA\\5417-06-2026 Mensal 06-07-2026 141701.xlsx - Data Comentário: 06/07/2026 14:16</t>
-        </is>
-      </c>
+      <c r="V72" t="inlineStr"/>
       <c r="W72" t="inlineStr"/>
       <c r="X72" t="inlineStr"/>
       <c r="Y72" t="inlineStr"/>
@@ -8111,11 +8102,11 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>5617</v>
+        <v>6705</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>NARCIZO ALVES CORDEIRO</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -8125,7 +8116,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -8139,10 +8130,10 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>7884</v>
+        <v>1793</v>
       </c>
       <c r="H73" t="n">
-        <v>9114</v>
+        <v>0</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -8151,21 +8142,25 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Log/Envio de Inconsistência (Mensal)</t>
+          <t>Mun - ISS Serv. Tomados</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
       <c r="L73" s="1" t="n">
-        <v>46218</v>
-      </c>
-      <c r="M73" t="inlineStr"/>
+        <v>46213</v>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
       <c r="N73" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O73" t="n">
-        <v>18120594</v>
+        <v>17948926</v>
       </c>
       <c r="P73" t="inlineStr">
         <is>
@@ -8179,11 +8174,11 @@
       </c>
       <c r="R73" t="inlineStr"/>
       <c r="S73" t="n">
-        <v>-7</v>
+        <v>-2</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>TECNO COM</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -8191,7 +8186,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V73" t="inlineStr"/>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 08/07/2026 - Data Comentário: 06/07/2026 15:51</t>
+        </is>
+      </c>
       <c r="W73" t="inlineStr"/>
       <c r="X73" t="inlineStr"/>
       <c r="Y73" t="inlineStr"/>
@@ -8205,7 +8204,7 @@
       <c r="AE73" t="inlineStr"/>
       <c r="AF73" t="inlineStr">
         <is>
-          <t>Tarefa</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="AG73" t="inlineStr">
@@ -8216,11 +8215,11 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>6705</v>
+        <v>6779</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>NARCIZO ALVES CORDEIRO</t>
+          <t>CORDEIRO E CIA LTDA</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -8274,7 +8273,7 @@
         </is>
       </c>
       <c r="O74" t="n">
-        <v>17948926</v>
+        <v>18084953</v>
       </c>
       <c r="P74" t="inlineStr">
         <is>
@@ -8295,11 +8294,7 @@
           <t>TECNO COM</t>
         </is>
       </c>
-      <c r="U74" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+      <c r="U74" t="inlineStr"/>
       <c r="V74" t="inlineStr">
         <is>
           <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 08/07/2026 - Data Comentário: 06/07/2026 15:51</t>
@@ -8329,11 +8324,11 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>6779</v>
+        <v>6885</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>CORDEIRO E CIA LTDA</t>
+          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -8387,7 +8382,7 @@
         </is>
       </c>
       <c r="O75" t="n">
-        <v>18084953</v>
+        <v>18134033</v>
       </c>
       <c r="P75" t="inlineStr">
         <is>
@@ -8405,7 +8400,7 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U75" t="inlineStr"/>
@@ -8438,11 +8433,11 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>6885</v>
+        <v>6703</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
+          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -8452,7 +8447,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -8466,7 +8461,7 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>1793</v>
+        <v>1796</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -8478,12 +8473,12 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Mun - ISS Serv. Tomados</t>
+          <t>Produtor Rural</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
       <c r="L76" s="1" t="n">
-        <v>46213</v>
+        <v>46211</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
@@ -8496,7 +8491,7 @@
         </is>
       </c>
       <c r="O76" t="n">
-        <v>18134033</v>
+        <v>18073096</v>
       </c>
       <c r="P76" t="inlineStr">
         <is>
@@ -8510,17 +8505,21 @@
       </c>
       <c r="R76" t="inlineStr"/>
       <c r="S76" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
-        </is>
-      </c>
-      <c r="U76" t="inlineStr"/>
+          <t>LIMA MOTA</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 08/07/2026 - Data Comentário: 06/07/2026 15:51</t>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 08/07/2026 - Data Comentário: 06/07/2026 14:49</t>
         </is>
       </c>
       <c r="W76" t="inlineStr"/>
@@ -8536,7 +8535,7 @@
       <c r="AE76" t="inlineStr"/>
       <c r="AF76" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Tarefa</t>
         </is>
       </c>
       <c r="AG76" t="inlineStr">
@@ -8547,11 +8546,11 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>6703</v>
+        <v>6705</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
+          <t>NARCIZO ALVES CORDEIRO</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -8561,7 +8560,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -8575,10 +8574,10 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>1796</v>
+        <v>6294</v>
       </c>
       <c r="H77" t="n">
-        <v>0</v>
+        <v>1788</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -8587,25 +8586,21 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Produtor Rural</t>
+          <t>Recebimento NFCE</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
       <c r="L77" s="1" t="n">
-        <v>46211</v>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>08/07/2026</t>
-        </is>
-      </c>
+        <v>46216</v>
+      </c>
+      <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O77" t="n">
-        <v>18073096</v>
+        <v>17948997</v>
       </c>
       <c r="P77" t="inlineStr">
         <is>
@@ -8619,11 +8614,11 @@
       </c>
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>LIMA MOTA</t>
+          <t>TECNO COM</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -8631,11 +8626,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V77" t="inlineStr">
-        <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 08/07/2026 - Data Comentário: 06/07/2026 14:49</t>
-        </is>
-      </c>
+      <c r="V77" t="inlineStr"/>
       <c r="W77" t="inlineStr"/>
       <c r="X77" t="inlineStr"/>
       <c r="Y77" t="inlineStr"/>
@@ -8660,11 +8651,11 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>6705</v>
+        <v>5617</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>NARCIZO ALVES CORDEIRO</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -8674,7 +8665,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -8688,10 +8679,10 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>6294</v>
+        <v>11303</v>
       </c>
       <c r="H78" t="n">
-        <v>1788</v>
+        <v>0</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -8700,12 +8691,12 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Recebimento NFCE</t>
+          <t>Retorno do Check-List Fiscal</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
       <c r="L78" s="1" t="n">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr">
@@ -8714,7 +8705,7 @@
         </is>
       </c>
       <c r="O78" t="n">
-        <v>17948997</v>
+        <v>17407963</v>
       </c>
       <c r="P78" t="inlineStr">
         <is>
@@ -8728,11 +8719,11 @@
       </c>
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="n">
-        <v>-5</v>
+        <v>-7</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -8765,11 +8756,11 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>5617</v>
+        <v>6704</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>TECNO COM INFORMATICA LTDA</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -8793,24 +8784,24 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>11303</v>
+        <v>951</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Retorno do Check-List Fiscal</t>
+          <t>Confirm Rec - ISS Tomados</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
       <c r="L79" s="1" t="n">
-        <v>46218</v>
+        <v>46213</v>
       </c>
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr">
@@ -8819,11 +8810,11 @@
         </is>
       </c>
       <c r="O79" t="n">
-        <v>17407963</v>
+        <v>17952349</v>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Cristina Leite</t>
+          <t>Victoria Virgens</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
@@ -8833,11 +8824,11 @@
       </c>
       <c r="R79" t="inlineStr"/>
       <c r="S79" t="n">
-        <v>-7</v>
+        <v>-2</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>TECNO COM</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
@@ -8845,7 +8836,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V79" t="inlineStr"/>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1793] sendo a ultima baixa feita [1793]-07/07/2026 19:15:35.. - Data Comentário: 07/07/2026 19:15</t>
+        </is>
+      </c>
       <c r="W79" t="inlineStr"/>
       <c r="X79" t="inlineStr"/>
       <c r="Y79" t="inlineStr"/>
@@ -8859,22 +8854,18 @@
       <c r="AE79" t="inlineStr"/>
       <c r="AF79" t="inlineStr">
         <is>
-          <t>Tarefa</t>
-        </is>
-      </c>
-      <c r="AG79" t="inlineStr">
-        <is>
-          <t>Ricardo Fischer</t>
-        </is>
-      </c>
+          <t>Imposto</t>
+        </is>
+      </c>
+      <c r="AG79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>6704</v>
+        <v>6278</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>TECNO COM INFORMATICA LTDA</t>
+          <t>EMPORIO DOS FRIOS LTDA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -8884,7 +8875,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Real - Anual</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -8898,19 +8889,19 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>951</v>
+        <v>6017</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Confirm Rec - ISS Tomados</t>
+          <t>Cobrança de inventário SPED ICMS</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
@@ -8924,11 +8915,11 @@
         </is>
       </c>
       <c r="O80" t="n">
-        <v>17952349</v>
+        <v>17539760</v>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Victoria Virgens</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
@@ -8942,7 +8933,7 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
@@ -8950,11 +8941,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V80" t="inlineStr">
-        <is>
-          <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1793] sendo a ultima baixa feita [1793]-07/07/2026 19:15:35.. - Data Comentário: 07/07/2026 19:15</t>
-        </is>
-      </c>
+      <c r="V80" t="inlineStr"/>
       <c r="W80" t="inlineStr"/>
       <c r="X80" t="inlineStr"/>
       <c r="Y80" t="inlineStr"/>
@@ -8968,18 +8955,18 @@
       <c r="AE80" t="inlineStr"/>
       <c r="AF80" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Tarefa</t>
         </is>
       </c>
       <c r="AG80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>6278</v>
+        <v>6404</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS LTDA</t>
+          <t>SOLAR INVESTIMENTOS LTDA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -8989,7 +8976,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Federal - Lucro Real - Anual</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -9029,11 +9016,11 @@
         </is>
       </c>
       <c r="O81" t="n">
-        <v>17539760</v>
+        <v>16962256</v>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
@@ -9047,7 +9034,7 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>SOLAR INVESTIMENTOS</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
@@ -9076,11 +9063,11 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>6404</v>
+        <v>6627</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS LTDA</t>
+          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -9090,12 +9077,12 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -9130,11 +9117,11 @@
         </is>
       </c>
       <c r="O82" t="n">
-        <v>16962256</v>
+        <v>17042432</v>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
@@ -9148,7 +9135,7 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS</t>
+          <t xml:space="preserve">GTG </t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
@@ -9177,11 +9164,11 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>6627</v>
+        <v>6704</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
+          <t>TECNO COM INFORMATICA LTDA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -9196,7 +9183,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -9231,7 +9218,7 @@
         </is>
       </c>
       <c r="O83" t="n">
-        <v>17042432</v>
+        <v>17952390</v>
       </c>
       <c r="P83" t="inlineStr">
         <is>
@@ -9249,7 +9236,7 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
+          <t>TECNO COM</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
@@ -9278,11 +9265,11 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>6704</v>
+        <v>6885</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>TECNO COM INFORMATICA LTDA</t>
+          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -9292,7 +9279,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -9332,7 +9319,7 @@
         </is>
       </c>
       <c r="O84" t="n">
-        <v>17952390</v>
+        <v>18128767</v>
       </c>
       <c r="P84" t="inlineStr">
         <is>
@@ -9350,14 +9337,10 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
-        </is>
-      </c>
-      <c r="U84" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>EMPORIO DOS FRIOS</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr"/>
       <c r="V84" t="inlineStr"/>
       <c r="W84" t="inlineStr"/>
       <c r="X84" t="inlineStr"/>
@@ -9379,11 +9362,11 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>6885</v>
+        <v>5417</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -9393,7 +9376,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -9403,11 +9386,11 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>6017</v>
+        <v>11746</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
@@ -9419,7 +9402,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Cobrança de inventário SPED ICMS</t>
+          <t>Distribuição de Lucro Mensal</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -9433,7 +9416,7 @@
         </is>
       </c>
       <c r="O85" t="n">
-        <v>18128767</v>
+        <v>17994309</v>
       </c>
       <c r="P85" t="inlineStr">
         <is>
@@ -9451,10 +9434,14 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
-        </is>
-      </c>
-      <c r="U85" t="inlineStr"/>
+          <t>NOSSO NOVO SUPERMERCADO</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V85" t="inlineStr"/>
       <c r="W85" t="inlineStr"/>
       <c r="X85" t="inlineStr"/>
@@ -9476,11 +9463,11 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>5417</v>
+        <v>5617</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -9500,7 +9487,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -9530,7 +9517,7 @@
         </is>
       </c>
       <c r="O86" t="n">
-        <v>17994309</v>
+        <v>18001695</v>
       </c>
       <c r="P86" t="inlineStr">
         <is>
@@ -9548,7 +9535,7 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
@@ -9577,11 +9564,11 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>5617</v>
+        <v>6224</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -9601,7 +9588,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -9631,11 +9618,11 @@
         </is>
       </c>
       <c r="O87" t="n">
-        <v>18001695</v>
+        <v>18004470</v>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
@@ -9678,11 +9665,11 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>6224</v>
+        <v>6278</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>EMPORIO DOS FRIOS LTDA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -9692,7 +9679,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Real - Anual</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -9702,7 +9689,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -9732,11 +9719,11 @@
         </is>
       </c>
       <c r="O88" t="n">
-        <v>18004470</v>
+        <v>17994320</v>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
@@ -9750,7 +9737,7 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
@@ -9779,11 +9766,11 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>6278</v>
+        <v>6279</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS LTDA</t>
+          <t>DIENNYFER DA S PEREIRA</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -9793,7 +9780,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Federal - Lucro Real - Anual</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -9803,7 +9790,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -9833,7 +9820,7 @@
         </is>
       </c>
       <c r="O89" t="n">
-        <v>17994320</v>
+        <v>17995240</v>
       </c>
       <c r="P89" t="inlineStr">
         <is>
@@ -9880,11 +9867,11 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>6279</v>
+        <v>6404</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>DIENNYFER DA S PEREIRA</t>
+          <t>SOLAR INVESTIMENTOS LTDA</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -9904,7 +9891,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -9934,11 +9921,11 @@
         </is>
       </c>
       <c r="O90" t="n">
-        <v>17995240</v>
+        <v>17994673</v>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
@@ -9952,7 +9939,7 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>SOLAR INVESTIMENTOS</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
@@ -9981,11 +9968,11 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>6404</v>
+        <v>6486</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS LTDA</t>
+          <t>PC GAMER GOIANIA LTDA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -9995,7 +9982,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -10035,7 +10022,7 @@
         </is>
       </c>
       <c r="O91" t="n">
-        <v>17994673</v>
+        <v>17994807</v>
       </c>
       <c r="P91" t="inlineStr">
         <is>
@@ -10053,7 +10040,7 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS</t>
+          <t>PC GAMER</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
@@ -10082,11 +10069,11 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>6486</v>
+        <v>6548</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>PC GAMER GOIANIA LTDA</t>
+          <t>GOIAS SILAGEM LTDA</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -10136,11 +10123,11 @@
         </is>
       </c>
       <c r="O92" t="n">
-        <v>17994807</v>
+        <v>18006049</v>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
@@ -10154,7 +10141,7 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>PC GAMER</t>
+          <t>GOIAS SILAGEM</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
@@ -10183,11 +10170,11 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>6548</v>
+        <v>6628</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM LTDA</t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -10197,12 +10184,12 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -10237,7 +10224,7 @@
         </is>
       </c>
       <c r="O93" t="n">
-        <v>18006049</v>
+        <v>18003254</v>
       </c>
       <c r="P93" t="inlineStr">
         <is>
@@ -10255,7 +10242,7 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM</t>
+          <t xml:space="preserve">GTG </t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
@@ -10284,11 +10271,11 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>6628</v>
+        <v>6703</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -10298,12 +10285,12 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -10338,7 +10325,7 @@
         </is>
       </c>
       <c r="O94" t="n">
-        <v>18003254</v>
+        <v>18004015</v>
       </c>
       <c r="P94" t="inlineStr">
         <is>
@@ -10356,7 +10343,7 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
+          <t>LIMA MOTA</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
@@ -10385,11 +10372,11 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>6703</v>
+        <v>6704</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
+          <t>TECNO COM INFORMATICA LTDA</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -10399,7 +10386,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -10439,7 +10426,7 @@
         </is>
       </c>
       <c r="O95" t="n">
-        <v>18004015</v>
+        <v>17995162</v>
       </c>
       <c r="P95" t="inlineStr">
         <is>
@@ -10457,7 +10444,7 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>LIMA MOTA</t>
+          <t>TECNO COM</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
@@ -10486,11 +10473,11 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>6704</v>
+        <v>6705</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>TECNO COM INFORMATICA LTDA</t>
+          <t>NARCIZO ALVES CORDEIRO</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -10500,7 +10487,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -10540,7 +10527,7 @@
         </is>
       </c>
       <c r="O96" t="n">
-        <v>17995162</v>
+        <v>18004026</v>
       </c>
       <c r="P96" t="inlineStr">
         <is>
@@ -10587,11 +10574,11 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>6705</v>
+        <v>6949</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>NARCIZO ALVES CORDEIRO</t>
+          <t>TEC GRUA LOCAÇÃO E COMERCIO DE EQUIPAMENTOS PARA CONSTRUÇÃO LTDA</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -10601,7 +10588,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -10611,70 +10598,77 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Reynaldo Santos</t>
         </is>
       </c>
       <c r="G97" t="n">
-        <v>11746</v>
+        <v>11615</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Distribuição de Lucro Mensal</t>
+          <t>Envio de ATA de Implantação - CTB I</t>
         </is>
       </c>
       <c r="K97" t="inlineStr"/>
       <c r="L97" s="1" t="n">
-        <v>46213</v>
-      </c>
-      <c r="M97" t="inlineStr"/>
+        <v>46206</v>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
       <c r="N97" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O97" t="n">
-        <v>18004026</v>
-      </c>
-      <c r="P97" t="inlineStr">
-        <is>
-          <t>Sergio Fernandes</t>
-        </is>
-      </c>
+        <v>18166586</v>
+      </c>
+      <c r="P97" t="inlineStr"/>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>Em Aberto</t>
-        </is>
-      </c>
-      <c r="R97" t="inlineStr"/>
+          <t>Baixado</t>
+        </is>
+      </c>
+      <c r="R97" s="1" t="n">
+        <v>46206.43215109954</v>
+      </c>
       <c r="S97" t="n">
-        <v>-2</v>
+        <v>5</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
-        </is>
-      </c>
-      <c r="U97" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="V97" t="inlineStr"/>
+          <t>TEC GRUA</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr"/>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 26/06/2026 
+Aguardando agendamento das implantações - Data Comentário: 18/06/2026 17:44</t>
+        </is>
+      </c>
       <c r="W97" t="inlineStr"/>
       <c r="X97" t="inlineStr"/>
       <c r="Y97" t="inlineStr"/>
       <c r="Z97" t="n">
         <v>0</v>
       </c>
-      <c r="AA97" t="inlineStr"/>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>Erika Santana</t>
+        </is>
+      </c>
       <c r="AB97" t="inlineStr"/>
       <c r="AC97" t="inlineStr"/>
       <c r="AD97" t="inlineStr"/>
@@ -10688,11 +10682,11 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>6949</v>
+        <v>6962</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>TEC GRUA LOCAÇÃO E COMERCIO DE EQUIPAMENTOS PARA CONSTRUÇÃO LTDA</t>
+          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -10735,18 +10729,14 @@
       <c r="L98" s="1" t="n">
         <v>46206</v>
       </c>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>26/06/2026</t>
-        </is>
-      </c>
+      <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O98" t="n">
-        <v>18166586</v>
+        <v>18186559</v>
       </c>
       <c r="P98" t="inlineStr"/>
       <c r="Q98" t="inlineStr">
@@ -10755,21 +10745,20 @@
         </is>
       </c>
       <c r="R98" s="1" t="n">
-        <v>46206.43215109954</v>
+        <v>46206.43205978009</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>TEC GRUA</t>
+          <t>PROMOTORAS GYN</t>
         </is>
       </c>
       <c r="U98" t="inlineStr"/>
       <c r="V98" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 26/06/2026 
-Aguardando agendamento das implantações - Data Comentário: 18/06/2026 17:44</t>
+          <t>Rotina Para Criar Tarefas Dos Clientes Novos - CodCliente: 6962; Tarefa Incluida: 11615; Vencimento: 17/06/2026 00:00:00; UsuarioResponsavel: erikas - Data Comentário: 17/06/2026 11:09</t>
         </is>
       </c>
       <c r="W98" t="inlineStr"/>
@@ -10796,11 +10785,11 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
+          <t>PROMOTORAS GYN LTDA</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -10850,7 +10839,7 @@
         </is>
       </c>
       <c r="O99" t="n">
-        <v>18186559</v>
+        <v>18186560</v>
       </c>
       <c r="P99" t="inlineStr"/>
       <c r="Q99" t="inlineStr">
@@ -10859,7 +10848,7 @@
         </is>
       </c>
       <c r="R99" s="1" t="n">
-        <v>46206.43205978009</v>
+        <v>46206.43206049768</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -10872,7 +10861,7 @@
       <c r="U99" t="inlineStr"/>
       <c r="V99" t="inlineStr">
         <is>
-          <t>Rotina Para Criar Tarefas Dos Clientes Novos - CodCliente: 6962; Tarefa Incluida: 11615; Vencimento: 17/06/2026 00:00:00; UsuarioResponsavel: erikas - Data Comentário: 17/06/2026 11:09</t>
+          <t>Rotina Para Criar Tarefas Dos Clientes Novos - CodCliente: 6963; Tarefa Incluida: 11615; Vencimento: 17/06/2026 00:00:00; UsuarioResponsavel: erikas - Data Comentário: 17/06/2026 11:09</t>
         </is>
       </c>
       <c r="W99" t="inlineStr"/>
@@ -10899,11 +10888,11 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>6963</v>
+        <v>6548</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN LTDA</t>
+          <t>GOIAS SILAGEM LTDA</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -10923,11 +10912,11 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G100" t="n">
-        <v>11615</v>
+        <v>11299</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
@@ -10939,12 +10928,12 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Envio de ATA de Implantação - CTB I</t>
+          <t>Retorno do Check-List</t>
         </is>
       </c>
       <c r="K100" t="inlineStr"/>
       <c r="L100" s="1" t="n">
-        <v>46206</v>
+        <v>46218</v>
       </c>
       <c r="M100" t="inlineStr"/>
       <c r="N100" t="inlineStr">
@@ -10953,31 +10942,35 @@
         </is>
       </c>
       <c r="O100" t="n">
-        <v>18186560</v>
-      </c>
-      <c r="P100" t="inlineStr"/>
+        <v>17968039</v>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Thais Souza</t>
+        </is>
+      </c>
       <c r="Q100" t="inlineStr">
         <is>
           <t>Baixado</t>
         </is>
       </c>
       <c r="R100" s="1" t="n">
-        <v>46206.43206049768</v>
+        <v>46204.75352534722</v>
       </c>
       <c r="S100" t="n">
-        <v>5</v>
+        <v>-7</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN</t>
-        </is>
-      </c>
-      <c r="U100" t="inlineStr"/>
-      <c r="V100" t="inlineStr">
-        <is>
-          <t>Rotina Para Criar Tarefas Dos Clientes Novos - CodCliente: 6963; Tarefa Incluida: 11615; Vencimento: 17/06/2026 00:00:00; UsuarioResponsavel: erikas - Data Comentário: 17/06/2026 11:09</t>
-        </is>
-      </c>
+          <t>GOIAS SILAGEM</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr"/>
       <c r="W100" t="inlineStr"/>
       <c r="X100" t="inlineStr"/>
       <c r="Y100" t="inlineStr"/>
@@ -10986,7 +10979,7 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>Erika Santana</t>
+          <t>Juan Rodrigues</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr"/>
@@ -10998,15 +10991,19 @@
           <t>Tarefa</t>
         </is>
       </c>
-      <c r="AG100" t="inlineStr"/>
+      <c r="AG100" t="inlineStr">
+        <is>
+          <t>Erika Santana</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM LTDA</t>
+          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -11021,7 +11018,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -11056,11 +11053,11 @@
         </is>
       </c>
       <c r="O101" t="n">
-        <v>17968039</v>
+        <v>17042639</v>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Thais Souza</t>
+          <t>Nathalia Lourenco</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
@@ -11069,14 +11066,14 @@
         </is>
       </c>
       <c r="R101" s="1" t="n">
-        <v>46204.75352534722</v>
+        <v>46204.75352809028</v>
       </c>
       <c r="S101" t="n">
         <v>-7</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM</t>
+          <t xml:space="preserve">GTG </t>
         </is>
       </c>
       <c r="U101" t="inlineStr">
@@ -11107,17 +11104,17 @@
       </c>
       <c r="AG101" t="inlineStr">
         <is>
-          <t>Erika Santana</t>
+          <t>Isabella Nascimento</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -11127,7 +11124,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -11167,7 +11164,7 @@
         </is>
       </c>
       <c r="O102" t="n">
-        <v>17042639</v>
+        <v>16960108</v>
       </c>
       <c r="P102" t="inlineStr">
         <is>
@@ -11180,7 +11177,7 @@
         </is>
       </c>
       <c r="R102" s="1" t="n">
-        <v>46204.75352809028</v>
+        <v>46204.7535284375</v>
       </c>
       <c r="S102" t="n">
         <v>-7</v>
@@ -11224,11 +11221,11 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>6628</v>
+        <v>6945</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -11278,11 +11275,11 @@
         </is>
       </c>
       <c r="O103" t="n">
-        <v>16960108</v>
+        <v>18163697</v>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Nathalia Lourenco</t>
+          <t>Laisa Rocha</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
@@ -11291,21 +11288,17 @@
         </is>
       </c>
       <c r="R103" s="1" t="n">
-        <v>46204.7535284375</v>
+        <v>46204.7535334838</v>
       </c>
       <c r="S103" t="n">
         <v>-7</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
-        </is>
-      </c>
-      <c r="U103" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>BRASIL DISTRIBUIDORA</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr"/>
       <c r="V103" t="inlineStr"/>
       <c r="W103" t="inlineStr"/>
       <c r="X103" t="inlineStr"/>
@@ -11335,11 +11328,11 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>6945</v>
+        <v>6962</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
+          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -11349,17 +11342,17 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Reynaldo Santos</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -11389,11 +11382,11 @@
         </is>
       </c>
       <c r="O104" t="n">
-        <v>18163697</v>
+        <v>18187976</v>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Laisa Rocha</t>
+          <t>Mirian Lima</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
@@ -11402,14 +11395,14 @@
         </is>
       </c>
       <c r="R104" s="1" t="n">
-        <v>46204.7535334838</v>
+        <v>46204.75353387732</v>
       </c>
       <c r="S104" t="n">
         <v>-7</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA</t>
+          <t>PROMOTORAS GYN</t>
         </is>
       </c>
       <c r="U104" t="inlineStr"/>
@@ -11442,11 +11435,11 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
+          <t>PROMOTORAS GYN LTDA</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -11496,7 +11489,7 @@
         </is>
       </c>
       <c r="O105" t="n">
-        <v>18187976</v>
+        <v>18187914</v>
       </c>
       <c r="P105" t="inlineStr">
         <is>
@@ -11509,7 +11502,7 @@
         </is>
       </c>
       <c r="R105" s="1" t="n">
-        <v>46204.75353387732</v>
+        <v>46204.75353515046</v>
       </c>
       <c r="S105" t="n">
         <v>-7</v>
@@ -11549,11 +11542,11 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>6963</v>
+        <v>5417</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN LTDA</t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -11573,18 +11566,18 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>11299</v>
+        <v>11297</v>
       </c>
       <c r="H106" t="n">
         <v>0</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL INDUSTRIA</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -11603,11 +11596,11 @@
         </is>
       </c>
       <c r="O106" t="n">
-        <v>18187914</v>
+        <v>17399442</v>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Mirian Lima</t>
+          <t>Eveny Silva</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
@@ -11616,17 +11609,21 @@
         </is>
       </c>
       <c r="R106" s="1" t="n">
-        <v>46204.75353515046</v>
+        <v>46204.75350494213</v>
       </c>
       <c r="S106" t="n">
         <v>-7</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN</t>
-        </is>
-      </c>
-      <c r="U106" t="inlineStr"/>
+          <t>NOSSO NOVO SUPERMERCADO</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V106" t="inlineStr"/>
       <c r="W106" t="inlineStr"/>
       <c r="X106" t="inlineStr"/>
@@ -11650,17 +11647,17 @@
       </c>
       <c r="AG106" t="inlineStr">
         <is>
-          <t>Isabella Nascimento</t>
+          <t>Karina Santos</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>5417</v>
+        <v>5617</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -11680,7 +11677,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -11710,11 +11707,11 @@
         </is>
       </c>
       <c r="O107" t="n">
-        <v>17399442</v>
+        <v>17407953</v>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Eveny Silva</t>
+          <t>Jackson Silva</t>
         </is>
       </c>
       <c r="Q107" t="inlineStr">
@@ -11723,14 +11720,14 @@
         </is>
       </c>
       <c r="R107" s="1" t="n">
-        <v>46204.75350494213</v>
+        <v>46204.75351072917</v>
       </c>
       <c r="S107" t="n">
         <v>-7</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U107" t="inlineStr">
@@ -11761,17 +11758,17 @@
       </c>
       <c r="AG107" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>5617</v>
+        <v>6224</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -11791,7 +11788,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -11821,7 +11818,7 @@
         </is>
       </c>
       <c r="O108" t="n">
-        <v>17407953</v>
+        <v>17689061</v>
       </c>
       <c r="P108" t="inlineStr">
         <is>
@@ -11834,7 +11831,7 @@
         </is>
       </c>
       <c r="R108" s="1" t="n">
-        <v>46204.75351072917</v>
+        <v>46204.75352068287</v>
       </c>
       <c r="S108" t="n">
         <v>-7</v>
@@ -11878,11 +11875,11 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>6224</v>
+        <v>6278</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>EMPORIO DOS FRIOS LTDA</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -11892,7 +11889,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Real - Anual</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -11902,7 +11899,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -11932,11 +11929,11 @@
         </is>
       </c>
       <c r="O109" t="n">
-        <v>17689061</v>
+        <v>17539888</v>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Jackson Silva</t>
+          <t>Isabela Lemos</t>
         </is>
       </c>
       <c r="Q109" t="inlineStr">
@@ -11945,14 +11942,14 @@
         </is>
       </c>
       <c r="R109" s="1" t="n">
-        <v>46204.75352068287</v>
+        <v>46204.75352175926</v>
       </c>
       <c r="S109" t="n">
         <v>-7</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U109" t="inlineStr">
@@ -11983,17 +11980,17 @@
       </c>
       <c r="AG109" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>6278</v>
+        <v>6704</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS LTDA</t>
+          <t>TECNO COM INFORMATICA LTDA</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -12003,7 +12000,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Federal - Lucro Real - Anual</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -12043,11 +12040,11 @@
         </is>
       </c>
       <c r="O110" t="n">
-        <v>17539888</v>
+        <v>17955432</v>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Isabela Lemos</t>
+          <t>Paulo Silva</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
@@ -12056,14 +12053,14 @@
         </is>
       </c>
       <c r="R110" s="1" t="n">
-        <v>46204.75352175926</v>
+        <v>46204.75353024306</v>
       </c>
       <c r="S110" t="n">
         <v>-7</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>TECNO COM</t>
         </is>
       </c>
       <c r="U110" t="inlineStr">
@@ -12100,11 +12097,11 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>6704</v>
+        <v>6705</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>TECNO COM INFORMATICA LTDA</t>
+          <t>NARCIZO ALVES CORDEIRO</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -12114,7 +12111,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -12154,7 +12151,7 @@
         </is>
       </c>
       <c r="O111" t="n">
-        <v>17955432</v>
+        <v>17955272</v>
       </c>
       <c r="P111" t="inlineStr">
         <is>
@@ -12167,7 +12164,7 @@
         </is>
       </c>
       <c r="R111" s="1" t="n">
-        <v>46204.75353024306</v>
+        <v>46204.7535309838</v>
       </c>
       <c r="S111" t="n">
         <v>-7</v>
@@ -12211,11 +12208,11 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>6705</v>
+        <v>6779</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>NARCIZO ALVES CORDEIRO</t>
+          <t>CORDEIRO E CIA LTDA</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -12265,7 +12262,7 @@
         </is>
       </c>
       <c r="O112" t="n">
-        <v>17955272</v>
+        <v>18056830</v>
       </c>
       <c r="P112" t="inlineStr">
         <is>
@@ -12278,7 +12275,7 @@
         </is>
       </c>
       <c r="R112" s="1" t="n">
-        <v>46204.7535309838</v>
+        <v>46204.75353240741</v>
       </c>
       <c r="S112" t="n">
         <v>-7</v>
@@ -12288,11 +12285,7 @@
           <t>TECNO COM</t>
         </is>
       </c>
-      <c r="U112" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+      <c r="U112" t="inlineStr"/>
       <c r="V112" t="inlineStr"/>
       <c r="W112" t="inlineStr"/>
       <c r="X112" t="inlineStr"/>
@@ -12322,11 +12315,11 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>6779</v>
+        <v>6885</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>CORDEIRO E CIA LTDA</t>
+          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -12376,11 +12369,11 @@
         </is>
       </c>
       <c r="O113" t="n">
-        <v>18056830</v>
+        <v>18128901</v>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Paulo Silva</t>
+          <t>Isabela Lemos</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr">
@@ -12389,14 +12382,14 @@
         </is>
       </c>
       <c r="R113" s="1" t="n">
-        <v>46204.75353240741</v>
+        <v>46204.75353278935</v>
       </c>
       <c r="S113" t="n">
         <v>-7</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U113" t="inlineStr"/>
@@ -12429,11 +12422,11 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>6885</v>
+        <v>6628</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -12448,7 +12441,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -12457,57 +12450,61 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>11297</v>
+        <v>11817</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Retorno do Check-List</t>
+          <t>Alteração dados cadastrais</t>
         </is>
       </c>
       <c r="K114" t="inlineStr"/>
       <c r="L114" s="1" t="n">
-        <v>46218</v>
+        <v>46205</v>
       </c>
       <c r="M114" t="inlineStr"/>
       <c r="N114" t="inlineStr">
         <is>
-          <t>06/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
       <c r="O114" t="n">
-        <v>18128901</v>
-      </c>
-      <c r="P114" t="inlineStr">
-        <is>
-          <t>Isabela Lemos</t>
-        </is>
-      </c>
+        <v>18199226</v>
+      </c>
+      <c r="P114" t="inlineStr"/>
       <c r="Q114" t="inlineStr">
         <is>
           <t>Baixado</t>
         </is>
       </c>
       <c r="R114" s="1" t="n">
-        <v>46204.75353278935</v>
+        <v>46205.599529375</v>
       </c>
       <c r="S114" t="n">
-        <v>-7</v>
+        <v>6</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
-        </is>
-      </c>
-      <c r="U114" t="inlineStr"/>
-      <c r="V114" t="inlineStr"/>
+          <t xml:space="preserve">GTG </t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Aplicação de promoção. - Data Comentário: 02/07/2026 11:13</t>
+        </is>
+      </c>
       <c r="W114" t="inlineStr"/>
       <c r="X114" t="inlineStr"/>
       <c r="Y114" t="inlineStr"/>
@@ -12516,7 +12513,7 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>Juan Rodrigues</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr"/>
@@ -12528,19 +12525,15 @@
           <t>Tarefa</t>
         </is>
       </c>
-      <c r="AG114" t="inlineStr">
-        <is>
-          <t>Fernanda Araujo</t>
-        </is>
-      </c>
+      <c r="AG114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>6628</v>
+        <v>5417</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -12550,21 +12543,21 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G115" t="n">
-        <v>11817</v>
+        <v>11815</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
@@ -12576,12 +12569,12 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Alteração dados cadastrais</t>
+          <t>Cálculo de férias individuais</t>
         </is>
       </c>
       <c r="K115" t="inlineStr"/>
       <c r="L115" s="1" t="n">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="M115" t="inlineStr"/>
       <c r="N115" t="inlineStr">
@@ -12590,7 +12583,7 @@
         </is>
       </c>
       <c r="O115" t="n">
-        <v>18199226</v>
+        <v>18196299</v>
       </c>
       <c r="P115" t="inlineStr"/>
       <c r="Q115" t="inlineStr">
@@ -12599,14 +12592,14 @@
         </is>
       </c>
       <c r="R115" s="1" t="n">
-        <v>46205.599529375</v>
+        <v>46204.71542079861</v>
       </c>
       <c r="S115" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
+          <t>NOSSO NOVO SUPERMERCADO</t>
         </is>
       </c>
       <c r="U115" t="inlineStr">
@@ -12614,11 +12607,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V115" t="inlineStr">
-        <is>
-          <t>Aplicação de promoção. - Data Comentário: 02/07/2026 11:13</t>
-        </is>
-      </c>
+      <c r="V115" t="inlineStr"/>
       <c r="W115" t="inlineStr"/>
       <c r="X115" t="inlineStr"/>
       <c r="Y115" t="inlineStr"/>
@@ -12627,7 +12616,7 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Mikael Teixeira</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr"/>
@@ -12697,7 +12686,7 @@
         </is>
       </c>
       <c r="O116" t="n">
-        <v>18196299</v>
+        <v>18196300</v>
       </c>
       <c r="P116" t="inlineStr"/>
       <c r="Q116" t="inlineStr">
@@ -12706,7 +12695,7 @@
         </is>
       </c>
       <c r="R116" s="1" t="n">
-        <v>46204.71542079861</v>
+        <v>46204.71542134259</v>
       </c>
       <c r="S116" t="n">
         <v>7</v>
@@ -12746,11 +12735,11 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>5417</v>
+        <v>6779</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>CORDEIRO E CIA LTDA</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -12760,7 +12749,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -12770,7 +12759,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -12800,7 +12789,7 @@
         </is>
       </c>
       <c r="O117" t="n">
-        <v>18196300</v>
+        <v>18195927</v>
       </c>
       <c r="P117" t="inlineStr"/>
       <c r="Q117" t="inlineStr">
@@ -12809,22 +12798,22 @@
         </is>
       </c>
       <c r="R117" s="1" t="n">
-        <v>46204.71542134259</v>
+        <v>46204.48446469908</v>
       </c>
       <c r="S117" t="n">
         <v>7</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
-        </is>
-      </c>
-      <c r="U117" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="V117" t="inlineStr"/>
+          <t>TECNO COM</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr"/>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Férias de 02/07/2026 a 10/07/2026. - Data Comentário: 01/07/2026 11:26</t>
+        </is>
+      </c>
       <c r="W117" t="inlineStr"/>
       <c r="X117" t="inlineStr"/>
       <c r="Y117" t="inlineStr"/>
@@ -12833,7 +12822,7 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>Mikael Teixeira</t>
+          <t>Kaique Souza</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr"/>
@@ -12849,11 +12838,11 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>6779</v>
+        <v>5417</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>CORDEIRO E CIA LTDA</t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -12863,7 +12852,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -12873,14 +12862,14 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G118" t="n">
-        <v>11815</v>
+        <v>5800</v>
       </c>
       <c r="H118" t="n">
-        <v>0</v>
+        <v>5776</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
@@ -12889,43 +12878,55 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Cálculo de férias individuais</t>
+          <t>CCT Lançamento Sd.508</t>
         </is>
       </c>
       <c r="K118" t="inlineStr"/>
       <c r="L118" s="1" t="n">
-        <v>46204</v>
-      </c>
-      <c r="M118" t="inlineStr"/>
+        <v>46205</v>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
+        </is>
+      </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>00/2026</t>
         </is>
       </c>
       <c r="O118" t="n">
-        <v>18195927</v>
-      </c>
-      <c r="P118" t="inlineStr"/>
+        <v>17399013</v>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Mikael Teixeira</t>
+        </is>
+      </c>
       <c r="Q118" t="inlineStr">
         <is>
           <t>Baixado</t>
         </is>
       </c>
       <c r="R118" s="1" t="n">
-        <v>46204.48446469908</v>
+        <v>46205.75412240741</v>
       </c>
       <c r="S118" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
-        </is>
-      </c>
-      <c r="U118" t="inlineStr"/>
+          <t>NOSSO NOVO SUPERMERCADO</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V118" t="inlineStr">
         <is>
-          <t>Férias de 02/07/2026 a 10/07/2026. - Data Comentário: 01/07/2026 11:26</t>
+          <t>2. Folha Processada aguardando OK do cliente para finalização   Previsão para conclusão dia 02/07/2026 - Data Comentário: 30/06/2026 15:03</t>
         </is>
       </c>
       <c r="W118" t="inlineStr"/>
@@ -12936,7 +12937,7 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>Kaique Souza</t>
+          <t>Mikael Teixeira</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr"/>
@@ -12952,11 +12953,11 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>5417</v>
+        <v>6224</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -12976,14 +12977,14 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G119" t="n">
-        <v>5800</v>
+        <v>5859</v>
       </c>
       <c r="H119" t="n">
-        <v>5776</v>
+        <v>5786</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
@@ -12992,29 +12993,25 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>CCT Lançamento Sd.508</t>
+          <t>Contribuição Assistencial</t>
         </is>
       </c>
       <c r="K119" t="inlineStr"/>
       <c r="L119" s="1" t="n">
-        <v>46205</v>
-      </c>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>02/07/2026</t>
-        </is>
-      </c>
+        <v>46206</v>
+      </c>
+      <c r="M119" t="inlineStr"/>
       <c r="N119" t="inlineStr">
         <is>
-          <t>00/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
       <c r="O119" t="n">
-        <v>17399013</v>
+        <v>17688763</v>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Mikael Teixeira</t>
+          <t>Tania Luz</t>
         </is>
       </c>
       <c r="Q119" t="inlineStr">
@@ -13023,14 +13020,14 @@
         </is>
       </c>
       <c r="R119" s="1" t="n">
-        <v>46205.75412240741</v>
+        <v>46205.75458568287</v>
       </c>
       <c r="S119" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U119" t="inlineStr">
@@ -13038,11 +13035,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V119" t="inlineStr">
-        <is>
-          <t>2. Folha Processada aguardando OK do cliente para finalização   Previsão para conclusão dia 02/07/2026 - Data Comentário: 30/06/2026 15:03</t>
-        </is>
-      </c>
+      <c r="V119" t="inlineStr"/>
       <c r="W119" t="inlineStr"/>
       <c r="X119" t="inlineStr"/>
       <c r="Y119" t="inlineStr"/>
@@ -13051,7 +13044,7 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>Mikael Teixeira</t>
+          <t>Tania Luz</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr"/>
@@ -13060,18 +13053,22 @@
       <c r="AE119" t="inlineStr"/>
       <c r="AF119" t="inlineStr">
         <is>
-          <t>Tarefa</t>
-        </is>
-      </c>
-      <c r="AG119" t="inlineStr"/>
+          <t>Imposto</t>
+        </is>
+      </c>
+      <c r="AG119" t="inlineStr">
+        <is>
+          <t>Edivaldo Veiga</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>6224</v>
+        <v>6628</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -13081,17 +13078,17 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -13121,11 +13118,11 @@
         </is>
       </c>
       <c r="O120" t="n">
-        <v>17688763</v>
+        <v>18052438</v>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Tania Luz</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="Q120" t="inlineStr">
@@ -13134,14 +13131,14 @@
         </is>
       </c>
       <c r="R120" s="1" t="n">
-        <v>46205.75458568287</v>
+        <v>46206.44903752315</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t xml:space="preserve">GTG </t>
         </is>
       </c>
       <c r="U120" t="inlineStr">
@@ -13158,7 +13155,7 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>Tania Luz</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr"/>
@@ -13172,17 +13169,17 @@
       </c>
       <c r="AG120" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>David Bragança</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>6628</v>
+        <v>6779</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>CORDEIRO E CIA LTDA</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -13197,7 +13194,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -13232,34 +13229,26 @@
         </is>
       </c>
       <c r="O121" t="n">
-        <v>18052438</v>
-      </c>
-      <c r="P121" t="inlineStr">
-        <is>
-          <t>Jakeline Silva</t>
-        </is>
-      </c>
+        <v>18090166</v>
+      </c>
+      <c r="P121" t="inlineStr"/>
       <c r="Q121" t="inlineStr">
         <is>
           <t>Baixado</t>
         </is>
       </c>
       <c r="R121" s="1" t="n">
-        <v>46206.44903752315</v>
+        <v>46199.48727971065</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
-        </is>
-      </c>
-      <c r="U121" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>TECNO COM</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr"/>
       <c r="V121" t="inlineStr"/>
       <c r="W121" t="inlineStr"/>
       <c r="X121" t="inlineStr"/>
@@ -13269,7 +13258,7 @@
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Kaique Souza</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr"/>
@@ -13281,19 +13270,15 @@
           <t>Imposto</t>
         </is>
       </c>
-      <c r="AG121" t="inlineStr">
-        <is>
-          <t>David Bragança</t>
-        </is>
-      </c>
+      <c r="AG121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>6779</v>
+        <v>6885</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>CORDEIRO E CIA LTDA</t>
+          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -13343,23 +13328,27 @@
         </is>
       </c>
       <c r="O122" t="n">
-        <v>18090166</v>
-      </c>
-      <c r="P122" t="inlineStr"/>
+        <v>18157259</v>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Vitor Guedes</t>
+        </is>
+      </c>
       <c r="Q122" t="inlineStr">
         <is>
           <t>Baixado</t>
         </is>
       </c>
       <c r="R122" s="1" t="n">
-        <v>46199.48727971065</v>
+        <v>46205.69236453703</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U122" t="inlineStr"/>
@@ -13372,7 +13361,7 @@
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>Kaique Souza</t>
+          <t>Vitor Guedes</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr"/>
@@ -13384,15 +13373,19 @@
           <t>Imposto</t>
         </is>
       </c>
-      <c r="AG122" t="inlineStr"/>
+      <c r="AG122" t="inlineStr">
+        <is>
+          <t>David Bragança</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>6885</v>
+        <v>6945</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
+          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -13407,7 +13400,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -13435,18 +13428,22 @@
       <c r="L123" s="1" t="n">
         <v>46206</v>
       </c>
-      <c r="M123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
       <c r="N123" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O123" t="n">
-        <v>18157259</v>
+        <v>18179094</v>
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Vitor Guedes</t>
+          <t>Santos Karina</t>
         </is>
       </c>
       <c r="Q123" t="inlineStr">
@@ -13455,18 +13452,23 @@
         </is>
       </c>
       <c r="R123" s="1" t="n">
-        <v>46205.69236453703</v>
+        <v>46209.43008613426</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>BRASIL DISTRIBUIDORA</t>
         </is>
       </c>
       <c r="U123" t="inlineStr"/>
-      <c r="V123" t="inlineStr"/>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 07/07/2026 
+cliente em implantação, em andamento - Data Comentário: 03/07/2026 17:19</t>
+        </is>
+      </c>
       <c r="W123" t="inlineStr"/>
       <c r="X123" t="inlineStr"/>
       <c r="Y123" t="inlineStr"/>
@@ -13475,7 +13477,7 @@
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>Vitor Guedes</t>
+          <t>Santos Karina</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr"/>
@@ -13489,17 +13491,17 @@
       </c>
       <c r="AG123" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Leandro Matos</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>6945</v>
+        <v>6486</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
+          <t>PC GAMER GOIANIA LTDA</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -13509,12 +13511,12 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -13523,10 +13525,10 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>5859</v>
+        <v>11542</v>
       </c>
       <c r="H124" t="n">
-        <v>5786</v>
+        <v>0</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
@@ -13535,29 +13537,25 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>Contribuição Assistencial</t>
+          <t>Envio Arq. eConsignado Cliente</t>
         </is>
       </c>
       <c r="K124" t="inlineStr"/>
       <c r="L124" s="1" t="n">
-        <v>46206</v>
-      </c>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>07/07/2026</t>
-        </is>
-      </c>
+        <v>46204</v>
+      </c>
+      <c r="M124" t="inlineStr"/>
       <c r="N124" t="inlineStr">
         <is>
-          <t>06/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
       <c r="O124" t="n">
-        <v>18179094</v>
+        <v>16976370</v>
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Santos Karina</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="Q124" t="inlineStr">
@@ -13566,23 +13564,22 @@
         </is>
       </c>
       <c r="R124" s="1" t="n">
-        <v>46209.43008613426</v>
+        <v>46204.5600265625</v>
       </c>
       <c r="S124" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA</t>
-        </is>
-      </c>
-      <c r="U124" t="inlineStr"/>
-      <c r="V124" t="inlineStr">
-        <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 07/07/2026 
-cliente em implantação, em andamento - Data Comentário: 03/07/2026 17:19</t>
-        </is>
-      </c>
+          <t>PC GAMER</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr"/>
       <c r="W124" t="inlineStr"/>
       <c r="X124" t="inlineStr"/>
       <c r="Y124" t="inlineStr"/>
@@ -13591,7 +13588,7 @@
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>Santos Karina</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr"/>
@@ -13600,22 +13597,22 @@
       <c r="AE124" t="inlineStr"/>
       <c r="AF124" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Obrigação Acessória</t>
         </is>
       </c>
       <c r="AG124" t="inlineStr">
         <is>
-          <t>Leandro Matos</t>
+          <t>David Bragança</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>6486</v>
+        <v>6548</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>PC GAMER GOIANIA LTDA</t>
+          <t>GOIAS SILAGEM LTDA</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -13665,11 +13662,11 @@
         </is>
       </c>
       <c r="O125" t="n">
-        <v>16976370</v>
+        <v>17222966</v>
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Daniel Moraes</t>
         </is>
       </c>
       <c r="Q125" t="inlineStr">
@@ -13678,14 +13675,14 @@
         </is>
       </c>
       <c r="R125" s="1" t="n">
-        <v>46204.5600265625</v>
+        <v>46196.71390480324</v>
       </c>
       <c r="S125" t="n">
         <v>7</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
-          <t>PC GAMER</t>
+          <t>GOIAS SILAGEM</t>
         </is>
       </c>
       <c r="U125" t="inlineStr">
@@ -13702,7 +13699,7 @@
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Evellin Bispo</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr"/>
@@ -13722,11 +13719,11 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>6548</v>
+        <v>6703</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM LTDA</t>
+          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -13736,7 +13733,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -13776,11 +13773,11 @@
         </is>
       </c>
       <c r="O126" t="n">
-        <v>17222966</v>
+        <v>18077183</v>
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Daniel Moraes</t>
+          <t>Ana Marcelino</t>
         </is>
       </c>
       <c r="Q126" t="inlineStr">
@@ -13789,14 +13786,14 @@
         </is>
       </c>
       <c r="R126" s="1" t="n">
-        <v>46196.71390480324</v>
+        <v>46198.70825575232</v>
       </c>
       <c r="S126" t="n">
         <v>7</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM</t>
+          <t>LIMA MOTA</t>
         </is>
       </c>
       <c r="U126" t="inlineStr">
@@ -13813,7 +13810,7 @@
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>Evellin Bispo</t>
+          <t>Elaine Assis</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr"/>
@@ -13827,17 +13824,17 @@
       </c>
       <c r="AG126" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>6703</v>
+        <v>6779</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
+          <t>CORDEIRO E CIA LTDA</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -13847,7 +13844,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -13887,11 +13884,11 @@
         </is>
       </c>
       <c r="O127" t="n">
-        <v>18077183</v>
+        <v>18090270</v>
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Ana Marcelino</t>
+          <t>Kaique Souza</t>
         </is>
       </c>
       <c r="Q127" t="inlineStr">
@@ -13900,21 +13897,17 @@
         </is>
       </c>
       <c r="R127" s="1" t="n">
-        <v>46198.70825575232</v>
+        <v>46196.59280127315</v>
       </c>
       <c r="S127" t="n">
         <v>7</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
-          <t>LIMA MOTA</t>
-        </is>
-      </c>
-      <c r="U127" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>TECNO COM</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr"/>
       <c r="V127" t="inlineStr"/>
       <c r="W127" t="inlineStr"/>
       <c r="X127" t="inlineStr"/>
@@ -13924,7 +13917,7 @@
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>Elaine Assis</t>
+          <t>Kaique Souza</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr"/>
@@ -13944,11 +13937,11 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>6779</v>
+        <v>6949</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>CORDEIRO E CIA LTDA</t>
+          <t>TEC GRUA LOCAÇÃO E COMERCIO DE EQUIPAMENTOS PARA CONSTRUÇÃO LTDA</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -13958,7 +13951,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -13968,7 +13961,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Reynaldo Santos</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -13998,11 +13991,11 @@
         </is>
       </c>
       <c r="O128" t="n">
-        <v>18090270</v>
+        <v>18190469</v>
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Kaique Souza</t>
+          <t>Gabriela Peres</t>
         </is>
       </c>
       <c r="Q128" t="inlineStr">
@@ -14011,14 +14004,14 @@
         </is>
       </c>
       <c r="R128" s="1" t="n">
-        <v>46196.59280127315</v>
+        <v>46204.41370118056</v>
       </c>
       <c r="S128" t="n">
         <v>7</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>TEC GRUA</t>
         </is>
       </c>
       <c r="U128" t="inlineStr"/>
@@ -14031,7 +14024,7 @@
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>Kaique Souza</t>
+          <t>Santos Karina</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr"/>
@@ -14045,17 +14038,17 @@
       </c>
       <c r="AG128" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>Leandro Matos</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>6949</v>
+        <v>6404</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>TEC GRUA LOCAÇÃO E COMERCIO DE EQUIPAMENTOS PARA CONSTRUÇÃO LTDA</t>
+          <t>SOLAR INVESTIMENTOS LTDA</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -14065,7 +14058,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -14075,11 +14068,11 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G129" t="n">
-        <v>11542</v>
+        <v>9746</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -14091,25 +14084,29 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>Envio Arq. eConsignado Cliente</t>
+          <t>eSocial – Fechamento Mensal</t>
         </is>
       </c>
       <c r="K129" t="inlineStr"/>
       <c r="L129" s="1" t="n">
-        <v>46204</v>
-      </c>
-      <c r="M129" t="inlineStr"/>
+        <v>46213</v>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
       <c r="O129" t="n">
-        <v>18190469</v>
+        <v>16962422</v>
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Gabriela Peres</t>
+          <t>Jhenifer Tenorio</t>
         </is>
       </c>
       <c r="Q129" t="inlineStr">
@@ -14118,18 +14115,26 @@
         </is>
       </c>
       <c r="R129" s="1" t="n">
-        <v>46204.41370118056</v>
+        <v>46209.71247704861</v>
       </c>
       <c r="S129" t="n">
-        <v>7</v>
+        <v>-2</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
-          <t>TEC GRUA</t>
-        </is>
-      </c>
-      <c r="U129" t="inlineStr"/>
-      <c r="V129" t="inlineStr"/>
+          <t>SOLAR INVESTIMENTOS</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 08/07/2026 - Data Comentário: 06/07/2026 12:40</t>
+        </is>
+      </c>
       <c r="W129" t="inlineStr"/>
       <c r="X129" t="inlineStr"/>
       <c r="Y129" t="inlineStr"/>
@@ -14138,7 +14143,7 @@
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>Santos Karina</t>
+          <t>Jhenifer Tenorio</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr"/>
@@ -14147,22 +14152,22 @@
       <c r="AE129" t="inlineStr"/>
       <c r="AF129" t="inlineStr">
         <is>
-          <t>Obrigação Acessória</t>
+          <t>Tarefa</t>
         </is>
       </c>
       <c r="AG129" t="inlineStr">
         <is>
-          <t>Leandro Matos</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>6404</v>
+        <v>6486</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS LTDA</t>
+          <t>PC GAMER GOIANIA LTDA</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -14172,7 +14177,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -14216,11 +14221,11 @@
         </is>
       </c>
       <c r="O130" t="n">
-        <v>16962422</v>
+        <v>16976298</v>
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Jhenifer Tenorio</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="Q130" t="inlineStr">
@@ -14229,14 +14234,14 @@
         </is>
       </c>
       <c r="R130" s="1" t="n">
-        <v>46209.71247704861</v>
+        <v>46209.71499087963</v>
       </c>
       <c r="S130" t="n">
         <v>-2</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS</t>
+          <t>PC GAMER</t>
         </is>
       </c>
       <c r="U130" t="inlineStr">
@@ -14246,7 +14251,8 @@
       </c>
       <c r="V130" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 08/07/2026 - Data Comentário: 06/07/2026 12:40</t>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 08/07/2026 
+PREVISÃO DE FINALIZAÇÃO: 08/07/2026 - Data Comentário: 06/07/2026 10:43</t>
         </is>
       </c>
       <c r="W130" t="inlineStr"/>
@@ -14257,7 +14263,7 @@
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>Jhenifer Tenorio</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr"/>
@@ -14271,17 +14277,17 @@
       </c>
       <c r="AG130" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>David Bragança</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>6486</v>
+        <v>6548</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PC GAMER GOIANIA LTDA</t>
+          <t>GOIAS SILAGEM LTDA</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -14335,11 +14341,11 @@
         </is>
       </c>
       <c r="O131" t="n">
-        <v>16976298</v>
+        <v>17222913</v>
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Daniel Moraes</t>
         </is>
       </c>
       <c r="Q131" t="inlineStr">
@@ -14348,14 +14354,14 @@
         </is>
       </c>
       <c r="R131" s="1" t="n">
-        <v>46209.71499087963</v>
+        <v>46211.48251296296</v>
       </c>
       <c r="S131" t="n">
         <v>-2</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
-          <t>PC GAMER</t>
+          <t>GOIAS SILAGEM</t>
         </is>
       </c>
       <c r="U131" t="inlineStr">
@@ -14366,7 +14372,7 @@
       <c r="V131" t="inlineStr">
         <is>
           <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 08/07/2026 
-PREVISÃO DE FINALIZAÇÃO: 08/07/2026 - Data Comentário: 06/07/2026 10:43</t>
+Previsão de conclusão em 08/07/2026. - Data Comentário: 07/07/2026 16:47</t>
         </is>
       </c>
       <c r="W131" t="inlineStr"/>
@@ -14377,7 +14383,7 @@
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Daniel Moraes</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr"/>

--- a/dados/base/goias.xlsx
+++ b/dados/base/goias.xlsx
@@ -3954,7 +3954,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3987,8 +3987,8 @@
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 10/07/2026 
-ESocial fechado, antecipação de envio. - Data Comentário: 08/07/2026 14:21</t>
+          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 14/07/2026 
+ESocial fechado, antecipação de envio. - Data Comentário: 10/07/2026 09:19</t>
         </is>
       </c>
       <c r="W33" t="inlineStr"/>
@@ -7281,10 +7281,10 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>1793</v>
+        <v>6294</v>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>1788</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -7293,25 +7293,21 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Mun - ISS Serv. Tomados</t>
+          <t>Recebimento NFCE</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
       <c r="L65" s="1" t="n">
-        <v>46213</v>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>08/07/2026</t>
-        </is>
-      </c>
+        <v>46216</v>
+      </c>
+      <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O65" t="n">
-        <v>17948926</v>
+        <v>17948997</v>
       </c>
       <c r="P65" t="inlineStr">
         <is>
@@ -7325,7 +7321,7 @@
       </c>
       <c r="R65" t="inlineStr"/>
       <c r="S65" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7337,11 +7333,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V65" t="inlineStr">
-        <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 08/07/2026 - Data Comentário: 06/07/2026 15:51</t>
-        </is>
-      </c>
+      <c r="V65" t="inlineStr"/>
       <c r="W65" t="inlineStr"/>
       <c r="X65" t="inlineStr"/>
       <c r="Y65" t="inlineStr"/>
@@ -7355,7 +7347,7 @@
       <c r="AE65" t="inlineStr"/>
       <c r="AF65" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Tarefa</t>
         </is>
       </c>
       <c r="AG65" t="inlineStr">
@@ -7366,11 +7358,11 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>6779</v>
+        <v>5617</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CORDEIRO E CIA LTDA</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -7380,7 +7372,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -7394,7 +7386,7 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>1793</v>
+        <v>11303</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -7406,25 +7398,21 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Mun - ISS Serv. Tomados</t>
+          <t>Retorno do Check-List Fiscal</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
       <c r="L66" s="1" t="n">
-        <v>46213</v>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>08/07/2026</t>
-        </is>
-      </c>
+        <v>46218</v>
+      </c>
+      <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O66" t="n">
-        <v>18084953</v>
+        <v>17407963</v>
       </c>
       <c r="P66" t="inlineStr">
         <is>
@@ -7438,19 +7426,19 @@
       </c>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
-        </is>
-      </c>
-      <c r="U66" t="inlineStr"/>
-      <c r="V66" t="inlineStr">
-        <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 08/07/2026 - Data Comentário: 06/07/2026 15:51</t>
-        </is>
-      </c>
+          <t>SUPER MAIS DO GOIÁS</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr"/>
       <c r="W66" t="inlineStr"/>
       <c r="X66" t="inlineStr"/>
       <c r="Y66" t="inlineStr"/>
@@ -7464,7 +7452,7 @@
       <c r="AE66" t="inlineStr"/>
       <c r="AF66" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Tarefa</t>
         </is>
       </c>
       <c r="AG66" t="inlineStr">
@@ -7475,11 +7463,11 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>6885</v>
+        <v>6962</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
+          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -7489,7 +7477,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -7499,45 +7487,41 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Reynaldo Santos</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>1793</v>
+        <v>950</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Mun - ISS Serv. Tomados</t>
+          <t>Confirm Rec - ISS Prestados</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
       <c r="L67" s="1" t="n">
         <v>46213</v>
       </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>08/07/2026</t>
-        </is>
-      </c>
+      <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O67" t="n">
-        <v>18134033</v>
+        <v>18188715</v>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Cristina Leite</t>
+          <t>Victoria Virgens</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
@@ -7551,13 +7535,13 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>PROMOTORAS GYN</t>
         </is>
       </c>
       <c r="U67" t="inlineStr"/>
       <c r="V67" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 08/07/2026 - Data Comentário: 06/07/2026 15:51</t>
+          <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1866] sendo a ultima baixa feita [1866]-08/07/2026 18:25:05.. - Data Comentário: 08/07/2026 18:24</t>
         </is>
       </c>
       <c r="W67" t="inlineStr"/>
@@ -7576,19 +7560,15 @@
           <t>Imposto</t>
         </is>
       </c>
-      <c r="AG67" t="inlineStr">
-        <is>
-          <t>Ricardo Fischer</t>
-        </is>
-      </c>
+      <c r="AG67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>6705</v>
+        <v>6963</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>NARCIZO ALVES CORDEIRO</t>
+          <t>PROMOTORAS GYN LTDA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -7598,7 +7578,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -7608,28 +7588,28 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Reynaldo Santos</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>6294</v>
+        <v>950</v>
       </c>
       <c r="H68" t="n">
-        <v>1788</v>
+        <v>0</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Recebimento NFCE</t>
+          <t>Confirm Rec - ISS Prestados</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
       <c r="L68" s="1" t="n">
-        <v>46216</v>
+        <v>46213</v>
       </c>
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
@@ -7638,11 +7618,11 @@
         </is>
       </c>
       <c r="O68" t="n">
-        <v>17948997</v>
+        <v>18188621</v>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Cristina Leite</t>
+          <t>Victoria Virgens</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
@@ -7652,19 +7632,19 @@
       </c>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
-        </is>
-      </c>
-      <c r="U68" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="V68" t="inlineStr"/>
+          <t>PROMOTORAS GYN</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr"/>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1866] sendo a ultima baixa feita [1866]-08/07/2026 18:24:46.. - Data Comentário: 08/07/2026 18:24</t>
+        </is>
+      </c>
       <c r="W68" t="inlineStr"/>
       <c r="X68" t="inlineStr"/>
       <c r="Y68" t="inlineStr"/>
@@ -7678,22 +7658,18 @@
       <c r="AE68" t="inlineStr"/>
       <c r="AF68" t="inlineStr">
         <is>
-          <t>Tarefa</t>
-        </is>
-      </c>
-      <c r="AG68" t="inlineStr">
-        <is>
-          <t>Ricardo Fischer</t>
-        </is>
-      </c>
+          <t>Imposto</t>
+        </is>
+      </c>
+      <c r="AG68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>5617</v>
+        <v>6705</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>NARCIZO ALVES CORDEIRO</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -7703,7 +7679,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -7717,24 +7693,24 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>11303</v>
+        <v>951</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Retorno do Check-List Fiscal</t>
+          <t>Confirm Rec - ISS Tomados</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" s="1" t="n">
-        <v>46218</v>
+        <v>46213</v>
       </c>
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
@@ -7743,11 +7719,11 @@
         </is>
       </c>
       <c r="O69" t="n">
-        <v>17407963</v>
+        <v>17952533</v>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Cristina Leite</t>
+          <t>Victoria Virgens</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
@@ -7757,11 +7733,11 @@
       </c>
       <c r="R69" t="inlineStr"/>
       <c r="S69" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>TECNO COM</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -7769,7 +7745,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V69" t="inlineStr"/>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1793] sendo a ultima baixa feita [1793]-10/07/2026 09:57:11.. - Data Comentário: 10/07/2026 09:56</t>
+        </is>
+      </c>
       <c r="W69" t="inlineStr"/>
       <c r="X69" t="inlineStr"/>
       <c r="Y69" t="inlineStr"/>
@@ -7783,22 +7763,18 @@
       <c r="AE69" t="inlineStr"/>
       <c r="AF69" t="inlineStr">
         <is>
-          <t>Tarefa</t>
-        </is>
-      </c>
-      <c r="AG69" t="inlineStr">
-        <is>
-          <t>Ricardo Fischer</t>
-        </is>
-      </c>
+          <t>Imposto</t>
+        </is>
+      </c>
+      <c r="AG69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>6962</v>
+        <v>6779</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
+          <t>CORDEIRO E CIA LTDA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -7808,7 +7784,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -7818,11 +7794,11 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -7834,7 +7810,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Confirm Rec - ISS Prestados</t>
+          <t>Confirm Rec - ISS Tomados</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -7848,7 +7824,7 @@
         </is>
       </c>
       <c r="O70" t="n">
-        <v>18188715</v>
+        <v>18056703</v>
       </c>
       <c r="P70" t="inlineStr">
         <is>
@@ -7866,13 +7842,13 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN</t>
+          <t>TECNO COM</t>
         </is>
       </c>
       <c r="U70" t="inlineStr"/>
       <c r="V70" t="inlineStr">
         <is>
-          <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1866] sendo a ultima baixa feita [1866]-08/07/2026 18:25:05.. - Data Comentário: 08/07/2026 18:24</t>
+          <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1793] sendo a ultima baixa feita [1793]-10/07/2026 09:57:11.. - Data Comentário: 10/07/2026 09:56</t>
         </is>
       </c>
       <c r="W70" t="inlineStr"/>
@@ -7895,11 +7871,11 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>6963</v>
+        <v>6885</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN LTDA</t>
+          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -7909,7 +7885,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -7919,11 +7895,11 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -7935,7 +7911,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Confirm Rec - ISS Prestados</t>
+          <t>Confirm Rec - ISS Tomados</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -7949,7 +7925,7 @@
         </is>
       </c>
       <c r="O71" t="n">
-        <v>18188621</v>
+        <v>18128657</v>
       </c>
       <c r="P71" t="inlineStr">
         <is>
@@ -7967,13 +7943,13 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U71" t="inlineStr"/>
       <c r="V71" t="inlineStr">
         <is>
-          <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1866] sendo a ultima baixa feita [1866]-08/07/2026 18:24:46.. - Data Comentário: 08/07/2026 18:24</t>
+          <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1793] sendo a ultima baixa feita [1793]-10/07/2026 09:57:12.. - Data Comentário: 10/07/2026 09:56</t>
         </is>
       </c>
       <c r="W71" t="inlineStr"/>
@@ -31687,11 +31663,11 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>6703</v>
+        <v>6705</v>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
+          <t>NARCIZO ALVES CORDEIRO</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -31701,7 +31677,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -31715,7 +31691,7 @@
         </is>
       </c>
       <c r="G287" t="n">
-        <v>1796</v>
+        <v>1793</v>
       </c>
       <c r="H287" t="n">
         <v>0</v>
@@ -31727,12 +31703,12 @@
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>Produtor Rural</t>
+          <t>Mun - ISS Serv. Tomados</t>
         </is>
       </c>
       <c r="K287" t="inlineStr"/>
       <c r="L287" s="1" t="n">
-        <v>46211</v>
+        <v>46213</v>
       </c>
       <c r="M287" t="inlineStr">
         <is>
@@ -31745,7 +31721,7 @@
         </is>
       </c>
       <c r="O287" t="n">
-        <v>18073096</v>
+        <v>17948926</v>
       </c>
       <c r="P287" t="inlineStr">
         <is>
@@ -31758,14 +31734,14 @@
         </is>
       </c>
       <c r="R287" s="1" t="n">
-        <v>46211.67827373843</v>
+        <v>46213.41471872685</v>
       </c>
       <c r="S287" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T287" t="inlineStr">
         <is>
-          <t>LIMA MOTA</t>
+          <t>TECNO COM</t>
         </is>
       </c>
       <c r="U287" t="inlineStr">
@@ -31775,7 +31751,7 @@
       </c>
       <c r="V287" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 08/07/2026 - Data Comentário: 06/07/2026 14:49</t>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 08/07/2026 - Data Comentário: 06/07/2026 15:51</t>
         </is>
       </c>
       <c r="W287" t="inlineStr"/>
@@ -31795,7 +31771,7 @@
       <c r="AE287" t="inlineStr"/>
       <c r="AF287" t="inlineStr">
         <is>
-          <t>Tarefa</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="AG287" t="inlineStr">
@@ -31806,11 +31782,11 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>6486</v>
+        <v>6779</v>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>PC GAMER GOIANIA LTDA</t>
+          <t>CORDEIRO E CIA LTDA</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -31820,7 +31796,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -31834,7 +31810,7 @@
         </is>
       </c>
       <c r="G288" t="n">
-        <v>11359</v>
+        <v>1793</v>
       </c>
       <c r="H288" t="n">
         <v>0</v>
@@ -31846,21 +31822,25 @@
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t xml:space="preserve">Recebimento - Sped ICMS </t>
+          <t>Mun - ISS Serv. Tomados</t>
         </is>
       </c>
       <c r="K288" t="inlineStr"/>
       <c r="L288" s="1" t="n">
-        <v>46205</v>
-      </c>
-      <c r="M288" t="inlineStr"/>
+        <v>46213</v>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
       <c r="N288" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O288" t="n">
-        <v>18155343</v>
+        <v>18084953</v>
       </c>
       <c r="P288" t="inlineStr">
         <is>
@@ -31873,22 +31853,22 @@
         </is>
       </c>
       <c r="R288" s="1" t="n">
-        <v>46205.45901570602</v>
+        <v>46213.41472034722</v>
       </c>
       <c r="S288" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="T288" t="inlineStr">
         <is>
-          <t>PC GAMER</t>
-        </is>
-      </c>
-      <c r="U288" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="V288" t="inlineStr"/>
+          <t>TECNO COM</t>
+        </is>
+      </c>
+      <c r="U288" t="inlineStr"/>
+      <c r="V288" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 08/07/2026 - Data Comentário: 06/07/2026 15:51</t>
+        </is>
+      </c>
       <c r="W288" t="inlineStr"/>
       <c r="X288" t="inlineStr"/>
       <c r="Y288" t="inlineStr"/>
@@ -31906,7 +31886,7 @@
       <c r="AE288" t="inlineStr"/>
       <c r="AF288" t="inlineStr">
         <is>
-          <t>Tarefa</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="AG288" t="inlineStr">
@@ -31917,11 +31897,11 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>6279</v>
+        <v>6885</v>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>DIENNYFER DA S PEREIRA</t>
+          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -31931,7 +31911,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -31941,14 +31921,14 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G289" t="n">
-        <v>6884</v>
+        <v>1793</v>
       </c>
       <c r="H289" t="n">
-        <v>1788</v>
+        <v>0</v>
       </c>
       <c r="I289" t="inlineStr">
         <is>
@@ -31957,21 +31937,25 @@
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>Recebimento de NF Serviços Tomados</t>
+          <t>Mun - ISS Serv. Tomados</t>
         </is>
       </c>
       <c r="K289" t="inlineStr"/>
       <c r="L289" s="1" t="n">
-        <v>46211</v>
-      </c>
-      <c r="M289" t="inlineStr"/>
+        <v>46213</v>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
       <c r="N289" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O289" t="n">
-        <v>17071044</v>
+        <v>18134033</v>
       </c>
       <c r="P289" t="inlineStr">
         <is>
@@ -31984,22 +31968,22 @@
         </is>
       </c>
       <c r="R289" s="1" t="n">
-        <v>46206.79257369213</v>
+        <v>46213.41472866898</v>
       </c>
       <c r="S289" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T289" t="inlineStr">
         <is>
           <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
-      <c r="U289" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="V289" t="inlineStr"/>
+      <c r="U289" t="inlineStr"/>
+      <c r="V289" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 08/07/2026 - Data Comentário: 06/07/2026 15:51</t>
+        </is>
+      </c>
       <c r="W289" t="inlineStr"/>
       <c r="X289" t="inlineStr"/>
       <c r="Y289" t="inlineStr"/>
@@ -32008,7 +31992,7 @@
       </c>
       <c r="AA289" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Cristina Leite</t>
         </is>
       </c>
       <c r="AB289" t="inlineStr"/>
@@ -32017,7 +32001,7 @@
       <c r="AE289" t="inlineStr"/>
       <c r="AF289" t="inlineStr">
         <is>
-          <t>Tarefa</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="AG289" t="inlineStr">
@@ -32028,11 +32012,11 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>6486</v>
+        <v>6703</v>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>PC GAMER GOIANIA LTDA</t>
+          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -32042,7 +32026,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -32056,10 +32040,10 @@
         </is>
       </c>
       <c r="G290" t="n">
-        <v>6884</v>
+        <v>1796</v>
       </c>
       <c r="H290" t="n">
-        <v>1788</v>
+        <v>0</v>
       </c>
       <c r="I290" t="inlineStr">
         <is>
@@ -32068,21 +32052,25 @@
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>Recebimento de NF Serviços Tomados</t>
+          <t>Produtor Rural</t>
         </is>
       </c>
       <c r="K290" t="inlineStr"/>
       <c r="L290" s="1" t="n">
         <v>46211</v>
       </c>
-      <c r="M290" t="inlineStr"/>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
       <c r="N290" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O290" t="n">
-        <v>16976205</v>
+        <v>18073096</v>
       </c>
       <c r="P290" t="inlineStr">
         <is>
@@ -32095,14 +32083,14 @@
         </is>
       </c>
       <c r="R290" s="1" t="n">
-        <v>46205.45918969908</v>
+        <v>46211.67827373843</v>
       </c>
       <c r="S290" t="n">
         <v>2</v>
       </c>
       <c r="T290" t="inlineStr">
         <is>
-          <t>PC GAMER</t>
+          <t>LIMA MOTA</t>
         </is>
       </c>
       <c r="U290" t="inlineStr">
@@ -32110,7 +32098,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V290" t="inlineStr"/>
+      <c r="V290" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 08/07/2026 - Data Comentário: 06/07/2026 14:49</t>
+        </is>
+      </c>
       <c r="W290" t="inlineStr"/>
       <c r="X290" t="inlineStr"/>
       <c r="Y290" t="inlineStr"/>
@@ -32139,11 +32131,11 @@
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>6705</v>
+        <v>6486</v>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>NARCIZO ALVES CORDEIRO</t>
+          <t>PC GAMER GOIANIA LTDA</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -32153,7 +32145,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -32167,10 +32159,10 @@
         </is>
       </c>
       <c r="G291" t="n">
-        <v>6884</v>
+        <v>11359</v>
       </c>
       <c r="H291" t="n">
-        <v>1788</v>
+        <v>0</v>
       </c>
       <c r="I291" t="inlineStr">
         <is>
@@ -32179,25 +32171,21 @@
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>Recebimento de NF Serviços Tomados</t>
+          <t xml:space="preserve">Recebimento - Sped ICMS </t>
         </is>
       </c>
       <c r="K291" t="inlineStr"/>
       <c r="L291" s="1" t="n">
-        <v>46211</v>
-      </c>
-      <c r="M291" t="inlineStr">
-        <is>
-          <t>08/07/2026</t>
-        </is>
-      </c>
+        <v>46205</v>
+      </c>
+      <c r="M291" t="inlineStr"/>
       <c r="N291" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O291" t="n">
-        <v>17949037</v>
+        <v>18155343</v>
       </c>
       <c r="P291" t="inlineStr">
         <is>
@@ -32210,14 +32198,14 @@
         </is>
       </c>
       <c r="R291" s="1" t="n">
-        <v>46211.37590150463</v>
+        <v>46205.45901570602</v>
       </c>
       <c r="S291" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="T291" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>PC GAMER</t>
         </is>
       </c>
       <c r="U291" t="inlineStr">
@@ -32225,11 +32213,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V291" t="inlineStr">
-        <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 08/07/2026 - Data Comentário: 06/07/2026 15:52</t>
-        </is>
-      </c>
+      <c r="V291" t="inlineStr"/>
       <c r="W291" t="inlineStr"/>
       <c r="X291" t="inlineStr"/>
       <c r="Y291" t="inlineStr"/>
@@ -32258,11 +32242,11 @@
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>6885</v>
+        <v>6279</v>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
+          <t>DIENNYFER DA S PEREIRA</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -32272,7 +32256,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -32282,7 +32266,7 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -32312,7 +32296,7 @@
         </is>
       </c>
       <c r="O292" t="n">
-        <v>18134133</v>
+        <v>17071044</v>
       </c>
       <c r="P292" t="inlineStr">
         <is>
@@ -32325,7 +32309,7 @@
         </is>
       </c>
       <c r="R292" s="1" t="n">
-        <v>46206.79256712963</v>
+        <v>46206.79257369213</v>
       </c>
       <c r="S292" t="n">
         <v>2</v>
@@ -32335,7 +32319,11 @@
           <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
-      <c r="U292" t="inlineStr"/>
+      <c r="U292" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V292" t="inlineStr"/>
       <c r="W292" t="inlineStr"/>
       <c r="X292" t="inlineStr"/>
@@ -32365,11 +32353,11 @@
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>6279</v>
+        <v>6486</v>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>DIENNYFER DA S PEREIRA</t>
+          <t>PC GAMER GOIANIA LTDA</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -32379,7 +32367,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -32389,11 +32377,11 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G293" t="n">
-        <v>6294</v>
+        <v>6884</v>
       </c>
       <c r="H293" t="n">
         <v>1788</v>
@@ -32405,12 +32393,12 @@
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>Recebimento NFCE</t>
+          <t>Recebimento de NF Serviços Tomados</t>
         </is>
       </c>
       <c r="K293" t="inlineStr"/>
       <c r="L293" s="1" t="n">
-        <v>46216</v>
+        <v>46211</v>
       </c>
       <c r="M293" t="inlineStr"/>
       <c r="N293" t="inlineStr">
@@ -32419,7 +32407,7 @@
         </is>
       </c>
       <c r="O293" t="n">
-        <v>17070959</v>
+        <v>16976205</v>
       </c>
       <c r="P293" t="inlineStr">
         <is>
@@ -32432,14 +32420,14 @@
         </is>
       </c>
       <c r="R293" s="1" t="n">
-        <v>46206.7921721875</v>
+        <v>46205.45918969908</v>
       </c>
       <c r="S293" t="n">
-        <v>-3</v>
+        <v>2</v>
       </c>
       <c r="T293" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>PC GAMER</t>
         </is>
       </c>
       <c r="U293" t="inlineStr">
@@ -32456,7 +32444,7 @@
       </c>
       <c r="AA293" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Cristina Leite</t>
         </is>
       </c>
       <c r="AB293" t="inlineStr"/>
@@ -32476,11 +32464,11 @@
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>6885</v>
+        <v>6705</v>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
+          <t>NARCIZO ALVES CORDEIRO</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -32504,7 +32492,7 @@
         </is>
       </c>
       <c r="G294" t="n">
-        <v>6294</v>
+        <v>6884</v>
       </c>
       <c r="H294" t="n">
         <v>1788</v>
@@ -32516,21 +32504,25 @@
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>Recebimento NFCE</t>
+          <t>Recebimento de NF Serviços Tomados</t>
         </is>
       </c>
       <c r="K294" t="inlineStr"/>
       <c r="L294" s="1" t="n">
-        <v>46216</v>
-      </c>
-      <c r="M294" t="inlineStr"/>
+        <v>46211</v>
+      </c>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
       <c r="N294" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O294" t="n">
-        <v>18134097</v>
+        <v>17949037</v>
       </c>
       <c r="P294" t="inlineStr">
         <is>
@@ -32543,18 +32535,26 @@
         </is>
       </c>
       <c r="R294" s="1" t="n">
-        <v>46206.7921681713</v>
+        <v>46211.37590150463</v>
       </c>
       <c r="S294" t="n">
-        <v>-3</v>
+        <v>2</v>
       </c>
       <c r="T294" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
-        </is>
-      </c>
-      <c r="U294" t="inlineStr"/>
-      <c r="V294" t="inlineStr"/>
+          <t>TECNO COM</t>
+        </is>
+      </c>
+      <c r="U294" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V294" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 08/07/2026 - Data Comentário: 06/07/2026 15:52</t>
+        </is>
+      </c>
       <c r="W294" t="inlineStr"/>
       <c r="X294" t="inlineStr"/>
       <c r="Y294" t="inlineStr"/>
@@ -32563,7 +32563,7 @@
       </c>
       <c r="AA294" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Cristina Leite</t>
         </is>
       </c>
       <c r="AB294" t="inlineStr"/>
@@ -32583,11 +32583,11 @@
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>5417</v>
+        <v>6885</v>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -32597,7 +32597,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -32607,14 +32607,14 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G295" t="n">
-        <v>11303</v>
+        <v>6884</v>
       </c>
       <c r="H295" t="n">
-        <v>0</v>
+        <v>1788</v>
       </c>
       <c r="I295" t="inlineStr">
         <is>
@@ -32623,12 +32623,12 @@
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>Retorno do Check-List Fiscal</t>
+          <t>Recebimento de NF Serviços Tomados</t>
         </is>
       </c>
       <c r="K295" t="inlineStr"/>
       <c r="L295" s="1" t="n">
-        <v>46218</v>
+        <v>46211</v>
       </c>
       <c r="M295" t="inlineStr"/>
       <c r="N295" t="inlineStr">
@@ -32637,7 +32637,7 @@
         </is>
       </c>
       <c r="O295" t="n">
-        <v>17399452</v>
+        <v>18134133</v>
       </c>
       <c r="P295" t="inlineStr">
         <is>
@@ -32650,26 +32650,18 @@
         </is>
       </c>
       <c r="R295" s="1" t="n">
-        <v>46210.37424872685</v>
+        <v>46206.79256712963</v>
       </c>
       <c r="S295" t="n">
-        <v>-5</v>
+        <v>2</v>
       </c>
       <c r="T295" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
-        </is>
-      </c>
-      <c r="U295" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="V295" t="inlineStr">
-        <is>
-          <t>Baixado via API integração MGC x Sistema de Analise Fiscal em 07/07/2026 08:56:44. - Data Comentário: 07/07/2026 08:55</t>
-        </is>
-      </c>
+          <t>EMPORIO DOS FRIOS</t>
+        </is>
+      </c>
+      <c r="U295" t="inlineStr"/>
+      <c r="V295" t="inlineStr"/>
       <c r="W295" t="inlineStr"/>
       <c r="X295" t="inlineStr"/>
       <c r="Y295" t="inlineStr"/>
@@ -32678,7 +32670,7 @@
       </c>
       <c r="AA295" t="inlineStr">
         <is>
-          <t>ex-funcionario</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="AB295" t="inlineStr"/>
@@ -32726,10 +32718,10 @@
         </is>
       </c>
       <c r="G296" t="n">
-        <v>11303</v>
+        <v>6294</v>
       </c>
       <c r="H296" t="n">
-        <v>0</v>
+        <v>1788</v>
       </c>
       <c r="I296" t="inlineStr">
         <is>
@@ -32738,12 +32730,12 @@
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>Retorno do Check-List Fiscal</t>
+          <t>Recebimento NFCE</t>
         </is>
       </c>
       <c r="K296" t="inlineStr"/>
       <c r="L296" s="1" t="n">
-        <v>46218</v>
+        <v>46216</v>
       </c>
       <c r="M296" t="inlineStr"/>
       <c r="N296" t="inlineStr">
@@ -32752,7 +32744,7 @@
         </is>
       </c>
       <c r="O296" t="n">
-        <v>17071101</v>
+        <v>17070959</v>
       </c>
       <c r="P296" t="inlineStr">
         <is>
@@ -32765,10 +32757,10 @@
         </is>
       </c>
       <c r="R296" s="1" t="n">
-        <v>46205.76232731481</v>
+        <v>46206.7921721875</v>
       </c>
       <c r="S296" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="T296" t="inlineStr">
         <is>
@@ -32789,7 +32781,7 @@
       </c>
       <c r="AA296" t="inlineStr">
         <is>
-          <t>Juan Rodrigues</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="AB296" t="inlineStr"/>
@@ -32809,11 +32801,11 @@
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>6486</v>
+        <v>6885</v>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>PC GAMER GOIANIA LTDA</t>
+          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -32823,7 +32815,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -32837,10 +32829,10 @@
         </is>
       </c>
       <c r="G297" t="n">
-        <v>11303</v>
+        <v>6294</v>
       </c>
       <c r="H297" t="n">
-        <v>0</v>
+        <v>1788</v>
       </c>
       <c r="I297" t="inlineStr">
         <is>
@@ -32849,12 +32841,12 @@
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>Retorno do Check-List Fiscal</t>
+          <t>Recebimento NFCE</t>
         </is>
       </c>
       <c r="K297" t="inlineStr"/>
       <c r="L297" s="1" t="n">
-        <v>46218</v>
+        <v>46216</v>
       </c>
       <c r="M297" t="inlineStr"/>
       <c r="N297" t="inlineStr">
@@ -32863,7 +32855,7 @@
         </is>
       </c>
       <c r="O297" t="n">
-        <v>16976349</v>
+        <v>18134097</v>
       </c>
       <c r="P297" t="inlineStr">
         <is>
@@ -32876,21 +32868,17 @@
         </is>
       </c>
       <c r="R297" s="1" t="n">
-        <v>46205.7623278588</v>
+        <v>46206.7921681713</v>
       </c>
       <c r="S297" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="T297" t="inlineStr">
         <is>
-          <t>PC GAMER</t>
-        </is>
-      </c>
-      <c r="U297" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>EMPORIO DOS FRIOS</t>
+        </is>
+      </c>
+      <c r="U297" t="inlineStr"/>
       <c r="V297" t="inlineStr"/>
       <c r="W297" t="inlineStr"/>
       <c r="X297" t="inlineStr"/>
@@ -32900,7 +32888,7 @@
       </c>
       <c r="AA297" t="inlineStr">
         <is>
-          <t>Juan Rodrigues</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="AB297" t="inlineStr"/>
@@ -32920,11 +32908,11 @@
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>6705</v>
+        <v>5417</v>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>NARCIZO ALVES CORDEIRO</t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -32934,7 +32922,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -32944,7 +32932,7 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G298" t="n">
@@ -32974,7 +32962,7 @@
         </is>
       </c>
       <c r="O298" t="n">
-        <v>17949077</v>
+        <v>17399452</v>
       </c>
       <c r="P298" t="inlineStr">
         <is>
@@ -32987,14 +32975,14 @@
         </is>
       </c>
       <c r="R298" s="1" t="n">
-        <v>46205.76232913195</v>
+        <v>46210.37424872685</v>
       </c>
       <c r="S298" t="n">
         <v>-5</v>
       </c>
       <c r="T298" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>NOSSO NOVO SUPERMERCADO</t>
         </is>
       </c>
       <c r="U298" t="inlineStr">
@@ -33002,7 +32990,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V298" t="inlineStr"/>
+      <c r="V298" t="inlineStr">
+        <is>
+          <t>Baixado via API integração MGC x Sistema de Analise Fiscal em 07/07/2026 08:56:44. - Data Comentário: 07/07/2026 08:55</t>
+        </is>
+      </c>
       <c r="W298" t="inlineStr"/>
       <c r="X298" t="inlineStr"/>
       <c r="Y298" t="inlineStr"/>
@@ -33011,7 +33003,7 @@
       </c>
       <c r="AA298" t="inlineStr">
         <is>
-          <t>Juan Rodrigues</t>
+          <t>ex-funcionario</t>
         </is>
       </c>
       <c r="AB298" t="inlineStr"/>
@@ -33031,11 +33023,11 @@
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>6885</v>
+        <v>6279</v>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
+          <t>DIENNYFER DA S PEREIRA</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -33045,7 +33037,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -33055,7 +33047,7 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G299" t="n">
@@ -33085,7 +33077,7 @@
         </is>
       </c>
       <c r="O299" t="n">
-        <v>18134169</v>
+        <v>17071101</v>
       </c>
       <c r="P299" t="inlineStr">
         <is>
@@ -33098,7 +33090,7 @@
         </is>
       </c>
       <c r="R299" s="1" t="n">
-        <v>46211.39581168981</v>
+        <v>46205.76232731481</v>
       </c>
       <c r="S299" t="n">
         <v>-5</v>
@@ -33108,12 +33100,12 @@
           <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
-      <c r="U299" t="inlineStr"/>
-      <c r="V299" t="inlineStr">
-        <is>
-          <t>Baixado via API integração MGC x Sistema de Analise Fiscal em 08/07/2026 09:27:45. - Data Comentário: 08/07/2026 09:26</t>
-        </is>
-      </c>
+      <c r="U299" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V299" t="inlineStr"/>
       <c r="W299" t="inlineStr"/>
       <c r="X299" t="inlineStr"/>
       <c r="Y299" t="inlineStr"/>
@@ -33122,7 +33114,7 @@
       </c>
       <c r="AA299" t="inlineStr">
         <is>
-          <t>ex-funcionario</t>
+          <t>Juan Rodrigues</t>
         </is>
       </c>
       <c r="AB299" t="inlineStr"/>
@@ -33142,11 +33134,11 @@
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>6703</v>
+        <v>6486</v>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
+          <t>PC GAMER GOIANIA LTDA</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -33156,7 +33148,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -33170,24 +33162,24 @@
         </is>
       </c>
       <c r="G300" t="n">
-        <v>950</v>
+        <v>11303</v>
       </c>
       <c r="H300" t="n">
         <v>0</v>
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>Confirm Rec - ISS Prestados</t>
+          <t>Retorno do Check-List Fiscal</t>
         </is>
       </c>
       <c r="K300" t="inlineStr"/>
       <c r="L300" s="1" t="n">
-        <v>46213</v>
+        <v>46218</v>
       </c>
       <c r="M300" t="inlineStr"/>
       <c r="N300" t="inlineStr">
@@ -33196,11 +33188,11 @@
         </is>
       </c>
       <c r="O300" t="n">
-        <v>17941144</v>
+        <v>16976349</v>
       </c>
       <c r="P300" t="inlineStr">
         <is>
-          <t>Victoria Virgens</t>
+          <t>Cristina Leite</t>
         </is>
       </c>
       <c r="Q300" t="inlineStr">
@@ -33209,14 +33201,14 @@
         </is>
       </c>
       <c r="R300" s="1" t="n">
-        <v>46210.67626055556</v>
+        <v>46205.7623278588</v>
       </c>
       <c r="S300" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="T300" t="inlineStr">
         <is>
-          <t>LIMA MOTA</t>
+          <t>PC GAMER</t>
         </is>
       </c>
       <c r="U300" t="inlineStr">
@@ -33224,11 +33216,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V300" t="inlineStr">
-        <is>
-          <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1792] sendo a ultima baixa feita [1792]-06/07/2026 17:54:38.. - Data Comentário: 06/07/2026 17:53</t>
-        </is>
-      </c>
+      <c r="V300" t="inlineStr"/>
       <c r="W300" t="inlineStr"/>
       <c r="X300" t="inlineStr"/>
       <c r="Y300" t="inlineStr"/>
@@ -33237,7 +33225,7 @@
       </c>
       <c r="AA300" t="inlineStr">
         <is>
-          <t>Victoria Virgens</t>
+          <t>Juan Rodrigues</t>
         </is>
       </c>
       <c r="AB300" t="inlineStr"/>
@@ -33246,18 +33234,22 @@
       <c r="AE300" t="inlineStr"/>
       <c r="AF300" t="inlineStr">
         <is>
-          <t>Imposto</t>
-        </is>
-      </c>
-      <c r="AG300" t="inlineStr"/>
+          <t>Tarefa</t>
+        </is>
+      </c>
+      <c r="AG300" t="inlineStr">
+        <is>
+          <t>Ricardo Fischer</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>6704</v>
+        <v>6705</v>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>TECNO COM INFORMATICA LTDA</t>
+          <t>NARCIZO ALVES CORDEIRO</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -33267,7 +33259,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -33281,24 +33273,24 @@
         </is>
       </c>
       <c r="G301" t="n">
-        <v>950</v>
+        <v>11303</v>
       </c>
       <c r="H301" t="n">
         <v>0</v>
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>Confirm Rec - ISS Prestados</t>
+          <t>Retorno do Check-List Fiscal</t>
         </is>
       </c>
       <c r="K301" t="inlineStr"/>
       <c r="L301" s="1" t="n">
-        <v>46213</v>
+        <v>46218</v>
       </c>
       <c r="M301" t="inlineStr"/>
       <c r="N301" t="inlineStr">
@@ -33307,11 +33299,11 @@
         </is>
       </c>
       <c r="O301" t="n">
-        <v>17952338</v>
+        <v>17949077</v>
       </c>
       <c r="P301" t="inlineStr">
         <is>
-          <t>Victoria Virgens</t>
+          <t>Cristina Leite</t>
         </is>
       </c>
       <c r="Q301" t="inlineStr">
@@ -33320,10 +33312,10 @@
         </is>
       </c>
       <c r="R301" s="1" t="n">
-        <v>46210.60626501157</v>
+        <v>46205.76232913195</v>
       </c>
       <c r="S301" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="T301" t="inlineStr">
         <is>
@@ -33335,11 +33327,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V301" t="inlineStr">
-        <is>
-          <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1792] sendo a ultima baixa feita [1792]-06/07/2026 14:56:57.. - Data Comentário: 06/07/2026 14:56</t>
-        </is>
-      </c>
+      <c r="V301" t="inlineStr"/>
       <c r="W301" t="inlineStr"/>
       <c r="X301" t="inlineStr"/>
       <c r="Y301" t="inlineStr"/>
@@ -33348,7 +33336,7 @@
       </c>
       <c r="AA301" t="inlineStr">
         <is>
-          <t>Victoria Virgens</t>
+          <t>Juan Rodrigues</t>
         </is>
       </c>
       <c r="AB301" t="inlineStr"/>
@@ -33357,18 +33345,22 @@
       <c r="AE301" t="inlineStr"/>
       <c r="AF301" t="inlineStr">
         <is>
-          <t>Imposto</t>
-        </is>
-      </c>
-      <c r="AG301" t="inlineStr"/>
+          <t>Tarefa</t>
+        </is>
+      </c>
+      <c r="AG301" t="inlineStr">
+        <is>
+          <t>Ricardo Fischer</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>6548</v>
+        <v>6885</v>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM LTDA</t>
+          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -33378,7 +33370,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -33392,24 +33384,24 @@
         </is>
       </c>
       <c r="G302" t="n">
-        <v>951</v>
+        <v>11303</v>
       </c>
       <c r="H302" t="n">
         <v>0</v>
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>Confirm Rec - ISS Tomados</t>
+          <t>Retorno do Check-List Fiscal</t>
         </is>
       </c>
       <c r="K302" t="inlineStr"/>
       <c r="L302" s="1" t="n">
-        <v>46213</v>
+        <v>46218</v>
       </c>
       <c r="M302" t="inlineStr"/>
       <c r="N302" t="inlineStr">
@@ -33418,11 +33410,11 @@
         </is>
       </c>
       <c r="O302" t="n">
-        <v>17222400</v>
+        <v>18134169</v>
       </c>
       <c r="P302" t="inlineStr">
         <is>
-          <t>Victoria Virgens</t>
+          <t>Cristina Leite</t>
         </is>
       </c>
       <c r="Q302" t="inlineStr">
@@ -33431,24 +33423,20 @@
         </is>
       </c>
       <c r="R302" s="1" t="n">
-        <v>46210.76622931713</v>
+        <v>46211.39581168981</v>
       </c>
       <c r="S302" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="T302" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM</t>
-        </is>
-      </c>
-      <c r="U302" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>EMPORIO DOS FRIOS</t>
+        </is>
+      </c>
+      <c r="U302" t="inlineStr"/>
       <c r="V302" t="inlineStr">
         <is>
-          <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1867] sendo a ultima baixa feita [1867]-07/07/2026 15:21:27.. - Data Comentário: 07/07/2026 15:20</t>
+          <t>Baixado via API integração MGC x Sistema de Analise Fiscal em 08/07/2026 09:27:45. - Data Comentário: 08/07/2026 09:26</t>
         </is>
       </c>
       <c r="W302" t="inlineStr"/>
@@ -33459,7 +33447,7 @@
       </c>
       <c r="AA302" t="inlineStr">
         <is>
-          <t>Victoria Virgens</t>
+          <t>ex-funcionario</t>
         </is>
       </c>
       <c r="AB302" t="inlineStr"/>
@@ -33468,18 +33456,22 @@
       <c r="AE302" t="inlineStr"/>
       <c r="AF302" t="inlineStr">
         <is>
-          <t>Imposto</t>
-        </is>
-      </c>
-      <c r="AG302" t="inlineStr"/>
+          <t>Tarefa</t>
+        </is>
+      </c>
+      <c r="AG302" t="inlineStr">
+        <is>
+          <t>Ricardo Fischer</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>6628</v>
+        <v>6703</v>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -33489,12 +33481,12 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
@@ -33503,7 +33495,7 @@
         </is>
       </c>
       <c r="G303" t="n">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="H303" t="n">
         <v>0</v>
@@ -33515,7 +33507,7 @@
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t>Confirm Rec - ISS Tomados</t>
+          <t>Confirm Rec - ISS Prestados</t>
         </is>
       </c>
       <c r="K303" t="inlineStr"/>
@@ -33529,7 +33521,7 @@
         </is>
       </c>
       <c r="O303" t="n">
-        <v>16959948</v>
+        <v>17941144</v>
       </c>
       <c r="P303" t="inlineStr">
         <is>
@@ -33542,14 +33534,14 @@
         </is>
       </c>
       <c r="R303" s="1" t="n">
-        <v>46210.6898024537</v>
+        <v>46210.67626055556</v>
       </c>
       <c r="S303" t="n">
         <v>0</v>
       </c>
       <c r="T303" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
+          <t>LIMA MOTA</t>
         </is>
       </c>
       <c r="U303" t="inlineStr">
@@ -33557,7 +33549,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V303" t="inlineStr"/>
+      <c r="V303" t="inlineStr">
+        <is>
+          <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1792] sendo a ultima baixa feita [1792]-06/07/2026 17:54:38.. - Data Comentário: 06/07/2026 17:53</t>
+        </is>
+      </c>
       <c r="W303" t="inlineStr"/>
       <c r="X303" t="inlineStr"/>
       <c r="Y303" t="inlineStr"/>
@@ -33582,11 +33578,11 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>6703</v>
+        <v>6704</v>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
+          <t>TECNO COM INFORMATICA LTDA</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -33596,7 +33592,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -33610,7 +33606,7 @@
         </is>
       </c>
       <c r="G304" t="n">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="H304" t="n">
         <v>0</v>
@@ -33622,7 +33618,7 @@
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>Confirm Rec - ISS Tomados</t>
+          <t>Confirm Rec - ISS Prestados</t>
         </is>
       </c>
       <c r="K304" t="inlineStr"/>
@@ -33636,7 +33632,7 @@
         </is>
       </c>
       <c r="O304" t="n">
-        <v>17941154</v>
+        <v>17952338</v>
       </c>
       <c r="P304" t="inlineStr">
         <is>
@@ -33649,14 +33645,14 @@
         </is>
       </c>
       <c r="R304" s="1" t="n">
-        <v>46210.76516364583</v>
+        <v>46210.60626501157</v>
       </c>
       <c r="S304" t="n">
         <v>0</v>
       </c>
       <c r="T304" t="inlineStr">
         <is>
-          <t>LIMA MOTA</t>
+          <t>TECNO COM</t>
         </is>
       </c>
       <c r="U304" t="inlineStr">
@@ -33666,7 +33662,7 @@
       </c>
       <c r="V304" t="inlineStr">
         <is>
-          <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1793] sendo a ultima baixa feita [1793]-03/07/2026 12:03:31.. - Data Comentário: 03/07/2026 12:02</t>
+          <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1792] sendo a ultima baixa feita [1792]-06/07/2026 14:56:57.. - Data Comentário: 06/07/2026 14:56</t>
         </is>
       </c>
       <c r="W304" t="inlineStr"/>
@@ -33693,11 +33689,11 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>6704</v>
+        <v>6548</v>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>TECNO COM INFORMATICA LTDA</t>
+          <t>GOIAS SILAGEM LTDA</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -33747,7 +33743,7 @@
         </is>
       </c>
       <c r="O305" t="n">
-        <v>17952349</v>
+        <v>17222400</v>
       </c>
       <c r="P305" t="inlineStr">
         <is>
@@ -33760,14 +33756,14 @@
         </is>
       </c>
       <c r="R305" s="1" t="n">
-        <v>46213.34372746528</v>
+        <v>46210.76622931713</v>
       </c>
       <c r="S305" t="n">
         <v>0</v>
       </c>
       <c r="T305" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>GOIAS SILAGEM</t>
         </is>
       </c>
       <c r="U305" t="inlineStr">
@@ -33777,7 +33773,7 @@
       </c>
       <c r="V305" t="inlineStr">
         <is>
-          <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1793] sendo a ultima baixa feita [1793]-07/07/2026 19:15:35.. - Data Comentário: 07/07/2026 19:15</t>
+          <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1867] sendo a ultima baixa feita [1867]-07/07/2026 15:21:27.. - Data Comentário: 07/07/2026 15:20</t>
         </is>
       </c>
       <c r="W305" t="inlineStr"/>
@@ -33804,11 +33800,11 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>6705</v>
+        <v>6628</v>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>NARCIZO ALVES CORDEIRO</t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -33823,7 +33819,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
@@ -33858,7 +33854,7 @@
         </is>
       </c>
       <c r="O306" t="n">
-        <v>17952533</v>
+        <v>16959948</v>
       </c>
       <c r="P306" t="inlineStr">
         <is>
@@ -33871,14 +33867,14 @@
         </is>
       </c>
       <c r="R306" s="1" t="n">
-        <v>46057.4012012963</v>
+        <v>46210.6898024537</v>
       </c>
       <c r="S306" t="n">
         <v>0</v>
       </c>
       <c r="T306" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t xml:space="preserve">GTG </t>
         </is>
       </c>
       <c r="U306" t="inlineStr">
@@ -33895,7 +33891,7 @@
       </c>
       <c r="AA306" t="inlineStr">
         <is>
-          <t>ex-funcionario</t>
+          <t>Victoria Virgens</t>
         </is>
       </c>
       <c r="AB306" t="inlineStr"/>
@@ -33911,11 +33907,11 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>6779</v>
+        <v>6703</v>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>CORDEIRO E CIA LTDA</t>
+          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -33925,7 +33921,7 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -33965,7 +33961,7 @@
         </is>
       </c>
       <c r="O307" t="n">
-        <v>18056703</v>
+        <v>17941154</v>
       </c>
       <c r="P307" t="inlineStr">
         <is>
@@ -33978,20 +33974,24 @@
         </is>
       </c>
       <c r="R307" s="1" t="n">
-        <v>46204.41790648148</v>
+        <v>46210.76516364583</v>
       </c>
       <c r="S307" t="n">
         <v>0</v>
       </c>
       <c r="T307" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
-        </is>
-      </c>
-      <c r="U307" t="inlineStr"/>
+          <t>LIMA MOTA</t>
+        </is>
+      </c>
+      <c r="U307" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V307" t="inlineStr">
         <is>
-          <t>Baixado via Rotina Configuração Após Baixa de tarefa, tarefas estão pedentes:[1793]. - Data Comentário: 01/07/2026 10:00</t>
+          <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1793] sendo a ultima baixa feita [1793]-03/07/2026 12:03:31.. - Data Comentário: 03/07/2026 12:02</t>
         </is>
       </c>
       <c r="W307" t="inlineStr"/>
@@ -34002,7 +34002,7 @@
       </c>
       <c r="AA307" t="inlineStr">
         <is>
-          <t>ex-funcionario</t>
+          <t>Victoria Virgens</t>
         </is>
       </c>
       <c r="AB307" t="inlineStr"/>
@@ -34018,11 +34018,11 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>6885</v>
+        <v>6704</v>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
+          <t>TECNO COM INFORMATICA LTDA</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -34032,7 +34032,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -34072,7 +34072,7 @@
         </is>
       </c>
       <c r="O308" t="n">
-        <v>18128657</v>
+        <v>17952349</v>
       </c>
       <c r="P308" t="inlineStr">
         <is>
@@ -34085,20 +34085,24 @@
         </is>
       </c>
       <c r="R308" s="1" t="n">
-        <v>46204.4179340625</v>
+        <v>46213.34372746528</v>
       </c>
       <c r="S308" t="n">
         <v>0</v>
       </c>
       <c r="T308" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
-        </is>
-      </c>
-      <c r="U308" t="inlineStr"/>
+          <t>TECNO COM</t>
+        </is>
+      </c>
+      <c r="U308" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V308" t="inlineStr">
         <is>
-          <t>Baixado via Rotina Configuração Após Baixa de tarefa, tarefas estão pedentes:[1793]. - Data Comentário: 01/07/2026 10:00</t>
+          <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1793] sendo a ultima baixa feita [1793]-07/07/2026 19:15:35.. - Data Comentário: 07/07/2026 19:15</t>
         </is>
       </c>
       <c r="W308" t="inlineStr"/>
@@ -34109,7 +34113,7 @@
       </c>
       <c r="AA308" t="inlineStr">
         <is>
-          <t>ex-funcionario</t>
+          <t>Victoria Virgens</t>
         </is>
       </c>
       <c r="AB308" t="inlineStr"/>
@@ -85545,7 +85549,7 @@
       <c r="V800" t="inlineStr">
         <is>
           <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 10/07/2026 
-Previsão de Conclusão 10/07/2026 - Data Comentário: 08/07/2026 14:46</t>
+Em decorrência das alterações da cbenef iremos concluir em 10/07 - Data Comentário: 10/07/2026 09:38</t>
         </is>
       </c>
       <c r="W800" t="inlineStr"/>

--- a/dados/base/goias.xlsx
+++ b/dados/base/goias.xlsx
@@ -2572,7 +2572,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2605,8 +2605,8 @@
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 10/07/2026 
-Empresa Implantação em processamento. - Data Comentário: 07/07/2026 15:25</t>
+          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 13/07/2026 
+Empresa Implantação em processamento. - Data Comentário: 10/07/2026 17:01</t>
         </is>
       </c>
       <c r="W20" t="inlineStr"/>

--- a/dados/base/goias.xlsx
+++ b/dados/base/goias.xlsx
@@ -43023,7 +43023,7 @@
       </c>
       <c r="R391" t="inlineStr"/>
       <c r="S391" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="T391" t="inlineStr">
         <is>
@@ -43128,7 +43128,7 @@
       </c>
       <c r="R392" t="inlineStr"/>
       <c r="S392" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="T392" t="inlineStr">
         <is>
@@ -43233,7 +43233,7 @@
       </c>
       <c r="R393" t="inlineStr"/>
       <c r="S393" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="T393" t="inlineStr">
         <is>
@@ -43338,7 +43338,7 @@
       </c>
       <c r="R394" t="inlineStr"/>
       <c r="S394" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="T394" t="inlineStr">
         <is>
@@ -43439,7 +43439,7 @@
       </c>
       <c r="R395" t="inlineStr"/>
       <c r="S395" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="T395" t="inlineStr">
         <is>
@@ -43540,7 +43540,7 @@
       </c>
       <c r="R396" t="inlineStr"/>
       <c r="S396" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="T396" t="inlineStr">
         <is>
@@ -43641,7 +43641,7 @@
       </c>
       <c r="R397" t="inlineStr"/>
       <c r="S397" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="T397" t="inlineStr">
         <is>
@@ -43746,7 +43746,7 @@
       </c>
       <c r="R398" t="inlineStr"/>
       <c r="S398" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="T398" t="inlineStr">
         <is>
@@ -43851,7 +43851,7 @@
       </c>
       <c r="R399" t="inlineStr"/>
       <c r="S399" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T399" t="inlineStr">
         <is>
@@ -43956,7 +43956,7 @@
       </c>
       <c r="R400" t="inlineStr"/>
       <c r="S400" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T400" t="inlineStr">
         <is>
@@ -44061,7 +44061,7 @@
       </c>
       <c r="R401" t="inlineStr"/>
       <c r="S401" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T401" t="inlineStr">
         <is>
@@ -44166,7 +44166,7 @@
       </c>
       <c r="R402" t="inlineStr"/>
       <c r="S402" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T402" t="inlineStr">
         <is>
@@ -44267,7 +44267,7 @@
       </c>
       <c r="R403" t="inlineStr"/>
       <c r="S403" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T403" t="inlineStr">
         <is>
@@ -44368,7 +44368,7 @@
       </c>
       <c r="R404" t="inlineStr"/>
       <c r="S404" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T404" t="inlineStr">
         <is>
@@ -44469,7 +44469,7 @@
       </c>
       <c r="R405" t="inlineStr"/>
       <c r="S405" t="n">
-        <v>-19</v>
+        <v>-18</v>
       </c>
       <c r="T405" t="inlineStr">
         <is>
@@ -44574,7 +44574,7 @@
       </c>
       <c r="R406" t="inlineStr"/>
       <c r="S406" t="n">
-        <v>-19</v>
+        <v>-18</v>
       </c>
       <c r="T406" t="inlineStr">
         <is>
@@ -44679,7 +44679,7 @@
       </c>
       <c r="R407" t="inlineStr"/>
       <c r="S407" t="n">
-        <v>-19</v>
+        <v>-18</v>
       </c>
       <c r="T407" t="inlineStr">
         <is>
@@ -44780,7 +44780,7 @@
       </c>
       <c r="R408" t="inlineStr"/>
       <c r="S408" t="n">
-        <v>-19</v>
+        <v>-18</v>
       </c>
       <c r="T408" t="inlineStr">
         <is>
@@ -44881,7 +44881,7 @@
       </c>
       <c r="R409" t="inlineStr"/>
       <c r="S409" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T409" t="inlineStr">
         <is>
@@ -44986,7 +44986,7 @@
       </c>
       <c r="R410" t="inlineStr"/>
       <c r="S410" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T410" t="inlineStr">
         <is>
@@ -45091,7 +45091,7 @@
       </c>
       <c r="R411" t="inlineStr"/>
       <c r="S411" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T411" t="inlineStr">
         <is>
@@ -45192,7 +45192,7 @@
       </c>
       <c r="R412" t="inlineStr"/>
       <c r="S412" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T412" t="inlineStr">
         <is>
@@ -45293,7 +45293,7 @@
       </c>
       <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="T413" t="inlineStr">
         <is>
@@ -45398,7 +45398,7 @@
       </c>
       <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="T414" t="inlineStr">
         <is>
@@ -45503,7 +45503,7 @@
       </c>
       <c r="R415" t="inlineStr"/>
       <c r="S415" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="T415" t="inlineStr">
         <is>
@@ -45604,7 +45604,7 @@
       </c>
       <c r="R416" t="inlineStr"/>
       <c r="S416" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="T416" t="inlineStr">
         <is>
@@ -45705,7 +45705,7 @@
       </c>
       <c r="R417" t="inlineStr"/>
       <c r="S417" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="T417" t="inlineStr">
         <is>
@@ -45810,7 +45810,7 @@
       </c>
       <c r="R418" t="inlineStr"/>
       <c r="S418" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="T418" t="inlineStr">
         <is>
@@ -45911,7 +45911,7 @@
       </c>
       <c r="R419" t="inlineStr"/>
       <c r="S419" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T419" t="inlineStr">
         <is>
@@ -46016,7 +46016,7 @@
       </c>
       <c r="R420" t="inlineStr"/>
       <c r="S420" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T420" t="inlineStr">
         <is>
@@ -46121,7 +46121,7 @@
       </c>
       <c r="R421" t="inlineStr"/>
       <c r="S421" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T421" t="inlineStr">
         <is>
@@ -46222,7 +46222,7 @@
       </c>
       <c r="R422" t="inlineStr"/>
       <c r="S422" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T422" t="inlineStr">
         <is>
@@ -46323,7 +46323,7 @@
       </c>
       <c r="R423" t="inlineStr"/>
       <c r="S423" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="T423" t="inlineStr">
         <is>
@@ -46428,7 +46428,7 @@
       </c>
       <c r="R424" t="inlineStr"/>
       <c r="S424" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="T424" t="inlineStr">
         <is>
@@ -46533,7 +46533,7 @@
       </c>
       <c r="R425" t="inlineStr"/>
       <c r="S425" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="T425" t="inlineStr">
         <is>
@@ -46638,7 +46638,7 @@
       </c>
       <c r="R426" t="inlineStr"/>
       <c r="S426" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="T426" t="inlineStr">
         <is>
@@ -46743,7 +46743,7 @@
       </c>
       <c r="R427" t="inlineStr"/>
       <c r="S427" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="T427" t="inlineStr">
         <is>
@@ -46848,7 +46848,7 @@
       </c>
       <c r="R428" t="inlineStr"/>
       <c r="S428" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="T428" t="inlineStr">
         <is>
@@ -46953,7 +46953,7 @@
       </c>
       <c r="R429" t="inlineStr"/>
       <c r="S429" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="T429" t="inlineStr">
         <is>
@@ -47058,7 +47058,7 @@
       </c>
       <c r="R430" t="inlineStr"/>
       <c r="S430" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="T430" t="inlineStr">
         <is>
@@ -47163,7 +47163,7 @@
       </c>
       <c r="R431" t="inlineStr"/>
       <c r="S431" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="T431" t="inlineStr">
         <is>
@@ -47268,7 +47268,7 @@
       </c>
       <c r="R432" t="inlineStr"/>
       <c r="S432" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="T432" t="inlineStr">
         <is>
@@ -47373,7 +47373,7 @@
       </c>
       <c r="R433" t="inlineStr"/>
       <c r="S433" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="T433" t="inlineStr">
         <is>
@@ -47474,7 +47474,7 @@
       </c>
       <c r="R434" t="inlineStr"/>
       <c r="S434" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="T434" t="inlineStr">
         <is>
@@ -47575,7 +47575,7 @@
       </c>
       <c r="R435" t="inlineStr"/>
       <c r="S435" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="T435" t="inlineStr">
         <is>
@@ -47680,7 +47680,7 @@
       </c>
       <c r="R436" t="inlineStr"/>
       <c r="S436" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="T436" t="inlineStr">
         <is>
@@ -47785,7 +47785,7 @@
       </c>
       <c r="R437" t="inlineStr"/>
       <c r="S437" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="T437" t="inlineStr">
         <is>
@@ -47890,7 +47890,7 @@
       </c>
       <c r="R438" t="inlineStr"/>
       <c r="S438" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="T438" t="inlineStr">
         <is>
@@ -47995,7 +47995,7 @@
       </c>
       <c r="R439" t="inlineStr"/>
       <c r="S439" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="T439" t="inlineStr">
         <is>
@@ -48100,7 +48100,7 @@
       </c>
       <c r="R440" t="inlineStr"/>
       <c r="S440" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T440" t="inlineStr">
         <is>
@@ -48205,7 +48205,7 @@
       </c>
       <c r="R441" t="inlineStr"/>
       <c r="S441" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T441" t="inlineStr">
         <is>
@@ -48310,7 +48310,7 @@
       </c>
       <c r="R442" t="inlineStr"/>
       <c r="S442" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T442" t="inlineStr">
         <is>
@@ -48415,7 +48415,7 @@
       </c>
       <c r="R443" t="inlineStr"/>
       <c r="S443" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T443" t="inlineStr">
         <is>
@@ -48520,7 +48520,7 @@
       </c>
       <c r="R444" t="inlineStr"/>
       <c r="S444" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T444" t="inlineStr">
         <is>
@@ -48625,7 +48625,7 @@
       </c>
       <c r="R445" t="inlineStr"/>
       <c r="S445" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T445" t="inlineStr">
         <is>
@@ -48730,7 +48730,7 @@
       </c>
       <c r="R446" t="inlineStr"/>
       <c r="S446" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T446" t="inlineStr">
         <is>
@@ -48835,7 +48835,7 @@
       </c>
       <c r="R447" t="inlineStr"/>
       <c r="S447" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T447" t="inlineStr">
         <is>
@@ -48940,7 +48940,7 @@
       </c>
       <c r="R448" t="inlineStr"/>
       <c r="S448" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T448" t="inlineStr">
         <is>
@@ -49045,7 +49045,7 @@
       </c>
       <c r="R449" t="inlineStr"/>
       <c r="S449" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T449" t="inlineStr">
         <is>
@@ -49150,7 +49150,7 @@
       </c>
       <c r="R450" t="inlineStr"/>
       <c r="S450" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T450" t="inlineStr">
         <is>
@@ -49251,7 +49251,7 @@
       </c>
       <c r="R451" t="inlineStr"/>
       <c r="S451" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T451" t="inlineStr">
         <is>
@@ -49352,7 +49352,7 @@
       </c>
       <c r="R452" t="inlineStr"/>
       <c r="S452" t="n">
-        <v>-19</v>
+        <v>-18</v>
       </c>
       <c r="T452" t="inlineStr">
         <is>
@@ -49457,7 +49457,7 @@
       </c>
       <c r="R453" t="inlineStr"/>
       <c r="S453" t="n">
-        <v>-19</v>
+        <v>-18</v>
       </c>
       <c r="T453" t="inlineStr">
         <is>
@@ -49562,7 +49562,7 @@
       </c>
       <c r="R454" t="inlineStr"/>
       <c r="S454" t="n">
-        <v>-19</v>
+        <v>-18</v>
       </c>
       <c r="T454" t="inlineStr">
         <is>
@@ -49667,7 +49667,7 @@
       </c>
       <c r="R455" t="inlineStr"/>
       <c r="S455" t="n">
-        <v>-19</v>
+        <v>-18</v>
       </c>
       <c r="T455" t="inlineStr">
         <is>
@@ -49772,7 +49772,7 @@
       </c>
       <c r="R456" t="inlineStr"/>
       <c r="S456" t="n">
-        <v>-19</v>
+        <v>-18</v>
       </c>
       <c r="T456" t="inlineStr">
         <is>
@@ -49877,7 +49877,7 @@
       </c>
       <c r="R457" t="inlineStr"/>
       <c r="S457" t="n">
-        <v>-19</v>
+        <v>-18</v>
       </c>
       <c r="T457" t="inlineStr">
         <is>
@@ -49982,7 +49982,7 @@
       </c>
       <c r="R458" t="inlineStr"/>
       <c r="S458" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="T458" t="inlineStr">
         <is>
@@ -50087,7 +50087,7 @@
       </c>
       <c r="R459" t="inlineStr"/>
       <c r="S459" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="T459" t="inlineStr">
         <is>
@@ -50192,7 +50192,7 @@
       </c>
       <c r="R460" t="inlineStr"/>
       <c r="S460" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="T460" t="inlineStr">
         <is>
@@ -50297,7 +50297,7 @@
       </c>
       <c r="R461" t="inlineStr"/>
       <c r="S461" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T461" t="inlineStr">
         <is>
@@ -50402,7 +50402,7 @@
       </c>
       <c r="R462" t="inlineStr"/>
       <c r="S462" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T462" t="inlineStr">
         <is>
@@ -50507,7 +50507,7 @@
       </c>
       <c r="R463" t="inlineStr"/>
       <c r="S463" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T463" t="inlineStr">
         <is>
@@ -50612,7 +50612,7 @@
       </c>
       <c r="R464" t="inlineStr"/>
       <c r="S464" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T464" t="inlineStr">
         <is>
@@ -50717,7 +50717,7 @@
       </c>
       <c r="R465" t="inlineStr"/>
       <c r="S465" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T465" t="inlineStr">
         <is>
@@ -50822,7 +50822,7 @@
       </c>
       <c r="R466" t="inlineStr"/>
       <c r="S466" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T466" t="inlineStr">
         <is>
@@ -50927,7 +50927,7 @@
       </c>
       <c r="R467" t="inlineStr"/>
       <c r="S467" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T467" t="inlineStr">
         <is>
@@ -51032,7 +51032,7 @@
       </c>
       <c r="R468" t="inlineStr"/>
       <c r="S468" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T468" t="inlineStr">
         <is>
@@ -51137,7 +51137,7 @@
       </c>
       <c r="R469" t="inlineStr"/>
       <c r="S469" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T469" t="inlineStr">
         <is>
@@ -51242,7 +51242,7 @@
       </c>
       <c r="R470" t="inlineStr"/>
       <c r="S470" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="T470" t="inlineStr">
         <is>
@@ -51347,7 +51347,7 @@
       </c>
       <c r="R471" t="inlineStr"/>
       <c r="S471" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="T471" t="inlineStr">
         <is>
@@ -51452,7 +51452,7 @@
       </c>
       <c r="R472" t="inlineStr"/>
       <c r="S472" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="T472" t="inlineStr">
         <is>
@@ -51557,7 +51557,7 @@
       </c>
       <c r="R473" t="inlineStr"/>
       <c r="S473" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="T473" t="inlineStr">
         <is>
@@ -51662,7 +51662,7 @@
       </c>
       <c r="R474" t="inlineStr"/>
       <c r="S474" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="T474" t="inlineStr">
         <is>
@@ -51767,7 +51767,7 @@
       </c>
       <c r="R475" t="inlineStr"/>
       <c r="S475" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="T475" t="inlineStr">
         <is>
@@ -51872,7 +51872,7 @@
       </c>
       <c r="R476" t="inlineStr"/>
       <c r="S476" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="T476" t="inlineStr">
         <is>
@@ -51977,7 +51977,7 @@
       </c>
       <c r="R477" t="inlineStr"/>
       <c r="S477" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="T477" t="inlineStr">
         <is>
@@ -52082,7 +52082,7 @@
       </c>
       <c r="R478" t="inlineStr"/>
       <c r="S478" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="T478" t="inlineStr">
         <is>
@@ -52187,7 +52187,7 @@
       </c>
       <c r="R479" t="inlineStr"/>
       <c r="S479" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="T479" t="inlineStr">
         <is>
@@ -52292,7 +52292,7 @@
       </c>
       <c r="R480" t="inlineStr"/>
       <c r="S480" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="T480" t="inlineStr">
         <is>
@@ -52393,7 +52393,7 @@
       </c>
       <c r="R481" t="inlineStr"/>
       <c r="S481" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="T481" t="inlineStr">
         <is>
@@ -52494,7 +52494,7 @@
       </c>
       <c r="R482" t="inlineStr"/>
       <c r="S482" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T482" t="inlineStr">
         <is>
@@ -52599,7 +52599,7 @@
       </c>
       <c r="R483" t="inlineStr"/>
       <c r="S483" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T483" t="inlineStr">
         <is>
@@ -52704,7 +52704,7 @@
       </c>
       <c r="R484" t="inlineStr"/>
       <c r="S484" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T484" t="inlineStr">
         <is>
@@ -52809,7 +52809,7 @@
       </c>
       <c r="R485" t="inlineStr"/>
       <c r="S485" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T485" t="inlineStr">
         <is>
@@ -52914,7 +52914,7 @@
       </c>
       <c r="R486" t="inlineStr"/>
       <c r="S486" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T486" t="inlineStr">
         <is>
@@ -53019,7 +53019,7 @@
       </c>
       <c r="R487" t="inlineStr"/>
       <c r="S487" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T487" t="inlineStr">
         <is>
@@ -53124,7 +53124,7 @@
       </c>
       <c r="R488" t="inlineStr"/>
       <c r="S488" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T488" t="inlineStr">
         <is>
@@ -53229,7 +53229,7 @@
       </c>
       <c r="R489" t="inlineStr"/>
       <c r="S489" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T489" t="inlineStr">
         <is>
@@ -53343,7 +53343,7 @@
       </c>
       <c r="R490" t="inlineStr"/>
       <c r="S490" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T490" t="inlineStr">
         <is>
@@ -53453,7 +53453,7 @@
       </c>
       <c r="R491" t="inlineStr"/>
       <c r="S491" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T491" t="inlineStr">
         <is>
@@ -53554,7 +53554,7 @@
       </c>
       <c r="R492" t="inlineStr"/>
       <c r="S492" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T492" t="inlineStr">
         <is>
@@ -53655,7 +53655,7 @@
       </c>
       <c r="R493" t="inlineStr"/>
       <c r="S493" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T493" t="inlineStr">
         <is>
@@ -53764,7 +53764,7 @@
       </c>
       <c r="R494" t="inlineStr"/>
       <c r="S494" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T494" t="inlineStr">
         <is>
@@ -53873,7 +53873,7 @@
       </c>
       <c r="R495" t="inlineStr"/>
       <c r="S495" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T495" t="inlineStr">
         <is>
@@ -53982,7 +53982,7 @@
       </c>
       <c r="R496" t="inlineStr"/>
       <c r="S496" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T496" t="inlineStr">
         <is>
@@ -54091,7 +54091,7 @@
       </c>
       <c r="R497" t="inlineStr"/>
       <c r="S497" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T497" t="inlineStr">
         <is>
@@ -54201,7 +54201,7 @@
       </c>
       <c r="R498" t="inlineStr"/>
       <c r="S498" t="n">
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="T498" t="inlineStr">
         <is>
@@ -54306,7 +54306,7 @@
       </c>
       <c r="R499" t="inlineStr"/>
       <c r="S499" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T499" t="inlineStr">
         <is>
@@ -54407,7 +54407,7 @@
       </c>
       <c r="R500" t="inlineStr"/>
       <c r="S500" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T500" t="inlineStr">
         <is>
@@ -54508,7 +54508,7 @@
       </c>
       <c r="R501" t="inlineStr"/>
       <c r="S501" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T501" t="inlineStr">
         <is>
@@ -54613,7 +54613,7 @@
       </c>
       <c r="R502" t="inlineStr"/>
       <c r="S502" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T502" t="inlineStr">
         <is>
@@ -54718,7 +54718,7 @@
       </c>
       <c r="R503" t="inlineStr"/>
       <c r="S503" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T503" t="inlineStr">
         <is>
@@ -54823,7 +54823,7 @@
       </c>
       <c r="R504" t="inlineStr"/>
       <c r="S504" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T504" t="inlineStr">
         <is>
@@ -54928,7 +54928,7 @@
       </c>
       <c r="R505" t="inlineStr"/>
       <c r="S505" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T505" t="inlineStr">
         <is>
@@ -55033,7 +55033,7 @@
       </c>
       <c r="R506" t="inlineStr"/>
       <c r="S506" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T506" t="inlineStr">
         <is>
@@ -55138,7 +55138,7 @@
       </c>
       <c r="R507" t="inlineStr"/>
       <c r="S507" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T507" t="inlineStr">
         <is>
@@ -55243,7 +55243,7 @@
       </c>
       <c r="R508" t="inlineStr"/>
       <c r="S508" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T508" t="inlineStr">
         <is>
@@ -55344,7 +55344,7 @@
       </c>
       <c r="R509" t="inlineStr"/>
       <c r="S509" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T509" t="inlineStr">
         <is>
@@ -55445,7 +55445,7 @@
       </c>
       <c r="R510" t="inlineStr"/>
       <c r="S510" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T510" t="inlineStr">
         <is>
@@ -55546,7 +55546,7 @@
       </c>
       <c r="R511" t="inlineStr"/>
       <c r="S511" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T511" t="inlineStr">
         <is>
@@ -55647,7 +55647,7 @@
       </c>
       <c r="R512" t="inlineStr"/>
       <c r="S512" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T512" t="inlineStr">
         <is>
@@ -55748,7 +55748,7 @@
       </c>
       <c r="R513" t="inlineStr"/>
       <c r="S513" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T513" t="inlineStr">
         <is>
@@ -55853,7 +55853,7 @@
       </c>
       <c r="R514" t="inlineStr"/>
       <c r="S514" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T514" t="inlineStr">
         <is>
@@ -55958,7 +55958,7 @@
       </c>
       <c r="R515" t="inlineStr"/>
       <c r="S515" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T515" t="inlineStr">
         <is>
@@ -56063,7 +56063,7 @@
       </c>
       <c r="R516" t="inlineStr"/>
       <c r="S516" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T516" t="inlineStr">
         <is>
@@ -56168,7 +56168,7 @@
       </c>
       <c r="R517" t="inlineStr"/>
       <c r="S517" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T517" t="inlineStr">
         <is>
@@ -56273,7 +56273,7 @@
       </c>
       <c r="R518" t="inlineStr"/>
       <c r="S518" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T518" t="inlineStr">
         <is>
@@ -56378,7 +56378,7 @@
       </c>
       <c r="R519" t="inlineStr"/>
       <c r="S519" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T519" t="inlineStr">
         <is>
@@ -56483,7 +56483,7 @@
       </c>
       <c r="R520" t="inlineStr"/>
       <c r="S520" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T520" t="inlineStr">
         <is>
@@ -56584,7 +56584,7 @@
       </c>
       <c r="R521" t="inlineStr"/>
       <c r="S521" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T521" t="inlineStr">
         <is>
@@ -56685,7 +56685,7 @@
       </c>
       <c r="R522" t="inlineStr"/>
       <c r="S522" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T522" t="inlineStr">
         <is>
@@ -56786,7 +56786,7 @@
       </c>
       <c r="R523" t="inlineStr"/>
       <c r="S523" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T523" t="inlineStr">
         <is>
@@ -56887,7 +56887,7 @@
       </c>
       <c r="R524" t="inlineStr"/>
       <c r="S524" t="n">
-        <v>-21</v>
+        <v>-20</v>
       </c>
       <c r="T524" t="inlineStr">
         <is>
@@ -56992,7 +56992,7 @@
       </c>
       <c r="R525" t="inlineStr"/>
       <c r="S525" t="n">
-        <v>-21</v>
+        <v>-20</v>
       </c>
       <c r="T525" t="inlineStr">
         <is>
@@ -57097,7 +57097,7 @@
       </c>
       <c r="R526" t="inlineStr"/>
       <c r="S526" t="n">
-        <v>-21</v>
+        <v>-20</v>
       </c>
       <c r="T526" t="inlineStr">
         <is>
@@ -57202,7 +57202,7 @@
       </c>
       <c r="R527" t="inlineStr"/>
       <c r="S527" t="n">
-        <v>-21</v>
+        <v>-20</v>
       </c>
       <c r="T527" t="inlineStr">
         <is>
@@ -57303,7 +57303,7 @@
       </c>
       <c r="R528" t="inlineStr"/>
       <c r="S528" t="n">
-        <v>-21</v>
+        <v>-20</v>
       </c>
       <c r="T528" t="inlineStr">
         <is>
@@ -57404,7 +57404,7 @@
       </c>
       <c r="R529" t="inlineStr"/>
       <c r="S529" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T529" t="inlineStr">
         <is>
@@ -57505,7 +57505,7 @@
       </c>
       <c r="R530" t="inlineStr"/>
       <c r="S530" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T530" t="inlineStr">
         <is>
@@ -57610,7 +57610,7 @@
       </c>
       <c r="R531" t="inlineStr"/>
       <c r="S531" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T531" t="inlineStr">
         <is>
@@ -57715,7 +57715,7 @@
       </c>
       <c r="R532" t="inlineStr"/>
       <c r="S532" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T532" t="inlineStr">
         <is>
@@ -57820,7 +57820,7 @@
       </c>
       <c r="R533" t="inlineStr"/>
       <c r="S533" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T533" t="inlineStr">
         <is>
@@ -57925,7 +57925,7 @@
       </c>
       <c r="R534" t="inlineStr"/>
       <c r="S534" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T534" t="inlineStr">
         <is>
@@ -58034,7 +58034,7 @@
       </c>
       <c r="R535" t="inlineStr"/>
       <c r="S535" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T535" t="inlineStr">
         <is>
@@ -58143,7 +58143,7 @@
       </c>
       <c r="R536" t="inlineStr"/>
       <c r="S536" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T536" t="inlineStr">
         <is>
@@ -58244,7 +58244,7 @@
       </c>
       <c r="R537" t="inlineStr"/>
       <c r="S537" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T537" t="inlineStr">
         <is>
@@ -58345,7 +58345,7 @@
       </c>
       <c r="R538" t="inlineStr"/>
       <c r="S538" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T538" t="inlineStr">
         <is>
@@ -58446,7 +58446,7 @@
       </c>
       <c r="R539" t="inlineStr"/>
       <c r="S539" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T539" t="inlineStr">
         <is>
@@ -58547,7 +58547,7 @@
       </c>
       <c r="R540" t="inlineStr"/>
       <c r="S540" t="n">
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="T540" t="inlineStr">
         <is>
@@ -58652,7 +58652,7 @@
       </c>
       <c r="R541" t="inlineStr"/>
       <c r="S541" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T541" t="inlineStr">
         <is>
@@ -58757,7 +58757,7 @@
       </c>
       <c r="R542" t="inlineStr"/>
       <c r="S542" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T542" t="inlineStr">
         <is>
@@ -58862,7 +58862,7 @@
       </c>
       <c r="R543" t="inlineStr"/>
       <c r="S543" t="n">
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="T543" t="inlineStr">
         <is>
@@ -58967,7 +58967,7 @@
       </c>
       <c r="R544" t="inlineStr"/>
       <c r="S544" t="n">
-        <v>-21</v>
+        <v>-20</v>
       </c>
       <c r="T544" t="inlineStr">
         <is>
@@ -59072,7 +59072,7 @@
       </c>
       <c r="R545" t="inlineStr"/>
       <c r="S545" t="n">
-        <v>-21</v>
+        <v>-20</v>
       </c>
       <c r="T545" t="inlineStr">
         <is>
@@ -59177,7 +59177,7 @@
       </c>
       <c r="R546" t="inlineStr"/>
       <c r="S546" t="n">
-        <v>-21</v>
+        <v>-20</v>
       </c>
       <c r="T546" t="inlineStr">
         <is>
@@ -59282,7 +59282,7 @@
       </c>
       <c r="R547" t="inlineStr"/>
       <c r="S547" t="n">
-        <v>-21</v>
+        <v>-20</v>
       </c>
       <c r="T547" t="inlineStr">
         <is>
@@ -59383,7 +59383,7 @@
       </c>
       <c r="R548" t="inlineStr"/>
       <c r="S548" t="n">
-        <v>-21</v>
+        <v>-20</v>
       </c>
       <c r="T548" t="inlineStr">
         <is>
@@ -59484,7 +59484,7 @@
       </c>
       <c r="R549" t="inlineStr"/>
       <c r="S549" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T549" t="inlineStr">
         <is>
@@ -59585,7 +59585,7 @@
       </c>
       <c r="R550" t="inlineStr"/>
       <c r="S550" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T550" t="inlineStr">
         <is>
@@ -59690,7 +59690,7 @@
       </c>
       <c r="R551" t="inlineStr"/>
       <c r="S551" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T551" t="inlineStr">
         <is>
@@ -59795,7 +59795,7 @@
       </c>
       <c r="R552" t="inlineStr"/>
       <c r="S552" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T552" t="inlineStr">
         <is>
@@ -59900,7 +59900,7 @@
       </c>
       <c r="R553" t="inlineStr"/>
       <c r="S553" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T553" t="inlineStr">
         <is>
@@ -60005,7 +60005,7 @@
       </c>
       <c r="R554" t="inlineStr"/>
       <c r="S554" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T554" t="inlineStr">
         <is>
@@ -60110,7 +60110,7 @@
       </c>
       <c r="R555" t="inlineStr"/>
       <c r="S555" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T555" t="inlineStr">
         <is>
@@ -60211,7 +60211,7 @@
       </c>
       <c r="R556" t="inlineStr"/>
       <c r="S556" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T556" t="inlineStr">
         <is>
@@ -60312,7 +60312,7 @@
       </c>
       <c r="R557" t="inlineStr"/>
       <c r="S557" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T557" t="inlineStr">
         <is>
@@ -60413,7 +60413,7 @@
       </c>
       <c r="R558" t="inlineStr"/>
       <c r="S558" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="T558" t="inlineStr">
         <is>
@@ -60518,7 +60518,7 @@
       </c>
       <c r="R559" t="inlineStr"/>
       <c r="S559" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="T559" t="inlineStr">
         <is>
@@ -60619,7 +60619,7 @@
       </c>
       <c r="R560" t="inlineStr"/>
       <c r="S560" t="n">
-        <v>-18</v>
+        <v>-17</v>
       </c>
       <c r="T560" t="inlineStr">
         <is>
@@ -60720,7 +60720,7 @@
       </c>
       <c r="R561" t="inlineStr"/>
       <c r="S561" t="n">
-        <v>-18</v>
+        <v>-17</v>
       </c>
       <c r="T561" t="inlineStr">
         <is>
@@ -60821,7 +60821,7 @@
       </c>
       <c r="R562" t="inlineStr"/>
       <c r="S562" t="n">
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="T562" t="inlineStr">
         <is>
@@ -60926,7 +60926,7 @@
       </c>
       <c r="R563" t="inlineStr"/>
       <c r="S563" t="n">
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="T563" t="inlineStr">
         <is>
@@ -61031,7 +61031,7 @@
       </c>
       <c r="R564" t="inlineStr"/>
       <c r="S564" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T564" t="inlineStr">
         <is>
@@ -61132,7 +61132,7 @@
       </c>
       <c r="R565" t="inlineStr"/>
       <c r="S565" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="T565" t="inlineStr">
         <is>
@@ -61237,7 +61237,7 @@
       </c>
       <c r="R566" t="inlineStr"/>
       <c r="S566" t="n">
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="T566" t="inlineStr">
         <is>
@@ -61342,7 +61342,7 @@
       </c>
       <c r="R567" t="inlineStr"/>
       <c r="S567" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T567" t="inlineStr">
         <is>
@@ -61447,7 +61447,7 @@
       </c>
       <c r="R568" t="inlineStr"/>
       <c r="S568" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="T568" t="inlineStr">
         <is>
@@ -61552,7 +61552,7 @@
       </c>
       <c r="R569" t="inlineStr"/>
       <c r="S569" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="T569" t="inlineStr">
         <is>
@@ -61657,7 +61657,7 @@
       </c>
       <c r="R570" t="inlineStr"/>
       <c r="S570" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="T570" t="inlineStr">
         <is>
@@ -61758,7 +61758,7 @@
       </c>
       <c r="R571" t="inlineStr"/>
       <c r="S571" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="T571" t="inlineStr">
         <is>
@@ -61859,7 +61859,7 @@
       </c>
       <c r="R572" t="inlineStr"/>
       <c r="S572" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T572" t="inlineStr">
         <is>
@@ -61964,7 +61964,7 @@
       </c>
       <c r="R573" t="inlineStr"/>
       <c r="S573" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T573" t="inlineStr">
         <is>
@@ -62069,7 +62069,7 @@
       </c>
       <c r="R574" t="inlineStr"/>
       <c r="S574" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T574" t="inlineStr">
         <is>
@@ -62174,7 +62174,7 @@
       </c>
       <c r="R575" t="inlineStr"/>
       <c r="S575" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="T575" t="inlineStr">
         <is>
@@ -62279,7 +62279,7 @@
       </c>
       <c r="R576" t="inlineStr"/>
       <c r="S576" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="T576" t="inlineStr">
         <is>
@@ -62384,7 +62384,7 @@
       </c>
       <c r="R577" t="inlineStr"/>
       <c r="S577" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="T577" t="inlineStr">
         <is>
@@ -62485,7 +62485,7 @@
       </c>
       <c r="R578" t="inlineStr"/>
       <c r="S578" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="T578" t="inlineStr">
         <is>
@@ -62586,7 +62586,7 @@
       </c>
       <c r="R579" t="inlineStr"/>
       <c r="S579" t="n">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="T579" t="inlineStr">
         <is>
@@ -62691,7 +62691,7 @@
       </c>
       <c r="R580" t="inlineStr"/>
       <c r="S580" t="n">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="T580" t="inlineStr">
         <is>
@@ -62796,7 +62796,7 @@
       </c>
       <c r="R581" t="inlineStr"/>
       <c r="S581" t="n">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="T581" t="inlineStr">
         <is>
@@ -62901,7 +62901,7 @@
       </c>
       <c r="R582" t="inlineStr"/>
       <c r="S582" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="T582" t="inlineStr">
         <is>
@@ -63006,7 +63006,7 @@
       </c>
       <c r="R583" t="inlineStr"/>
       <c r="S583" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="T583" t="inlineStr">
         <is>
@@ -63107,7 +63107,7 @@
       </c>
       <c r="R584" t="inlineStr"/>
       <c r="S584" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="T584" t="inlineStr">
         <is>
@@ -63208,7 +63208,7 @@
       </c>
       <c r="R585" t="inlineStr"/>
       <c r="S585" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T585" t="inlineStr">
         <is>
@@ -63313,7 +63313,7 @@
       </c>
       <c r="R586" t="inlineStr"/>
       <c r="S586" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T586" t="inlineStr">
         <is>
@@ -63418,7 +63418,7 @@
       </c>
       <c r="R587" t="inlineStr"/>
       <c r="S587" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T587" t="inlineStr">
         <is>
@@ -63523,7 +63523,7 @@
       </c>
       <c r="R588" t="inlineStr"/>
       <c r="S588" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T588" t="inlineStr">
         <is>
@@ -63628,7 +63628,7 @@
       </c>
       <c r="R589" t="inlineStr"/>
       <c r="S589" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T589" t="inlineStr">
         <is>
@@ -63729,7 +63729,7 @@
       </c>
       <c r="R590" t="inlineStr"/>
       <c r="S590" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="T590" t="inlineStr">
         <is>
@@ -63834,7 +63834,7 @@
       </c>
       <c r="R591" t="inlineStr"/>
       <c r="S591" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="T591" t="inlineStr">
         <is>
@@ -63939,7 +63939,7 @@
       </c>
       <c r="R592" t="inlineStr"/>
       <c r="S592" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="T592" t="inlineStr">
         <is>
@@ -64044,7 +64044,7 @@
       </c>
       <c r="R593" t="inlineStr"/>
       <c r="S593" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="T593" t="inlineStr">
         <is>
@@ -64149,7 +64149,7 @@
       </c>
       <c r="R594" t="inlineStr"/>
       <c r="S594" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="T594" t="inlineStr">
         <is>
@@ -64254,7 +64254,7 @@
       </c>
       <c r="R595" t="inlineStr"/>
       <c r="S595" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="T595" t="inlineStr">
         <is>
@@ -64359,7 +64359,7 @@
       </c>
       <c r="R596" t="inlineStr"/>
       <c r="S596" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T596" t="inlineStr">
         <is>
@@ -64464,7 +64464,7 @@
       </c>
       <c r="R597" t="inlineStr"/>
       <c r="S597" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T597" t="inlineStr">
         <is>
@@ -64569,7 +64569,7 @@
       </c>
       <c r="R598" t="inlineStr"/>
       <c r="S598" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T598" t="inlineStr">
         <is>
@@ -64674,7 +64674,7 @@
       </c>
       <c r="R599" t="inlineStr"/>
       <c r="S599" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T599" t="inlineStr">
         <is>
@@ -64779,7 +64779,7 @@
       </c>
       <c r="R600" t="inlineStr"/>
       <c r="S600" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T600" t="inlineStr">
         <is>
@@ -64884,7 +64884,7 @@
       </c>
       <c r="R601" t="inlineStr"/>
       <c r="S601" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T601" t="inlineStr">
         <is>
@@ -64989,7 +64989,7 @@
       </c>
       <c r="R602" t="inlineStr"/>
       <c r="S602" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T602" t="inlineStr">
         <is>
@@ -65094,7 +65094,7 @@
       </c>
       <c r="R603" t="inlineStr"/>
       <c r="S603" t="n">
-        <v>-18</v>
+        <v>-17</v>
       </c>
       <c r="T603" t="inlineStr">
         <is>
@@ -65199,7 +65199,7 @@
       </c>
       <c r="R604" t="inlineStr"/>
       <c r="S604" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T604" t="inlineStr">
         <is>
@@ -65304,7 +65304,7 @@
       </c>
       <c r="R605" t="inlineStr"/>
       <c r="S605" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T605" t="inlineStr">
         <is>
@@ -65405,7 +65405,7 @@
       </c>
       <c r="R606" t="inlineStr"/>
       <c r="S606" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T606" t="inlineStr">
         <is>
@@ -65506,7 +65506,7 @@
       </c>
       <c r="R607" t="inlineStr"/>
       <c r="S607" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="T607" t="inlineStr">
         <is>
@@ -65611,7 +65611,7 @@
       </c>
       <c r="R608" t="inlineStr"/>
       <c r="S608" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="T608" t="inlineStr">
         <is>
@@ -65716,7 +65716,7 @@
       </c>
       <c r="R609" t="inlineStr"/>
       <c r="S609" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T609" t="inlineStr">
         <is>
@@ -65821,7 +65821,7 @@
       </c>
       <c r="R610" t="inlineStr"/>
       <c r="S610" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T610" t="inlineStr">
         <is>
@@ -65926,7 +65926,7 @@
       </c>
       <c r="R611" t="inlineStr"/>
       <c r="S611" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T611" t="inlineStr">
         <is>
@@ -66031,7 +66031,7 @@
       </c>
       <c r="R612" t="inlineStr"/>
       <c r="S612" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="T612" t="inlineStr">
         <is>
@@ -66136,7 +66136,7 @@
       </c>
       <c r="R613" t="inlineStr"/>
       <c r="S613" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="T613" t="inlineStr">
         <is>
@@ -66241,7 +66241,7 @@
       </c>
       <c r="R614" t="inlineStr"/>
       <c r="S614" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="T614" t="inlineStr">
         <is>
@@ -66346,7 +66346,7 @@
       </c>
       <c r="R615" t="inlineStr"/>
       <c r="S615" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="T615" t="inlineStr">
         <is>
@@ -66451,7 +66451,7 @@
       </c>
       <c r="R616" t="inlineStr"/>
       <c r="S616" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="T616" t="inlineStr">
         <is>
@@ -66556,7 +66556,7 @@
       </c>
       <c r="R617" t="inlineStr"/>
       <c r="S617" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="T617" t="inlineStr">
         <is>
@@ -66661,7 +66661,7 @@
       </c>
       <c r="R618" t="inlineStr"/>
       <c r="S618" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="T618" t="inlineStr">
         <is>
@@ -66766,7 +66766,7 @@
       </c>
       <c r="R619" t="inlineStr"/>
       <c r="S619" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="T619" t="inlineStr">
         <is>
@@ -66871,7 +66871,7 @@
       </c>
       <c r="R620" t="inlineStr"/>
       <c r="S620" t="n">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="T620" t="inlineStr">
         <is>
@@ -66976,7 +66976,7 @@
       </c>
       <c r="R621" t="inlineStr"/>
       <c r="S621" t="n">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="T621" t="inlineStr">
         <is>
@@ -67081,7 +67081,7 @@
       </c>
       <c r="R622" t="inlineStr"/>
       <c r="S622" t="n">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="T622" t="inlineStr">
         <is>
@@ -67186,7 +67186,7 @@
       </c>
       <c r="R623" t="inlineStr"/>
       <c r="S623" t="n">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="T623" t="inlineStr">
         <is>
@@ -67291,7 +67291,7 @@
       </c>
       <c r="R624" t="inlineStr"/>
       <c r="S624" t="n">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="T624" t="inlineStr">
         <is>
@@ -67402,7 +67402,7 @@
       </c>
       <c r="R625" t="inlineStr"/>
       <c r="S625" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T625" t="inlineStr">
         <is>
@@ -67503,7 +67503,7 @@
       </c>
       <c r="R626" t="inlineStr"/>
       <c r="S626" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T626" t="inlineStr">
         <is>
@@ -67600,7 +67600,7 @@
       </c>
       <c r="R627" t="inlineStr"/>
       <c r="S627" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T627" t="inlineStr">
         <is>
@@ -67697,7 +67697,7 @@
       </c>
       <c r="R628" t="inlineStr"/>
       <c r="S628" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T628" t="inlineStr">
         <is>
@@ -67794,7 +67794,7 @@
       </c>
       <c r="R629" t="inlineStr"/>
       <c r="S629" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T629" t="inlineStr">
         <is>
@@ -67895,7 +67895,7 @@
       </c>
       <c r="R630" t="inlineStr"/>
       <c r="S630" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T630" t="inlineStr">
         <is>
@@ -67996,7 +67996,7 @@
       </c>
       <c r="R631" t="inlineStr"/>
       <c r="S631" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T631" t="inlineStr">
         <is>
@@ -68097,7 +68097,7 @@
       </c>
       <c r="R632" t="inlineStr"/>
       <c r="S632" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T632" t="inlineStr">
         <is>
@@ -68198,7 +68198,7 @@
       </c>
       <c r="R633" t="inlineStr"/>
       <c r="S633" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T633" t="inlineStr">
         <is>
@@ -68299,7 +68299,7 @@
       </c>
       <c r="R634" t="inlineStr"/>
       <c r="S634" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T634" t="inlineStr">
         <is>
@@ -68400,7 +68400,7 @@
       </c>
       <c r="R635" t="inlineStr"/>
       <c r="S635" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T635" t="inlineStr">
         <is>
@@ -68501,7 +68501,7 @@
       </c>
       <c r="R636" t="inlineStr"/>
       <c r="S636" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T636" t="inlineStr">
         <is>
@@ -68602,7 +68602,7 @@
       </c>
       <c r="R637" t="inlineStr"/>
       <c r="S637" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T637" t="inlineStr">
         <is>
@@ -68703,7 +68703,7 @@
       </c>
       <c r="R638" t="inlineStr"/>
       <c r="S638" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T638" t="inlineStr">
         <is>
@@ -68804,7 +68804,7 @@
       </c>
       <c r="R639" t="inlineStr"/>
       <c r="S639" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T639" t="inlineStr">
         <is>
@@ -68905,7 +68905,7 @@
       </c>
       <c r="R640" t="inlineStr"/>
       <c r="S640" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T640" t="inlineStr">
         <is>
@@ -69006,7 +69006,7 @@
       </c>
       <c r="R641" t="inlineStr"/>
       <c r="S641" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T641" t="inlineStr">
         <is>
@@ -69107,7 +69107,7 @@
       </c>
       <c r="R642" t="inlineStr"/>
       <c r="S642" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T642" t="inlineStr">
         <is>
@@ -69204,7 +69204,7 @@
       </c>
       <c r="R643" t="inlineStr"/>
       <c r="S643" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T643" t="inlineStr">
         <is>
@@ -69301,7 +69301,7 @@
       </c>
       <c r="R644" t="inlineStr"/>
       <c r="S644" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T644" t="inlineStr">
         <is>
@@ -69398,7 +69398,7 @@
       </c>
       <c r="R645" t="inlineStr"/>
       <c r="S645" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T645" t="inlineStr">
         <is>
@@ -69495,7 +69495,7 @@
       </c>
       <c r="R646" t="inlineStr"/>
       <c r="S646" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T646" t="inlineStr">
         <is>
@@ -69592,7 +69592,7 @@
       </c>
       <c r="R647" t="inlineStr"/>
       <c r="S647" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T647" t="inlineStr">
         <is>
@@ -69689,7 +69689,7 @@
       </c>
       <c r="R648" t="inlineStr"/>
       <c r="S648" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T648" t="inlineStr">
         <is>
@@ -69790,7 +69790,7 @@
       </c>
       <c r="R649" t="inlineStr"/>
       <c r="S649" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T649" t="inlineStr">
         <is>
@@ -69891,7 +69891,7 @@
       </c>
       <c r="R650" t="inlineStr"/>
       <c r="S650" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T650" t="inlineStr">
         <is>
@@ -69992,7 +69992,7 @@
       </c>
       <c r="R651" t="inlineStr"/>
       <c r="S651" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T651" t="inlineStr">
         <is>
@@ -70093,7 +70093,7 @@
       </c>
       <c r="R652" t="inlineStr"/>
       <c r="S652" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T652" t="inlineStr">
         <is>
@@ -70194,7 +70194,7 @@
       </c>
       <c r="R653" t="inlineStr"/>
       <c r="S653" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T653" t="inlineStr">
         <is>
@@ -70295,7 +70295,7 @@
       </c>
       <c r="R654" t="inlineStr"/>
       <c r="S654" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T654" t="inlineStr">
         <is>
@@ -70396,7 +70396,7 @@
       </c>
       <c r="R655" t="inlineStr"/>
       <c r="S655" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T655" t="inlineStr">
         <is>
@@ -70493,7 +70493,7 @@
       </c>
       <c r="R656" t="inlineStr"/>
       <c r="S656" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T656" t="inlineStr">
         <is>
@@ -70590,7 +70590,7 @@
       </c>
       <c r="R657" t="inlineStr"/>
       <c r="S657" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T657" t="inlineStr">
         <is>
@@ -70687,7 +70687,7 @@
       </c>
       <c r="R658" t="inlineStr"/>
       <c r="S658" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T658" t="inlineStr">
         <is>
@@ -70784,7 +70784,7 @@
       </c>
       <c r="R659" t="inlineStr"/>
       <c r="S659" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T659" t="inlineStr">
         <is>
@@ -70881,7 +70881,7 @@
       </c>
       <c r="R660" t="inlineStr"/>
       <c r="S660" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T660" t="inlineStr">
         <is>
@@ -70978,7 +70978,7 @@
       </c>
       <c r="R661" t="inlineStr"/>
       <c r="S661" t="n">
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="T661" t="inlineStr">
         <is>
@@ -71079,7 +71079,7 @@
       </c>
       <c r="R662" t="inlineStr"/>
       <c r="S662" t="n">
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="T662" t="inlineStr">
         <is>
@@ -71180,7 +71180,7 @@
       </c>
       <c r="R663" t="inlineStr"/>
       <c r="S663" t="n">
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="T663" t="inlineStr">
         <is>
@@ -71281,7 +71281,7 @@
       </c>
       <c r="R664" t="inlineStr"/>
       <c r="S664" t="n">
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="T664" t="inlineStr">
         <is>
@@ -71382,7 +71382,7 @@
       </c>
       <c r="R665" t="inlineStr"/>
       <c r="S665" t="n">
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="T665" t="inlineStr">
         <is>
@@ -71483,7 +71483,7 @@
       </c>
       <c r="R666" t="inlineStr"/>
       <c r="S666" t="n">
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="T666" t="inlineStr">
         <is>
@@ -71584,7 +71584,7 @@
       </c>
       <c r="R667" t="inlineStr"/>
       <c r="S667" t="n">
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="T667" t="inlineStr">
         <is>
@@ -71685,7 +71685,7 @@
       </c>
       <c r="R668" t="inlineStr"/>
       <c r="S668" t="n">
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="T668" t="inlineStr">
         <is>
@@ -71786,7 +71786,7 @@
       </c>
       <c r="R669" t="inlineStr"/>
       <c r="S669" t="n">
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="T669" t="inlineStr">
         <is>
@@ -71887,7 +71887,7 @@
       </c>
       <c r="R670" t="inlineStr"/>
       <c r="S670" t="n">
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="T670" t="inlineStr">
         <is>
@@ -71984,7 +71984,7 @@
       </c>
       <c r="R671" t="inlineStr"/>
       <c r="S671" t="n">
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="T671" t="inlineStr">
         <is>
@@ -72081,7 +72081,7 @@
       </c>
       <c r="R672" t="inlineStr"/>
       <c r="S672" t="n">
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="T672" t="inlineStr">
         <is>
@@ -72178,7 +72178,7 @@
       </c>
       <c r="R673" t="inlineStr"/>
       <c r="S673" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T673" t="inlineStr">
         <is>
@@ -72279,7 +72279,7 @@
       </c>
       <c r="R674" t="inlineStr"/>
       <c r="S674" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T674" t="inlineStr">
         <is>
@@ -72380,7 +72380,7 @@
       </c>
       <c r="R675" t="inlineStr"/>
       <c r="S675" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T675" t="inlineStr">
         <is>
@@ -72481,7 +72481,7 @@
       </c>
       <c r="R676" t="inlineStr"/>
       <c r="S676" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T676" t="inlineStr">
         <is>
@@ -72582,7 +72582,7 @@
       </c>
       <c r="R677" t="inlineStr"/>
       <c r="S677" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T677" t="inlineStr">
         <is>
@@ -72683,7 +72683,7 @@
       </c>
       <c r="R678" t="inlineStr"/>
       <c r="S678" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T678" t="inlineStr">
         <is>
@@ -72784,7 +72784,7 @@
       </c>
       <c r="R679" t="inlineStr"/>
       <c r="S679" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T679" t="inlineStr">
         <is>
@@ -72885,7 +72885,7 @@
       </c>
       <c r="R680" t="inlineStr"/>
       <c r="S680" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T680" t="inlineStr">
         <is>
@@ -72986,7 +72986,7 @@
       </c>
       <c r="R681" t="inlineStr"/>
       <c r="S681" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T681" t="inlineStr">
         <is>
@@ -73087,7 +73087,7 @@
       </c>
       <c r="R682" t="inlineStr"/>
       <c r="S682" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T682" t="inlineStr">
         <is>
@@ -73188,7 +73188,7 @@
       </c>
       <c r="R683" t="inlineStr"/>
       <c r="S683" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T683" t="inlineStr">
         <is>
@@ -73289,7 +73289,7 @@
       </c>
       <c r="R684" t="inlineStr"/>
       <c r="S684" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T684" t="inlineStr">
         <is>
@@ -73390,7 +73390,7 @@
       </c>
       <c r="R685" t="inlineStr"/>
       <c r="S685" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T685" t="inlineStr">
         <is>
@@ -73491,7 +73491,7 @@
       </c>
       <c r="R686" t="inlineStr"/>
       <c r="S686" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T686" t="inlineStr">
         <is>
@@ -73588,7 +73588,7 @@
       </c>
       <c r="R687" t="inlineStr"/>
       <c r="S687" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T687" t="inlineStr">
         <is>
@@ -73685,7 +73685,7 @@
       </c>
       <c r="R688" t="inlineStr"/>
       <c r="S688" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T688" t="inlineStr">
         <is>
@@ -73782,7 +73782,7 @@
       </c>
       <c r="R689" t="inlineStr"/>
       <c r="S689" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T689" t="inlineStr">
         <is>
@@ -73879,7 +73879,7 @@
       </c>
       <c r="R690" t="inlineStr"/>
       <c r="S690" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T690" t="inlineStr">
         <is>
@@ -73976,7 +73976,7 @@
       </c>
       <c r="R691" t="inlineStr"/>
       <c r="S691" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T691" t="inlineStr">
         <is>
@@ -74073,7 +74073,7 @@
       </c>
       <c r="R692" t="inlineStr"/>
       <c r="S692" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T692" t="inlineStr">
         <is>
@@ -74174,7 +74174,7 @@
       </c>
       <c r="R693" t="inlineStr"/>
       <c r="S693" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T693" t="inlineStr">
         <is>
@@ -74275,7 +74275,7 @@
       </c>
       <c r="R694" t="inlineStr"/>
       <c r="S694" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T694" t="inlineStr">
         <is>
@@ -74376,7 +74376,7 @@
       </c>
       <c r="R695" t="inlineStr"/>
       <c r="S695" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T695" t="inlineStr">
         <is>
@@ -74477,7 +74477,7 @@
       </c>
       <c r="R696" t="inlineStr"/>
       <c r="S696" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T696" t="inlineStr">
         <is>
@@ -74578,7 +74578,7 @@
       </c>
       <c r="R697" t="inlineStr"/>
       <c r="S697" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T697" t="inlineStr">
         <is>
@@ -74679,7 +74679,7 @@
       </c>
       <c r="R698" t="inlineStr"/>
       <c r="S698" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T698" t="inlineStr">
         <is>
@@ -74780,7 +74780,7 @@
       </c>
       <c r="R699" t="inlineStr"/>
       <c r="S699" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T699" t="inlineStr">
         <is>
@@ -74877,7 +74877,7 @@
       </c>
       <c r="R700" t="inlineStr"/>
       <c r="S700" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T700" t="inlineStr">
         <is>
@@ -74974,7 +74974,7 @@
       </c>
       <c r="R701" t="inlineStr"/>
       <c r="S701" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T701" t="inlineStr">
         <is>
@@ -75071,7 +75071,7 @@
       </c>
       <c r="R702" t="inlineStr"/>
       <c r="S702" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T702" t="inlineStr">
         <is>
@@ -75168,7 +75168,7 @@
       </c>
       <c r="R703" t="inlineStr"/>
       <c r="S703" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T703" t="inlineStr">
         <is>
@@ -75265,7 +75265,7 @@
       </c>
       <c r="R704" t="inlineStr"/>
       <c r="S704" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T704" t="inlineStr">
         <is>
@@ -75362,7 +75362,7 @@
       </c>
       <c r="R705" t="inlineStr"/>
       <c r="S705" t="n">
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="T705" t="inlineStr">
         <is>
@@ -75463,7 +75463,7 @@
       </c>
       <c r="R706" t="inlineStr"/>
       <c r="S706" t="n">
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="T706" t="inlineStr">
         <is>
@@ -75564,7 +75564,7 @@
       </c>
       <c r="R707" t="inlineStr"/>
       <c r="S707" t="n">
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="T707" t="inlineStr">
         <is>
@@ -75663,7 +75663,7 @@
         <v>46209.66158305555</v>
       </c>
       <c r="S708" t="n">
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="T708" t="inlineStr">
         <is>
@@ -75766,7 +75766,7 @@
         <v>46203.00285659722</v>
       </c>
       <c r="S709" t="n">
-        <v>-18</v>
+        <v>-17</v>
       </c>
       <c r="T709" t="inlineStr">
         <is>
@@ -75877,7 +75877,7 @@
         <v>46203.00296711805</v>
       </c>
       <c r="S710" t="n">
-        <v>-18</v>
+        <v>-17</v>
       </c>
       <c r="T710" t="inlineStr">
         <is>
@@ -75984,7 +75984,7 @@
         <v>46204.72937350695</v>
       </c>
       <c r="S711" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="T711" t="inlineStr">
         <is>
@@ -76095,7 +76095,7 @@
         <v>46206.41464283565</v>
       </c>
       <c r="S712" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T712" t="inlineStr">
         <is>
@@ -76206,7 +76206,7 @@
         <v>46206.70573774305</v>
       </c>
       <c r="S713" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T713" t="inlineStr">
         <is>
@@ -76317,7 +76317,7 @@
         <v>46206.70573846065</v>
       </c>
       <c r="S714" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T714" t="inlineStr">
         <is>
@@ -76428,7 +76428,7 @@
         <v>46211.41697137732</v>
       </c>
       <c r="S715" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T715" t="inlineStr">
         <is>
@@ -76539,7 +76539,7 @@
         <v>46203.3758668287</v>
       </c>
       <c r="S716" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T716" t="inlineStr">
         <is>
@@ -76650,7 +76650,7 @@
         <v>46203.37586737268</v>
       </c>
       <c r="S717" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T717" t="inlineStr">
         <is>
@@ -76761,7 +76761,7 @@
         <v>46203.37586936342</v>
       </c>
       <c r="S718" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T718" t="inlineStr">
         <is>
@@ -76872,7 +76872,7 @@
         <v>46205.45020773148</v>
       </c>
       <c r="S719" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T719" t="inlineStr">
         <is>
@@ -76983,7 +76983,7 @@
         <v>46205.45020809027</v>
       </c>
       <c r="S720" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T720" t="inlineStr">
         <is>
@@ -77094,7 +77094,7 @@
         <v>46205.45020880787</v>
       </c>
       <c r="S721" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T721" t="inlineStr">
         <is>
@@ -77201,7 +77201,7 @@
         <v>46203.37587081019</v>
       </c>
       <c r="S722" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T722" t="inlineStr">
         <is>
@@ -77308,7 +77308,7 @@
         <v>46206.62907918981</v>
       </c>
       <c r="S723" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T723" t="inlineStr">
         <is>
@@ -77419,7 +77419,7 @@
         <v>46204.00354291667</v>
       </c>
       <c r="S724" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T724" t="inlineStr">
         <is>
@@ -77530,7 +77530,7 @@
         <v>46206.44786171296</v>
       </c>
       <c r="S725" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T725" t="inlineStr">
         <is>
@@ -77641,7 +77641,7 @@
         <v>46203.71390146991</v>
       </c>
       <c r="S726" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T726" t="inlineStr">
         <is>
@@ -77752,7 +77752,7 @@
         <v>46203.00370568287</v>
       </c>
       <c r="S727" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="T727" t="inlineStr">
         <is>
@@ -77863,7 +77863,7 @@
         <v>46209.779275</v>
       </c>
       <c r="S728" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T728" t="inlineStr">
         <is>
@@ -77978,7 +77978,7 @@
         <v>46188.33599649306</v>
       </c>
       <c r="S729" t="n">
-        <v>-18</v>
+        <v>-17</v>
       </c>
       <c r="T729" t="inlineStr">
         <is>
@@ -78089,7 +78089,7 @@
         <v>46204.3759534375</v>
       </c>
       <c r="S730" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="T730" t="inlineStr">
         <is>
@@ -78200,7 +78200,7 @@
         <v>46206.79235917824</v>
       </c>
       <c r="S731" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="T731" t="inlineStr">
         <is>
@@ -78311,7 +78311,7 @@
         <v>46206.79235393518</v>
       </c>
       <c r="S732" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="T732" t="inlineStr">
         <is>
@@ -78422,7 +78422,7 @@
         <v>46210.75621153935</v>
       </c>
       <c r="S733" t="n">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="T733" t="inlineStr">
         <is>
@@ -78541,7 +78541,7 @@
         <v>46213.36370773148</v>
       </c>
       <c r="S734" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T734" t="inlineStr">
         <is>
@@ -78656,7 +78656,7 @@
         <v>46204.04179737269</v>
       </c>
       <c r="S735" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T735" t="inlineStr">
         <is>
@@ -78767,7 +78767,7 @@
         <v>46057.40119486111</v>
       </c>
       <c r="S736" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T736" t="inlineStr">
         <is>
@@ -78874,7 +78874,7 @@
         <v>46204.04187399305</v>
       </c>
       <c r="S737" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T737" t="inlineStr">
         <is>
@@ -78981,7 +78981,7 @@
         <v>46204.04188738426</v>
       </c>
       <c r="S738" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T738" t="inlineStr">
         <is>
@@ -79088,7 +79088,7 @@
         <v>46210.80007584491</v>
       </c>
       <c r="S739" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T739" t="inlineStr">
         <is>
@@ -79191,7 +79191,7 @@
         <v>46204.16684155093</v>
       </c>
       <c r="S740" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T740" t="inlineStr">
         <is>
@@ -79302,7 +79302,7 @@
         <v>46023.15052158565</v>
       </c>
       <c r="S741" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T741" t="inlineStr">
         <is>
@@ -79409,7 +79409,7 @@
         <v>46204.12510590278</v>
       </c>
       <c r="S742" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T742" t="inlineStr">
         <is>
@@ -79520,7 +79520,7 @@
         <v>46204.37521674769</v>
       </c>
       <c r="S743" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T743" t="inlineStr">
         <is>
@@ -79631,7 +79631,7 @@
         <v>46057.39078310185</v>
       </c>
       <c r="S744" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T744" t="inlineStr">
         <is>
@@ -79738,7 +79738,7 @@
         <v>46204.29183217593</v>
       </c>
       <c r="S745" t="n">
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="T745" t="inlineStr">
         <is>
@@ -79849,7 +79849,7 @@
         <v>46204.33341168981</v>
       </c>
       <c r="S746" t="n">
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="T746" t="inlineStr">
         <is>
@@ -79960,7 +79960,7 @@
         <v>46204.25011258102</v>
       </c>
       <c r="S747" t="n">
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="T747" t="inlineStr">
         <is>
@@ -80071,7 +80071,7 @@
         <v>46204.37522271991</v>
       </c>
       <c r="S748" t="n">
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="T748" t="inlineStr">
         <is>
@@ -80182,7 +80182,7 @@
         <v>46204.25009074074</v>
       </c>
       <c r="S749" t="n">
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="T749" t="inlineStr">
         <is>
@@ -80293,7 +80293,7 @@
         <v>46204.37521859954</v>
       </c>
       <c r="S750" t="n">
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="T750" t="inlineStr">
         <is>
@@ -80404,7 +80404,7 @@
         <v>46204.41730355324</v>
       </c>
       <c r="S751" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T751" t="inlineStr">
         <is>
@@ -80515,7 +80515,7 @@
         <v>46023.15053034722</v>
       </c>
       <c r="S752" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T752" t="inlineStr">
         <is>
@@ -80622,7 +80622,7 @@
         <v>46204.41680613426</v>
       </c>
       <c r="S753" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T753" t="inlineStr">
         <is>
@@ -80733,7 +80733,7 @@
         <v>46204.41687068287</v>
       </c>
       <c r="S754" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T754" t="inlineStr">
         <is>
@@ -80844,7 +80844,7 @@
         <v>46204.41788634259</v>
       </c>
       <c r="S755" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T755" t="inlineStr">
         <is>
@@ -80955,7 +80955,7 @@
         <v>46057.3907997338</v>
       </c>
       <c r="S756" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T756" t="inlineStr">
         <is>
@@ -81058,7 +81058,7 @@
         <v>46192.56685792824</v>
       </c>
       <c r="S757" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T757" t="inlineStr">
         <is>
@@ -81157,7 +81157,7 @@
         <v>46192.56339828703</v>
       </c>
       <c r="S758" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T758" t="inlineStr">
         <is>
@@ -81260,7 +81260,7 @@
         <v>46204.41730447917</v>
       </c>
       <c r="S759" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T759" t="inlineStr">
         <is>
@@ -81371,7 +81371,7 @@
         <v>46204.41751620371</v>
       </c>
       <c r="S760" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T760" t="inlineStr">
         <is>
@@ -81482,7 +81482,7 @@
         <v>46204.41687126157</v>
       </c>
       <c r="S761" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T761" t="inlineStr">
         <is>
@@ -81593,7 +81593,7 @@
         <v>46204.41788753472</v>
       </c>
       <c r="S762" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T762" t="inlineStr">
         <is>
@@ -81704,7 +81704,7 @@
         <v>46204.41788796296</v>
       </c>
       <c r="S763" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T763" t="inlineStr">
         <is>
@@ -81811,7 +81811,7 @@
         <v>46168.72822039352</v>
       </c>
       <c r="S764" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T764" t="inlineStr">
         <is>
@@ -81910,7 +81910,7 @@
         <v>46192.56687770833</v>
       </c>
       <c r="S765" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T765" t="inlineStr">
         <is>
@@ -82009,7 +82009,7 @@
         <v>46192.56342578704</v>
       </c>
       <c r="S766" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T766" t="inlineStr">
         <is>
@@ -82112,7 +82112,7 @@
         <v>46213.75219915509</v>
       </c>
       <c r="S767" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T767" t="inlineStr">
         <is>
@@ -82219,7 +82219,7 @@
         <v>46213.75220699074</v>
       </c>
       <c r="S768" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T768" t="inlineStr">
         <is>
@@ -82326,7 +82326,7 @@
         <v>46213.75224594907</v>
       </c>
       <c r="S769" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T769" t="inlineStr">
         <is>
@@ -82433,7 +82433,7 @@
         <v>46213.75225217592</v>
       </c>
       <c r="S770" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T770" t="inlineStr">
         <is>
@@ -82540,7 +82540,7 @@
         <v>46213.75219873842</v>
       </c>
       <c r="S771" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T771" t="inlineStr">
         <is>
@@ -82647,7 +82647,7 @@
         <v>46213.75220643519</v>
       </c>
       <c r="S772" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T772" t="inlineStr">
         <is>
@@ -82754,7 +82754,7 @@
         <v>46213.75224560185</v>
       </c>
       <c r="S773" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T773" t="inlineStr">
         <is>
@@ -82861,7 +82861,7 @@
         <v>46213.75225246528</v>
       </c>
       <c r="S774" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T774" t="inlineStr">
         <is>
@@ -82968,7 +82968,7 @@
         <v>46174.04914510417</v>
       </c>
       <c r="S775" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="T775" t="inlineStr">
         <is>
@@ -83079,7 +83079,7 @@
         <v>46174.04916258102</v>
       </c>
       <c r="S776" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="T776" t="inlineStr">
         <is>
@@ -83190,7 +83190,7 @@
         <v>46174.04899652778</v>
       </c>
       <c r="S777" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="T777" t="inlineStr">
         <is>
@@ -83301,7 +83301,7 @@
         <v>46174.04886894676</v>
       </c>
       <c r="S778" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="T778" t="inlineStr">
         <is>
@@ -83412,7 +83412,7 @@
         <v>46174.04901342592</v>
       </c>
       <c r="S779" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="T779" t="inlineStr">
         <is>
@@ -83523,7 +83523,7 @@
         <v>46174.04899452546</v>
       </c>
       <c r="S780" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="T780" t="inlineStr">
         <is>
@@ -83634,7 +83634,7 @@
         <v>46174.04894753472</v>
       </c>
       <c r="S781" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="T781" t="inlineStr">
         <is>
@@ -83745,7 +83745,7 @@
         <v>46174.0003128125</v>
       </c>
       <c r="S782" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T782" t="inlineStr">
         <is>
@@ -83852,7 +83852,7 @@
         <v>46174.0003128125</v>
       </c>
       <c r="S783" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T783" t="inlineStr">
         <is>
@@ -83955,7 +83955,7 @@
         <v>46174.0003128125</v>
       </c>
       <c r="S784" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T784" t="inlineStr">
         <is>
@@ -84062,7 +84062,7 @@
         <v>46174.0003128125</v>
       </c>
       <c r="S785" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T785" t="inlineStr">
         <is>
@@ -84169,7 +84169,7 @@
         <v>46174.0003128125</v>
       </c>
       <c r="S786" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T786" t="inlineStr">
         <is>
@@ -84276,7 +84276,7 @@
         <v>46211.76825706018</v>
       </c>
       <c r="S787" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T787" t="inlineStr">
         <is>
@@ -84387,7 +84387,7 @@
         <v>46209.77926392361</v>
       </c>
       <c r="S788" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T788" t="inlineStr">
         <is>
@@ -84458,37 +84458,41 @@
         </is>
       </c>
       <c r="G789" t="n">
-        <v>9791</v>
+        <v>11613</v>
       </c>
       <c r="H789" t="n">
         <v>0</v>
       </c>
       <c r="I789" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="J789" t="inlineStr">
         <is>
-          <t>Aplicação de Modelo - Pendente - GOIAS</t>
+          <t>Envio de ATA de Implantação - CTB V - GOIAS</t>
         </is>
       </c>
       <c r="K789" t="inlineStr"/>
       <c r="L789" s="1" t="n">
-        <v>46206</v>
-      </c>
-      <c r="M789" t="inlineStr"/>
+        <v>46213</v>
+      </c>
+      <c r="M789" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
       <c r="N789" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O789" t="n">
-        <v>18189077</v>
+        <v>18189089</v>
       </c>
       <c r="P789" t="inlineStr">
         <is>
-          <t>Mauricio Lermen</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="Q789" t="inlineStr">
@@ -84498,7 +84502,7 @@
       </c>
       <c r="R789" t="inlineStr"/>
       <c r="S789" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="T789" t="inlineStr">
         <is>
@@ -84508,8 +84512,8 @@
       <c r="U789" t="inlineStr"/>
       <c r="V789" t="inlineStr">
         <is>
-          <t>Sem informações para a realização da tarefa  
-Empresa de implantação, sem docs ou procurações. - Data Comentário: 24/06/2026 15:43</t>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 17/07/2026 
+implantação não foi marcada ainda. - Data Comentário: 10/07/2026 17:02</t>
         </is>
       </c>
       <c r="W789" t="inlineStr"/>
@@ -84519,16 +84523,8 @@
       <c r="AA789" t="inlineStr"/>
       <c r="AB789" t="inlineStr"/>
       <c r="AC789" t="inlineStr"/>
-      <c r="AD789" t="inlineStr">
-        <is>
-          <t>Aguardando implantação do cliente para que seja possível a realização da tarefa - AI09 - Data Comentário: 06/07/2026 12:41</t>
-        </is>
-      </c>
-      <c r="AE789" t="inlineStr">
-        <is>
-          <t>10/07/2026</t>
-        </is>
-      </c>
+      <c r="AD789" t="inlineStr"/>
+      <c r="AE789" t="inlineStr"/>
       <c r="AF789" t="inlineStr">
         <is>
           <t>Tarefa</t>
@@ -84566,37 +84562,41 @@
         </is>
       </c>
       <c r="G790" t="n">
-        <v>9791</v>
+        <v>11613</v>
       </c>
       <c r="H790" t="n">
         <v>0</v>
       </c>
       <c r="I790" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="J790" t="inlineStr">
         <is>
-          <t>Aplicação de Modelo - Pendente - GOIAS</t>
+          <t>Envio de ATA de Implantação - CTB V - GOIAS</t>
         </is>
       </c>
       <c r="K790" t="inlineStr"/>
       <c r="L790" s="1" t="n">
-        <v>46206</v>
-      </c>
-      <c r="M790" t="inlineStr"/>
+        <v>46213</v>
+      </c>
+      <c r="M790" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
       <c r="N790" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O790" t="n">
-        <v>18189076</v>
+        <v>18189088</v>
       </c>
       <c r="P790" t="inlineStr">
         <is>
-          <t>Mauricio Lermen</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="Q790" t="inlineStr">
@@ -84606,7 +84606,7 @@
       </c>
       <c r="R790" t="inlineStr"/>
       <c r="S790" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="T790" t="inlineStr">
         <is>
@@ -84616,8 +84616,8 @@
       <c r="U790" t="inlineStr"/>
       <c r="V790" t="inlineStr">
         <is>
-          <t>Sem informações para a realização da tarefa  
-Empresa de implantação, sem docs ou procurações. - Data Comentário: 24/06/2026 15:43</t>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 17/07/2026 
+implantação não foi marcada ainda. - Data Comentário: 10/07/2026 17:02</t>
         </is>
       </c>
       <c r="W790" t="inlineStr"/>
@@ -84627,16 +84627,8 @@
       <c r="AA790" t="inlineStr"/>
       <c r="AB790" t="inlineStr"/>
       <c r="AC790" t="inlineStr"/>
-      <c r="AD790" t="inlineStr">
-        <is>
-          <t>Aguardando implantação do cliente para que seja possível a realização da tarefa - AI09 - Data Comentário: 06/07/2026 12:41</t>
-        </is>
-      </c>
-      <c r="AE790" t="inlineStr">
-        <is>
-          <t>10/07/2026</t>
-        </is>
-      </c>
+      <c r="AD790" t="inlineStr"/>
+      <c r="AE790" t="inlineStr"/>
       <c r="AF790" t="inlineStr">
         <is>
           <t>Tarefa</t>
@@ -84674,37 +84666,41 @@
         </is>
       </c>
       <c r="G791" t="n">
-        <v>9791</v>
+        <v>11613</v>
       </c>
       <c r="H791" t="n">
         <v>0</v>
       </c>
       <c r="I791" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="J791" t="inlineStr">
         <is>
-          <t>Aplicação de Modelo - Pendente - SP</t>
+          <t>Envio de ATA de Implantação - CTB V - SP</t>
         </is>
       </c>
       <c r="K791" t="inlineStr"/>
       <c r="L791" s="1" t="n">
-        <v>46205</v>
-      </c>
-      <c r="M791" t="inlineStr"/>
+        <v>46213</v>
+      </c>
+      <c r="M791" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
       <c r="N791" t="inlineStr">
         <is>
           <t>07/2026</t>
         </is>
       </c>
       <c r="O791" t="n">
-        <v>18195067</v>
+        <v>18195072</v>
       </c>
       <c r="P791" t="inlineStr">
         <is>
-          <t>Mauricio Lermen</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="Q791" t="inlineStr">
@@ -84714,7 +84710,7 @@
       </c>
       <c r="R791" t="inlineStr"/>
       <c r="S791" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="T791" t="inlineStr">
         <is>
@@ -84724,8 +84720,8 @@
       <c r="U791" t="inlineStr"/>
       <c r="V791" t="inlineStr">
         <is>
-          <t>Sem informações para a realização da tarefa  
-Empresa de implantação sem procuração ou documentos - Data Comentário: 01/07/2026 17:48</t>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 17/07/2026 
+implantação não foi marcada ainda. - Data Comentário: 10/07/2026 17:02</t>
         </is>
       </c>
       <c r="W791" t="inlineStr"/>
@@ -84735,16 +84731,8 @@
       <c r="AA791" t="inlineStr"/>
       <c r="AB791" t="inlineStr"/>
       <c r="AC791" t="inlineStr"/>
-      <c r="AD791" t="inlineStr">
-        <is>
-          <t>Aguardando implantação do cliente para que seja possível a realização da tarefa - AI09 - Data Comentário: 06/07/2026 12:41</t>
-        </is>
-      </c>
-      <c r="AE791" t="inlineStr">
-        <is>
-          <t>10/07/2026</t>
-        </is>
-      </c>
+      <c r="AD791" t="inlineStr"/>
+      <c r="AE791" t="inlineStr"/>
       <c r="AF791" t="inlineStr">
         <is>
           <t>Tarefa</t>
@@ -84754,11 +84742,11 @@
     </row>
     <row r="792">
       <c r="A792" t="n">
-        <v>6627</v>
+        <v>6966</v>
       </c>
       <c r="B792" t="inlineStr">
         <is>
-          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
+          <t>HELBRAZ COMERCIO DE PAPELARIA LTDA</t>
         </is>
       </c>
       <c r="C792" t="inlineStr">
@@ -84768,55 +84756,51 @@
       </c>
       <c r="D792" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E792" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F792" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Reynaldo Santos</t>
         </is>
       </c>
       <c r="G792" t="n">
-        <v>7026</v>
+        <v>9791</v>
       </c>
       <c r="H792" t="n">
         <v>0</v>
       </c>
       <c r="I792" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="J792" t="inlineStr">
         <is>
-          <t>Movimento - Sistema de Análise</t>
+          <t>Aplicação de Modelo - Pendente - GOIAS</t>
         </is>
       </c>
       <c r="K792" t="inlineStr"/>
       <c r="L792" s="1" t="n">
-        <v>46167</v>
-      </c>
-      <c r="M792" t="inlineStr">
-        <is>
-          <t>17/07/2026</t>
-        </is>
-      </c>
+        <v>46206</v>
+      </c>
+      <c r="M792" t="inlineStr"/>
       <c r="N792" t="inlineStr">
         <is>
-          <t>04/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
       <c r="O792" t="n">
-        <v>18048469</v>
+        <v>18189077</v>
       </c>
       <c r="P792" t="inlineStr">
         <is>
-          <t>Denis Reis</t>
+          <t>Mauricio Lermen</t>
         </is>
       </c>
       <c r="Q792" t="inlineStr">
@@ -84826,21 +84810,18 @@
       </c>
       <c r="R792" t="inlineStr"/>
       <c r="S792" t="n">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="T792" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
-        </is>
-      </c>
-      <c r="U792" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>HELBRAZ</t>
+        </is>
+      </c>
+      <c r="U792" t="inlineStr"/>
       <c r="V792" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 17/07/2026 - Data Comentário: 07/07/2026 18:12</t>
+          <t>Sem informações para a realização da tarefa  
+Empresa de implantação, sem docs ou procurações. - Data Comentário: 24/06/2026 15:43</t>
         </is>
       </c>
       <c r="W792" t="inlineStr"/>
@@ -84852,7 +84833,7 @@
       <c r="AC792" t="inlineStr"/>
       <c r="AD792" t="inlineStr">
         <is>
-          <t>A operação e o GC estão ajustando os créditos de meses anteriores para que o valor desse mês seja ajustado. A Gerente Priscila Volpe está em contato direto com o GC e informou que a tarefa deve ser concluída até o fim desta semana. - Data Comentário: 06/07/2026 12:41</t>
+          <t>Aguardando implantação do cliente para que seja possível a realização da tarefa - AI09 - Data Comentário: 06/07/2026 12:41</t>
         </is>
       </c>
       <c r="AE792" t="inlineStr">
@@ -84865,19 +84846,15 @@
           <t>Tarefa</t>
         </is>
       </c>
-      <c r="AG792" t="inlineStr">
-        <is>
-          <t>Nayara Oliveira</t>
-        </is>
-      </c>
+      <c r="AG792" t="inlineStr"/>
     </row>
     <row r="793">
       <c r="A793" t="n">
-        <v>6224</v>
+        <v>6967</v>
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>JL DISTRIBUIDORA DE PAPELARIA LTDA</t>
         </is>
       </c>
       <c r="C793" t="inlineStr">
@@ -84887,7 +84864,7 @@
       </c>
       <c r="D793" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E793" t="inlineStr">
@@ -84897,41 +84874,41 @@
       </c>
       <c r="F793" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Reynaldo Santos</t>
         </is>
       </c>
       <c r="G793" t="n">
-        <v>1802</v>
+        <v>9791</v>
       </c>
       <c r="H793" t="n">
         <v>0</v>
       </c>
       <c r="I793" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="J793" t="inlineStr">
         <is>
-          <t>Est - ICMS RPA - CÓD. 046-2</t>
+          <t>Aplicação de Modelo - Pendente - GOIAS</t>
         </is>
       </c>
       <c r="K793" t="inlineStr"/>
       <c r="L793" s="1" t="n">
-        <v>46182</v>
+        <v>46206</v>
       </c>
       <c r="M793" t="inlineStr"/>
       <c r="N793" t="inlineStr">
         <is>
-          <t>05/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
       <c r="O793" t="n">
-        <v>17688680</v>
+        <v>18189076</v>
       </c>
       <c r="P793" t="inlineStr">
         <is>
-          <t>Cristina Leite</t>
+          <t>Mauricio Lermen</t>
         </is>
       </c>
       <c r="Q793" t="inlineStr">
@@ -84941,21 +84918,18 @@
       </c>
       <c r="R793" t="inlineStr"/>
       <c r="S793" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="T793" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
-        </is>
-      </c>
-      <c r="U793" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>HELBRAZ</t>
+        </is>
+      </c>
+      <c r="U793" t="inlineStr"/>
       <c r="V793" t="inlineStr">
         <is>
-          <t>Atraso do Cliente, cobrança ativa, GC e GM ciente do atraso - Data Comentário: 25/06/2026 16:00</t>
+          <t>Sem informações para a realização da tarefa  
+Empresa de implantação, sem docs ou procurações. - Data Comentário: 24/06/2026 15:43</t>
         </is>
       </c>
       <c r="W793" t="inlineStr"/>
@@ -84967,32 +84941,28 @@
       <c r="AC793" t="inlineStr"/>
       <c r="AD793" t="inlineStr">
         <is>
-          <t>Atraso do cliente, o atraso do cliente já é recorrente e de ciência do Master e do Gerente de Contas. - Data Comentário: 10/07/2026 10:23</t>
+          <t>Aguardando implantação do cliente para que seja possível a realização da tarefa - AI09 - Data Comentário: 06/07/2026 12:41</t>
         </is>
       </c>
       <c r="AE793" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
       <c r="AF793" t="inlineStr">
         <is>
-          <t>Imposto</t>
-        </is>
-      </c>
-      <c r="AG793" t="inlineStr">
-        <is>
-          <t>Ricardo Fischer</t>
-        </is>
-      </c>
+          <t>Tarefa</t>
+        </is>
+      </c>
+      <c r="AG793" t="inlineStr"/>
     </row>
     <row r="794">
       <c r="A794" t="n">
-        <v>6224</v>
+        <v>6981</v>
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t xml:space="preserve">LUIZ GOMES DA SILVA - O GOIANO </t>
         </is>
       </c>
       <c r="C794" t="inlineStr">
@@ -85012,41 +84982,41 @@
       </c>
       <c r="F794" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Reynaldo Santos</t>
         </is>
       </c>
       <c r="G794" t="n">
-        <v>1808</v>
+        <v>9791</v>
       </c>
       <c r="H794" t="n">
         <v>0</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="J794" t="inlineStr">
         <is>
-          <t>Fed - PIS/COFINS Não Cumul/Mon - 5856</t>
+          <t>Aplicação de Modelo - Pendente - SP</t>
         </is>
       </c>
       <c r="K794" t="inlineStr"/>
       <c r="L794" s="1" t="n">
-        <v>46195</v>
+        <v>46205</v>
       </c>
       <c r="M794" t="inlineStr"/>
       <c r="N794" t="inlineStr">
         <is>
-          <t>05/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
       <c r="O794" t="n">
-        <v>17688690</v>
+        <v>18195067</v>
       </c>
       <c r="P794" t="inlineStr">
         <is>
-          <t>Cristina Leite</t>
+          <t>Mauricio Lermen</t>
         </is>
       </c>
       <c r="Q794" t="inlineStr">
@@ -85056,21 +85026,18 @@
       </c>
       <c r="R794" t="inlineStr"/>
       <c r="S794" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="T794" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
-        </is>
-      </c>
-      <c r="U794" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>SUPERMERCADO AVENIDA</t>
+        </is>
+      </c>
+      <c r="U794" t="inlineStr"/>
       <c r="V794" t="inlineStr">
         <is>
-          <t>Atraso de envio do cliente, consultar pendências no check list - Data Comentário: 23/06/2026 15:41</t>
+          <t>Sem informações para a realização da tarefa  
+Empresa de implantação sem procuração ou documentos - Data Comentário: 01/07/2026 17:48</t>
         </is>
       </c>
       <c r="W794" t="inlineStr"/>
@@ -85082,7 +85049,7 @@
       <c r="AC794" t="inlineStr"/>
       <c r="AD794" t="inlineStr">
         <is>
-          <t>Atraso do cliente, o atraso do cliente já é recorrente e de ciência do Master e do Gerente de Contas. - Data Comentário: 10/07/2026 10:23</t>
+          <t>Aguardando implantação do cliente para que seja possível a realização da tarefa - AI09 - Data Comentário: 06/07/2026 12:41</t>
         </is>
       </c>
       <c r="AE794" t="inlineStr">
@@ -85092,22 +85059,18 @@
       </c>
       <c r="AF794" t="inlineStr">
         <is>
-          <t>Imposto</t>
-        </is>
-      </c>
-      <c r="AG794" t="inlineStr">
-        <is>
-          <t>Ricardo Fischer</t>
-        </is>
-      </c>
+          <t>Tarefa</t>
+        </is>
+      </c>
+      <c r="AG794" t="inlineStr"/>
     </row>
     <row r="795">
       <c r="A795" t="n">
-        <v>6224</v>
+        <v>6966</v>
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>HELBRAZ COMERCIO DE PAPELARIA LTDA</t>
         </is>
       </c>
       <c r="C795" t="inlineStr">
@@ -85117,7 +85080,7 @@
       </c>
       <c r="D795" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E795" t="inlineStr">
@@ -85127,45 +85090,45 @@
       </c>
       <c r="F795" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Reynaldo Santos</t>
         </is>
       </c>
       <c r="G795" t="n">
-        <v>7877</v>
+        <v>11616</v>
       </c>
       <c r="H795" t="n">
         <v>0</v>
       </c>
       <c r="I795" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="J795" t="inlineStr">
         <is>
-          <t>Movimento - Analise de Balanço Lucro Real</t>
+          <t>Envio de ATA de Implantação - DP - GOIAS</t>
         </is>
       </c>
       <c r="K795" t="inlineStr"/>
       <c r="L795" s="1" t="n">
-        <v>46171</v>
+        <v>46213</v>
       </c>
       <c r="M795" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="N795" t="inlineStr">
         <is>
-          <t>04/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
       <c r="O795" t="n">
-        <v>18076566</v>
+        <v>18189085</v>
       </c>
       <c r="P795" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Mauricio Lermen</t>
         </is>
       </c>
       <c r="Q795" t="inlineStr">
@@ -85175,22 +85138,18 @@
       </c>
       <c r="R795" t="inlineStr"/>
       <c r="S795" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="T795" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
-        </is>
-      </c>
-      <c r="U795" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>HELBRAZ</t>
+        </is>
+      </c>
+      <c r="U795" t="inlineStr"/>
       <c r="V795" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 03/07/2026 
-Devido as ocorrências com Cbenef e atendimetnos a cliente precisamos reprogramar conclusão para 03/07/2026 - Data Comentário: 03/07/2026 08:15</t>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 30/06/2026 
+CLIENTE COM VIGÊNCIA A PARTIR DE 08/2026, IMPLANTAÇÃO NÃO AGENDADA. - Data Comentário: 19/06/2026 17:53</t>
         </is>
       </c>
       <c r="W795" t="inlineStr"/>
@@ -85200,16 +85159,8 @@
       <c r="AA795" t="inlineStr"/>
       <c r="AB795" t="inlineStr"/>
       <c r="AC795" t="inlineStr"/>
-      <c r="AD795" t="inlineStr">
-        <is>
-          <t>Os GC's estão respondendo as importações do Contábil conforme vão sendo realizadas, o GD Sérgio informou que a previsão é concluir na próxima semana - Data Comentário: 06/07/2026 12:42</t>
-        </is>
-      </c>
-      <c r="AE795" t="inlineStr">
-        <is>
-          <t>13/07/2026</t>
-        </is>
-      </c>
+      <c r="AD795" t="inlineStr"/>
+      <c r="AE795" t="inlineStr"/>
       <c r="AF795" t="inlineStr">
         <is>
           <t>Tarefa</t>
@@ -85219,11 +85170,11 @@
     </row>
     <row r="796">
       <c r="A796" t="n">
-        <v>6966</v>
+        <v>6967</v>
       </c>
       <c r="B796" t="inlineStr">
         <is>
-          <t>HELBRAZ COMERCIO DE PAPELARIA LTDA</t>
+          <t>JL DISTRIBUIDORA DE PAPELARIA LTDA</t>
         </is>
       </c>
       <c r="C796" t="inlineStr">
@@ -85247,19 +85198,19 @@
         </is>
       </c>
       <c r="G796" t="n">
-        <v>11613</v>
+        <v>11616</v>
       </c>
       <c r="H796" t="n">
         <v>0</v>
       </c>
       <c r="I796" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="J796" t="inlineStr">
         <is>
-          <t>Envio de ATA de Implantação - CTB V - GOIAS</t>
+          <t>Envio de ATA de Implantação - DP - GOIAS</t>
         </is>
       </c>
       <c r="K796" t="inlineStr"/>
@@ -85268,7 +85219,7 @@
       </c>
       <c r="M796" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="N796" t="inlineStr">
@@ -85277,21 +85228,21 @@
         </is>
       </c>
       <c r="O796" t="n">
-        <v>18189089</v>
+        <v>18189084</v>
       </c>
       <c r="P796" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Mauricio Lermen</t>
         </is>
       </c>
       <c r="Q796" t="inlineStr">
         <is>
-          <t>Em Aberto</t>
+          <t>Em Atraso</t>
         </is>
       </c>
       <c r="R796" t="inlineStr"/>
       <c r="S796" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T796" t="inlineStr">
         <is>
@@ -85301,8 +85252,8 @@
       <c r="U796" t="inlineStr"/>
       <c r="V796" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 17/07/2026 
-implantação não foi marcada ainda. - Data Comentário: 10/07/2026 17:02</t>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 30/06/2026 
+CLIENTE COM VIGÊNCIA A PARTIR DE 08/2026, IMPLANTAÇÃO NÃO AGENDADA. - Data Comentário: 19/06/2026 17:53</t>
         </is>
       </c>
       <c r="W796" t="inlineStr"/>
@@ -85323,11 +85274,11 @@
     </row>
     <row r="797">
       <c r="A797" t="n">
-        <v>6967</v>
+        <v>6981</v>
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>JL DISTRIBUIDORA DE PAPELARIA LTDA</t>
+          <t xml:space="preserve">LUIZ GOMES DA SILVA - O GOIANO </t>
         </is>
       </c>
       <c r="C797" t="inlineStr">
@@ -85337,7 +85288,7 @@
       </c>
       <c r="D797" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E797" t="inlineStr">
@@ -85351,19 +85302,19 @@
         </is>
       </c>
       <c r="G797" t="n">
-        <v>11613</v>
+        <v>11616</v>
       </c>
       <c r="H797" t="n">
         <v>0</v>
       </c>
       <c r="I797" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="J797" t="inlineStr">
         <is>
-          <t>Envio de ATA de Implantação - CTB V - GOIAS</t>
+          <t>Envio de ATA de Implantação - DP - SP</t>
         </is>
       </c>
       <c r="K797" t="inlineStr"/>
@@ -85372,41 +85323,41 @@
       </c>
       <c r="M797" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="N797" t="inlineStr">
         <is>
-          <t>06/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
       <c r="O797" t="n">
-        <v>18189088</v>
+        <v>18195071</v>
       </c>
       <c r="P797" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Mauricio Lermen</t>
         </is>
       </c>
       <c r="Q797" t="inlineStr">
         <is>
-          <t>Em Aberto</t>
+          <t>Em Atraso</t>
         </is>
       </c>
       <c r="R797" t="inlineStr"/>
       <c r="S797" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T797" t="inlineStr">
         <is>
-          <t>HELBRAZ</t>
+          <t>SUPERMERCADO AVENIDA</t>
         </is>
       </c>
       <c r="U797" t="inlineStr"/>
       <c r="V797" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 17/07/2026 
-implantação não foi marcada ainda. - Data Comentário: 10/07/2026 17:02</t>
+          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 10/08/2026 
+Implantação ainda não realizada, empresas de agosto - Data Comentário: 01/07/2026 17:50</t>
         </is>
       </c>
       <c r="W797" t="inlineStr"/>
@@ -85427,11 +85378,11 @@
     </row>
     <row r="798">
       <c r="A798" t="n">
-        <v>6981</v>
+        <v>6627</v>
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUIZ GOMES DA SILVA - O GOIANO </t>
+          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C798" t="inlineStr">
@@ -85446,33 +85397,33 @@
       </c>
       <c r="E798" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F798" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G798" t="n">
-        <v>11613</v>
+        <v>7026</v>
       </c>
       <c r="H798" t="n">
         <v>0</v>
       </c>
       <c r="I798" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J798" t="inlineStr">
         <is>
-          <t>Envio de ATA de Implantação - CTB V - SP</t>
+          <t>Movimento - Sistema de Análise</t>
         </is>
       </c>
       <c r="K798" t="inlineStr"/>
       <c r="L798" s="1" t="n">
-        <v>46213</v>
+        <v>46167</v>
       </c>
       <c r="M798" t="inlineStr">
         <is>
@@ -85481,36 +85432,39 @@
       </c>
       <c r="N798" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>04/2026</t>
         </is>
       </c>
       <c r="O798" t="n">
-        <v>18195072</v>
+        <v>18048469</v>
       </c>
       <c r="P798" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Denis Reis</t>
         </is>
       </c>
       <c r="Q798" t="inlineStr">
         <is>
-          <t>Em Aberto</t>
+          <t>Em Atraso</t>
         </is>
       </c>
       <c r="R798" t="inlineStr"/>
       <c r="S798" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="T798" t="inlineStr">
         <is>
-          <t>SUPERMERCADO AVENIDA</t>
-        </is>
-      </c>
-      <c r="U798" t="inlineStr"/>
+          <t xml:space="preserve">GTG </t>
+        </is>
+      </c>
+      <c r="U798" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V798" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 17/07/2026 
-implantação não foi marcada ainda. - Data Comentário: 10/07/2026 17:02</t>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 17/07/2026 - Data Comentário: 07/07/2026 18:12</t>
         </is>
       </c>
       <c r="W798" t="inlineStr"/>
@@ -85520,22 +85474,34 @@
       <c r="AA798" t="inlineStr"/>
       <c r="AB798" t="inlineStr"/>
       <c r="AC798" t="inlineStr"/>
-      <c r="AD798" t="inlineStr"/>
-      <c r="AE798" t="inlineStr"/>
+      <c r="AD798" t="inlineStr">
+        <is>
+          <t>A operação e o GC estão ajustando os créditos de meses anteriores para que o valor desse mês seja ajustado. A Gerente Priscila Volpe está em contato direto com o GC e informou que a tarefa deve ser concluída até o fim desta semana. - Data Comentário: 06/07/2026 12:41</t>
+        </is>
+      </c>
+      <c r="AE798" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
       <c r="AF798" t="inlineStr">
         <is>
           <t>Tarefa</t>
         </is>
       </c>
-      <c r="AG798" t="inlineStr"/>
+      <c r="AG798" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
     </row>
     <row r="799">
       <c r="A799" t="n">
-        <v>6966</v>
+        <v>6224</v>
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>HELBRAZ COMERCIO DE PAPELARIA LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C799" t="inlineStr">
@@ -85545,7 +85511,7 @@
       </c>
       <c r="D799" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E799" t="inlineStr">
@@ -85555,66 +85521,65 @@
       </c>
       <c r="F799" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G799" t="n">
-        <v>11616</v>
+        <v>1802</v>
       </c>
       <c r="H799" t="n">
         <v>0</v>
       </c>
       <c r="I799" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J799" t="inlineStr">
         <is>
-          <t>Envio de ATA de Implantação - DP - GOIAS</t>
+          <t>Est - ICMS RPA - CÓD. 046-2</t>
         </is>
       </c>
       <c r="K799" t="inlineStr"/>
       <c r="L799" s="1" t="n">
-        <v>46213</v>
-      </c>
-      <c r="M799" t="inlineStr">
-        <is>
-          <t>30/06/2026</t>
-        </is>
-      </c>
+        <v>46182</v>
+      </c>
+      <c r="M799" t="inlineStr"/>
       <c r="N799" t="inlineStr">
         <is>
-          <t>06/2026</t>
+          <t>05/2026</t>
         </is>
       </c>
       <c r="O799" t="n">
-        <v>18189085</v>
+        <v>17688680</v>
       </c>
       <c r="P799" t="inlineStr">
         <is>
-          <t>Mauricio Lermen</t>
+          <t>Cristina Leite</t>
         </is>
       </c>
       <c r="Q799" t="inlineStr">
         <is>
-          <t>Em Aberto</t>
+          <t>Em Atraso</t>
         </is>
       </c>
       <c r="R799" t="inlineStr"/>
       <c r="S799" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="T799" t="inlineStr">
         <is>
-          <t>HELBRAZ</t>
-        </is>
-      </c>
-      <c r="U799" t="inlineStr"/>
+          <t>SUPER MAIS DO GOIÁS</t>
+        </is>
+      </c>
+      <c r="U799" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V799" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 30/06/2026 
-CLIENTE COM VIGÊNCIA A PARTIR DE 08/2026, IMPLANTAÇÃO NÃO AGENDADA. - Data Comentário: 19/06/2026 17:53</t>
+          <t>Atraso do Cliente, cobrança ativa, GC e GM ciente do atraso - Data Comentário: 25/06/2026 16:00</t>
         </is>
       </c>
       <c r="W799" t="inlineStr"/>
@@ -85624,22 +85589,34 @@
       <c r="AA799" t="inlineStr"/>
       <c r="AB799" t="inlineStr"/>
       <c r="AC799" t="inlineStr"/>
-      <c r="AD799" t="inlineStr"/>
-      <c r="AE799" t="inlineStr"/>
+      <c r="AD799" t="inlineStr">
+        <is>
+          <t>Atraso do cliente, o atraso do cliente já é recorrente e de ciência do Master e do Gerente de Contas. - Data Comentário: 10/07/2026 10:23</t>
+        </is>
+      </c>
+      <c r="AE799" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
       <c r="AF799" t="inlineStr">
         <is>
-          <t>Tarefa</t>
-        </is>
-      </c>
-      <c r="AG799" t="inlineStr"/>
+          <t>Imposto</t>
+        </is>
+      </c>
+      <c r="AG799" t="inlineStr">
+        <is>
+          <t>Ricardo Fischer</t>
+        </is>
+      </c>
     </row>
     <row r="800">
       <c r="A800" t="n">
-        <v>6967</v>
+        <v>6224</v>
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>JL DISTRIBUIDORA DE PAPELARIA LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C800" t="inlineStr">
@@ -85649,7 +85626,7 @@
       </c>
       <c r="D800" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E800" t="inlineStr">
@@ -85659,66 +85636,65 @@
       </c>
       <c r="F800" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G800" t="n">
-        <v>11616</v>
+        <v>1808</v>
       </c>
       <c r="H800" t="n">
         <v>0</v>
       </c>
       <c r="I800" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J800" t="inlineStr">
         <is>
-          <t>Envio de ATA de Implantação - DP - GOIAS</t>
+          <t>Fed - PIS/COFINS Não Cumul/Mon - 5856</t>
         </is>
       </c>
       <c r="K800" t="inlineStr"/>
       <c r="L800" s="1" t="n">
-        <v>46213</v>
-      </c>
-      <c r="M800" t="inlineStr">
-        <is>
-          <t>30/06/2026</t>
-        </is>
-      </c>
+        <v>46195</v>
+      </c>
+      <c r="M800" t="inlineStr"/>
       <c r="N800" t="inlineStr">
         <is>
-          <t>06/2026</t>
+          <t>05/2026</t>
         </is>
       </c>
       <c r="O800" t="n">
-        <v>18189084</v>
+        <v>17688690</v>
       </c>
       <c r="P800" t="inlineStr">
         <is>
-          <t>Mauricio Lermen</t>
+          <t>Cristina Leite</t>
         </is>
       </c>
       <c r="Q800" t="inlineStr">
         <is>
-          <t>Em Aberto</t>
+          <t>Em Atraso</t>
         </is>
       </c>
       <c r="R800" t="inlineStr"/>
       <c r="S800" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="T800" t="inlineStr">
         <is>
-          <t>HELBRAZ</t>
-        </is>
-      </c>
-      <c r="U800" t="inlineStr"/>
+          <t>SUPER MAIS DO GOIÁS</t>
+        </is>
+      </c>
+      <c r="U800" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V800" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 30/06/2026 
-CLIENTE COM VIGÊNCIA A PARTIR DE 08/2026, IMPLANTAÇÃO NÃO AGENDADA. - Data Comentário: 19/06/2026 17:53</t>
+          <t>Atraso de envio do cliente, consultar pendências no check list - Data Comentário: 23/06/2026 15:41</t>
         </is>
       </c>
       <c r="W800" t="inlineStr"/>
@@ -85728,22 +85704,34 @@
       <c r="AA800" t="inlineStr"/>
       <c r="AB800" t="inlineStr"/>
       <c r="AC800" t="inlineStr"/>
-      <c r="AD800" t="inlineStr"/>
-      <c r="AE800" t="inlineStr"/>
+      <c r="AD800" t="inlineStr">
+        <is>
+          <t>Atraso do cliente, o atraso do cliente já é recorrente e de ciência do Master e do Gerente de Contas. - Data Comentário: 10/07/2026 10:23</t>
+        </is>
+      </c>
+      <c r="AE800" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
       <c r="AF800" t="inlineStr">
         <is>
-          <t>Tarefa</t>
-        </is>
-      </c>
-      <c r="AG800" t="inlineStr"/>
+          <t>Imposto</t>
+        </is>
+      </c>
+      <c r="AG800" t="inlineStr">
+        <is>
+          <t>Ricardo Fischer</t>
+        </is>
+      </c>
     </row>
     <row r="801">
       <c r="A801" t="n">
-        <v>6981</v>
+        <v>6966</v>
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUIZ GOMES DA SILVA - O GOIANO </t>
+          <t>HELBRAZ COMERCIO DE PAPELARIA LTDA</t>
         </is>
       </c>
       <c r="C801" t="inlineStr">
@@ -85753,7 +85741,7 @@
       </c>
       <c r="D801" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E801" t="inlineStr">
@@ -85767,62 +85755,57 @@
         </is>
       </c>
       <c r="G801" t="n">
-        <v>11616</v>
+        <v>11618</v>
       </c>
       <c r="H801" t="n">
         <v>0</v>
       </c>
       <c r="I801" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J801" t="inlineStr">
         <is>
-          <t>Envio de ATA de Implantação - DP - SP</t>
+          <t>Envio de ATA de Implantação - EF V - GOIAS</t>
         </is>
       </c>
       <c r="K801" t="inlineStr"/>
       <c r="L801" s="1" t="n">
         <v>46213</v>
       </c>
-      <c r="M801" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
-        </is>
-      </c>
+      <c r="M801" t="inlineStr"/>
       <c r="N801" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
       <c r="O801" t="n">
-        <v>18195071</v>
+        <v>18189093</v>
       </c>
       <c r="P801" t="inlineStr">
         <is>
-          <t>Mauricio Lermen</t>
+          <t>Claudineia Rodrigues</t>
         </is>
       </c>
       <c r="Q801" t="inlineStr">
         <is>
-          <t>Em Aberto</t>
+          <t>Em Atraso</t>
         </is>
       </c>
       <c r="R801" t="inlineStr"/>
       <c r="S801" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T801" t="inlineStr">
         <is>
-          <t>SUPERMERCADO AVENIDA</t>
+          <t>HELBRAZ</t>
         </is>
       </c>
       <c r="U801" t="inlineStr"/>
       <c r="V801" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 10/08/2026 
-Implantação ainda não realizada, empresas de agosto - Data Comentário: 01/07/2026 17:50</t>
+          <t>Rotina Para Criar Tarefas Dos Clientes Novos - CodCliente: 6966; Tarefa Incluida: 11618; Vencimento: 19/06/2026 00:00:00; UsuarioResponsavel: Claudineia - Data Comentário: 19/06/2026 17:06</t>
         </is>
       </c>
       <c r="W801" t="inlineStr"/>
@@ -85839,15 +85822,19 @@
           <t>Tarefa</t>
         </is>
       </c>
-      <c r="AG801" t="inlineStr"/>
+      <c r="AG801" t="inlineStr">
+        <is>
+          <t>Claudineia Rodrigues</t>
+        </is>
+      </c>
     </row>
     <row r="802">
       <c r="A802" t="n">
-        <v>6966</v>
+        <v>6967</v>
       </c>
       <c r="B802" t="inlineStr">
         <is>
-          <t>HELBRAZ COMERCIO DE PAPELARIA LTDA</t>
+          <t>JL DISTRIBUIDORA DE PAPELARIA LTDA</t>
         </is>
       </c>
       <c r="C802" t="inlineStr">
@@ -85897,7 +85884,7 @@
         </is>
       </c>
       <c r="O802" t="n">
-        <v>18189093</v>
+        <v>18189092</v>
       </c>
       <c r="P802" t="inlineStr">
         <is>
@@ -85906,12 +85893,12 @@
       </c>
       <c r="Q802" t="inlineStr">
         <is>
-          <t>Em Aberto</t>
+          <t>Em Atraso</t>
         </is>
       </c>
       <c r="R802" t="inlineStr"/>
       <c r="S802" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T802" t="inlineStr">
         <is>
@@ -85921,7 +85908,7 @@
       <c r="U802" t="inlineStr"/>
       <c r="V802" t="inlineStr">
         <is>
-          <t>Rotina Para Criar Tarefas Dos Clientes Novos - CodCliente: 6966; Tarefa Incluida: 11618; Vencimento: 19/06/2026 00:00:00; UsuarioResponsavel: Claudineia - Data Comentário: 19/06/2026 17:06</t>
+          <t>Rotina Para Criar Tarefas Dos Clientes Novos - CodCliente: 6967; Tarefa Incluida: 11618; Vencimento: 19/06/2026 00:00:00; UsuarioResponsavel: Claudineia - Data Comentário: 19/06/2026 17:06</t>
         </is>
       </c>
       <c r="W802" t="inlineStr"/>
@@ -85946,11 +85933,11 @@
     </row>
     <row r="803">
       <c r="A803" t="n">
-        <v>6967</v>
+        <v>6981</v>
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>JL DISTRIBUIDORA DE PAPELARIA LTDA</t>
+          <t xml:space="preserve">LUIZ GOMES DA SILVA - O GOIANO </t>
         </is>
       </c>
       <c r="C803" t="inlineStr">
@@ -85960,7 +85947,7 @@
       </c>
       <c r="D803" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E803" t="inlineStr">
@@ -85986,7 +85973,7 @@
       </c>
       <c r="J803" t="inlineStr">
         <is>
-          <t>Envio de ATA de Implantação - EF V - GOIAS</t>
+          <t>Envio de ATA de Implantação - EF V - SP</t>
         </is>
       </c>
       <c r="K803" t="inlineStr"/>
@@ -85996,11 +85983,11 @@
       <c r="M803" t="inlineStr"/>
       <c r="N803" t="inlineStr">
         <is>
-          <t>06/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
       <c r="O803" t="n">
-        <v>18189092</v>
+        <v>18195073</v>
       </c>
       <c r="P803" t="inlineStr">
         <is>
@@ -86009,22 +85996,22 @@
       </c>
       <c r="Q803" t="inlineStr">
         <is>
-          <t>Em Aberto</t>
+          <t>Em Atraso</t>
         </is>
       </c>
       <c r="R803" t="inlineStr"/>
       <c r="S803" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T803" t="inlineStr">
         <is>
-          <t>HELBRAZ</t>
+          <t>SUPERMERCADO AVENIDA</t>
         </is>
       </c>
       <c r="U803" t="inlineStr"/>
       <c r="V803" t="inlineStr">
         <is>
-          <t>Rotina Para Criar Tarefas Dos Clientes Novos - CodCliente: 6967; Tarefa Incluida: 11618; Vencimento: 19/06/2026 00:00:00; UsuarioResponsavel: Claudineia - Data Comentário: 19/06/2026 17:06</t>
+          <t>Rotina Para Criar Tarefas Dos Clientes Novos - CodCliente: 6981; Tarefa Incluida: 11618; Vencimento: 01/07/2026 00:00:00; UsuarioResponsavel: Claudineia - Data Comentário: 01/07/2026 09:04</t>
         </is>
       </c>
       <c r="W803" t="inlineStr"/>
@@ -86049,11 +86036,11 @@
     </row>
     <row r="804">
       <c r="A804" t="n">
-        <v>6981</v>
+        <v>6224</v>
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUIZ GOMES DA SILVA - O GOIANO </t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C804" t="inlineStr">
@@ -86073,61 +86060,70 @@
       </c>
       <c r="F804" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G804" t="n">
-        <v>11618</v>
+        <v>7877</v>
       </c>
       <c r="H804" t="n">
         <v>0</v>
       </c>
       <c r="I804" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="J804" t="inlineStr">
         <is>
-          <t>Envio de ATA de Implantação - EF V - SP</t>
+          <t>Movimento - Analise de Balanço Lucro Real</t>
         </is>
       </c>
       <c r="K804" t="inlineStr"/>
       <c r="L804" s="1" t="n">
-        <v>46213</v>
-      </c>
-      <c r="M804" t="inlineStr"/>
+        <v>46171</v>
+      </c>
+      <c r="M804" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
       <c r="N804" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>04/2026</t>
         </is>
       </c>
       <c r="O804" t="n">
-        <v>18195073</v>
+        <v>18076566</v>
       </c>
       <c r="P804" t="inlineStr">
         <is>
-          <t>Claudineia Rodrigues</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="Q804" t="inlineStr">
         <is>
-          <t>Em Aberto</t>
+          <t>Em Atraso</t>
         </is>
       </c>
       <c r="R804" t="inlineStr"/>
       <c r="S804" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="T804" t="inlineStr">
         <is>
-          <t>SUPERMERCADO AVENIDA</t>
-        </is>
-      </c>
-      <c r="U804" t="inlineStr"/>
+          <t>SUPER MAIS DO GOIÁS</t>
+        </is>
+      </c>
+      <c r="U804" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V804" t="inlineStr">
         <is>
-          <t>Rotina Para Criar Tarefas Dos Clientes Novos - CodCliente: 6981; Tarefa Incluida: 11618; Vencimento: 01/07/2026 00:00:00; UsuarioResponsavel: Claudineia - Data Comentário: 01/07/2026 09:04</t>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 03/07/2026 
+Devido as ocorrências com Cbenef e atendimetnos a cliente precisamos reprogramar conclusão para 03/07/2026 - Data Comentário: 03/07/2026 08:15</t>
         </is>
       </c>
       <c r="W804" t="inlineStr"/>
@@ -86137,18 +86133,22 @@
       <c r="AA804" t="inlineStr"/>
       <c r="AB804" t="inlineStr"/>
       <c r="AC804" t="inlineStr"/>
-      <c r="AD804" t="inlineStr"/>
-      <c r="AE804" t="inlineStr"/>
+      <c r="AD804" t="inlineStr">
+        <is>
+          <t>Os GC's estão respondendo as importações do Contábil conforme vão sendo realizadas, o GD Sérgio informou que a previsão é concluir na próxima semana - Data Comentário: 06/07/2026 12:42</t>
+        </is>
+      </c>
+      <c r="AE804" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
       <c r="AF804" t="inlineStr">
         <is>
           <t>Tarefa</t>
         </is>
       </c>
-      <c r="AG804" t="inlineStr">
-        <is>
-          <t>Claudineia Rodrigues</t>
-        </is>
-      </c>
+      <c r="AG804" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dados/base/goias.xlsx
+++ b/dados/base/goias.xlsx
@@ -657,7 +657,7 @@
       </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
       </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -899,11 +899,11 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>5617</v>
+        <v>6962</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -923,14 +923,14 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Reynaldo Santos</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>5905</v>
+        <v>11616</v>
       </c>
       <c r="H5" t="n">
-        <v>5784</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -939,12 +939,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Folha Mensal/Pró-Labore</t>
+          <t>Envio de ATA de Implantação - DP</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" s="1" t="n">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
@@ -953,11 +953,11 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>17407675</v>
+        <v>18186553</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tania Luz</t>
+          <t>Mauricio Lermen</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -967,21 +967,17 @@
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>PROMOTORAS GYN</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
         <is>
-          <t>8. Serviços Suspensos. - Data Comentário: 08/07/2026 10:25</t>
+          <t>Rotina Para Criar Tarefas Dos Clientes Novos - CodCliente: 6962; Tarefa Incluida: 11616; Vencimento: 17/06/2026 00:00:00; UsuarioResponsavel: mauricio - Data Comentário: 17/06/2026 11:09</t>
         </is>
       </c>
       <c r="W5" t="inlineStr"/>
@@ -997,22 +993,18 @@
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>Obrigação Acessória</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>Edivaldo Veiga</t>
-        </is>
-      </c>
+          <t>Tarefa</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>6224</v>
+        <v>6963</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>PROMOTORAS GYN LTDA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1032,14 +1024,14 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Reynaldo Santos</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>5905</v>
+        <v>11616</v>
       </c>
       <c r="H6" t="n">
-        <v>5784</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -1048,12 +1040,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Folha Mensal/Pró-Labore</t>
+          <t>Envio de ATA de Implantação - DP</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" s="1" t="n">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
@@ -1062,11 +1054,11 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>17688813</v>
+        <v>18186554</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tania Luz</t>
+          <t>Mauricio Lermen</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1076,21 +1068,17 @@
       </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>PROMOTORAS GYN</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
-          <t>8. Serviços Suspensos. - Data Comentário: 08/07/2026 10:25</t>
+          <t>Rotina Para Criar Tarefas Dos Clientes Novos - CodCliente: 6963; Tarefa Incluida: 11616; Vencimento: 17/06/2026 00:00:00; UsuarioResponsavel: mauricio - Data Comentário: 17/06/2026 11:09</t>
         </is>
       </c>
       <c r="W6" t="inlineStr"/>
@@ -1106,14 +1094,10 @@
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>Obrigação Acessória</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>Edivaldo Veiga</t>
-        </is>
-      </c>
+          <t>Tarefa</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1145,10 +1129,10 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>5853</v>
+        <v>9746</v>
       </c>
       <c r="H7" t="n">
-        <v>5784</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1157,12 +1141,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>FOPAG Impressão PDF</t>
+          <t>eSocial – Fechamento Mensal</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" s="1" t="n">
-        <v>46210</v>
+        <v>46213</v>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
@@ -1171,7 +1155,7 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>17407635</v>
+        <v>17407922</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1185,7 +1169,7 @@
       </c>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1199,7 +1183,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>8. Serviços Suspensos. - Data Comentário: 03/07/2026 08:40</t>
+          <t>8. Serviços Suspensos. - Data Comentário: 08/07/2026 10:25</t>
         </is>
       </c>
       <c r="W7" t="inlineStr"/>
@@ -1254,10 +1238,10 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>5853</v>
+        <v>9746</v>
       </c>
       <c r="H8" t="n">
-        <v>5784</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1266,12 +1250,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>FOPAG Impressão PDF</t>
+          <t>eSocial – Fechamento Mensal</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" s="1" t="n">
-        <v>46210</v>
+        <v>46213</v>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
@@ -1280,7 +1264,7 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>17688753</v>
+        <v>17689040</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -1294,7 +1278,7 @@
       </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1308,7 +1292,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>8. Serviços Suspensos. - Data Comentário: 03/07/2026 08:39</t>
+          <t>8. Serviços Suspensos. - Data Comentário: 08/07/2026 10:25</t>
         </is>
       </c>
       <c r="W8" t="inlineStr"/>
@@ -1335,11 +1319,11 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>5617</v>
+        <v>6945</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1349,12 +1333,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1363,10 +1347,10 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>5906</v>
+        <v>9746</v>
       </c>
       <c r="H9" t="n">
-        <v>5784</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1375,25 +1359,29 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Recibo de Pagamento</t>
+          <t>eSocial – Fechamento Mensal</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" s="1" t="n">
-        <v>46209</v>
-      </c>
-      <c r="M9" t="inlineStr"/>
+        <v>46213</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>17407685</v>
+        <v>18179152</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Tania Luz</t>
+          <t>Santos Karina</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1403,21 +1391,18 @@
       </c>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>BRASIL DISTRIBUIDORA</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>8. Serviços Suspensos. - Data Comentário: 03/07/2026 08:40</t>
+          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 13/07/2026 
+Empresa Implantação em processamento. - Data Comentário: 10/07/2026 17:01</t>
         </is>
       </c>
       <c r="W9" t="inlineStr"/>
@@ -1438,17 +1423,17 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Leandro Matos</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>6224</v>
+        <v>5617</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1468,11 +1453,11 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>5906</v>
+        <v>5905</v>
       </c>
       <c r="H10" t="n">
         <v>5784</v>
@@ -1484,12 +1469,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Recibo de Pagamento</t>
+          <t>Folha Mensal/Pró-Labore</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" s="1" t="n">
-        <v>46209</v>
+        <v>46206</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
@@ -1498,7 +1483,7 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>17688823</v>
+        <v>17407675</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -1512,7 +1497,7 @@
       </c>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1526,7 +1511,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>8. Serviços Suspensos. - Data Comentário: 03/07/2026 08:39</t>
+          <t>8. Serviços Suspensos. - Data Comentário: 08/07/2026 10:25</t>
         </is>
       </c>
       <c r="W10" t="inlineStr"/>
@@ -1542,7 +1527,7 @@
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>Tarefa</t>
+          <t>Obrigação Acessória</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -1553,11 +1538,11 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>5617</v>
+        <v>6224</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1577,11 +1562,11 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>5907</v>
+        <v>5905</v>
       </c>
       <c r="H11" t="n">
         <v>5784</v>
@@ -1593,12 +1578,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Relação Bancária - Salário</t>
+          <t>Folha Mensal/Pró-Labore</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" s="1" t="n">
-        <v>46209</v>
+        <v>46206</v>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
@@ -1607,7 +1592,7 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>17407695</v>
+        <v>17688813</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
@@ -1621,7 +1606,7 @@
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1635,7 +1620,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>8. Serviços Suspensos. - Data Comentário: 03/07/2026 08:40</t>
+          <t>8. Serviços Suspensos. - Data Comentário: 08/07/2026 10:25</t>
         </is>
       </c>
       <c r="W11" t="inlineStr"/>
@@ -1651,7 +1636,7 @@
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>Tarefa</t>
+          <t>Obrigação Acessória</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -1662,11 +1647,11 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>6224</v>
+        <v>5617</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1686,11 +1671,11 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>5907</v>
+        <v>5853</v>
       </c>
       <c r="H12" t="n">
         <v>5784</v>
@@ -1702,12 +1687,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Relação Bancária - Salário</t>
+          <t>FOPAG Impressão PDF</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
@@ -1716,7 +1701,7 @@
         </is>
       </c>
       <c r="O12" t="n">
-        <v>17688833</v>
+        <v>17407635</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
@@ -1744,7 +1729,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>8. Serviços Suspensos. - Data Comentário: 03/07/2026 08:39</t>
+          <t>8. Serviços Suspensos. - Data Comentário: 03/07/2026 08:40</t>
         </is>
       </c>
       <c r="W12" t="inlineStr"/>
@@ -1799,24 +1784,24 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1802</v>
+        <v>5853</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>5784</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Est - ICMS RPA - CÓD. 046-2</t>
+          <t>FOPAG Impressão PDF</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" s="1" t="n">
-        <v>46212</v>
+        <v>46210</v>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
@@ -1825,11 +1810,11 @@
         </is>
       </c>
       <c r="O13" t="n">
-        <v>17688681</v>
+        <v>17688753</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Cristina Leite</t>
+          <t>Tania Luz</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1839,7 +1824,7 @@
       </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1853,7 +1838,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>Atraso do Cliente, cobrança ativa, GC e GM ciente do atraso - Data Comentário: 06/07/2026 15:17</t>
+          <t>8. Serviços Suspensos. - Data Comentário: 03/07/2026 08:39</t>
         </is>
       </c>
       <c r="W13" t="inlineStr"/>
@@ -1869,22 +1854,22 @@
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Tarefa</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>6224</v>
+        <v>5617</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1904,28 +1889,28 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>11665</v>
+        <v>5906</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>5784</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>GIAM (TO)</t>
+          <t>Recibo de Pagamento</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" s="1" t="n">
-        <v>46212</v>
+        <v>46209</v>
       </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
@@ -1934,11 +1919,11 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>18076580</v>
+        <v>17407685</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Cristina Leite</t>
+          <t>Tania Luz</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1948,7 +1933,7 @@
       </c>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1962,7 +1947,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>Atraso do Cliente, cobrança ativa, GC e GM ciente do atraso - Data Comentário: 06/07/2026 15:55</t>
+          <t>8. Serviços Suspensos. - Data Comentário: 03/07/2026 08:40</t>
         </is>
       </c>
       <c r="W14" t="inlineStr"/>
@@ -1983,17 +1968,17 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>6486</v>
+        <v>6224</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PC GAMER GOIANIA LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2013,14 +1998,14 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>5800</v>
+        <v>5906</v>
       </c>
       <c r="H15" t="n">
-        <v>5776</v>
+        <v>5784</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -2029,43 +2014,39 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>CCT Lançamento Sd.663</t>
+          <t>Recibo de Pagamento</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" s="1" t="n">
-        <v>46216</v>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>13/07/2026</t>
-        </is>
-      </c>
+        <v>46209</v>
+      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>00/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>17901201</v>
+        <v>17688823</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Tania Luz</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Em Aberto</t>
+          <t>Em Atraso</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>-3</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>PC GAMER</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2075,8 +2056,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 13/07/2026 
-Foi enviada para a empresa planilha de reajuste e informações sobre termo aditivo do sindicato. Estamos aguardando retorno para aplicação e calculo das complementares. - Data Comentário: 07/07/2026 16:24</t>
+          <t>8. Serviços Suspensos. - Data Comentário: 03/07/2026 08:39</t>
         </is>
       </c>
       <c r="W15" t="inlineStr"/>
@@ -2097,17 +2077,17 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>6962</v>
+        <v>5617</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2127,14 +2107,14 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>11616</v>
+        <v>5907</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>5784</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -2143,12 +2123,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Envio de ATA de Implantação - DP</t>
+          <t>Relação Bancária - Salário</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" s="1" t="n">
-        <v>46213</v>
+        <v>46209</v>
       </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
@@ -2157,31 +2137,35 @@
         </is>
       </c>
       <c r="O16" t="n">
-        <v>18186553</v>
+        <v>17407695</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Mauricio Lermen</t>
+          <t>Tania Luz</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Em Aberto</t>
+          <t>Em Atraso</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr"/>
+          <t>SUPER MAIS DO GOIÁS</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Rotina Para Criar Tarefas Dos Clientes Novos - CodCliente: 6962; Tarefa Incluida: 11616; Vencimento: 17/06/2026 00:00:00; UsuarioResponsavel: mauricio - Data Comentário: 17/06/2026 11:09</t>
+          <t>8. Serviços Suspensos. - Data Comentário: 03/07/2026 08:40</t>
         </is>
       </c>
       <c r="W16" t="inlineStr"/>
@@ -2200,15 +2184,19 @@
           <t>Tarefa</t>
         </is>
       </c>
-      <c r="AG16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>Edivaldo Veiga</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>6963</v>
+        <v>6224</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2228,14 +2216,14 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>11616</v>
+        <v>5907</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>5784</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -2244,12 +2232,12 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Envio de ATA de Implantação - DP</t>
+          <t>Relação Bancária - Salário</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" s="1" t="n">
-        <v>46213</v>
+        <v>46209</v>
       </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
@@ -2258,31 +2246,35 @@
         </is>
       </c>
       <c r="O17" t="n">
-        <v>18186554</v>
+        <v>17688833</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Mauricio Lermen</t>
+          <t>Tania Luz</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Em Aberto</t>
+          <t>Em Atraso</t>
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr"/>
+          <t>SUPER MAIS DO GOIÁS</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>Rotina Para Criar Tarefas Dos Clientes Novos - CodCliente: 6963; Tarefa Incluida: 11616; Vencimento: 17/06/2026 00:00:00; UsuarioResponsavel: mauricio - Data Comentário: 17/06/2026 11:09</t>
+          <t>8. Serviços Suspensos. - Data Comentário: 03/07/2026 08:39</t>
         </is>
       </c>
       <c r="W17" t="inlineStr"/>
@@ -2301,15 +2293,19 @@
           <t>Tarefa</t>
         </is>
       </c>
-      <c r="AG17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>Edivaldo Veiga</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>5617</v>
+        <v>6949</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>TEC GRUA LOCAÇÃO E COMERCIO DE EQUIPAMENTOS PARA CONSTRUÇÃO LTDA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2329,65 +2325,66 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Reynaldo Santos</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>9746</v>
+        <v>11617</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>eSocial – Fechamento Mensal</t>
+          <t>Envio de ATA de Implantação - EF I</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" s="1" t="n">
         <v>46213</v>
       </c>
-      <c r="M18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>17407922</v>
+        <v>18166588</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Tania Luz</t>
+          <t>Priscila Volpe</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Em Aberto</t>
+          <t>Em Atraso</t>
         </is>
       </c>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>TEC GRUA</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr">
         <is>
-          <t>8. Serviços Suspensos. - Data Comentário: 08/07/2026 10:25</t>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 31/07/2026 
+ainda não foi realizado as implantações - Data Comentário: 01/07/2026 13:38</t>
         </is>
       </c>
       <c r="W18" t="inlineStr"/>
@@ -2408,17 +2405,17 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>6224</v>
+        <v>6962</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2438,65 +2435,66 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Reynaldo Santos</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>9746</v>
+        <v>11617</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>eSocial – Fechamento Mensal</t>
+          <t>Envio de ATA de Implantação - EF I</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" s="1" t="n">
         <v>46213</v>
       </c>
-      <c r="M19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O19" t="n">
-        <v>17689040</v>
+        <v>18186565</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Tania Luz</t>
+          <t>Priscila Volpe</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Em Aberto</t>
+          <t>Em Atraso</t>
         </is>
       </c>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>PROMOTORAS GYN</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr">
         <is>
-          <t>8. Serviços Suspensos. - Data Comentário: 08/07/2026 10:25</t>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 31/07/2026 
+ainda não foi realizado as implantações - Data Comentário: 01/07/2026 13:38</t>
         </is>
       </c>
       <c r="W19" t="inlineStr"/>
@@ -2517,17 +2515,17 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>6945</v>
+        <v>6963</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
+          <t>PROMOTORAS GYN LTDA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2537,33 +2535,33 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Reynaldo Santos</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>9746</v>
+        <v>11617</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>eSocial – Fechamento Mensal</t>
+          <t>Envio de ATA de Implantação - EF I</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -2572,7 +2570,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2581,32 +2579,32 @@
         </is>
       </c>
       <c r="O20" t="n">
-        <v>18179152</v>
+        <v>18186566</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Santos Karina</t>
+          <t>Priscila Volpe</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>Em Aberto</t>
+          <t>Em Atraso</t>
         </is>
       </c>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA</t>
+          <t>PROMOTORAS GYN</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 13/07/2026 
-Empresa Implantação em processamento. - Data Comentário: 10/07/2026 17:01</t>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 31/07/2026 
+ainda não foi realizado as implantações - Data Comentário: 01/07/2026 13:38</t>
         </is>
       </c>
       <c r="W20" t="inlineStr"/>
@@ -2627,17 +2625,17 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>Leandro Matos</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>5417</v>
+        <v>6224</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2657,28 +2655,28 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>5867</v>
+        <v>1802</v>
       </c>
       <c r="H21" t="n">
-        <v>5786</v>
+        <v>0</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>GFD - FGTS Digital Mensal</t>
+          <t>Est - ICMS RPA - CÓD. 046-2</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" s="1" t="n">
-        <v>46218</v>
+        <v>46212</v>
       </c>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
@@ -2687,25 +2685,25 @@
         </is>
       </c>
       <c r="O21" t="n">
-        <v>17399054</v>
+        <v>17688681</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Mikael Teixeira</t>
+          <t>Cristina Leite</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Em Aberto</t>
+          <t>Em Atraso</t>
         </is>
       </c>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>-5</v>
+        <v>2</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2713,7 +2711,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr"/>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Atraso do Cliente, cobrança ativa, GC e GM ciente do atraso - Data Comentário: 06/07/2026 15:17</t>
+        </is>
+      </c>
       <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr"/>
@@ -2730,15 +2732,19 @@
           <t>Imposto</t>
         </is>
       </c>
-      <c r="AG21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>Ricardo Fischer</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>5617</v>
+        <v>6224</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2758,28 +2764,28 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>5867</v>
+        <v>11665</v>
       </c>
       <c r="H22" t="n">
-        <v>5786</v>
+        <v>0</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>GFD - FGTS Digital Mensal</t>
+          <t>GIAM (TO)</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" s="1" t="n">
-        <v>46218</v>
+        <v>46212</v>
       </c>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
@@ -2788,21 +2794,21 @@
         </is>
       </c>
       <c r="O22" t="n">
-        <v>17407645</v>
+        <v>18076580</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Tania Luz</t>
+          <t>Cristina Leite</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>Em Aberto</t>
+          <t>Em Atraso</t>
         </is>
       </c>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="n">
-        <v>-5</v>
+        <v>2</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2814,7 +2820,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr"/>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Atraso do Cliente, cobrança ativa, GC e GM ciente do atraso - Data Comentário: 06/07/2026 15:55</t>
+        </is>
+      </c>
       <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr"/>
@@ -2828,22 +2838,22 @@
       <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Tarefa</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>6224</v>
+        <v>5417</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2863,28 +2873,28 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>5867</v>
+        <v>11746</v>
       </c>
       <c r="H23" t="n">
-        <v>5786</v>
+        <v>0</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>GFD - FGTS Digital Mensal</t>
+          <t>Distribuição de Lucro Mensal</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" s="1" t="n">
-        <v>46218</v>
+        <v>46213</v>
       </c>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
@@ -2893,25 +2903,25 @@
         </is>
       </c>
       <c r="O23" t="n">
-        <v>17688773</v>
+        <v>17994309</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Tania Luz</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>Em Aberto</t>
+          <t>Em Atraso</t>
         </is>
       </c>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="n">
-        <v>-5</v>
+        <v>1</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>NOSSO NOVO SUPERMERCADO</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2933,22 +2943,18 @@
       <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>Imposto</t>
-        </is>
-      </c>
-      <c r="AG23" t="inlineStr">
-        <is>
-          <t>Edivaldo Veiga</t>
-        </is>
-      </c>
+          <t>Tarefa</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>6486</v>
+        <v>5617</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>PC GAMER GOIANIA LTDA</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2972,55 +2978,51 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>5867</v>
+        <v>11746</v>
       </c>
       <c r="H24" t="n">
-        <v>5786</v>
+        <v>0</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>GFD - FGTS Digital Mensal</t>
+          <t>Distribuição de Lucro Mensal</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" s="1" t="n">
-        <v>46218</v>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>13/07/2026</t>
-        </is>
-      </c>
+        <v>46213</v>
+      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O24" t="n">
-        <v>16976054</v>
+        <v>18001695</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>Em Aberto</t>
+          <t>Em Atraso</t>
         </is>
       </c>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="n">
-        <v>-5</v>
+        <v>1</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>PC GAMER</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3028,12 +3030,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 13/07/2026 
-PREVISÃO DE CONCLUSÃO: 13/07/2026 - Data Comentário: 07/07/2026 16:32</t>
-        </is>
-      </c>
+      <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr"/>
       <c r="X24" t="inlineStr"/>
       <c r="Y24" t="inlineStr"/>
@@ -3047,22 +3044,18 @@
       <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>Imposto</t>
-        </is>
-      </c>
-      <c r="AG24" t="inlineStr">
-        <is>
-          <t>David Bragança</t>
-        </is>
-      </c>
+          <t>Tarefa</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>6548</v>
+        <v>6278</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM LTDA</t>
+          <t>EMPORIO DOS FRIOS LTDA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3072,7 +3065,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Real - Anual</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -3086,24 +3079,24 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>5867</v>
+        <v>11746</v>
       </c>
       <c r="H25" t="n">
-        <v>5786</v>
+        <v>0</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>GFD - FGTS Digital Mensal</t>
+          <t>Distribuição de Lucro Mensal</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" s="1" t="n">
-        <v>46218</v>
+        <v>46213</v>
       </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
@@ -3112,25 +3105,25 @@
         </is>
       </c>
       <c r="O25" t="n">
-        <v>17222615</v>
+        <v>17994320</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Daniel Moraes</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>Em Aberto</t>
+          <t>Em Atraso</t>
         </is>
       </c>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="n">
-        <v>-5</v>
+        <v>1</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3152,22 +3145,18 @@
       <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>Imposto</t>
-        </is>
-      </c>
-      <c r="AG25" t="inlineStr">
-        <is>
-          <t>David Bragança</t>
-        </is>
-      </c>
+          <t>Tarefa</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>6627</v>
+        <v>6279</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
+          <t>DIENNYFER DA S PEREIRA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3177,69 +3166,65 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>5867</v>
+        <v>11746</v>
       </c>
       <c r="H26" t="n">
-        <v>5786</v>
+        <v>0</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>GFD - FGTS Digital Mensal</t>
+          <t>Distribuição de Lucro Mensal</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" s="1" t="n">
-        <v>46218</v>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>13/07/2026</t>
-        </is>
-      </c>
+        <v>46213</v>
+      </c>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O26" t="n">
-        <v>18068530</v>
+        <v>17995240</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>Em Aberto</t>
+          <t>Em Atraso</t>
         </is>
       </c>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="n">
-        <v>-5</v>
+        <v>1</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3247,12 +3232,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 13/07/2026 
-PREVISÃO DE CONCLUSÃO: 13/07/2026 - Data Comentário: 07/07/2026 16:32</t>
-        </is>
-      </c>
+      <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr"/>
       <c r="X26" t="inlineStr"/>
       <c r="Y26" t="inlineStr"/>
@@ -3266,22 +3246,18 @@
       <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>Imposto</t>
-        </is>
-      </c>
-      <c r="AG26" t="inlineStr">
-        <is>
-          <t>David Bragança</t>
-        </is>
-      </c>
+          <t>Tarefa</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>6628</v>
+        <v>6548</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>GOIAS SILAGEM LTDA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3291,12 +3267,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3305,55 +3281,51 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>5867</v>
+        <v>11746</v>
       </c>
       <c r="H27" t="n">
-        <v>5786</v>
+        <v>0</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>GFD - FGTS Digital Mensal</t>
+          <t>Distribuição de Lucro Mensal</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" s="1" t="n">
-        <v>46218</v>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>13/07/2026</t>
-        </is>
-      </c>
+        <v>46213</v>
+      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O27" t="n">
-        <v>18052449</v>
+        <v>18006049</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>Em Aberto</t>
+          <t>Em Atraso</t>
         </is>
       </c>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="n">
-        <v>-5</v>
+        <v>1</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
+          <t>GOIAS SILAGEM</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3361,12 +3333,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 13/07/2026 
-PREVISÃO DE CONCLUSÃO: 13/07/2026 - Data Comentário: 07/07/2026 16:32</t>
-        </is>
-      </c>
+      <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="inlineStr"/>
       <c r="Y27" t="inlineStr"/>
@@ -3380,22 +3347,18 @@
       <c r="AE27" t="inlineStr"/>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>Imposto</t>
-        </is>
-      </c>
-      <c r="AG27" t="inlineStr">
-        <is>
-          <t>David Bragança</t>
-        </is>
-      </c>
+          <t>Tarefa</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>6703</v>
+        <v>6628</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3405,12 +3368,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3419,55 +3382,51 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>5867</v>
+        <v>11746</v>
       </c>
       <c r="H28" t="n">
-        <v>5786</v>
+        <v>0</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>GFD - FGTS Digital Mensal</t>
+          <t>Distribuição de Lucro Mensal</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" s="1" t="n">
-        <v>46218</v>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>13/07/2026</t>
-        </is>
-      </c>
+        <v>46213</v>
+      </c>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O28" t="n">
-        <v>18077099</v>
+        <v>18003254</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Ana Marcelino</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>Em Aberto</t>
+          <t>Em Atraso</t>
         </is>
       </c>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="n">
-        <v>-5</v>
+        <v>1</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>LIMA MOTA</t>
+          <t xml:space="preserve">GTG </t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3475,11 +3434,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 13/07/2026 - Data Comentário: 10/07/2026 08:29</t>
-        </is>
-      </c>
+      <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr"/>
       <c r="Y28" t="inlineStr"/>
@@ -3493,22 +3448,18 @@
       <c r="AE28" t="inlineStr"/>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>Imposto</t>
-        </is>
-      </c>
-      <c r="AG28" t="inlineStr">
-        <is>
-          <t>Sara Cavalheiro</t>
-        </is>
-      </c>
+          <t>Tarefa</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>6779</v>
+        <v>6703</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CORDEIRO E CIA LTDA</t>
+          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3518,7 +3469,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3532,64 +3483,59 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>5867</v>
+        <v>11746</v>
       </c>
       <c r="H29" t="n">
-        <v>5786</v>
+        <v>0</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>GFD - FGTS Digital Mensal</t>
+          <t>Distribuição de Lucro Mensal</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" s="1" t="n">
-        <v>46218</v>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>14/07/2026</t>
-        </is>
-      </c>
+        <v>46213</v>
+      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O29" t="n">
-        <v>18090176</v>
+        <v>18004015</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kaique Souza</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>Em Aberto</t>
+          <t>Em Atraso</t>
         </is>
       </c>
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="n">
-        <v>-5</v>
+        <v>1</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 14/07/2026 
-ESocial fechado, antecipação de envio. - Data Comentário: 10/07/2026 09:19</t>
-        </is>
-      </c>
+          <t>LIMA MOTA</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr"/>
       <c r="X29" t="inlineStr"/>
       <c r="Y29" t="inlineStr"/>
@@ -3603,22 +3549,18 @@
       <c r="AE29" t="inlineStr"/>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>Imposto</t>
-        </is>
-      </c>
-      <c r="AG29" t="inlineStr">
-        <is>
-          <t>Sara Cavalheiro</t>
-        </is>
-      </c>
+          <t>Tarefa</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>6885</v>
+        <v>6704</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
+          <t>TECNO COM INFORMATICA LTDA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3628,7 +3570,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3642,24 +3584,24 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>5867</v>
+        <v>11746</v>
       </c>
       <c r="H30" t="n">
-        <v>5786</v>
+        <v>0</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>GFD - FGTS Digital Mensal</t>
+          <t>Distribuição de Lucro Mensal</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" s="1" t="n">
-        <v>46218</v>
+        <v>46213</v>
       </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
@@ -3668,28 +3610,32 @@
         </is>
       </c>
       <c r="O30" t="n">
-        <v>18157267</v>
+        <v>17995162</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Vitor Guedes</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>Em Aberto</t>
+          <t>Em Atraso</t>
         </is>
       </c>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="n">
-        <v>-5</v>
+        <v>1</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr"/>
+          <t>TECNO COM</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr"/>
@@ -3704,22 +3650,18 @@
       <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>Imposto</t>
-        </is>
-      </c>
-      <c r="AG30" t="inlineStr">
-        <is>
-          <t>David Bragança</t>
-        </is>
-      </c>
+          <t>Tarefa</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>6945</v>
+        <v>6705</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
+          <t>NARCIZO ALVES CORDEIRO</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3734,7 +3676,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3743,24 +3685,24 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>5867</v>
+        <v>11746</v>
       </c>
       <c r="H31" t="n">
-        <v>5786</v>
+        <v>0</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>GFD - FGTS Digital Mensal</t>
+          <t>Distribuição de Lucro Mensal</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" s="1" t="n">
-        <v>46218</v>
+        <v>46213</v>
       </c>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
@@ -3769,28 +3711,32 @@
         </is>
       </c>
       <c r="O31" t="n">
-        <v>18179101</v>
+        <v>18004026</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Santos Karina</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>Em Aberto</t>
+          <t>Em Atraso</t>
         </is>
       </c>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="n">
-        <v>-5</v>
+        <v>1</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr"/>
+          <t>TECNO COM</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr"/>
@@ -3805,22 +3751,18 @@
       <c r="AE31" t="inlineStr"/>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>Imposto</t>
-        </is>
-      </c>
-      <c r="AG31" t="inlineStr">
-        <is>
-          <t>Leandro Matos</t>
-        </is>
-      </c>
+          <t>Tarefa</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>6949</v>
+        <v>6486</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>TEC GRUA LOCAÇÃO E COMERCIO DE EQUIPAMENTOS PARA CONSTRUÇÃO LTDA</t>
+          <t>PC GAMER GOIANIA LTDA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3840,14 +3782,14 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>6348</v>
+        <v>5800</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>5776</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -3856,25 +3798,29 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>RESCISÃO - RESCISÃO</t>
+          <t>CCT Lançamento Sd.663</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" s="1" t="n">
-        <v>46218</v>
-      </c>
-      <c r="M32" t="inlineStr"/>
+        <v>46216</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>00/2026</t>
         </is>
       </c>
       <c r="O32" t="n">
-        <v>18201961</v>
+        <v>17901201</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Gabriela Peres</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -3884,17 +3830,22 @@
       </c>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>TEC GRUA</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr"/>
+          <t>PC GAMER</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>Pedido de demissão - Desconto de Aviso em 07/07/2026 - Pgto 17/07/2026 - Data Comentário: 08/07/2026 11:16</t>
+          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 13/07/2026 
+Foi enviada para a empresa planilha de reajuste e informações sobre termo aditivo do sindicato. Estamos aguardando retorno para aplicação e calculo das complementares. - Data Comentário: 07/07/2026 16:24</t>
         </is>
       </c>
       <c r="W32" t="inlineStr"/>
@@ -3910,22 +3861,22 @@
       <c r="AE32" t="inlineStr"/>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Tarefa</t>
         </is>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>Leandro Matos</t>
+          <t>David Bragança</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>6949</v>
+        <v>5417</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>TEC GRUA LOCAÇÃO E COMERCIO DE EQUIPAMENTOS PARA CONSTRUÇÃO LTDA</t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3945,45 +3896,41 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>11617</v>
+        <v>5867</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>5786</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Envio de ATA de Implantação - EF I</t>
+          <t>GFD - FGTS Digital Mensal</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" s="1" t="n">
-        <v>46213</v>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>31/07/2026</t>
-        </is>
-      </c>
+        <v>46218</v>
+      </c>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O33" t="n">
-        <v>18166588</v>
+        <v>17399054</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Priscila Volpe</t>
+          <t>Mikael Teixeira</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -3993,20 +3940,19 @@
       </c>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>TEC GRUA</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 31/07/2026 
-ainda não foi realizado as implantações - Data Comentário: 01/07/2026 13:38</t>
-        </is>
-      </c>
+          <t>NOSSO NOVO SUPERMERCADO</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr"/>
       <c r="Y33" t="inlineStr"/>
@@ -4020,22 +3966,18 @@
       <c r="AE33" t="inlineStr"/>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>Tarefa</t>
-        </is>
-      </c>
-      <c r="AG33" t="inlineStr">
-        <is>
-          <t>Nayara Oliveira</t>
-        </is>
-      </c>
+          <t>Imposto</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>6962</v>
+        <v>5617</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4055,45 +3997,41 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>11617</v>
+        <v>5867</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>5786</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Envio de ATA de Implantação - EF I</t>
+          <t>GFD - FGTS Digital Mensal</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" s="1" t="n">
-        <v>46213</v>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>31/07/2026</t>
-        </is>
-      </c>
+        <v>46218</v>
+      </c>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O34" t="n">
-        <v>18186565</v>
+        <v>17407645</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Priscila Volpe</t>
+          <t>Tania Luz</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -4103,20 +4041,19 @@
       </c>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 31/07/2026 
-ainda não foi realizado as implantações - Data Comentário: 01/07/2026 13:38</t>
-        </is>
-      </c>
+          <t>SUPER MAIS DO GOIÁS</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr"/>
       <c r="X34" t="inlineStr"/>
       <c r="Y34" t="inlineStr"/>
@@ -4130,22 +4067,22 @@
       <c r="AE34" t="inlineStr"/>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>Tarefa</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>6963</v>
+        <v>6224</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4165,45 +4102,41 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>11617</v>
+        <v>5867</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>5786</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Envio de ATA de Implantação - EF I</t>
+          <t>GFD - FGTS Digital Mensal</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" s="1" t="n">
-        <v>46213</v>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>31/07/2026</t>
-        </is>
-      </c>
+        <v>46218</v>
+      </c>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O35" t="n">
-        <v>18186566</v>
+        <v>17688773</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Priscila Volpe</t>
+          <t>Tania Luz</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -4213,20 +4146,19 @@
       </c>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 31/07/2026 
-ainda não foi realizado as implantações - Data Comentário: 01/07/2026 13:38</t>
-        </is>
-      </c>
+          <t>SUPER MAIS DO GOIÁS</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr"/>
       <c r="W35" t="inlineStr"/>
       <c r="X35" t="inlineStr"/>
       <c r="Y35" t="inlineStr"/>
@@ -4240,22 +4172,22 @@
       <c r="AE35" t="inlineStr"/>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>Tarefa</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>6628</v>
+        <v>6486</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>PC GAMER GOIANIA LTDA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -4265,12 +4197,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4279,37 +4211,41 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>1875</v>
+        <v>5867</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>5786</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Est - Sintegra Interestadual</t>
+          <t>GFD - FGTS Digital Mensal</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" s="1" t="n">
         <v>46218</v>
       </c>
-      <c r="M36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O36" t="n">
-        <v>17988660</v>
+        <v>16976054</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Fernando Bastos</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -4319,11 +4255,11 @@
       </c>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
+          <t>PC GAMER</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4331,7 +4267,12 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr"/>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 13/07/2026 
+PREVISÃO DE CONCLUSÃO: 13/07/2026 - Data Comentário: 07/07/2026 16:32</t>
+        </is>
+      </c>
       <c r="W36" t="inlineStr"/>
       <c r="X36" t="inlineStr"/>
       <c r="Y36" t="inlineStr"/>
@@ -4345,12 +4286,12 @@
       <c r="AE36" t="inlineStr"/>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>Obrigação Acessória</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>David Bragança</t>
         </is>
       </c>
     </row>
@@ -4384,24 +4325,24 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>6805</v>
+        <v>5867</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>5786</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Fed - EFD - REINF - Entrega e PDF</t>
+          <t>GFD - FGTS Digital Mensal</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" s="1" t="n">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
@@ -4410,11 +4351,11 @@
         </is>
       </c>
       <c r="O37" t="n">
-        <v>17222740</v>
+        <v>17222615</v>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Cristiana Grizostomo</t>
+          <t>Daniel Moraes</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -4424,7 +4365,7 @@
       </c>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4450,12 +4391,12 @@
       <c r="AE37" t="inlineStr"/>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>Obrigação Acessória</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>David Bragança</t>
         </is>
       </c>
     </row>
@@ -4489,37 +4430,41 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>6805</v>
+        <v>5867</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>5786</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Fed - EFD - REINF - Entrega e PDF</t>
+          <t>GFD - FGTS Digital Mensal</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" s="1" t="n">
-        <v>46216</v>
-      </c>
-      <c r="M38" t="inlineStr"/>
+        <v>46218</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O38" t="n">
-        <v>18085517</v>
+        <v>18068530</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Denis Reis</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -4529,7 +4474,7 @@
       </c>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4541,7 +4486,12 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V38" t="inlineStr"/>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 13/07/2026 
+PREVISÃO DE CONCLUSÃO: 13/07/2026 - Data Comentário: 07/07/2026 16:32</t>
+        </is>
+      </c>
       <c r="W38" t="inlineStr"/>
       <c r="X38" t="inlineStr"/>
       <c r="Y38" t="inlineStr"/>
@@ -4555,12 +4505,12 @@
       <c r="AE38" t="inlineStr"/>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>Obrigação Acessória</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>David Bragança</t>
         </is>
       </c>
     </row>
@@ -4594,37 +4544,41 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>6805</v>
+        <v>5867</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>5786</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Fed - EFD - REINF - Entrega e PDF</t>
+          <t>GFD - FGTS Digital Mensal</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" s="1" t="n">
-        <v>46216</v>
-      </c>
-      <c r="M39" t="inlineStr"/>
+        <v>46218</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O39" t="n">
-        <v>17988707</v>
+        <v>18052449</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Fernando Bastos</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -4634,7 +4588,7 @@
       </c>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4646,7 +4600,12 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V39" t="inlineStr"/>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 13/07/2026 
+PREVISÃO DE CONCLUSÃO: 13/07/2026 - Data Comentário: 07/07/2026 16:32</t>
+        </is>
+      </c>
       <c r="W39" t="inlineStr"/>
       <c r="X39" t="inlineStr"/>
       <c r="Y39" t="inlineStr"/>
@@ -4660,22 +4619,22 @@
       <c r="AE39" t="inlineStr"/>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>Obrigação Acessória</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>David Bragança</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>6962</v>
+        <v>6703</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
+          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -4685,7 +4644,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4695,41 +4654,45 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>6805</v>
+        <v>5867</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>5786</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Fed - EFD - REINF - Entrega e PDF</t>
+          <t>GFD - FGTS Digital Mensal</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" s="1" t="n">
-        <v>46216</v>
-      </c>
-      <c r="M40" t="inlineStr"/>
+        <v>46218</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O40" t="n">
-        <v>18186993</v>
+        <v>18077099</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Denis Reis</t>
+          <t>Ana Marcelino</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -4739,15 +4702,23 @@
       </c>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr"/>
+          <t>LIMA MOTA</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 13/07/2026 - Data Comentário: 10/07/2026 08:29</t>
+        </is>
+      </c>
       <c r="W40" t="inlineStr"/>
       <c r="X40" t="inlineStr"/>
       <c r="Y40" t="inlineStr"/>
@@ -4761,22 +4732,22 @@
       <c r="AE40" t="inlineStr"/>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>Obrigação Acessória</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>6963</v>
+        <v>6779</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN LTDA</t>
+          <t>CORDEIRO E CIA LTDA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -4786,7 +4757,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4796,41 +4767,45 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>6805</v>
+        <v>5867</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>5786</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Fed - EFD - REINF - Entrega e PDF</t>
+          <t>GFD - FGTS Digital Mensal</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" s="1" t="n">
-        <v>46216</v>
-      </c>
-      <c r="M41" t="inlineStr"/>
+        <v>46218</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O41" t="n">
-        <v>18187259</v>
+        <v>18090176</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Denis Reis</t>
+          <t>Kaique Souza</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -4840,15 +4815,20 @@
       </c>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN</t>
+          <t>TECNO COM</t>
         </is>
       </c>
       <c r="U41" t="inlineStr"/>
-      <c r="V41" t="inlineStr"/>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 14/07/2026 
+ESocial fechado, antecipação de envio. - Data Comentário: 10/07/2026 09:19</t>
+        </is>
+      </c>
       <c r="W41" t="inlineStr"/>
       <c r="X41" t="inlineStr"/>
       <c r="Y41" t="inlineStr"/>
@@ -4862,22 +4842,22 @@
       <c r="AE41" t="inlineStr"/>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>Obrigação Acessória</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>6627</v>
+        <v>6885</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
+          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -4887,12 +4867,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4901,19 +4881,19 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>10674</v>
+        <v>5867</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>5786</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Relatório de Entrada para Classificação</t>
+          <t>GFD - FGTS Digital Mensal</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -4927,11 +4907,11 @@
         </is>
       </c>
       <c r="O42" t="n">
-        <v>17968443</v>
+        <v>18157267</v>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Denis Reis</t>
+          <t>Vitor Guedes</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -4941,18 +4921,14 @@
       </c>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>EMPORIO DOS FRIOS</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr"/>
       <c r="W42" t="inlineStr"/>
       <c r="X42" t="inlineStr"/>
@@ -4967,22 +4943,22 @@
       <c r="AE42" t="inlineStr"/>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>Tarefa</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>David Bragança</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>6962</v>
+        <v>6945</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
+          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4992,33 +4968,33 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>10674</v>
+        <v>5867</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>5786</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Relatório de Entrada para Classificação</t>
+          <t>GFD - FGTS Digital Mensal</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -5032,11 +5008,11 @@
         </is>
       </c>
       <c r="O43" t="n">
-        <v>18187014</v>
+        <v>18179101</v>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Denis Reis</t>
+          <t>Santos Karina</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
@@ -5046,11 +5022,11 @@
       </c>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN</t>
+          <t>BRASIL DISTRIBUIDORA</t>
         </is>
       </c>
       <c r="U43" t="inlineStr"/>
@@ -5068,22 +5044,22 @@
       <c r="AE43" t="inlineStr"/>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>Tarefa</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Leandro Matos</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>6963</v>
+        <v>6949</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN LTDA</t>
+          <t>TEC GRUA LOCAÇÃO E COMERCIO DE EQUIPAMENTOS PARA CONSTRUÇÃO LTDA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -5107,19 +5083,19 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>10674</v>
+        <v>6348</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Relatório de Entrada para Classificação</t>
+          <t>RESCISÃO - RESCISÃO</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -5129,15 +5105,15 @@
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
-          <t>06/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
       <c r="O44" t="n">
-        <v>18187280</v>
+        <v>18201961</v>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Denis Reis</t>
+          <t>Gabriela Peres</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -5147,15 +5123,19 @@
       </c>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN</t>
+          <t>TEC GRUA</t>
         </is>
       </c>
       <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr"/>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Pedido de demissão - Desconto de Aviso em 07/07/2026 - Pgto 17/07/2026 - Data Comentário: 08/07/2026 11:16</t>
+        </is>
+      </c>
       <c r="W44" t="inlineStr"/>
       <c r="X44" t="inlineStr"/>
       <c r="Y44" t="inlineStr"/>
@@ -5169,22 +5149,22 @@
       <c r="AE44" t="inlineStr"/>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>Tarefa</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Leandro Matos</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>6705</v>
+        <v>6628</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>NARCIZO ALVES CORDEIRO</t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -5199,7 +5179,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -5208,14 +5188,14 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>6298</v>
+        <v>1875</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5234,11 +5214,11 @@
         </is>
       </c>
       <c r="O45" t="n">
-        <v>17949007</v>
+        <v>17988660</v>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Cristina Leite</t>
+          <t>Fernando Bastos</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -5248,11 +5228,11 @@
       </c>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t xml:space="preserve">GTG </t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5279,17 +5259,17 @@
       </c>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>6885</v>
+        <v>6548</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
+          <t>GOIAS SILAGEM LTDA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -5299,7 +5279,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -5313,24 +5293,24 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>6298</v>
+        <v>6805</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Est - Sintegra Interestadual</t>
+          <t>Fed - EFD - REINF - Entrega e PDF</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" s="1" t="n">
-        <v>46218</v>
+        <v>46216</v>
       </c>
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
@@ -5339,11 +5319,11 @@
         </is>
       </c>
       <c r="O46" t="n">
-        <v>18134106</v>
+        <v>17222740</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Cristina Leite</t>
+          <t>Cristiana Grizostomo</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -5353,14 +5333,18 @@
       </c>
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr"/>
+          <t>GOIAS SILAGEM</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V46" t="inlineStr"/>
       <c r="W46" t="inlineStr"/>
       <c r="X46" t="inlineStr"/>
@@ -5380,17 +5364,17 @@
       </c>
       <c r="AG46" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>5417</v>
+        <v>6627</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -5405,23 +5389,23 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>6806</v>
+        <v>6805</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5440,11 +5424,11 @@
         </is>
       </c>
       <c r="O47" t="n">
-        <v>17399228</v>
+        <v>18085517</v>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Cristina Leite</t>
+          <t>Denis Reis</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
@@ -5454,11 +5438,11 @@
       </c>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
+          <t xml:space="preserve">GTG </t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5485,17 +5469,17 @@
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>5617</v>
+        <v>6628</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -5505,12 +5489,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -5519,14 +5503,14 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>6806</v>
+        <v>6805</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5545,11 +5529,11 @@
         </is>
       </c>
       <c r="O48" t="n">
-        <v>17407789</v>
+        <v>17988707</v>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Cristina Leite</t>
+          <t>Fernando Bastos</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -5559,11 +5543,11 @@
       </c>
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t xml:space="preserve">GTG </t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5590,17 +5574,17 @@
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>6224</v>
+        <v>6962</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -5620,18 +5604,18 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Reynaldo Santos</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>6806</v>
+        <v>6805</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5650,11 +5634,11 @@
         </is>
       </c>
       <c r="O49" t="n">
-        <v>17688917</v>
+        <v>18186993</v>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Cristina Leite</t>
+          <t>Denis Reis</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -5664,18 +5648,14 @@
       </c>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>PROMOTORAS GYN</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr"/>
       <c r="V49" t="inlineStr"/>
       <c r="W49" t="inlineStr"/>
       <c r="X49" t="inlineStr"/>
@@ -5695,17 +5675,17 @@
       </c>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>6278</v>
+        <v>6963</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS LTDA</t>
+          <t>PROMOTORAS GYN LTDA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -5715,7 +5695,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Federal - Lucro Real - Anual</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -5725,18 +5705,18 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Reynaldo Santos</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>6806</v>
+        <v>6805</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -5755,11 +5735,11 @@
         </is>
       </c>
       <c r="O50" t="n">
-        <v>17148836</v>
+        <v>18187259</v>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Cristina Leite</t>
+          <t>Denis Reis</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
@@ -5769,18 +5749,14 @@
       </c>
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>PROMOTORAS GYN</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr"/>
       <c r="V50" t="inlineStr"/>
       <c r="W50" t="inlineStr"/>
       <c r="X50" t="inlineStr"/>
@@ -5800,17 +5776,17 @@
       </c>
       <c r="AG50" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>6279</v>
+        <v>6627</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>DIENNYFER DA S PEREIRA</t>
+          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -5820,38 +5796,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>6806</v>
+        <v>10674</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Fed - EFD - REINF - Entrega e PDF</t>
+          <t>Relatório de Entrada para Classificação</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" s="1" t="n">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
@@ -5860,11 +5836,11 @@
         </is>
       </c>
       <c r="O51" t="n">
-        <v>17071031</v>
+        <v>17968443</v>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Cristina Leite</t>
+          <t>Denis Reis</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
@@ -5874,11 +5850,11 @@
       </c>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t xml:space="preserve">GTG </t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5900,22 +5876,22 @@
       <c r="AE51" t="inlineStr"/>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>Obrigação Acessória</t>
+          <t>Tarefa</t>
         </is>
       </c>
       <c r="AG51" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>6404</v>
+        <v>6962</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS LTDA</t>
+          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -5925,7 +5901,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -5935,28 +5911,28 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Reynaldo Santos</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>6806</v>
+        <v>10674</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Fed - EFD - REINF - Entrega e PDF</t>
+          <t>Relatório de Entrada para Classificação</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" s="1" t="n">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
@@ -5965,11 +5941,11 @@
         </is>
       </c>
       <c r="O52" t="n">
-        <v>16962306</v>
+        <v>18187014</v>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Cristina Leite</t>
+          <t>Denis Reis</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
@@ -5979,18 +5955,14 @@
       </c>
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>PROMOTORAS GYN</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr"/>
       <c r="V52" t="inlineStr"/>
       <c r="W52" t="inlineStr"/>
       <c r="X52" t="inlineStr"/>
@@ -6005,22 +5977,22 @@
       <c r="AE52" t="inlineStr"/>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>Obrigação Acessória</t>
+          <t>Tarefa</t>
         </is>
       </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>6486</v>
+        <v>6963</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>PC GAMER GOIANIA LTDA</t>
+          <t>PROMOTORAS GYN LTDA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -6040,28 +6012,28 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Reynaldo Santos</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>6806</v>
+        <v>10674</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Fed - EFD - REINF - Entrega e PDF</t>
+          <t>Relatório de Entrada para Classificação</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" s="1" t="n">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
@@ -6070,11 +6042,11 @@
         </is>
       </c>
       <c r="O53" t="n">
-        <v>16976185</v>
+        <v>18187280</v>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Cristina Leite</t>
+          <t>Denis Reis</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
@@ -6084,18 +6056,14 @@
       </c>
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>PC GAMER</t>
-        </is>
-      </c>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>PROMOTORAS GYN</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr"/>
       <c r="V53" t="inlineStr"/>
       <c r="W53" t="inlineStr"/>
       <c r="X53" t="inlineStr"/>
@@ -6110,22 +6078,22 @@
       <c r="AE53" t="inlineStr"/>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>Obrigação Acessória</t>
+          <t>Tarefa</t>
         </is>
       </c>
       <c r="AG53" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>6703</v>
+        <v>6705</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
+          <t>NARCIZO ALVES CORDEIRO</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -6135,7 +6103,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -6149,7 +6117,7 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>6806</v>
+        <v>6298</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -6161,12 +6129,12 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Fed - EFD - REINF - Entrega e PDF</t>
+          <t>Est - Sintegra Interestadual</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" s="1" t="n">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
@@ -6175,7 +6143,7 @@
         </is>
       </c>
       <c r="O54" t="n">
-        <v>17948856</v>
+        <v>17949007</v>
       </c>
       <c r="P54" t="inlineStr">
         <is>
@@ -6189,11 +6157,11 @@
       </c>
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>LIMA MOTA</t>
+          <t>TECNO COM</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6226,11 +6194,11 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>6704</v>
+        <v>6885</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>TECNO COM INFORMATICA LTDA</t>
+          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -6240,7 +6208,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -6254,7 +6222,7 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>6806</v>
+        <v>6298</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -6266,12 +6234,12 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Fed - EFD - REINF - Entrega e PDF</t>
+          <t>Est - Sintegra Interestadual</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" s="1" t="n">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
@@ -6280,7 +6248,7 @@
         </is>
       </c>
       <c r="O55" t="n">
-        <v>18085295</v>
+        <v>18134106</v>
       </c>
       <c r="P55" t="inlineStr">
         <is>
@@ -6294,18 +6262,14 @@
       </c>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
-        </is>
-      </c>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>EMPORIO DOS FRIOS</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr"/>
       <c r="V55" t="inlineStr"/>
       <c r="W55" t="inlineStr"/>
       <c r="X55" t="inlineStr"/>
@@ -6331,11 +6295,11 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>6705</v>
+        <v>5417</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NARCIZO ALVES CORDEIRO</t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -6345,7 +6309,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -6355,7 +6319,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -6385,7 +6349,7 @@
         </is>
       </c>
       <c r="O56" t="n">
-        <v>17949027</v>
+        <v>17399228</v>
       </c>
       <c r="P56" t="inlineStr">
         <is>
@@ -6399,11 +6363,11 @@
       </c>
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>NOSSO NOVO SUPERMERCADO</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6436,11 +6400,11 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>6779</v>
+        <v>5617</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CORDEIRO E CIA LTDA</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -6450,7 +6414,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -6490,7 +6454,7 @@
         </is>
       </c>
       <c r="O57" t="n">
-        <v>18085064</v>
+        <v>17407789</v>
       </c>
       <c r="P57" t="inlineStr">
         <is>
@@ -6504,14 +6468,18 @@
       </c>
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
-        </is>
-      </c>
-      <c r="U57" t="inlineStr"/>
+          <t>SUPER MAIS DO GOIÁS</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V57" t="inlineStr"/>
       <c r="W57" t="inlineStr"/>
       <c r="X57" t="inlineStr"/>
@@ -6537,11 +6505,11 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>6885</v>
+        <v>6224</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -6551,7 +6519,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -6561,7 +6529,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -6591,7 +6559,7 @@
         </is>
       </c>
       <c r="O58" t="n">
-        <v>18134124</v>
+        <v>17688917</v>
       </c>
       <c r="P58" t="inlineStr">
         <is>
@@ -6605,14 +6573,18 @@
       </c>
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr"/>
+          <t>SUPER MAIS DO GOIÁS</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V58" t="inlineStr"/>
       <c r="W58" t="inlineStr"/>
       <c r="X58" t="inlineStr"/>
@@ -6638,11 +6610,11 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>5617</v>
+        <v>6278</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>EMPORIO DOS FRIOS LTDA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -6652,7 +6624,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Real - Anual</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -6666,10 +6638,10 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>7884</v>
+        <v>6806</v>
       </c>
       <c r="H59" t="n">
-        <v>9114</v>
+        <v>0</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -6678,12 +6650,12 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Log/Envio de Inconsistência (Mensal)</t>
+          <t>Fed - EFD - REINF - Entrega e PDF</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" s="1" t="n">
-        <v>46218</v>
+        <v>46216</v>
       </c>
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
@@ -6692,7 +6664,7 @@
         </is>
       </c>
       <c r="O59" t="n">
-        <v>18120594</v>
+        <v>17148836</v>
       </c>
       <c r="P59" t="inlineStr">
         <is>
@@ -6706,11 +6678,11 @@
       </c>
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6718,11 +6690,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>Atraso do Cliente, cobrança ativa, GC e GM ciente do atraso - Data Comentário: 10/07/2026 10:31</t>
-        </is>
-      </c>
+      <c r="V59" t="inlineStr"/>
       <c r="W59" t="inlineStr"/>
       <c r="X59" t="inlineStr"/>
       <c r="Y59" t="inlineStr"/>
@@ -6736,7 +6704,7 @@
       <c r="AE59" t="inlineStr"/>
       <c r="AF59" t="inlineStr">
         <is>
-          <t>Tarefa</t>
+          <t>Obrigação Acessória</t>
         </is>
       </c>
       <c r="AG59" t="inlineStr">
@@ -6747,11 +6715,11 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>5617</v>
+        <v>6279</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>DIENNYFER DA S PEREIRA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -6761,7 +6729,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -6771,11 +6739,11 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>11303</v>
+        <v>6806</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -6787,12 +6755,12 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Retorno do Check-List Fiscal</t>
+          <t>Fed - EFD - REINF - Entrega e PDF</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" s="1" t="n">
-        <v>46218</v>
+        <v>46216</v>
       </c>
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
@@ -6801,7 +6769,7 @@
         </is>
       </c>
       <c r="O60" t="n">
-        <v>17407963</v>
+        <v>17071031</v>
       </c>
       <c r="P60" t="inlineStr">
         <is>
@@ -6815,11 +6783,11 @@
       </c>
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6841,7 +6809,7 @@
       <c r="AE60" t="inlineStr"/>
       <c r="AF60" t="inlineStr">
         <is>
-          <t>Tarefa</t>
+          <t>Obrigação Acessória</t>
         </is>
       </c>
       <c r="AG60" t="inlineStr">
@@ -6852,11 +6820,11 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>SOLAR INVESTIMENTOS LTDA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -6866,7 +6834,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -6876,28 +6844,28 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>11746</v>
+        <v>6806</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Distribuição de Lucro Mensal</t>
+          <t>Fed - EFD - REINF - Entrega e PDF</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
@@ -6906,11 +6874,11 @@
         </is>
       </c>
       <c r="O61" t="n">
-        <v>17994309</v>
+        <v>16962306</v>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Cristina Leite</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
@@ -6920,11 +6888,11 @@
       </c>
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
+          <t>SOLAR INVESTIMENTOS</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -6946,18 +6914,22 @@
       <c r="AE61" t="inlineStr"/>
       <c r="AF61" t="inlineStr">
         <is>
-          <t>Tarefa</t>
-        </is>
-      </c>
-      <c r="AG61" t="inlineStr"/>
+          <t>Obrigação Acessória</t>
+        </is>
+      </c>
+      <c r="AG61" t="inlineStr">
+        <is>
+          <t>Ricardo Fischer</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>5617</v>
+        <v>6486</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>PC GAMER GOIANIA LTDA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -6981,24 +6953,24 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>11746</v>
+        <v>6806</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Distribuição de Lucro Mensal</t>
+          <t>Fed - EFD - REINF - Entrega e PDF</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
@@ -7007,11 +6979,11 @@
         </is>
       </c>
       <c r="O62" t="n">
-        <v>18001695</v>
+        <v>16976185</v>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Cristina Leite</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
@@ -7021,11 +6993,11 @@
       </c>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>PC GAMER</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7047,18 +7019,22 @@
       <c r="AE62" t="inlineStr"/>
       <c r="AF62" t="inlineStr">
         <is>
-          <t>Tarefa</t>
-        </is>
-      </c>
-      <c r="AG62" t="inlineStr"/>
+          <t>Obrigação Acessória</t>
+        </is>
+      </c>
+      <c r="AG62" t="inlineStr">
+        <is>
+          <t>Ricardo Fischer</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>6278</v>
+        <v>6703</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS LTDA</t>
+          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -7068,7 +7044,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Federal - Lucro Real - Anual</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -7082,24 +7058,24 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>11746</v>
+        <v>6806</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Distribuição de Lucro Mensal</t>
+          <t>Fed - EFD - REINF - Entrega e PDF</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
       <c r="L63" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
@@ -7108,11 +7084,11 @@
         </is>
       </c>
       <c r="O63" t="n">
-        <v>17994320</v>
+        <v>17948856</v>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Cristina Leite</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
@@ -7122,11 +7098,11 @@
       </c>
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>LIMA MOTA</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7148,18 +7124,22 @@
       <c r="AE63" t="inlineStr"/>
       <c r="AF63" t="inlineStr">
         <is>
-          <t>Tarefa</t>
-        </is>
-      </c>
-      <c r="AG63" t="inlineStr"/>
+          <t>Obrigação Acessória</t>
+        </is>
+      </c>
+      <c r="AG63" t="inlineStr">
+        <is>
+          <t>Ricardo Fischer</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>6279</v>
+        <v>6704</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>DIENNYFER DA S PEREIRA</t>
+          <t>TECNO COM INFORMATICA LTDA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -7169,7 +7149,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -7179,28 +7159,28 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>11746</v>
+        <v>6806</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Distribuição de Lucro Mensal</t>
+          <t>Fed - EFD - REINF - Entrega e PDF</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
       <c r="L64" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
@@ -7209,11 +7189,11 @@
         </is>
       </c>
       <c r="O64" t="n">
-        <v>17995240</v>
+        <v>18085295</v>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Cristina Leite</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
@@ -7223,11 +7203,11 @@
       </c>
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>TECNO COM</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7249,18 +7229,22 @@
       <c r="AE64" t="inlineStr"/>
       <c r="AF64" t="inlineStr">
         <is>
-          <t>Tarefa</t>
-        </is>
-      </c>
-      <c r="AG64" t="inlineStr"/>
+          <t>Obrigação Acessória</t>
+        </is>
+      </c>
+      <c r="AG64" t="inlineStr">
+        <is>
+          <t>Ricardo Fischer</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>6548</v>
+        <v>6705</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM LTDA</t>
+          <t>NARCIZO ALVES CORDEIRO</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -7270,7 +7254,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -7284,24 +7268,24 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>11746</v>
+        <v>6806</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Distribuição de Lucro Mensal</t>
+          <t>Fed - EFD - REINF - Entrega e PDF</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
       <c r="L65" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr">
@@ -7310,11 +7294,11 @@
         </is>
       </c>
       <c r="O65" t="n">
-        <v>18006049</v>
+        <v>17949027</v>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Cristina Leite</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
@@ -7324,11 +7308,11 @@
       </c>
       <c r="R65" t="inlineStr"/>
       <c r="S65" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM</t>
+          <t>TECNO COM</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7350,18 +7334,22 @@
       <c r="AE65" t="inlineStr"/>
       <c r="AF65" t="inlineStr">
         <is>
-          <t>Tarefa</t>
-        </is>
-      </c>
-      <c r="AG65" t="inlineStr"/>
+          <t>Obrigação Acessória</t>
+        </is>
+      </c>
+      <c r="AG65" t="inlineStr">
+        <is>
+          <t>Ricardo Fischer</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>6628</v>
+        <v>6779</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>CORDEIRO E CIA LTDA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -7376,7 +7364,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -7385,24 +7373,24 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>11746</v>
+        <v>6806</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Distribuição de Lucro Mensal</t>
+          <t>Fed - EFD - REINF - Entrega e PDF</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
       <c r="L66" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr">
@@ -7411,11 +7399,11 @@
         </is>
       </c>
       <c r="O66" t="n">
-        <v>18003254</v>
+        <v>18085064</v>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Cristina Leite</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
@@ -7425,18 +7413,14 @@
       </c>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
-        </is>
-      </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>TECNO COM</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr"/>
       <c r="V66" t="inlineStr"/>
       <c r="W66" t="inlineStr"/>
       <c r="X66" t="inlineStr"/>
@@ -7451,18 +7435,22 @@
       <c r="AE66" t="inlineStr"/>
       <c r="AF66" t="inlineStr">
         <is>
-          <t>Tarefa</t>
-        </is>
-      </c>
-      <c r="AG66" t="inlineStr"/>
+          <t>Obrigação Acessória</t>
+        </is>
+      </c>
+      <c r="AG66" t="inlineStr">
+        <is>
+          <t>Ricardo Fischer</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>6703</v>
+        <v>6885</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
+          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -7472,7 +7460,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -7486,24 +7474,24 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>11746</v>
+        <v>6806</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Distribuição de Lucro Mensal</t>
+          <t>Fed - EFD - REINF - Entrega e PDF</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
       <c r="L67" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
@@ -7512,11 +7500,11 @@
         </is>
       </c>
       <c r="O67" t="n">
-        <v>18004015</v>
+        <v>18134124</v>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Cristina Leite</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
@@ -7526,18 +7514,14 @@
       </c>
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>LIMA MOTA</t>
-        </is>
-      </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>EMPORIO DOS FRIOS</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr"/>
       <c r="V67" t="inlineStr"/>
       <c r="W67" t="inlineStr"/>
       <c r="X67" t="inlineStr"/>
@@ -7552,18 +7536,22 @@
       <c r="AE67" t="inlineStr"/>
       <c r="AF67" t="inlineStr">
         <is>
-          <t>Tarefa</t>
-        </is>
-      </c>
-      <c r="AG67" t="inlineStr"/>
+          <t>Obrigação Acessória</t>
+        </is>
+      </c>
+      <c r="AG67" t="inlineStr">
+        <is>
+          <t>Ricardo Fischer</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>6704</v>
+        <v>5617</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>TECNO COM INFORMATICA LTDA</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -7587,24 +7575,24 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>11746</v>
+        <v>7884</v>
       </c>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>9114</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Distribuição de Lucro Mensal</t>
+          <t>Log/Envio de Inconsistência (Mensal)</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
       <c r="L68" s="1" t="n">
-        <v>46213</v>
+        <v>46218</v>
       </c>
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
@@ -7613,11 +7601,11 @@
         </is>
       </c>
       <c r="O68" t="n">
-        <v>17995162</v>
+        <v>18120594</v>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Cristina Leite</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
@@ -7627,11 +7615,11 @@
       </c>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -7639,7 +7627,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V68" t="inlineStr"/>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Atraso do Cliente, cobrança ativa, GC e GM ciente do atraso - Data Comentário: 10/07/2026 10:31</t>
+        </is>
+      </c>
       <c r="W68" t="inlineStr"/>
       <c r="X68" t="inlineStr"/>
       <c r="Y68" t="inlineStr"/>
@@ -7656,15 +7648,19 @@
           <t>Tarefa</t>
         </is>
       </c>
-      <c r="AG68" t="inlineStr"/>
+      <c r="AG68" t="inlineStr">
+        <is>
+          <t>Ricardo Fischer</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>6705</v>
+        <v>5617</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>NARCIZO ALVES CORDEIRO</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -7674,7 +7670,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -7688,24 +7684,24 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>11746</v>
+        <v>11303</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Distribuição de Lucro Mensal</t>
+          <t>Retorno do Check-List Fiscal</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" s="1" t="n">
-        <v>46213</v>
+        <v>46218</v>
       </c>
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
@@ -7714,11 +7710,11 @@
         </is>
       </c>
       <c r="O69" t="n">
-        <v>18004026</v>
+        <v>17407963</v>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Cristina Leite</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
@@ -7728,11 +7724,11 @@
       </c>
       <c r="R69" t="inlineStr"/>
       <c r="S69" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -7757,7 +7753,11 @@
           <t>Tarefa</t>
         </is>
       </c>
-      <c r="AG69" t="inlineStr"/>
+      <c r="AG69" t="inlineStr">
+        <is>
+          <t>Ricardo Fischer</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7831,7 +7831,7 @@
         <v>46206.43215109954</v>
       </c>
       <c r="S70" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7935,7 +7935,7 @@
         <v>46206.43205978009</v>
       </c>
       <c r="S71" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8038,7 +8038,7 @@
         <v>46206.43206049768</v>
       </c>
       <c r="S72" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
         <v>46204.75352534722</v>
       </c>
       <c r="S73" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
         <v>46204.75352809028</v>
       </c>
       <c r="S74" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8367,7 +8367,7 @@
         <v>46204.7535284375</v>
       </c>
       <c r="S75" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8478,7 +8478,7 @@
         <v>46204.7535334838</v>
       </c>
       <c r="S76" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8585,7 +8585,7 @@
         <v>46204.75353387732</v>
       </c>
       <c r="S77" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         <v>46204.75353515046</v>
       </c>
       <c r="S78" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8799,7 +8799,7 @@
         <v>46204.75350494213</v>
       </c>
       <c r="S79" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         <v>46204.75351072917</v>
       </c>
       <c r="S80" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>46204.75352068287</v>
       </c>
       <c r="S81" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9132,7 +9132,7 @@
         <v>46204.75352175926</v>
       </c>
       <c r="S82" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         <v>46204.75353024306</v>
       </c>
       <c r="S83" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>46204.7535309838</v>
       </c>
       <c r="S84" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         <v>46204.75353240741</v>
       </c>
       <c r="S85" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         <v>46204.75353278935</v>
       </c>
       <c r="S86" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9675,7 +9675,7 @@
         <v>46205.599529375</v>
       </c>
       <c r="S87" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>46204.71542079861</v>
       </c>
       <c r="S88" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9885,7 +9885,7 @@
         <v>46204.71542134259</v>
       </c>
       <c r="S89" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9988,7 +9988,7 @@
         <v>46204.48446469908</v>
       </c>
       <c r="S90" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10099,7 +10099,7 @@
         <v>46205.75412240741</v>
       </c>
       <c r="S91" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10210,7 +10210,7 @@
         <v>46205.75458568287</v>
       </c>
       <c r="S92" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10321,7 +10321,7 @@
         <v>46206.44903752315</v>
       </c>
       <c r="S93" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10428,7 +10428,7 @@
         <v>46199.48727971065</v>
       </c>
       <c r="S94" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10531,7 +10531,7 @@
         <v>46205.69236453703</v>
       </c>
       <c r="S95" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>46209.43008613426</v>
       </c>
       <c r="S96" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10754,7 +10754,7 @@
         <v>46204.5600265625</v>
       </c>
       <c r="S97" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10865,7 +10865,7 @@
         <v>46196.71390480324</v>
       </c>
       <c r="S98" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10976,7 +10976,7 @@
         <v>46198.70825575232</v>
       </c>
       <c r="S99" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11087,7 +11087,7 @@
         <v>46196.59280127315</v>
       </c>
       <c r="S100" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>46204.41370118056</v>
       </c>
       <c r="S101" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11305,7 +11305,7 @@
         <v>46213.6834903125</v>
       </c>
       <c r="S102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11421,7 +11421,7 @@
         <v>46209.71247704861</v>
       </c>
       <c r="S103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11540,7 +11540,7 @@
         <v>46209.71499087963</v>
       </c>
       <c r="S104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11660,7 +11660,7 @@
         <v>46211.48251296296</v>
       </c>
       <c r="S105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11780,7 +11780,7 @@
         <v>46210.47222041667</v>
       </c>
       <c r="S106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
         <v>46211.58264625</v>
       </c>
       <c r="S107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12020,7 +12020,7 @@
         <v>46210.48132625</v>
       </c>
       <c r="S108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12140,7 +12140,7 @@
         <v>46210.45896016204</v>
       </c>
       <c r="S109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12256,7 +12256,7 @@
         <v>46210.72289299768</v>
       </c>
       <c r="S110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12368,7 +12368,7 @@
         <v>46211.59005767361</v>
       </c>
       <c r="S111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12484,7 +12484,7 @@
         <v>46206.54816894676</v>
       </c>
       <c r="S112" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12599,7 +12599,7 @@
         <v>46206.55861924768</v>
       </c>
       <c r="S113" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12718,7 +12718,7 @@
         <v>46206.67165491898</v>
       </c>
       <c r="S114" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12837,7 +12837,7 @@
         <v>46206.67202474537</v>
       </c>
       <c r="S115" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12956,7 +12956,7 @@
         <v>46206.62892094907</v>
       </c>
       <c r="S116" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13075,7 +13075,7 @@
         <v>46206.64427289352</v>
       </c>
       <c r="S117" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13190,7 +13190,7 @@
         <v>46205.6924828125</v>
       </c>
       <c r="S118" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13305,7 +13305,7 @@
         <v>46206.69765491898</v>
       </c>
       <c r="S119" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13416,7 +13416,7 @@
         <v>46206.65603582176</v>
       </c>
       <c r="S120" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13523,7 +13523,7 @@
         <v>46209.41001810185</v>
       </c>
       <c r="S121" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13634,7 +13634,7 @@
         <v>46209.41001846065</v>
       </c>
       <c r="S122" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13745,7 +13745,7 @@
         <v>46209.41001900463</v>
       </c>
       <c r="S123" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13856,7 +13856,7 @@
         <v>46206.62881552083</v>
       </c>
       <c r="S124" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13971,7 +13971,7 @@
         <v>46206.64398119213</v>
       </c>
       <c r="S125" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -14082,7 +14082,7 @@
         <v>46209.55182975694</v>
       </c>
       <c r="S126" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -14189,7 +14189,7 @@
         <v>46211.39936383102</v>
       </c>
       <c r="S127" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -14296,7 +14296,7 @@
         <v>46204.50154423611</v>
       </c>
       <c r="S128" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -14407,7 +14407,7 @@
         <v>46196.69558237268</v>
       </c>
       <c r="S129" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14518,7 +14518,7 @@
         <v>46198.71108606482</v>
       </c>
       <c r="S130" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -14629,7 +14629,7 @@
         <v>46196.59315405093</v>
       </c>
       <c r="S131" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -14736,7 +14736,7 @@
         <v>46204.42181446759</v>
       </c>
       <c r="S132" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>46204.48462402778</v>
       </c>
       <c r="S133" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14946,7 +14946,7 @@
         <v>46195.57837077546</v>
       </c>
       <c r="S134" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -15053,7 +15053,7 @@
         <v>46188.39084737268</v>
       </c>
       <c r="S135" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -15164,7 +15164,7 @@
         <v>46188.39085099537</v>
       </c>
       <c r="S136" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -15271,7 +15271,7 @@
         <v>46189.61008070602</v>
       </c>
       <c r="S137" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -15378,7 +15378,7 @@
         <v>46185.66827939815</v>
       </c>
       <c r="S138" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -15489,7 +15489,7 @@
         <v>46190.56460636574</v>
       </c>
       <c r="S139" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -15600,7 +15600,7 @@
         <v>46185.66566952546</v>
       </c>
       <c r="S140" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -15711,7 +15711,7 @@
         <v>46185.66535266204</v>
       </c>
       <c r="S141" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -15822,7 +15822,7 @@
         <v>46185.69383032407</v>
       </c>
       <c r="S142" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -15929,7 +15929,7 @@
         <v>46195.70875512731</v>
       </c>
       <c r="S143" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -16036,7 +16036,7 @@
         <v>46195.70011658565</v>
       </c>
       <c r="S144" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -16147,7 +16147,7 @@
         <v>46205.59156991898</v>
       </c>
       <c r="S145" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -16267,7 +16267,7 @@
         <v>46205.73670511574</v>
       </c>
       <c r="S146" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -16387,7 +16387,7 @@
         <v>46205.7367062037</v>
       </c>
       <c r="S147" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -16507,7 +16507,7 @@
         <v>46206.43991525463</v>
       </c>
       <c r="S148" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -16623,7 +16623,7 @@
         <v>46205.34573362269</v>
       </c>
       <c r="S149" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -16734,7 +16734,7 @@
         <v>46206.65428631944</v>
       </c>
       <c r="S150" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -16841,7 +16841,7 @@
         <v>46199.67793730324</v>
       </c>
       <c r="S151" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -16952,7 +16952,7 @@
         <v>46206.55866898148</v>
       </c>
       <c r="S152" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -17063,7 +17063,7 @@
         <v>46206.6716975926</v>
       </c>
       <c r="S153" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -17174,7 +17174,7 @@
         <v>46206.67205873843</v>
       </c>
       <c r="S154" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -17285,7 +17285,7 @@
         <v>46206.62895168982</v>
       </c>
       <c r="S155" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -17400,7 +17400,7 @@
         <v>46206.6443237037</v>
       </c>
       <c r="S156" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -17511,7 +17511,7 @@
         <v>46205.69251481481</v>
       </c>
       <c r="S157" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -17618,7 +17618,7 @@
         <v>46206.69781152777</v>
       </c>
       <c r="S158" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -17725,7 +17725,7 @@
         <v>46206.65440622685</v>
       </c>
       <c r="S159" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -17836,7 +17836,7 @@
         <v>46206.40915328704</v>
       </c>
       <c r="S160" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -17951,7 +17951,7 @@
         <v>46206.55870388889</v>
       </c>
       <c r="S161" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -18062,7 +18062,7 @@
         <v>46206.67172778935</v>
       </c>
       <c r="S162" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -18173,7 +18173,7 @@
         <v>46206.67209291667</v>
       </c>
       <c r="S163" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -18284,7 +18284,7 @@
         <v>46206.62899021991</v>
       </c>
       <c r="S164" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -18399,7 +18399,7 @@
         <v>46206.64435354167</v>
       </c>
       <c r="S165" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -18510,7 +18510,7 @@
         <v>46205.69254519676</v>
       </c>
       <c r="S166" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -18617,7 +18617,7 @@
         <v>46206.69786020833</v>
       </c>
       <c r="S167" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -18720,7 +18720,7 @@
         <v>46206.65479178241</v>
       </c>
       <c r="S168" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -18831,7 +18831,7 @@
         <v>46210.4994990162</v>
       </c>
       <c r="S169" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -18947,7 +18947,7 @@
         <v>46211.45479957176</v>
       </c>
       <c r="S170" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -19055,7 +19055,7 @@
         <v>46211.59924370371</v>
       </c>
       <c r="S171" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -19166,7 +19166,7 @@
         <v>46203.71388695601</v>
       </c>
       <c r="S172" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -19277,7 +19277,7 @@
         <v>46206.79368510417</v>
       </c>
       <c r="S173" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -19384,7 +19384,7 @@
         <v>46206.79368695602</v>
       </c>
       <c r="S174" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>
@@ -19491,7 +19491,7 @@
         <v>46203.71358417824</v>
       </c>
       <c r="S175" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T175" t="inlineStr">
         <is>
@@ -19602,7 +19602,7 @@
         <v>46205.46012403935</v>
       </c>
       <c r="S176" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -19713,7 +19713,7 @@
         <v>46206.79339394676</v>
       </c>
       <c r="S177" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -19820,7 +19820,7 @@
         <v>46206.79339563657</v>
       </c>
       <c r="S178" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -19927,7 +19927,7 @@
         <v>46203.71368457176</v>
       </c>
       <c r="S179" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -20038,7 +20038,7 @@
         <v>46205.4602116551</v>
       </c>
       <c r="S180" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -20149,7 +20149,7 @@
         <v>46206.79348040509</v>
       </c>
       <c r="S181" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T181" t="inlineStr">
         <is>
@@ -20256,7 +20256,7 @@
         <v>46206.79348244213</v>
       </c>
       <c r="S182" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -20363,7 +20363,7 @@
         <v>46203.71312577547</v>
       </c>
       <c r="S183" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -20474,7 +20474,7 @@
         <v>46206.79261038194</v>
       </c>
       <c r="S184" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -20581,7 +20581,7 @@
         <v>46206.79261369213</v>
       </c>
       <c r="S185" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -20688,7 +20688,7 @@
         <v>46206.79369521991</v>
       </c>
       <c r="S186" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -20795,7 +20795,7 @@
         <v>46206.79369363426</v>
       </c>
       <c r="S187" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -20902,7 +20902,7 @@
         <v>46203.71373487268</v>
       </c>
       <c r="S188" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -21013,7 +21013,7 @@
         <v>46205.46026211805</v>
       </c>
       <c r="S189" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -21124,7 +21124,7 @@
         <v>46206.79353869213</v>
       </c>
       <c r="S190" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -21231,7 +21231,7 @@
         <v>46206.79354065972</v>
       </c>
       <c r="S191" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -21338,7 +21338,7 @@
         <v>46209.46657106481</v>
       </c>
       <c r="S192" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -21445,7 +21445,7 @@
         <v>46209.46657106481</v>
       </c>
       <c r="S193" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -21552,7 +21552,7 @@
         <v>46206.79251087963</v>
       </c>
       <c r="S194" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -21659,7 +21659,7 @@
         <v>46206.79251215278</v>
       </c>
       <c r="S195" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -21766,7 +21766,7 @@
         <v>46206.79252202546</v>
       </c>
       <c r="S196" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T196" t="inlineStr">
         <is>
@@ -21873,7 +21873,7 @@
         <v>46206.79252349537</v>
       </c>
       <c r="S197" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T197" t="inlineStr">
         <is>
@@ -21980,7 +21980,7 @@
         <v>46203.71378568287</v>
       </c>
       <c r="S198" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -22091,7 +22091,7 @@
         <v>46205.46031030093</v>
       </c>
       <c r="S199" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T199" t="inlineStr">
         <is>
@@ -22202,7 +22202,7 @@
         <v>46206.79359788194</v>
       </c>
       <c r="S200" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T200" t="inlineStr">
         <is>
@@ -22309,7 +22309,7 @@
         <v>46206.7935997338</v>
       </c>
       <c r="S201" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -22416,7 +22416,7 @@
         <v>46203.71384140047</v>
       </c>
       <c r="S202" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T202" t="inlineStr">
         <is>
@@ -22527,7 +22527,7 @@
         <v>46205.4603590625</v>
       </c>
       <c r="S203" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T203" t="inlineStr">
         <is>
@@ -22638,7 +22638,7 @@
         <v>46206.79364525463</v>
       </c>
       <c r="S204" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T204" t="inlineStr">
         <is>
@@ -22745,7 +22745,7 @@
         <v>46206.79364730324</v>
       </c>
       <c r="S205" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T205" t="inlineStr">
         <is>
@@ -22856,7 +22856,7 @@
         <v>46209.45242072917</v>
       </c>
       <c r="S206" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T206" t="inlineStr">
         <is>
@@ -22975,7 +22975,7 @@
         <v>46211.76742385417</v>
       </c>
       <c r="S207" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T207" t="inlineStr">
         <is>
@@ -23090,7 +23090,7 @@
         <v>46211.76720232639</v>
       </c>
       <c r="S208" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T208" t="inlineStr">
         <is>
@@ -23205,7 +23205,7 @@
         <v>46210.63989674769</v>
       </c>
       <c r="S209" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T209" t="inlineStr">
         <is>
@@ -23325,7 +23325,7 @@
         <v>46209.49997177083</v>
       </c>
       <c r="S210" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T210" t="inlineStr">
         <is>
@@ -23444,7 +23444,7 @@
         <v>46211.76683576389</v>
       </c>
       <c r="S211" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T211" t="inlineStr">
         <is>
@@ -23559,7 +23559,7 @@
         <v>46211.76723488426</v>
       </c>
       <c r="S212" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T212" t="inlineStr">
         <is>
@@ -23670,7 +23670,7 @@
         <v>46211.79243741898</v>
       </c>
       <c r="S213" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T213" t="inlineStr">
         <is>
@@ -23777,7 +23777,7 @@
         <v>46211.79243900463</v>
       </c>
       <c r="S214" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T214" t="inlineStr">
         <is>
@@ -23884,7 +23884,7 @@
         <v>46204.37644915509</v>
       </c>
       <c r="S215" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T215" t="inlineStr">
         <is>
@@ -23995,7 +23995,7 @@
         <v>46204.37595123843</v>
       </c>
       <c r="S216" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T216" t="inlineStr">
         <is>
@@ -24106,7 +24106,7 @@
         <v>46204.37595258102</v>
       </c>
       <c r="S217" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T217" t="inlineStr">
         <is>
@@ -24217,7 +24217,7 @@
         <v>46206.79235609954</v>
       </c>
       <c r="S218" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T218" t="inlineStr">
         <is>
@@ -24328,7 +24328,7 @@
         <v>46205.45902149306</v>
       </c>
       <c r="S219" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T219" t="inlineStr">
         <is>
@@ -24439,7 +24439,7 @@
         <v>46206.79235100694</v>
       </c>
       <c r="S220" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T220" t="inlineStr">
         <is>
@@ -24550,7 +24550,7 @@
         <v>46204.37667199074</v>
       </c>
       <c r="S221" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T221" t="inlineStr">
         <is>
@@ -24661,7 +24661,7 @@
         <v>46204.37677195602</v>
       </c>
       <c r="S222" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T222" t="inlineStr">
         <is>
@@ -24772,7 +24772,7 @@
         <v>46204.37677268519</v>
       </c>
       <c r="S223" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T223" t="inlineStr">
         <is>
@@ -24883,7 +24883,7 @@
         <v>46204.37681211805</v>
       </c>
       <c r="S224" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T224" t="inlineStr">
         <is>
@@ -24994,7 +24994,7 @@
         <v>46206.7926803588</v>
       </c>
       <c r="S225" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T225" t="inlineStr">
         <is>
@@ -25105,7 +25105,7 @@
         <v>46204.37581924768</v>
       </c>
       <c r="S226" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T226" t="inlineStr">
         <is>
@@ -25216,7 +25216,7 @@
         <v>46204.37582079861</v>
       </c>
       <c r="S227" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T227" t="inlineStr">
         <is>
@@ -25327,7 +25327,7 @@
         <v>46206.79232175926</v>
       </c>
       <c r="S228" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T228" t="inlineStr">
         <is>
@@ -25438,7 +25438,7 @@
         <v>46205.45901322916</v>
       </c>
       <c r="S229" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T229" t="inlineStr">
         <is>
@@ -25549,7 +25549,7 @@
         <v>46206.79231805556</v>
       </c>
       <c r="S230" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T230" t="inlineStr">
         <is>
@@ -25660,7 +25660,7 @@
         <v>46204.37531446759</v>
       </c>
       <c r="S231" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T231" t="inlineStr">
         <is>
@@ -25771,7 +25771,7 @@
         <v>46204.37541623843</v>
       </c>
       <c r="S232" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T232" t="inlineStr">
         <is>
@@ -25882,7 +25882,7 @@
         <v>46204.37531940972</v>
       </c>
       <c r="S233" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T233" t="inlineStr">
         <is>
@@ -25993,7 +25993,7 @@
         <v>46206.79216188657</v>
       </c>
       <c r="S234" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T234" t="inlineStr">
         <is>
@@ -26104,7 +26104,7 @@
         <v>46206.79215482639</v>
       </c>
       <c r="S235" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T235" t="inlineStr">
         <is>
@@ -26215,7 +26215,7 @@
         <v>46204.375303125</v>
       </c>
       <c r="S236" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T236" t="inlineStr">
         <is>
@@ -26326,7 +26326,7 @@
         <v>46205.45874525463</v>
       </c>
       <c r="S237" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T237" t="inlineStr">
         <is>
@@ -26437,7 +26437,7 @@
         <v>46204.37542565972</v>
       </c>
       <c r="S238" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T238" t="inlineStr">
         <is>
@@ -26548,7 +26548,7 @@
         <v>46206.79216226852</v>
       </c>
       <c r="S239" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T239" t="inlineStr">
         <is>
@@ -26659,7 +26659,7 @@
         <v>46204.45863723379</v>
       </c>
       <c r="S240" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T240" t="inlineStr">
         <is>
@@ -26770,7 +26770,7 @@
         <v>46206.79216269676</v>
       </c>
       <c r="S241" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T241" t="inlineStr">
         <is>
@@ -26877,7 +26877,7 @@
         <v>46205.4461572338</v>
       </c>
       <c r="S242" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="T242" t="inlineStr">
         <is>
@@ -26992,7 +26992,7 @@
         <v>46211.34394196759</v>
       </c>
       <c r="S243" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T243" t="inlineStr">
         <is>
@@ -27103,7 +27103,7 @@
         <v>46209.34400659722</v>
       </c>
       <c r="S244" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T244" t="inlineStr">
         <is>
@@ -27214,7 +27214,7 @@
         <v>46209.34400416667</v>
       </c>
       <c r="S245" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T245" t="inlineStr">
         <is>
@@ -27325,7 +27325,7 @@
         <v>46209.37540871528</v>
       </c>
       <c r="S246" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T246" t="inlineStr">
         <is>
@@ -27436,7 +27436,7 @@
         <v>46206.76069471065</v>
       </c>
       <c r="S247" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T247" t="inlineStr">
         <is>
@@ -27547,7 +27547,7 @@
         <v>46206.76073368055</v>
       </c>
       <c r="S248" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T248" t="inlineStr">
         <is>
@@ -27658,7 +27658,7 @@
         <v>46209.37538854167</v>
       </c>
       <c r="S249" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T249" t="inlineStr">
         <is>
@@ -27769,7 +27769,7 @@
         <v>46205.42742766203</v>
       </c>
       <c r="S250" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T250" t="inlineStr">
         <is>
@@ -27880,7 +27880,7 @@
         <v>46209.3754105324</v>
       </c>
       <c r="S251" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T251" t="inlineStr">
         <is>
@@ -27991,7 +27991,7 @@
         <v>46206.76073530092</v>
       </c>
       <c r="S252" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T252" t="inlineStr">
         <is>
@@ -28102,7 +28102,7 @@
         <v>46209.37540651621</v>
       </c>
       <c r="S253" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T253" t="inlineStr">
         <is>
@@ -28213,7 +28213,7 @@
         <v>46206.76073472222</v>
       </c>
       <c r="S254" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T254" t="inlineStr">
         <is>
@@ -28320,7 +28320,7 @@
         <v>46206.47265292824</v>
       </c>
       <c r="S255" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T255" t="inlineStr">
         <is>
@@ -28428,7 +28428,7 @@
         <v>46213.43891172454</v>
       </c>
       <c r="S256" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="T256" t="inlineStr">
         <is>
@@ -28547,7 +28547,7 @@
         <v>46209.74627188657</v>
       </c>
       <c r="S257" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T257" t="inlineStr">
         <is>
@@ -28662,7 +28662,7 @@
         <v>46206.50269079861</v>
       </c>
       <c r="S258" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T258" t="inlineStr">
         <is>
@@ -28777,7 +28777,7 @@
         <v>46209.7462744213</v>
       </c>
       <c r="S259" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T259" t="inlineStr">
         <is>
@@ -28892,7 +28892,7 @@
         <v>46209.62289283565</v>
       </c>
       <c r="S260" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T260" t="inlineStr">
         <is>
@@ -29007,7 +29007,7 @@
         <v>46210.7847958912</v>
       </c>
       <c r="S261" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T261" t="inlineStr">
         <is>
@@ -29126,7 +29126,7 @@
         <v>46210.80248869213</v>
       </c>
       <c r="S262" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T262" t="inlineStr">
         <is>
@@ -29245,7 +29245,7 @@
         <v>46210.78479861111</v>
       </c>
       <c r="S263" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T263" t="inlineStr">
         <is>
@@ -29364,7 +29364,7 @@
         <v>46210.78479896991</v>
       </c>
       <c r="S264" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T264" t="inlineStr">
         <is>
@@ -29479,7 +29479,7 @@
         <v>46206.50244357639</v>
       </c>
       <c r="S265" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T265" t="inlineStr">
         <is>
@@ -29594,7 +29594,7 @@
         <v>46210.80248940973</v>
       </c>
       <c r="S266" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T266" t="inlineStr">
         <is>
@@ -29709,7 +29709,7 @@
         <v>46206.50244393518</v>
       </c>
       <c r="S267" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T267" t="inlineStr">
         <is>
@@ -29824,7 +29824,7 @@
         <v>46210.80249175926</v>
       </c>
       <c r="S268" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T268" t="inlineStr">
         <is>
@@ -29943,7 +29943,7 @@
         <v>46213.41471872685</v>
       </c>
       <c r="S269" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T269" t="inlineStr">
         <is>
@@ -30062,7 +30062,7 @@
         <v>46213.41472034722</v>
       </c>
       <c r="S270" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T270" t="inlineStr">
         <is>
@@ -30177,7 +30177,7 @@
         <v>46213.41472866898</v>
       </c>
       <c r="S271" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T271" t="inlineStr">
         <is>
@@ -30292,7 +30292,7 @@
         <v>46211.67827373843</v>
       </c>
       <c r="S272" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T272" t="inlineStr">
         <is>
@@ -30407,7 +30407,7 @@
         <v>46205.45901570602</v>
       </c>
       <c r="S273" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T273" t="inlineStr">
         <is>
@@ -30518,7 +30518,7 @@
         <v>46206.79257369213</v>
       </c>
       <c r="S274" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T274" t="inlineStr">
         <is>
@@ -30629,7 +30629,7 @@
         <v>46205.45918969908</v>
       </c>
       <c r="S275" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T275" t="inlineStr">
         <is>
@@ -30744,7 +30744,7 @@
         <v>46211.37590150463</v>
       </c>
       <c r="S276" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T276" t="inlineStr">
         <is>
@@ -30859,7 +30859,7 @@
         <v>46206.79256712963</v>
       </c>
       <c r="S277" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T277" t="inlineStr">
         <is>
@@ -30966,7 +30966,7 @@
         <v>46206.7921721875</v>
       </c>
       <c r="S278" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T278" t="inlineStr">
         <is>
@@ -31077,7 +31077,7 @@
         <v>46213.79217554398</v>
       </c>
       <c r="S279" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T279" t="inlineStr">
         <is>
@@ -31188,7 +31188,7 @@
         <v>46206.7921681713</v>
       </c>
       <c r="S280" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T280" t="inlineStr">
         <is>
@@ -31295,7 +31295,7 @@
         <v>46210.37424872685</v>
       </c>
       <c r="S281" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="T281" t="inlineStr">
         <is>
@@ -31410,7 +31410,7 @@
         <v>46205.76232731481</v>
       </c>
       <c r="S282" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="T282" t="inlineStr">
         <is>
@@ -31521,7 +31521,7 @@
         <v>46205.7623278588</v>
       </c>
       <c r="S283" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="T283" t="inlineStr">
         <is>
@@ -31632,7 +31632,7 @@
         <v>46205.76232913195</v>
       </c>
       <c r="S284" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="T284" t="inlineStr">
         <is>
@@ -31743,7 +31743,7 @@
         <v>46211.39581168981</v>
       </c>
       <c r="S285" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="T285" t="inlineStr">
         <is>
@@ -31854,7 +31854,7 @@
         <v>46210.67626055556</v>
       </c>
       <c r="S286" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T286" t="inlineStr">
         <is>
@@ -31965,7 +31965,7 @@
         <v>46210.60626501157</v>
       </c>
       <c r="S287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T287" t="inlineStr">
         <is>
@@ -32076,7 +32076,7 @@
         <v>46213.64570789352</v>
       </c>
       <c r="S288" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T288" t="inlineStr">
         <is>
@@ -32183,7 +32183,7 @@
         <v>46213.6457087963</v>
       </c>
       <c r="S289" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T289" t="inlineStr">
         <is>
@@ -32290,7 +32290,7 @@
         <v>46210.76622931713</v>
       </c>
       <c r="S290" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T290" t="inlineStr">
         <is>
@@ -32401,7 +32401,7 @@
         <v>46210.6898024537</v>
       </c>
       <c r="S291" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T291" t="inlineStr">
         <is>
@@ -32508,7 +32508,7 @@
         <v>46210.76516364583</v>
       </c>
       <c r="S292" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T292" t="inlineStr">
         <is>
@@ -32619,7 +32619,7 @@
         <v>46213.34372746528</v>
       </c>
       <c r="S293" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T293" t="inlineStr">
         <is>
@@ -32730,7 +32730,7 @@
         <v>46213.63923525463</v>
       </c>
       <c r="S294" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T294" t="inlineStr">
         <is>
@@ -32841,7 +32841,7 @@
         <v>46213.63947451389</v>
       </c>
       <c r="S295" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T295" t="inlineStr">
         <is>
@@ -32948,7 +32948,7 @@
         <v>46213.64188018518</v>
       </c>
       <c r="S296" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T296" t="inlineStr">
         <is>
@@ -33055,7 +33055,7 @@
         <v>46210.68980878472</v>
       </c>
       <c r="S297" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T297" t="inlineStr">
         <is>
@@ -33158,7 +33158,7 @@
         <v>46213.64228201389</v>
       </c>
       <c r="S298" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T298" t="inlineStr">
         <is>
@@ -33265,7 +33265,7 @@
         <v>46213.35361152777</v>
       </c>
       <c r="S299" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T299" t="inlineStr">
         <is>
@@ -33372,7 +33372,7 @@
         <v>46206.65276246528</v>
       </c>
       <c r="S300" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T300" t="inlineStr">
         <is>
@@ -33479,7 +33479,7 @@
         <v>46206.65277079861</v>
       </c>
       <c r="S301" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T301" t="inlineStr">
         <is>
@@ -33586,7 +33586,7 @@
         <v>46206.65274155093</v>
       </c>
       <c r="S302" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T302" t="inlineStr">
         <is>
@@ -33693,7 +33693,7 @@
         <v>46206.65274189815</v>
       </c>
       <c r="S303" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T303" t="inlineStr">
         <is>
@@ -33800,7 +33800,7 @@
         <v>46206.65274228009</v>
       </c>
       <c r="S304" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T304" t="inlineStr">
         <is>
@@ -33907,7 +33907,7 @@
         <v>46206.65275096065</v>
       </c>
       <c r="S305" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T305" t="inlineStr">
         <is>
@@ -34014,7 +34014,7 @@
         <v>46206.65275582176</v>
       </c>
       <c r="S306" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T306" t="inlineStr">
         <is>
@@ -34121,7 +34121,7 @@
         <v>46206.65276396991</v>
       </c>
       <c r="S307" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T307" t="inlineStr">
         <is>
@@ -34228,7 +34228,7 @@
         <v>46206.65277951389</v>
       </c>
       <c r="S308" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T308" t="inlineStr">
         <is>
@@ -34335,7 +34335,7 @@
         <v>46206.65278059028</v>
       </c>
       <c r="S309" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T309" t="inlineStr">
         <is>
@@ -34442,7 +34442,7 @@
         <v>46206.65278711806</v>
       </c>
       <c r="S310" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T310" t="inlineStr">
         <is>
@@ -34549,7 +34549,7 @@
         <v>46206.65278746527</v>
       </c>
       <c r="S311" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T311" t="inlineStr">
         <is>
@@ -34656,7 +34656,7 @@
         <v>46206.65278857639</v>
       </c>
       <c r="S312" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T312" t="inlineStr">
         <is>
@@ -34763,7 +34763,7 @@
         <v>46206.65279270833</v>
       </c>
       <c r="S313" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T313" t="inlineStr">
         <is>
@@ -34866,7 +34866,7 @@
         <v>46206.65279922454</v>
       </c>
       <c r="S314" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T314" t="inlineStr">
         <is>
@@ -34969,7 +34969,7 @@
         <v>46206.65280755787</v>
       </c>
       <c r="S315" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T315" t="inlineStr">
         <is>
@@ -35072,7 +35072,7 @@
         <v>46206.65280844907</v>
       </c>
       <c r="S316" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T316" t="inlineStr">
         <is>
@@ -35175,7 +35175,7 @@
         <v>46206.65280972223</v>
       </c>
       <c r="S317" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T317" t="inlineStr">
         <is>
@@ -35278,7 +35278,7 @@
         <v>46206.65281026621</v>
       </c>
       <c r="S318" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T318" t="inlineStr">
         <is>
@@ -35381,7 +35381,7 @@
         <v>46203.79329967593</v>
       </c>
       <c r="S319" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T319" t="inlineStr">
         <is>
@@ -35488,7 +35488,7 @@
         <v>46203.79332754629</v>
       </c>
       <c r="S320" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T320" t="inlineStr">
         <is>
@@ -35595,7 +35595,7 @@
         <v>46203.79350829861</v>
       </c>
       <c r="S321" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T321" t="inlineStr">
         <is>
@@ -35702,7 +35702,7 @@
         <v>46203.79357234954</v>
       </c>
       <c r="S322" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T322" t="inlineStr">
         <is>
@@ -35809,7 +35809,7 @@
         <v>46203.7936177662</v>
       </c>
       <c r="S323" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T323" t="inlineStr">
         <is>
@@ -35916,7 +35916,7 @@
         <v>46203.79366831019</v>
       </c>
       <c r="S324" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T324" t="inlineStr">
         <is>
@@ -36023,7 +36023,7 @@
         <v>46203.79371640046</v>
       </c>
       <c r="S325" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T325" t="inlineStr">
         <is>
@@ -36130,7 +36130,7 @@
         <v>46203.79372402778</v>
       </c>
       <c r="S326" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T326" t="inlineStr">
         <is>
@@ -36237,7 +36237,7 @@
         <v>46203.79376344907</v>
       </c>
       <c r="S327" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T327" t="inlineStr">
         <is>
@@ -36344,7 +36344,7 @@
         <v>46203.79376959491</v>
       </c>
       <c r="S328" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T328" t="inlineStr">
         <is>
@@ -36451,7 +36451,7 @@
         <v>46203.79377528935</v>
       </c>
       <c r="S329" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T329" t="inlineStr">
         <is>
@@ -36558,7 +36558,7 @@
         <v>46204.5021846875</v>
       </c>
       <c r="S330" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T330" t="inlineStr">
         <is>
@@ -36661,7 +36661,7 @@
         <v>46203.79384251157</v>
       </c>
       <c r="S331" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T331" t="inlineStr">
         <is>
@@ -36764,7 +36764,7 @@
         <v>46204.50231476852</v>
       </c>
       <c r="S332" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T332" t="inlineStr">
         <is>
@@ -36867,7 +36867,7 @@
         <v>46204.77955170139</v>
       </c>
       <c r="S333" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T333" t="inlineStr">
         <is>
@@ -36970,7 +36970,7 @@
         <v>46204.77955260417</v>
       </c>
       <c r="S334" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T334" t="inlineStr">
         <is>
@@ -37073,7 +37073,7 @@
         <v>46204.77955333333</v>
       </c>
       <c r="S335" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T335" t="inlineStr">
         <is>
@@ -37176,7 +37176,7 @@
         <v>46196.70294318287</v>
       </c>
       <c r="S336" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T336" t="inlineStr">
         <is>
@@ -37283,7 +37283,7 @@
         <v>46196.70294915509</v>
       </c>
       <c r="S337" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T337" t="inlineStr">
         <is>
@@ -37390,7 +37390,7 @@
         <v>46196.70300431713</v>
       </c>
       <c r="S338" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T338" t="inlineStr">
         <is>
@@ -37497,7 +37497,7 @@
         <v>46196.70300539352</v>
       </c>
       <c r="S339" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T339" t="inlineStr">
         <is>
@@ -37604,7 +37604,7 @@
         <v>46196.70300612268</v>
       </c>
       <c r="S340" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T340" t="inlineStr">
         <is>
@@ -37711,7 +37711,7 @@
         <v>46196.70301788195</v>
       </c>
       <c r="S341" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T341" t="inlineStr">
         <is>
@@ -37818,7 +37818,7 @@
         <v>46196.70303107639</v>
       </c>
       <c r="S342" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T342" t="inlineStr">
         <is>
@@ -37925,7 +37925,7 @@
         <v>46196.70303379629</v>
       </c>
       <c r="S343" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T343" t="inlineStr">
         <is>
@@ -38032,7 +38032,7 @@
         <v>46196.70303469907</v>
       </c>
       <c r="S344" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T344" t="inlineStr">
         <is>
@@ -38139,7 +38139,7 @@
         <v>46196.70303524305</v>
       </c>
       <c r="S345" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T345" t="inlineStr">
         <is>
@@ -38246,7 +38246,7 @@
         <v>46196.70304373842</v>
       </c>
       <c r="S346" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T346" t="inlineStr">
         <is>
@@ -38349,7 +38349,7 @@
         <v>46196.70304771991</v>
       </c>
       <c r="S347" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T347" t="inlineStr">
         <is>
@@ -38452,7 +38452,7 @@
         <v>46206.65312673611</v>
       </c>
       <c r="S348" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T348" t="inlineStr">
         <is>
@@ -38559,7 +38559,7 @@
         <v>46206.65314806713</v>
       </c>
       <c r="S349" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T349" t="inlineStr">
         <is>
@@ -38666,7 +38666,7 @@
         <v>46206.6533227662</v>
       </c>
       <c r="S350" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T350" t="inlineStr">
         <is>
@@ -38773,7 +38773,7 @@
         <v>46206.65332584491</v>
       </c>
       <c r="S351" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T351" t="inlineStr">
         <is>
@@ -38880,7 +38880,7 @@
         <v>46206.65332746528</v>
       </c>
       <c r="S352" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T352" t="inlineStr">
         <is>
@@ -38987,7 +38987,7 @@
         <v>46206.6533497338</v>
       </c>
       <c r="S353" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T353" t="inlineStr">
         <is>
@@ -39094,7 +39094,7 @@
         <v>46206.65335243056</v>
       </c>
       <c r="S354" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T354" t="inlineStr">
         <is>
@@ -39201,7 +39201,7 @@
         <v>46206.65335459491</v>
       </c>
       <c r="S355" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T355" t="inlineStr">
         <is>
@@ -39308,7 +39308,7 @@
         <v>46206.6533571412</v>
       </c>
       <c r="S356" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T356" t="inlineStr">
         <is>
@@ -39415,7 +39415,7 @@
         <v>46206.65335732639</v>
       </c>
       <c r="S357" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T357" t="inlineStr">
         <is>
@@ -39522,7 +39522,7 @@
         <v>46206.65336203704</v>
       </c>
       <c r="S358" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T358" t="inlineStr">
         <is>
@@ -39629,7 +39629,7 @@
         <v>46206.65336258102</v>
       </c>
       <c r="S359" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T359" t="inlineStr">
         <is>
@@ -39736,7 +39736,7 @@
         <v>46206.65336273148</v>
       </c>
       <c r="S360" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T360" t="inlineStr">
         <is>
@@ -39843,7 +39843,7 @@
         <v>46206.65336582176</v>
       </c>
       <c r="S361" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T361" t="inlineStr">
         <is>
@@ -39946,7 +39946,7 @@
         <v>46206.65337017361</v>
       </c>
       <c r="S362" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T362" t="inlineStr">
         <is>
@@ -40049,7 +40049,7 @@
         <v>46206.65337484953</v>
       </c>
       <c r="S363" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T363" t="inlineStr">
         <is>
@@ -40152,7 +40152,7 @@
         <v>46206.6533755787</v>
       </c>
       <c r="S364" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T364" t="inlineStr">
         <is>
@@ -40255,7 +40255,7 @@
         <v>46206.65337596065</v>
       </c>
       <c r="S365" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T365" t="inlineStr">
         <is>
@@ -40358,7 +40358,7 @@
         <v>46206.65337630787</v>
       </c>
       <c r="S366" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T366" t="inlineStr">
         <is>
@@ -40461,7 +40461,7 @@
         <v>46203.79329930556</v>
       </c>
       <c r="S367" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T367" t="inlineStr">
         <is>
@@ -40568,7 +40568,7 @@
         <v>46203.79332729166</v>
       </c>
       <c r="S368" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T368" t="inlineStr">
         <is>
@@ -40675,7 +40675,7 @@
         <v>46203.79350855324</v>
       </c>
       <c r="S369" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T369" t="inlineStr">
         <is>
@@ -40782,7 +40782,7 @@
         <v>46203.79357210648</v>
       </c>
       <c r="S370" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T370" t="inlineStr">
         <is>
@@ -40889,7 +40889,7 @@
         <v>46203.79361802083</v>
       </c>
       <c r="S371" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T371" t="inlineStr">
         <is>
@@ -40996,7 +40996,7 @@
         <v>46203.7936680787</v>
       </c>
       <c r="S372" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T372" t="inlineStr">
         <is>
@@ -41103,7 +41103,7 @@
         <v>46203.79371605324</v>
       </c>
       <c r="S373" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T373" t="inlineStr">
         <is>
@@ -41210,7 +41210,7 @@
         <v>46203.79372373842</v>
       </c>
       <c r="S374" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T374" t="inlineStr">
         <is>
@@ -41317,7 +41317,7 @@
         <v>46203.79376369213</v>
       </c>
       <c r="S375" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T375" t="inlineStr">
         <is>
@@ -41424,7 +41424,7 @@
         <v>46203.79376936342</v>
       </c>
       <c r="S376" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T376" t="inlineStr">
         <is>
@@ -41531,7 +41531,7 @@
         <v>46203.79377502315</v>
       </c>
       <c r="S377" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T377" t="inlineStr">
         <is>
@@ -41638,7 +41638,7 @@
         <v>46204.50218425926</v>
       </c>
       <c r="S378" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T378" t="inlineStr">
         <is>
@@ -41741,7 +41741,7 @@
         <v>46203.79384278935</v>
       </c>
       <c r="S379" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T379" t="inlineStr">
         <is>
@@ -41844,7 +41844,7 @@
         <v>46204.50231513889</v>
       </c>
       <c r="S380" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T380" t="inlineStr">
         <is>
@@ -41947,7 +41947,7 @@
         <v>46213.47701689815</v>
       </c>
       <c r="S381" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T381" t="inlineStr">
         <is>
@@ -42050,7 +42050,7 @@
         <v>46213.4770175926</v>
       </c>
       <c r="S382" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T382" t="inlineStr">
         <is>
@@ -42153,7 +42153,7 @@
         <v>46213.4770175926</v>
       </c>
       <c r="S383" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T383" t="inlineStr">
         <is>
@@ -42256,7 +42256,7 @@
         <v>46213.56919034723</v>
       </c>
       <c r="S384" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T384" t="inlineStr">
         <is>
@@ -42363,7 +42363,7 @@
         <v>46213.56920064815</v>
       </c>
       <c r="S385" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T385" t="inlineStr">
         <is>
@@ -42470,7 +42470,7 @@
         <v>46213.56920517361</v>
       </c>
       <c r="S386" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T386" t="inlineStr">
         <is>
@@ -42577,7 +42577,7 @@
         <v>46206.39939344907</v>
       </c>
       <c r="S387" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T387" t="inlineStr">
         <is>
@@ -42689,7 +42689,7 @@
         <v>46205.46612821759</v>
       </c>
       <c r="S388" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T388" t="inlineStr">
         <is>
@@ -42801,7 +42801,7 @@
         <v>46205.44509731481</v>
       </c>
       <c r="S389" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T389" t="inlineStr">
         <is>
@@ -42913,7 +42913,7 @@
         <v>46206.40619622685</v>
       </c>
       <c r="S390" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T390" t="inlineStr">
         <is>

--- a/dados/base/goias.xlsx
+++ b/dados/base/goias.xlsx
@@ -84502,7 +84502,7 @@
       </c>
       <c r="R789" t="inlineStr"/>
       <c r="S789" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T789" t="inlineStr">
         <is>
@@ -84606,7 +84606,7 @@
       </c>
       <c r="R790" t="inlineStr"/>
       <c r="S790" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T790" t="inlineStr">
         <is>
@@ -84710,7 +84710,7 @@
       </c>
       <c r="R791" t="inlineStr"/>
       <c r="S791" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T791" t="inlineStr">
         <is>
@@ -84810,7 +84810,7 @@
       </c>
       <c r="R792" t="inlineStr"/>
       <c r="S792" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T792" t="inlineStr">
         <is>
@@ -84918,7 +84918,7 @@
       </c>
       <c r="R793" t="inlineStr"/>
       <c r="S793" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T793" t="inlineStr">
         <is>
@@ -85026,7 +85026,7 @@
       </c>
       <c r="R794" t="inlineStr"/>
       <c r="S794" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T794" t="inlineStr">
         <is>
@@ -85138,7 +85138,7 @@
       </c>
       <c r="R795" t="inlineStr"/>
       <c r="S795" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T795" t="inlineStr">
         <is>
@@ -85242,7 +85242,7 @@
       </c>
       <c r="R796" t="inlineStr"/>
       <c r="S796" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T796" t="inlineStr">
         <is>
@@ -85346,7 +85346,7 @@
       </c>
       <c r="R797" t="inlineStr"/>
       <c r="S797" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T797" t="inlineStr">
         <is>
@@ -85450,7 +85450,7 @@
       </c>
       <c r="R798" t="inlineStr"/>
       <c r="S798" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="T798" t="inlineStr">
         <is>
@@ -85565,7 +85565,7 @@
       </c>
       <c r="R799" t="inlineStr"/>
       <c r="S799" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="T799" t="inlineStr">
         <is>
@@ -85680,7 +85680,7 @@
       </c>
       <c r="R800" t="inlineStr"/>
       <c r="S800" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T800" t="inlineStr">
         <is>
@@ -85795,7 +85795,7 @@
       </c>
       <c r="R801" t="inlineStr"/>
       <c r="S801" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T801" t="inlineStr">
         <is>
@@ -85898,7 +85898,7 @@
       </c>
       <c r="R802" t="inlineStr"/>
       <c r="S802" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T802" t="inlineStr">
         <is>
@@ -86001,7 +86001,7 @@
       </c>
       <c r="R803" t="inlineStr"/>
       <c r="S803" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T803" t="inlineStr">
         <is>
@@ -86108,7 +86108,7 @@
       </c>
       <c r="R804" t="inlineStr"/>
       <c r="S804" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="T804" t="inlineStr">
         <is>

--- a/dados/base/goias.xlsx
+++ b/dados/base/goias.xlsx
@@ -84556,7 +84556,7 @@
       </c>
       <c r="R789" t="inlineStr"/>
       <c r="S789" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T789" t="inlineStr">
         <is>
@@ -84660,7 +84660,7 @@
       </c>
       <c r="R790" t="inlineStr"/>
       <c r="S790" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T790" t="inlineStr">
         <is>
@@ -84764,7 +84764,7 @@
       </c>
       <c r="R791" t="inlineStr"/>
       <c r="S791" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T791" t="inlineStr">
         <is>
@@ -84864,7 +84864,7 @@
       </c>
       <c r="R792" t="inlineStr"/>
       <c r="S792" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T792" t="inlineStr">
         <is>
@@ -84972,7 +84972,7 @@
       </c>
       <c r="R793" t="inlineStr"/>
       <c r="S793" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T793" t="inlineStr">
         <is>
@@ -85080,7 +85080,7 @@
       </c>
       <c r="R794" t="inlineStr"/>
       <c r="S794" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T794" t="inlineStr">
         <is>
@@ -85192,7 +85192,7 @@
       </c>
       <c r="R795" t="inlineStr"/>
       <c r="S795" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T795" t="inlineStr">
         <is>
@@ -85296,7 +85296,7 @@
       </c>
       <c r="R796" t="inlineStr"/>
       <c r="S796" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T796" t="inlineStr">
         <is>
@@ -85400,7 +85400,7 @@
       </c>
       <c r="R797" t="inlineStr"/>
       <c r="S797" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T797" t="inlineStr">
         <is>
@@ -85504,7 +85504,7 @@
       </c>
       <c r="R798" t="inlineStr"/>
       <c r="S798" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="T798" t="inlineStr">
         <is>
@@ -85619,7 +85619,7 @@
       </c>
       <c r="R799" t="inlineStr"/>
       <c r="S799" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="T799" t="inlineStr">
         <is>
@@ -85734,7 +85734,7 @@
       </c>
       <c r="R800" t="inlineStr"/>
       <c r="S800" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T800" t="inlineStr">
         <is>
@@ -85849,7 +85849,7 @@
       </c>
       <c r="R801" t="inlineStr"/>
       <c r="S801" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T801" t="inlineStr">
         <is>
@@ -85952,7 +85952,7 @@
       </c>
       <c r="R802" t="inlineStr"/>
       <c r="S802" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T802" t="inlineStr">
         <is>
@@ -86055,7 +86055,7 @@
       </c>
       <c r="R803" t="inlineStr"/>
       <c r="S803" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T803" t="inlineStr">
         <is>
@@ -86162,7 +86162,7 @@
       </c>
       <c r="R804" t="inlineStr"/>
       <c r="S804" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="T804" t="inlineStr">
         <is>

--- a/dados/base/goias.xlsx
+++ b/dados/base/goias.xlsx
@@ -2366,7 +2366,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2403,8 +2403,8 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 13/07/2026 
-Foi enviada para a empresa planilha de reajuste e informações sobre termo aditivo do sindicato. Estamos aguardando retorno para aplicação e calculo das complementares. - Data Comentário: 07/07/2026 16:24</t>
+          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 14/07/2026 
+Foi enviada para a empresa planilha de reajuste e informações sobre termo aditivo do sindicato. Estamos aguardando retorno para aplicação e calculo das complementares. - Data Comentário: 13/07/2026 09:43</t>
         </is>
       </c>
       <c r="W18" t="inlineStr"/>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2828,8 +2828,8 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 13/07/2026 
-PREVISÃO DE CONCLUSÃO: 13/07/2026 - Data Comentário: 07/07/2026 16:32</t>
+          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 14/07/2026 
+PREVISÃO DE CONCLUSÃO: 14/07/2026 - Data Comentário: 13/07/2026 09:52</t>
         </is>
       </c>
       <c r="W22" t="inlineStr"/>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2942,8 +2942,8 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 14/07/2026 
-Previsão pra finalizar em 14/07/2026 - Data Comentário: 13/07/2026 08:27</t>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 15/07/2026 
+Previsão pra finalizar em 15/07/2026 - Data Comentário: 13/07/2026 09:06</t>
         </is>
       </c>
       <c r="W23" t="inlineStr"/>
@@ -3468,7 +3468,11 @@
       <c r="L28" s="1" t="n">
         <v>46218</v>
       </c>
-      <c r="M28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr">
         <is>
           <t>06/2026</t>
@@ -3497,7 +3501,12 @@
         </is>
       </c>
       <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 14/07/2026 
+Previsão de conclusão: 14/07/2026 - Data Comentário: 13/07/2026 09:31</t>
+        </is>
+      </c>
       <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr"/>
       <c r="Y28" t="inlineStr"/>
@@ -3569,7 +3578,11 @@
       <c r="L29" s="1" t="n">
         <v>46218</v>
       </c>
-      <c r="M29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr">
         <is>
           <t>06/2026</t>
@@ -3598,7 +3611,12 @@
         </is>
       </c>
       <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 14/07/2026 
+Empresa em implantação. - Data Comentário: 13/07/2026 09:25</t>
+        </is>
+      </c>
       <c r="W29" t="inlineStr"/>
       <c r="X29" t="inlineStr"/>
       <c r="Y29" t="inlineStr"/>
@@ -84601,12 +84619,12 @@
       <c r="AC789" t="inlineStr"/>
       <c r="AD789" t="inlineStr">
         <is>
-          <t>Aguardando implantação do cliente para que seja possível a realização da tarefa - AI09 - Data Comentário: 06/07/2026 12:41</t>
+          <t>Aguardando implantação do cliente para que seja possível a realização da tarefa - AI09. - Data Comentário: 13/07/2026 09:09</t>
         </is>
       </c>
       <c r="AE789" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="AF789" t="inlineStr">
@@ -84709,12 +84727,12 @@
       <c r="AC790" t="inlineStr"/>
       <c r="AD790" t="inlineStr">
         <is>
-          <t>Aguardando implantação do cliente para que seja possível a realização da tarefa - AI09 - Data Comentário: 06/07/2026 12:41</t>
+          <t>Aguardando implantação do cliente para que seja possível a realização da tarefa - AI09. - Data Comentário: 13/07/2026 09:09</t>
         </is>
       </c>
       <c r="AE790" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="AF790" t="inlineStr">
@@ -84817,12 +84835,12 @@
       <c r="AC791" t="inlineStr"/>
       <c r="AD791" t="inlineStr">
         <is>
-          <t>Aguardando implantação do cliente para que seja possível a realização da tarefa - AI09 - Data Comentário: 06/07/2026 12:41</t>
+          <t>Aguardando implantação do cliente para que seja possível a realização da tarefa - AI09. - Data Comentário: 13/07/2026 09:09</t>
         </is>
       </c>
       <c r="AE791" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="AF791" t="inlineStr">
@@ -84932,12 +84950,12 @@
       <c r="AC792" t="inlineStr"/>
       <c r="AD792" t="inlineStr">
         <is>
-          <t>A operação e o GC estão ajustando os créditos de meses anteriores para que o valor desse mês seja ajustado. A Gerente Priscila Volpe está em contato direto com o GC e informou que a tarefa deve ser concluída até o fim desta semana. - Data Comentário: 06/07/2026 12:41</t>
+          <t>A operação e o GC estão ajustando os créditos de meses anteriores para que o valor desse mês seja ajustado. A Gerente Priscila Volpe está em contato direto com o GC e informou que a tarefa será concluída o quanto antes - Data Comentário: 13/07/2026 09:09</t>
         </is>
       </c>
       <c r="AE792" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="AF792" t="inlineStr">
@@ -85162,12 +85180,12 @@
       <c r="AC794" t="inlineStr"/>
       <c r="AD794" t="inlineStr">
         <is>
-          <t>Atraso do cliente, o atraso do cliente já é recorrente e de ciência do Master e do Gerente de Contas. - Data Comentário: 10/07/2026 10:23</t>
+          <t>Atraso do cliente, o atraso do cliente já é recorrente e de ciência do Master e do Gerente de Contas. - Data Comentário: 10/07/2026 10:23 - Data Comentário: 13/07/2026 09:09</t>
         </is>
       </c>
       <c r="AE794" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="AF794" t="inlineStr">

--- a/dados/base/goias.xlsx
+++ b/dados/base/goias.xlsx
@@ -2478,7 +2478,11 @@
       <c r="L19" s="1" t="n">
         <v>46218</v>
       </c>
-      <c r="M19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr">
         <is>
           <t>06/2026</t>
@@ -2511,7 +2515,12 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr"/>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 14/07/2026 
+Em processo de emissão - Data Comentário: 13/07/2026 11:58</t>
+        </is>
+      </c>
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr"/>
       <c r="Y19" t="inlineStr"/>
@@ -4767,7 +4776,11 @@
       <c r="L40" s="1" t="n">
         <v>46218</v>
       </c>
-      <c r="M40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>15/07/2026</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr">
         <is>
           <t>06/2026</t>
@@ -4800,7 +4813,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V40" t="inlineStr"/>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 15/07/2026 - Data Comentário: 13/07/2026 12:06</t>
+        </is>
+      </c>
       <c r="W40" t="inlineStr"/>
       <c r="X40" t="inlineStr"/>
       <c r="Y40" t="inlineStr"/>
@@ -4872,7 +4889,11 @@
       <c r="L41" s="1" t="n">
         <v>46216</v>
       </c>
-      <c r="M41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr">
         <is>
           <t>06/2026</t>
@@ -4905,7 +4926,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr"/>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 13/07/2026 - Data Comentário: 13/07/2026 12:04</t>
+        </is>
+      </c>
       <c r="W41" t="inlineStr"/>
       <c r="X41" t="inlineStr"/>
       <c r="Y41" t="inlineStr"/>
@@ -4977,7 +5002,11 @@
       <c r="L42" s="1" t="n">
         <v>46216</v>
       </c>
-      <c r="M42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr">
         <is>
           <t>06/2026</t>
@@ -5010,7 +5039,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr"/>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 13/07/2026 - Data Comentário: 13/07/2026 12:04</t>
+        </is>
+      </c>
       <c r="W42" t="inlineStr"/>
       <c r="X42" t="inlineStr"/>
       <c r="Y42" t="inlineStr"/>
@@ -5082,7 +5115,11 @@
       <c r="L43" s="1" t="n">
         <v>46216</v>
       </c>
-      <c r="M43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr">
         <is>
           <t>06/2026</t>
@@ -5115,7 +5152,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr"/>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 13/07/2026 - Data Comentário: 13/07/2026 12:04</t>
+        </is>
+      </c>
       <c r="W43" t="inlineStr"/>
       <c r="X43" t="inlineStr"/>
       <c r="Y43" t="inlineStr"/>
@@ -5187,7 +5228,11 @@
       <c r="L44" s="1" t="n">
         <v>46216</v>
       </c>
-      <c r="M44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr">
         <is>
           <t>06/2026</t>
@@ -5220,7 +5265,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V44" t="inlineStr"/>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 13/07/2026 - Data Comentário: 13/07/2026 12:04</t>
+        </is>
+      </c>
       <c r="W44" t="inlineStr"/>
       <c r="X44" t="inlineStr"/>
       <c r="Y44" t="inlineStr"/>
@@ -5292,7 +5341,11 @@
       <c r="L45" s="1" t="n">
         <v>46216</v>
       </c>
-      <c r="M45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr">
         <is>
           <t>06/2026</t>
@@ -5325,7 +5378,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V45" t="inlineStr"/>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 13/07/2026 - Data Comentário: 13/07/2026 12:04</t>
+        </is>
+      </c>
       <c r="W45" t="inlineStr"/>
       <c r="X45" t="inlineStr"/>
       <c r="Y45" t="inlineStr"/>
@@ -5397,7 +5454,11 @@
       <c r="L46" s="1" t="n">
         <v>46216</v>
       </c>
-      <c r="M46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr">
         <is>
           <t>06/2026</t>
@@ -5430,7 +5491,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V46" t="inlineStr"/>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 13/07/2026 - Data Comentário: 13/07/2026 12:04</t>
+        </is>
+      </c>
       <c r="W46" t="inlineStr"/>
       <c r="X46" t="inlineStr"/>
       <c r="Y46" t="inlineStr"/>
@@ -5502,7 +5567,11 @@
       <c r="L47" s="1" t="n">
         <v>46216</v>
       </c>
-      <c r="M47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr">
         <is>
           <t>06/2026</t>
@@ -5535,7 +5604,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V47" t="inlineStr"/>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 13/07/2026 - Data Comentário: 13/07/2026 12:04</t>
+        </is>
+      </c>
       <c r="W47" t="inlineStr"/>
       <c r="X47" t="inlineStr"/>
       <c r="Y47" t="inlineStr"/>
@@ -5607,7 +5680,11 @@
       <c r="L48" s="1" t="n">
         <v>46216</v>
       </c>
-      <c r="M48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr">
         <is>
           <t>06/2026</t>
@@ -5640,7 +5717,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V48" t="inlineStr"/>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 13/07/2026 - Data Comentário: 13/07/2026 12:04</t>
+        </is>
+      </c>
       <c r="W48" t="inlineStr"/>
       <c r="X48" t="inlineStr"/>
       <c r="Y48" t="inlineStr"/>
@@ -5712,7 +5793,11 @@
       <c r="L49" s="1" t="n">
         <v>46216</v>
       </c>
-      <c r="M49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr">
         <is>
           <t>06/2026</t>
@@ -5745,7 +5830,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V49" t="inlineStr"/>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 13/07/2026 - Data Comentário: 13/07/2026 12:04</t>
+        </is>
+      </c>
       <c r="W49" t="inlineStr"/>
       <c r="X49" t="inlineStr"/>
       <c r="Y49" t="inlineStr"/>
@@ -5817,7 +5906,11 @@
       <c r="L50" s="1" t="n">
         <v>46216</v>
       </c>
-      <c r="M50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr">
         <is>
           <t>06/2026</t>
@@ -5850,7 +5943,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V50" t="inlineStr"/>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 13/07/2026 - Data Comentário: 13/07/2026 12:04</t>
+        </is>
+      </c>
       <c r="W50" t="inlineStr"/>
       <c r="X50" t="inlineStr"/>
       <c r="Y50" t="inlineStr"/>
@@ -5922,7 +6019,11 @@
       <c r="L51" s="1" t="n">
         <v>46216</v>
       </c>
-      <c r="M51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr">
         <is>
           <t>06/2026</t>
@@ -5951,7 +6052,11 @@
         </is>
       </c>
       <c r="U51" t="inlineStr"/>
-      <c r="V51" t="inlineStr"/>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 13/07/2026 - Data Comentário: 13/07/2026 12:04</t>
+        </is>
+      </c>
       <c r="W51" t="inlineStr"/>
       <c r="X51" t="inlineStr"/>
       <c r="Y51" t="inlineStr"/>
@@ -6023,7 +6128,11 @@
       <c r="L52" s="1" t="n">
         <v>46216</v>
       </c>
-      <c r="M52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr">
         <is>
           <t>06/2026</t>
@@ -6052,7 +6161,11 @@
         </is>
       </c>
       <c r="U52" t="inlineStr"/>
-      <c r="V52" t="inlineStr"/>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 13/07/2026 - Data Comentário: 13/07/2026 12:04</t>
+        </is>
+      </c>
       <c r="W52" t="inlineStr"/>
       <c r="X52" t="inlineStr"/>
       <c r="Y52" t="inlineStr"/>
@@ -52707,7 +52820,11 @@
       <c r="L483" s="1" t="n">
         <v>46220</v>
       </c>
-      <c r="M483" t="inlineStr"/>
+      <c r="M483" t="inlineStr">
+        <is>
+          <t>16/07/2026</t>
+        </is>
+      </c>
       <c r="N483" t="inlineStr">
         <is>
           <t>07/2026</t>
@@ -52740,7 +52857,12 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V483" t="inlineStr"/>
+      <c r="V483" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 16/07/2026 
+Em processamento - Data Comentário: 13/07/2026 12:01</t>
+        </is>
+      </c>
       <c r="W483" t="inlineStr"/>
       <c r="X483" t="inlineStr"/>
       <c r="Y483" t="inlineStr"/>

--- a/dados/base/goias.xlsx
+++ b/dados/base/goias.xlsx
@@ -3650,11 +3650,11 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>6949</v>
+        <v>6628</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>TEC GRUA LOCAÇÃO E COMERCIO DE EQUIPAMENTOS PARA CONSTRUÇÃO LTDA</t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3664,33 +3664,33 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>6348</v>
+        <v>1875</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>RESCISÃO - RESCISÃO</t>
+          <t>Est - Sintegra Interestadual</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -3700,15 +3700,15 @@
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
       <c r="O30" t="n">
-        <v>18201961</v>
+        <v>17988660</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Gabriela Peres</t>
+          <t>Fernando Bastos</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -3722,15 +3722,15 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>TEC GRUA</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>Pedido de demissão - Desconto de Aviso em 07/07/2026 - Pgto 17/07/2026 - Data Comentário: 08/07/2026 11:16</t>
-        </is>
-      </c>
+          <t xml:space="preserve">GTG </t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr"/>
       <c r="Y30" t="inlineStr"/>
@@ -3744,22 +3744,22 @@
       <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Obrigação Acessória</t>
         </is>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>Leandro Matos</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>6628</v>
+        <v>6548</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>GOIAS SILAGEM LTDA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3783,7 +3783,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1875</v>
+        <v>6805</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -3795,25 +3795,29 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Est - Sintegra Interestadual</t>
+          <t>Fed - EFD - REINF - Entrega e PDF</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" s="1" t="n">
-        <v>46218</v>
-      </c>
-      <c r="M31" t="inlineStr"/>
+        <v>46216</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O31" t="n">
-        <v>17988660</v>
+        <v>17222740</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Fernando Bastos</t>
+          <t>Cristiana Grizostomo</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -3823,11 +3827,11 @@
       </c>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
+          <t>GOIAS SILAGEM</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3835,7 +3839,12 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr"/>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 13/07/2026 
+Tarefas em andamento de efetivação nesta data. - Data Comentário: 13/07/2026 10:09</t>
+        </is>
+      </c>
       <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr"/>
       <c r="Y31" t="inlineStr"/>
@@ -3860,11 +3869,11 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>6548</v>
+        <v>6628</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM LTDA</t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3874,12 +3883,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3918,11 +3927,11 @@
         </is>
       </c>
       <c r="O32" t="n">
-        <v>17222740</v>
+        <v>17988707</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Cristiana Grizostomo</t>
+          <t>Fernando Bastos</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -3936,7 +3945,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM</t>
+          <t xml:space="preserve">GTG </t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3947,7 +3956,7 @@
       <c r="V32" t="inlineStr">
         <is>
           <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 13/07/2026 
-Tarefas em andamento de efetivação nesta data. - Data Comentário: 13/07/2026 10:09</t>
+em execução - Data Comentário: 13/07/2026 11:31</t>
         </is>
       </c>
       <c r="W32" t="inlineStr"/>
@@ -3974,11 +3983,11 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>6628</v>
+        <v>6962</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3988,17 +3997,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Reynaldo Santos</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4032,11 +4041,11 @@
         </is>
       </c>
       <c r="O33" t="n">
-        <v>17988707</v>
+        <v>18186993</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Fernando Bastos</t>
+          <t>Denis Reis</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -4050,18 +4059,14 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>PROMOTORAS GYN</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr">
         <is>
           <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 13/07/2026 
-em execução - Data Comentário: 13/07/2026 11:31</t>
+em execução - Data Comentário: 13/07/2026 10:49</t>
         </is>
       </c>
       <c r="W33" t="inlineStr"/>
@@ -4088,11 +4093,11 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
+          <t>PROMOTORAS GYN LTDA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4146,7 +4151,7 @@
         </is>
       </c>
       <c r="O34" t="n">
-        <v>18186993</v>
+        <v>18187259</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
@@ -4198,11 +4203,11 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>6963</v>
+        <v>6627</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN LTDA</t>
+          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4217,16 +4222,16 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>6805</v>
+        <v>10674</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -4238,25 +4243,21 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Fed - EFD - REINF - Entrega e PDF</t>
+          <t>Relatório de Entrada para Classificação</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" s="1" t="n">
-        <v>46216</v>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>13/07/2026</t>
-        </is>
-      </c>
+        <v>46218</v>
+      </c>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O35" t="n">
-        <v>18187259</v>
+        <v>17968443</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
@@ -4270,20 +4271,19 @@
       </c>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 13/07/2026 
-em execução - Data Comentário: 13/07/2026 10:49</t>
-        </is>
-      </c>
+          <t xml:space="preserve">GTG </t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr"/>
       <c r="W35" t="inlineStr"/>
       <c r="X35" t="inlineStr"/>
       <c r="Y35" t="inlineStr"/>
@@ -4297,7 +4297,7 @@
       <c r="AE35" t="inlineStr"/>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>Obrigação Acessória</t>
+          <t>Tarefa</t>
         </is>
       </c>
       <c r="AG35" t="inlineStr">
@@ -4308,11 +4308,11 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>6627</v>
+        <v>6962</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
+          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Reynaldo Santos</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4362,7 +4362,7 @@
         </is>
       </c>
       <c r="O36" t="n">
-        <v>17968443</v>
+        <v>18187014</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
@@ -4380,14 +4380,10 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>PROMOTORAS GYN</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr"/>
       <c r="X36" t="inlineStr"/>
@@ -4413,11 +4409,11 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
+          <t>PROMOTORAS GYN LTDA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -4467,7 +4463,7 @@
         </is>
       </c>
       <c r="O37" t="n">
-        <v>18187014</v>
+        <v>18187280</v>
       </c>
       <c r="P37" t="inlineStr">
         <is>
@@ -4514,11 +4510,11 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>6963</v>
+        <v>6705</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN LTDA</t>
+          <t>NARCIZO ALVES CORDEIRO</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4528,7 +4524,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4538,41 +4534,45 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>10674</v>
+        <v>6298</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Relatório de Entrada para Classificação</t>
+          <t>Est - Sintegra Interestadual</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" s="1" t="n">
         <v>46218</v>
       </c>
-      <c r="M38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>15/07/2026</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O38" t="n">
-        <v>18187280</v>
+        <v>17949007</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Denis Reis</t>
+          <t>Cristina Leite</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -4586,11 +4586,19 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr"/>
+          <t>TECNO COM</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 15/07/2026 - Data Comentário: 13/07/2026 12:06</t>
+        </is>
+      </c>
       <c r="W38" t="inlineStr"/>
       <c r="X38" t="inlineStr"/>
       <c r="Y38" t="inlineStr"/>
@@ -4604,22 +4612,22 @@
       <c r="AE38" t="inlineStr"/>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>Tarefa</t>
+          <t>Obrigação Acessória</t>
         </is>
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>6705</v>
+        <v>5617</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>NARCIZO ALVES CORDEIRO</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -4629,7 +4637,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4643,7 +4651,7 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>6298</v>
+        <v>6806</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -4655,16 +4663,16 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Est - Sintegra Interestadual</t>
+          <t>Fed - EFD - REINF - Entrega e PDF</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" s="1" t="n">
-        <v>46218</v>
+        <v>46216</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4673,7 +4681,7 @@
         </is>
       </c>
       <c r="O39" t="n">
-        <v>17949007</v>
+        <v>17407789</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
@@ -4687,11 +4695,11 @@
       </c>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4701,7 +4709,7 @@
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 15/07/2026 - Data Comentário: 13/07/2026 12:06</t>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 13/07/2026 - Data Comentário: 13/07/2026 12:04</t>
         </is>
       </c>
       <c r="W39" t="inlineStr"/>
@@ -4728,11 +4736,11 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>5617</v>
+        <v>6224</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -4752,7 +4760,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -4786,7 +4794,7 @@
         </is>
       </c>
       <c r="O40" t="n">
-        <v>17407789</v>
+        <v>17688917</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
@@ -4841,11 +4849,11 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>6224</v>
+        <v>6278</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>EMPORIO DOS FRIOS LTDA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -4855,7 +4863,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Real - Anual</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4865,7 +4873,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -4899,7 +4907,7 @@
         </is>
       </c>
       <c r="O41" t="n">
-        <v>17688917</v>
+        <v>17148836</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
@@ -4917,7 +4925,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4954,11 +4962,11 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>6278</v>
+        <v>6279</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS LTDA</t>
+          <t>DIENNYFER DA S PEREIRA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -4968,7 +4976,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Federal - Lucro Real - Anual</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4978,7 +4986,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5012,7 +5020,7 @@
         </is>
       </c>
       <c r="O42" t="n">
-        <v>17148836</v>
+        <v>17071031</v>
       </c>
       <c r="P42" t="inlineStr">
         <is>
@@ -5067,11 +5075,11 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>6279</v>
+        <v>6404</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>DIENNYFER DA S PEREIRA</t>
+          <t>SOLAR INVESTIMENTOS LTDA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -5091,7 +5099,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5125,7 +5133,7 @@
         </is>
       </c>
       <c r="O43" t="n">
-        <v>17071031</v>
+        <v>16962306</v>
       </c>
       <c r="P43" t="inlineStr">
         <is>
@@ -5143,7 +5151,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>SOLAR INVESTIMENTOS</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5180,11 +5188,11 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>6404</v>
+        <v>6486</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS LTDA</t>
+          <t>PC GAMER GOIANIA LTDA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -5194,7 +5202,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -5238,7 +5246,7 @@
         </is>
       </c>
       <c r="O44" t="n">
-        <v>16962306</v>
+        <v>16976185</v>
       </c>
       <c r="P44" t="inlineStr">
         <is>
@@ -5256,7 +5264,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS</t>
+          <t>PC GAMER</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5293,11 +5301,11 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>6486</v>
+        <v>6704</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>PC GAMER GOIANIA LTDA</t>
+          <t>TECNO COM INFORMATICA LTDA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -5351,7 +5359,7 @@
         </is>
       </c>
       <c r="O45" t="n">
-        <v>16976185</v>
+        <v>18085295</v>
       </c>
       <c r="P45" t="inlineStr">
         <is>
@@ -5369,7 +5377,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>PC GAMER</t>
+          <t>TECNO COM</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5406,11 +5414,11 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>6704</v>
+        <v>6705</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>TECNO COM INFORMATICA LTDA</t>
+          <t>NARCIZO ALVES CORDEIRO</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -5420,7 +5428,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -5464,7 +5472,7 @@
         </is>
       </c>
       <c r="O46" t="n">
-        <v>18085295</v>
+        <v>17949027</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
@@ -5519,11 +5527,11 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>6705</v>
+        <v>6779</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>NARCIZO ALVES CORDEIRO</t>
+          <t>CORDEIRO E CIA LTDA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -5577,7 +5585,7 @@
         </is>
       </c>
       <c r="O47" t="n">
-        <v>17949027</v>
+        <v>18085064</v>
       </c>
       <c r="P47" t="inlineStr">
         <is>
@@ -5598,11 +5606,7 @@
           <t>TECNO COM</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+      <c r="U47" t="inlineStr"/>
       <c r="V47" t="inlineStr">
         <is>
           <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 13/07/2026 - Data Comentário: 13/07/2026 12:04</t>
@@ -5632,11 +5636,11 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>6779</v>
+        <v>6885</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CORDEIRO E CIA LTDA</t>
+          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -5690,7 +5694,7 @@
         </is>
       </c>
       <c r="O48" t="n">
-        <v>18085064</v>
+        <v>18134124</v>
       </c>
       <c r="P48" t="inlineStr">
         <is>
@@ -5708,7 +5712,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U48" t="inlineStr"/>
@@ -5741,11 +5745,11 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>6885</v>
+        <v>5617</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -5755,7 +5759,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5769,10 +5773,10 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>6806</v>
+        <v>7884</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>9114</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -5781,25 +5785,21 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Fed - EFD - REINF - Entrega e PDF</t>
+          <t>Log/Envio de Inconsistência (Mensal)</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" s="1" t="n">
-        <v>46216</v>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>13/07/2026</t>
-        </is>
-      </c>
+        <v>46218</v>
+      </c>
+      <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O49" t="n">
-        <v>18134124</v>
+        <v>18120594</v>
       </c>
       <c r="P49" t="inlineStr">
         <is>
@@ -5813,17 +5813,21 @@
       </c>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr"/>
+          <t>SUPER MAIS DO GOIÁS</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 13/07/2026 - Data Comentário: 13/07/2026 12:04</t>
+          <t>Atraso do Cliente, cobrança ativa, GC e GM ciente do atraso - Data Comentário: 10/07/2026 10:31</t>
         </is>
       </c>
       <c r="W49" t="inlineStr"/>
@@ -5839,7 +5843,7 @@
       <c r="AE49" t="inlineStr"/>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>Obrigação Acessória</t>
+          <t>Tarefa</t>
         </is>
       </c>
       <c r="AG49" t="inlineStr">
@@ -5878,10 +5882,10 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>7884</v>
+        <v>11303</v>
       </c>
       <c r="H50" t="n">
-        <v>9114</v>
+        <v>0</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -5890,7 +5894,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Log/Envio de Inconsistência (Mensal)</t>
+          <t>Retorno do Check-List Fiscal</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -5904,7 +5908,7 @@
         </is>
       </c>
       <c r="O50" t="n">
-        <v>18120594</v>
+        <v>17407963</v>
       </c>
       <c r="P50" t="inlineStr">
         <is>
@@ -5930,11 +5934,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>Atraso do Cliente, cobrança ativa, GC e GM ciente do atraso - Data Comentário: 10/07/2026 10:31</t>
-        </is>
-      </c>
+      <c r="V50" t="inlineStr"/>
       <c r="W50" t="inlineStr"/>
       <c r="X50" t="inlineStr"/>
       <c r="Y50" t="inlineStr"/>
@@ -5959,11 +5959,11 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>5617</v>
+        <v>6949</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>TEC GRUA LOCAÇÃO E COMERCIO DE EQUIPAMENTOS PARA CONSTRUÇÃO LTDA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -5983,70 +5983,77 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Reynaldo Santos</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>11303</v>
+        <v>11615</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Retorno do Check-List Fiscal</t>
+          <t>Envio de ATA de Implantação - CTB I</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" s="1" t="n">
-        <v>46218</v>
-      </c>
-      <c r="M51" t="inlineStr"/>
+        <v>46206</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O51" t="n">
-        <v>17407963</v>
-      </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>Cristina Leite</t>
-        </is>
-      </c>
+        <v>18166586</v>
+      </c>
+      <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>Em Aberto</t>
-        </is>
-      </c>
-      <c r="R51" t="inlineStr"/>
+          <t>Baixado</t>
+        </is>
+      </c>
+      <c r="R51" s="1" t="n">
+        <v>46206.43215109954</v>
+      </c>
       <c r="S51" t="n">
-        <v>-2</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="V51" t="inlineStr"/>
+          <t>TEC GRUA</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 26/06/2026 
+Aguardando agendamento das implantações - Data Comentário: 18/06/2026 17:44</t>
+        </is>
+      </c>
       <c r="W51" t="inlineStr"/>
       <c r="X51" t="inlineStr"/>
       <c r="Y51" t="inlineStr"/>
       <c r="Z51" t="n">
         <v>0</v>
       </c>
-      <c r="AA51" t="inlineStr"/>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>Erika Santana</t>
+        </is>
+      </c>
       <c r="AB51" t="inlineStr"/>
       <c r="AC51" t="inlineStr"/>
       <c r="AD51" t="inlineStr"/>
@@ -6056,19 +6063,15 @@
           <t>Tarefa</t>
         </is>
       </c>
-      <c r="AG51" t="inlineStr">
-        <is>
-          <t>Ricardo Fischer</t>
-        </is>
-      </c>
+      <c r="AG51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>6949</v>
+        <v>6962</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>TEC GRUA LOCAÇÃO E COMERCIO DE EQUIPAMENTOS PARA CONSTRUÇÃO LTDA</t>
+          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -6111,18 +6114,14 @@
       <c r="L52" s="1" t="n">
         <v>46206</v>
       </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>26/06/2026</t>
-        </is>
-      </c>
+      <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O52" t="n">
-        <v>18166586</v>
+        <v>18186559</v>
       </c>
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr">
@@ -6131,21 +6130,20 @@
         </is>
       </c>
       <c r="R52" s="1" t="n">
-        <v>46206.43215109954</v>
+        <v>46206.43205978009</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>TEC GRUA</t>
+          <t>PROMOTORAS GYN</t>
         </is>
       </c>
       <c r="U52" t="inlineStr"/>
       <c r="V52" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 26/06/2026 
-Aguardando agendamento das implantações - Data Comentário: 18/06/2026 17:44</t>
+          <t>Rotina Para Criar Tarefas Dos Clientes Novos - CodCliente: 6962; Tarefa Incluida: 11615; Vencimento: 17/06/2026 00:00:00; UsuarioResponsavel: erikas - Data Comentário: 17/06/2026 11:09</t>
         </is>
       </c>
       <c r="W52" t="inlineStr"/>
@@ -6172,11 +6170,11 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
+          <t>PROMOTORAS GYN LTDA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -6226,7 +6224,7 @@
         </is>
       </c>
       <c r="O53" t="n">
-        <v>18186559</v>
+        <v>18186560</v>
       </c>
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr">
@@ -6235,7 +6233,7 @@
         </is>
       </c>
       <c r="R53" s="1" t="n">
-        <v>46206.43205978009</v>
+        <v>46206.43206049768</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6248,7 +6246,7 @@
       <c r="U53" t="inlineStr"/>
       <c r="V53" t="inlineStr">
         <is>
-          <t>Rotina Para Criar Tarefas Dos Clientes Novos - CodCliente: 6962; Tarefa Incluida: 11615; Vencimento: 17/06/2026 00:00:00; UsuarioResponsavel: erikas - Data Comentário: 17/06/2026 11:09</t>
+          <t>Rotina Para Criar Tarefas Dos Clientes Novos - CodCliente: 6963; Tarefa Incluida: 11615; Vencimento: 17/06/2026 00:00:00; UsuarioResponsavel: erikas - Data Comentário: 17/06/2026 11:09</t>
         </is>
       </c>
       <c r="W53" t="inlineStr"/>
@@ -6275,11 +6273,11 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>6963</v>
+        <v>6548</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN LTDA</t>
+          <t>GOIAS SILAGEM LTDA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -6299,11 +6297,11 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>11615</v>
+        <v>11299</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -6315,12 +6313,12 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Envio de ATA de Implantação - CTB I</t>
+          <t>Retorno do Check-List</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" s="1" t="n">
-        <v>46206</v>
+        <v>46218</v>
       </c>
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
@@ -6329,31 +6327,35 @@
         </is>
       </c>
       <c r="O54" t="n">
-        <v>18186560</v>
-      </c>
-      <c r="P54" t="inlineStr"/>
+        <v>17968039</v>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Thais Souza</t>
+        </is>
+      </c>
       <c r="Q54" t="inlineStr">
         <is>
           <t>Baixado</t>
         </is>
       </c>
       <c r="R54" s="1" t="n">
-        <v>46206.43206049768</v>
+        <v>46204.75352534722</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>-2</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN</t>
-        </is>
-      </c>
-      <c r="U54" t="inlineStr"/>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>Rotina Para Criar Tarefas Dos Clientes Novos - CodCliente: 6963; Tarefa Incluida: 11615; Vencimento: 17/06/2026 00:00:00; UsuarioResponsavel: erikas - Data Comentário: 17/06/2026 11:09</t>
-        </is>
-      </c>
+          <t>GOIAS SILAGEM</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr"/>
       <c r="W54" t="inlineStr"/>
       <c r="X54" t="inlineStr"/>
       <c r="Y54" t="inlineStr"/>
@@ -6362,7 +6364,7 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>Erika Santana</t>
+          <t>Juan Rodrigues</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr"/>
@@ -6374,15 +6376,19 @@
           <t>Tarefa</t>
         </is>
       </c>
-      <c r="AG54" t="inlineStr"/>
+      <c r="AG54" t="inlineStr">
+        <is>
+          <t>Erika Santana</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM LTDA</t>
+          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -6397,7 +6403,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -6432,11 +6438,11 @@
         </is>
       </c>
       <c r="O55" t="n">
-        <v>17968039</v>
+        <v>17042639</v>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Thais Souza</t>
+          <t>Nathalia Lourenco</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
@@ -6445,14 +6451,14 @@
         </is>
       </c>
       <c r="R55" s="1" t="n">
-        <v>46204.75352534722</v>
+        <v>46204.75352809028</v>
       </c>
       <c r="S55" t="n">
         <v>-2</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM</t>
+          <t xml:space="preserve">GTG </t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6483,17 +6489,17 @@
       </c>
       <c r="AG55" t="inlineStr">
         <is>
-          <t>Erika Santana</t>
+          <t>Isabella Nascimento</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -6503,7 +6509,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -6543,7 +6549,7 @@
         </is>
       </c>
       <c r="O56" t="n">
-        <v>17042639</v>
+        <v>16960108</v>
       </c>
       <c r="P56" t="inlineStr">
         <is>
@@ -6556,7 +6562,7 @@
         </is>
       </c>
       <c r="R56" s="1" t="n">
-        <v>46204.75352809028</v>
+        <v>46204.7535284375</v>
       </c>
       <c r="S56" t="n">
         <v>-2</v>
@@ -6600,11 +6606,11 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>6628</v>
+        <v>6945</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -6654,11 +6660,11 @@
         </is>
       </c>
       <c r="O57" t="n">
-        <v>16960108</v>
+        <v>18163697</v>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Nathalia Lourenco</t>
+          <t>Laisa Rocha</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
@@ -6667,21 +6673,17 @@
         </is>
       </c>
       <c r="R57" s="1" t="n">
-        <v>46204.7535284375</v>
+        <v>46204.7535334838</v>
       </c>
       <c r="S57" t="n">
         <v>-2</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
-        </is>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>BRASIL DISTRIBUIDORA</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr"/>
       <c r="V57" t="inlineStr"/>
       <c r="W57" t="inlineStr"/>
       <c r="X57" t="inlineStr"/>
@@ -6711,11 +6713,11 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>6945</v>
+        <v>6962</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
+          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -6725,17 +6727,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Reynaldo Santos</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -6765,11 +6767,11 @@
         </is>
       </c>
       <c r="O58" t="n">
-        <v>18163697</v>
+        <v>18187976</v>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Laisa Rocha</t>
+          <t>Mirian Lima</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
@@ -6778,14 +6780,14 @@
         </is>
       </c>
       <c r="R58" s="1" t="n">
-        <v>46204.7535334838</v>
+        <v>46204.75353387732</v>
       </c>
       <c r="S58" t="n">
         <v>-2</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA</t>
+          <t>PROMOTORAS GYN</t>
         </is>
       </c>
       <c r="U58" t="inlineStr"/>
@@ -6818,11 +6820,11 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
+          <t>PROMOTORAS GYN LTDA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -6872,7 +6874,7 @@
         </is>
       </c>
       <c r="O59" t="n">
-        <v>18187976</v>
+        <v>18187914</v>
       </c>
       <c r="P59" t="inlineStr">
         <is>
@@ -6885,7 +6887,7 @@
         </is>
       </c>
       <c r="R59" s="1" t="n">
-        <v>46204.75353387732</v>
+        <v>46204.75353515046</v>
       </c>
       <c r="S59" t="n">
         <v>-2</v>
@@ -6925,11 +6927,11 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>6963</v>
+        <v>5417</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN LTDA</t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -6949,18 +6951,18 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>11299</v>
+        <v>11297</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL INDUSTRIA</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -6979,11 +6981,11 @@
         </is>
       </c>
       <c r="O60" t="n">
-        <v>18187914</v>
+        <v>17399442</v>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Mirian Lima</t>
+          <t>Eveny Silva</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
@@ -6992,17 +6994,21 @@
         </is>
       </c>
       <c r="R60" s="1" t="n">
-        <v>46204.75353515046</v>
+        <v>46204.75350494213</v>
       </c>
       <c r="S60" t="n">
         <v>-2</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN</t>
-        </is>
-      </c>
-      <c r="U60" t="inlineStr"/>
+          <t>NOSSO NOVO SUPERMERCADO</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V60" t="inlineStr"/>
       <c r="W60" t="inlineStr"/>
       <c r="X60" t="inlineStr"/>
@@ -7026,17 +7032,17 @@
       </c>
       <c r="AG60" t="inlineStr">
         <is>
-          <t>Isabella Nascimento</t>
+          <t>Karina Santos</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>5417</v>
+        <v>5617</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -7056,7 +7062,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7086,11 +7092,11 @@
         </is>
       </c>
       <c r="O61" t="n">
-        <v>17399442</v>
+        <v>17407953</v>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Eveny Silva</t>
+          <t>Jackson Silva</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
@@ -7099,14 +7105,14 @@
         </is>
       </c>
       <c r="R61" s="1" t="n">
-        <v>46204.75350494213</v>
+        <v>46204.75351072917</v>
       </c>
       <c r="S61" t="n">
         <v>-2</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -7137,17 +7143,17 @@
       </c>
       <c r="AG61" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>5617</v>
+        <v>6224</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -7167,7 +7173,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7197,7 +7203,7 @@
         </is>
       </c>
       <c r="O62" t="n">
-        <v>17407953</v>
+        <v>17689061</v>
       </c>
       <c r="P62" t="inlineStr">
         <is>
@@ -7210,7 +7216,7 @@
         </is>
       </c>
       <c r="R62" s="1" t="n">
-        <v>46204.75351072917</v>
+        <v>46204.75352068287</v>
       </c>
       <c r="S62" t="n">
         <v>-2</v>
@@ -7254,11 +7260,11 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>6224</v>
+        <v>6278</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>EMPORIO DOS FRIOS LTDA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -7268,7 +7274,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Real - Anual</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -7278,7 +7284,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7308,11 +7314,11 @@
         </is>
       </c>
       <c r="O63" t="n">
-        <v>17689061</v>
+        <v>17539888</v>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Jackson Silva</t>
+          <t>Isabela Lemos</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
@@ -7321,14 +7327,14 @@
         </is>
       </c>
       <c r="R63" s="1" t="n">
-        <v>46204.75352068287</v>
+        <v>46204.75352175926</v>
       </c>
       <c r="S63" t="n">
         <v>-2</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7359,17 +7365,17 @@
       </c>
       <c r="AG63" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>6278</v>
+        <v>6704</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS LTDA</t>
+          <t>TECNO COM INFORMATICA LTDA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -7379,7 +7385,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Federal - Lucro Real - Anual</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -7419,11 +7425,11 @@
         </is>
       </c>
       <c r="O64" t="n">
-        <v>17539888</v>
+        <v>17955432</v>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Isabela Lemos</t>
+          <t>Paulo Silva</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
@@ -7432,14 +7438,14 @@
         </is>
       </c>
       <c r="R64" s="1" t="n">
-        <v>46204.75352175926</v>
+        <v>46204.75353024306</v>
       </c>
       <c r="S64" t="n">
         <v>-2</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>TECNO COM</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7476,11 +7482,11 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>6704</v>
+        <v>6705</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>TECNO COM INFORMATICA LTDA</t>
+          <t>NARCIZO ALVES CORDEIRO</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -7490,7 +7496,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -7530,7 +7536,7 @@
         </is>
       </c>
       <c r="O65" t="n">
-        <v>17955432</v>
+        <v>17955272</v>
       </c>
       <c r="P65" t="inlineStr">
         <is>
@@ -7543,7 +7549,7 @@
         </is>
       </c>
       <c r="R65" s="1" t="n">
-        <v>46204.75353024306</v>
+        <v>46204.7535309838</v>
       </c>
       <c r="S65" t="n">
         <v>-2</v>
@@ -7587,11 +7593,11 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>6705</v>
+        <v>6779</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NARCIZO ALVES CORDEIRO</t>
+          <t>CORDEIRO E CIA LTDA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -7641,7 +7647,7 @@
         </is>
       </c>
       <c r="O66" t="n">
-        <v>17955272</v>
+        <v>18056830</v>
       </c>
       <c r="P66" t="inlineStr">
         <is>
@@ -7654,7 +7660,7 @@
         </is>
       </c>
       <c r="R66" s="1" t="n">
-        <v>46204.7535309838</v>
+        <v>46204.75353240741</v>
       </c>
       <c r="S66" t="n">
         <v>-2</v>
@@ -7664,11 +7670,7 @@
           <t>TECNO COM</t>
         </is>
       </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+      <c r="U66" t="inlineStr"/>
       <c r="V66" t="inlineStr"/>
       <c r="W66" t="inlineStr"/>
       <c r="X66" t="inlineStr"/>
@@ -7698,11 +7700,11 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>6779</v>
+        <v>6885</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CORDEIRO E CIA LTDA</t>
+          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -7752,11 +7754,11 @@
         </is>
       </c>
       <c r="O67" t="n">
-        <v>18056830</v>
+        <v>18128901</v>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Paulo Silva</t>
+          <t>Isabela Lemos</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
@@ -7765,14 +7767,14 @@
         </is>
       </c>
       <c r="R67" s="1" t="n">
-        <v>46204.75353240741</v>
+        <v>46204.75353278935</v>
       </c>
       <c r="S67" t="n">
         <v>-2</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U67" t="inlineStr"/>
@@ -7805,11 +7807,11 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>6885</v>
+        <v>6628</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -7824,7 +7826,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -7833,57 +7835,61 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>11297</v>
+        <v>11817</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Retorno do Check-List</t>
+          <t>Alteração dados cadastrais</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
       <c r="L68" s="1" t="n">
-        <v>46218</v>
+        <v>46205</v>
       </c>
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
-          <t>06/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
       <c r="O68" t="n">
-        <v>18128901</v>
-      </c>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>Isabela Lemos</t>
-        </is>
-      </c>
+        <v>18199226</v>
+      </c>
+      <c r="P68" t="inlineStr"/>
       <c r="Q68" t="inlineStr">
         <is>
           <t>Baixado</t>
         </is>
       </c>
       <c r="R68" s="1" t="n">
-        <v>46204.75353278935</v>
+        <v>46205.599529375</v>
       </c>
       <c r="S68" t="n">
-        <v>-2</v>
+        <v>11</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
-        </is>
-      </c>
-      <c r="U68" t="inlineStr"/>
-      <c r="V68" t="inlineStr"/>
+          <t xml:space="preserve">GTG </t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Aplicação de promoção. - Data Comentário: 02/07/2026 11:13</t>
+        </is>
+      </c>
       <c r="W68" t="inlineStr"/>
       <c r="X68" t="inlineStr"/>
       <c r="Y68" t="inlineStr"/>
@@ -7892,7 +7898,7 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>Juan Rodrigues</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr"/>
@@ -7904,19 +7910,15 @@
           <t>Tarefa</t>
         </is>
       </c>
-      <c r="AG68" t="inlineStr">
-        <is>
-          <t>Fernanda Araujo</t>
-        </is>
-      </c>
+      <c r="AG68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>6628</v>
+        <v>5417</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -7926,21 +7928,21 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>11817</v>
+        <v>11815</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -7952,12 +7954,12 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Alteração dados cadastrais</t>
+          <t>Cálculo de férias individuais</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" s="1" t="n">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
@@ -7966,7 +7968,7 @@
         </is>
       </c>
       <c r="O69" t="n">
-        <v>18199226</v>
+        <v>18196299</v>
       </c>
       <c r="P69" t="inlineStr"/>
       <c r="Q69" t="inlineStr">
@@ -7975,14 +7977,14 @@
         </is>
       </c>
       <c r="R69" s="1" t="n">
-        <v>46205.599529375</v>
+        <v>46204.71542079861</v>
       </c>
       <c r="S69" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
+          <t>NOSSO NOVO SUPERMERCADO</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -7990,11 +7992,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>Aplicação de promoção. - Data Comentário: 02/07/2026 11:13</t>
-        </is>
-      </c>
+      <c r="V69" t="inlineStr"/>
       <c r="W69" t="inlineStr"/>
       <c r="X69" t="inlineStr"/>
       <c r="Y69" t="inlineStr"/>
@@ -8003,7 +8001,7 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Mikael Teixeira</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr"/>
@@ -8073,7 +8071,7 @@
         </is>
       </c>
       <c r="O70" t="n">
-        <v>18196299</v>
+        <v>18196300</v>
       </c>
       <c r="P70" t="inlineStr"/>
       <c r="Q70" t="inlineStr">
@@ -8082,7 +8080,7 @@
         </is>
       </c>
       <c r="R70" s="1" t="n">
-        <v>46204.71542079861</v>
+        <v>46204.71542134259</v>
       </c>
       <c r="S70" t="n">
         <v>12</v>
@@ -8122,11 +8120,11 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>5417</v>
+        <v>6779</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>CORDEIRO E CIA LTDA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -8136,7 +8134,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -8146,7 +8144,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8176,7 +8174,7 @@
         </is>
       </c>
       <c r="O71" t="n">
-        <v>18196300</v>
+        <v>18195927</v>
       </c>
       <c r="P71" t="inlineStr"/>
       <c r="Q71" t="inlineStr">
@@ -8185,22 +8183,22 @@
         </is>
       </c>
       <c r="R71" s="1" t="n">
-        <v>46204.71542134259</v>
+        <v>46204.48446469908</v>
       </c>
       <c r="S71" t="n">
         <v>12</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
-        </is>
-      </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="V71" t="inlineStr"/>
+          <t>TECNO COM</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr"/>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Férias de 02/07/2026 a 10/07/2026. - Data Comentário: 01/07/2026 11:26</t>
+        </is>
+      </c>
       <c r="W71" t="inlineStr"/>
       <c r="X71" t="inlineStr"/>
       <c r="Y71" t="inlineStr"/>
@@ -8209,7 +8207,7 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>Mikael Teixeira</t>
+          <t>Kaique Souza</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr"/>
@@ -8225,11 +8223,11 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>6779</v>
+        <v>5417</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>CORDEIRO E CIA LTDA</t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -8239,7 +8237,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -8249,14 +8247,14 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>11815</v>
+        <v>5800</v>
       </c>
       <c r="H72" t="n">
-        <v>0</v>
+        <v>5776</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -8265,43 +8263,55 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Cálculo de férias individuais</t>
+          <t>CCT Lançamento Sd.508</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
       <c r="L72" s="1" t="n">
-        <v>46204</v>
-      </c>
-      <c r="M72" t="inlineStr"/>
+        <v>46205</v>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>00/2026</t>
         </is>
       </c>
       <c r="O72" t="n">
-        <v>18195927</v>
-      </c>
-      <c r="P72" t="inlineStr"/>
+        <v>17399013</v>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Mikael Teixeira</t>
+        </is>
+      </c>
       <c r="Q72" t="inlineStr">
         <is>
           <t>Baixado</t>
         </is>
       </c>
       <c r="R72" s="1" t="n">
-        <v>46204.48446469908</v>
+        <v>46205.75412240741</v>
       </c>
       <c r="S72" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
-        </is>
-      </c>
-      <c r="U72" t="inlineStr"/>
+          <t>NOSSO NOVO SUPERMERCADO</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>Férias de 02/07/2026 a 10/07/2026. - Data Comentário: 01/07/2026 11:26</t>
+          <t>2. Folha Processada aguardando OK do cliente para finalização   Previsão para conclusão dia 02/07/2026 - Data Comentário: 30/06/2026 15:03</t>
         </is>
       </c>
       <c r="W72" t="inlineStr"/>
@@ -8312,7 +8322,7 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>Kaique Souza</t>
+          <t>Mikael Teixeira</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr"/>
@@ -8328,11 +8338,11 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>5417</v>
+        <v>6224</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -8352,14 +8362,14 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>5800</v>
+        <v>5859</v>
       </c>
       <c r="H73" t="n">
-        <v>5776</v>
+        <v>5786</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -8368,29 +8378,25 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>CCT Lançamento Sd.508</t>
+          <t>Contribuição Assistencial</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
       <c r="L73" s="1" t="n">
-        <v>46205</v>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>02/07/2026</t>
-        </is>
-      </c>
+        <v>46206</v>
+      </c>
+      <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr">
         <is>
-          <t>00/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
       <c r="O73" t="n">
-        <v>17399013</v>
+        <v>17688763</v>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Mikael Teixeira</t>
+          <t>Tania Luz</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
@@ -8399,14 +8405,14 @@
         </is>
       </c>
       <c r="R73" s="1" t="n">
-        <v>46205.75412240741</v>
+        <v>46205.75458568287</v>
       </c>
       <c r="S73" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -8414,11 +8420,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V73" t="inlineStr">
-        <is>
-          <t>2. Folha Processada aguardando OK do cliente para finalização   Previsão para conclusão dia 02/07/2026 - Data Comentário: 30/06/2026 15:03</t>
-        </is>
-      </c>
+      <c r="V73" t="inlineStr"/>
       <c r="W73" t="inlineStr"/>
       <c r="X73" t="inlineStr"/>
       <c r="Y73" t="inlineStr"/>
@@ -8427,7 +8429,7 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>Mikael Teixeira</t>
+          <t>Tania Luz</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr"/>
@@ -8436,18 +8438,22 @@
       <c r="AE73" t="inlineStr"/>
       <c r="AF73" t="inlineStr">
         <is>
-          <t>Tarefa</t>
-        </is>
-      </c>
-      <c r="AG73" t="inlineStr"/>
+          <t>Imposto</t>
+        </is>
+      </c>
+      <c r="AG73" t="inlineStr">
+        <is>
+          <t>Edivaldo Veiga</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>6224</v>
+        <v>6628</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -8457,17 +8463,17 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -8497,11 +8503,11 @@
         </is>
       </c>
       <c r="O74" t="n">
-        <v>17688763</v>
+        <v>18052438</v>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Tania Luz</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
@@ -8510,14 +8516,14 @@
         </is>
       </c>
       <c r="R74" s="1" t="n">
-        <v>46205.75458568287</v>
+        <v>46206.44903752315</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t xml:space="preserve">GTG </t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -8534,7 +8540,7 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>Tania Luz</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr"/>
@@ -8548,17 +8554,17 @@
       </c>
       <c r="AG74" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>David Bragança</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>6628</v>
+        <v>6779</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>CORDEIRO E CIA LTDA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -8573,7 +8579,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -8608,34 +8614,26 @@
         </is>
       </c>
       <c r="O75" t="n">
-        <v>18052438</v>
-      </c>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>Jakeline Silva</t>
-        </is>
-      </c>
+        <v>18090166</v>
+      </c>
+      <c r="P75" t="inlineStr"/>
       <c r="Q75" t="inlineStr">
         <is>
           <t>Baixado</t>
         </is>
       </c>
       <c r="R75" s="1" t="n">
-        <v>46206.44903752315</v>
+        <v>46199.48727971065</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
-        </is>
-      </c>
-      <c r="U75" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>TECNO COM</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr"/>
       <c r="V75" t="inlineStr"/>
       <c r="W75" t="inlineStr"/>
       <c r="X75" t="inlineStr"/>
@@ -8645,7 +8643,7 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Kaique Souza</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr"/>
@@ -8657,19 +8655,15 @@
           <t>Imposto</t>
         </is>
       </c>
-      <c r="AG75" t="inlineStr">
-        <is>
-          <t>David Bragança</t>
-        </is>
-      </c>
+      <c r="AG75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>6779</v>
+        <v>6885</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>CORDEIRO E CIA LTDA</t>
+          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -8719,23 +8713,27 @@
         </is>
       </c>
       <c r="O76" t="n">
-        <v>18090166</v>
-      </c>
-      <c r="P76" t="inlineStr"/>
+        <v>18157259</v>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Vitor Guedes</t>
+        </is>
+      </c>
       <c r="Q76" t="inlineStr">
         <is>
           <t>Baixado</t>
         </is>
       </c>
       <c r="R76" s="1" t="n">
-        <v>46199.48727971065</v>
+        <v>46205.69236453703</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U76" t="inlineStr"/>
@@ -8748,7 +8746,7 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>Kaique Souza</t>
+          <t>Vitor Guedes</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr"/>
@@ -8760,15 +8758,19 @@
           <t>Imposto</t>
         </is>
       </c>
-      <c r="AG76" t="inlineStr"/>
+      <c r="AG76" t="inlineStr">
+        <is>
+          <t>David Bragança</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>6885</v>
+        <v>6945</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
+          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -8783,7 +8785,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -8811,18 +8813,22 @@
       <c r="L77" s="1" t="n">
         <v>46206</v>
       </c>
-      <c r="M77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
       <c r="N77" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O77" t="n">
-        <v>18157259</v>
+        <v>18179094</v>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Vitor Guedes</t>
+          <t>Santos Karina</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
@@ -8831,18 +8837,23 @@
         </is>
       </c>
       <c r="R77" s="1" t="n">
-        <v>46205.69236453703</v>
+        <v>46209.43008613426</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>BRASIL DISTRIBUIDORA</t>
         </is>
       </c>
       <c r="U77" t="inlineStr"/>
-      <c r="V77" t="inlineStr"/>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 07/07/2026 
+cliente em implantação, em andamento - Data Comentário: 03/07/2026 17:19</t>
+        </is>
+      </c>
       <c r="W77" t="inlineStr"/>
       <c r="X77" t="inlineStr"/>
       <c r="Y77" t="inlineStr"/>
@@ -8851,7 +8862,7 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>Vitor Guedes</t>
+          <t>Santos Karina</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr"/>
@@ -8865,17 +8876,17 @@
       </c>
       <c r="AG77" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Leandro Matos</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>6945</v>
+        <v>6486</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
+          <t>PC GAMER GOIANIA LTDA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -8885,12 +8896,12 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -8899,10 +8910,10 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>5859</v>
+        <v>11542</v>
       </c>
       <c r="H78" t="n">
-        <v>5786</v>
+        <v>0</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -8911,29 +8922,25 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Contribuição Assistencial</t>
+          <t>Envio Arq. eConsignado Cliente</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
       <c r="L78" s="1" t="n">
-        <v>46206</v>
-      </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>07/07/2026</t>
-        </is>
-      </c>
+        <v>46204</v>
+      </c>
+      <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr">
         <is>
-          <t>06/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
       <c r="O78" t="n">
-        <v>18179094</v>
+        <v>16976370</v>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Santos Karina</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
@@ -8942,23 +8949,22 @@
         </is>
       </c>
       <c r="R78" s="1" t="n">
-        <v>46209.43008613426</v>
+        <v>46204.5600265625</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA</t>
-        </is>
-      </c>
-      <c r="U78" t="inlineStr"/>
-      <c r="V78" t="inlineStr">
-        <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 07/07/2026 
-cliente em implantação, em andamento - Data Comentário: 03/07/2026 17:19</t>
-        </is>
-      </c>
+          <t>PC GAMER</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr"/>
       <c r="W78" t="inlineStr"/>
       <c r="X78" t="inlineStr"/>
       <c r="Y78" t="inlineStr"/>
@@ -8967,7 +8973,7 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>Santos Karina</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr"/>
@@ -8976,22 +8982,22 @@
       <c r="AE78" t="inlineStr"/>
       <c r="AF78" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Obrigação Acessória</t>
         </is>
       </c>
       <c r="AG78" t="inlineStr">
         <is>
-          <t>Leandro Matos</t>
+          <t>David Bragança</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>6486</v>
+        <v>6548</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>PC GAMER GOIANIA LTDA</t>
+          <t>GOIAS SILAGEM LTDA</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -9041,11 +9047,11 @@
         </is>
       </c>
       <c r="O79" t="n">
-        <v>16976370</v>
+        <v>17222966</v>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Daniel Moraes</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
@@ -9054,14 +9060,14 @@
         </is>
       </c>
       <c r="R79" s="1" t="n">
-        <v>46204.5600265625</v>
+        <v>46196.71390480324</v>
       </c>
       <c r="S79" t="n">
         <v>12</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>PC GAMER</t>
+          <t>GOIAS SILAGEM</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
@@ -9078,7 +9084,7 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Evellin Bispo</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr"/>
@@ -9098,11 +9104,11 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>6548</v>
+        <v>6703</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM LTDA</t>
+          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -9112,7 +9118,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -9152,11 +9158,11 @@
         </is>
       </c>
       <c r="O80" t="n">
-        <v>17222966</v>
+        <v>18077183</v>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Daniel Moraes</t>
+          <t>Ana Marcelino</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
@@ -9165,14 +9171,14 @@
         </is>
       </c>
       <c r="R80" s="1" t="n">
-        <v>46196.71390480324</v>
+        <v>46198.70825575232</v>
       </c>
       <c r="S80" t="n">
         <v>12</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM</t>
+          <t>LIMA MOTA</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
@@ -9189,7 +9195,7 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>Evellin Bispo</t>
+          <t>Elaine Assis</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr"/>
@@ -9203,17 +9209,17 @@
       </c>
       <c r="AG80" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>6703</v>
+        <v>6779</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
+          <t>CORDEIRO E CIA LTDA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -9223,7 +9229,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -9263,11 +9269,11 @@
         </is>
       </c>
       <c r="O81" t="n">
-        <v>18077183</v>
+        <v>18090270</v>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Ana Marcelino</t>
+          <t>Kaique Souza</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
@@ -9276,21 +9282,17 @@
         </is>
       </c>
       <c r="R81" s="1" t="n">
-        <v>46198.70825575232</v>
+        <v>46196.59280127315</v>
       </c>
       <c r="S81" t="n">
         <v>12</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>LIMA MOTA</t>
-        </is>
-      </c>
-      <c r="U81" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>TECNO COM</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr"/>
       <c r="V81" t="inlineStr"/>
       <c r="W81" t="inlineStr"/>
       <c r="X81" t="inlineStr"/>
@@ -9300,7 +9302,7 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>Elaine Assis</t>
+          <t>Kaique Souza</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr"/>
@@ -9320,11 +9322,11 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>6779</v>
+        <v>6949</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>CORDEIRO E CIA LTDA</t>
+          <t>TEC GRUA LOCAÇÃO E COMERCIO DE EQUIPAMENTOS PARA CONSTRUÇÃO LTDA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -9334,7 +9336,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -9344,7 +9346,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Reynaldo Santos</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -9374,11 +9376,11 @@
         </is>
       </c>
       <c r="O82" t="n">
-        <v>18090270</v>
+        <v>18190469</v>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Kaique Souza</t>
+          <t>Gabriela Peres</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
@@ -9387,14 +9389,14 @@
         </is>
       </c>
       <c r="R82" s="1" t="n">
-        <v>46196.59280127315</v>
+        <v>46204.41370118056</v>
       </c>
       <c r="S82" t="n">
         <v>12</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>TEC GRUA</t>
         </is>
       </c>
       <c r="U82" t="inlineStr"/>
@@ -9407,7 +9409,7 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>Kaique Souza</t>
+          <t>Santos Karina</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr"/>
@@ -9421,17 +9423,17 @@
       </c>
       <c r="AG82" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>Leandro Matos</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>6949</v>
+        <v>5417</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>TEC GRUA LOCAÇÃO E COMERCIO DE EQUIPAMENTOS PARA CONSTRUÇÃO LTDA</t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -9451,11 +9453,11 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>11542</v>
+        <v>9746</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -9467,25 +9469,29 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Envio Arq. eConsignado Cliente</t>
+          <t>eSocial – Fechamento Mensal</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
       <c r="L83" s="1" t="n">
-        <v>46204</v>
-      </c>
-      <c r="M83" t="inlineStr"/>
+        <v>46213</v>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
       <c r="O83" t="n">
-        <v>18190469</v>
+        <v>17399401</v>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Gabriela Peres</t>
+          <t>Mikael Teixeira</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
@@ -9494,18 +9500,27 @@
         </is>
       </c>
       <c r="R83" s="1" t="n">
-        <v>46204.41370118056</v>
+        <v>46213.6834903125</v>
       </c>
       <c r="S83" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>TEC GRUA</t>
-        </is>
-      </c>
-      <c r="U83" t="inlineStr"/>
-      <c r="V83" t="inlineStr"/>
+          <t>NOSSO NOVO SUPERMERCADO</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 10/07/2026 
+está com diferenças de valores entre sistema x esocial, estamos regularizando - Data Comentário: 08/07/2026 17:11</t>
+        </is>
+      </c>
       <c r="W83" t="inlineStr"/>
       <c r="X83" t="inlineStr"/>
       <c r="Y83" t="inlineStr"/>
@@ -9514,7 +9529,7 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>Santos Karina</t>
+          <t>Mikael Teixeira</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr"/>
@@ -9523,22 +9538,18 @@
       <c r="AE83" t="inlineStr"/>
       <c r="AF83" t="inlineStr">
         <is>
-          <t>Obrigação Acessória</t>
-        </is>
-      </c>
-      <c r="AG83" t="inlineStr">
-        <is>
-          <t>Leandro Matos</t>
-        </is>
-      </c>
+          <t>Tarefa</t>
+        </is>
+      </c>
+      <c r="AG83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>SOLAR INVESTIMENTOS LTDA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -9548,7 +9559,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -9558,7 +9569,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -9583,7 +9594,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -9592,11 +9603,11 @@
         </is>
       </c>
       <c r="O84" t="n">
-        <v>17399401</v>
+        <v>16962422</v>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Mikael Teixeira</t>
+          <t>Jhenifer Tenorio</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
@@ -9605,14 +9616,14 @@
         </is>
       </c>
       <c r="R84" s="1" t="n">
-        <v>46213.6834903125</v>
+        <v>46209.71247704861</v>
       </c>
       <c r="S84" t="n">
         <v>3</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
+          <t>SOLAR INVESTIMENTOS</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
@@ -9622,8 +9633,7 @@
       </c>
       <c r="V84" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 10/07/2026 
-está com diferenças de valores entre sistema x esocial, estamos regularizando - Data Comentário: 08/07/2026 17:11</t>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 08/07/2026 - Data Comentário: 06/07/2026 12:40</t>
         </is>
       </c>
       <c r="W84" t="inlineStr"/>
@@ -9634,7 +9644,7 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>Mikael Teixeira</t>
+          <t>Jhenifer Tenorio</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr"/>
@@ -9646,15 +9656,19 @@
           <t>Tarefa</t>
         </is>
       </c>
-      <c r="AG84" t="inlineStr"/>
+      <c r="AG84" t="inlineStr">
+        <is>
+          <t>Sara Cavalheiro</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>6404</v>
+        <v>6486</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS LTDA</t>
+          <t>PC GAMER GOIANIA LTDA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -9664,7 +9678,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -9708,11 +9722,11 @@
         </is>
       </c>
       <c r="O85" t="n">
-        <v>16962422</v>
+        <v>16976298</v>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Jhenifer Tenorio</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
@@ -9721,14 +9735,14 @@
         </is>
       </c>
       <c r="R85" s="1" t="n">
-        <v>46209.71247704861</v>
+        <v>46209.71499087963</v>
       </c>
       <c r="S85" t="n">
         <v>3</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS</t>
+          <t>PC GAMER</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
@@ -9738,7 +9752,8 @@
       </c>
       <c r="V85" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 08/07/2026 - Data Comentário: 06/07/2026 12:40</t>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 08/07/2026 
+PREVISÃO DE FINALIZAÇÃO: 08/07/2026 - Data Comentário: 06/07/2026 10:43</t>
         </is>
       </c>
       <c r="W85" t="inlineStr"/>
@@ -9749,7 +9764,7 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>Jhenifer Tenorio</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr"/>
@@ -9763,17 +9778,17 @@
       </c>
       <c r="AG85" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>David Bragança</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>6486</v>
+        <v>6548</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>PC GAMER GOIANIA LTDA</t>
+          <t>GOIAS SILAGEM LTDA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -9827,11 +9842,11 @@
         </is>
       </c>
       <c r="O86" t="n">
-        <v>16976298</v>
+        <v>17222913</v>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Daniel Moraes</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
@@ -9840,14 +9855,14 @@
         </is>
       </c>
       <c r="R86" s="1" t="n">
-        <v>46209.71499087963</v>
+        <v>46211.48251296296</v>
       </c>
       <c r="S86" t="n">
         <v>3</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>PC GAMER</t>
+          <t>GOIAS SILAGEM</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
@@ -9858,7 +9873,7 @@
       <c r="V86" t="inlineStr">
         <is>
           <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 08/07/2026 
-PREVISÃO DE FINALIZAÇÃO: 08/07/2026 - Data Comentário: 06/07/2026 10:43</t>
+Previsão de conclusão em 08/07/2026. - Data Comentário: 07/07/2026 16:47</t>
         </is>
       </c>
       <c r="W86" t="inlineStr"/>
@@ -9869,7 +9884,7 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Daniel Moraes</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr"/>
@@ -9889,11 +9904,11 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM LTDA</t>
+          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -9908,7 +9923,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -9947,11 +9962,11 @@
         </is>
       </c>
       <c r="O87" t="n">
-        <v>17222913</v>
+        <v>18068609</v>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Daniel Moraes</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
@@ -9960,14 +9975,14 @@
         </is>
       </c>
       <c r="R87" s="1" t="n">
-        <v>46211.48251296296</v>
+        <v>46210.47222041667</v>
       </c>
       <c r="S87" t="n">
         <v>3</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM</t>
+          <t xml:space="preserve">GTG </t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
@@ -9978,7 +9993,7 @@
       <c r="V87" t="inlineStr">
         <is>
           <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 08/07/2026 
-Previsão de conclusão em 08/07/2026. - Data Comentário: 07/07/2026 16:47</t>
+PREVISÃO DE FINALIZAÇÃO: 08/07/2026 - Data Comentário: 06/07/2026 10:43</t>
         </is>
       </c>
       <c r="W87" t="inlineStr"/>
@@ -9989,7 +10004,7 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>Daniel Moraes</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr"/>
@@ -10009,11 +10024,11 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -10023,7 +10038,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -10067,7 +10082,7 @@
         </is>
       </c>
       <c r="O88" t="n">
-        <v>18068609</v>
+        <v>18052528</v>
       </c>
       <c r="P88" t="inlineStr">
         <is>
@@ -10080,7 +10095,7 @@
         </is>
       </c>
       <c r="R88" s="1" t="n">
-        <v>46210.47222041667</v>
+        <v>46211.58264625</v>
       </c>
       <c r="S88" t="n">
         <v>3</v>
@@ -10097,8 +10112,8 @@
       </c>
       <c r="V88" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 08/07/2026 
-PREVISÃO DE FINALIZAÇÃO: 08/07/2026 - Data Comentário: 06/07/2026 10:43</t>
+          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 08/07/2026 
+EMPRESA SOLICITOU REABERTURA DA FOLHA PARA ALTERAÇÃO NO COLABORADOR TSN : Maycon Gomes da Silva. AGUARDANDO FECHAMENTO ESOCIAL PARA BAIXA. - Data Comentário: 08/07/2026 09:12</t>
         </is>
       </c>
       <c r="W88" t="inlineStr"/>
@@ -10129,11 +10144,11 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>6628</v>
+        <v>6703</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -10143,12 +10158,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -10178,7 +10193,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -10187,11 +10202,11 @@
         </is>
       </c>
       <c r="O89" t="n">
-        <v>18052528</v>
+        <v>18077161</v>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Ana Marcelino</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
@@ -10200,14 +10215,14 @@
         </is>
       </c>
       <c r="R89" s="1" t="n">
-        <v>46211.58264625</v>
+        <v>46210.48132625</v>
       </c>
       <c r="S89" t="n">
         <v>3</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
+          <t>LIMA MOTA</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
@@ -10217,8 +10232,8 @@
       </c>
       <c r="V89" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 08/07/2026 
-EMPRESA SOLICITOU REABERTURA DA FOLHA PARA ALTERAÇÃO NO COLABORADOR TSN : Maycon Gomes da Silva. AGUARDANDO FECHAMENTO ESOCIAL PARA BAIXA. - Data Comentário: 08/07/2026 09:12</t>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 07/07/2026 
+Previsão de conclusão 07/07/2026. - Data Comentário: 07/07/2026 10:22</t>
         </is>
       </c>
       <c r="W89" t="inlineStr"/>
@@ -10229,7 +10244,7 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Elaine Assis</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr"/>
@@ -10243,17 +10258,17 @@
       </c>
       <c r="AG89" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>6703</v>
+        <v>6779</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
+          <t>CORDEIRO E CIA LTDA</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -10263,7 +10278,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -10298,7 +10313,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -10307,11 +10322,11 @@
         </is>
       </c>
       <c r="O90" t="n">
-        <v>18077161</v>
+        <v>18090248</v>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Ana Marcelino</t>
+          <t>Kaique Souza</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
@@ -10320,25 +10335,21 @@
         </is>
       </c>
       <c r="R90" s="1" t="n">
-        <v>46210.48132625</v>
+        <v>46210.45896016204</v>
       </c>
       <c r="S90" t="n">
         <v>3</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>LIMA MOTA</t>
-        </is>
-      </c>
-      <c r="U90" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>TECNO COM</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr"/>
       <c r="V90" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 07/07/2026 
-Previsão de conclusão 07/07/2026. - Data Comentário: 07/07/2026 10:22</t>
+          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 10/07/2026 
+ESocial será baixado no vencimento para evitar retificações por solicitações do cliente. - Data Comentário: 03/07/2026 14:17</t>
         </is>
       </c>
       <c r="W90" t="inlineStr"/>
@@ -10349,7 +10360,7 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>Elaine Assis</t>
+          <t>Kaique Souza</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr"/>
@@ -10369,11 +10380,11 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>6779</v>
+        <v>6885</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>CORDEIRO E CIA LTDA</t>
+          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -10418,7 +10429,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -10427,11 +10438,11 @@
         </is>
       </c>
       <c r="O91" t="n">
-        <v>18090248</v>
+        <v>18157325</v>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Kaique Souza</t>
+          <t>Vitor Guedes</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
@@ -10440,21 +10451,21 @@
         </is>
       </c>
       <c r="R91" s="1" t="n">
-        <v>46210.45896016204</v>
+        <v>46210.72289299768</v>
       </c>
       <c r="S91" t="n">
         <v>3</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U91" t="inlineStr"/>
       <c r="V91" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 10/07/2026 
-ESocial será baixado no vencimento para evitar retificações por solicitações do cliente. - Data Comentário: 03/07/2026 14:17</t>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 07/07/2026 
+PREVISÃO DE CONCLUSÃO: 07/07/2026 - Data Comentário: 07/07/2026 13:13</t>
         </is>
       </c>
       <c r="W91" t="inlineStr"/>
@@ -10465,7 +10476,7 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>Kaique Souza</t>
+          <t>Vitor Guedes</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr"/>
@@ -10479,17 +10490,17 @@
       </c>
       <c r="AG91" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>David Bragança</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>6885</v>
+        <v>6279</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
+          <t>DIENNYFER DA S PEREIRA</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -10499,7 +10510,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -10509,11 +10520,11 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G92" t="n">
-        <v>9746</v>
+        <v>10905</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
@@ -10525,7 +10536,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>eSocial – Fechamento Mensal</t>
+          <t>eSocial - Fechamento SM</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
@@ -10534,7 +10545,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -10543,20 +10554,16 @@
         </is>
       </c>
       <c r="O92" t="n">
-        <v>18157325</v>
-      </c>
-      <c r="P92" t="inlineStr">
-        <is>
-          <t>Vitor Guedes</t>
-        </is>
-      </c>
+        <v>18195935</v>
+      </c>
+      <c r="P92" t="inlineStr"/>
       <c r="Q92" t="inlineStr">
         <is>
           <t>Baixado</t>
         </is>
       </c>
       <c r="R92" s="1" t="n">
-        <v>46210.72289299768</v>
+        <v>46211.59005767361</v>
       </c>
       <c r="S92" t="n">
         <v>3</v>
@@ -10566,11 +10573,15 @@
           <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
-      <c r="U92" t="inlineStr"/>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V92" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 07/07/2026 
-PREVISÃO DE CONCLUSÃO: 07/07/2026 - Data Comentário: 07/07/2026 13:13</t>
+          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 10/07/2026 
+Chamado aberto para a Controladoria para realização da baixa - nº 80915. - Data Comentário: 08/07/2026 13:52</t>
         </is>
       </c>
       <c r="W92" t="inlineStr"/>
@@ -10581,7 +10592,7 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>Vitor Guedes</t>
+          <t>Gabriel Amaral</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr"/>
@@ -10590,22 +10601,18 @@
       <c r="AE92" t="inlineStr"/>
       <c r="AF92" t="inlineStr">
         <is>
-          <t>Tarefa</t>
-        </is>
-      </c>
-      <c r="AG92" t="inlineStr">
-        <is>
-          <t>David Bragança</t>
-        </is>
-      </c>
+          <t>Obrigação Acessória</t>
+        </is>
+      </c>
+      <c r="AG92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>6279</v>
+        <v>5417</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>DIENNYFER DA S PEREIRA</t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -10615,7 +10622,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -10625,14 +10632,14 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G93" t="n">
-        <v>10905</v>
+        <v>5905</v>
       </c>
       <c r="H93" t="n">
-        <v>0</v>
+        <v>5784</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -10641,16 +10648,16 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>eSocial - Fechamento SM</t>
+          <t>Folha Mensal/Pró-Labore</t>
         </is>
       </c>
       <c r="K93" t="inlineStr"/>
       <c r="L93" s="1" t="n">
-        <v>46213</v>
+        <v>46206</v>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -10659,23 +10666,27 @@
         </is>
       </c>
       <c r="O93" t="n">
-        <v>18195935</v>
-      </c>
-      <c r="P93" t="inlineStr"/>
+        <v>17399094</v>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Mikael Teixeira</t>
+        </is>
+      </c>
       <c r="Q93" t="inlineStr">
         <is>
           <t>Baixado</t>
         </is>
       </c>
       <c r="R93" s="1" t="n">
-        <v>46211.59005767361</v>
+        <v>46206.54816894676</v>
       </c>
       <c r="S93" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>NOSSO NOVO SUPERMERCADO</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
@@ -10685,8 +10696,7 @@
       </c>
       <c r="V93" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 10/07/2026 
-Chamado aberto para a Controladoria para realização da baixa - nº 80915. - Data Comentário: 08/07/2026 13:52</t>
+          <t>3. Folha, Aguardando Resumo p/ Processamento   Previsão para conclusão dia 03/07/2026 - Data Comentário: 30/06/2026 15:48</t>
         </is>
       </c>
       <c r="W93" t="inlineStr"/>
@@ -10697,7 +10707,7 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>Gabriel Amaral</t>
+          <t>Mikael Teixeira</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr"/>
@@ -10713,11 +10723,11 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>5417</v>
+        <v>6486</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>PC GAMER GOIANIA LTDA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -10737,7 +10747,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -10771,11 +10781,11 @@
         </is>
       </c>
       <c r="O94" t="n">
-        <v>17399094</v>
+        <v>16976084</v>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Mikael Teixeira</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
@@ -10784,14 +10794,14 @@
         </is>
       </c>
       <c r="R94" s="1" t="n">
-        <v>46206.54816894676</v>
+        <v>46206.55861924768</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
+          <t>PC GAMER</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
@@ -10801,7 +10811,7 @@
       </c>
       <c r="V94" t="inlineStr">
         <is>
-          <t>3. Folha, Aguardando Resumo p/ Processamento   Previsão para conclusão dia 03/07/2026 - Data Comentário: 30/06/2026 15:48</t>
+          <t>2. Folha Processada aguardando OK do cliente para finalização   Previsão para conclusão dia 03/07/2026 - Data Comentário: 02/07/2026 15:13</t>
         </is>
       </c>
       <c r="W94" t="inlineStr"/>
@@ -10812,7 +10822,7 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>Mikael Teixeira</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr"/>
@@ -10824,15 +10834,19 @@
           <t>Obrigação Acessória</t>
         </is>
       </c>
-      <c r="AG94" t="inlineStr"/>
+      <c r="AG94" t="inlineStr">
+        <is>
+          <t>David Bragança</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>6486</v>
+        <v>6627</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>PC GAMER GOIANIA LTDA</t>
+          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -10847,7 +10861,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -10886,7 +10900,7 @@
         </is>
       </c>
       <c r="O95" t="n">
-        <v>16976084</v>
+        <v>18068575</v>
       </c>
       <c r="P95" t="inlineStr">
         <is>
@@ -10899,14 +10913,14 @@
         </is>
       </c>
       <c r="R95" s="1" t="n">
-        <v>46206.55861924768</v>
+        <v>46206.67165491898</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>PC GAMER</t>
+          <t xml:space="preserve">GTG </t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
@@ -10916,7 +10930,7 @@
       </c>
       <c r="V95" t="inlineStr">
         <is>
-          <t>2. Folha Processada aguardando OK do cliente para finalização   Previsão para conclusão dia 03/07/2026 - Data Comentário: 02/07/2026 15:13</t>
+          <t>2. Folha Processada aguardando OK do cliente para finalização  Previsão para conclusão dia 03/07/2026 - Data Comentário: 03/07/2026 09:21</t>
         </is>
       </c>
       <c r="W95" t="inlineStr"/>
@@ -10947,11 +10961,11 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -10961,7 +10975,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -11005,7 +11019,7 @@
         </is>
       </c>
       <c r="O96" t="n">
-        <v>18068575</v>
+        <v>18052494</v>
       </c>
       <c r="P96" t="inlineStr">
         <is>
@@ -11018,7 +11032,7 @@
         </is>
       </c>
       <c r="R96" s="1" t="n">
-        <v>46206.67165491898</v>
+        <v>46206.67202474537</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11066,11 +11080,11 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>6628</v>
+        <v>6703</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -11080,12 +11094,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -11124,11 +11138,11 @@
         </is>
       </c>
       <c r="O97" t="n">
-        <v>18052494</v>
+        <v>18077130</v>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Ana Marcelino</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr">
@@ -11137,14 +11151,14 @@
         </is>
       </c>
       <c r="R97" s="1" t="n">
-        <v>46206.67202474537</v>
+        <v>46206.62892094907</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
+          <t>LIMA MOTA</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
@@ -11154,7 +11168,7 @@
       </c>
       <c r="V97" t="inlineStr">
         <is>
-          <t>2. Folha Processada aguardando OK do cliente para finalização  Previsão para conclusão dia 03/07/2026 - Data Comentário: 03/07/2026 09:21</t>
+          <t>2. Folha Processada aguardando OK do cliente para finalização   Previsão para conclusão dia 03/07/2026 - Data Comentário: 02/07/2026 17:14</t>
         </is>
       </c>
       <c r="W97" t="inlineStr"/>
@@ -11165,7 +11179,7 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Elaine Assis</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr"/>
@@ -11179,17 +11193,17 @@
       </c>
       <c r="AG97" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>6703</v>
+        <v>6779</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
+          <t>CORDEIRO E CIA LTDA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -11199,7 +11213,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -11234,7 +11248,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -11243,11 +11257,11 @@
         </is>
       </c>
       <c r="O98" t="n">
-        <v>18077130</v>
+        <v>18090217</v>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Ana Marcelino</t>
+          <t>Kaique Souza</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
@@ -11256,24 +11270,20 @@
         </is>
       </c>
       <c r="R98" s="1" t="n">
-        <v>46206.62892094907</v>
+        <v>46206.64427289352</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>LIMA MOTA</t>
-        </is>
-      </c>
-      <c r="U98" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>TECNO COM</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr"/>
       <c r="V98" t="inlineStr">
         <is>
-          <t>2. Folha Processada aguardando OK do cliente para finalização   Previsão para conclusão dia 03/07/2026 - Data Comentário: 02/07/2026 17:14</t>
+          <t>2. Folha Processada aguardando OK do cliente para finalização   Previsão para conclusão dia 06/07/2026 - Data Comentário: 03/07/2026 14:18</t>
         </is>
       </c>
       <c r="W98" t="inlineStr"/>
@@ -11284,7 +11294,7 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>Elaine Assis</t>
+          <t>Kaique Souza</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr"/>
@@ -11304,11 +11314,11 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>6779</v>
+        <v>6885</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>CORDEIRO E CIA LTDA</t>
+          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -11353,7 +11363,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -11362,11 +11372,11 @@
         </is>
       </c>
       <c r="O99" t="n">
-        <v>18090217</v>
+        <v>18157300</v>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Kaique Souza</t>
+          <t>Vitor Guedes</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr">
@@ -11375,20 +11385,20 @@
         </is>
       </c>
       <c r="R99" s="1" t="n">
-        <v>46206.64427289352</v>
+        <v>46205.6924828125</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U99" t="inlineStr"/>
       <c r="V99" t="inlineStr">
         <is>
-          <t>2. Folha Processada aguardando OK do cliente para finalização   Previsão para conclusão dia 06/07/2026 - Data Comentário: 03/07/2026 14:18</t>
+          <t>2. Folha Processada aguardando OK do cliente para finalização   Previsão para conclusão dia 02/07/2026 - Data Comentário: 02/07/2026 10:31</t>
         </is>
       </c>
       <c r="W99" t="inlineStr"/>
@@ -11399,7 +11409,7 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>Kaique Souza</t>
+          <t>Vitor Guedes</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr"/>
@@ -11413,17 +11423,17 @@
       </c>
       <c r="AG99" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>David Bragança</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>6885</v>
+        <v>6945</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
+          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -11438,7 +11448,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -11468,7 +11478,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -11477,11 +11487,11 @@
         </is>
       </c>
       <c r="O100" t="n">
-        <v>18157300</v>
+        <v>18179130</v>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Vitor Guedes</t>
+          <t>Santos Karina</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
@@ -11490,20 +11500,20 @@
         </is>
       </c>
       <c r="R100" s="1" t="n">
-        <v>46205.6924828125</v>
+        <v>46206.69765491898</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>BRASIL DISTRIBUIDORA</t>
         </is>
       </c>
       <c r="U100" t="inlineStr"/>
       <c r="V100" t="inlineStr">
         <is>
-          <t>2. Folha Processada aguardando OK do cliente para finalização   Previsão para conclusão dia 02/07/2026 - Data Comentário: 02/07/2026 10:31</t>
+          <t>2. Folha Processada aguardando OK do cliente para finalização   Previsão para conclusão dia 03/07/2026 - Data Comentário: 03/07/2026 16:19</t>
         </is>
       </c>
       <c r="W100" t="inlineStr"/>
@@ -11514,7 +11524,7 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>Vitor Guedes</t>
+          <t>Santos Karina</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr"/>
@@ -11528,17 +11538,17 @@
       </c>
       <c r="AG100" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Leandro Matos</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>6945</v>
+        <v>5417</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -11548,21 +11558,21 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>5905</v>
+        <v>5853</v>
       </c>
       <c r="H101" t="n">
         <v>5784</v>
@@ -11574,29 +11584,25 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Folha Mensal/Pró-Labore</t>
+          <t>FOPAG Impressão PDF</t>
         </is>
       </c>
       <c r="K101" t="inlineStr"/>
       <c r="L101" s="1" t="n">
-        <v>46206</v>
-      </c>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
+        <v>46210</v>
+      </c>
+      <c r="M101" t="inlineStr"/>
       <c r="N101" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O101" t="n">
-        <v>18179130</v>
+        <v>17399034</v>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Santos Karina</t>
+          <t>Mikael Teixeira</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
@@ -11605,22 +11611,22 @@
         </is>
       </c>
       <c r="R101" s="1" t="n">
-        <v>46206.69765491898</v>
+        <v>46206.65603582176</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA</t>
-        </is>
-      </c>
-      <c r="U101" t="inlineStr"/>
-      <c r="V101" t="inlineStr">
-        <is>
-          <t>2. Folha Processada aguardando OK do cliente para finalização   Previsão para conclusão dia 03/07/2026 - Data Comentário: 03/07/2026 16:19</t>
-        </is>
-      </c>
+          <t>NOSSO NOVO SUPERMERCADO</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr"/>
       <c r="W101" t="inlineStr"/>
       <c r="X101" t="inlineStr"/>
       <c r="Y101" t="inlineStr"/>
@@ -11629,7 +11635,7 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>Santos Karina</t>
+          <t>Mikael Teixeira</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr"/>
@@ -11638,22 +11644,18 @@
       <c r="AE101" t="inlineStr"/>
       <c r="AF101" t="inlineStr">
         <is>
-          <t>Obrigação Acessória</t>
-        </is>
-      </c>
-      <c r="AG101" t="inlineStr">
-        <is>
-          <t>Leandro Matos</t>
-        </is>
-      </c>
+          <t>Tarefa</t>
+        </is>
+      </c>
+      <c r="AG101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>5417</v>
+        <v>6486</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>PC GAMER GOIANIA LTDA</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -11673,7 +11675,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -11703,11 +11705,11 @@
         </is>
       </c>
       <c r="O102" t="n">
-        <v>17399034</v>
+        <v>16976044</v>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Mikael Teixeira</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
@@ -11716,14 +11718,14 @@
         </is>
       </c>
       <c r="R102" s="1" t="n">
-        <v>46206.65603582176</v>
+        <v>46209.41001810185</v>
       </c>
       <c r="S102" t="n">
         <v>6</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
+          <t>PC GAMER</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
@@ -11740,7 +11742,7 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>Mikael Teixeira</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr"/>
@@ -11752,15 +11754,19 @@
           <t>Tarefa</t>
         </is>
       </c>
-      <c r="AG102" t="inlineStr"/>
+      <c r="AG102" t="inlineStr">
+        <is>
+          <t>David Bragança</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>6486</v>
+        <v>6627</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>PC GAMER GOIANIA LTDA</t>
+          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -11775,7 +11781,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -11810,7 +11816,7 @@
         </is>
       </c>
       <c r="O103" t="n">
-        <v>16976044</v>
+        <v>18068508</v>
       </c>
       <c r="P103" t="inlineStr">
         <is>
@@ -11823,14 +11829,14 @@
         </is>
       </c>
       <c r="R103" s="1" t="n">
-        <v>46209.41001810185</v>
+        <v>46209.41001846065</v>
       </c>
       <c r="S103" t="n">
         <v>6</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>PC GAMER</t>
+          <t xml:space="preserve">GTG </t>
         </is>
       </c>
       <c r="U103" t="inlineStr">
@@ -11867,11 +11873,11 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -11881,7 +11887,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -11921,7 +11927,7 @@
         </is>
       </c>
       <c r="O104" t="n">
-        <v>18068508</v>
+        <v>18052427</v>
       </c>
       <c r="P104" t="inlineStr">
         <is>
@@ -11934,7 +11940,7 @@
         </is>
       </c>
       <c r="R104" s="1" t="n">
-        <v>46209.41001846065</v>
+        <v>46209.41001900463</v>
       </c>
       <c r="S104" t="n">
         <v>6</v>
@@ -11978,11 +11984,11 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>6628</v>
+        <v>6703</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -11992,12 +11998,12 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -12032,11 +12038,11 @@
         </is>
       </c>
       <c r="O105" t="n">
-        <v>18052427</v>
+        <v>18077089</v>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Ana Marcelino</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
@@ -12045,14 +12051,14 @@
         </is>
       </c>
       <c r="R105" s="1" t="n">
-        <v>46209.41001900463</v>
+        <v>46206.62881552083</v>
       </c>
       <c r="S105" t="n">
         <v>6</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
+          <t>LIMA MOTA</t>
         </is>
       </c>
       <c r="U105" t="inlineStr">
@@ -12069,7 +12075,7 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Elaine Assis</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr"/>
@@ -12083,17 +12089,17 @@
       </c>
       <c r="AG105" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>6703</v>
+        <v>6779</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
+          <t>CORDEIRO E CIA LTDA</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -12103,7 +12109,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -12136,18 +12142,22 @@
       <c r="L106" s="1" t="n">
         <v>46210</v>
       </c>
-      <c r="M106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
       <c r="N106" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O106" t="n">
-        <v>18077089</v>
+        <v>18090156</v>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Ana Marcelino</t>
+          <t>Kaique Souza</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
@@ -12156,22 +12166,22 @@
         </is>
       </c>
       <c r="R106" s="1" t="n">
-        <v>46206.62881552083</v>
+        <v>46206.64398119213</v>
       </c>
       <c r="S106" t="n">
         <v>6</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>LIMA MOTA</t>
-        </is>
-      </c>
-      <c r="U106" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="V106" t="inlineStr"/>
+          <t>TECNO COM</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr"/>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>2. Folha Processada aguardando OK do cliente para finalização   Previsão para conclusão dia 06/07/2026 - Data Comentário: 03/07/2026 14:17</t>
+        </is>
+      </c>
       <c r="W106" t="inlineStr"/>
       <c r="X106" t="inlineStr"/>
       <c r="Y106" t="inlineStr"/>
@@ -12180,7 +12190,7 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>Elaine Assis</t>
+          <t>Kaique Souza</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr"/>
@@ -12200,11 +12210,11 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>6779</v>
+        <v>6885</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>CORDEIRO E CIA LTDA</t>
+          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -12247,22 +12257,18 @@
       <c r="L107" s="1" t="n">
         <v>46210</v>
       </c>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>06/07/2026</t>
-        </is>
-      </c>
+      <c r="M107" t="inlineStr"/>
       <c r="N107" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O107" t="n">
-        <v>18090156</v>
+        <v>18157251</v>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Kaique Souza</t>
+          <t>Vitor Guedes</t>
         </is>
       </c>
       <c r="Q107" t="inlineStr">
@@ -12271,22 +12277,18 @@
         </is>
       </c>
       <c r="R107" s="1" t="n">
-        <v>46206.64398119213</v>
+        <v>46209.55182975694</v>
       </c>
       <c r="S107" t="n">
         <v>6</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U107" t="inlineStr"/>
-      <c r="V107" t="inlineStr">
-        <is>
-          <t>2. Folha Processada aguardando OK do cliente para finalização   Previsão para conclusão dia 06/07/2026 - Data Comentário: 03/07/2026 14:17</t>
-        </is>
-      </c>
+      <c r="V107" t="inlineStr"/>
       <c r="W107" t="inlineStr"/>
       <c r="X107" t="inlineStr"/>
       <c r="Y107" t="inlineStr"/>
@@ -12295,7 +12297,7 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>Kaique Souza</t>
+          <t>Vitor Guedes</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr"/>
@@ -12309,17 +12311,17 @@
       </c>
       <c r="AG107" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>David Bragança</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>6885</v>
+        <v>6945</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
+          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -12334,7 +12336,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -12369,11 +12371,11 @@
         </is>
       </c>
       <c r="O108" t="n">
-        <v>18157251</v>
+        <v>18179087</v>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Vitor Guedes</t>
+          <t>Santos Karina</t>
         </is>
       </c>
       <c r="Q108" t="inlineStr">
@@ -12382,14 +12384,14 @@
         </is>
       </c>
       <c r="R108" s="1" t="n">
-        <v>46209.55182975694</v>
+        <v>46211.39936383102</v>
       </c>
       <c r="S108" t="n">
         <v>6</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>BRASIL DISTRIBUIDORA</t>
         </is>
       </c>
       <c r="U108" t="inlineStr"/>
@@ -12402,7 +12404,7 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>Vitor Guedes</t>
+          <t>Santos Karina</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr"/>
@@ -12416,17 +12418,17 @@
       </c>
       <c r="AG108" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Leandro Matos</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>6945</v>
+        <v>6486</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
+          <t>PC GAMER GOIANIA LTDA</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -12436,12 +12438,12 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -12450,10 +12452,10 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>5853</v>
+        <v>11541</v>
       </c>
       <c r="H109" t="n">
-        <v>5784</v>
+        <v>0</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
@@ -12462,25 +12464,25 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>FOPAG Impressão PDF</t>
+          <t>Importação Arq. eConsignado Único</t>
         </is>
       </c>
       <c r="K109" t="inlineStr"/>
       <c r="L109" s="1" t="n">
-        <v>46210</v>
+        <v>46204</v>
       </c>
       <c r="M109" t="inlineStr"/>
       <c r="N109" t="inlineStr">
         <is>
-          <t>06/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
       <c r="O109" t="n">
-        <v>18179087</v>
+        <v>16976360</v>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Santos Karina</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="Q109" t="inlineStr">
@@ -12489,17 +12491,21 @@
         </is>
       </c>
       <c r="R109" s="1" t="n">
-        <v>46211.39936383102</v>
+        <v>46204.50154423611</v>
       </c>
       <c r="S109" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA</t>
-        </is>
-      </c>
-      <c r="U109" t="inlineStr"/>
+          <t>PC GAMER</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V109" t="inlineStr"/>
       <c r="W109" t="inlineStr"/>
       <c r="X109" t="inlineStr"/>
@@ -12509,7 +12515,7 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>Santos Karina</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr"/>
@@ -12518,22 +12524,22 @@
       <c r="AE109" t="inlineStr"/>
       <c r="AF109" t="inlineStr">
         <is>
-          <t>Tarefa</t>
+          <t>Obrigação Acessória</t>
         </is>
       </c>
       <c r="AG109" t="inlineStr">
         <is>
-          <t>Leandro Matos</t>
+          <t>David Bragança</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>6486</v>
+        <v>6548</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>PC GAMER GOIANIA LTDA</t>
+          <t>GOIAS SILAGEM LTDA</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -12583,11 +12589,11 @@
         </is>
       </c>
       <c r="O110" t="n">
-        <v>16976360</v>
+        <v>17222946</v>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Daniel Moraes</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
@@ -12596,14 +12602,14 @@
         </is>
       </c>
       <c r="R110" s="1" t="n">
-        <v>46204.50154423611</v>
+        <v>46196.69558237268</v>
       </c>
       <c r="S110" t="n">
         <v>12</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
-          <t>PC GAMER</t>
+          <t>GOIAS SILAGEM</t>
         </is>
       </c>
       <c r="U110" t="inlineStr">
@@ -12620,7 +12626,7 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Evellin Bispo</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr"/>
@@ -12640,11 +12646,11 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>6548</v>
+        <v>6703</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM LTDA</t>
+          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -12654,7 +12660,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -12694,11 +12700,11 @@
         </is>
       </c>
       <c r="O111" t="n">
-        <v>17222946</v>
+        <v>18077173</v>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Daniel Moraes</t>
+          <t>Ana Marcelino</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr">
@@ -12707,14 +12713,14 @@
         </is>
       </c>
       <c r="R111" s="1" t="n">
-        <v>46196.69558237268</v>
+        <v>46198.71108606482</v>
       </c>
       <c r="S111" t="n">
         <v>12</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM</t>
+          <t>LIMA MOTA</t>
         </is>
       </c>
       <c r="U111" t="inlineStr">
@@ -12731,7 +12737,7 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>Evellin Bispo</t>
+          <t>Elaine Assis</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr"/>
@@ -12745,17 +12751,17 @@
       </c>
       <c r="AG111" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>6703</v>
+        <v>6779</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
+          <t>CORDEIRO E CIA LTDA</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -12765,7 +12771,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -12805,11 +12811,11 @@
         </is>
       </c>
       <c r="O112" t="n">
-        <v>18077173</v>
+        <v>18090260</v>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Ana Marcelino</t>
+          <t>Kaique Souza</t>
         </is>
       </c>
       <c r="Q112" t="inlineStr">
@@ -12818,21 +12824,17 @@
         </is>
       </c>
       <c r="R112" s="1" t="n">
-        <v>46198.71108606482</v>
+        <v>46196.59315405093</v>
       </c>
       <c r="S112" t="n">
         <v>12</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>LIMA MOTA</t>
-        </is>
-      </c>
-      <c r="U112" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>TECNO COM</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr"/>
       <c r="V112" t="inlineStr"/>
       <c r="W112" t="inlineStr"/>
       <c r="X112" t="inlineStr"/>
@@ -12842,7 +12844,7 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>Elaine Assis</t>
+          <t>Kaique Souza</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr"/>
@@ -12862,11 +12864,11 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>6779</v>
+        <v>6949</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>CORDEIRO E CIA LTDA</t>
+          <t>TEC GRUA LOCAÇÃO E COMERCIO DE EQUIPAMENTOS PARA CONSTRUÇÃO LTDA</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -12876,7 +12878,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -12886,7 +12888,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Reynaldo Santos</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -12916,11 +12918,11 @@
         </is>
       </c>
       <c r="O113" t="n">
-        <v>18090260</v>
+        <v>18190463</v>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Kaique Souza</t>
+          <t>Gabriela Peres</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr">
@@ -12929,14 +12931,14 @@
         </is>
       </c>
       <c r="R113" s="1" t="n">
-        <v>46196.59315405093</v>
+        <v>46204.42181446759</v>
       </c>
       <c r="S113" t="n">
         <v>12</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>TEC GRUA</t>
         </is>
       </c>
       <c r="U113" t="inlineStr"/>
@@ -12949,7 +12951,7 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>Kaique Souza</t>
+          <t>Santos Karina</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr"/>
@@ -12963,17 +12965,17 @@
       </c>
       <c r="AG113" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>Leandro Matos</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>6949</v>
+        <v>6779</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>TEC GRUA LOCAÇÃO E COMERCIO DE EQUIPAMENTOS PARA CONSTRUÇÃO LTDA</t>
+          <t>CORDEIRO E CIA LTDA</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -12983,7 +12985,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -12993,11 +12995,11 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G114" t="n">
-        <v>11541</v>
+        <v>11813</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -13009,7 +13011,7 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Importação Arq. eConsignado Único</t>
+          <t>Lançamentos de atestados</t>
         </is>
       </c>
       <c r="K114" t="inlineStr"/>
@@ -13019,35 +13021,35 @@
       <c r="M114" t="inlineStr"/>
       <c r="N114" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
       <c r="O114" t="n">
-        <v>18190463</v>
-      </c>
-      <c r="P114" t="inlineStr">
-        <is>
-          <t>Gabriela Peres</t>
-        </is>
-      </c>
+        <v>18195904</v>
+      </c>
+      <c r="P114" t="inlineStr"/>
       <c r="Q114" t="inlineStr">
         <is>
           <t>Baixado</t>
         </is>
       </c>
       <c r="R114" s="1" t="n">
-        <v>46204.42181446759</v>
+        <v>46204.48462402778</v>
       </c>
       <c r="S114" t="n">
         <v>12</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
-          <t>TEC GRUA</t>
+          <t>TECNO COM</t>
         </is>
       </c>
       <c r="U114" t="inlineStr"/>
-      <c r="V114" t="inlineStr"/>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Atestado de dois dias em 26/06/2026. - Data Comentário: 01/07/2026 11:15</t>
+        </is>
+      </c>
       <c r="W114" t="inlineStr"/>
       <c r="X114" t="inlineStr"/>
       <c r="Y114" t="inlineStr"/>
@@ -13056,7 +13058,7 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>Santos Karina</t>
+          <t>Kaique Souza</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr"/>
@@ -13065,22 +13067,18 @@
       <c r="AE114" t="inlineStr"/>
       <c r="AF114" t="inlineStr">
         <is>
-          <t>Obrigação Acessória</t>
-        </is>
-      </c>
-      <c r="AG114" t="inlineStr">
-        <is>
-          <t>Leandro Matos</t>
-        </is>
-      </c>
+          <t>Tarefa</t>
+        </is>
+      </c>
+      <c r="AG114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>6779</v>
+        <v>5417</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>CORDEIRO E CIA LTDA</t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -13090,7 +13088,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -13100,11 +13098,11 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G115" t="n">
-        <v>11813</v>
+        <v>5792</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
@@ -13116,12 +13114,12 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Lançamentos de atestados</t>
+          <t>Periódicos - Mensal</t>
         </is>
       </c>
       <c r="K115" t="inlineStr"/>
       <c r="L115" s="1" t="n">
-        <v>46204</v>
+        <v>46209</v>
       </c>
       <c r="M115" t="inlineStr"/>
       <c r="N115" t="inlineStr">
@@ -13130,31 +13128,35 @@
         </is>
       </c>
       <c r="O115" t="n">
-        <v>18195904</v>
-      </c>
-      <c r="P115" t="inlineStr"/>
+        <v>17399005</v>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Mikael Teixeira</t>
+        </is>
+      </c>
       <c r="Q115" t="inlineStr">
         <is>
           <t>Baixado</t>
         </is>
       </c>
       <c r="R115" s="1" t="n">
-        <v>46204.48462402778</v>
+        <v>46195.57837077546</v>
       </c>
       <c r="S115" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
-        </is>
-      </c>
-      <c r="U115" t="inlineStr"/>
-      <c r="V115" t="inlineStr">
-        <is>
-          <t>Atestado de dois dias em 26/06/2026. - Data Comentário: 01/07/2026 11:15</t>
-        </is>
-      </c>
+          <t>NOSSO NOVO SUPERMERCADO</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr"/>
       <c r="W115" t="inlineStr"/>
       <c r="X115" t="inlineStr"/>
       <c r="Y115" t="inlineStr"/>
@@ -13163,7 +13165,7 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>Kaique Souza</t>
+          <t>Mikael Teixeira</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr"/>
@@ -13179,11 +13181,11 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>5417</v>
+        <v>5617</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -13203,7 +13205,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -13233,11 +13235,11 @@
         </is>
       </c>
       <c r="O116" t="n">
-        <v>17399005</v>
+        <v>17407619</v>
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Mikael Teixeira</t>
+          <t>Tania Luz</t>
         </is>
       </c>
       <c r="Q116" t="inlineStr">
@@ -13246,14 +13248,14 @@
         </is>
       </c>
       <c r="R116" s="1" t="n">
-        <v>46195.57837077546</v>
+        <v>46188.39084737268</v>
       </c>
       <c r="S116" t="n">
         <v>7</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U116" t="inlineStr">
@@ -13270,7 +13272,7 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>Mikael Teixeira</t>
+          <t>Tania Luz</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr"/>
@@ -13282,15 +13284,19 @@
           <t>Tarefa</t>
         </is>
       </c>
-      <c r="AG116" t="inlineStr"/>
+      <c r="AG116" t="inlineStr">
+        <is>
+          <t>Edivaldo Veiga</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>5617</v>
+        <v>6224</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -13310,7 +13316,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -13340,7 +13346,7 @@
         </is>
       </c>
       <c r="O117" t="n">
-        <v>17407619</v>
+        <v>17688723</v>
       </c>
       <c r="P117" t="inlineStr">
         <is>
@@ -13353,7 +13359,7 @@
         </is>
       </c>
       <c r="R117" s="1" t="n">
-        <v>46188.39084737268</v>
+        <v>46188.39085099537</v>
       </c>
       <c r="S117" t="n">
         <v>7</v>
@@ -13397,11 +13403,11 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>6224</v>
+        <v>6279</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>DIENNYFER DA S PEREIRA</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -13411,7 +13417,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -13451,27 +13457,23 @@
         </is>
       </c>
       <c r="O118" t="n">
-        <v>17688723</v>
-      </c>
-      <c r="P118" t="inlineStr">
-        <is>
-          <t>Tania Luz</t>
-        </is>
-      </c>
+        <v>17645987</v>
+      </c>
+      <c r="P118" t="inlineStr"/>
       <c r="Q118" t="inlineStr">
         <is>
           <t>Baixado</t>
         </is>
       </c>
       <c r="R118" s="1" t="n">
-        <v>46188.39085099537</v>
+        <v>46189.61008070602</v>
       </c>
       <c r="S118" t="n">
         <v>7</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U118" t="inlineStr">
@@ -13488,7 +13490,7 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>Tania Luz</t>
+          <t>Elaine Assis</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr"/>
@@ -13500,19 +13502,15 @@
           <t>Tarefa</t>
         </is>
       </c>
-      <c r="AG118" t="inlineStr">
-        <is>
-          <t>Edivaldo Veiga</t>
-        </is>
-      </c>
+      <c r="AG118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>6279</v>
+        <v>6486</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>DIENNYFER DA S PEREIRA</t>
+          <t>PC GAMER GOIANIA LTDA</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -13522,7 +13520,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -13532,7 +13530,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -13562,23 +13560,27 @@
         </is>
       </c>
       <c r="O119" t="n">
-        <v>17645987</v>
-      </c>
-      <c r="P119" t="inlineStr"/>
+        <v>16976014</v>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Jakeline Silva</t>
+        </is>
+      </c>
       <c r="Q119" t="inlineStr">
         <is>
           <t>Baixado</t>
         </is>
       </c>
       <c r="R119" s="1" t="n">
-        <v>46189.61008070602</v>
+        <v>46185.66827939815</v>
       </c>
       <c r="S119" t="n">
         <v>7</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>PC GAMER</t>
         </is>
       </c>
       <c r="U119" t="inlineStr">
@@ -13595,7 +13597,7 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>Elaine Assis</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr"/>
@@ -13607,15 +13609,19 @@
           <t>Tarefa</t>
         </is>
       </c>
-      <c r="AG119" t="inlineStr"/>
+      <c r="AG119" t="inlineStr">
+        <is>
+          <t>David Bragança</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>6486</v>
+        <v>6548</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>PC GAMER GOIANIA LTDA</t>
+          <t>GOIAS SILAGEM LTDA</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -13665,11 +13671,11 @@
         </is>
       </c>
       <c r="O120" t="n">
-        <v>16976014</v>
+        <v>17222547</v>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Daniel Moraes</t>
         </is>
       </c>
       <c r="Q120" t="inlineStr">
@@ -13678,14 +13684,14 @@
         </is>
       </c>
       <c r="R120" s="1" t="n">
-        <v>46185.66827939815</v>
+        <v>46190.56460636574</v>
       </c>
       <c r="S120" t="n">
         <v>7</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
-          <t>PC GAMER</t>
+          <t>GOIAS SILAGEM</t>
         </is>
       </c>
       <c r="U120" t="inlineStr">
@@ -13702,7 +13708,7 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Evellin Bispo</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr"/>
@@ -13722,11 +13728,11 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM LTDA</t>
+          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -13741,7 +13747,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -13776,11 +13782,11 @@
         </is>
       </c>
       <c r="O121" t="n">
-        <v>17222547</v>
+        <v>18068472</v>
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Daniel Moraes</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="Q121" t="inlineStr">
@@ -13789,14 +13795,14 @@
         </is>
       </c>
       <c r="R121" s="1" t="n">
-        <v>46190.56460636574</v>
+        <v>46185.66566952546</v>
       </c>
       <c r="S121" t="n">
         <v>7</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM</t>
+          <t xml:space="preserve">GTG </t>
         </is>
       </c>
       <c r="U121" t="inlineStr">
@@ -13813,7 +13819,7 @@
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>Evellin Bispo</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr"/>
@@ -13833,11 +13839,11 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -13847,7 +13853,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -13887,7 +13893,7 @@
         </is>
       </c>
       <c r="O122" t="n">
-        <v>18068472</v>
+        <v>18052393</v>
       </c>
       <c r="P122" t="inlineStr">
         <is>
@@ -13900,7 +13906,7 @@
         </is>
       </c>
       <c r="R122" s="1" t="n">
-        <v>46185.66566952546</v>
+        <v>46185.66535266204</v>
       </c>
       <c r="S122" t="n">
         <v>7</v>
@@ -13944,11 +13950,11 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>6628</v>
+        <v>6779</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>CORDEIRO E CIA LTDA</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -13963,7 +13969,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -13998,11 +14004,11 @@
         </is>
       </c>
       <c r="O123" t="n">
-        <v>18052393</v>
+        <v>18090122</v>
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Kaique Souza</t>
         </is>
       </c>
       <c r="Q123" t="inlineStr">
@@ -14011,21 +14017,17 @@
         </is>
       </c>
       <c r="R123" s="1" t="n">
-        <v>46185.66535266204</v>
+        <v>46185.69383032407</v>
       </c>
       <c r="S123" t="n">
         <v>7</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
-        </is>
-      </c>
-      <c r="U123" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>TECNO COM</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr"/>
       <c r="V123" t="inlineStr"/>
       <c r="W123" t="inlineStr"/>
       <c r="X123" t="inlineStr"/>
@@ -14035,7 +14037,7 @@
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Kaique Souza</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr"/>
@@ -14049,17 +14051,17 @@
       </c>
       <c r="AG123" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>6779</v>
+        <v>6885</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>CORDEIRO E CIA LTDA</t>
+          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -14109,11 +14111,11 @@
         </is>
       </c>
       <c r="O124" t="n">
-        <v>18090122</v>
+        <v>18157217</v>
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Kaique Souza</t>
+          <t>Vitor Guedes</t>
         </is>
       </c>
       <c r="Q124" t="inlineStr">
@@ -14122,14 +14124,14 @@
         </is>
       </c>
       <c r="R124" s="1" t="n">
-        <v>46185.69383032407</v>
+        <v>46195.70875512731</v>
       </c>
       <c r="S124" t="n">
         <v>7</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U124" t="inlineStr"/>
@@ -14142,7 +14144,7 @@
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>Kaique Souza</t>
+          <t>Elaine Assis</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr"/>
@@ -14156,17 +14158,17 @@
       </c>
       <c r="AG124" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>David Bragança</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>6885</v>
+        <v>6945</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
+          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -14181,7 +14183,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -14216,11 +14218,11 @@
         </is>
       </c>
       <c r="O125" t="n">
-        <v>18157217</v>
+        <v>18179059</v>
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Vitor Guedes</t>
+          <t>Santos Karina</t>
         </is>
       </c>
       <c r="Q125" t="inlineStr">
@@ -14229,14 +14231,14 @@
         </is>
       </c>
       <c r="R125" s="1" t="n">
-        <v>46195.70875512731</v>
+        <v>46195.70011658565</v>
       </c>
       <c r="S125" t="n">
         <v>7</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>BRASIL DISTRIBUIDORA</t>
         </is>
       </c>
       <c r="U125" t="inlineStr"/>
@@ -14249,7 +14251,7 @@
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>Elaine Assis</t>
+          <t>Santos Karina</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr"/>
@@ -14263,17 +14265,17 @@
       </c>
       <c r="AG125" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Leandro Matos</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>6945</v>
+        <v>6486</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
+          <t>PC GAMER GOIANIA LTDA</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -14283,12 +14285,12 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -14297,10 +14299,10 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>5792</v>
+        <v>5838</v>
       </c>
       <c r="H126" t="n">
-        <v>0</v>
+        <v>5784</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
@@ -14309,25 +14311,29 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Periódicos - Mensal</t>
+          <t>Rebto planilha/Resumo de Folha (01)</t>
         </is>
       </c>
       <c r="K126" t="inlineStr"/>
       <c r="L126" s="1" t="n">
-        <v>46209</v>
-      </c>
-      <c r="M126" t="inlineStr"/>
+        <v>46204</v>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
       <c r="N126" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O126" t="n">
-        <v>18179059</v>
+        <v>18157805</v>
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Santos Karina</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="Q126" t="inlineStr">
@@ -14336,18 +14342,27 @@
         </is>
       </c>
       <c r="R126" s="1" t="n">
-        <v>46195.70011658565</v>
+        <v>46205.59156991898</v>
       </c>
       <c r="S126" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA</t>
-        </is>
-      </c>
-      <c r="U126" t="inlineStr"/>
-      <c r="V126" t="inlineStr"/>
+          <t>PC GAMER</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 03/07/2026 
+Cliente informou que será enviado até 03/07. - Data Comentário: 01/07/2026 17:28</t>
+        </is>
+      </c>
       <c r="W126" t="inlineStr"/>
       <c r="X126" t="inlineStr"/>
       <c r="Y126" t="inlineStr"/>
@@ -14356,7 +14371,7 @@
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>Santos Karina</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr"/>
@@ -14370,17 +14385,17 @@
       </c>
       <c r="AG126" t="inlineStr">
         <is>
-          <t>Leandro Matos</t>
+          <t>David Bragança</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>6486</v>
+        <v>6627</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>PC GAMER GOIANIA LTDA</t>
+          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -14395,7 +14410,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -14434,7 +14449,7 @@
         </is>
       </c>
       <c r="O127" t="n">
-        <v>18157805</v>
+        <v>18157813</v>
       </c>
       <c r="P127" t="inlineStr">
         <is>
@@ -14447,14 +14462,14 @@
         </is>
       </c>
       <c r="R127" s="1" t="n">
-        <v>46205.59156991898</v>
+        <v>46205.73670511574</v>
       </c>
       <c r="S127" t="n">
         <v>12</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
-          <t>PC GAMER</t>
+          <t xml:space="preserve">GTG </t>
         </is>
       </c>
       <c r="U127" t="inlineStr">
@@ -14496,11 +14511,11 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -14510,7 +14525,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -14554,7 +14569,7 @@
         </is>
       </c>
       <c r="O128" t="n">
-        <v>18157813</v>
+        <v>18157796</v>
       </c>
       <c r="P128" t="inlineStr">
         <is>
@@ -14567,7 +14582,7 @@
         </is>
       </c>
       <c r="R128" s="1" t="n">
-        <v>46205.73670511574</v>
+        <v>46205.7367062037</v>
       </c>
       <c r="S128" t="n">
         <v>12</v>
@@ -14616,11 +14631,11 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>6628</v>
+        <v>6703</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -14630,12 +14645,12 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -14665,7 +14680,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -14674,11 +14689,11 @@
         </is>
       </c>
       <c r="O129" t="n">
-        <v>18157796</v>
+        <v>18195913</v>
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Ana Marcelino</t>
         </is>
       </c>
       <c r="Q129" t="inlineStr">
@@ -14687,14 +14702,14 @@
         </is>
       </c>
       <c r="R129" s="1" t="n">
-        <v>46205.7367062037</v>
+        <v>46206.43991525463</v>
       </c>
       <c r="S129" t="n">
         <v>12</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
+          <t>LIMA MOTA</t>
         </is>
       </c>
       <c r="U129" t="inlineStr">
@@ -14704,8 +14719,8 @@
       </c>
       <c r="V129" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 03/07/2026 
-Cliente informou que será enviado até 03/07. - Data Comentário: 01/07/2026 17:28</t>
+          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 02/07/2026 
+Em contato com o cliente, o mesmo informou que enviará até amanhã 02/07 - Data Comentário: 01/07/2026 16:29</t>
         </is>
       </c>
       <c r="W129" t="inlineStr"/>
@@ -14716,7 +14731,7 @@
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Elaine Assis</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr"/>
@@ -14730,17 +14745,17 @@
       </c>
       <c r="AG129" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>6703</v>
+        <v>6548</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
+          <t>GOIAS SILAGEM LTDA</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -14750,7 +14765,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -14764,7 +14779,7 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>5838</v>
+        <v>5839</v>
       </c>
       <c r="H130" t="n">
         <v>5784</v>
@@ -14776,29 +14791,25 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>Rebto planilha/Resumo de Folha (01)</t>
+          <t>Rebto planilha/Resumo de Folha (02)</t>
         </is>
       </c>
       <c r="K130" t="inlineStr"/>
       <c r="L130" s="1" t="n">
-        <v>46204</v>
-      </c>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>02/07/2026</t>
-        </is>
-      </c>
+        <v>46205</v>
+      </c>
+      <c r="M130" t="inlineStr"/>
       <c r="N130" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O130" t="n">
-        <v>18195913</v>
+        <v>18158841</v>
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Ana Marcelino</t>
+          <t>Daniel Moraes</t>
         </is>
       </c>
       <c r="Q130" t="inlineStr">
@@ -14807,14 +14818,14 @@
         </is>
       </c>
       <c r="R130" s="1" t="n">
-        <v>46206.43991525463</v>
+        <v>46205.34573362269</v>
       </c>
       <c r="S130" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
-          <t>LIMA MOTA</t>
+          <t>GOIAS SILAGEM</t>
         </is>
       </c>
       <c r="U130" t="inlineStr">
@@ -14822,12 +14833,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V130" t="inlineStr">
-        <is>
-          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 02/07/2026 
-Em contato com o cliente, o mesmo informou que enviará até amanhã 02/07 - Data Comentário: 01/07/2026 16:29</t>
-        </is>
-      </c>
+      <c r="V130" t="inlineStr"/>
       <c r="W130" t="inlineStr"/>
       <c r="X130" t="inlineStr"/>
       <c r="Y130" t="inlineStr"/>
@@ -14836,7 +14842,7 @@
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>Elaine Assis</t>
+          <t>Evellin Bispo</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr"/>
@@ -14850,17 +14856,17 @@
       </c>
       <c r="AG130" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>David Bragança</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>6548</v>
+        <v>5417</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM LTDA</t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -14880,11 +14886,11 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G131" t="n">
-        <v>5839</v>
+        <v>5906</v>
       </c>
       <c r="H131" t="n">
         <v>5784</v>
@@ -14896,12 +14902,12 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>Rebto planilha/Resumo de Folha (02)</t>
+          <t>Recibo de Pagamento</t>
         </is>
       </c>
       <c r="K131" t="inlineStr"/>
       <c r="L131" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="M131" t="inlineStr"/>
       <c r="N131" t="inlineStr">
@@ -14910,11 +14916,11 @@
         </is>
       </c>
       <c r="O131" t="n">
-        <v>18158841</v>
+        <v>17399104</v>
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Daniel Moraes</t>
+          <t>Mikael Teixeira</t>
         </is>
       </c>
       <c r="Q131" t="inlineStr">
@@ -14923,14 +14929,14 @@
         </is>
       </c>
       <c r="R131" s="1" t="n">
-        <v>46205.34573362269</v>
+        <v>46206.65428631944</v>
       </c>
       <c r="S131" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM</t>
+          <t>NOSSO NOVO SUPERMERCADO</t>
         </is>
       </c>
       <c r="U131" t="inlineStr">
@@ -14947,7 +14953,7 @@
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>Evellin Bispo</t>
+          <t>Mikael Teixeira</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr"/>
@@ -14959,19 +14965,15 @@
           <t>Tarefa</t>
         </is>
       </c>
-      <c r="AG131" t="inlineStr">
-        <is>
-          <t>David Bragança</t>
-        </is>
-      </c>
+      <c r="AG131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>SOLAR INVESTIMENTOS LTDA</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -14981,7 +14983,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -14991,7 +14993,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -15021,11 +15023,11 @@
         </is>
       </c>
       <c r="O132" t="n">
-        <v>17399104</v>
+        <v>16962228</v>
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Mikael Teixeira</t>
+          <t>Jhenifer Tenorio</t>
         </is>
       </c>
       <c r="Q132" t="inlineStr">
@@ -15034,14 +15036,14 @@
         </is>
       </c>
       <c r="R132" s="1" t="n">
-        <v>46206.65428631944</v>
+        <v>46199.67793730324</v>
       </c>
       <c r="S132" t="n">
         <v>7</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
+          <t>SOLAR INVESTIMENTOS</t>
         </is>
       </c>
       <c r="U132" t="inlineStr">
@@ -15058,7 +15060,7 @@
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>Mikael Teixeira</t>
+          <t>Jhenifer Tenorio</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr"/>
@@ -15070,15 +15072,19 @@
           <t>Tarefa</t>
         </is>
       </c>
-      <c r="AG132" t="inlineStr"/>
+      <c r="AG132" t="inlineStr">
+        <is>
+          <t>Sara Cavalheiro</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>6404</v>
+        <v>6486</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS LTDA</t>
+          <t>PC GAMER GOIANIA LTDA</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -15088,7 +15094,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -15128,11 +15134,11 @@
         </is>
       </c>
       <c r="O133" t="n">
-        <v>16962228</v>
+        <v>16976094</v>
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Jhenifer Tenorio</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="Q133" t="inlineStr">
@@ -15141,14 +15147,14 @@
         </is>
       </c>
       <c r="R133" s="1" t="n">
-        <v>46199.67793730324</v>
+        <v>46206.55866898148</v>
       </c>
       <c r="S133" t="n">
         <v>7</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS</t>
+          <t>PC GAMER</t>
         </is>
       </c>
       <c r="U133" t="inlineStr">
@@ -15165,7 +15171,7 @@
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>Jhenifer Tenorio</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr"/>
@@ -15179,17 +15185,17 @@
       </c>
       <c r="AG133" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>David Bragança</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>6486</v>
+        <v>6627</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PC GAMER GOIANIA LTDA</t>
+          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -15204,7 +15210,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -15239,7 +15245,7 @@
         </is>
       </c>
       <c r="O134" t="n">
-        <v>16976094</v>
+        <v>18068586</v>
       </c>
       <c r="P134" t="inlineStr">
         <is>
@@ -15252,14 +15258,14 @@
         </is>
       </c>
       <c r="R134" s="1" t="n">
-        <v>46206.55866898148</v>
+        <v>46206.6716975926</v>
       </c>
       <c r="S134" t="n">
         <v>7</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
-          <t>PC GAMER</t>
+          <t xml:space="preserve">GTG </t>
         </is>
       </c>
       <c r="U134" t="inlineStr">
@@ -15296,11 +15302,11 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -15310,7 +15316,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -15350,7 +15356,7 @@
         </is>
       </c>
       <c r="O135" t="n">
-        <v>18068586</v>
+        <v>18052505</v>
       </c>
       <c r="P135" t="inlineStr">
         <is>
@@ -15363,7 +15369,7 @@
         </is>
       </c>
       <c r="R135" s="1" t="n">
-        <v>46206.6716975926</v>
+        <v>46206.67205873843</v>
       </c>
       <c r="S135" t="n">
         <v>7</v>
@@ -15407,11 +15413,11 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>6628</v>
+        <v>6703</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -15421,12 +15427,12 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -15461,11 +15467,11 @@
         </is>
       </c>
       <c r="O136" t="n">
-        <v>18052505</v>
+        <v>18077140</v>
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Ana Marcelino</t>
         </is>
       </c>
       <c r="Q136" t="inlineStr">
@@ -15474,14 +15480,14 @@
         </is>
       </c>
       <c r="R136" s="1" t="n">
-        <v>46206.67205873843</v>
+        <v>46206.62895168982</v>
       </c>
       <c r="S136" t="n">
         <v>7</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
+          <t>LIMA MOTA</t>
         </is>
       </c>
       <c r="U136" t="inlineStr">
@@ -15498,7 +15504,7 @@
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Elaine Assis</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr"/>
@@ -15512,17 +15518,17 @@
       </c>
       <c r="AG136" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>6703</v>
+        <v>6779</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
+          <t>CORDEIRO E CIA LTDA</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -15532,7 +15538,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -15565,18 +15571,22 @@
       <c r="L137" s="1" t="n">
         <v>46209</v>
       </c>
-      <c r="M137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
       <c r="N137" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O137" t="n">
-        <v>18077140</v>
+        <v>18090227</v>
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Ana Marcelino</t>
+          <t>Kaique Souza</t>
         </is>
       </c>
       <c r="Q137" t="inlineStr">
@@ -15585,22 +15595,22 @@
         </is>
       </c>
       <c r="R137" s="1" t="n">
-        <v>46206.62895168982</v>
+        <v>46206.6443237037</v>
       </c>
       <c r="S137" t="n">
         <v>7</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
-          <t>LIMA MOTA</t>
-        </is>
-      </c>
-      <c r="U137" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="V137" t="inlineStr"/>
+          <t>TECNO COM</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr"/>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>2. Folha Processada aguardando OK do cliente para finalização   Previsão para conclusão dia 06/07/2026 - Data Comentário: 03/07/2026 14:18</t>
+        </is>
+      </c>
       <c r="W137" t="inlineStr"/>
       <c r="X137" t="inlineStr"/>
       <c r="Y137" t="inlineStr"/>
@@ -15609,7 +15619,7 @@
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>Elaine Assis</t>
+          <t>Kaique Souza</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr"/>
@@ -15629,11 +15639,11 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>6779</v>
+        <v>6885</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>CORDEIRO E CIA LTDA</t>
+          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -15676,22 +15686,18 @@
       <c r="L138" s="1" t="n">
         <v>46209</v>
       </c>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>06/07/2026</t>
-        </is>
-      </c>
+      <c r="M138" t="inlineStr"/>
       <c r="N138" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O138" t="n">
-        <v>18090227</v>
+        <v>18157308</v>
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Kaique Souza</t>
+          <t>Vitor Guedes</t>
         </is>
       </c>
       <c r="Q138" t="inlineStr">
@@ -15700,22 +15706,18 @@
         </is>
       </c>
       <c r="R138" s="1" t="n">
-        <v>46206.6443237037</v>
+        <v>46205.69251481481</v>
       </c>
       <c r="S138" t="n">
         <v>7</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U138" t="inlineStr"/>
-      <c r="V138" t="inlineStr">
-        <is>
-          <t>2. Folha Processada aguardando OK do cliente para finalização   Previsão para conclusão dia 06/07/2026 - Data Comentário: 03/07/2026 14:18</t>
-        </is>
-      </c>
+      <c r="V138" t="inlineStr"/>
       <c r="W138" t="inlineStr"/>
       <c r="X138" t="inlineStr"/>
       <c r="Y138" t="inlineStr"/>
@@ -15724,7 +15726,7 @@
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>Kaique Souza</t>
+          <t>Vitor Guedes</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr"/>
@@ -15738,17 +15740,17 @@
       </c>
       <c r="AG138" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>David Bragança</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>6885</v>
+        <v>6945</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
+          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -15763,7 +15765,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -15798,11 +15800,11 @@
         </is>
       </c>
       <c r="O139" t="n">
-        <v>18157308</v>
+        <v>18179137</v>
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Vitor Guedes</t>
+          <t>Santos Karina</t>
         </is>
       </c>
       <c r="Q139" t="inlineStr">
@@ -15811,14 +15813,14 @@
         </is>
       </c>
       <c r="R139" s="1" t="n">
-        <v>46205.69251481481</v>
+        <v>46206.69781152777</v>
       </c>
       <c r="S139" t="n">
         <v>7</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>BRASIL DISTRIBUIDORA</t>
         </is>
       </c>
       <c r="U139" t="inlineStr"/>
@@ -15831,7 +15833,7 @@
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>Vitor Guedes</t>
+          <t>Santos Karina</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr"/>
@@ -15845,17 +15847,17 @@
       </c>
       <c r="AG139" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Leandro Matos</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>6945</v>
+        <v>5417</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -15865,21 +15867,21 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G140" t="n">
-        <v>5906</v>
+        <v>5907</v>
       </c>
       <c r="H140" t="n">
         <v>5784</v>
@@ -15891,7 +15893,7 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Recibo de Pagamento</t>
+          <t>Relação Bancária - Salário</t>
         </is>
       </c>
       <c r="K140" t="inlineStr"/>
@@ -15905,11 +15907,11 @@
         </is>
       </c>
       <c r="O140" t="n">
-        <v>18179137</v>
+        <v>17399114</v>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Santos Karina</t>
+          <t>Mikael Teixeira</t>
         </is>
       </c>
       <c r="Q140" t="inlineStr">
@@ -15918,17 +15920,21 @@
         </is>
       </c>
       <c r="R140" s="1" t="n">
-        <v>46206.69781152777</v>
+        <v>46206.65440622685</v>
       </c>
       <c r="S140" t="n">
         <v>7</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA</t>
-        </is>
-      </c>
-      <c r="U140" t="inlineStr"/>
+          <t>NOSSO NOVO SUPERMERCADO</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V140" t="inlineStr"/>
       <c r="W140" t="inlineStr"/>
       <c r="X140" t="inlineStr"/>
@@ -15938,7 +15944,7 @@
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>Santos Karina</t>
+          <t>Mikael Teixeira</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr"/>
@@ -15950,19 +15956,15 @@
           <t>Tarefa</t>
         </is>
       </c>
-      <c r="AG140" t="inlineStr">
-        <is>
-          <t>Leandro Matos</t>
-        </is>
-      </c>
+      <c r="AG140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>SOLAR INVESTIMENTOS LTDA</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -15972,7 +15974,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -15982,7 +15984,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -16005,18 +16007,22 @@
       <c r="L141" s="1" t="n">
         <v>46209</v>
       </c>
-      <c r="M141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
       <c r="N141" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O141" t="n">
-        <v>17399114</v>
+        <v>16962238</v>
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Mikael Teixeira</t>
+          <t>Jhenifer Tenorio</t>
         </is>
       </c>
       <c r="Q141" t="inlineStr">
@@ -16025,14 +16031,14 @@
         </is>
       </c>
       <c r="R141" s="1" t="n">
-        <v>46206.65440622685</v>
+        <v>46206.40915328704</v>
       </c>
       <c r="S141" t="n">
         <v>7</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
+          <t>SOLAR INVESTIMENTOS</t>
         </is>
       </c>
       <c r="U141" t="inlineStr">
@@ -16040,7 +16046,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V141" t="inlineStr"/>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 03/07/2026 - Data Comentário: 26/06/2026 16:43</t>
+        </is>
+      </c>
       <c r="W141" t="inlineStr"/>
       <c r="X141" t="inlineStr"/>
       <c r="Y141" t="inlineStr"/>
@@ -16049,7 +16059,7 @@
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>Mikael Teixeira</t>
+          <t>Jhenifer Tenorio</t>
         </is>
       </c>
       <c r="AB141" t="inlineStr"/>
@@ -16061,15 +16071,19 @@
           <t>Tarefa</t>
         </is>
       </c>
-      <c r="AG141" t="inlineStr"/>
+      <c r="AG141" t="inlineStr">
+        <is>
+          <t>Sara Cavalheiro</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>6404</v>
+        <v>6486</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS LTDA</t>
+          <t>PC GAMER GOIANIA LTDA</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -16079,7 +16093,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -16112,22 +16126,18 @@
       <c r="L142" s="1" t="n">
         <v>46209</v>
       </c>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
+      <c r="M142" t="inlineStr"/>
       <c r="N142" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O142" t="n">
-        <v>16962238</v>
+        <v>16976104</v>
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Jhenifer Tenorio</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="Q142" t="inlineStr">
@@ -16136,14 +16146,14 @@
         </is>
       </c>
       <c r="R142" s="1" t="n">
-        <v>46206.40915328704</v>
+        <v>46206.55870388889</v>
       </c>
       <c r="S142" t="n">
         <v>7</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS</t>
+          <t>PC GAMER</t>
         </is>
       </c>
       <c r="U142" t="inlineStr">
@@ -16151,11 +16161,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V142" t="inlineStr">
-        <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 03/07/2026 - Data Comentário: 26/06/2026 16:43</t>
-        </is>
-      </c>
+      <c r="V142" t="inlineStr"/>
       <c r="W142" t="inlineStr"/>
       <c r="X142" t="inlineStr"/>
       <c r="Y142" t="inlineStr"/>
@@ -16164,7 +16170,7 @@
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>Jhenifer Tenorio</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="AB142" t="inlineStr"/>
@@ -16178,17 +16184,17 @@
       </c>
       <c r="AG142" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>David Bragança</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>6486</v>
+        <v>6627</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>PC GAMER GOIANIA LTDA</t>
+          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -16203,7 +16209,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -16238,7 +16244,7 @@
         </is>
       </c>
       <c r="O143" t="n">
-        <v>16976104</v>
+        <v>18068597</v>
       </c>
       <c r="P143" t="inlineStr">
         <is>
@@ -16251,14 +16257,14 @@
         </is>
       </c>
       <c r="R143" s="1" t="n">
-        <v>46206.55870388889</v>
+        <v>46206.67172778935</v>
       </c>
       <c r="S143" t="n">
         <v>7</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
-          <t>PC GAMER</t>
+          <t xml:space="preserve">GTG </t>
         </is>
       </c>
       <c r="U143" t="inlineStr">
@@ -16295,11 +16301,11 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -16309,7 +16315,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -16349,7 +16355,7 @@
         </is>
       </c>
       <c r="O144" t="n">
-        <v>18068597</v>
+        <v>18052516</v>
       </c>
       <c r="P144" t="inlineStr">
         <is>
@@ -16362,7 +16368,7 @@
         </is>
       </c>
       <c r="R144" s="1" t="n">
-        <v>46206.67172778935</v>
+        <v>46206.67209291667</v>
       </c>
       <c r="S144" t="n">
         <v>7</v>
@@ -16406,11 +16412,11 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>6628</v>
+        <v>6703</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -16420,12 +16426,12 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -16460,11 +16466,11 @@
         </is>
       </c>
       <c r="O145" t="n">
-        <v>18052516</v>
+        <v>18077150</v>
       </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Ana Marcelino</t>
         </is>
       </c>
       <c r="Q145" t="inlineStr">
@@ -16473,14 +16479,14 @@
         </is>
       </c>
       <c r="R145" s="1" t="n">
-        <v>46206.67209291667</v>
+        <v>46206.62899021991</v>
       </c>
       <c r="S145" t="n">
         <v>7</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
+          <t>LIMA MOTA</t>
         </is>
       </c>
       <c r="U145" t="inlineStr">
@@ -16497,7 +16503,7 @@
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Elaine Assis</t>
         </is>
       </c>
       <c r="AB145" t="inlineStr"/>
@@ -16511,17 +16517,17 @@
       </c>
       <c r="AG145" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>6703</v>
+        <v>6779</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
+          <t>CORDEIRO E CIA LTDA</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -16531,7 +16537,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -16564,18 +16570,22 @@
       <c r="L146" s="1" t="n">
         <v>46209</v>
       </c>
-      <c r="M146" t="inlineStr"/>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
       <c r="N146" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O146" t="n">
-        <v>18077150</v>
+        <v>18090237</v>
       </c>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Ana Marcelino</t>
+          <t>Kaique Souza</t>
         </is>
       </c>
       <c r="Q146" t="inlineStr">
@@ -16584,22 +16594,22 @@
         </is>
       </c>
       <c r="R146" s="1" t="n">
-        <v>46206.62899021991</v>
+        <v>46206.64435354167</v>
       </c>
       <c r="S146" t="n">
         <v>7</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
-          <t>LIMA MOTA</t>
-        </is>
-      </c>
-      <c r="U146" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="V146" t="inlineStr"/>
+          <t>TECNO COM</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr"/>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>2. Folha Processada aguardando OK do cliente para finalização   Previsão para conclusão dia 06/07/2026 - Data Comentário: 03/07/2026 14:18</t>
+        </is>
+      </c>
       <c r="W146" t="inlineStr"/>
       <c r="X146" t="inlineStr"/>
       <c r="Y146" t="inlineStr"/>
@@ -16608,7 +16618,7 @@
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>Elaine Assis</t>
+          <t>Kaique Souza</t>
         </is>
       </c>
       <c r="AB146" t="inlineStr"/>
@@ -16628,11 +16638,11 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>6779</v>
+        <v>6885</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>CORDEIRO E CIA LTDA</t>
+          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -16675,22 +16685,18 @@
       <c r="L147" s="1" t="n">
         <v>46209</v>
       </c>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>06/07/2026</t>
-        </is>
-      </c>
+      <c r="M147" t="inlineStr"/>
       <c r="N147" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O147" t="n">
-        <v>18090237</v>
+        <v>18157316</v>
       </c>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Kaique Souza</t>
+          <t>Vitor Guedes</t>
         </is>
       </c>
       <c r="Q147" t="inlineStr">
@@ -16699,22 +16705,18 @@
         </is>
       </c>
       <c r="R147" s="1" t="n">
-        <v>46206.64435354167</v>
+        <v>46205.69254519676</v>
       </c>
       <c r="S147" t="n">
         <v>7</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U147" t="inlineStr"/>
-      <c r="V147" t="inlineStr">
-        <is>
-          <t>2. Folha Processada aguardando OK do cliente para finalização   Previsão para conclusão dia 06/07/2026 - Data Comentário: 03/07/2026 14:18</t>
-        </is>
-      </c>
+      <c r="V147" t="inlineStr"/>
       <c r="W147" t="inlineStr"/>
       <c r="X147" t="inlineStr"/>
       <c r="Y147" t="inlineStr"/>
@@ -16723,7 +16725,7 @@
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>Kaique Souza</t>
+          <t>Vitor Guedes</t>
         </is>
       </c>
       <c r="AB147" t="inlineStr"/>
@@ -16737,17 +16739,17 @@
       </c>
       <c r="AG147" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>David Bragança</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>6885</v>
+        <v>6945</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
+          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -16762,7 +16764,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -16797,11 +16799,11 @@
         </is>
       </c>
       <c r="O148" t="n">
-        <v>18157316</v>
+        <v>18179144</v>
       </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Vitor Guedes</t>
+          <t>Santos Karina</t>
         </is>
       </c>
       <c r="Q148" t="inlineStr">
@@ -16810,14 +16812,14 @@
         </is>
       </c>
       <c r="R148" s="1" t="n">
-        <v>46205.69254519676</v>
+        <v>46206.69786020833</v>
       </c>
       <c r="S148" t="n">
         <v>7</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>BRASIL DISTRIBUIDORA</t>
         </is>
       </c>
       <c r="U148" t="inlineStr"/>
@@ -16830,7 +16832,7 @@
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>Vitor Guedes</t>
+          <t>Santos Karina</t>
         </is>
       </c>
       <c r="AB148" t="inlineStr"/>
@@ -16844,17 +16846,17 @@
       </c>
       <c r="AG148" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Leandro Matos</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>6945</v>
+        <v>5417</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -16864,24 +16866,24 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G149" t="n">
-        <v>5907</v>
+        <v>6348</v>
       </c>
       <c r="H149" t="n">
-        <v>5784</v>
+        <v>0</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
@@ -16890,45 +16892,49 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>Relação Bancária - Salário</t>
+          <t>RESCISÃO - RESCISÃO</t>
         </is>
       </c>
       <c r="K149" t="inlineStr"/>
       <c r="L149" s="1" t="n">
-        <v>46209</v>
+        <v>46211</v>
       </c>
       <c r="M149" t="inlineStr"/>
       <c r="N149" t="inlineStr">
         <is>
-          <t>06/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
       <c r="O149" t="n">
-        <v>18179144</v>
-      </c>
-      <c r="P149" t="inlineStr">
-        <is>
-          <t>Santos Karina</t>
-        </is>
-      </c>
+        <v>18178265</v>
+      </c>
+      <c r="P149" t="inlineStr"/>
       <c r="Q149" t="inlineStr">
         <is>
           <t>Baixado</t>
         </is>
       </c>
       <c r="R149" s="1" t="n">
-        <v>46206.69786020833</v>
+        <v>46206.65479178241</v>
       </c>
       <c r="S149" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA</t>
-        </is>
-      </c>
-      <c r="U149" t="inlineStr"/>
-      <c r="V149" t="inlineStr"/>
+          <t>NOSSO NOVO SUPERMERCADO</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>Pedido de demissão com aviso trabalhado em 01/06/2026 - vencimento da rescisão em 10/07/2026 - Data Comentário: 02/06/2026 11:20</t>
+        </is>
+      </c>
       <c r="W149" t="inlineStr"/>
       <c r="X149" t="inlineStr"/>
       <c r="Y149" t="inlineStr"/>
@@ -16937,7 +16943,7 @@
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>Santos Karina</t>
+          <t>Mikael Teixeira</t>
         </is>
       </c>
       <c r="AB149" t="inlineStr"/>
@@ -16946,22 +16952,18 @@
       <c r="AE149" t="inlineStr"/>
       <c r="AF149" t="inlineStr">
         <is>
-          <t>Tarefa</t>
-        </is>
-      </c>
-      <c r="AG149" t="inlineStr">
-        <is>
-          <t>Leandro Matos</t>
-        </is>
-      </c>
+          <t>Imposto</t>
+        </is>
+      </c>
+      <c r="AG149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>5417</v>
+        <v>6486</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>PC GAMER GOIANIA LTDA</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -16981,7 +16983,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -17002,16 +17004,20 @@
       </c>
       <c r="K150" t="inlineStr"/>
       <c r="L150" s="1" t="n">
-        <v>46211</v>
-      </c>
-      <c r="M150" t="inlineStr"/>
+        <v>46210</v>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
       <c r="N150" t="inlineStr">
         <is>
           <t>07/2026</t>
         </is>
       </c>
       <c r="O150" t="n">
-        <v>18178265</v>
+        <v>18167066</v>
       </c>
       <c r="P150" t="inlineStr"/>
       <c r="Q150" t="inlineStr">
@@ -17020,14 +17026,14 @@
         </is>
       </c>
       <c r="R150" s="1" t="n">
-        <v>46206.65479178241</v>
+        <v>46210.4994990162</v>
       </c>
       <c r="S150" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
+          <t>PC GAMER</t>
         </is>
       </c>
       <c r="U150" t="inlineStr">
@@ -17037,7 +17043,8 @@
       </c>
       <c r="V150" t="inlineStr">
         <is>
-          <t>Pedido de demissão com aviso trabalhado em 01/06/2026 - vencimento da rescisão em 10/07/2026 - Data Comentário: 02/06/2026 11:20</t>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 07/07/2026 
+PREVISÃO DE CONCLUSÃO: 07/07/2026 - Data Comentário: 06/07/2026 10:44</t>
         </is>
       </c>
       <c r="W150" t="inlineStr"/>
@@ -17048,7 +17055,7 @@
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>Mikael Teixeira</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="AB150" t="inlineStr"/>
@@ -17064,11 +17071,11 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>6486</v>
+        <v>6949</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>PC GAMER GOIANIA LTDA</t>
+          <t>TEC GRUA LOCAÇÃO E COMERCIO DE EQUIPAMENTOS PARA CONSTRUÇÃO LTDA</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -17088,7 +17095,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Reynaldo Santos</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -17109,11 +17116,11 @@
       </c>
       <c r="K151" t="inlineStr"/>
       <c r="L151" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -17122,34 +17129,34 @@
         </is>
       </c>
       <c r="O151" t="n">
-        <v>18167066</v>
-      </c>
-      <c r="P151" t="inlineStr"/>
+        <v>18199991</v>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>Gabriela Peres</t>
+        </is>
+      </c>
       <c r="Q151" t="inlineStr">
         <is>
           <t>Baixado</t>
         </is>
       </c>
       <c r="R151" s="1" t="n">
-        <v>46210.4994990162</v>
+        <v>46211.45479957176</v>
       </c>
       <c r="S151" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
-          <t>PC GAMER</t>
-        </is>
-      </c>
-      <c r="U151" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>TEC GRUA</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr"/>
       <c r="V151" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 07/07/2026 
-PREVISÃO DE CONCLUSÃO: 07/07/2026 - Data Comentário: 06/07/2026 10:44</t>
+          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 08/07/2026 
+Empresa em implantação, aguardando retorno do cliente para finalização. - Data Comentário: 07/07/2026 15:23</t>
         </is>
       </c>
       <c r="W151" t="inlineStr"/>
@@ -17160,7 +17167,7 @@
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Gabriela Peres</t>
         </is>
       </c>
       <c r="AB151" t="inlineStr"/>
@@ -17172,7 +17179,11 @@
           <t>Imposto</t>
         </is>
       </c>
-      <c r="AG151" t="inlineStr"/>
+      <c r="AG151" t="inlineStr">
+        <is>
+          <t>Leandro Matos</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -17221,20 +17232,16 @@
       </c>
       <c r="K152" t="inlineStr"/>
       <c r="L152" s="1" t="n">
-        <v>46211</v>
-      </c>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>08/07/2026</t>
-        </is>
-      </c>
+        <v>46218</v>
+      </c>
+      <c r="M152" t="inlineStr"/>
       <c r="N152" t="inlineStr">
         <is>
           <t>07/2026</t>
         </is>
       </c>
       <c r="O152" t="n">
-        <v>18199991</v>
+        <v>18201961</v>
       </c>
       <c r="P152" t="inlineStr">
         <is>
@@ -17247,10 +17254,10 @@
         </is>
       </c>
       <c r="R152" s="1" t="n">
-        <v>46211.45479957176</v>
+        <v>46216.61943571759</v>
       </c>
       <c r="S152" t="n">
-        <v>5</v>
+        <v>-2</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -17260,8 +17267,7 @@
       <c r="U152" t="inlineStr"/>
       <c r="V152" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 08/07/2026 
-Empresa em implantação, aguardando retorno do cliente para finalização. - Data Comentário: 07/07/2026 15:23</t>
+          <t>Pedido de demissão - Desconto de Aviso em 07/07/2026 - Pgto 17/07/2026 - Data Comentário: 08/07/2026 11:16</t>
         </is>
       </c>
       <c r="W152" t="inlineStr"/>

--- a/dados/base/goias.xlsx
+++ b/dados/base/goias.xlsx
@@ -53182,7 +53182,11 @@
       <c r="L486" s="1" t="n">
         <v>46220</v>
       </c>
-      <c r="M486" t="inlineStr"/>
+      <c r="M486" t="inlineStr">
+        <is>
+          <t>15/07/2026</t>
+        </is>
+      </c>
       <c r="N486" t="inlineStr">
         <is>
           <t>07/2026</t>
@@ -53211,7 +53215,12 @@
         </is>
       </c>
       <c r="U486" t="inlineStr"/>
-      <c r="V486" t="inlineStr"/>
+      <c r="V486" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 15/07/2026 
+Previsão de conclusão 15/07/2026 - Data Comentário: 13/07/2026 15:28</t>
+        </is>
+      </c>
       <c r="W486" t="inlineStr"/>
       <c r="X486" t="inlineStr"/>
       <c r="Y486" t="inlineStr"/>

--- a/dados/base/goias.xlsx
+++ b/dados/base/goias.xlsx
@@ -17131,11 +17131,7 @@
       <c r="O151" t="n">
         <v>18199991</v>
       </c>
-      <c r="P151" t="inlineStr">
-        <is>
-          <t>Gabriela Peres</t>
-        </is>
-      </c>
+      <c r="P151" t="inlineStr"/>
       <c r="Q151" t="inlineStr">
         <is>
           <t>Baixado</t>
@@ -17179,11 +17175,7 @@
           <t>Imposto</t>
         </is>
       </c>
-      <c r="AG151" t="inlineStr">
-        <is>
-          <t>Leandro Matos</t>
-        </is>
-      </c>
+      <c r="AG151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -17243,11 +17235,7 @@
       <c r="O152" t="n">
         <v>18201961</v>
       </c>
-      <c r="P152" t="inlineStr">
-        <is>
-          <t>Gabriela Peres</t>
-        </is>
-      </c>
+      <c r="P152" t="inlineStr"/>
       <c r="Q152" t="inlineStr">
         <is>
           <t>Baixado</t>
@@ -17290,11 +17278,7 @@
           <t>Imposto</t>
         </is>
       </c>
-      <c r="AG152" t="inlineStr">
-        <is>
-          <t>Leandro Matos</t>
-        </is>
-      </c>
+      <c r="AG152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">

--- a/dados/base/goias.xlsx
+++ b/dados/base/goias.xlsx
@@ -3583,7 +3583,11 @@
       <c r="L29" s="1" t="n">
         <v>46218</v>
       </c>
-      <c r="M29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr">
         <is>
           <t>06/2026</t>
@@ -3616,7 +3620,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr"/>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 14/07/2026 - Data Comentário: 13/07/2026 19:28</t>
+        </is>
+      </c>
       <c r="W29" t="inlineStr"/>
       <c r="X29" t="inlineStr"/>
       <c r="Y29" t="inlineStr"/>

--- a/dados/base/goias.xlsx
+++ b/dados/base/goias.xlsx
@@ -42837,7 +42837,7 @@
       </c>
       <c r="R386" t="inlineStr"/>
       <c r="S386" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T386" t="inlineStr">
         <is>
@@ -42942,7 +42942,7 @@
       </c>
       <c r="R387" t="inlineStr"/>
       <c r="S387" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T387" t="inlineStr">
         <is>
@@ -43047,7 +43047,7 @@
       </c>
       <c r="R388" t="inlineStr"/>
       <c r="S388" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T388" t="inlineStr">
         <is>
@@ -43152,7 +43152,7 @@
       </c>
       <c r="R389" t="inlineStr"/>
       <c r="S389" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T389" t="inlineStr">
         <is>
@@ -43253,7 +43253,7 @@
       </c>
       <c r="R390" t="inlineStr"/>
       <c r="S390" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T390" t="inlineStr">
         <is>
@@ -43354,7 +43354,7 @@
       </c>
       <c r="R391" t="inlineStr"/>
       <c r="S391" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T391" t="inlineStr">
         <is>
@@ -43455,7 +43455,7 @@
       </c>
       <c r="R392" t="inlineStr"/>
       <c r="S392" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T392" t="inlineStr">
         <is>
@@ -43560,7 +43560,7 @@
       </c>
       <c r="R393" t="inlineStr"/>
       <c r="S393" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T393" t="inlineStr">
         <is>
@@ -43665,7 +43665,7 @@
       </c>
       <c r="R394" t="inlineStr"/>
       <c r="S394" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="T394" t="inlineStr">
         <is>
@@ -43770,7 +43770,7 @@
       </c>
       <c r="R395" t="inlineStr"/>
       <c r="S395" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="T395" t="inlineStr">
         <is>
@@ -43875,7 +43875,7 @@
       </c>
       <c r="R396" t="inlineStr"/>
       <c r="S396" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="T396" t="inlineStr">
         <is>
@@ -43980,7 +43980,7 @@
       </c>
       <c r="R397" t="inlineStr"/>
       <c r="S397" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="T397" t="inlineStr">
         <is>
@@ -44081,7 +44081,7 @@
       </c>
       <c r="R398" t="inlineStr"/>
       <c r="S398" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="T398" t="inlineStr">
         <is>
@@ -44182,7 +44182,7 @@
       </c>
       <c r="R399" t="inlineStr"/>
       <c r="S399" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="T399" t="inlineStr">
         <is>
@@ -44283,7 +44283,7 @@
       </c>
       <c r="R400" t="inlineStr"/>
       <c r="S400" t="n">
-        <v>-16</v>
+        <v>-15</v>
       </c>
       <c r="T400" t="inlineStr">
         <is>
@@ -44388,7 +44388,7 @@
       </c>
       <c r="R401" t="inlineStr"/>
       <c r="S401" t="n">
-        <v>-16</v>
+        <v>-15</v>
       </c>
       <c r="T401" t="inlineStr">
         <is>
@@ -44493,7 +44493,7 @@
       </c>
       <c r="R402" t="inlineStr"/>
       <c r="S402" t="n">
-        <v>-16</v>
+        <v>-15</v>
       </c>
       <c r="T402" t="inlineStr">
         <is>
@@ -44594,7 +44594,7 @@
       </c>
       <c r="R403" t="inlineStr"/>
       <c r="S403" t="n">
-        <v>-16</v>
+        <v>-15</v>
       </c>
       <c r="T403" t="inlineStr">
         <is>
@@ -44695,7 +44695,7 @@
       </c>
       <c r="R404" t="inlineStr"/>
       <c r="S404" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="T404" t="inlineStr">
         <is>
@@ -44800,7 +44800,7 @@
       </c>
       <c r="R405" t="inlineStr"/>
       <c r="S405" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="T405" t="inlineStr">
         <is>
@@ -44905,7 +44905,7 @@
       </c>
       <c r="R406" t="inlineStr"/>
       <c r="S406" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="T406" t="inlineStr">
         <is>
@@ -45006,7 +45006,7 @@
       </c>
       <c r="R407" t="inlineStr"/>
       <c r="S407" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="T407" t="inlineStr">
         <is>
@@ -45107,7 +45107,7 @@
       </c>
       <c r="R408" t="inlineStr"/>
       <c r="S408" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T408" t="inlineStr">
         <is>
@@ -45212,7 +45212,7 @@
       </c>
       <c r="R409" t="inlineStr"/>
       <c r="S409" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T409" t="inlineStr">
         <is>
@@ -45317,7 +45317,7 @@
       </c>
       <c r="R410" t="inlineStr"/>
       <c r="S410" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T410" t="inlineStr">
         <is>
@@ -45418,7 +45418,7 @@
       </c>
       <c r="R411" t="inlineStr"/>
       <c r="S411" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T411" t="inlineStr">
         <is>
@@ -45519,7 +45519,7 @@
       </c>
       <c r="R412" t="inlineStr"/>
       <c r="S412" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T412" t="inlineStr">
         <is>
@@ -45624,7 +45624,7 @@
       </c>
       <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T413" t="inlineStr">
         <is>
@@ -45725,7 +45725,7 @@
       </c>
       <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T414" t="inlineStr">
         <is>
@@ -45830,7 +45830,7 @@
       </c>
       <c r="R415" t="inlineStr"/>
       <c r="S415" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T415" t="inlineStr">
         <is>
@@ -45935,7 +45935,7 @@
       </c>
       <c r="R416" t="inlineStr"/>
       <c r="S416" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T416" t="inlineStr">
         <is>
@@ -46036,7 +46036,7 @@
       </c>
       <c r="R417" t="inlineStr"/>
       <c r="S417" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T417" t="inlineStr">
         <is>
@@ -46137,7 +46137,7 @@
       </c>
       <c r="R418" t="inlineStr"/>
       <c r="S418" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T418" t="inlineStr">
         <is>
@@ -46242,7 +46242,7 @@
       </c>
       <c r="R419" t="inlineStr"/>
       <c r="S419" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T419" t="inlineStr">
         <is>
@@ -46347,7 +46347,7 @@
       </c>
       <c r="R420" t="inlineStr"/>
       <c r="S420" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T420" t="inlineStr">
         <is>
@@ -46452,7 +46452,7 @@
       </c>
       <c r="R421" t="inlineStr"/>
       <c r="S421" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T421" t="inlineStr">
         <is>
@@ -46557,7 +46557,7 @@
       </c>
       <c r="R422" t="inlineStr"/>
       <c r="S422" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T422" t="inlineStr">
         <is>
@@ -46662,7 +46662,7 @@
       </c>
       <c r="R423" t="inlineStr"/>
       <c r="S423" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T423" t="inlineStr">
         <is>
@@ -46767,7 +46767,7 @@
       </c>
       <c r="R424" t="inlineStr"/>
       <c r="S424" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T424" t="inlineStr">
         <is>
@@ -46872,7 +46872,7 @@
       </c>
       <c r="R425" t="inlineStr"/>
       <c r="S425" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T425" t="inlineStr">
         <is>
@@ -46977,7 +46977,7 @@
       </c>
       <c r="R426" t="inlineStr"/>
       <c r="S426" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T426" t="inlineStr">
         <is>
@@ -47082,7 +47082,7 @@
       </c>
       <c r="R427" t="inlineStr"/>
       <c r="S427" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T427" t="inlineStr">
         <is>
@@ -47187,7 +47187,7 @@
       </c>
       <c r="R428" t="inlineStr"/>
       <c r="S428" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T428" t="inlineStr">
         <is>
@@ -47288,7 +47288,7 @@
       </c>
       <c r="R429" t="inlineStr"/>
       <c r="S429" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T429" t="inlineStr">
         <is>
@@ -47389,7 +47389,7 @@
       </c>
       <c r="R430" t="inlineStr"/>
       <c r="S430" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T430" t="inlineStr">
         <is>
@@ -47494,7 +47494,7 @@
       </c>
       <c r="R431" t="inlineStr"/>
       <c r="S431" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T431" t="inlineStr">
         <is>
@@ -47599,7 +47599,7 @@
       </c>
       <c r="R432" t="inlineStr"/>
       <c r="S432" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T432" t="inlineStr">
         <is>
@@ -47704,7 +47704,7 @@
       </c>
       <c r="R433" t="inlineStr"/>
       <c r="S433" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T433" t="inlineStr">
         <is>
@@ -47809,7 +47809,7 @@
       </c>
       <c r="R434" t="inlineStr"/>
       <c r="S434" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T434" t="inlineStr">
         <is>
@@ -47914,7 +47914,7 @@
       </c>
       <c r="R435" t="inlineStr"/>
       <c r="S435" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="T435" t="inlineStr">
         <is>
@@ -48019,7 +48019,7 @@
       </c>
       <c r="R436" t="inlineStr"/>
       <c r="S436" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="T436" t="inlineStr">
         <is>
@@ -48124,7 +48124,7 @@
       </c>
       <c r="R437" t="inlineStr"/>
       <c r="S437" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="T437" t="inlineStr">
         <is>
@@ -48229,7 +48229,7 @@
       </c>
       <c r="R438" t="inlineStr"/>
       <c r="S438" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="T438" t="inlineStr">
         <is>
@@ -48334,7 +48334,7 @@
       </c>
       <c r="R439" t="inlineStr"/>
       <c r="S439" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="T439" t="inlineStr">
         <is>
@@ -48439,7 +48439,7 @@
       </c>
       <c r="R440" t="inlineStr"/>
       <c r="S440" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="T440" t="inlineStr">
         <is>
@@ -48544,7 +48544,7 @@
       </c>
       <c r="R441" t="inlineStr"/>
       <c r="S441" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="T441" t="inlineStr">
         <is>
@@ -48649,7 +48649,7 @@
       </c>
       <c r="R442" t="inlineStr"/>
       <c r="S442" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="T442" t="inlineStr">
         <is>
@@ -48754,7 +48754,7 @@
       </c>
       <c r="R443" t="inlineStr"/>
       <c r="S443" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="T443" t="inlineStr">
         <is>
@@ -48859,7 +48859,7 @@
       </c>
       <c r="R444" t="inlineStr"/>
       <c r="S444" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="T444" t="inlineStr">
         <is>
@@ -48964,7 +48964,7 @@
       </c>
       <c r="R445" t="inlineStr"/>
       <c r="S445" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="T445" t="inlineStr">
         <is>
@@ -49065,7 +49065,7 @@
       </c>
       <c r="R446" t="inlineStr"/>
       <c r="S446" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="T446" t="inlineStr">
         <is>
@@ -49166,7 +49166,7 @@
       </c>
       <c r="R447" t="inlineStr"/>
       <c r="S447" t="n">
-        <v>-16</v>
+        <v>-15</v>
       </c>
       <c r="T447" t="inlineStr">
         <is>
@@ -49271,7 +49271,7 @@
       </c>
       <c r="R448" t="inlineStr"/>
       <c r="S448" t="n">
-        <v>-16</v>
+        <v>-15</v>
       </c>
       <c r="T448" t="inlineStr">
         <is>
@@ -49376,7 +49376,7 @@
       </c>
       <c r="R449" t="inlineStr"/>
       <c r="S449" t="n">
-        <v>-16</v>
+        <v>-15</v>
       </c>
       <c r="T449" t="inlineStr">
         <is>
@@ -49481,7 +49481,7 @@
       </c>
       <c r="R450" t="inlineStr"/>
       <c r="S450" t="n">
-        <v>-16</v>
+        <v>-15</v>
       </c>
       <c r="T450" t="inlineStr">
         <is>
@@ -49586,7 +49586,7 @@
       </c>
       <c r="R451" t="inlineStr"/>
       <c r="S451" t="n">
-        <v>-16</v>
+        <v>-15</v>
       </c>
       <c r="T451" t="inlineStr">
         <is>
@@ -49691,7 +49691,7 @@
       </c>
       <c r="R452" t="inlineStr"/>
       <c r="S452" t="n">
-        <v>-16</v>
+        <v>-15</v>
       </c>
       <c r="T452" t="inlineStr">
         <is>
@@ -49796,7 +49796,7 @@
       </c>
       <c r="R453" t="inlineStr"/>
       <c r="S453" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="T453" t="inlineStr">
         <is>
@@ -49901,7 +49901,7 @@
       </c>
       <c r="R454" t="inlineStr"/>
       <c r="S454" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="T454" t="inlineStr">
         <is>
@@ -50006,7 +50006,7 @@
       </c>
       <c r="R455" t="inlineStr"/>
       <c r="S455" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="T455" t="inlineStr">
         <is>
@@ -50111,7 +50111,7 @@
       </c>
       <c r="R456" t="inlineStr"/>
       <c r="S456" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="T456" t="inlineStr">
         <is>
@@ -50216,7 +50216,7 @@
       </c>
       <c r="R457" t="inlineStr"/>
       <c r="S457" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="T457" t="inlineStr">
         <is>
@@ -50321,7 +50321,7 @@
       </c>
       <c r="R458" t="inlineStr"/>
       <c r="S458" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="T458" t="inlineStr">
         <is>
@@ -50426,7 +50426,7 @@
       </c>
       <c r="R459" t="inlineStr"/>
       <c r="S459" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="T459" t="inlineStr">
         <is>
@@ -50531,7 +50531,7 @@
       </c>
       <c r="R460" t="inlineStr"/>
       <c r="S460" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="T460" t="inlineStr">
         <is>
@@ -50636,7 +50636,7 @@
       </c>
       <c r="R461" t="inlineStr"/>
       <c r="S461" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="T461" t="inlineStr">
         <is>
@@ -50741,7 +50741,7 @@
       </c>
       <c r="R462" t="inlineStr"/>
       <c r="S462" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="T462" t="inlineStr">
         <is>
@@ -50846,7 +50846,7 @@
       </c>
       <c r="R463" t="inlineStr"/>
       <c r="S463" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="T463" t="inlineStr">
         <is>
@@ -50951,7 +50951,7 @@
       </c>
       <c r="R464" t="inlineStr"/>
       <c r="S464" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="T464" t="inlineStr">
         <is>
@@ -51056,7 +51056,7 @@
       </c>
       <c r="R465" t="inlineStr"/>
       <c r="S465" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T465" t="inlineStr">
         <is>
@@ -51161,7 +51161,7 @@
       </c>
       <c r="R466" t="inlineStr"/>
       <c r="S466" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T466" t="inlineStr">
         <is>
@@ -51266,7 +51266,7 @@
       </c>
       <c r="R467" t="inlineStr"/>
       <c r="S467" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T467" t="inlineStr">
         <is>
@@ -51371,7 +51371,7 @@
       </c>
       <c r="R468" t="inlineStr"/>
       <c r="S468" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T468" t="inlineStr">
         <is>
@@ -51476,7 +51476,7 @@
       </c>
       <c r="R469" t="inlineStr"/>
       <c r="S469" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T469" t="inlineStr">
         <is>
@@ -51581,7 +51581,7 @@
       </c>
       <c r="R470" t="inlineStr"/>
       <c r="S470" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T470" t="inlineStr">
         <is>
@@ -51686,7 +51686,7 @@
       </c>
       <c r="R471" t="inlineStr"/>
       <c r="S471" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T471" t="inlineStr">
         <is>
@@ -51791,7 +51791,7 @@
       </c>
       <c r="R472" t="inlineStr"/>
       <c r="S472" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T472" t="inlineStr">
         <is>
@@ -51896,7 +51896,7 @@
       </c>
       <c r="R473" t="inlineStr"/>
       <c r="S473" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T473" t="inlineStr">
         <is>
@@ -52001,7 +52001,7 @@
       </c>
       <c r="R474" t="inlineStr"/>
       <c r="S474" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T474" t="inlineStr">
         <is>
@@ -52106,7 +52106,7 @@
       </c>
       <c r="R475" t="inlineStr"/>
       <c r="S475" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T475" t="inlineStr">
         <is>
@@ -52207,7 +52207,7 @@
       </c>
       <c r="R476" t="inlineStr"/>
       <c r="S476" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T476" t="inlineStr">
         <is>
@@ -52308,7 +52308,7 @@
       </c>
       <c r="R477" t="inlineStr"/>
       <c r="S477" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T477" t="inlineStr">
         <is>
@@ -52413,7 +52413,7 @@
       </c>
       <c r="R478" t="inlineStr"/>
       <c r="S478" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T478" t="inlineStr">
         <is>
@@ -52518,7 +52518,7 @@
       </c>
       <c r="R479" t="inlineStr"/>
       <c r="S479" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T479" t="inlineStr">
         <is>
@@ -52623,7 +52623,7 @@
       </c>
       <c r="R480" t="inlineStr"/>
       <c r="S480" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T480" t="inlineStr">
         <is>
@@ -52728,7 +52728,7 @@
       </c>
       <c r="R481" t="inlineStr"/>
       <c r="S481" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T481" t="inlineStr">
         <is>
@@ -52833,7 +52833,7 @@
       </c>
       <c r="R482" t="inlineStr"/>
       <c r="S482" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T482" t="inlineStr">
         <is>
@@ -52942,7 +52942,7 @@
       </c>
       <c r="R483" t="inlineStr"/>
       <c r="S483" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T483" t="inlineStr">
         <is>
@@ -53052,7 +53052,7 @@
       </c>
       <c r="R484" t="inlineStr"/>
       <c r="S484" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T484" t="inlineStr">
         <is>
@@ -53166,7 +53166,7 @@
       </c>
       <c r="R485" t="inlineStr"/>
       <c r="S485" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T485" t="inlineStr">
         <is>
@@ -53280,7 +53280,7 @@
       </c>
       <c r="R486" t="inlineStr"/>
       <c r="S486" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T486" t="inlineStr">
         <is>
@@ -53386,7 +53386,7 @@
       </c>
       <c r="R487" t="inlineStr"/>
       <c r="S487" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T487" t="inlineStr">
         <is>
@@ -53495,7 +53495,7 @@
       </c>
       <c r="R488" t="inlineStr"/>
       <c r="S488" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T488" t="inlineStr">
         <is>
@@ -53604,7 +53604,7 @@
       </c>
       <c r="R489" t="inlineStr"/>
       <c r="S489" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T489" t="inlineStr">
         <is>
@@ -53717,7 +53717,7 @@
       </c>
       <c r="R490" t="inlineStr"/>
       <c r="S490" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T490" t="inlineStr">
         <is>
@@ -53831,7 +53831,7 @@
       </c>
       <c r="R491" t="inlineStr"/>
       <c r="S491" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T491" t="inlineStr">
         <is>
@@ -53941,7 +53941,7 @@
       </c>
       <c r="R492" t="inlineStr"/>
       <c r="S492" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="T492" t="inlineStr">
         <is>
@@ -54046,7 +54046,7 @@
       </c>
       <c r="R493" t="inlineStr"/>
       <c r="S493" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T493" t="inlineStr">
         <is>
@@ -54147,7 +54147,7 @@
       </c>
       <c r="R494" t="inlineStr"/>
       <c r="S494" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T494" t="inlineStr">
         <is>
@@ -54248,7 +54248,7 @@
       </c>
       <c r="R495" t="inlineStr"/>
       <c r="S495" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T495" t="inlineStr">
         <is>
@@ -54353,7 +54353,7 @@
       </c>
       <c r="R496" t="inlineStr"/>
       <c r="S496" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T496" t="inlineStr">
         <is>
@@ -54458,7 +54458,7 @@
       </c>
       <c r="R497" t="inlineStr"/>
       <c r="S497" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T497" t="inlineStr">
         <is>
@@ -54563,7 +54563,7 @@
       </c>
       <c r="R498" t="inlineStr"/>
       <c r="S498" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T498" t="inlineStr">
         <is>
@@ -54668,7 +54668,7 @@
       </c>
       <c r="R499" t="inlineStr"/>
       <c r="S499" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T499" t="inlineStr">
         <is>
@@ -54773,7 +54773,7 @@
       </c>
       <c r="R500" t="inlineStr"/>
       <c r="S500" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T500" t="inlineStr">
         <is>
@@ -54878,7 +54878,7 @@
       </c>
       <c r="R501" t="inlineStr"/>
       <c r="S501" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T501" t="inlineStr">
         <is>
@@ -54983,7 +54983,7 @@
       </c>
       <c r="R502" t="inlineStr"/>
       <c r="S502" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T502" t="inlineStr">
         <is>
@@ -55084,7 +55084,7 @@
       </c>
       <c r="R503" t="inlineStr"/>
       <c r="S503" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T503" t="inlineStr">
         <is>
@@ -55185,7 +55185,7 @@
       </c>
       <c r="R504" t="inlineStr"/>
       <c r="S504" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T504" t="inlineStr">
         <is>
@@ -55286,7 +55286,7 @@
       </c>
       <c r="R505" t="inlineStr"/>
       <c r="S505" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T505" t="inlineStr">
         <is>
@@ -55387,7 +55387,7 @@
       </c>
       <c r="R506" t="inlineStr"/>
       <c r="S506" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T506" t="inlineStr">
         <is>
@@ -55488,7 +55488,7 @@
       </c>
       <c r="R507" t="inlineStr"/>
       <c r="S507" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T507" t="inlineStr">
         <is>
@@ -55593,7 +55593,7 @@
       </c>
       <c r="R508" t="inlineStr"/>
       <c r="S508" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T508" t="inlineStr">
         <is>
@@ -55698,7 +55698,7 @@
       </c>
       <c r="R509" t="inlineStr"/>
       <c r="S509" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T509" t="inlineStr">
         <is>
@@ -55803,7 +55803,7 @@
       </c>
       <c r="R510" t="inlineStr"/>
       <c r="S510" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T510" t="inlineStr">
         <is>
@@ -55908,7 +55908,7 @@
       </c>
       <c r="R511" t="inlineStr"/>
       <c r="S511" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T511" t="inlineStr">
         <is>
@@ -56013,7 +56013,7 @@
       </c>
       <c r="R512" t="inlineStr"/>
       <c r="S512" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T512" t="inlineStr">
         <is>
@@ -56118,7 +56118,7 @@
       </c>
       <c r="R513" t="inlineStr"/>
       <c r="S513" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T513" t="inlineStr">
         <is>
@@ -56223,7 +56223,7 @@
       </c>
       <c r="R514" t="inlineStr"/>
       <c r="S514" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T514" t="inlineStr">
         <is>
@@ -56324,7 +56324,7 @@
       </c>
       <c r="R515" t="inlineStr"/>
       <c r="S515" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T515" t="inlineStr">
         <is>
@@ -56425,7 +56425,7 @@
       </c>
       <c r="R516" t="inlineStr"/>
       <c r="S516" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T516" t="inlineStr">
         <is>
@@ -56526,7 +56526,7 @@
       </c>
       <c r="R517" t="inlineStr"/>
       <c r="S517" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T517" t="inlineStr">
         <is>
@@ -56627,7 +56627,7 @@
       </c>
       <c r="R518" t="inlineStr"/>
       <c r="S518" t="n">
-        <v>-18</v>
+        <v>-17</v>
       </c>
       <c r="T518" t="inlineStr">
         <is>
@@ -56732,7 +56732,7 @@
       </c>
       <c r="R519" t="inlineStr"/>
       <c r="S519" t="n">
-        <v>-18</v>
+        <v>-17</v>
       </c>
       <c r="T519" t="inlineStr">
         <is>
@@ -56837,7 +56837,7 @@
       </c>
       <c r="R520" t="inlineStr"/>
       <c r="S520" t="n">
-        <v>-18</v>
+        <v>-17</v>
       </c>
       <c r="T520" t="inlineStr">
         <is>
@@ -56942,7 +56942,7 @@
       </c>
       <c r="R521" t="inlineStr"/>
       <c r="S521" t="n">
-        <v>-18</v>
+        <v>-17</v>
       </c>
       <c r="T521" t="inlineStr">
         <is>
@@ -57043,7 +57043,7 @@
       </c>
       <c r="R522" t="inlineStr"/>
       <c r="S522" t="n">
-        <v>-18</v>
+        <v>-17</v>
       </c>
       <c r="T522" t="inlineStr">
         <is>
@@ -57148,7 +57148,7 @@
       </c>
       <c r="R523" t="inlineStr"/>
       <c r="S523" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T523" t="inlineStr">
         <is>
@@ -57253,7 +57253,7 @@
       </c>
       <c r="R524" t="inlineStr"/>
       <c r="S524" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T524" t="inlineStr">
         <is>
@@ -57354,7 +57354,7 @@
       </c>
       <c r="R525" t="inlineStr"/>
       <c r="S525" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T525" t="inlineStr">
         <is>
@@ -57455,7 +57455,7 @@
       </c>
       <c r="R526" t="inlineStr"/>
       <c r="S526" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T526" t="inlineStr">
         <is>
@@ -57560,7 +57560,7 @@
       </c>
       <c r="R527" t="inlineStr"/>
       <c r="S527" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T527" t="inlineStr">
         <is>
@@ -57665,7 +57665,7 @@
       </c>
       <c r="R528" t="inlineStr"/>
       <c r="S528" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T528" t="inlineStr">
         <is>
@@ -57770,7 +57770,7 @@
       </c>
       <c r="R529" t="inlineStr"/>
       <c r="S529" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T529" t="inlineStr">
         <is>
@@ -57875,7 +57875,7 @@
       </c>
       <c r="R530" t="inlineStr"/>
       <c r="S530" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T530" t="inlineStr">
         <is>
@@ -57984,7 +57984,7 @@
       </c>
       <c r="R531" t="inlineStr"/>
       <c r="S531" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T531" t="inlineStr">
         <is>
@@ -58093,7 +58093,7 @@
       </c>
       <c r="R532" t="inlineStr"/>
       <c r="S532" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T532" t="inlineStr">
         <is>
@@ -58194,7 +58194,7 @@
       </c>
       <c r="R533" t="inlineStr"/>
       <c r="S533" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T533" t="inlineStr">
         <is>
@@ -58295,7 +58295,7 @@
       </c>
       <c r="R534" t="inlineStr"/>
       <c r="S534" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T534" t="inlineStr">
         <is>
@@ -58396,7 +58396,7 @@
       </c>
       <c r="R535" t="inlineStr"/>
       <c r="S535" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T535" t="inlineStr">
         <is>
@@ -58497,7 +58497,7 @@
       </c>
       <c r="R536" t="inlineStr"/>
       <c r="S536" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="T536" t="inlineStr">
         <is>
@@ -58602,7 +58602,7 @@
       </c>
       <c r="R537" t="inlineStr"/>
       <c r="S537" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T537" t="inlineStr">
         <is>
@@ -58707,7 +58707,7 @@
       </c>
       <c r="R538" t="inlineStr"/>
       <c r="S538" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T538" t="inlineStr">
         <is>
@@ -58812,7 +58812,7 @@
       </c>
       <c r="R539" t="inlineStr"/>
       <c r="S539" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="T539" t="inlineStr">
         <is>
@@ -58917,7 +58917,7 @@
       </c>
       <c r="R540" t="inlineStr"/>
       <c r="S540" t="n">
-        <v>-18</v>
+        <v>-17</v>
       </c>
       <c r="T540" t="inlineStr">
         <is>
@@ -59022,7 +59022,7 @@
       </c>
       <c r="R541" t="inlineStr"/>
       <c r="S541" t="n">
-        <v>-18</v>
+        <v>-17</v>
       </c>
       <c r="T541" t="inlineStr">
         <is>
@@ -59127,7 +59127,7 @@
       </c>
       <c r="R542" t="inlineStr"/>
       <c r="S542" t="n">
-        <v>-18</v>
+        <v>-17</v>
       </c>
       <c r="T542" t="inlineStr">
         <is>
@@ -59232,7 +59232,7 @@
       </c>
       <c r="R543" t="inlineStr"/>
       <c r="S543" t="n">
-        <v>-18</v>
+        <v>-17</v>
       </c>
       <c r="T543" t="inlineStr">
         <is>
@@ -59333,7 +59333,7 @@
       </c>
       <c r="R544" t="inlineStr"/>
       <c r="S544" t="n">
-        <v>-18</v>
+        <v>-17</v>
       </c>
       <c r="T544" t="inlineStr">
         <is>
@@ -59434,7 +59434,7 @@
       </c>
       <c r="R545" t="inlineStr"/>
       <c r="S545" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T545" t="inlineStr">
         <is>
@@ -59535,7 +59535,7 @@
       </c>
       <c r="R546" t="inlineStr"/>
       <c r="S546" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T546" t="inlineStr">
         <is>
@@ -59640,7 +59640,7 @@
       </c>
       <c r="R547" t="inlineStr"/>
       <c r="S547" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T547" t="inlineStr">
         <is>
@@ -59745,7 +59745,7 @@
       </c>
       <c r="R548" t="inlineStr"/>
       <c r="S548" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T548" t="inlineStr">
         <is>
@@ -59850,7 +59850,7 @@
       </c>
       <c r="R549" t="inlineStr"/>
       <c r="S549" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T549" t="inlineStr">
         <is>
@@ -59955,7 +59955,7 @@
       </c>
       <c r="R550" t="inlineStr"/>
       <c r="S550" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T550" t="inlineStr">
         <is>
@@ -60060,7 +60060,7 @@
       </c>
       <c r="R551" t="inlineStr"/>
       <c r="S551" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T551" t="inlineStr">
         <is>
@@ -60161,7 +60161,7 @@
       </c>
       <c r="R552" t="inlineStr"/>
       <c r="S552" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T552" t="inlineStr">
         <is>
@@ -60262,7 +60262,7 @@
       </c>
       <c r="R553" t="inlineStr"/>
       <c r="S553" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T553" t="inlineStr">
         <is>
@@ -60367,7 +60367,7 @@
       </c>
       <c r="R554" t="inlineStr"/>
       <c r="S554" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T554" t="inlineStr">
         <is>
@@ -60468,7 +60468,7 @@
       </c>
       <c r="R555" t="inlineStr"/>
       <c r="S555" t="n">
-        <v>-15</v>
+        <v>-14</v>
       </c>
       <c r="T555" t="inlineStr">
         <is>
@@ -60569,7 +60569,7 @@
       </c>
       <c r="R556" t="inlineStr"/>
       <c r="S556" t="n">
-        <v>-15</v>
+        <v>-14</v>
       </c>
       <c r="T556" t="inlineStr">
         <is>
@@ -60670,7 +60670,7 @@
       </c>
       <c r="R557" t="inlineStr"/>
       <c r="S557" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="T557" t="inlineStr">
         <is>
@@ -60775,7 +60775,7 @@
       </c>
       <c r="R558" t="inlineStr"/>
       <c r="S558" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="T558" t="inlineStr">
         <is>
@@ -60880,7 +60880,7 @@
       </c>
       <c r="R559" t="inlineStr"/>
       <c r="S559" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T559" t="inlineStr">
         <is>
@@ -60981,7 +60981,7 @@
       </c>
       <c r="R560" t="inlineStr"/>
       <c r="S560" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T560" t="inlineStr">
         <is>
@@ -61086,7 +61086,7 @@
       </c>
       <c r="R561" t="inlineStr"/>
       <c r="S561" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="T561" t="inlineStr">
         <is>
@@ -61191,7 +61191,7 @@
       </c>
       <c r="R562" t="inlineStr"/>
       <c r="S562" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T562" t="inlineStr">
         <is>
@@ -61296,7 +61296,7 @@
       </c>
       <c r="R563" t="inlineStr"/>
       <c r="S563" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T563" t="inlineStr">
         <is>
@@ -61401,7 +61401,7 @@
       </c>
       <c r="R564" t="inlineStr"/>
       <c r="S564" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="T564" t="inlineStr">
         <is>
@@ -61506,7 +61506,7 @@
       </c>
       <c r="R565" t="inlineStr"/>
       <c r="S565" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="T565" t="inlineStr">
         <is>
@@ -61611,7 +61611,7 @@
       </c>
       <c r="R566" t="inlineStr"/>
       <c r="S566" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="T566" t="inlineStr">
         <is>
@@ -61712,7 +61712,7 @@
       </c>
       <c r="R567" t="inlineStr"/>
       <c r="S567" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="T567" t="inlineStr">
         <is>
@@ -61817,7 +61817,7 @@
       </c>
       <c r="R568" t="inlineStr"/>
       <c r="S568" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T568" t="inlineStr">
         <is>
@@ -61927,7 +61927,7 @@
       </c>
       <c r="R569" t="inlineStr"/>
       <c r="S569" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T569" t="inlineStr">
         <is>
@@ -62037,7 +62037,7 @@
       </c>
       <c r="R570" t="inlineStr"/>
       <c r="S570" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T570" t="inlineStr">
         <is>
@@ -62147,7 +62147,7 @@
       </c>
       <c r="R571" t="inlineStr"/>
       <c r="S571" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T571" t="inlineStr">
         <is>
@@ -62261,7 +62261,7 @@
       </c>
       <c r="R572" t="inlineStr"/>
       <c r="S572" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T572" t="inlineStr">
         <is>
@@ -62375,7 +62375,7 @@
       </c>
       <c r="R573" t="inlineStr"/>
       <c r="S573" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T573" t="inlineStr">
         <is>
@@ -62485,7 +62485,7 @@
       </c>
       <c r="R574" t="inlineStr"/>
       <c r="S574" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="T574" t="inlineStr">
         <is>
@@ -62590,7 +62590,7 @@
       </c>
       <c r="R575" t="inlineStr"/>
       <c r="S575" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="T575" t="inlineStr">
         <is>
@@ -62695,7 +62695,7 @@
       </c>
       <c r="R576" t="inlineStr"/>
       <c r="S576" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="T576" t="inlineStr">
         <is>
@@ -62796,7 +62796,7 @@
       </c>
       <c r="R577" t="inlineStr"/>
       <c r="S577" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="T577" t="inlineStr">
         <is>
@@ -62897,7 +62897,7 @@
       </c>
       <c r="R578" t="inlineStr"/>
       <c r="S578" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T578" t="inlineStr">
         <is>
@@ -63002,7 +63002,7 @@
       </c>
       <c r="R579" t="inlineStr"/>
       <c r="S579" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T579" t="inlineStr">
         <is>
@@ -63111,7 +63111,7 @@
       </c>
       <c r="R580" t="inlineStr"/>
       <c r="S580" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T580" t="inlineStr">
         <is>
@@ -63221,7 +63221,7 @@
       </c>
       <c r="R581" t="inlineStr"/>
       <c r="S581" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="T581" t="inlineStr">
         <is>
@@ -63326,7 +63326,7 @@
       </c>
       <c r="R582" t="inlineStr"/>
       <c r="S582" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="T582" t="inlineStr">
         <is>
@@ -63427,7 +63427,7 @@
       </c>
       <c r="R583" t="inlineStr"/>
       <c r="S583" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="T583" t="inlineStr">
         <is>
@@ -63528,7 +63528,7 @@
       </c>
       <c r="R584" t="inlineStr"/>
       <c r="S584" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="T584" t="inlineStr">
         <is>
@@ -63633,7 +63633,7 @@
       </c>
       <c r="R585" t="inlineStr"/>
       <c r="S585" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="T585" t="inlineStr">
         <is>
@@ -63738,7 +63738,7 @@
       </c>
       <c r="R586" t="inlineStr"/>
       <c r="S586" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="T586" t="inlineStr">
         <is>
@@ -63843,7 +63843,7 @@
       </c>
       <c r="R587" t="inlineStr"/>
       <c r="S587" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="T587" t="inlineStr">
         <is>
@@ -63952,7 +63952,7 @@
       </c>
       <c r="R588" t="inlineStr"/>
       <c r="S588" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T588" t="inlineStr">
         <is>
@@ -64065,7 +64065,7 @@
       </c>
       <c r="R589" t="inlineStr"/>
       <c r="S589" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T589" t="inlineStr">
         <is>
@@ -64178,7 +64178,7 @@
       </c>
       <c r="R590" t="inlineStr"/>
       <c r="S590" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T590" t="inlineStr">
         <is>
@@ -64291,7 +64291,7 @@
       </c>
       <c r="R591" t="inlineStr"/>
       <c r="S591" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T591" t="inlineStr">
         <is>
@@ -64404,7 +64404,7 @@
       </c>
       <c r="R592" t="inlineStr"/>
       <c r="S592" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T592" t="inlineStr">
         <is>
@@ -64517,7 +64517,7 @@
       </c>
       <c r="R593" t="inlineStr"/>
       <c r="S593" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T593" t="inlineStr">
         <is>
@@ -64626,7 +64626,7 @@
       </c>
       <c r="R594" t="inlineStr"/>
       <c r="S594" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T594" t="inlineStr">
         <is>
@@ -64731,7 +64731,7 @@
       </c>
       <c r="R595" t="inlineStr"/>
       <c r="S595" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T595" t="inlineStr">
         <is>
@@ -64836,7 +64836,7 @@
       </c>
       <c r="R596" t="inlineStr"/>
       <c r="S596" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T596" t="inlineStr">
         <is>
@@ -64941,7 +64941,7 @@
       </c>
       <c r="R597" t="inlineStr"/>
       <c r="S597" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T597" t="inlineStr">
         <is>
@@ -65046,7 +65046,7 @@
       </c>
       <c r="R598" t="inlineStr"/>
       <c r="S598" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T598" t="inlineStr">
         <is>
@@ -65151,7 +65151,7 @@
       </c>
       <c r="R599" t="inlineStr"/>
       <c r="S599" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T599" t="inlineStr">
         <is>
@@ -65256,7 +65256,7 @@
       </c>
       <c r="R600" t="inlineStr"/>
       <c r="S600" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T600" t="inlineStr">
         <is>
@@ -65361,7 +65361,7 @@
       </c>
       <c r="R601" t="inlineStr"/>
       <c r="S601" t="n">
-        <v>-15</v>
+        <v>-14</v>
       </c>
       <c r="T601" t="inlineStr">
         <is>
@@ -65470,7 +65470,7 @@
       </c>
       <c r="R602" t="inlineStr"/>
       <c r="S602" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T602" t="inlineStr">
         <is>
@@ -65583,7 +65583,7 @@
       </c>
       <c r="R603" t="inlineStr"/>
       <c r="S603" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T603" t="inlineStr">
         <is>
@@ -65692,7 +65692,7 @@
       </c>
       <c r="R604" t="inlineStr"/>
       <c r="S604" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T604" t="inlineStr">
         <is>
@@ -65797,7 +65797,7 @@
       </c>
       <c r="R605" t="inlineStr"/>
       <c r="S605" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T605" t="inlineStr">
         <is>
@@ -65902,7 +65902,7 @@
       </c>
       <c r="R606" t="inlineStr"/>
       <c r="S606" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T606" t="inlineStr">
         <is>
@@ -66007,7 +66007,7 @@
       </c>
       <c r="R607" t="inlineStr"/>
       <c r="S607" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T607" t="inlineStr">
         <is>
@@ -66112,7 +66112,7 @@
       </c>
       <c r="R608" t="inlineStr"/>
       <c r="S608" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T608" t="inlineStr">
         <is>
@@ -66217,7 +66217,7 @@
       </c>
       <c r="R609" t="inlineStr"/>
       <c r="S609" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T609" t="inlineStr">
         <is>
@@ -66322,7 +66322,7 @@
       </c>
       <c r="R610" t="inlineStr"/>
       <c r="S610" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="T610" t="inlineStr">
         <is>
@@ -66427,7 +66427,7 @@
       </c>
       <c r="R611" t="inlineStr"/>
       <c r="S611" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="T611" t="inlineStr">
         <is>
@@ -66532,7 +66532,7 @@
       </c>
       <c r="R612" t="inlineStr"/>
       <c r="S612" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="T612" t="inlineStr">
         <is>
@@ -66637,7 +66637,7 @@
       </c>
       <c r="R613" t="inlineStr"/>
       <c r="S613" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="T613" t="inlineStr">
         <is>
@@ -66742,7 +66742,7 @@
       </c>
       <c r="R614" t="inlineStr"/>
       <c r="S614" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="T614" t="inlineStr">
         <is>
@@ -66847,7 +66847,7 @@
       </c>
       <c r="R615" t="inlineStr"/>
       <c r="S615" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="T615" t="inlineStr">
         <is>
@@ -66952,7 +66952,7 @@
       </c>
       <c r="R616" t="inlineStr"/>
       <c r="S616" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="T616" t="inlineStr">
         <is>
@@ -67057,7 +67057,7 @@
       </c>
       <c r="R617" t="inlineStr"/>
       <c r="S617" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="T617" t="inlineStr">
         <is>
@@ -67162,7 +67162,7 @@
       </c>
       <c r="R618" t="inlineStr"/>
       <c r="S618" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T618" t="inlineStr">
         <is>
@@ -67267,7 +67267,7 @@
       </c>
       <c r="R619" t="inlineStr"/>
       <c r="S619" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T619" t="inlineStr">
         <is>
@@ -67372,7 +67372,7 @@
       </c>
       <c r="R620" t="inlineStr"/>
       <c r="S620" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T620" t="inlineStr">
         <is>
@@ -67477,7 +67477,7 @@
       </c>
       <c r="R621" t="inlineStr"/>
       <c r="S621" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T621" t="inlineStr">
         <is>
@@ -67582,7 +67582,7 @@
       </c>
       <c r="R622" t="inlineStr"/>
       <c r="S622" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T622" t="inlineStr">
         <is>
@@ -67693,7 +67693,7 @@
       </c>
       <c r="R623" t="inlineStr"/>
       <c r="S623" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T623" t="inlineStr">
         <is>
@@ -67794,7 +67794,7 @@
       </c>
       <c r="R624" t="inlineStr"/>
       <c r="S624" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="T624" t="inlineStr">
         <is>
@@ -67891,7 +67891,7 @@
       </c>
       <c r="R625" t="inlineStr"/>
       <c r="S625" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T625" t="inlineStr">
         <is>
@@ -67992,7 +67992,7 @@
       </c>
       <c r="R626" t="inlineStr"/>
       <c r="S626" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T626" t="inlineStr">
         <is>
@@ -68093,7 +68093,7 @@
       </c>
       <c r="R627" t="inlineStr"/>
       <c r="S627" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T627" t="inlineStr">
         <is>
@@ -68194,7 +68194,7 @@
       </c>
       <c r="R628" t="inlineStr"/>
       <c r="S628" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T628" t="inlineStr">
         <is>
@@ -68295,7 +68295,7 @@
       </c>
       <c r="R629" t="inlineStr"/>
       <c r="S629" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T629" t="inlineStr">
         <is>
@@ -68396,7 +68396,7 @@
       </c>
       <c r="R630" t="inlineStr"/>
       <c r="S630" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T630" t="inlineStr">
         <is>
@@ -68497,7 +68497,7 @@
       </c>
       <c r="R631" t="inlineStr"/>
       <c r="S631" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T631" t="inlineStr">
         <is>
@@ -68598,7 +68598,7 @@
       </c>
       <c r="R632" t="inlineStr"/>
       <c r="S632" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T632" t="inlineStr">
         <is>
@@ -68699,7 +68699,7 @@
       </c>
       <c r="R633" t="inlineStr"/>
       <c r="S633" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T633" t="inlineStr">
         <is>
@@ -68800,7 +68800,7 @@
       </c>
       <c r="R634" t="inlineStr"/>
       <c r="S634" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T634" t="inlineStr">
         <is>
@@ -68901,7 +68901,7 @@
       </c>
       <c r="R635" t="inlineStr"/>
       <c r="S635" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T635" t="inlineStr">
         <is>
@@ -69002,7 +69002,7 @@
       </c>
       <c r="R636" t="inlineStr"/>
       <c r="S636" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T636" t="inlineStr">
         <is>
@@ -69103,7 +69103,7 @@
       </c>
       <c r="R637" t="inlineStr"/>
       <c r="S637" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T637" t="inlineStr">
         <is>
@@ -69204,7 +69204,7 @@
       </c>
       <c r="R638" t="inlineStr"/>
       <c r="S638" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T638" t="inlineStr">
         <is>
@@ -69301,7 +69301,7 @@
       </c>
       <c r="R639" t="inlineStr"/>
       <c r="S639" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T639" t="inlineStr">
         <is>
@@ -69398,7 +69398,7 @@
       </c>
       <c r="R640" t="inlineStr"/>
       <c r="S640" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T640" t="inlineStr">
         <is>
@@ -69495,7 +69495,7 @@
       </c>
       <c r="R641" t="inlineStr"/>
       <c r="S641" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T641" t="inlineStr">
         <is>
@@ -69592,7 +69592,7 @@
       </c>
       <c r="R642" t="inlineStr"/>
       <c r="S642" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T642" t="inlineStr">
         <is>
@@ -69689,7 +69689,7 @@
       </c>
       <c r="R643" t="inlineStr"/>
       <c r="S643" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T643" t="inlineStr">
         <is>
@@ -69786,7 +69786,7 @@
       </c>
       <c r="R644" t="inlineStr"/>
       <c r="S644" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T644" t="inlineStr">
         <is>
@@ -69887,7 +69887,7 @@
       </c>
       <c r="R645" t="inlineStr"/>
       <c r="S645" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T645" t="inlineStr">
         <is>
@@ -69988,7 +69988,7 @@
       </c>
       <c r="R646" t="inlineStr"/>
       <c r="S646" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T646" t="inlineStr">
         <is>
@@ -70089,7 +70089,7 @@
       </c>
       <c r="R647" t="inlineStr"/>
       <c r="S647" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T647" t="inlineStr">
         <is>
@@ -70190,7 +70190,7 @@
       </c>
       <c r="R648" t="inlineStr"/>
       <c r="S648" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T648" t="inlineStr">
         <is>
@@ -70291,7 +70291,7 @@
       </c>
       <c r="R649" t="inlineStr"/>
       <c r="S649" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T649" t="inlineStr">
         <is>
@@ -70392,7 +70392,7 @@
       </c>
       <c r="R650" t="inlineStr"/>
       <c r="S650" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T650" t="inlineStr">
         <is>
@@ -70493,7 +70493,7 @@
       </c>
       <c r="R651" t="inlineStr"/>
       <c r="S651" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T651" t="inlineStr">
         <is>
@@ -70590,7 +70590,7 @@
       </c>
       <c r="R652" t="inlineStr"/>
       <c r="S652" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T652" t="inlineStr">
         <is>
@@ -70687,7 +70687,7 @@
       </c>
       <c r="R653" t="inlineStr"/>
       <c r="S653" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T653" t="inlineStr">
         <is>
@@ -70784,7 +70784,7 @@
       </c>
       <c r="R654" t="inlineStr"/>
       <c r="S654" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T654" t="inlineStr">
         <is>
@@ -70881,7 +70881,7 @@
       </c>
       <c r="R655" t="inlineStr"/>
       <c r="S655" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T655" t="inlineStr">
         <is>
@@ -70978,7 +70978,7 @@
       </c>
       <c r="R656" t="inlineStr"/>
       <c r="S656" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T656" t="inlineStr">
         <is>
@@ -71075,7 +71075,7 @@
       </c>
       <c r="R657" t="inlineStr"/>
       <c r="S657" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="T657" t="inlineStr">
         <is>
@@ -71176,7 +71176,7 @@
       </c>
       <c r="R658" t="inlineStr"/>
       <c r="S658" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="T658" t="inlineStr">
         <is>
@@ -71277,7 +71277,7 @@
       </c>
       <c r="R659" t="inlineStr"/>
       <c r="S659" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="T659" t="inlineStr">
         <is>
@@ -71378,7 +71378,7 @@
       </c>
       <c r="R660" t="inlineStr"/>
       <c r="S660" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="T660" t="inlineStr">
         <is>
@@ -71479,7 +71479,7 @@
       </c>
       <c r="R661" t="inlineStr"/>
       <c r="S661" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="T661" t="inlineStr">
         <is>
@@ -71580,7 +71580,7 @@
       </c>
       <c r="R662" t="inlineStr"/>
       <c r="S662" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="T662" t="inlineStr">
         <is>
@@ -71681,7 +71681,7 @@
       </c>
       <c r="R663" t="inlineStr"/>
       <c r="S663" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="T663" t="inlineStr">
         <is>
@@ -71782,7 +71782,7 @@
       </c>
       <c r="R664" t="inlineStr"/>
       <c r="S664" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="T664" t="inlineStr">
         <is>
@@ -71883,7 +71883,7 @@
       </c>
       <c r="R665" t="inlineStr"/>
       <c r="S665" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="T665" t="inlineStr">
         <is>
@@ -71984,7 +71984,7 @@
       </c>
       <c r="R666" t="inlineStr"/>
       <c r="S666" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="T666" t="inlineStr">
         <is>
@@ -72081,7 +72081,7 @@
       </c>
       <c r="R667" t="inlineStr"/>
       <c r="S667" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="T667" t="inlineStr">
         <is>
@@ -72178,7 +72178,7 @@
       </c>
       <c r="R668" t="inlineStr"/>
       <c r="S668" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="T668" t="inlineStr">
         <is>
@@ -72275,7 +72275,7 @@
       </c>
       <c r="R669" t="inlineStr"/>
       <c r="S669" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T669" t="inlineStr">
         <is>
@@ -72376,7 +72376,7 @@
       </c>
       <c r="R670" t="inlineStr"/>
       <c r="S670" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T670" t="inlineStr">
         <is>
@@ -72477,7 +72477,7 @@
       </c>
       <c r="R671" t="inlineStr"/>
       <c r="S671" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T671" t="inlineStr">
         <is>
@@ -72578,7 +72578,7 @@
       </c>
       <c r="R672" t="inlineStr"/>
       <c r="S672" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T672" t="inlineStr">
         <is>
@@ -72679,7 +72679,7 @@
       </c>
       <c r="R673" t="inlineStr"/>
       <c r="S673" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T673" t="inlineStr">
         <is>
@@ -72780,7 +72780,7 @@
       </c>
       <c r="R674" t="inlineStr"/>
       <c r="S674" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T674" t="inlineStr">
         <is>
@@ -72881,7 +72881,7 @@
       </c>
       <c r="R675" t="inlineStr"/>
       <c r="S675" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T675" t="inlineStr">
         <is>
@@ -72982,7 +72982,7 @@
       </c>
       <c r="R676" t="inlineStr"/>
       <c r="S676" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T676" t="inlineStr">
         <is>
@@ -73083,7 +73083,7 @@
       </c>
       <c r="R677" t="inlineStr"/>
       <c r="S677" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T677" t="inlineStr">
         <is>
@@ -73184,7 +73184,7 @@
       </c>
       <c r="R678" t="inlineStr"/>
       <c r="S678" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T678" t="inlineStr">
         <is>
@@ -73285,7 +73285,7 @@
       </c>
       <c r="R679" t="inlineStr"/>
       <c r="S679" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T679" t="inlineStr">
         <is>
@@ -73386,7 +73386,7 @@
       </c>
       <c r="R680" t="inlineStr"/>
       <c r="S680" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T680" t="inlineStr">
         <is>
@@ -73487,7 +73487,7 @@
       </c>
       <c r="R681" t="inlineStr"/>
       <c r="S681" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T681" t="inlineStr">
         <is>
@@ -73588,7 +73588,7 @@
       </c>
       <c r="R682" t="inlineStr"/>
       <c r="S682" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T682" t="inlineStr">
         <is>
@@ -73685,7 +73685,7 @@
       </c>
       <c r="R683" t="inlineStr"/>
       <c r="S683" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T683" t="inlineStr">
         <is>
@@ -73782,7 +73782,7 @@
       </c>
       <c r="R684" t="inlineStr"/>
       <c r="S684" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T684" t="inlineStr">
         <is>
@@ -73879,7 +73879,7 @@
       </c>
       <c r="R685" t="inlineStr"/>
       <c r="S685" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T685" t="inlineStr">
         <is>
@@ -73976,7 +73976,7 @@
       </c>
       <c r="R686" t="inlineStr"/>
       <c r="S686" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T686" t="inlineStr">
         <is>
@@ -74073,7 +74073,7 @@
       </c>
       <c r="R687" t="inlineStr"/>
       <c r="S687" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T687" t="inlineStr">
         <is>
@@ -74170,7 +74170,7 @@
       </c>
       <c r="R688" t="inlineStr"/>
       <c r="S688" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T688" t="inlineStr">
         <is>
@@ -74271,7 +74271,7 @@
       </c>
       <c r="R689" t="inlineStr"/>
       <c r="S689" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T689" t="inlineStr">
         <is>
@@ -74372,7 +74372,7 @@
       </c>
       <c r="R690" t="inlineStr"/>
       <c r="S690" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T690" t="inlineStr">
         <is>
@@ -74473,7 +74473,7 @@
       </c>
       <c r="R691" t="inlineStr"/>
       <c r="S691" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T691" t="inlineStr">
         <is>
@@ -74574,7 +74574,7 @@
       </c>
       <c r="R692" t="inlineStr"/>
       <c r="S692" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T692" t="inlineStr">
         <is>
@@ -74675,7 +74675,7 @@
       </c>
       <c r="R693" t="inlineStr"/>
       <c r="S693" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T693" t="inlineStr">
         <is>
@@ -74776,7 +74776,7 @@
       </c>
       <c r="R694" t="inlineStr"/>
       <c r="S694" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T694" t="inlineStr">
         <is>
@@ -74877,7 +74877,7 @@
       </c>
       <c r="R695" t="inlineStr"/>
       <c r="S695" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T695" t="inlineStr">
         <is>
@@ -74974,7 +74974,7 @@
       </c>
       <c r="R696" t="inlineStr"/>
       <c r="S696" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T696" t="inlineStr">
         <is>
@@ -75071,7 +75071,7 @@
       </c>
       <c r="R697" t="inlineStr"/>
       <c r="S697" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T697" t="inlineStr">
         <is>
@@ -75168,7 +75168,7 @@
       </c>
       <c r="R698" t="inlineStr"/>
       <c r="S698" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T698" t="inlineStr">
         <is>
@@ -75265,7 +75265,7 @@
       </c>
       <c r="R699" t="inlineStr"/>
       <c r="S699" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T699" t="inlineStr">
         <is>
@@ -75362,7 +75362,7 @@
       </c>
       <c r="R700" t="inlineStr"/>
       <c r="S700" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T700" t="inlineStr">
         <is>
@@ -75459,7 +75459,7 @@
       </c>
       <c r="R701" t="inlineStr"/>
       <c r="S701" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="T701" t="inlineStr">
         <is>
@@ -75560,7 +75560,7 @@
       </c>
       <c r="R702" t="inlineStr"/>
       <c r="S702" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="T702" t="inlineStr">
         <is>
@@ -75661,7 +75661,7 @@
       </c>
       <c r="R703" t="inlineStr"/>
       <c r="S703" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="T703" t="inlineStr">
         <is>
@@ -75760,7 +75760,7 @@
         <v>46209.66158305555</v>
       </c>
       <c r="S704" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="T704" t="inlineStr">
         <is>
@@ -75863,7 +75863,7 @@
         <v>46203.00285659722</v>
       </c>
       <c r="S705" t="n">
-        <v>-15</v>
+        <v>-14</v>
       </c>
       <c r="T705" t="inlineStr">
         <is>
@@ -75974,7 +75974,7 @@
         <v>46203.00296711805</v>
       </c>
       <c r="S706" t="n">
-        <v>-15</v>
+        <v>-14</v>
       </c>
       <c r="T706" t="inlineStr">
         <is>
@@ -76081,7 +76081,7 @@
         <v>46204.72937350695</v>
       </c>
       <c r="S707" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T707" t="inlineStr">
         <is>
@@ -76192,7 +76192,7 @@
         <v>46206.41464283565</v>
       </c>
       <c r="S708" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T708" t="inlineStr">
         <is>
@@ -76303,7 +76303,7 @@
         <v>46206.70573774305</v>
       </c>
       <c r="S709" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T709" t="inlineStr">
         <is>
@@ -76414,7 +76414,7 @@
         <v>46206.70573846065</v>
       </c>
       <c r="S710" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T710" t="inlineStr">
         <is>
@@ -76525,7 +76525,7 @@
         <v>46211.41697137732</v>
       </c>
       <c r="S711" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T711" t="inlineStr">
         <is>
@@ -76636,7 +76636,7 @@
         <v>46203.3758668287</v>
       </c>
       <c r="S712" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T712" t="inlineStr">
         <is>
@@ -76747,7 +76747,7 @@
         <v>46203.37586737268</v>
       </c>
       <c r="S713" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T713" t="inlineStr">
         <is>
@@ -76858,7 +76858,7 @@
         <v>46203.37586936342</v>
       </c>
       <c r="S714" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T714" t="inlineStr">
         <is>
@@ -76969,7 +76969,7 @@
         <v>46205.45020773148</v>
       </c>
       <c r="S715" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T715" t="inlineStr">
         <is>
@@ -77080,7 +77080,7 @@
         <v>46205.45020809027</v>
       </c>
       <c r="S716" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T716" t="inlineStr">
         <is>
@@ -77191,7 +77191,7 @@
         <v>46205.45020880787</v>
       </c>
       <c r="S717" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T717" t="inlineStr">
         <is>
@@ -77298,7 +77298,7 @@
         <v>46203.37587081019</v>
       </c>
       <c r="S718" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T718" t="inlineStr">
         <is>
@@ -77405,7 +77405,7 @@
         <v>46216.44618675926</v>
       </c>
       <c r="S719" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T719" t="inlineStr">
         <is>
@@ -77512,7 +77512,7 @@
         <v>46206.62907918981</v>
       </c>
       <c r="S720" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T720" t="inlineStr">
         <is>
@@ -77623,7 +77623,7 @@
         <v>46204.00354291667</v>
       </c>
       <c r="S721" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T721" t="inlineStr">
         <is>
@@ -77734,7 +77734,7 @@
         <v>46216.76160721065</v>
       </c>
       <c r="S722" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T722" t="inlineStr">
         <is>
@@ -77841,7 +77841,7 @@
         <v>46206.44786171296</v>
       </c>
       <c r="S723" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T723" t="inlineStr">
         <is>
@@ -77952,7 +77952,7 @@
         <v>46203.71390146991</v>
       </c>
       <c r="S724" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T724" t="inlineStr">
         <is>
@@ -78063,7 +78063,7 @@
         <v>46203.00370568287</v>
       </c>
       <c r="S725" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T725" t="inlineStr">
         <is>
@@ -78174,7 +78174,7 @@
         <v>46216.46069332176</v>
       </c>
       <c r="S726" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="T726" t="inlineStr">
         <is>
@@ -78285,7 +78285,7 @@
         <v>46209.779275</v>
       </c>
       <c r="S727" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T727" t="inlineStr">
         <is>
@@ -78400,7 +78400,7 @@
         <v>46188.33599649306</v>
       </c>
       <c r="S728" t="n">
-        <v>-15</v>
+        <v>-14</v>
       </c>
       <c r="T728" t="inlineStr">
         <is>
@@ -78511,7 +78511,7 @@
         <v>46204.3759534375</v>
       </c>
       <c r="S729" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T729" t="inlineStr">
         <is>
@@ -78622,7 +78622,7 @@
         <v>46206.79235917824</v>
       </c>
       <c r="S730" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T730" t="inlineStr">
         <is>
@@ -78733,7 +78733,7 @@
         <v>46206.79235393518</v>
       </c>
       <c r="S731" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="T731" t="inlineStr">
         <is>
@@ -78844,7 +78844,7 @@
         <v>46210.75621153935</v>
       </c>
       <c r="S732" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="T732" t="inlineStr">
         <is>
@@ -78963,7 +78963,7 @@
         <v>46213.36370773148</v>
       </c>
       <c r="S733" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T733" t="inlineStr">
         <is>
@@ -79078,7 +79078,7 @@
         <v>46204.04179737269</v>
       </c>
       <c r="S734" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T734" t="inlineStr">
         <is>
@@ -79189,7 +79189,7 @@
         <v>46057.40119486111</v>
       </c>
       <c r="S735" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T735" t="inlineStr">
         <is>
@@ -79296,7 +79296,7 @@
         <v>46204.04187399305</v>
       </c>
       <c r="S736" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T736" t="inlineStr">
         <is>
@@ -79403,7 +79403,7 @@
         <v>46204.04188738426</v>
       </c>
       <c r="S737" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T737" t="inlineStr">
         <is>
@@ -79510,7 +79510,7 @@
         <v>46210.80007584491</v>
       </c>
       <c r="S738" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T738" t="inlineStr">
         <is>
@@ -79613,7 +79613,7 @@
         <v>46204.16684155093</v>
       </c>
       <c r="S739" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T739" t="inlineStr">
         <is>
@@ -79724,7 +79724,7 @@
         <v>46023.15052158565</v>
       </c>
       <c r="S740" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T740" t="inlineStr">
         <is>
@@ -79831,7 +79831,7 @@
         <v>46204.12510590278</v>
       </c>
       <c r="S741" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T741" t="inlineStr">
         <is>
@@ -79942,7 +79942,7 @@
         <v>46204.37521674769</v>
       </c>
       <c r="S742" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T742" t="inlineStr">
         <is>
@@ -80053,7 +80053,7 @@
         <v>46057.39078310185</v>
       </c>
       <c r="S743" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T743" t="inlineStr">
         <is>
@@ -80160,7 +80160,7 @@
         <v>46216.49331971065</v>
       </c>
       <c r="S744" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T744" t="inlineStr">
         <is>
@@ -80263,7 +80263,7 @@
         <v>46216.49332078703</v>
       </c>
       <c r="S745" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T745" t="inlineStr">
         <is>
@@ -80366,7 +80366,7 @@
         <v>46204.29183217593</v>
       </c>
       <c r="S746" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="T746" t="inlineStr">
         <is>
@@ -80477,7 +80477,7 @@
         <v>46204.33341168981</v>
       </c>
       <c r="S747" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="T747" t="inlineStr">
         <is>
@@ -80588,7 +80588,7 @@
         <v>46204.25011258102</v>
       </c>
       <c r="S748" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="T748" t="inlineStr">
         <is>
@@ -80699,7 +80699,7 @@
         <v>46204.37522271991</v>
       </c>
       <c r="S749" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="T749" t="inlineStr">
         <is>
@@ -80810,7 +80810,7 @@
         <v>46204.25009074074</v>
       </c>
       <c r="S750" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="T750" t="inlineStr">
         <is>
@@ -80921,7 +80921,7 @@
         <v>46204.37521859954</v>
       </c>
       <c r="S751" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="T751" t="inlineStr">
         <is>
@@ -81032,7 +81032,7 @@
         <v>46204.41730355324</v>
       </c>
       <c r="S752" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="T752" t="inlineStr">
         <is>
@@ -81143,7 +81143,7 @@
         <v>46023.15053034722</v>
       </c>
       <c r="S753" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="T753" t="inlineStr">
         <is>
@@ -81250,7 +81250,7 @@
         <v>46204.41680613426</v>
       </c>
       <c r="S754" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="T754" t="inlineStr">
         <is>
@@ -81361,7 +81361,7 @@
         <v>46204.41687068287</v>
       </c>
       <c r="S755" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="T755" t="inlineStr">
         <is>
@@ -81472,7 +81472,7 @@
         <v>46204.41788634259</v>
       </c>
       <c r="S756" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="T756" t="inlineStr">
         <is>
@@ -81583,7 +81583,7 @@
         <v>46057.3907997338</v>
       </c>
       <c r="S757" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="T757" t="inlineStr">
         <is>
@@ -81686,7 +81686,7 @@
         <v>46192.56685792824</v>
       </c>
       <c r="S758" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="T758" t="inlineStr">
         <is>
@@ -81785,7 +81785,7 @@
         <v>46192.56339828703</v>
       </c>
       <c r="S759" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="T759" t="inlineStr">
         <is>
@@ -81888,7 +81888,7 @@
         <v>46204.41730447917</v>
       </c>
       <c r="S760" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T760" t="inlineStr">
         <is>
@@ -81999,7 +81999,7 @@
         <v>46204.41751620371</v>
       </c>
       <c r="S761" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T761" t="inlineStr">
         <is>
@@ -82110,7 +82110,7 @@
         <v>46204.41687126157</v>
       </c>
       <c r="S762" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T762" t="inlineStr">
         <is>
@@ -82221,7 +82221,7 @@
         <v>46204.41788753472</v>
       </c>
       <c r="S763" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T763" t="inlineStr">
         <is>
@@ -82332,7 +82332,7 @@
         <v>46204.41788796296</v>
       </c>
       <c r="S764" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T764" t="inlineStr">
         <is>
@@ -82439,7 +82439,7 @@
         <v>46168.72822039352</v>
       </c>
       <c r="S765" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T765" t="inlineStr">
         <is>
@@ -82538,7 +82538,7 @@
         <v>46192.56687770833</v>
       </c>
       <c r="S766" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T766" t="inlineStr">
         <is>
@@ -82637,7 +82637,7 @@
         <v>46192.56342578704</v>
       </c>
       <c r="S767" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="T767" t="inlineStr">
         <is>
@@ -82740,7 +82740,7 @@
         <v>46213.75219915509</v>
       </c>
       <c r="S768" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T768" t="inlineStr">
         <is>
@@ -82847,7 +82847,7 @@
         <v>46213.75220699074</v>
       </c>
       <c r="S769" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T769" t="inlineStr">
         <is>
@@ -82954,7 +82954,7 @@
         <v>46213.75224594907</v>
       </c>
       <c r="S770" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T770" t="inlineStr">
         <is>
@@ -83061,7 +83061,7 @@
         <v>46213.75225217592</v>
       </c>
       <c r="S771" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T771" t="inlineStr">
         <is>
@@ -83168,7 +83168,7 @@
         <v>46213.75219873842</v>
       </c>
       <c r="S772" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T772" t="inlineStr">
         <is>
@@ -83275,7 +83275,7 @@
         <v>46213.75220643519</v>
       </c>
       <c r="S773" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T773" t="inlineStr">
         <is>
@@ -83382,7 +83382,7 @@
         <v>46213.75224560185</v>
       </c>
       <c r="S774" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T774" t="inlineStr">
         <is>
@@ -83489,7 +83489,7 @@
         <v>46213.75225246528</v>
       </c>
       <c r="S775" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="T775" t="inlineStr">
         <is>
@@ -83596,7 +83596,7 @@
         <v>46174.04914510417</v>
       </c>
       <c r="S776" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T776" t="inlineStr">
         <is>
@@ -83707,7 +83707,7 @@
         <v>46174.04916258102</v>
       </c>
       <c r="S777" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T777" t="inlineStr">
         <is>
@@ -83818,7 +83818,7 @@
         <v>46174.04899652778</v>
       </c>
       <c r="S778" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T778" t="inlineStr">
         <is>
@@ -83929,7 +83929,7 @@
         <v>46174.04886894676</v>
       </c>
       <c r="S779" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T779" t="inlineStr">
         <is>
@@ -84040,7 +84040,7 @@
         <v>46174.04901342592</v>
       </c>
       <c r="S780" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T780" t="inlineStr">
         <is>
@@ -84151,7 +84151,7 @@
         <v>46174.04899452546</v>
       </c>
       <c r="S781" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T781" t="inlineStr">
         <is>
@@ -84262,7 +84262,7 @@
         <v>46174.04894753472</v>
       </c>
       <c r="S782" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T782" t="inlineStr">
         <is>
@@ -84373,7 +84373,7 @@
         <v>46174.0003128125</v>
       </c>
       <c r="S783" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="T783" t="inlineStr">
         <is>
@@ -84480,7 +84480,7 @@
         <v>46174.0003128125</v>
       </c>
       <c r="S784" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="T784" t="inlineStr">
         <is>
@@ -84583,7 +84583,7 @@
         <v>46174.0003128125</v>
       </c>
       <c r="S785" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="T785" t="inlineStr">
         <is>
@@ -84690,7 +84690,7 @@
         <v>46174.0003128125</v>
       </c>
       <c r="S786" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="T786" t="inlineStr">
         <is>
@@ -84797,7 +84797,7 @@
         <v>46174.0003128125</v>
       </c>
       <c r="S787" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="T787" t="inlineStr">
         <is>
@@ -84904,7 +84904,7 @@
         <v>46211.76825706018</v>
       </c>
       <c r="S788" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="T788" t="inlineStr">
         <is>
@@ -85015,7 +85015,7 @@
         <v>46209.77926392361</v>
       </c>
       <c r="S789" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="T789" t="inlineStr">
         <is>
@@ -85126,7 +85126,7 @@
       </c>
       <c r="R790" t="inlineStr"/>
       <c r="S790" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T790" t="inlineStr">
         <is>
@@ -85234,7 +85234,7 @@
       </c>
       <c r="R791" t="inlineStr"/>
       <c r="S791" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T791" t="inlineStr">
         <is>
@@ -85342,7 +85342,7 @@
       </c>
       <c r="R792" t="inlineStr"/>
       <c r="S792" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T792" t="inlineStr">
         <is>
@@ -85454,7 +85454,7 @@
       </c>
       <c r="R793" t="inlineStr"/>
       <c r="S793" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="T793" t="inlineStr">
         <is>
@@ -85569,7 +85569,7 @@
       </c>
       <c r="R794" t="inlineStr"/>
       <c r="S794" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="T794" t="inlineStr">
         <is>
@@ -85684,7 +85684,7 @@
       </c>
       <c r="R795" t="inlineStr"/>
       <c r="S795" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T795" t="inlineStr">
         <is>
@@ -85803,7 +85803,7 @@
       </c>
       <c r="R796" t="inlineStr"/>
       <c r="S796" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="T796" t="inlineStr">
         <is>

--- a/dados/base/goias.xlsx
+++ b/dados/base/goias.xlsx
@@ -657,7 +657,7 @@
       </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -793,11 +793,11 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6949</v>
+        <v>6486</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TEC GRUA LOCAÇÃO E COMERCIO DE EQUIPAMENTOS PARA CONSTRUÇÃO LTDA</t>
+          <t>PC GAMER GOIANIA LTDA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -817,14 +817,14 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>11616</v>
+        <v>5800</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>5776</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -833,29 +833,29 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Envio de ATA de Implantação - DP</t>
+          <t>CCT Lançamento Sd.663</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" s="1" t="n">
-        <v>46209</v>
+        <v>46216</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>06/2026</t>
+          <t>00/2026</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>18166584</v>
+        <v>17901201</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mauricio Lermen</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -865,18 +865,22 @@
       </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>TEC GRUA</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr"/>
+          <t>PC GAMER</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 20/07/2026 
-Inicio em 07/2026 implantação pendente agendada para 13/07 - Data Comentário: 06/07/2026 17:19</t>
+          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 14/07/2026 
+Foi enviada para a empresa planilha de reajuste e informações sobre termo aditivo do sindicato. Estamos aguardando retorno para aplicação e calculo das complementares. - Data Comentário: 13/07/2026 09:43</t>
         </is>
       </c>
       <c r="W4" t="inlineStr"/>
@@ -895,15 +899,19 @@
           <t>Tarefa</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>David Bragança</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>5617</v>
+        <v>6949</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>TEC GRUA LOCAÇÃO E COMERCIO DE EQUIPAMENTOS PARA CONSTRUÇÃO LTDA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -923,11 +931,11 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Reynaldo Santos</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>9746</v>
+        <v>11616</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -939,25 +947,29 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>eSocial – Fechamento Mensal</t>
+          <t>Envio de ATA de Implantação - DP</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" s="1" t="n">
-        <v>46213</v>
-      </c>
-      <c r="M5" t="inlineStr"/>
+        <v>46209</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>17407922</v>
+        <v>18166584</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tania Luz</t>
+          <t>Mauricio Lermen</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -967,21 +979,18 @@
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>TEC GRUA</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
         <is>
-          <t>8. Serviços Suspensos. - Data Comentário: 08/07/2026 10:25</t>
+          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 20/07/2026 
+Inicio em 07/2026 implantação pendente agendada para 13/07 - Data Comentário: 06/07/2026 17:19</t>
         </is>
       </c>
       <c r="W5" t="inlineStr"/>
@@ -1000,19 +1009,15 @@
           <t>Tarefa</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>Edivaldo Veiga</t>
-        </is>
-      </c>
+      <c r="AG5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>6224</v>
+        <v>5617</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1032,7 +1037,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1062,7 +1067,7 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>17689040</v>
+        <v>17407922</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -1076,7 +1081,7 @@
       </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1117,11 +1122,11 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>5617</v>
+        <v>6224</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1141,14 +1146,14 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>5905</v>
+        <v>9746</v>
       </c>
       <c r="H7" t="n">
-        <v>5784</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1157,12 +1162,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Folha Mensal/Pró-Labore</t>
+          <t>eSocial – Fechamento Mensal</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" s="1" t="n">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
@@ -1171,7 +1176,7 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>17407675</v>
+        <v>17689040</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1185,7 +1190,7 @@
       </c>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1215,7 +1220,7 @@
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>Obrigação Acessória</t>
+          <t>Tarefa</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -1226,11 +1231,11 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>6224</v>
+        <v>5617</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1250,7 +1255,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1280,7 +1285,7 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>17688813</v>
+        <v>17407675</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -1294,7 +1299,7 @@
       </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1335,11 +1340,11 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>5617</v>
+        <v>6224</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1359,11 +1364,11 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>5853</v>
+        <v>5905</v>
       </c>
       <c r="H9" t="n">
         <v>5784</v>
@@ -1375,12 +1380,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>FOPAG Impressão PDF</t>
+          <t>Folha Mensal/Pró-Labore</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" s="1" t="n">
-        <v>46210</v>
+        <v>46206</v>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
@@ -1389,7 +1394,7 @@
         </is>
       </c>
       <c r="O9" t="n">
-        <v>17407635</v>
+        <v>17688813</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
@@ -1403,7 +1408,7 @@
       </c>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1417,7 +1422,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>8. Serviços Suspensos. - Data Comentário: 03/07/2026 08:40</t>
+          <t>8. Serviços Suspensos. - Data Comentário: 08/07/2026 10:25</t>
         </is>
       </c>
       <c r="W9" t="inlineStr"/>
@@ -1433,7 +1438,7 @@
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>Tarefa</t>
+          <t>Obrigação Acessória</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -1444,11 +1449,11 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>6224</v>
+        <v>5617</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1468,7 +1473,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1498,7 +1503,7 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>17688753</v>
+        <v>17407635</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -1512,7 +1517,7 @@
       </c>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1526,7 +1531,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>8. Serviços Suspensos. - Data Comentário: 03/07/2026 08:39</t>
+          <t>8. Serviços Suspensos. - Data Comentário: 03/07/2026 08:40</t>
         </is>
       </c>
       <c r="W10" t="inlineStr"/>
@@ -1553,11 +1558,11 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>5617</v>
+        <v>6224</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1577,11 +1582,11 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>5906</v>
+        <v>5853</v>
       </c>
       <c r="H11" t="n">
         <v>5784</v>
@@ -1593,12 +1598,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Recibo de Pagamento</t>
+          <t>FOPAG Impressão PDF</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
@@ -1607,7 +1612,7 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>17407685</v>
+        <v>17688753</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
@@ -1635,7 +1640,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>8. Serviços Suspensos. - Data Comentário: 03/07/2026 08:40</t>
+          <t>8. Serviços Suspensos. - Data Comentário: 03/07/2026 08:39</t>
         </is>
       </c>
       <c r="W11" t="inlineStr"/>
@@ -1662,11 +1667,11 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>6224</v>
+        <v>5617</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1686,7 +1691,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1716,7 +1721,7 @@
         </is>
       </c>
       <c r="O12" t="n">
-        <v>17688823</v>
+        <v>17407685</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
@@ -1730,7 +1735,7 @@
       </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1744,7 +1749,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>8. Serviços Suspensos. - Data Comentário: 03/07/2026 08:39</t>
+          <t>8. Serviços Suspensos. - Data Comentário: 03/07/2026 08:40</t>
         </is>
       </c>
       <c r="W12" t="inlineStr"/>
@@ -1771,11 +1776,11 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>5617</v>
+        <v>6224</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1795,11 +1800,11 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>5907</v>
+        <v>5906</v>
       </c>
       <c r="H13" t="n">
         <v>5784</v>
@@ -1811,7 +1816,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Relação Bancária - Salário</t>
+          <t>Recibo de Pagamento</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1825,7 +1830,7 @@
         </is>
       </c>
       <c r="O13" t="n">
-        <v>17407695</v>
+        <v>17688823</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
@@ -1839,7 +1844,7 @@
       </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1853,7 +1858,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>8. Serviços Suspensos. - Data Comentário: 03/07/2026 08:40</t>
+          <t>8. Serviços Suspensos. - Data Comentário: 03/07/2026 08:39</t>
         </is>
       </c>
       <c r="W13" t="inlineStr"/>
@@ -1880,11 +1885,11 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>6224</v>
+        <v>5617</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1904,7 +1909,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1934,7 +1939,7 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>17688833</v>
+        <v>17407695</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
@@ -1948,7 +1953,7 @@
       </c>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1962,7 +1967,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>8. Serviços Suspensos. - Data Comentário: 03/07/2026 08:39</t>
+          <t>8. Serviços Suspensos. - Data Comentário: 03/07/2026 08:40</t>
         </is>
       </c>
       <c r="W14" t="inlineStr"/>
@@ -2017,24 +2022,24 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1802</v>
+        <v>5907</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>5784</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Est - ICMS RPA - CÓD. 046-2</t>
+          <t>Relação Bancária - Salário</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" s="1" t="n">
-        <v>46212</v>
+        <v>46209</v>
       </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
@@ -2043,11 +2048,11 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>17688681</v>
+        <v>17688833</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Cristina Leite</t>
+          <t>Tania Luz</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -2057,7 +2062,7 @@
       </c>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2071,7 +2076,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>Atraso do Cliente, cobrança ativa, GC e GM ciente do atraso - Data Comentário: 06/07/2026 15:17</t>
+          <t>8. Serviços Suspensos. - Data Comentário: 03/07/2026 08:39</t>
         </is>
       </c>
       <c r="W15" t="inlineStr"/>
@@ -2087,22 +2092,22 @@
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Tarefa</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>6224</v>
+        <v>6548</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>GOIAS SILAGEM LTDA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2122,41 +2127,45 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>11665</v>
+        <v>6805</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>GIAM (TO)</t>
+          <t>Fed - EFD - REINF - Entrega e PDF</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" s="1" t="n">
-        <v>46212</v>
-      </c>
-      <c r="M16" t="inlineStr"/>
+        <v>46216</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>18076580</v>
+        <v>17222740</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Cristina Leite</t>
+          <t>Cristiana Grizostomo</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -2166,11 +2175,11 @@
       </c>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>GOIAS SILAGEM</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2180,7 +2189,8 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Atraso do Cliente, cobrança ativa, GC e GM ciente do atraso - Data Comentário: 06/07/2026 15:55</t>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 13/07/2026 
+Tarefas em andamento de efetivação nesta data. - Data Comentário: 13/07/2026 10:09</t>
         </is>
       </c>
       <c r="W16" t="inlineStr"/>
@@ -2196,22 +2206,22 @@
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>Tarefa</t>
+          <t>Obrigação Acessória</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>6486</v>
+        <v>6224</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PC GAMER GOIANIA LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2231,59 +2241,55 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>5800</v>
+        <v>1802</v>
       </c>
       <c r="H17" t="n">
-        <v>5776</v>
+        <v>0</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>CCT Lançamento Sd.663</t>
+          <t>Est - ICMS RPA - CÓD. 046-2</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" s="1" t="n">
-        <v>46216</v>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>14/07/2026</t>
-        </is>
-      </c>
+        <v>46212</v>
+      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>00/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>17901201</v>
+        <v>17688681</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Cristina Leite</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Em Aberto</t>
+          <t>Em Atraso</t>
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>PC GAMER</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2293,8 +2299,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 14/07/2026 
-Foi enviada para a empresa planilha de reajuste e informações sobre termo aditivo do sindicato. Estamos aguardando retorno para aplicação e calculo das complementares. - Data Comentário: 13/07/2026 09:43</t>
+          <t>Atraso do Cliente, cobrança ativa, GC e GM ciente do atraso - Data Comentário: 06/07/2026 15:17</t>
         </is>
       </c>
       <c r="W17" t="inlineStr"/>
@@ -2310,22 +2315,22 @@
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>Tarefa</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>5417</v>
+        <v>6885</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2335,7 +2340,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2345,28 +2350,28 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>5867</v>
+        <v>6806</v>
       </c>
       <c r="H18" t="n">
-        <v>5786</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>GFD - FGTS Digital Mensal</t>
+          <t>Fed - EFD - REINF - Entrega e PDF</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" s="1" t="n">
-        <v>46218</v>
+        <v>46216</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -2379,36 +2384,31 @@
         </is>
       </c>
       <c r="O18" t="n">
-        <v>17399054</v>
+        <v>18134124</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Mikael Teixeira</t>
+          <t>Cristina Leite</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Em Aberto</t>
+          <t>Em Atraso</t>
         </is>
       </c>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>EMPORIO DOS FRIOS</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 14/07/2026 
-Em processo de emissão - Data Comentário: 13/07/2026 11:58</t>
+          <t>Atraso da Operação, processo em elaboração conforme data prevista  Previsão para conclusão dia 14/07/2026 - Data Comentário: 13/07/2026 18:10</t>
         </is>
       </c>
       <c r="W18" t="inlineStr"/>
@@ -2424,18 +2424,22 @@
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>Imposto</t>
-        </is>
-      </c>
-      <c r="AG18" t="inlineStr"/>
+          <t>Obrigação Acessória</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>Ricardo Fischer</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>5617</v>
+        <v>6224</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2455,28 +2459,28 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>5867</v>
+        <v>11665</v>
       </c>
       <c r="H19" t="n">
-        <v>5786</v>
+        <v>0</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>GFD - FGTS Digital Mensal</t>
+          <t>GIAM (TO)</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" s="1" t="n">
-        <v>46218</v>
+        <v>46212</v>
       </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
@@ -2485,21 +2489,21 @@
         </is>
       </c>
       <c r="O19" t="n">
-        <v>17407645</v>
+        <v>18076580</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Tania Luz</t>
+          <t>Cristina Leite</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Em Aberto</t>
+          <t>Em Atraso</t>
         </is>
       </c>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>-2</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2511,7 +2515,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr"/>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Atraso do Cliente, cobrança ativa, GC e GM ciente do atraso - Data Comentário: 06/07/2026 15:55</t>
+        </is>
+      </c>
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr"/>
       <c r="Y19" t="inlineStr"/>
@@ -2525,22 +2533,22 @@
       <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Tarefa</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>6224</v>
+        <v>5417</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2560,7 +2568,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2583,18 +2591,22 @@
       <c r="L20" s="1" t="n">
         <v>46218</v>
       </c>
-      <c r="M20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O20" t="n">
-        <v>17688773</v>
+        <v>17399054</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Tania Luz</t>
+          <t>Mikael Teixeira</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -2604,11 +2616,11 @@
       </c>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>NOSSO NOVO SUPERMERCADO</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2616,7 +2628,12 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr"/>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 14/07/2026 
+Em processo de emissão - Data Comentário: 13/07/2026 11:58</t>
+        </is>
+      </c>
       <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr"/>
       <c r="Y20" t="inlineStr"/>
@@ -2633,19 +2650,15 @@
           <t>Imposto</t>
         </is>
       </c>
-      <c r="AG20" t="inlineStr">
-        <is>
-          <t>Edivaldo Veiga</t>
-        </is>
-      </c>
+      <c r="AG20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>6486</v>
+        <v>5617</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PC GAMER GOIANIA LTDA</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2688,22 +2701,18 @@
       <c r="L21" s="1" t="n">
         <v>46218</v>
       </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>14/07/2026</t>
-        </is>
-      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O21" t="n">
-        <v>16976054</v>
+        <v>17407645</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Tania Luz</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -2713,11 +2722,11 @@
       </c>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>PC GAMER</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2725,12 +2734,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 14/07/2026 
-PREVISÃO DE CONCLUSÃO: 14/07/2026 - Data Comentário: 13/07/2026 09:52</t>
-        </is>
-      </c>
+      <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr"/>
@@ -2749,17 +2753,17 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>6548</v>
+        <v>6224</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2779,7 +2783,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -2802,22 +2806,18 @@
       <c r="L22" s="1" t="n">
         <v>46218</v>
       </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>15/07/2026</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O22" t="n">
-        <v>17222615</v>
+        <v>17688773</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Daniel Moraes</t>
+          <t>Tania Luz</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -2827,11 +2827,11 @@
       </c>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2839,12 +2839,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 15/07/2026 
-Previsão pra finalizar em 15/07/2026 - Data Comentário: 13/07/2026 09:06</t>
-        </is>
-      </c>
+      <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr"/>
@@ -2863,17 +2858,17 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>6627</v>
+        <v>6486</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
+          <t>PC GAMER GOIANIA LTDA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2888,7 +2883,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2927,7 +2922,7 @@
         </is>
       </c>
       <c r="O23" t="n">
-        <v>18068530</v>
+        <v>16976054</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
@@ -2941,11 +2936,11 @@
       </c>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
+          <t>PC GAMER</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2955,8 +2950,8 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 14/07/2026 
-Previsão de conclusão 14/07 - Data Comentário: 13/07/2026 10:02</t>
+          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 14/07/2026 
+PREVISÃO DE CONCLUSÃO: 14/07/2026 - Data Comentário: 13/07/2026 09:52</t>
         </is>
       </c>
       <c r="W23" t="inlineStr"/>
@@ -2983,11 +2978,11 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>6628</v>
+        <v>6548</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>GOIAS SILAGEM LTDA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2997,12 +2992,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -3032,7 +3027,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3041,11 +3036,11 @@
         </is>
       </c>
       <c r="O24" t="n">
-        <v>18052449</v>
+        <v>17222615</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Daniel Moraes</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -3055,11 +3050,11 @@
       </c>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
+          <t>GOIAS SILAGEM</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3069,8 +3064,8 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 14/07/2026 
-Previsão de conclusão 14/07 - Data Comentário: 13/07/2026 10:02</t>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 15/07/2026 
+Previsão pra finalizar em 15/07/2026 - Data Comentário: 13/07/2026 09:06</t>
         </is>
       </c>
       <c r="W24" t="inlineStr"/>
@@ -3097,11 +3092,11 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>6779</v>
+        <v>6627</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CORDEIRO E CIA LTDA</t>
+          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3111,12 +3106,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3155,11 +3150,11 @@
         </is>
       </c>
       <c r="O25" t="n">
-        <v>18090176</v>
+        <v>18068530</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kaique Souza</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -3169,18 +3164,22 @@
       </c>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr"/>
+          <t xml:space="preserve">GTG </t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 14/07/2026 
-ESocial fechado, antecipação de envio. - Data Comentário: 10/07/2026 09:19</t>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 14/07/2026 
+Previsão de conclusão 14/07 - Data Comentário: 13/07/2026 10:02</t>
         </is>
       </c>
       <c r="W25" t="inlineStr"/>
@@ -3201,17 +3200,17 @@
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>David Bragança</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>6885</v>
+        <v>6628</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3226,7 +3225,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3265,11 +3264,11 @@
         </is>
       </c>
       <c r="O26" t="n">
-        <v>18157267</v>
+        <v>18052449</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Vitor Guedes</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -3279,18 +3278,22 @@
       </c>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr"/>
+          <t xml:space="preserve">GTG </t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V26" t="inlineStr">
         <is>
           <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 14/07/2026 
-Previsão de conclusão: 14/07/2026 - Data Comentário: 13/07/2026 09:31</t>
+Previsão de conclusão 14/07 - Data Comentário: 13/07/2026 10:02</t>
         </is>
       </c>
       <c r="W26" t="inlineStr"/>
@@ -3317,11 +3320,11 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>6628</v>
+        <v>6779</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>CORDEIRO E CIA LTDA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3336,7 +3339,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3345,37 +3348,41 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1875</v>
+        <v>5867</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>5786</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Est - Sintegra Interestadual</t>
+          <t>GFD - FGTS Digital Mensal</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" s="1" t="n">
         <v>46218</v>
       </c>
-      <c r="M27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O27" t="n">
-        <v>17988660</v>
+        <v>18090176</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Fernando Bastos</t>
+          <t>Kaique Souza</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -3385,19 +3392,20 @@
       </c>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr"/>
+          <t>TECNO COM</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 14/07/2026 
+ESocial fechado, antecipação de envio. - Data Comentário: 10/07/2026 09:19</t>
+        </is>
+      </c>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="inlineStr"/>
       <c r="Y27" t="inlineStr"/>
@@ -3411,22 +3419,22 @@
       <c r="AE27" t="inlineStr"/>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>Obrigação Acessória</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>6548</v>
+        <v>6885</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM LTDA</t>
+          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3436,7 +3444,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3450,28 +3458,28 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>6805</v>
+        <v>5867</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>5786</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Fed - EFD - REINF - Entrega e PDF</t>
+          <t>GFD - FGTS Digital Mensal</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" s="1" t="n">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3480,11 +3488,11 @@
         </is>
       </c>
       <c r="O28" t="n">
-        <v>17222740</v>
+        <v>18157267</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Cristiana Grizostomo</t>
+          <t>Vitor Guedes</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -3494,22 +3502,18 @@
       </c>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>EMPORIO DOS FRIOS</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 13/07/2026 
-Tarefas em andamento de efetivação nesta data. - Data Comentário: 13/07/2026 10:09</t>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 14/07/2026 
+Previsão de conclusão: 14/07/2026 - Data Comentário: 13/07/2026 09:31</t>
         </is>
       </c>
       <c r="W28" t="inlineStr"/>
@@ -3525,22 +3529,22 @@
       <c r="AE28" t="inlineStr"/>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>Obrigação Acessória</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>David Bragança</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3550,7 +3554,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3564,7 +3568,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>10674</v>
+        <v>1875</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -3576,29 +3580,25 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Relatório de Entrada para Classificação</t>
+          <t>Est - Sintegra Interestadual</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" s="1" t="n">
         <v>46218</v>
       </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>14/07/2026</t>
-        </is>
-      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O29" t="n">
-        <v>17968443</v>
+        <v>17988660</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Denis Reis</t>
+          <t>Fernando Bastos</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3620,11 +3620,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 14/07/2026 - Data Comentário: 13/07/2026 19:28</t>
-        </is>
-      </c>
+      <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr"/>
       <c r="X29" t="inlineStr"/>
       <c r="Y29" t="inlineStr"/>
@@ -3638,7 +3634,7 @@
       <c r="AE29" t="inlineStr"/>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>Tarefa</t>
+          <t>Obrigação Acessória</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">
@@ -3649,11 +3645,11 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>6962</v>
+        <v>6627</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
+          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3668,12 +3664,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3696,14 +3692,18 @@
       <c r="L30" s="1" t="n">
         <v>46218</v>
       </c>
-      <c r="M30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O30" t="n">
-        <v>18187014</v>
+        <v>17968443</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
@@ -3717,15 +3717,23 @@
       </c>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
+          <t xml:space="preserve">GTG </t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 14/07/2026 - Data Comentário: 13/07/2026 19:28</t>
+        </is>
+      </c>
       <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr"/>
       <c r="Y30" t="inlineStr"/>
@@ -3750,11 +3758,11 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>6963</v>
+        <v>6962</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN LTDA</t>
+          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3804,7 +3812,7 @@
         </is>
       </c>
       <c r="O31" t="n">
-        <v>18187280</v>
+        <v>18187014</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
@@ -3818,7 +3826,7 @@
       </c>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3851,11 +3859,11 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>6705</v>
+        <v>6963</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>NARCIZO ALVES CORDEIRO</t>
+          <t>PROMOTORAS GYN LTDA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3865,7 +3873,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3875,45 +3883,41 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Reynaldo Santos</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>6298</v>
+        <v>10674</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Est - Sintegra Interestadual</t>
+          <t>Relatório de Entrada para Classificação</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" s="1" t="n">
         <v>46218</v>
       </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>15/07/2026</t>
-        </is>
-      </c>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O32" t="n">
-        <v>17949007</v>
+        <v>18187280</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Cristina Leite</t>
+          <t>Denis Reis</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -3923,23 +3927,15 @@
       </c>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 15/07/2026 - Data Comentário: 13/07/2026 12:06</t>
-        </is>
-      </c>
+          <t>PROMOTORAS GYN</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr"/>
       <c r="Y32" t="inlineStr"/>
@@ -3953,22 +3949,22 @@
       <c r="AE32" t="inlineStr"/>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>Obrigação Acessória</t>
+          <t>Tarefa</t>
         </is>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>6885</v>
+        <v>6705</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
+          <t>NARCIZO ALVES CORDEIRO</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3992,7 +3988,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>6806</v>
+        <v>6298</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -4004,16 +4000,16 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Fed - EFD - REINF - Entrega e PDF</t>
+          <t>Est - Sintegra Interestadual</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" s="1" t="n">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -4022,7 +4018,7 @@
         </is>
       </c>
       <c r="O33" t="n">
-        <v>18134124</v>
+        <v>17949007</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
@@ -4036,17 +4032,21 @@
       </c>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr"/>
+          <t>TECNO COM</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>Atraso da Operação, processo em elaboração conforme data prevista  Previsão para conclusão dia 14/07/2026 - Data Comentário: 13/07/2026 18:10</t>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 15/07/2026 - Data Comentário: 13/07/2026 12:06</t>
         </is>
       </c>
       <c r="W33" t="inlineStr"/>
@@ -4141,7 +4141,7 @@
       </c>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
       </c>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
         <v>46206.43215109954</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>46206.43205978009</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4564,7 +4564,7 @@
         <v>46206.43206049768</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4671,7 +4671,7 @@
         <v>46204.75352534722</v>
       </c>
       <c r="S39" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>46204.75352809028</v>
       </c>
       <c r="S40" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4893,7 +4893,7 @@
         <v>46204.7535284375</v>
       </c>
       <c r="S41" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
         <v>46204.7535334838</v>
       </c>
       <c r="S42" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5111,7 +5111,7 @@
         <v>46204.75353387732</v>
       </c>
       <c r="S43" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5218,7 +5218,7 @@
         <v>46204.75353515046</v>
       </c>
       <c r="S44" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>46204.75350494213</v>
       </c>
       <c r="S45" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5436,7 +5436,7 @@
         <v>46204.75351072917</v>
       </c>
       <c r="S46" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5547,7 +5547,7 @@
         <v>46204.75352068287</v>
       </c>
       <c r="S47" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5658,7 +5658,7 @@
         <v>46204.75352175926</v>
       </c>
       <c r="S48" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5769,7 +5769,7 @@
         <v>46204.75353024306</v>
       </c>
       <c r="S49" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5880,7 +5880,7 @@
         <v>46204.7535309838</v>
       </c>
       <c r="S50" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
         <v>46204.75353240741</v>
       </c>
       <c r="S51" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         <v>46204.75353278935</v>
       </c>
       <c r="S52" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6201,7 +6201,7 @@
         <v>46205.599529375</v>
       </c>
       <c r="S53" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
         <v>46204.71542079861</v>
       </c>
       <c r="S54" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6411,7 +6411,7 @@
         <v>46204.71542134259</v>
       </c>
       <c r="S55" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6514,7 +6514,7 @@
         <v>46204.48446469908</v>
       </c>
       <c r="S56" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6625,7 +6625,7 @@
         <v>46205.75412240741</v>
       </c>
       <c r="S57" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>46205.75458568287</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6847,7 +6847,7 @@
         <v>46206.44903752315</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
         <v>46199.48727971065</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7057,7 +7057,7 @@
         <v>46205.69236453703</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7168,7 +7168,7 @@
         <v>46209.43008613426</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7280,7 +7280,7 @@
         <v>46204.5600265625</v>
       </c>
       <c r="S63" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
         <v>46196.71390480324</v>
       </c>
       <c r="S64" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7502,7 +7502,7 @@
         <v>46198.70825575232</v>
       </c>
       <c r="S65" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7613,7 +7613,7 @@
         <v>46196.59280127315</v>
       </c>
       <c r="S66" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>46204.41370118056</v>
       </c>
       <c r="S67" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
         <v>46213.6834903125</v>
       </c>
       <c r="S68" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7947,7 +7947,7 @@
         <v>46209.71247704861</v>
       </c>
       <c r="S69" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8066,7 +8066,7 @@
         <v>46209.71499087963</v>
       </c>
       <c r="S70" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8186,7 +8186,7 @@
         <v>46211.48251296296</v>
       </c>
       <c r="S71" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8306,7 +8306,7 @@
         <v>46210.47222041667</v>
       </c>
       <c r="S72" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
         <v>46211.58264625</v>
       </c>
       <c r="S73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8546,7 +8546,7 @@
         <v>46210.48132625</v>
       </c>
       <c r="S74" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
         <v>46210.45896016204</v>
       </c>
       <c r="S75" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
         <v>46210.72289299768</v>
       </c>
       <c r="S76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8898,7 +8898,7 @@
         <v>46216.74133621528</v>
       </c>
       <c r="S77" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
         <v>46211.59005767361</v>
       </c>
       <c r="S78" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9126,7 +9126,7 @@
         <v>46206.54816894676</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
         <v>46206.55861924768</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
         <v>46206.67165491898</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9479,7 +9479,7 @@
         <v>46206.67202474537</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9598,7 +9598,7 @@
         <v>46206.62892094907</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9717,7 +9717,7 @@
         <v>46206.64427289352</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9832,7 +9832,7 @@
         <v>46205.6924828125</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9947,7 +9947,7 @@
         <v>46206.69765491898</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10058,7 +10058,7 @@
         <v>46206.65603582176</v>
       </c>
       <c r="S87" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10165,7 +10165,7 @@
         <v>46209.41001810185</v>
       </c>
       <c r="S88" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10276,7 +10276,7 @@
         <v>46209.41001846065</v>
       </c>
       <c r="S89" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10387,7 +10387,7 @@
         <v>46209.41001900463</v>
       </c>
       <c r="S90" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10498,7 +10498,7 @@
         <v>46206.62881552083</v>
       </c>
       <c r="S91" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
         <v>46206.64398119213</v>
       </c>
       <c r="S92" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10724,7 +10724,7 @@
         <v>46209.55182975694</v>
       </c>
       <c r="S93" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10831,7 +10831,7 @@
         <v>46211.39936383102</v>
       </c>
       <c r="S94" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10938,7 +10938,7 @@
         <v>46216.76160633102</v>
       </c>
       <c r="S95" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11053,7 +11053,7 @@
         <v>46216.76160648148</v>
       </c>
       <c r="S96" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11164,7 +11164,7 @@
         <v>46204.50154423611</v>
       </c>
       <c r="S97" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11275,7 +11275,7 @@
         <v>46196.69558237268</v>
       </c>
       <c r="S98" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11386,7 +11386,7 @@
         <v>46198.71108606482</v>
       </c>
       <c r="S99" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11497,7 +11497,7 @@
         <v>46196.59315405093</v>
       </c>
       <c r="S100" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11604,7 +11604,7 @@
         <v>46204.42181446759</v>
       </c>
       <c r="S101" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11707,7 +11707,7 @@
         <v>46204.48462402778</v>
       </c>
       <c r="S102" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11814,7 +11814,7 @@
         <v>46195.57837077546</v>
       </c>
       <c r="S103" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11921,7 +11921,7 @@
         <v>46188.39084737268</v>
       </c>
       <c r="S104" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12032,7 +12032,7 @@
         <v>46188.39085099537</v>
       </c>
       <c r="S105" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>46189.61008070602</v>
       </c>
       <c r="S106" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12246,7 +12246,7 @@
         <v>46185.66827939815</v>
       </c>
       <c r="S107" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12357,7 +12357,7 @@
         <v>46190.56460636574</v>
       </c>
       <c r="S108" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12468,7 +12468,7 @@
         <v>46185.66566952546</v>
       </c>
       <c r="S109" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12579,7 +12579,7 @@
         <v>46185.66535266204</v>
       </c>
       <c r="S110" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12690,7 +12690,7 @@
         <v>46185.69383032407</v>
       </c>
       <c r="S111" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12797,7 +12797,7 @@
         <v>46195.70875512731</v>
       </c>
       <c r="S112" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12904,7 +12904,7 @@
         <v>46195.70011658565</v>
       </c>
       <c r="S113" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
         <v>46205.59156991898</v>
       </c>
       <c r="S114" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -13135,7 +13135,7 @@
         <v>46205.73670511574</v>
       </c>
       <c r="S115" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13255,7 +13255,7 @@
         <v>46205.7367062037</v>
       </c>
       <c r="S116" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13375,7 +13375,7 @@
         <v>46206.43991525463</v>
       </c>
       <c r="S117" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13491,7 +13491,7 @@
         <v>46205.34573362269</v>
       </c>
       <c r="S118" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13602,7 +13602,7 @@
         <v>46206.65428631944</v>
       </c>
       <c r="S119" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13709,7 +13709,7 @@
         <v>46199.67793730324</v>
       </c>
       <c r="S120" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13820,7 +13820,7 @@
         <v>46206.55866898148</v>
       </c>
       <c r="S121" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13931,7 +13931,7 @@
         <v>46206.6716975926</v>
       </c>
       <c r="S122" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -14042,7 +14042,7 @@
         <v>46206.67205873843</v>
       </c>
       <c r="S123" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -14153,7 +14153,7 @@
         <v>46206.62895168982</v>
       </c>
       <c r="S124" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -14268,7 +14268,7 @@
         <v>46206.6443237037</v>
       </c>
       <c r="S125" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -14379,7 +14379,7 @@
         <v>46205.69251481481</v>
       </c>
       <c r="S126" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -14486,7 +14486,7 @@
         <v>46206.69781152777</v>
       </c>
       <c r="S127" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -14593,7 +14593,7 @@
         <v>46206.65440622685</v>
       </c>
       <c r="S128" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -14704,7 +14704,7 @@
         <v>46206.40915328704</v>
       </c>
       <c r="S129" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14819,7 +14819,7 @@
         <v>46206.55870388889</v>
       </c>
       <c r="S130" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -14930,7 +14930,7 @@
         <v>46206.67172778935</v>
       </c>
       <c r="S131" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15041,7 +15041,7 @@
         <v>46206.67209291667</v>
       </c>
       <c r="S132" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -15152,7 +15152,7 @@
         <v>46206.62899021991</v>
       </c>
       <c r="S133" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -15267,7 +15267,7 @@
         <v>46206.64435354167</v>
       </c>
       <c r="S134" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -15378,7 +15378,7 @@
         <v>46205.69254519676</v>
       </c>
       <c r="S135" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -15485,7 +15485,7 @@
         <v>46206.69786020833</v>
       </c>
       <c r="S136" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         <v>46206.65479178241</v>
       </c>
       <c r="S137" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -15699,7 +15699,7 @@
         <v>46210.4994990162</v>
       </c>
       <c r="S138" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -15811,7 +15811,7 @@
         <v>46211.45479957176</v>
       </c>
       <c r="S139" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -15915,7 +15915,7 @@
         <v>46216.61943571759</v>
       </c>
       <c r="S140" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -16018,7 +16018,7 @@
         <v>46211.59924370371</v>
       </c>
       <c r="S141" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -16129,7 +16129,7 @@
         <v>46203.71388695601</v>
       </c>
       <c r="S142" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -16240,7 +16240,7 @@
         <v>46206.79368510417</v>
       </c>
       <c r="S143" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -16347,7 +16347,7 @@
         <v>46206.79368695602</v>
       </c>
       <c r="S144" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -16454,7 +16454,7 @@
         <v>46203.71358417824</v>
       </c>
       <c r="S145" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -16565,7 +16565,7 @@
         <v>46205.46012403935</v>
       </c>
       <c r="S146" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -16676,7 +16676,7 @@
         <v>46206.79339394676</v>
       </c>
       <c r="S147" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -16783,7 +16783,7 @@
         <v>46206.79339563657</v>
       </c>
       <c r="S148" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -16890,7 +16890,7 @@
         <v>46203.71368457176</v>
       </c>
       <c r="S149" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -17001,7 +17001,7 @@
         <v>46205.4602116551</v>
       </c>
       <c r="S150" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -17112,7 +17112,7 @@
         <v>46206.79348040509</v>
       </c>
       <c r="S151" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -17219,7 +17219,7 @@
         <v>46206.79348244213</v>
       </c>
       <c r="S152" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -17326,7 +17326,7 @@
         <v>46203.71312577547</v>
       </c>
       <c r="S153" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -17437,7 +17437,7 @@
         <v>46206.79261038194</v>
       </c>
       <c r="S154" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -17544,7 +17544,7 @@
         <v>46206.79261369213</v>
       </c>
       <c r="S155" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -17651,7 +17651,7 @@
         <v>46206.79369521991</v>
       </c>
       <c r="S156" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -17758,7 +17758,7 @@
         <v>46206.79369363426</v>
       </c>
       <c r="S157" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -17865,7 +17865,7 @@
         <v>46203.71373487268</v>
       </c>
       <c r="S158" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -17976,7 +17976,7 @@
         <v>46205.46026211805</v>
       </c>
       <c r="S159" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -18087,7 +18087,7 @@
         <v>46206.79353869213</v>
       </c>
       <c r="S160" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -18194,7 +18194,7 @@
         <v>46206.79354065972</v>
       </c>
       <c r="S161" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -18301,7 +18301,7 @@
         <v>46209.46657106481</v>
       </c>
       <c r="S162" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -18408,7 +18408,7 @@
         <v>46209.46657106481</v>
       </c>
       <c r="S163" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -18515,7 +18515,7 @@
         <v>46206.79251087963</v>
       </c>
       <c r="S164" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -18622,7 +18622,7 @@
         <v>46206.79251215278</v>
       </c>
       <c r="S165" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -18729,7 +18729,7 @@
         <v>46206.79252202546</v>
       </c>
       <c r="S166" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -18836,7 +18836,7 @@
         <v>46206.79252349537</v>
       </c>
       <c r="S167" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -18943,7 +18943,7 @@
         <v>46203.71378568287</v>
       </c>
       <c r="S168" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -19054,7 +19054,7 @@
         <v>46205.46031030093</v>
       </c>
       <c r="S169" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -19165,7 +19165,7 @@
         <v>46206.79359788194</v>
       </c>
       <c r="S170" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -19272,7 +19272,7 @@
         <v>46206.7935997338</v>
       </c>
       <c r="S171" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -19379,7 +19379,7 @@
         <v>46203.71384140047</v>
       </c>
       <c r="S172" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -19490,7 +19490,7 @@
         <v>46205.4603590625</v>
       </c>
       <c r="S173" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -19601,7 +19601,7 @@
         <v>46206.79364525463</v>
       </c>
       <c r="S174" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>
@@ -19708,7 +19708,7 @@
         <v>46206.79364730324</v>
       </c>
       <c r="S175" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T175" t="inlineStr">
         <is>
@@ -19819,7 +19819,7 @@
         <v>46216.5789241088</v>
       </c>
       <c r="S176" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -19939,7 +19939,7 @@
         <v>46216.78167138889</v>
       </c>
       <c r="S177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -20059,7 +20059,7 @@
         <v>46216.77738425926</v>
       </c>
       <c r="S178" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -20175,7 +20175,7 @@
         <v>46216.76226002315</v>
       </c>
       <c r="S179" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -20291,7 +20291,7 @@
         <v>46209.45242072917</v>
       </c>
       <c r="S180" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -20410,7 +20410,7 @@
         <v>46211.76742385417</v>
       </c>
       <c r="S181" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T181" t="inlineStr">
         <is>
@@ -20525,7 +20525,7 @@
         <v>46211.76720232639</v>
       </c>
       <c r="S182" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -20640,7 +20640,7 @@
         <v>46210.63989674769</v>
       </c>
       <c r="S183" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -20760,7 +20760,7 @@
         <v>46209.49997177083</v>
       </c>
       <c r="S184" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -20879,7 +20879,7 @@
         <v>46211.76683576389</v>
       </c>
       <c r="S185" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -20994,7 +20994,7 @@
         <v>46211.76723488426</v>
       </c>
       <c r="S186" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -21105,7 +21105,7 @@
         <v>46211.79243741898</v>
       </c>
       <c r="S187" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -21212,7 +21212,7 @@
         <v>46211.79243900463</v>
       </c>
       <c r="S188" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -21319,7 +21319,7 @@
         <v>46204.37644915509</v>
       </c>
       <c r="S189" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -21430,7 +21430,7 @@
         <v>46204.37595123843</v>
       </c>
       <c r="S190" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -21541,7 +21541,7 @@
         <v>46204.37595258102</v>
       </c>
       <c r="S191" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -21652,7 +21652,7 @@
         <v>46206.79235609954</v>
       </c>
       <c r="S192" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -21763,7 +21763,7 @@
         <v>46205.45902149306</v>
       </c>
       <c r="S193" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         <v>46206.79235100694</v>
       </c>
       <c r="S194" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -21985,7 +21985,7 @@
         <v>46204.37667199074</v>
       </c>
       <c r="S195" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -22096,7 +22096,7 @@
         <v>46204.37677195602</v>
       </c>
       <c r="S196" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T196" t="inlineStr">
         <is>
@@ -22207,7 +22207,7 @@
         <v>46204.37677268519</v>
       </c>
       <c r="S197" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T197" t="inlineStr">
         <is>
@@ -22318,7 +22318,7 @@
         <v>46204.37681211805</v>
       </c>
       <c r="S198" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -22429,7 +22429,7 @@
         <v>46206.7926803588</v>
       </c>
       <c r="S199" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T199" t="inlineStr">
         <is>
@@ -22540,7 +22540,7 @@
         <v>46204.37581924768</v>
       </c>
       <c r="S200" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T200" t="inlineStr">
         <is>
@@ -22651,7 +22651,7 @@
         <v>46204.37582079861</v>
       </c>
       <c r="S201" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -22762,7 +22762,7 @@
         <v>46206.79232175926</v>
       </c>
       <c r="S202" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T202" t="inlineStr">
         <is>
@@ -22873,7 +22873,7 @@
         <v>46205.45901322916</v>
       </c>
       <c r="S203" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T203" t="inlineStr">
         <is>
@@ -22984,7 +22984,7 @@
         <v>46206.79231805556</v>
       </c>
       <c r="S204" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T204" t="inlineStr">
         <is>
@@ -23095,7 +23095,7 @@
         <v>46204.37531446759</v>
       </c>
       <c r="S205" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T205" t="inlineStr">
         <is>
@@ -23206,7 +23206,7 @@
         <v>46204.37541623843</v>
       </c>
       <c r="S206" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T206" t="inlineStr">
         <is>
@@ -23317,7 +23317,7 @@
         <v>46204.37531940972</v>
       </c>
       <c r="S207" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T207" t="inlineStr">
         <is>
@@ -23428,7 +23428,7 @@
         <v>46206.79216188657</v>
       </c>
       <c r="S208" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T208" t="inlineStr">
         <is>
@@ -23539,7 +23539,7 @@
         <v>46206.79215482639</v>
       </c>
       <c r="S209" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T209" t="inlineStr">
         <is>
@@ -23650,7 +23650,7 @@
         <v>46204.375303125</v>
       </c>
       <c r="S210" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T210" t="inlineStr">
         <is>
@@ -23761,7 +23761,7 @@
         <v>46205.45874525463</v>
       </c>
       <c r="S211" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T211" t="inlineStr">
         <is>
@@ -23872,7 +23872,7 @@
         <v>46204.37542565972</v>
       </c>
       <c r="S212" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T212" t="inlineStr">
         <is>
@@ -23983,7 +23983,7 @@
         <v>46206.79216226852</v>
       </c>
       <c r="S213" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T213" t="inlineStr">
         <is>
@@ -24094,7 +24094,7 @@
         <v>46204.45863723379</v>
       </c>
       <c r="S214" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T214" t="inlineStr">
         <is>
@@ -24205,7 +24205,7 @@
         <v>46206.79216269676</v>
       </c>
       <c r="S215" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T215" t="inlineStr">
         <is>
@@ -24312,7 +24312,7 @@
         <v>46205.4461572338</v>
       </c>
       <c r="S216" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="T216" t="inlineStr">
         <is>
@@ -24427,7 +24427,7 @@
         <v>46211.34394196759</v>
       </c>
       <c r="S217" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T217" t="inlineStr">
         <is>
@@ -24538,7 +24538,7 @@
         <v>46209.34400659722</v>
       </c>
       <c r="S218" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T218" t="inlineStr">
         <is>
@@ -24649,7 +24649,7 @@
         <v>46209.34400416667</v>
       </c>
       <c r="S219" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T219" t="inlineStr">
         <is>
@@ -24760,7 +24760,7 @@
         <v>46209.37540871528</v>
       </c>
       <c r="S220" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T220" t="inlineStr">
         <is>
@@ -24871,7 +24871,7 @@
         <v>46206.76069471065</v>
       </c>
       <c r="S221" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T221" t="inlineStr">
         <is>
@@ -24982,7 +24982,7 @@
         <v>46206.76073368055</v>
       </c>
       <c r="S222" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T222" t="inlineStr">
         <is>
@@ -25093,7 +25093,7 @@
         <v>46209.37538854167</v>
       </c>
       <c r="S223" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T223" t="inlineStr">
         <is>
@@ -25204,7 +25204,7 @@
         <v>46205.42742766203</v>
       </c>
       <c r="S224" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T224" t="inlineStr">
         <is>
@@ -25315,7 +25315,7 @@
         <v>46209.3754105324</v>
       </c>
       <c r="S225" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T225" t="inlineStr">
         <is>
@@ -25426,7 +25426,7 @@
         <v>46206.76073530092</v>
       </c>
       <c r="S226" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T226" t="inlineStr">
         <is>
@@ -25537,7 +25537,7 @@
         <v>46209.37540651621</v>
       </c>
       <c r="S227" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T227" t="inlineStr">
         <is>
@@ -25648,7 +25648,7 @@
         <v>46206.76073472222</v>
       </c>
       <c r="S228" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T228" t="inlineStr">
         <is>
@@ -25755,7 +25755,7 @@
         <v>46206.47265292824</v>
       </c>
       <c r="S229" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T229" t="inlineStr">
         <is>
@@ -25863,7 +25863,7 @@
         <v>46216.4607102662</v>
       </c>
       <c r="S230" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="T230" t="inlineStr">
         <is>
@@ -25978,7 +25978,7 @@
         <v>46216.54223067129</v>
       </c>
       <c r="S231" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T231" t="inlineStr">
         <is>
@@ -26097,7 +26097,7 @@
         <v>46216.70691956019</v>
       </c>
       <c r="S232" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T232" t="inlineStr">
         <is>
@@ -26216,7 +26216,7 @@
         <v>46216.74139769676</v>
       </c>
       <c r="S233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T233" t="inlineStr">
         <is>
@@ -26335,7 +26335,7 @@
         <v>46216.70692208334</v>
       </c>
       <c r="S234" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T234" t="inlineStr">
         <is>
@@ -26454,7 +26454,7 @@
         <v>46216.7069231713</v>
       </c>
       <c r="S235" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T235" t="inlineStr">
         <is>
@@ -26573,7 +26573,7 @@
         <v>46216.74139806713</v>
       </c>
       <c r="S236" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T236" t="inlineStr">
         <is>
@@ -26692,7 +26692,7 @@
         <v>46216.70692371528</v>
       </c>
       <c r="S237" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T237" t="inlineStr">
         <is>
@@ -26811,7 +26811,7 @@
         <v>46216.54223627315</v>
       </c>
       <c r="S238" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T238" t="inlineStr">
         <is>
@@ -26930,7 +26930,7 @@
         <v>46216.75000510416</v>
       </c>
       <c r="S239" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T239" t="inlineStr">
         <is>
@@ -27049,7 +27049,7 @@
         <v>46216.75000582176</v>
       </c>
       <c r="S240" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T240" t="inlineStr">
         <is>
@@ -27168,7 +27168,7 @@
         <v>46216.75000619213</v>
       </c>
       <c r="S241" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T241" t="inlineStr">
         <is>
@@ -27279,7 +27279,7 @@
         <v>46213.43891172454</v>
       </c>
       <c r="S242" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="T242" t="inlineStr">
         <is>
@@ -27398,7 +27398,7 @@
         <v>46209.74627188657</v>
       </c>
       <c r="S243" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T243" t="inlineStr">
         <is>
@@ -27513,7 +27513,7 @@
         <v>46206.50269079861</v>
       </c>
       <c r="S244" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T244" t="inlineStr">
         <is>
@@ -27628,7 +27628,7 @@
         <v>46209.7462744213</v>
       </c>
       <c r="S245" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T245" t="inlineStr">
         <is>
@@ -27743,7 +27743,7 @@
         <v>46209.62289283565</v>
       </c>
       <c r="S246" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T246" t="inlineStr">
         <is>
@@ -27858,7 +27858,7 @@
         <v>46210.7847958912</v>
       </c>
       <c r="S247" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T247" t="inlineStr">
         <is>
@@ -27977,7 +27977,7 @@
         <v>46210.80248869213</v>
       </c>
       <c r="S248" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T248" t="inlineStr">
         <is>
@@ -28096,7 +28096,7 @@
         <v>46210.78479861111</v>
       </c>
       <c r="S249" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T249" t="inlineStr">
         <is>
@@ -28215,7 +28215,7 @@
         <v>46210.78479896991</v>
       </c>
       <c r="S250" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T250" t="inlineStr">
         <is>
@@ -28330,7 +28330,7 @@
         <v>46206.50244357639</v>
       </c>
       <c r="S251" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T251" t="inlineStr">
         <is>
@@ -28445,7 +28445,7 @@
         <v>46210.80248940973</v>
       </c>
       <c r="S252" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T252" t="inlineStr">
         <is>
@@ -28560,7 +28560,7 @@
         <v>46206.50244393518</v>
       </c>
       <c r="S253" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T253" t="inlineStr">
         <is>
@@ -28675,7 +28675,7 @@
         <v>46210.80249175926</v>
       </c>
       <c r="S254" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T254" t="inlineStr">
         <is>
@@ -28794,7 +28794,7 @@
         <v>46213.41471872685</v>
       </c>
       <c r="S255" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T255" t="inlineStr">
         <is>
@@ -28913,7 +28913,7 @@
         <v>46213.41472034722</v>
       </c>
       <c r="S256" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T256" t="inlineStr">
         <is>
@@ -29028,7 +29028,7 @@
         <v>46213.41472866898</v>
       </c>
       <c r="S257" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T257" t="inlineStr">
         <is>
@@ -29143,7 +29143,7 @@
         <v>46211.67827373843</v>
       </c>
       <c r="S258" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T258" t="inlineStr">
         <is>
@@ -29258,7 +29258,7 @@
         <v>46205.45901570602</v>
       </c>
       <c r="S259" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T259" t="inlineStr">
         <is>
@@ -29369,7 +29369,7 @@
         <v>46206.79257369213</v>
       </c>
       <c r="S260" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T260" t="inlineStr">
         <is>
@@ -29480,7 +29480,7 @@
         <v>46205.45918969908</v>
       </c>
       <c r="S261" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T261" t="inlineStr">
         <is>
@@ -29595,7 +29595,7 @@
         <v>46211.37590150463</v>
       </c>
       <c r="S262" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T262" t="inlineStr">
         <is>
@@ -29710,7 +29710,7 @@
         <v>46206.79256712963</v>
       </c>
       <c r="S263" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T263" t="inlineStr">
         <is>
@@ -29817,7 +29817,7 @@
         <v>46206.7921721875</v>
       </c>
       <c r="S264" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T264" t="inlineStr">
         <is>
@@ -29928,7 +29928,7 @@
         <v>46213.79217554398</v>
       </c>
       <c r="S265" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T265" t="inlineStr">
         <is>
@@ -30039,7 +30039,7 @@
         <v>46206.7921681713</v>
       </c>
       <c r="S266" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T266" t="inlineStr">
         <is>
@@ -30146,7 +30146,7 @@
         <v>46210.37424872685</v>
       </c>
       <c r="S267" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="T267" t="inlineStr">
         <is>
@@ -30261,7 +30261,7 @@
         <v>46205.76232731481</v>
       </c>
       <c r="S268" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="T268" t="inlineStr">
         <is>
@@ -30372,7 +30372,7 @@
         <v>46205.7623278588</v>
       </c>
       <c r="S269" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="T269" t="inlineStr">
         <is>
@@ -30483,7 +30483,7 @@
         <v>46205.76232913195</v>
       </c>
       <c r="S270" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="T270" t="inlineStr">
         <is>
@@ -30594,7 +30594,7 @@
         <v>46211.39581168981</v>
       </c>
       <c r="S271" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="T271" t="inlineStr">
         <is>
@@ -30705,7 +30705,7 @@
         <v>46210.67626055556</v>
       </c>
       <c r="S272" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T272" t="inlineStr">
         <is>
@@ -30816,7 +30816,7 @@
         <v>46210.60626501157</v>
       </c>
       <c r="S273" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T273" t="inlineStr">
         <is>
@@ -30927,7 +30927,7 @@
         <v>46213.64570789352</v>
       </c>
       <c r="S274" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T274" t="inlineStr">
         <is>
@@ -31034,7 +31034,7 @@
         <v>46213.6457087963</v>
       </c>
       <c r="S275" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T275" t="inlineStr">
         <is>
@@ -31141,7 +31141,7 @@
         <v>46210.76622931713</v>
       </c>
       <c r="S276" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T276" t="inlineStr">
         <is>
@@ -31252,7 +31252,7 @@
         <v>46210.6898024537</v>
       </c>
       <c r="S277" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T277" t="inlineStr">
         <is>
@@ -31359,7 +31359,7 @@
         <v>46210.76516364583</v>
       </c>
       <c r="S278" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T278" t="inlineStr">
         <is>
@@ -31470,7 +31470,7 @@
         <v>46213.34372746528</v>
       </c>
       <c r="S279" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T279" t="inlineStr">
         <is>
@@ -31581,7 +31581,7 @@
         <v>46213.63923525463</v>
       </c>
       <c r="S280" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T280" t="inlineStr">
         <is>
@@ -31692,7 +31692,7 @@
         <v>46213.63947451389</v>
       </c>
       <c r="S281" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T281" t="inlineStr">
         <is>
@@ -31799,7 +31799,7 @@
         <v>46213.64188018518</v>
       </c>
       <c r="S282" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T282" t="inlineStr">
         <is>
@@ -31906,7 +31906,7 @@
         <v>46210.68980878472</v>
       </c>
       <c r="S283" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T283" t="inlineStr">
         <is>
@@ -32009,7 +32009,7 @@
         <v>46213.64228201389</v>
       </c>
       <c r="S284" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T284" t="inlineStr">
         <is>
@@ -32116,7 +32116,7 @@
         <v>46213.35361152777</v>
       </c>
       <c r="S285" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T285" t="inlineStr">
         <is>
@@ -32223,7 +32223,7 @@
         <v>46206.65276246528</v>
       </c>
       <c r="S286" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T286" t="inlineStr">
         <is>
@@ -32330,7 +32330,7 @@
         <v>46206.65277079861</v>
       </c>
       <c r="S287" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T287" t="inlineStr">
         <is>
@@ -32437,7 +32437,7 @@
         <v>46206.65274155093</v>
       </c>
       <c r="S288" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T288" t="inlineStr">
         <is>
@@ -32544,7 +32544,7 @@
         <v>46206.65274189815</v>
       </c>
       <c r="S289" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T289" t="inlineStr">
         <is>
@@ -32651,7 +32651,7 @@
         <v>46206.65274228009</v>
       </c>
       <c r="S290" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T290" t="inlineStr">
         <is>
@@ -32758,7 +32758,7 @@
         <v>46206.65275096065</v>
       </c>
       <c r="S291" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T291" t="inlineStr">
         <is>
@@ -32865,7 +32865,7 @@
         <v>46206.65275582176</v>
       </c>
       <c r="S292" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T292" t="inlineStr">
         <is>
@@ -32972,7 +32972,7 @@
         <v>46206.65276396991</v>
       </c>
       <c r="S293" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T293" t="inlineStr">
         <is>
@@ -33079,7 +33079,7 @@
         <v>46206.65277951389</v>
       </c>
       <c r="S294" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T294" t="inlineStr">
         <is>
@@ -33186,7 +33186,7 @@
         <v>46206.65278059028</v>
       </c>
       <c r="S295" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T295" t="inlineStr">
         <is>
@@ -33293,7 +33293,7 @@
         <v>46206.65278711806</v>
       </c>
       <c r="S296" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T296" t="inlineStr">
         <is>
@@ -33400,7 +33400,7 @@
         <v>46206.65278746527</v>
       </c>
       <c r="S297" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T297" t="inlineStr">
         <is>
@@ -33507,7 +33507,7 @@
         <v>46206.65278857639</v>
       </c>
       <c r="S298" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T298" t="inlineStr">
         <is>
@@ -33614,7 +33614,7 @@
         <v>46206.65279270833</v>
       </c>
       <c r="S299" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T299" t="inlineStr">
         <is>
@@ -33717,7 +33717,7 @@
         <v>46206.65279922454</v>
       </c>
       <c r="S300" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T300" t="inlineStr">
         <is>
@@ -33820,7 +33820,7 @@
         <v>46206.65280755787</v>
       </c>
       <c r="S301" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T301" t="inlineStr">
         <is>
@@ -33923,7 +33923,7 @@
         <v>46206.65280844907</v>
       </c>
       <c r="S302" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T302" t="inlineStr">
         <is>
@@ -34026,7 +34026,7 @@
         <v>46206.65280972223</v>
       </c>
       <c r="S303" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T303" t="inlineStr">
         <is>
@@ -34129,7 +34129,7 @@
         <v>46206.65281026621</v>
       </c>
       <c r="S304" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T304" t="inlineStr">
         <is>
@@ -34232,7 +34232,7 @@
         <v>46203.79329967593</v>
       </c>
       <c r="S305" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T305" t="inlineStr">
         <is>
@@ -34339,7 +34339,7 @@
         <v>46203.79332754629</v>
       </c>
       <c r="S306" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T306" t="inlineStr">
         <is>
@@ -34446,7 +34446,7 @@
         <v>46203.79350829861</v>
       </c>
       <c r="S307" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T307" t="inlineStr">
         <is>
@@ -34553,7 +34553,7 @@
         <v>46203.79357234954</v>
       </c>
       <c r="S308" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T308" t="inlineStr">
         <is>
@@ -34660,7 +34660,7 @@
         <v>46203.7936177662</v>
       </c>
       <c r="S309" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T309" t="inlineStr">
         <is>
@@ -34767,7 +34767,7 @@
         <v>46203.79366831019</v>
       </c>
       <c r="S310" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T310" t="inlineStr">
         <is>
@@ -34874,7 +34874,7 @@
         <v>46203.79371640046</v>
       </c>
       <c r="S311" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T311" t="inlineStr">
         <is>
@@ -34981,7 +34981,7 @@
         <v>46203.79372402778</v>
       </c>
       <c r="S312" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T312" t="inlineStr">
         <is>
@@ -35088,7 +35088,7 @@
         <v>46203.79376344907</v>
       </c>
       <c r="S313" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T313" t="inlineStr">
         <is>
@@ -35195,7 +35195,7 @@
         <v>46203.79376959491</v>
       </c>
       <c r="S314" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T314" t="inlineStr">
         <is>
@@ -35302,7 +35302,7 @@
         <v>46203.79377528935</v>
       </c>
       <c r="S315" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T315" t="inlineStr">
         <is>
@@ -35409,7 +35409,7 @@
         <v>46204.5021846875</v>
       </c>
       <c r="S316" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T316" t="inlineStr">
         <is>
@@ -35512,7 +35512,7 @@
         <v>46203.79384251157</v>
       </c>
       <c r="S317" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T317" t="inlineStr">
         <is>
@@ -35615,7 +35615,7 @@
         <v>46204.50231476852</v>
       </c>
       <c r="S318" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T318" t="inlineStr">
         <is>
@@ -35718,7 +35718,7 @@
         <v>46204.77955170139</v>
       </c>
       <c r="S319" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T319" t="inlineStr">
         <is>
@@ -35821,7 +35821,7 @@
         <v>46204.77955260417</v>
       </c>
       <c r="S320" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T320" t="inlineStr">
         <is>
@@ -35924,7 +35924,7 @@
         <v>46204.77955333333</v>
       </c>
       <c r="S321" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T321" t="inlineStr">
         <is>
@@ -36027,7 +36027,7 @@
         <v>46196.70294318287</v>
       </c>
       <c r="S322" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T322" t="inlineStr">
         <is>
@@ -36134,7 +36134,7 @@
         <v>46196.70294915509</v>
       </c>
       <c r="S323" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T323" t="inlineStr">
         <is>
@@ -36241,7 +36241,7 @@
         <v>46196.70300431713</v>
       </c>
       <c r="S324" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T324" t="inlineStr">
         <is>
@@ -36348,7 +36348,7 @@
         <v>46196.70300539352</v>
       </c>
       <c r="S325" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T325" t="inlineStr">
         <is>
@@ -36455,7 +36455,7 @@
         <v>46196.70300612268</v>
       </c>
       <c r="S326" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T326" t="inlineStr">
         <is>
@@ -36562,7 +36562,7 @@
         <v>46196.70301788195</v>
       </c>
       <c r="S327" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T327" t="inlineStr">
         <is>
@@ -36669,7 +36669,7 @@
         <v>46196.70303107639</v>
       </c>
       <c r="S328" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T328" t="inlineStr">
         <is>
@@ -36776,7 +36776,7 @@
         <v>46196.70303379629</v>
       </c>
       <c r="S329" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T329" t="inlineStr">
         <is>
@@ -36883,7 +36883,7 @@
         <v>46196.70303469907</v>
       </c>
       <c r="S330" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T330" t="inlineStr">
         <is>
@@ -36990,7 +36990,7 @@
         <v>46196.70303524305</v>
       </c>
       <c r="S331" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T331" t="inlineStr">
         <is>
@@ -37097,7 +37097,7 @@
         <v>46196.70304373842</v>
       </c>
       <c r="S332" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T332" t="inlineStr">
         <is>
@@ -37200,7 +37200,7 @@
         <v>46196.70304771991</v>
       </c>
       <c r="S333" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T333" t="inlineStr">
         <is>
@@ -37303,7 +37303,7 @@
         <v>46206.65312673611</v>
       </c>
       <c r="S334" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T334" t="inlineStr">
         <is>
@@ -37410,7 +37410,7 @@
         <v>46206.65314806713</v>
       </c>
       <c r="S335" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T335" t="inlineStr">
         <is>
@@ -37517,7 +37517,7 @@
         <v>46206.6533227662</v>
       </c>
       <c r="S336" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T336" t="inlineStr">
         <is>
@@ -37624,7 +37624,7 @@
         <v>46206.65332584491</v>
       </c>
       <c r="S337" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T337" t="inlineStr">
         <is>
@@ -37731,7 +37731,7 @@
         <v>46206.65332746528</v>
       </c>
       <c r="S338" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T338" t="inlineStr">
         <is>
@@ -37838,7 +37838,7 @@
         <v>46206.6533497338</v>
       </c>
       <c r="S339" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T339" t="inlineStr">
         <is>
@@ -37945,7 +37945,7 @@
         <v>46206.65335243056</v>
       </c>
       <c r="S340" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T340" t="inlineStr">
         <is>
@@ -38052,7 +38052,7 @@
         <v>46206.65335459491</v>
       </c>
       <c r="S341" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T341" t="inlineStr">
         <is>
@@ -38159,7 +38159,7 @@
         <v>46206.6533571412</v>
       </c>
       <c r="S342" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T342" t="inlineStr">
         <is>
@@ -38266,7 +38266,7 @@
         <v>46206.65335732639</v>
       </c>
       <c r="S343" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T343" t="inlineStr">
         <is>
@@ -38373,7 +38373,7 @@
         <v>46206.65336203704</v>
       </c>
       <c r="S344" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T344" t="inlineStr">
         <is>
@@ -38480,7 +38480,7 @@
         <v>46206.65336258102</v>
       </c>
       <c r="S345" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T345" t="inlineStr">
         <is>
@@ -38587,7 +38587,7 @@
         <v>46206.65336273148</v>
       </c>
       <c r="S346" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T346" t="inlineStr">
         <is>
@@ -38694,7 +38694,7 @@
         <v>46206.65336582176</v>
       </c>
       <c r="S347" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T347" t="inlineStr">
         <is>
@@ -38797,7 +38797,7 @@
         <v>46206.65337017361</v>
       </c>
       <c r="S348" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T348" t="inlineStr">
         <is>
@@ -38900,7 +38900,7 @@
         <v>46206.65337484953</v>
       </c>
       <c r="S349" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T349" t="inlineStr">
         <is>
@@ -39003,7 +39003,7 @@
         <v>46206.6533755787</v>
       </c>
       <c r="S350" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T350" t="inlineStr">
         <is>
@@ -39106,7 +39106,7 @@
         <v>46206.65337596065</v>
       </c>
       <c r="S351" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T351" t="inlineStr">
         <is>
@@ -39209,7 +39209,7 @@
         <v>46206.65337630787</v>
       </c>
       <c r="S352" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T352" t="inlineStr">
         <is>
@@ -39312,7 +39312,7 @@
         <v>46203.79329930556</v>
       </c>
       <c r="S353" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T353" t="inlineStr">
         <is>
@@ -39419,7 +39419,7 @@
         <v>46203.79332729166</v>
       </c>
       <c r="S354" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T354" t="inlineStr">
         <is>
@@ -39526,7 +39526,7 @@
         <v>46203.79350855324</v>
       </c>
       <c r="S355" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T355" t="inlineStr">
         <is>
@@ -39633,7 +39633,7 @@
         <v>46203.79357210648</v>
       </c>
       <c r="S356" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T356" t="inlineStr">
         <is>
@@ -39740,7 +39740,7 @@
         <v>46203.79361802083</v>
       </c>
       <c r="S357" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T357" t="inlineStr">
         <is>
@@ -39847,7 +39847,7 @@
         <v>46203.7936680787</v>
       </c>
       <c r="S358" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T358" t="inlineStr">
         <is>
@@ -39954,7 +39954,7 @@
         <v>46203.79371605324</v>
       </c>
       <c r="S359" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T359" t="inlineStr">
         <is>
@@ -40061,7 +40061,7 @@
         <v>46203.79372373842</v>
       </c>
       <c r="S360" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T360" t="inlineStr">
         <is>
@@ -40168,7 +40168,7 @@
         <v>46203.79376369213</v>
       </c>
       <c r="S361" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T361" t="inlineStr">
         <is>
@@ -40275,7 +40275,7 @@
         <v>46203.79376936342</v>
       </c>
       <c r="S362" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T362" t="inlineStr">
         <is>
@@ -40382,7 +40382,7 @@
         <v>46203.79377502315</v>
       </c>
       <c r="S363" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T363" t="inlineStr">
         <is>
@@ -40489,7 +40489,7 @@
         <v>46204.50218425926</v>
       </c>
       <c r="S364" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T364" t="inlineStr">
         <is>
@@ -40592,7 +40592,7 @@
         <v>46203.79384278935</v>
       </c>
       <c r="S365" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T365" t="inlineStr">
         <is>
@@ -40695,7 +40695,7 @@
         <v>46204.50231513889</v>
       </c>
       <c r="S366" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T366" t="inlineStr">
         <is>
@@ -40798,7 +40798,7 @@
         <v>46213.47701689815</v>
       </c>
       <c r="S367" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T367" t="inlineStr">
         <is>
@@ -40901,7 +40901,7 @@
         <v>46213.4770175926</v>
       </c>
       <c r="S368" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T368" t="inlineStr">
         <is>
@@ -41004,7 +41004,7 @@
         <v>46213.4770175926</v>
       </c>
       <c r="S369" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T369" t="inlineStr">
         <is>
@@ -41107,7 +41107,7 @@
         <v>46215.35320414352</v>
       </c>
       <c r="S370" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T370" t="inlineStr">
         <is>
@@ -41214,7 +41214,7 @@
         <v>46215.35320613426</v>
       </c>
       <c r="S371" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T371" t="inlineStr">
         <is>
@@ -41321,7 +41321,7 @@
         <v>46213.56919034723</v>
       </c>
       <c r="S372" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T372" t="inlineStr">
         <is>
@@ -41428,7 +41428,7 @@
         <v>46215.35320667824</v>
       </c>
       <c r="S373" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T373" t="inlineStr">
         <is>
@@ -41535,7 +41535,7 @@
         <v>46215.35320722222</v>
       </c>
       <c r="S374" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T374" t="inlineStr">
         <is>
@@ -41642,7 +41642,7 @@
         <v>46213.56920064815</v>
       </c>
       <c r="S375" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T375" t="inlineStr">
         <is>
@@ -41749,7 +41749,7 @@
         <v>46213.56920517361</v>
       </c>
       <c r="S376" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T376" t="inlineStr">
         <is>
@@ -41856,7 +41856,7 @@
         <v>46215.3532077662</v>
       </c>
       <c r="S377" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T377" t="inlineStr">
         <is>
@@ -41963,7 +41963,7 @@
         <v>46215.35320831018</v>
       </c>
       <c r="S378" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T378" t="inlineStr">
         <is>
@@ -42070,7 +42070,7 @@
         <v>46215.35320885417</v>
       </c>
       <c r="S379" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T379" t="inlineStr">
         <is>
@@ -42177,7 +42177,7 @@
         <v>46215.35320957176</v>
       </c>
       <c r="S380" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T380" t="inlineStr">
         <is>
@@ -42284,7 +42284,7 @@
         <v>46215.35321011574</v>
       </c>
       <c r="S381" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T381" t="inlineStr">
         <is>
@@ -42391,7 +42391,7 @@
         <v>46206.39939344907</v>
       </c>
       <c r="S382" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T382" t="inlineStr">
         <is>
@@ -42503,7 +42503,7 @@
         <v>46205.46612821759</v>
       </c>
       <c r="S383" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T383" t="inlineStr">
         <is>
@@ -42615,7 +42615,7 @@
         <v>46205.44509731481</v>
       </c>
       <c r="S384" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T384" t="inlineStr">
         <is>
@@ -42727,7 +42727,7 @@
         <v>46206.40619622685</v>
       </c>
       <c r="S385" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T385" t="inlineStr">
         <is>

--- a/dados/base/goias.xlsx
+++ b/dados/base/goias.xlsx
@@ -62232,11 +62232,11 @@
     </row>
     <row r="571">
       <c r="A571" t="n">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM LTDA</t>
+          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
@@ -62251,7 +62251,7 @@
       </c>
       <c r="E571" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F571" t="inlineStr">
@@ -62286,11 +62286,11 @@
         </is>
       </c>
       <c r="O571" t="n">
-        <v>18094897</v>
+        <v>18048471</v>
       </c>
       <c r="P571" t="inlineStr">
         <is>
-          <t>Cristiana Grizostomo</t>
+          <t>Denis Reis</t>
         </is>
       </c>
       <c r="Q571" t="inlineStr">
@@ -62304,7 +62304,7 @@
       </c>
       <c r="T571" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM</t>
+          <t xml:space="preserve">GTG </t>
         </is>
       </c>
       <c r="U571" t="inlineStr">
@@ -62337,11 +62337,11 @@
     </row>
     <row r="572">
       <c r="A572" t="n">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
@@ -62351,7 +62351,7 @@
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E572" t="inlineStr">
@@ -62384,18 +62384,22 @@
       <c r="L572" s="1" t="n">
         <v>46226</v>
       </c>
-      <c r="M572" t="inlineStr"/>
+      <c r="M572" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
       <c r="N572" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O572" t="n">
-        <v>18048471</v>
+        <v>18094908</v>
       </c>
       <c r="P572" t="inlineStr">
         <is>
-          <t>Denis Reis</t>
+          <t>Fernando Bastos</t>
         </is>
       </c>
       <c r="Q572" t="inlineStr">
@@ -62417,7 +62421,12 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V572" t="inlineStr"/>
+      <c r="V572" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 14/07/2026 
+em execução - Data Comentário: 13/07/2026 11:30</t>
+        </is>
+      </c>
       <c r="W572" t="inlineStr"/>
       <c r="X572" t="inlineStr"/>
       <c r="Y572" t="inlineStr"/>
@@ -62442,11 +62451,11 @@
     </row>
     <row r="573">
       <c r="A573" t="n">
-        <v>6628</v>
+        <v>6548</v>
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>GOIAS SILAGEM LTDA</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
@@ -62456,12 +62465,12 @@
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E573" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F573" t="inlineStr">
@@ -62470,10 +62479,10 @@
         </is>
       </c>
       <c r="G573" t="n">
-        <v>7026</v>
+        <v>1914</v>
       </c>
       <c r="H573" t="n">
-        <v>0</v>
+        <v>1862</v>
       </c>
       <c r="I573" t="inlineStr">
         <is>
@@ -62482,29 +62491,25 @@
       </c>
       <c r="J573" t="inlineStr">
         <is>
-          <t>Movimento - Sistema de Análise</t>
+          <t>Receitas Financeiras ( Aplicação Financeira )</t>
         </is>
       </c>
       <c r="K573" t="inlineStr"/>
       <c r="L573" s="1" t="n">
-        <v>46226</v>
-      </c>
-      <c r="M573" t="inlineStr">
-        <is>
-          <t>14/07/2026</t>
-        </is>
-      </c>
+        <v>46224</v>
+      </c>
+      <c r="M573" t="inlineStr"/>
       <c r="N573" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O573" t="n">
-        <v>18094908</v>
+        <v>17988589</v>
       </c>
       <c r="P573" t="inlineStr">
         <is>
-          <t>Fernando Bastos</t>
+          <t>Cristiana Grizostomo</t>
         </is>
       </c>
       <c r="Q573" t="inlineStr">
@@ -62514,11 +62519,11 @@
       </c>
       <c r="R573" t="inlineStr"/>
       <c r="S573" t="n">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="T573" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
+          <t>GOIAS SILAGEM</t>
         </is>
       </c>
       <c r="U573" t="inlineStr">
@@ -62526,12 +62531,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V573" t="inlineStr">
-        <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 14/07/2026 
-em execução - Data Comentário: 13/07/2026 11:30</t>
-        </is>
-      </c>
+      <c r="V573" t="inlineStr"/>
       <c r="W573" t="inlineStr"/>
       <c r="X573" t="inlineStr"/>
       <c r="Y573" t="inlineStr"/>
@@ -62556,11 +62556,11 @@
     </row>
     <row r="574">
       <c r="A574" t="n">
-        <v>6548</v>
+        <v>6962</v>
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM LTDA</t>
+          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
@@ -62580,7 +62580,7 @@
       </c>
       <c r="F574" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Reynaldo Santos</t>
         </is>
       </c>
       <c r="G574" t="n">
@@ -62610,11 +62610,11 @@
         </is>
       </c>
       <c r="O574" t="n">
-        <v>17988589</v>
+        <v>18186972</v>
       </c>
       <c r="P574" t="inlineStr">
         <is>
-          <t>Cristiana Grizostomo</t>
+          <t>Denis Reis</t>
         </is>
       </c>
       <c r="Q574" t="inlineStr">
@@ -62628,14 +62628,10 @@
       </c>
       <c r="T574" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM</t>
-        </is>
-      </c>
-      <c r="U574" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>PROMOTORAS GYN</t>
+        </is>
+      </c>
+      <c r="U574" t="inlineStr"/>
       <c r="V574" t="inlineStr"/>
       <c r="W574" t="inlineStr"/>
       <c r="X574" t="inlineStr"/>
@@ -62661,11 +62657,11 @@
     </row>
     <row r="575">
       <c r="A575" t="n">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
+          <t>PROMOTORAS GYN LTDA</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
@@ -62715,7 +62711,7 @@
         </is>
       </c>
       <c r="O575" t="n">
-        <v>18186972</v>
+        <v>18187238</v>
       </c>
       <c r="P575" t="inlineStr">
         <is>
@@ -62762,11 +62758,11 @@
     </row>
     <row r="576">
       <c r="A576" t="n">
-        <v>6963</v>
+        <v>5417</v>
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN LTDA</t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
@@ -62786,28 +62782,28 @@
       </c>
       <c r="F576" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G576" t="n">
-        <v>1914</v>
+        <v>6759</v>
       </c>
       <c r="H576" t="n">
-        <v>1862</v>
+        <v>1788</v>
       </c>
       <c r="I576" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J576" t="inlineStr">
         <is>
-          <t>Receitas Financeiras ( Aplicação Financeira )</t>
+          <t>Digitalização de NF Ativo</t>
         </is>
       </c>
       <c r="K576" t="inlineStr"/>
       <c r="L576" s="1" t="n">
-        <v>46224</v>
+        <v>46227</v>
       </c>
       <c r="M576" t="inlineStr"/>
       <c r="N576" t="inlineStr">
@@ -62816,11 +62812,11 @@
         </is>
       </c>
       <c r="O576" t="n">
-        <v>18187238</v>
+        <v>17399188</v>
       </c>
       <c r="P576" t="inlineStr">
         <is>
-          <t>Denis Reis</t>
+          <t>Cristina Leite</t>
         </is>
       </c>
       <c r="Q576" t="inlineStr">
@@ -62830,14 +62826,18 @@
       </c>
       <c r="R576" t="inlineStr"/>
       <c r="S576" t="n">
-        <v>-7</v>
+        <v>-10</v>
       </c>
       <c r="T576" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN</t>
-        </is>
-      </c>
-      <c r="U576" t="inlineStr"/>
+          <t>NOSSO NOVO SUPERMERCADO</t>
+        </is>
+      </c>
+      <c r="U576" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V576" t="inlineStr"/>
       <c r="W576" t="inlineStr"/>
       <c r="X576" t="inlineStr"/>
@@ -62857,17 +62857,17 @@
       </c>
       <c r="AG576" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="n">
-        <v>5417</v>
+        <v>6279</v>
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>DIENNYFER DA S PEREIRA</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
@@ -62877,7 +62877,7 @@
       </c>
       <c r="D577" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E577" t="inlineStr">
@@ -62887,7 +62887,7 @@
       </c>
       <c r="F577" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G577" t="n">
@@ -62917,7 +62917,7 @@
         </is>
       </c>
       <c r="O577" t="n">
-        <v>17399188</v>
+        <v>17071010</v>
       </c>
       <c r="P577" t="inlineStr">
         <is>
@@ -62935,7 +62935,7 @@
       </c>
       <c r="T577" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U577" t="inlineStr">
@@ -62968,11 +62968,11 @@
     </row>
     <row r="578">
       <c r="A578" t="n">
-        <v>6279</v>
+        <v>6486</v>
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>DIENNYFER DA S PEREIRA</t>
+          <t>PC GAMER GOIANIA LTDA</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
@@ -62982,7 +62982,7 @@
       </c>
       <c r="D578" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E578" t="inlineStr">
@@ -62992,7 +62992,7 @@
       </c>
       <c r="F578" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G578" t="n">
@@ -63022,7 +63022,7 @@
         </is>
       </c>
       <c r="O578" t="n">
-        <v>17071010</v>
+        <v>16976175</v>
       </c>
       <c r="P578" t="inlineStr">
         <is>
@@ -63040,7 +63040,7 @@
       </c>
       <c r="T578" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>PC GAMER</t>
         </is>
       </c>
       <c r="U578" t="inlineStr">
@@ -63073,11 +63073,11 @@
     </row>
     <row r="579">
       <c r="A579" t="n">
-        <v>6486</v>
+        <v>6705</v>
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>PC GAMER GOIANIA LTDA</t>
+          <t>NARCIZO ALVES CORDEIRO</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
@@ -63087,7 +63087,7 @@
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E579" t="inlineStr">
@@ -63127,7 +63127,7 @@
         </is>
       </c>
       <c r="O579" t="n">
-        <v>16976175</v>
+        <v>17949017</v>
       </c>
       <c r="P579" t="inlineStr">
         <is>
@@ -63145,7 +63145,7 @@
       </c>
       <c r="T579" t="inlineStr">
         <is>
-          <t>PC GAMER</t>
+          <t>TECNO COM</t>
         </is>
       </c>
       <c r="U579" t="inlineStr">
@@ -63178,11 +63178,11 @@
     </row>
     <row r="580">
       <c r="A580" t="n">
-        <v>6705</v>
+        <v>5417</v>
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>NARCIZO ALVES CORDEIRO</t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
@@ -63192,7 +63192,7 @@
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E580" t="inlineStr">
@@ -63202,14 +63202,14 @@
       </c>
       <c r="F580" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G580" t="n">
-        <v>6759</v>
+        <v>11678</v>
       </c>
       <c r="H580" t="n">
-        <v>1788</v>
+        <v>0</v>
       </c>
       <c r="I580" t="inlineStr">
         <is>
@@ -63218,21 +63218,25 @@
       </c>
       <c r="J580" t="inlineStr">
         <is>
-          <t>Digitalização de NF Ativo</t>
+          <t>Encerramento de Competência – ISS Prefeitura</t>
         </is>
       </c>
       <c r="K580" t="inlineStr"/>
       <c r="L580" s="1" t="n">
-        <v>46227</v>
-      </c>
-      <c r="M580" t="inlineStr"/>
+        <v>46219</v>
+      </c>
+      <c r="M580" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
       <c r="N580" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O580" t="n">
-        <v>17949017</v>
+        <v>16948686</v>
       </c>
       <c r="P580" t="inlineStr">
         <is>
@@ -63246,11 +63250,11 @@
       </c>
       <c r="R580" t="inlineStr"/>
       <c r="S580" t="n">
-        <v>-10</v>
+        <v>-2</v>
       </c>
       <c r="T580" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>NOSSO NOVO SUPERMERCADO</t>
         </is>
       </c>
       <c r="U580" t="inlineStr">
@@ -63258,7 +63262,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V580" t="inlineStr"/>
+      <c r="V580" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 17/07/2026 - Data Comentário: 13/07/2026 11:43</t>
+        </is>
+      </c>
       <c r="W580" t="inlineStr"/>
       <c r="X580" t="inlineStr"/>
       <c r="Y580" t="inlineStr"/>
@@ -63283,11 +63291,11 @@
     </row>
     <row r="581">
       <c r="A581" t="n">
-        <v>5417</v>
+        <v>6224</v>
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
@@ -63307,7 +63315,7 @@
       </c>
       <c r="F581" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G581" t="n">
@@ -63341,7 +63349,7 @@
         </is>
       </c>
       <c r="O581" t="n">
-        <v>16948686</v>
+        <v>17206055</v>
       </c>
       <c r="P581" t="inlineStr">
         <is>
@@ -63359,7 +63367,7 @@
       </c>
       <c r="T581" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U581" t="inlineStr">
@@ -63396,11 +63404,11 @@
     </row>
     <row r="582">
       <c r="A582" t="n">
-        <v>6224</v>
+        <v>6278</v>
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>EMPORIO DOS FRIOS LTDA</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
@@ -63410,7 +63418,7 @@
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Real - Anual</t>
         </is>
       </c>
       <c r="E582" t="inlineStr">
@@ -63420,7 +63428,7 @@
       </c>
       <c r="F582" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G582" t="n">
@@ -63454,7 +63462,7 @@
         </is>
       </c>
       <c r="O582" t="n">
-        <v>17206055</v>
+        <v>17148907</v>
       </c>
       <c r="P582" t="inlineStr">
         <is>
@@ -63472,7 +63480,7 @@
       </c>
       <c r="T582" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U582" t="inlineStr">
@@ -63509,11 +63517,11 @@
     </row>
     <row r="583">
       <c r="A583" t="n">
-        <v>6278</v>
+        <v>6279</v>
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS LTDA</t>
+          <t>DIENNYFER DA S PEREIRA</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
@@ -63523,7 +63531,7 @@
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>Federal - Lucro Real - Anual</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E583" t="inlineStr">
@@ -63533,7 +63541,7 @@
       </c>
       <c r="F583" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G583" t="n">
@@ -63567,7 +63575,7 @@
         </is>
       </c>
       <c r="O583" t="n">
-        <v>17148907</v>
+        <v>17071145</v>
       </c>
       <c r="P583" t="inlineStr">
         <is>
@@ -63622,11 +63630,11 @@
     </row>
     <row r="584">
       <c r="A584" t="n">
-        <v>6279</v>
+        <v>6404</v>
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>DIENNYFER DA S PEREIRA</t>
+          <t>SOLAR INVESTIMENTOS LTDA</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
@@ -63646,7 +63654,7 @@
       </c>
       <c r="F584" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G584" t="n">
@@ -63680,7 +63688,7 @@
         </is>
       </c>
       <c r="O584" t="n">
-        <v>17071145</v>
+        <v>16962482</v>
       </c>
       <c r="P584" t="inlineStr">
         <is>
@@ -63698,7 +63706,7 @@
       </c>
       <c r="T584" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>SOLAR INVESTIMENTOS</t>
         </is>
       </c>
       <c r="U584" t="inlineStr">
@@ -63735,11 +63743,11 @@
     </row>
     <row r="585">
       <c r="A585" t="n">
-        <v>6404</v>
+        <v>6486</v>
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS LTDA</t>
+          <t>PC GAMER GOIANIA LTDA</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
@@ -63749,7 +63757,7 @@
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E585" t="inlineStr">
@@ -63793,7 +63801,7 @@
         </is>
       </c>
       <c r="O585" t="n">
-        <v>16962482</v>
+        <v>16976379</v>
       </c>
       <c r="P585" t="inlineStr">
         <is>
@@ -63811,7 +63819,7 @@
       </c>
       <c r="T585" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS</t>
+          <t>PC GAMER</t>
         </is>
       </c>
       <c r="U585" t="inlineStr">
@@ -63848,11 +63856,11 @@
     </row>
     <row r="586">
       <c r="A586" t="n">
-        <v>6486</v>
+        <v>5617</v>
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>PC GAMER GOIANIA LTDA</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
@@ -63876,7 +63884,7 @@
         </is>
       </c>
       <c r="G586" t="n">
-        <v>11678</v>
+        <v>1802</v>
       </c>
       <c r="H586" t="n">
         <v>0</v>
@@ -63888,25 +63896,21 @@
       </c>
       <c r="J586" t="inlineStr">
         <is>
-          <t>Encerramento de Competência – ISS Prefeitura</t>
+          <t>Est - ICMS RPA - CÓD. 046-2</t>
         </is>
       </c>
       <c r="K586" t="inlineStr"/>
       <c r="L586" s="1" t="n">
-        <v>46219</v>
-      </c>
-      <c r="M586" t="inlineStr">
-        <is>
-          <t>17/07/2026</t>
-        </is>
-      </c>
+        <v>46220</v>
+      </c>
+      <c r="M586" t="inlineStr"/>
       <c r="N586" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O586" t="n">
-        <v>16976379</v>
+        <v>17407589</v>
       </c>
       <c r="P586" t="inlineStr">
         <is>
@@ -63920,11 +63924,11 @@
       </c>
       <c r="R586" t="inlineStr"/>
       <c r="S586" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="T586" t="inlineStr">
         <is>
-          <t>PC GAMER</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U586" t="inlineStr">
@@ -63932,11 +63936,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V586" t="inlineStr">
-        <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 17/07/2026 - Data Comentário: 13/07/2026 11:43</t>
-        </is>
-      </c>
+      <c r="V586" t="inlineStr"/>
       <c r="W586" t="inlineStr"/>
       <c r="X586" t="inlineStr"/>
       <c r="Y586" t="inlineStr"/>
@@ -63950,7 +63950,7 @@
       <c r="AE586" t="inlineStr"/>
       <c r="AF586" t="inlineStr">
         <is>
-          <t>Tarefa</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="AG586" t="inlineStr">
@@ -63961,11 +63961,11 @@
     </row>
     <row r="587">
       <c r="A587" t="n">
-        <v>5617</v>
+        <v>6703</v>
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
@@ -63975,7 +63975,7 @@
       </c>
       <c r="D587" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E587" t="inlineStr">
@@ -64015,7 +64015,7 @@
         </is>
       </c>
       <c r="O587" t="n">
-        <v>17407589</v>
+        <v>17948794</v>
       </c>
       <c r="P587" t="inlineStr">
         <is>
@@ -64033,7 +64033,7 @@
       </c>
       <c r="T587" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>LIMA MOTA</t>
         </is>
       </c>
       <c r="U587" t="inlineStr">
@@ -64066,11 +64066,11 @@
     </row>
     <row r="588">
       <c r="A588" t="n">
-        <v>6703</v>
+        <v>6704</v>
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
+          <t>TECNO COM INFORMATICA LTDA</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
@@ -64080,7 +64080,7 @@
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E588" t="inlineStr">
@@ -64120,7 +64120,7 @@
         </is>
       </c>
       <c r="O588" t="n">
-        <v>17948794</v>
+        <v>18085196</v>
       </c>
       <c r="P588" t="inlineStr">
         <is>
@@ -64138,7 +64138,7 @@
       </c>
       <c r="T588" t="inlineStr">
         <is>
-          <t>LIMA MOTA</t>
+          <t>TECNO COM</t>
         </is>
       </c>
       <c r="U588" t="inlineStr">
@@ -64171,11 +64171,11 @@
     </row>
     <row r="589">
       <c r="A589" t="n">
-        <v>6704</v>
+        <v>5417</v>
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>TECNO COM INFORMATICA LTDA</t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
@@ -64195,11 +64195,11 @@
       </c>
       <c r="F589" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G589" t="n">
-        <v>1802</v>
+        <v>11286</v>
       </c>
       <c r="H589" t="n">
         <v>0</v>
@@ -64211,7 +64211,7 @@
       </c>
       <c r="J589" t="inlineStr">
         <is>
-          <t>Est - ICMS RPA - CÓD. 046-2</t>
+          <t>Est - ICMS RPA - CÓD. 046-2 (GO)</t>
         </is>
       </c>
       <c r="K589" t="inlineStr"/>
@@ -64225,7 +64225,7 @@
         </is>
       </c>
       <c r="O589" t="n">
-        <v>18085196</v>
+        <v>17399432</v>
       </c>
       <c r="P589" t="inlineStr">
         <is>
@@ -64243,7 +64243,7 @@
       </c>
       <c r="T589" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>NOSSO NOVO SUPERMERCADO</t>
         </is>
       </c>
       <c r="U589" t="inlineStr">
@@ -64276,11 +64276,11 @@
     </row>
     <row r="590">
       <c r="A590" t="n">
-        <v>5417</v>
+        <v>6278</v>
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>EMPORIO DOS FRIOS LTDA</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
@@ -64290,7 +64290,7 @@
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Real - Anual</t>
         </is>
       </c>
       <c r="E590" t="inlineStr">
@@ -64300,7 +64300,7 @@
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G590" t="n">
@@ -64330,7 +64330,7 @@
         </is>
       </c>
       <c r="O590" t="n">
-        <v>17399432</v>
+        <v>17148888</v>
       </c>
       <c r="P590" t="inlineStr">
         <is>
@@ -64348,7 +64348,7 @@
       </c>
       <c r="T590" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U590" t="inlineStr">
@@ -64381,11 +64381,11 @@
     </row>
     <row r="591">
       <c r="A591" t="n">
-        <v>6278</v>
+        <v>6279</v>
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS LTDA</t>
+          <t>DIENNYFER DA S PEREIRA</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
@@ -64395,7 +64395,7 @@
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>Federal - Lucro Real - Anual</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E591" t="inlineStr">
@@ -64405,7 +64405,7 @@
       </c>
       <c r="F591" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G591" t="n">
@@ -64435,7 +64435,7 @@
         </is>
       </c>
       <c r="O591" t="n">
-        <v>17148888</v>
+        <v>18087655</v>
       </c>
       <c r="P591" t="inlineStr">
         <is>
@@ -64486,11 +64486,11 @@
     </row>
     <row r="592">
       <c r="A592" t="n">
-        <v>6279</v>
+        <v>6404</v>
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>DIENNYFER DA S PEREIRA</t>
+          <t>SOLAR INVESTIMENTOS LTDA</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
@@ -64510,7 +64510,7 @@
       </c>
       <c r="F592" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G592" t="n">
@@ -64540,7 +64540,7 @@
         </is>
       </c>
       <c r="O592" t="n">
-        <v>18087655</v>
+        <v>16962462</v>
       </c>
       <c r="P592" t="inlineStr">
         <is>
@@ -64558,7 +64558,7 @@
       </c>
       <c r="T592" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>SOLAR INVESTIMENTOS</t>
         </is>
       </c>
       <c r="U592" t="inlineStr">
@@ -64591,11 +64591,11 @@
     </row>
     <row r="593">
       <c r="A593" t="n">
-        <v>6404</v>
+        <v>6705</v>
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS LTDA</t>
+          <t>NARCIZO ALVES CORDEIRO</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
@@ -64605,7 +64605,7 @@
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E593" t="inlineStr">
@@ -64619,7 +64619,7 @@
         </is>
       </c>
       <c r="G593" t="n">
-        <v>11286</v>
+        <v>1803</v>
       </c>
       <c r="H593" t="n">
         <v>0</v>
@@ -64631,21 +64631,21 @@
       </c>
       <c r="J593" t="inlineStr">
         <is>
-          <t>Est - ICMS RPA - CÓD. 046-2 (GO)</t>
+          <t>Est - ICMS SN - Diferencial Alíquota</t>
         </is>
       </c>
       <c r="K593" t="inlineStr"/>
       <c r="L593" s="1" t="n">
-        <v>46220</v>
+        <v>46231</v>
       </c>
       <c r="M593" t="inlineStr"/>
       <c r="N593" t="inlineStr">
         <is>
-          <t>06/2026</t>
+          <t>05/2026</t>
         </is>
       </c>
       <c r="O593" t="n">
-        <v>16962462</v>
+        <v>17948935</v>
       </c>
       <c r="P593" t="inlineStr">
         <is>
@@ -64659,11 +64659,11 @@
       </c>
       <c r="R593" t="inlineStr"/>
       <c r="S593" t="n">
-        <v>-3</v>
+        <v>-14</v>
       </c>
       <c r="T593" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS</t>
+          <t>TECNO COM</t>
         </is>
       </c>
       <c r="U593" t="inlineStr">
@@ -64696,11 +64696,11 @@
     </row>
     <row r="594">
       <c r="A594" t="n">
-        <v>6705</v>
+        <v>6404</v>
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>NARCIZO ALVES CORDEIRO</t>
+          <t>SOLAR INVESTIMENTOS LTDA</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
@@ -64710,7 +64710,7 @@
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E594" t="inlineStr">
@@ -64724,7 +64724,7 @@
         </is>
       </c>
       <c r="G594" t="n">
-        <v>1803</v>
+        <v>1810</v>
       </c>
       <c r="H594" t="n">
         <v>0</v>
@@ -64736,21 +64736,21 @@
       </c>
       <c r="J594" t="inlineStr">
         <is>
-          <t>Est - ICMS SN - Diferencial Alíquota</t>
+          <t>Fed - IRPJ/CSLL</t>
         </is>
       </c>
       <c r="K594" t="inlineStr"/>
       <c r="L594" s="1" t="n">
-        <v>46231</v>
+        <v>46230</v>
       </c>
       <c r="M594" t="inlineStr"/>
       <c r="N594" t="inlineStr">
         <is>
-          <t>05/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
       <c r="O594" t="n">
-        <v>17948935</v>
+        <v>16962177</v>
       </c>
       <c r="P594" t="inlineStr">
         <is>
@@ -64764,11 +64764,11 @@
       </c>
       <c r="R594" t="inlineStr"/>
       <c r="S594" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T594" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>SOLAR INVESTIMENTOS</t>
         </is>
       </c>
       <c r="U594" t="inlineStr">
@@ -64801,11 +64801,11 @@
     </row>
     <row r="595">
       <c r="A595" t="n">
-        <v>6404</v>
+        <v>6703</v>
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS LTDA</t>
+          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
@@ -64855,7 +64855,7 @@
         </is>
       </c>
       <c r="O595" t="n">
-        <v>16962177</v>
+        <v>17948812</v>
       </c>
       <c r="P595" t="inlineStr">
         <is>
@@ -64873,7 +64873,7 @@
       </c>
       <c r="T595" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS</t>
+          <t>LIMA MOTA</t>
         </is>
       </c>
       <c r="U595" t="inlineStr">
@@ -64906,11 +64906,11 @@
     </row>
     <row r="596">
       <c r="A596" t="n">
-        <v>6703</v>
+        <v>5417</v>
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
@@ -64920,7 +64920,7 @@
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E596" t="inlineStr">
@@ -64930,11 +64930,11 @@
       </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G596" t="n">
-        <v>1810</v>
+        <v>6762</v>
       </c>
       <c r="H596" t="n">
         <v>0</v>
@@ -64946,12 +64946,12 @@
       </c>
       <c r="J596" t="inlineStr">
         <is>
-          <t>Fed - IRPJ/CSLL</t>
+          <t>Fed - IRRF s/ Aluguel - 3208</t>
         </is>
       </c>
       <c r="K596" t="inlineStr"/>
       <c r="L596" s="1" t="n">
-        <v>46230</v>
+        <v>46220</v>
       </c>
       <c r="M596" t="inlineStr"/>
       <c r="N596" t="inlineStr">
@@ -64960,7 +64960,7 @@
         </is>
       </c>
       <c r="O596" t="n">
-        <v>17948812</v>
+        <v>17399198</v>
       </c>
       <c r="P596" t="inlineStr">
         <is>
@@ -64974,11 +64974,11 @@
       </c>
       <c r="R596" t="inlineStr"/>
       <c r="S596" t="n">
-        <v>-13</v>
+        <v>-3</v>
       </c>
       <c r="T596" t="inlineStr">
         <is>
-          <t>LIMA MOTA</t>
+          <t>NOSSO NOVO SUPERMERCADO</t>
         </is>
       </c>
       <c r="U596" t="inlineStr">
@@ -65011,11 +65011,11 @@
     </row>
     <row r="597">
       <c r="A597" t="n">
-        <v>5417</v>
+        <v>5617</v>
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
@@ -65035,7 +65035,7 @@
       </c>
       <c r="F597" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G597" t="n">
@@ -65065,7 +65065,7 @@
         </is>
       </c>
       <c r="O597" t="n">
-        <v>17399198</v>
+        <v>17407769</v>
       </c>
       <c r="P597" t="inlineStr">
         <is>
@@ -65083,7 +65083,7 @@
       </c>
       <c r="T597" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U597" t="inlineStr">
@@ -65116,11 +65116,11 @@
     </row>
     <row r="598">
       <c r="A598" t="n">
-        <v>5617</v>
+        <v>6224</v>
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
@@ -65140,7 +65140,7 @@
       </c>
       <c r="F598" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G598" t="n">
@@ -65170,7 +65170,7 @@
         </is>
       </c>
       <c r="O598" t="n">
-        <v>17407769</v>
+        <v>17688897</v>
       </c>
       <c r="P598" t="inlineStr">
         <is>
@@ -65221,11 +65221,11 @@
     </row>
     <row r="599">
       <c r="A599" t="n">
-        <v>6224</v>
+        <v>6279</v>
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>DIENNYFER DA S PEREIRA</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
@@ -65235,7 +65235,7 @@
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E599" t="inlineStr">
@@ -65249,7 +65249,7 @@
         </is>
       </c>
       <c r="G599" t="n">
-        <v>6762</v>
+        <v>1807</v>
       </c>
       <c r="H599" t="n">
         <v>0</v>
@@ -65261,12 +65261,12 @@
       </c>
       <c r="J599" t="inlineStr">
         <is>
-          <t>Fed - IRRF s/ Aluguel - 3208</t>
+          <t>Fed - PIS/COFINS Cumulativo - 2172</t>
         </is>
       </c>
       <c r="K599" t="inlineStr"/>
       <c r="L599" s="1" t="n">
-        <v>46220</v>
+        <v>46225</v>
       </c>
       <c r="M599" t="inlineStr"/>
       <c r="N599" t="inlineStr">
@@ -65275,7 +65275,7 @@
         </is>
       </c>
       <c r="O599" t="n">
-        <v>17688897</v>
+        <v>18087644</v>
       </c>
       <c r="P599" t="inlineStr">
         <is>
@@ -65289,11 +65289,11 @@
       </c>
       <c r="R599" t="inlineStr"/>
       <c r="S599" t="n">
-        <v>-3</v>
+        <v>-8</v>
       </c>
       <c r="T599" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U599" t="inlineStr">
@@ -65326,11 +65326,11 @@
     </row>
     <row r="600">
       <c r="A600" t="n">
-        <v>6279</v>
+        <v>6404</v>
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>DIENNYFER DA S PEREIRA</t>
+          <t>SOLAR INVESTIMENTOS LTDA</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
@@ -65350,7 +65350,7 @@
       </c>
       <c r="F600" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G600" t="n">
@@ -65380,7 +65380,7 @@
         </is>
       </c>
       <c r="O600" t="n">
-        <v>18087644</v>
+        <v>16962169</v>
       </c>
       <c r="P600" t="inlineStr">
         <is>
@@ -65398,7 +65398,7 @@
       </c>
       <c r="T600" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>SOLAR INVESTIMENTOS</t>
         </is>
       </c>
       <c r="U600" t="inlineStr">
@@ -65431,11 +65431,11 @@
     </row>
     <row r="601">
       <c r="A601" t="n">
-        <v>6404</v>
+        <v>6703</v>
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS LTDA</t>
+          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
@@ -65485,7 +65485,7 @@
         </is>
       </c>
       <c r="O601" t="n">
-        <v>16962169</v>
+        <v>17948804</v>
       </c>
       <c r="P601" t="inlineStr">
         <is>
@@ -65503,7 +65503,7 @@
       </c>
       <c r="T601" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS</t>
+          <t>LIMA MOTA</t>
         </is>
       </c>
       <c r="U601" t="inlineStr">
@@ -65536,11 +65536,11 @@
     </row>
     <row r="602">
       <c r="A602" t="n">
-        <v>6703</v>
+        <v>5417</v>
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
@@ -65550,7 +65550,7 @@
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E602" t="inlineStr">
@@ -65560,11 +65560,11 @@
       </c>
       <c r="F602" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G602" t="n">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="H602" t="n">
         <v>0</v>
@@ -65576,7 +65576,7 @@
       </c>
       <c r="J602" t="inlineStr">
         <is>
-          <t>Fed - PIS/COFINS Cumulativo - 2172</t>
+          <t>Fed - PIS/COFINS Não Cumul/Mon - 5856</t>
         </is>
       </c>
       <c r="K602" t="inlineStr"/>
@@ -65590,7 +65590,7 @@
         </is>
       </c>
       <c r="O602" t="n">
-        <v>17948804</v>
+        <v>17398963</v>
       </c>
       <c r="P602" t="inlineStr">
         <is>
@@ -65608,7 +65608,7 @@
       </c>
       <c r="T602" t="inlineStr">
         <is>
-          <t>LIMA MOTA</t>
+          <t>NOSSO NOVO SUPERMERCADO</t>
         </is>
       </c>
       <c r="U602" t="inlineStr">
@@ -65641,11 +65641,11 @@
     </row>
     <row r="603">
       <c r="A603" t="n">
-        <v>5417</v>
+        <v>5617</v>
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
@@ -65665,7 +65665,7 @@
       </c>
       <c r="F603" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G603" t="n">
@@ -65695,7 +65695,7 @@
         </is>
       </c>
       <c r="O603" t="n">
-        <v>17398963</v>
+        <v>17407599</v>
       </c>
       <c r="P603" t="inlineStr">
         <is>
@@ -65713,7 +65713,7 @@
       </c>
       <c r="T603" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U603" t="inlineStr">
@@ -65746,11 +65746,11 @@
     </row>
     <row r="604">
       <c r="A604" t="n">
-        <v>5617</v>
+        <v>6224</v>
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
@@ -65770,7 +65770,7 @@
       </c>
       <c r="F604" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G604" t="n">
@@ -65800,7 +65800,7 @@
         </is>
       </c>
       <c r="O604" t="n">
-        <v>17407599</v>
+        <v>17688691</v>
       </c>
       <c r="P604" t="inlineStr">
         <is>
@@ -65851,11 +65851,11 @@
     </row>
     <row r="605">
       <c r="A605" t="n">
-        <v>6224</v>
+        <v>6278</v>
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>EMPORIO DOS FRIOS LTDA</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
@@ -65865,7 +65865,7 @@
       </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Real - Anual</t>
         </is>
       </c>
       <c r="E605" t="inlineStr">
@@ -65875,7 +65875,7 @@
       </c>
       <c r="F605" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G605" t="n">
@@ -65905,7 +65905,7 @@
         </is>
       </c>
       <c r="O605" t="n">
-        <v>17688691</v>
+        <v>17148704</v>
       </c>
       <c r="P605" t="inlineStr">
         <is>
@@ -65923,7 +65923,7 @@
       </c>
       <c r="T605" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U605" t="inlineStr">
@@ -65956,11 +65956,11 @@
     </row>
     <row r="606">
       <c r="A606" t="n">
-        <v>6278</v>
+        <v>6704</v>
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS LTDA</t>
+          <t>TECNO COM INFORMATICA LTDA</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
@@ -65970,7 +65970,7 @@
       </c>
       <c r="D606" t="inlineStr">
         <is>
-          <t>Federal - Lucro Real - Anual</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E606" t="inlineStr">
@@ -66010,7 +66010,7 @@
         </is>
       </c>
       <c r="O606" t="n">
-        <v>17148704</v>
+        <v>18085207</v>
       </c>
       <c r="P606" t="inlineStr">
         <is>
@@ -66028,7 +66028,7 @@
       </c>
       <c r="T606" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>TECNO COM</t>
         </is>
       </c>
       <c r="U606" t="inlineStr">
@@ -66061,11 +66061,11 @@
     </row>
     <row r="607">
       <c r="A607" t="n">
-        <v>6704</v>
+        <v>5617</v>
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>TECNO COM INFORMATICA LTDA</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
@@ -66089,7 +66089,7 @@
         </is>
       </c>
       <c r="G607" t="n">
-        <v>1808</v>
+        <v>7025</v>
       </c>
       <c r="H607" t="n">
         <v>0</v>
@@ -66101,12 +66101,12 @@
       </c>
       <c r="J607" t="inlineStr">
         <is>
-          <t>Fed - PIS/COFINS Não Cumul/Mon - 5856</t>
+          <t>Movimento - Sistema de Análise</t>
         </is>
       </c>
       <c r="K607" t="inlineStr"/>
       <c r="L607" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="M607" t="inlineStr"/>
       <c r="N607" t="inlineStr">
@@ -66115,7 +66115,7 @@
         </is>
       </c>
       <c r="O607" t="n">
-        <v>18085207</v>
+        <v>17407819</v>
       </c>
       <c r="P607" t="inlineStr">
         <is>
@@ -66129,11 +66129,11 @@
       </c>
       <c r="R607" t="inlineStr"/>
       <c r="S607" t="n">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="T607" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U607" t="inlineStr">
@@ -66155,7 +66155,7 @@
       <c r="AE607" t="inlineStr"/>
       <c r="AF607" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Tarefa</t>
         </is>
       </c>
       <c r="AG607" t="inlineStr">
@@ -66166,11 +66166,11 @@
     </row>
     <row r="608">
       <c r="A608" t="n">
-        <v>5617</v>
+        <v>6278</v>
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>EMPORIO DOS FRIOS LTDA</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
@@ -66180,7 +66180,7 @@
       </c>
       <c r="D608" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Real - Anual</t>
         </is>
       </c>
       <c r="E608" t="inlineStr">
@@ -66220,7 +66220,7 @@
         </is>
       </c>
       <c r="O608" t="n">
-        <v>17407819</v>
+        <v>17539786</v>
       </c>
       <c r="P608" t="inlineStr">
         <is>
@@ -66238,7 +66238,7 @@
       </c>
       <c r="T608" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U608" t="inlineStr">
@@ -66271,11 +66271,11 @@
     </row>
     <row r="609">
       <c r="A609" t="n">
-        <v>6278</v>
+        <v>6279</v>
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS LTDA</t>
+          <t>DIENNYFER DA S PEREIRA</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
@@ -66285,7 +66285,7 @@
       </c>
       <c r="D609" t="inlineStr">
         <is>
-          <t>Federal - Lucro Real - Anual</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E609" t="inlineStr">
@@ -66295,7 +66295,7 @@
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G609" t="n">
@@ -66325,7 +66325,7 @@
         </is>
       </c>
       <c r="O609" t="n">
-        <v>17539786</v>
+        <v>17646092</v>
       </c>
       <c r="P609" t="inlineStr">
         <is>
@@ -66376,11 +66376,11 @@
     </row>
     <row r="610">
       <c r="A610" t="n">
-        <v>6279</v>
+        <v>6486</v>
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>DIENNYFER DA S PEREIRA</t>
+          <t>PC GAMER GOIANIA LTDA</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
@@ -66390,7 +66390,7 @@
       </c>
       <c r="D610" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E610" t="inlineStr">
@@ -66400,7 +66400,7 @@
       </c>
       <c r="F610" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G610" t="n">
@@ -66430,7 +66430,7 @@
         </is>
       </c>
       <c r="O610" t="n">
-        <v>17646092</v>
+        <v>16976225</v>
       </c>
       <c r="P610" t="inlineStr">
         <is>
@@ -66448,7 +66448,7 @@
       </c>
       <c r="T610" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>PC GAMER</t>
         </is>
       </c>
       <c r="U610" t="inlineStr">
@@ -66456,7 +66456,13 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V610" t="inlineStr"/>
+      <c r="V610" t="inlineStr">
+        <is>
+          <t>Integração com Sistema de Análise 
+ICMS liberado, aguardo a validação do SPED Contribuições. 
+Data Simulação: 06/07/2026 18:42:09 - Data Comentário: 06/07/2026 19:12</t>
+        </is>
+      </c>
       <c r="W610" t="inlineStr"/>
       <c r="X610" t="inlineStr"/>
       <c r="Y610" t="inlineStr"/>
@@ -66481,11 +66487,11 @@
     </row>
     <row r="611">
       <c r="A611" t="n">
-        <v>6486</v>
+        <v>6705</v>
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>PC GAMER GOIANIA LTDA</t>
+          <t>NARCIZO ALVES CORDEIRO</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
@@ -66495,7 +66501,7 @@
       </c>
       <c r="D611" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E611" t="inlineStr">
@@ -66509,24 +66515,24 @@
         </is>
       </c>
       <c r="G611" t="n">
-        <v>7025</v>
+        <v>945</v>
       </c>
       <c r="H611" t="n">
         <v>0</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="J611" t="inlineStr">
         <is>
-          <t>Movimento - Sistema de Análise</t>
+          <t>Confirm Rec - DAS</t>
         </is>
       </c>
       <c r="K611" t="inlineStr"/>
       <c r="L611" s="1" t="n">
-        <v>46226</v>
+        <v>46223</v>
       </c>
       <c r="M611" t="inlineStr"/>
       <c r="N611" t="inlineStr">
@@ -66535,11 +66541,11 @@
         </is>
       </c>
       <c r="O611" t="n">
-        <v>16976225</v>
+        <v>17952522</v>
       </c>
       <c r="P611" t="inlineStr">
         <is>
-          <t>Cristina Leite</t>
+          <t>Victoria Virgens</t>
         </is>
       </c>
       <c r="Q611" t="inlineStr">
@@ -66549,11 +66555,11 @@
       </c>
       <c r="R611" t="inlineStr"/>
       <c r="S611" t="n">
-        <v>-9</v>
+        <v>-6</v>
       </c>
       <c r="T611" t="inlineStr">
         <is>
-          <t>PC GAMER</t>
+          <t>TECNO COM</t>
         </is>
       </c>
       <c r="U611" t="inlineStr">
@@ -66563,9 +66569,7 @@
       </c>
       <c r="V611" t="inlineStr">
         <is>
-          <t>Integração com Sistema de Análise 
-ICMS liberado, aguardo a validação do SPED Contribuições. 
-Data Simulação: 06/07/2026 18:42:09 - Data Comentário: 06/07/2026 19:12</t>
+          <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1805] sendo a ultima baixa feita [1805]-14/07/2026 10:55:51.. - Data Comentário: 14/07/2026 10:54</t>
         </is>
       </c>
       <c r="W611" t="inlineStr"/>
@@ -66581,22 +66585,18 @@
       <c r="AE611" t="inlineStr"/>
       <c r="AF611" t="inlineStr">
         <is>
-          <t>Tarefa</t>
-        </is>
-      </c>
-      <c r="AG611" t="inlineStr">
-        <is>
-          <t>Ricardo Fischer</t>
-        </is>
-      </c>
+          <t>Imposto</t>
+        </is>
+      </c>
+      <c r="AG611" t="inlineStr"/>
     </row>
     <row r="612">
       <c r="A612" t="n">
-        <v>6705</v>
+        <v>6779</v>
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>NARCIZO ALVES CORDEIRO</t>
+          <t>CORDEIRO E CIA LTDA</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
@@ -66646,7 +66646,7 @@
         </is>
       </c>
       <c r="O612" t="n">
-        <v>17952522</v>
+        <v>18056693</v>
       </c>
       <c r="P612" t="inlineStr">
         <is>
@@ -66667,14 +66667,10 @@
           <t>TECNO COM</t>
         </is>
       </c>
-      <c r="U612" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+      <c r="U612" t="inlineStr"/>
       <c r="V612" t="inlineStr">
         <is>
-          <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1805] sendo a ultima baixa feita [1805]-14/07/2026 10:55:51.. - Data Comentário: 14/07/2026 10:54</t>
+          <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1805] sendo a ultima baixa feita [1805]-14/07/2026 10:55:52.. - Data Comentário: 14/07/2026 10:54</t>
         </is>
       </c>
       <c r="W612" t="inlineStr"/>
@@ -66697,11 +66693,11 @@
     </row>
     <row r="613">
       <c r="A613" t="n">
-        <v>6779</v>
+        <v>6885</v>
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>CORDEIRO E CIA LTDA</t>
+          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
@@ -66751,7 +66747,7 @@
         </is>
       </c>
       <c r="O613" t="n">
-        <v>18056693</v>
+        <v>18128639</v>
       </c>
       <c r="P613" t="inlineStr">
         <is>
@@ -66769,13 +66765,13 @@
       </c>
       <c r="T613" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U613" t="inlineStr"/>
       <c r="V613" t="inlineStr">
         <is>
-          <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1805] sendo a ultima baixa feita [1805]-14/07/2026 10:55:52.. - Data Comentário: 14/07/2026 10:54</t>
+          <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1805] sendo a ultima baixa feita [1805]-14/07/2026 09:05:39.. - Data Comentário: 14/07/2026 09:04</t>
         </is>
       </c>
       <c r="W613" t="inlineStr"/>
@@ -66798,11 +66794,11 @@
     </row>
     <row r="614">
       <c r="A614" t="n">
-        <v>6885</v>
+        <v>6627</v>
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
+          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
@@ -66812,12 +66808,12 @@
       </c>
       <c r="D614" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E614" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F614" t="inlineStr">
@@ -66826,7 +66822,7 @@
         </is>
       </c>
       <c r="G614" t="n">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="H614" t="n">
         <v>0</v>
@@ -66838,7 +66834,7 @@
       </c>
       <c r="J614" t="inlineStr">
         <is>
-          <t>Confirm Rec - DAS</t>
+          <t>Confirm Rec - ICMS RPA</t>
         </is>
       </c>
       <c r="K614" t="inlineStr"/>
@@ -66852,7 +66848,7 @@
         </is>
       </c>
       <c r="O614" t="n">
-        <v>18128639</v>
+        <v>17042267</v>
       </c>
       <c r="P614" t="inlineStr">
         <is>
@@ -66870,15 +66866,15 @@
       </c>
       <c r="T614" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
-        </is>
-      </c>
-      <c r="U614" t="inlineStr"/>
-      <c r="V614" t="inlineStr">
-        <is>
-          <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1805] sendo a ultima baixa feita [1805]-14/07/2026 09:05:39.. - Data Comentário: 14/07/2026 09:04</t>
-        </is>
-      </c>
+          <t xml:space="preserve">GTG </t>
+        </is>
+      </c>
+      <c r="U614" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V614" t="inlineStr"/>
       <c r="W614" t="inlineStr"/>
       <c r="X614" t="inlineStr"/>
       <c r="Y614" t="inlineStr"/>
@@ -66899,11 +66895,11 @@
     </row>
     <row r="615">
       <c r="A615" t="n">
-        <v>6627</v>
+        <v>6885</v>
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
+          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
@@ -66913,12 +66909,12 @@
       </c>
       <c r="D615" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E615" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F615" t="inlineStr">
@@ -66927,7 +66923,7 @@
         </is>
       </c>
       <c r="G615" t="n">
-        <v>946</v>
+        <v>953</v>
       </c>
       <c r="H615" t="n">
         <v>0</v>
@@ -66939,12 +66935,12 @@
       </c>
       <c r="J615" t="inlineStr">
         <is>
-          <t>Confirm Rec - ICMS RPA</t>
+          <t>Confirm Rec - PIS/COFINS</t>
         </is>
       </c>
       <c r="K615" t="inlineStr"/>
       <c r="L615" s="1" t="n">
-        <v>46223</v>
+        <v>46227</v>
       </c>
       <c r="M615" t="inlineStr"/>
       <c r="N615" t="inlineStr">
@@ -66953,7 +66949,7 @@
         </is>
       </c>
       <c r="O615" t="n">
-        <v>17042267</v>
+        <v>18128666</v>
       </c>
       <c r="P615" t="inlineStr">
         <is>
@@ -66967,18 +66963,14 @@
       </c>
       <c r="R615" t="inlineStr"/>
       <c r="S615" t="n">
-        <v>-6</v>
+        <v>-10</v>
       </c>
       <c r="T615" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
-        </is>
-      </c>
-      <c r="U615" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>EMPORIO DOS FRIOS</t>
+        </is>
+      </c>
+      <c r="U615" t="inlineStr"/>
       <c r="V615" t="inlineStr"/>
       <c r="W615" t="inlineStr"/>
       <c r="X615" t="inlineStr"/>
@@ -67000,11 +66992,11 @@
     </row>
     <row r="616">
       <c r="A616" t="n">
-        <v>6885</v>
+        <v>5417</v>
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
@@ -67014,7 +67006,7 @@
       </c>
       <c r="D616" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E616" t="inlineStr">
@@ -67024,11 +67016,11 @@
       </c>
       <c r="F616" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G616" t="n">
-        <v>953</v>
+        <v>9086</v>
       </c>
       <c r="H616" t="n">
         <v>0</v>
@@ -67040,21 +67032,21 @@
       </c>
       <c r="J616" t="inlineStr">
         <is>
-          <t>Confirm Rec - PIS/COFINS</t>
+          <t>Consulta Cx Postal - 2º Quinzena</t>
         </is>
       </c>
       <c r="K616" t="inlineStr"/>
       <c r="L616" s="1" t="n">
-        <v>46227</v>
+        <v>46220</v>
       </c>
       <c r="M616" t="inlineStr"/>
       <c r="N616" t="inlineStr">
         <is>
-          <t>06/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
       <c r="O616" t="n">
-        <v>18128666</v>
+        <v>17399361</v>
       </c>
       <c r="P616" t="inlineStr">
         <is>
@@ -67068,14 +67060,18 @@
       </c>
       <c r="R616" t="inlineStr"/>
       <c r="S616" t="n">
-        <v>-10</v>
+        <v>-3</v>
       </c>
       <c r="T616" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
-        </is>
-      </c>
-      <c r="U616" t="inlineStr"/>
+          <t>NOSSO NOVO SUPERMERCADO</t>
+        </is>
+      </c>
+      <c r="U616" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V616" t="inlineStr"/>
       <c r="W616" t="inlineStr"/>
       <c r="X616" t="inlineStr"/>
@@ -67090,18 +67086,18 @@
       <c r="AE616" t="inlineStr"/>
       <c r="AF616" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Obrigação Acessória</t>
         </is>
       </c>
       <c r="AG616" t="inlineStr"/>
     </row>
     <row r="617">
       <c r="A617" t="n">
-        <v>5417</v>
+        <v>5617</v>
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
@@ -67121,7 +67117,7 @@
       </c>
       <c r="F617" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G617" t="n">
@@ -67151,7 +67147,7 @@
         </is>
       </c>
       <c r="O617" t="n">
-        <v>17399361</v>
+        <v>17407882</v>
       </c>
       <c r="P617" t="inlineStr">
         <is>
@@ -67169,7 +67165,7 @@
       </c>
       <c r="T617" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U617" t="inlineStr">
@@ -67198,11 +67194,11 @@
     </row>
     <row r="618">
       <c r="A618" t="n">
-        <v>5617</v>
+        <v>6224</v>
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
@@ -67222,7 +67218,7 @@
       </c>
       <c r="F618" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G618" t="n">
@@ -67252,7 +67248,7 @@
         </is>
       </c>
       <c r="O618" t="n">
-        <v>17407882</v>
+        <v>17689000</v>
       </c>
       <c r="P618" t="inlineStr">
         <is>
@@ -67299,11 +67295,11 @@
     </row>
     <row r="619">
       <c r="A619" t="n">
-        <v>6224</v>
+        <v>6278</v>
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>EMPORIO DOS FRIOS LTDA</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
@@ -67313,7 +67309,7 @@
       </c>
       <c r="D619" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Real - Anual</t>
         </is>
       </c>
       <c r="E619" t="inlineStr">
@@ -67323,7 +67319,7 @@
       </c>
       <c r="F619" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G619" t="n">
@@ -67353,7 +67349,7 @@
         </is>
       </c>
       <c r="O619" t="n">
-        <v>17689000</v>
+        <v>17539858</v>
       </c>
       <c r="P619" t="inlineStr">
         <is>
@@ -67371,7 +67367,7 @@
       </c>
       <c r="T619" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U619" t="inlineStr">
@@ -67400,11 +67396,11 @@
     </row>
     <row r="620">
       <c r="A620" t="n">
-        <v>6278</v>
+        <v>6279</v>
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS LTDA</t>
+          <t>DIENNYFER DA S PEREIRA</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
@@ -67414,7 +67410,7 @@
       </c>
       <c r="D620" t="inlineStr">
         <is>
-          <t>Federal - Lucro Real - Anual</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E620" t="inlineStr">
@@ -67424,7 +67420,7 @@
       </c>
       <c r="F620" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G620" t="n">
@@ -67454,7 +67450,7 @@
         </is>
       </c>
       <c r="O620" t="n">
-        <v>17539858</v>
+        <v>17646135</v>
       </c>
       <c r="P620" t="inlineStr">
         <is>
@@ -67501,11 +67497,11 @@
     </row>
     <row r="621">
       <c r="A621" t="n">
-        <v>6279</v>
+        <v>6404</v>
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>DIENNYFER DA S PEREIRA</t>
+          <t>SOLAR INVESTIMENTOS LTDA</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
@@ -67525,7 +67521,7 @@
       </c>
       <c r="F621" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G621" t="n">
@@ -67555,7 +67551,7 @@
         </is>
       </c>
       <c r="O621" t="n">
-        <v>17646135</v>
+        <v>16962378</v>
       </c>
       <c r="P621" t="inlineStr">
         <is>
@@ -67573,7 +67569,7 @@
       </c>
       <c r="T621" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>SOLAR INVESTIMENTOS</t>
         </is>
       </c>
       <c r="U621" t="inlineStr">
@@ -67602,11 +67598,11 @@
     </row>
     <row r="622">
       <c r="A622" t="n">
-        <v>6404</v>
+        <v>6486</v>
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS LTDA</t>
+          <t>PC GAMER GOIANIA LTDA</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
@@ -67616,7 +67612,7 @@
       </c>
       <c r="D622" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E622" t="inlineStr">
@@ -67656,7 +67652,7 @@
         </is>
       </c>
       <c r="O622" t="n">
-        <v>16962378</v>
+        <v>16976268</v>
       </c>
       <c r="P622" t="inlineStr">
         <is>
@@ -67674,7 +67670,7 @@
       </c>
       <c r="T622" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS</t>
+          <t>PC GAMER</t>
         </is>
       </c>
       <c r="U622" t="inlineStr">
@@ -67703,11 +67699,11 @@
     </row>
     <row r="623">
       <c r="A623" t="n">
-        <v>6486</v>
+        <v>6548</v>
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>PC GAMER GOIANIA LTDA</t>
+          <t>GOIAS SILAGEM LTDA</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
@@ -67757,7 +67753,7 @@
         </is>
       </c>
       <c r="O623" t="n">
-        <v>16976268</v>
+        <v>17222863</v>
       </c>
       <c r="P623" t="inlineStr">
         <is>
@@ -67775,7 +67771,7 @@
       </c>
       <c r="T623" t="inlineStr">
         <is>
-          <t>PC GAMER</t>
+          <t>GOIAS SILAGEM</t>
         </is>
       </c>
       <c r="U623" t="inlineStr">
@@ -67804,11 +67800,11 @@
     </row>
     <row r="624">
       <c r="A624" t="n">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM LTDA</t>
+          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
@@ -67823,7 +67819,7 @@
       </c>
       <c r="E624" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F624" t="inlineStr">
@@ -67858,7 +67854,7 @@
         </is>
       </c>
       <c r="O624" t="n">
-        <v>17222863</v>
+        <v>17042583</v>
       </c>
       <c r="P624" t="inlineStr">
         <is>
@@ -67876,7 +67872,7 @@
       </c>
       <c r="T624" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM</t>
+          <t xml:space="preserve">GTG </t>
         </is>
       </c>
       <c r="U624" t="inlineStr">
@@ -67905,11 +67901,11 @@
     </row>
     <row r="625">
       <c r="A625" t="n">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
@@ -67919,7 +67915,7 @@
       </c>
       <c r="D625" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E625" t="inlineStr">
@@ -67959,7 +67955,7 @@
         </is>
       </c>
       <c r="O625" t="n">
-        <v>17042583</v>
+        <v>16960072</v>
       </c>
       <c r="P625" t="inlineStr">
         <is>
@@ -68006,11 +68002,11 @@
     </row>
     <row r="626">
       <c r="A626" t="n">
-        <v>6628</v>
+        <v>6703</v>
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
@@ -68020,12 +68016,12 @@
       </c>
       <c r="D626" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E626" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F626" t="inlineStr">
@@ -68060,7 +68056,7 @@
         </is>
       </c>
       <c r="O626" t="n">
-        <v>16960072</v>
+        <v>17941215</v>
       </c>
       <c r="P626" t="inlineStr">
         <is>
@@ -68078,7 +68074,7 @@
       </c>
       <c r="T626" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
+          <t>LIMA MOTA</t>
         </is>
       </c>
       <c r="U626" t="inlineStr">
@@ -68107,11 +68103,11 @@
     </row>
     <row r="627">
       <c r="A627" t="n">
-        <v>6703</v>
+        <v>6704</v>
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
+          <t>TECNO COM INFORMATICA LTDA</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
@@ -68121,7 +68117,7 @@
       </c>
       <c r="D627" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E627" t="inlineStr">
@@ -68161,7 +68157,7 @@
         </is>
       </c>
       <c r="O627" t="n">
-        <v>17941215</v>
+        <v>17952442</v>
       </c>
       <c r="P627" t="inlineStr">
         <is>
@@ -68179,7 +68175,7 @@
       </c>
       <c r="T627" t="inlineStr">
         <is>
-          <t>LIMA MOTA</t>
+          <t>TECNO COM</t>
         </is>
       </c>
       <c r="U627" t="inlineStr">
@@ -68208,11 +68204,11 @@
     </row>
     <row r="628">
       <c r="A628" t="n">
-        <v>6704</v>
+        <v>6705</v>
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>TECNO COM INFORMATICA LTDA</t>
+          <t>NARCIZO ALVES CORDEIRO</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
@@ -68222,7 +68218,7 @@
       </c>
       <c r="D628" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E628" t="inlineStr">
@@ -68262,7 +68258,7 @@
         </is>
       </c>
       <c r="O628" t="n">
-        <v>17952442</v>
+        <v>17952622</v>
       </c>
       <c r="P628" t="inlineStr">
         <is>
@@ -68309,11 +68305,11 @@
     </row>
     <row r="629">
       <c r="A629" t="n">
-        <v>6705</v>
+        <v>6779</v>
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>NARCIZO ALVES CORDEIRO</t>
+          <t>CORDEIRO E CIA LTDA</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
@@ -68363,7 +68359,7 @@
         </is>
       </c>
       <c r="O629" t="n">
-        <v>17952622</v>
+        <v>18056799</v>
       </c>
       <c r="P629" t="inlineStr">
         <is>
@@ -68384,11 +68380,7 @@
           <t>TECNO COM</t>
         </is>
       </c>
-      <c r="U629" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+      <c r="U629" t="inlineStr"/>
       <c r="V629" t="inlineStr"/>
       <c r="W629" t="inlineStr"/>
       <c r="X629" t="inlineStr"/>
@@ -68410,11 +68402,11 @@
     </row>
     <row r="630">
       <c r="A630" t="n">
-        <v>6779</v>
+        <v>6885</v>
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>CORDEIRO E CIA LTDA</t>
+          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
@@ -68464,7 +68456,7 @@
         </is>
       </c>
       <c r="O630" t="n">
-        <v>18056799</v>
+        <v>18128837</v>
       </c>
       <c r="P630" t="inlineStr">
         <is>
@@ -68482,7 +68474,7 @@
       </c>
       <c r="T630" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U630" t="inlineStr"/>
@@ -68507,11 +68499,11 @@
     </row>
     <row r="631">
       <c r="A631" t="n">
-        <v>6885</v>
+        <v>6945</v>
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
+          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
@@ -68526,7 +68518,7 @@
       </c>
       <c r="E631" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F631" t="inlineStr">
@@ -68561,7 +68553,7 @@
         </is>
       </c>
       <c r="O631" t="n">
-        <v>18128837</v>
+        <v>18164549</v>
       </c>
       <c r="P631" t="inlineStr">
         <is>
@@ -68579,7 +68571,7 @@
       </c>
       <c r="T631" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>BRASIL DISTRIBUIDORA</t>
         </is>
       </c>
       <c r="U631" t="inlineStr"/>
@@ -68604,11 +68596,11 @@
     </row>
     <row r="632">
       <c r="A632" t="n">
-        <v>6945</v>
+        <v>6949</v>
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
+          <t>TEC GRUA LOCAÇÃO E COMERCIO DE EQUIPAMENTOS PARA CONSTRUÇÃO LTDA</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
@@ -68618,17 +68610,17 @@
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E632" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F632" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Reynaldo Santos</t>
         </is>
       </c>
       <c r="G632" t="n">
@@ -68658,7 +68650,7 @@
         </is>
       </c>
       <c r="O632" t="n">
-        <v>18164549</v>
+        <v>18178185</v>
       </c>
       <c r="P632" t="inlineStr">
         <is>
@@ -68676,7 +68668,7 @@
       </c>
       <c r="T632" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA</t>
+          <t>TEC GRUA</t>
         </is>
       </c>
       <c r="U632" t="inlineStr"/>
@@ -68701,11 +68693,11 @@
     </row>
     <row r="633">
       <c r="A633" t="n">
-        <v>6949</v>
+        <v>6962</v>
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>TEC GRUA LOCAÇÃO E COMERCIO DE EQUIPAMENTOS PARA CONSTRUÇÃO LTDA</t>
+          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
@@ -68755,7 +68747,7 @@
         </is>
       </c>
       <c r="O633" t="n">
-        <v>18178185</v>
+        <v>18188772</v>
       </c>
       <c r="P633" t="inlineStr">
         <is>
@@ -68773,7 +68765,7 @@
       </c>
       <c r="T633" t="inlineStr">
         <is>
-          <t>TEC GRUA</t>
+          <t>PROMOTORAS GYN</t>
         </is>
       </c>
       <c r="U633" t="inlineStr"/>
@@ -68798,11 +68790,11 @@
     </row>
     <row r="634">
       <c r="A634" t="n">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
+          <t>PROMOTORAS GYN LTDA</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
@@ -68852,7 +68844,7 @@
         </is>
       </c>
       <c r="O634" t="n">
-        <v>18188772</v>
+        <v>18188678</v>
       </c>
       <c r="P634" t="inlineStr">
         <is>
@@ -68895,11 +68887,11 @@
     </row>
     <row r="635">
       <c r="A635" t="n">
-        <v>6963</v>
+        <v>6224</v>
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
@@ -68919,11 +68911,11 @@
       </c>
       <c r="F635" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G635" t="n">
-        <v>9086</v>
+        <v>940</v>
       </c>
       <c r="H635" t="n">
         <v>0</v>
@@ -68935,7 +68927,7 @@
       </c>
       <c r="J635" t="inlineStr">
         <is>
-          <t>Consulta Cx Postal - 2º Quinzena</t>
+          <t>DEC - Consulta 2º Quinzena</t>
         </is>
       </c>
       <c r="K635" t="inlineStr"/>
@@ -68949,7 +68941,7 @@
         </is>
       </c>
       <c r="O635" t="n">
-        <v>18188678</v>
+        <v>17688584</v>
       </c>
       <c r="P635" t="inlineStr">
         <is>
@@ -68967,10 +68959,14 @@
       </c>
       <c r="T635" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN</t>
-        </is>
-      </c>
-      <c r="U635" t="inlineStr"/>
+          <t>SUPER MAIS DO GOIÁS</t>
+        </is>
+      </c>
+      <c r="U635" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V635" t="inlineStr"/>
       <c r="W635" t="inlineStr"/>
       <c r="X635" t="inlineStr"/>
@@ -68992,11 +68988,11 @@
     </row>
     <row r="636">
       <c r="A636" t="n">
-        <v>6224</v>
+        <v>6548</v>
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>GOIAS SILAGEM LTDA</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
@@ -69016,7 +69012,7 @@
       </c>
       <c r="F636" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G636" t="n">
@@ -69046,7 +69042,7 @@
         </is>
       </c>
       <c r="O636" t="n">
-        <v>17688584</v>
+        <v>17222364</v>
       </c>
       <c r="P636" t="inlineStr">
         <is>
@@ -69064,7 +69060,7 @@
       </c>
       <c r="T636" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>GOIAS SILAGEM</t>
         </is>
       </c>
       <c r="U636" t="inlineStr">
@@ -69093,11 +69089,11 @@
     </row>
     <row r="637">
       <c r="A637" t="n">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM LTDA</t>
+          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
@@ -69112,7 +69108,7 @@
       </c>
       <c r="E637" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F637" t="inlineStr">
@@ -69147,7 +69143,7 @@
         </is>
       </c>
       <c r="O637" t="n">
-        <v>17222364</v>
+        <v>17042219</v>
       </c>
       <c r="P637" t="inlineStr">
         <is>
@@ -69165,7 +69161,7 @@
       </c>
       <c r="T637" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM</t>
+          <t xml:space="preserve">GTG </t>
         </is>
       </c>
       <c r="U637" t="inlineStr">
@@ -69194,11 +69190,11 @@
     </row>
     <row r="638">
       <c r="A638" t="n">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
@@ -69208,7 +69204,7 @@
       </c>
       <c r="D638" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E638" t="inlineStr">
@@ -69248,7 +69244,7 @@
         </is>
       </c>
       <c r="O638" t="n">
-        <v>17042219</v>
+        <v>16959924</v>
       </c>
       <c r="P638" t="inlineStr">
         <is>
@@ -69295,11 +69291,11 @@
     </row>
     <row r="639">
       <c r="A639" t="n">
-        <v>6628</v>
+        <v>6703</v>
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
@@ -69309,12 +69305,12 @@
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F639" t="inlineStr">
@@ -69349,7 +69345,7 @@
         </is>
       </c>
       <c r="O639" t="n">
-        <v>16959924</v>
+        <v>17941110</v>
       </c>
       <c r="P639" t="inlineStr">
         <is>
@@ -69367,7 +69363,7 @@
       </c>
       <c r="T639" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
+          <t>LIMA MOTA</t>
         </is>
       </c>
       <c r="U639" t="inlineStr">
@@ -69396,11 +69392,11 @@
     </row>
     <row r="640">
       <c r="A640" t="n">
-        <v>6703</v>
+        <v>6704</v>
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
+          <t>TECNO COM INFORMATICA LTDA</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
@@ -69410,7 +69406,7 @@
       </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E640" t="inlineStr">
@@ -69450,7 +69446,7 @@
         </is>
       </c>
       <c r="O640" t="n">
-        <v>17941110</v>
+        <v>17952290</v>
       </c>
       <c r="P640" t="inlineStr">
         <is>
@@ -69468,7 +69464,7 @@
       </c>
       <c r="T640" t="inlineStr">
         <is>
-          <t>LIMA MOTA</t>
+          <t>TECNO COM</t>
         </is>
       </c>
       <c r="U640" t="inlineStr">
@@ -69497,11 +69493,11 @@
     </row>
     <row r="641">
       <c r="A641" t="n">
-        <v>6704</v>
+        <v>6705</v>
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>TECNO COM INFORMATICA LTDA</t>
+          <t>NARCIZO ALVES CORDEIRO</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
@@ -69511,7 +69507,7 @@
       </c>
       <c r="D641" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E641" t="inlineStr">
@@ -69551,7 +69547,7 @@
         </is>
       </c>
       <c r="O641" t="n">
-        <v>17952290</v>
+        <v>17952489</v>
       </c>
       <c r="P641" t="inlineStr">
         <is>
@@ -69598,11 +69594,11 @@
     </row>
     <row r="642">
       <c r="A642" t="n">
-        <v>6705</v>
+        <v>6779</v>
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>NARCIZO ALVES CORDEIRO</t>
+          <t>CORDEIRO E CIA LTDA</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
@@ -69652,7 +69648,7 @@
         </is>
       </c>
       <c r="O642" t="n">
-        <v>17952489</v>
+        <v>18056683</v>
       </c>
       <c r="P642" t="inlineStr">
         <is>
@@ -69673,11 +69669,7 @@
           <t>TECNO COM</t>
         </is>
       </c>
-      <c r="U642" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+      <c r="U642" t="inlineStr"/>
       <c r="V642" t="inlineStr"/>
       <c r="W642" t="inlineStr"/>
       <c r="X642" t="inlineStr"/>
@@ -69699,11 +69691,11 @@
     </row>
     <row r="643">
       <c r="A643" t="n">
-        <v>6779</v>
+        <v>6885</v>
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>CORDEIRO E CIA LTDA</t>
+          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
@@ -69753,7 +69745,7 @@
         </is>
       </c>
       <c r="O643" t="n">
-        <v>18056683</v>
+        <v>18128612</v>
       </c>
       <c r="P643" t="inlineStr">
         <is>
@@ -69771,7 +69763,7 @@
       </c>
       <c r="T643" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U643" t="inlineStr"/>
@@ -69796,11 +69788,11 @@
     </row>
     <row r="644">
       <c r="A644" t="n">
-        <v>6885</v>
+        <v>6945</v>
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
+          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
@@ -69815,7 +69807,7 @@
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F644" t="inlineStr">
@@ -69850,7 +69842,7 @@
         </is>
       </c>
       <c r="O644" t="n">
-        <v>18128612</v>
+        <v>18164471</v>
       </c>
       <c r="P644" t="inlineStr">
         <is>
@@ -69868,7 +69860,7 @@
       </c>
       <c r="T644" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>BRASIL DISTRIBUIDORA</t>
         </is>
       </c>
       <c r="U644" t="inlineStr"/>
@@ -69893,11 +69885,11 @@
     </row>
     <row r="645">
       <c r="A645" t="n">
-        <v>6945</v>
+        <v>6949</v>
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
+          <t>TEC GRUA LOCAÇÃO E COMERCIO DE EQUIPAMENTOS PARA CONSTRUÇÃO LTDA</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
@@ -69907,17 +69899,17 @@
       </c>
       <c r="D645" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F645" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Reynaldo Santos</t>
         </is>
       </c>
       <c r="G645" t="n">
@@ -69947,7 +69939,7 @@
         </is>
       </c>
       <c r="O645" t="n">
-        <v>18164471</v>
+        <v>18178118</v>
       </c>
       <c r="P645" t="inlineStr">
         <is>
@@ -69965,7 +69957,7 @@
       </c>
       <c r="T645" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA</t>
+          <t>TEC GRUA</t>
         </is>
       </c>
       <c r="U645" t="inlineStr"/>
@@ -69990,11 +69982,11 @@
     </row>
     <row r="646">
       <c r="A646" t="n">
-        <v>6949</v>
+        <v>6962</v>
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>TEC GRUA LOCAÇÃO E COMERCIO DE EQUIPAMENTOS PARA CONSTRUÇÃO LTDA</t>
+          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
@@ -70044,7 +70036,7 @@
         </is>
       </c>
       <c r="O646" t="n">
-        <v>18178118</v>
+        <v>18188701</v>
       </c>
       <c r="P646" t="inlineStr">
         <is>
@@ -70062,7 +70054,7 @@
       </c>
       <c r="T646" t="inlineStr">
         <is>
-          <t>TEC GRUA</t>
+          <t>PROMOTORAS GYN</t>
         </is>
       </c>
       <c r="U646" t="inlineStr"/>
@@ -70087,11 +70079,11 @@
     </row>
     <row r="647">
       <c r="A647" t="n">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
+          <t>PROMOTORAS GYN LTDA</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
@@ -70141,7 +70133,7 @@
         </is>
       </c>
       <c r="O647" t="n">
-        <v>18188701</v>
+        <v>18188607</v>
       </c>
       <c r="P647" t="inlineStr">
         <is>
@@ -70184,11 +70176,11 @@
     </row>
     <row r="648">
       <c r="A648" t="n">
-        <v>6963</v>
+        <v>5417</v>
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN LTDA</t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
@@ -70208,11 +70200,11 @@
       </c>
       <c r="F648" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G648" t="n">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="H648" t="n">
         <v>0</v>
@@ -70224,21 +70216,21 @@
       </c>
       <c r="J648" t="inlineStr">
         <is>
-          <t>DEC - Consulta 2º Quinzena</t>
+          <t>Inclusão de Ata de Reunião</t>
         </is>
       </c>
       <c r="K648" t="inlineStr"/>
       <c r="L648" s="1" t="n">
-        <v>46220</v>
+        <v>46233</v>
       </c>
       <c r="M648" t="inlineStr"/>
       <c r="N648" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
       <c r="O648" t="n">
-        <v>18188607</v>
+        <v>17398857</v>
       </c>
       <c r="P648" t="inlineStr">
         <is>
@@ -70252,14 +70244,18 @@
       </c>
       <c r="R648" t="inlineStr"/>
       <c r="S648" t="n">
-        <v>-3</v>
+        <v>-16</v>
       </c>
       <c r="T648" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN</t>
-        </is>
-      </c>
-      <c r="U648" t="inlineStr"/>
+          <t>NOSSO NOVO SUPERMERCADO</t>
+        </is>
+      </c>
+      <c r="U648" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V648" t="inlineStr"/>
       <c r="W648" t="inlineStr"/>
       <c r="X648" t="inlineStr"/>
@@ -70274,18 +70270,18 @@
       <c r="AE648" t="inlineStr"/>
       <c r="AF648" t="inlineStr">
         <is>
-          <t>Obrigação Acessória</t>
+          <t>Tarefa</t>
         </is>
       </c>
       <c r="AG648" t="inlineStr"/>
     </row>
     <row r="649">
       <c r="A649" t="n">
-        <v>5417</v>
+        <v>5617</v>
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
@@ -70305,7 +70301,7 @@
       </c>
       <c r="F649" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G649" t="n">
@@ -70335,7 +70331,7 @@
         </is>
       </c>
       <c r="O649" t="n">
-        <v>17398857</v>
+        <v>17407517</v>
       </c>
       <c r="P649" t="inlineStr">
         <is>
@@ -70353,7 +70349,7 @@
       </c>
       <c r="T649" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U649" t="inlineStr">
@@ -70382,11 +70378,11 @@
     </row>
     <row r="650">
       <c r="A650" t="n">
-        <v>5617</v>
+        <v>6224</v>
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
@@ -70406,7 +70402,7 @@
       </c>
       <c r="F650" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G650" t="n">
@@ -70436,7 +70432,7 @@
         </is>
       </c>
       <c r="O650" t="n">
-        <v>17407517</v>
+        <v>17688603</v>
       </c>
       <c r="P650" t="inlineStr">
         <is>
@@ -70483,11 +70479,11 @@
     </row>
     <row r="651">
       <c r="A651" t="n">
-        <v>6224</v>
+        <v>6278</v>
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>EMPORIO DOS FRIOS LTDA</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
@@ -70497,7 +70493,7 @@
       </c>
       <c r="D651" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Real - Anual</t>
         </is>
       </c>
       <c r="E651" t="inlineStr">
@@ -70507,7 +70503,7 @@
       </c>
       <c r="F651" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G651" t="n">
@@ -70537,7 +70533,7 @@
         </is>
       </c>
       <c r="O651" t="n">
-        <v>17688603</v>
+        <v>17539698</v>
       </c>
       <c r="P651" t="inlineStr">
         <is>
@@ -70555,7 +70551,7 @@
       </c>
       <c r="T651" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U651" t="inlineStr">
@@ -70584,11 +70580,11 @@
     </row>
     <row r="652">
       <c r="A652" t="n">
-        <v>6278</v>
+        <v>6279</v>
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS LTDA</t>
+          <t>DIENNYFER DA S PEREIRA</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
@@ -70598,7 +70594,7 @@
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>Federal - Lucro Real - Anual</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E652" t="inlineStr">
@@ -70608,7 +70604,7 @@
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G652" t="n">
@@ -70638,7 +70634,7 @@
         </is>
       </c>
       <c r="O652" t="n">
-        <v>17539698</v>
+        <v>17645913</v>
       </c>
       <c r="P652" t="inlineStr">
         <is>
@@ -70685,11 +70681,11 @@
     </row>
     <row r="653">
       <c r="A653" t="n">
-        <v>6279</v>
+        <v>6486</v>
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>DIENNYFER DA S PEREIRA</t>
+          <t>PC GAMER GOIANIA LTDA</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
@@ -70699,7 +70695,7 @@
       </c>
       <c r="D653" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E653" t="inlineStr">
@@ -70709,7 +70705,7 @@
       </c>
       <c r="F653" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G653" t="n">
@@ -70739,7 +70735,7 @@
         </is>
       </c>
       <c r="O653" t="n">
-        <v>17645913</v>
+        <v>16975888</v>
       </c>
       <c r="P653" t="inlineStr">
         <is>
@@ -70757,7 +70753,7 @@
       </c>
       <c r="T653" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>PC GAMER</t>
         </is>
       </c>
       <c r="U653" t="inlineStr">
@@ -70786,11 +70782,11 @@
     </row>
     <row r="654">
       <c r="A654" t="n">
-        <v>6486</v>
+        <v>6703</v>
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>PC GAMER GOIANIA LTDA</t>
+          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
@@ -70800,7 +70796,7 @@
       </c>
       <c r="D654" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E654" t="inlineStr">
@@ -70840,7 +70836,7 @@
         </is>
       </c>
       <c r="O654" t="n">
-        <v>16975888</v>
+        <v>17941120</v>
       </c>
       <c r="P654" t="inlineStr">
         <is>
@@ -70858,7 +70854,7 @@
       </c>
       <c r="T654" t="inlineStr">
         <is>
-          <t>PC GAMER</t>
+          <t>LIMA MOTA</t>
         </is>
       </c>
       <c r="U654" t="inlineStr">
@@ -70887,11 +70883,11 @@
     </row>
     <row r="655">
       <c r="A655" t="n">
-        <v>6703</v>
+        <v>6704</v>
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
+          <t>TECNO COM INFORMATICA LTDA</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
@@ -70901,7 +70897,7 @@
       </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E655" t="inlineStr">
@@ -70941,7 +70937,7 @@
         </is>
       </c>
       <c r="O655" t="n">
-        <v>17941120</v>
+        <v>17952312</v>
       </c>
       <c r="P655" t="inlineStr">
         <is>
@@ -70959,7 +70955,7 @@
       </c>
       <c r="T655" t="inlineStr">
         <is>
-          <t>LIMA MOTA</t>
+          <t>TECNO COM</t>
         </is>
       </c>
       <c r="U655" t="inlineStr">
@@ -70988,11 +70984,11 @@
     </row>
     <row r="656">
       <c r="A656" t="n">
-        <v>6704</v>
+        <v>6705</v>
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>TECNO COM INFORMATICA LTDA</t>
+          <t>NARCIZO ALVES CORDEIRO</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
@@ -71002,7 +70998,7 @@
       </c>
       <c r="D656" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E656" t="inlineStr">
@@ -71042,7 +71038,7 @@
         </is>
       </c>
       <c r="O656" t="n">
-        <v>17952312</v>
+        <v>17952511</v>
       </c>
       <c r="P656" t="inlineStr">
         <is>
@@ -71089,11 +71085,11 @@
     </row>
     <row r="657">
       <c r="A657" t="n">
-        <v>6705</v>
+        <v>6885</v>
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>NARCIZO ALVES CORDEIRO</t>
+          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
@@ -71143,7 +71139,7 @@
         </is>
       </c>
       <c r="O657" t="n">
-        <v>17952511</v>
+        <v>18128630</v>
       </c>
       <c r="P657" t="inlineStr">
         <is>
@@ -71161,14 +71157,10 @@
       </c>
       <c r="T657" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
-        </is>
-      </c>
-      <c r="U657" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>EMPORIO DOS FRIOS</t>
+        </is>
+      </c>
+      <c r="U657" t="inlineStr"/>
       <c r="V657" t="inlineStr"/>
       <c r="W657" t="inlineStr"/>
       <c r="X657" t="inlineStr"/>
@@ -71190,11 +71182,11 @@
     </row>
     <row r="658">
       <c r="A658" t="n">
-        <v>6885</v>
+        <v>6962</v>
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
+          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
@@ -71204,7 +71196,7 @@
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E658" t="inlineStr">
@@ -71214,7 +71206,7 @@
       </c>
       <c r="F658" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Reynaldo Santos</t>
         </is>
       </c>
       <c r="G658" t="n">
@@ -71244,7 +71236,7 @@
         </is>
       </c>
       <c r="O658" t="n">
-        <v>18128630</v>
+        <v>18188708</v>
       </c>
       <c r="P658" t="inlineStr">
         <is>
@@ -71262,7 +71254,7 @@
       </c>
       <c r="T658" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>PROMOTORAS GYN</t>
         </is>
       </c>
       <c r="U658" t="inlineStr"/>
@@ -71287,11 +71279,11 @@
     </row>
     <row r="659">
       <c r="A659" t="n">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
+          <t>PROMOTORAS GYN LTDA</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
@@ -71341,7 +71333,7 @@
         </is>
       </c>
       <c r="O659" t="n">
-        <v>18188708</v>
+        <v>18188614</v>
       </c>
       <c r="P659" t="inlineStr">
         <is>
@@ -71384,11 +71376,11 @@
     </row>
     <row r="660">
       <c r="A660" t="n">
-        <v>6963</v>
+        <v>5417</v>
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN LTDA</t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
@@ -71408,41 +71400,41 @@
       </c>
       <c r="F660" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G660" t="n">
-        <v>943</v>
+        <v>9088</v>
       </c>
       <c r="H660" t="n">
         <v>0</v>
       </c>
       <c r="I660" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="J660" t="inlineStr">
         <is>
-          <t>Inclusão de Ata de Reunião</t>
+          <t>Conferência Consulta Cx Postal - 2º Quinzena</t>
         </is>
       </c>
       <c r="K660" t="inlineStr"/>
       <c r="L660" s="1" t="n">
-        <v>46233</v>
+        <v>46220</v>
       </c>
       <c r="M660" t="inlineStr"/>
       <c r="N660" t="inlineStr">
         <is>
-          <t>06/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
       <c r="O660" t="n">
-        <v>18188614</v>
+        <v>17399381</v>
       </c>
       <c r="P660" t="inlineStr">
         <is>
-          <t>Victoria Virgens</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="Q660" t="inlineStr">
@@ -71452,14 +71444,18 @@
       </c>
       <c r="R660" t="inlineStr"/>
       <c r="S660" t="n">
-        <v>-16</v>
+        <v>-3</v>
       </c>
       <c r="T660" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN</t>
-        </is>
-      </c>
-      <c r="U660" t="inlineStr"/>
+          <t>NOSSO NOVO SUPERMERCADO</t>
+        </is>
+      </c>
+      <c r="U660" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V660" t="inlineStr"/>
       <c r="W660" t="inlineStr"/>
       <c r="X660" t="inlineStr"/>
@@ -71474,18 +71470,18 @@
       <c r="AE660" t="inlineStr"/>
       <c r="AF660" t="inlineStr">
         <is>
-          <t>Tarefa</t>
+          <t>Obrigação Acessória</t>
         </is>
       </c>
       <c r="AG660" t="inlineStr"/>
     </row>
     <row r="661">
       <c r="A661" t="n">
-        <v>5417</v>
+        <v>5617</v>
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
@@ -71505,7 +71501,7 @@
       </c>
       <c r="F661" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G661" t="n">
@@ -71535,7 +71531,7 @@
         </is>
       </c>
       <c r="O661" t="n">
-        <v>17399381</v>
+        <v>17407902</v>
       </c>
       <c r="P661" t="inlineStr">
         <is>
@@ -71553,7 +71549,7 @@
       </c>
       <c r="T661" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U661" t="inlineStr">
@@ -71582,11 +71578,11 @@
     </row>
     <row r="662">
       <c r="A662" t="n">
-        <v>5617</v>
+        <v>6224</v>
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
@@ -71606,7 +71602,7 @@
       </c>
       <c r="F662" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G662" t="n">
@@ -71636,11 +71632,11 @@
         </is>
       </c>
       <c r="O662" t="n">
-        <v>17407902</v>
+        <v>17689020</v>
       </c>
       <c r="P662" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="Q662" t="inlineStr">
@@ -71683,11 +71679,11 @@
     </row>
     <row r="663">
       <c r="A663" t="n">
-        <v>6224</v>
+        <v>6278</v>
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>EMPORIO DOS FRIOS LTDA</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
@@ -71697,7 +71693,7 @@
       </c>
       <c r="D663" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Real - Anual</t>
         </is>
       </c>
       <c r="E663" t="inlineStr">
@@ -71707,7 +71703,7 @@
       </c>
       <c r="F663" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G663" t="n">
@@ -71737,11 +71733,11 @@
         </is>
       </c>
       <c r="O663" t="n">
-        <v>17689020</v>
+        <v>17539878</v>
       </c>
       <c r="P663" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="Q663" t="inlineStr">
@@ -71755,7 +71751,7 @@
       </c>
       <c r="T663" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U663" t="inlineStr">
@@ -71784,11 +71780,11 @@
     </row>
     <row r="664">
       <c r="A664" t="n">
-        <v>6278</v>
+        <v>6279</v>
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS LTDA</t>
+          <t>DIENNYFER DA S PEREIRA</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
@@ -71798,7 +71794,7 @@
       </c>
       <c r="D664" t="inlineStr">
         <is>
-          <t>Federal - Lucro Real - Anual</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E664" t="inlineStr">
@@ -71808,7 +71804,7 @@
       </c>
       <c r="F664" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G664" t="n">
@@ -71838,7 +71834,7 @@
         </is>
       </c>
       <c r="O664" t="n">
-        <v>17539878</v>
+        <v>17646155</v>
       </c>
       <c r="P664" t="inlineStr">
         <is>
@@ -71885,11 +71881,11 @@
     </row>
     <row r="665">
       <c r="A665" t="n">
-        <v>6279</v>
+        <v>6404</v>
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>DIENNYFER DA S PEREIRA</t>
+          <t>SOLAR INVESTIMENTOS LTDA</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
@@ -71909,7 +71905,7 @@
       </c>
       <c r="F665" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G665" t="n">
@@ -71939,11 +71935,11 @@
         </is>
       </c>
       <c r="O665" t="n">
-        <v>17646155</v>
+        <v>16962398</v>
       </c>
       <c r="P665" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="Q665" t="inlineStr">
@@ -71957,7 +71953,7 @@
       </c>
       <c r="T665" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>SOLAR INVESTIMENTOS</t>
         </is>
       </c>
       <c r="U665" t="inlineStr">
@@ -71986,11 +71982,11 @@
     </row>
     <row r="666">
       <c r="A666" t="n">
-        <v>6404</v>
+        <v>6486</v>
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS LTDA</t>
+          <t>PC GAMER GOIANIA LTDA</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
@@ -72000,7 +71996,7 @@
       </c>
       <c r="D666" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E666" t="inlineStr">
@@ -72040,7 +72036,7 @@
         </is>
       </c>
       <c r="O666" t="n">
-        <v>16962398</v>
+        <v>16976288</v>
       </c>
       <c r="P666" t="inlineStr">
         <is>
@@ -72058,7 +72054,7 @@
       </c>
       <c r="T666" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS</t>
+          <t>PC GAMER</t>
         </is>
       </c>
       <c r="U666" t="inlineStr">
@@ -72087,11 +72083,11 @@
     </row>
     <row r="667">
       <c r="A667" t="n">
-        <v>6486</v>
+        <v>6548</v>
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>PC GAMER GOIANIA LTDA</t>
+          <t>GOIAS SILAGEM LTDA</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
@@ -72141,11 +72137,11 @@
         </is>
       </c>
       <c r="O667" t="n">
-        <v>16976288</v>
+        <v>17222895</v>
       </c>
       <c r="P667" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="Q667" t="inlineStr">
@@ -72159,7 +72155,7 @@
       </c>
       <c r="T667" t="inlineStr">
         <is>
-          <t>PC GAMER</t>
+          <t>GOIAS SILAGEM</t>
         </is>
       </c>
       <c r="U667" t="inlineStr">
@@ -72188,11 +72184,11 @@
     </row>
     <row r="668">
       <c r="A668" t="n">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM LTDA</t>
+          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
@@ -72207,7 +72203,7 @@
       </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F668" t="inlineStr">
@@ -72242,7 +72238,7 @@
         </is>
       </c>
       <c r="O668" t="n">
-        <v>17222895</v>
+        <v>17042622</v>
       </c>
       <c r="P668" t="inlineStr">
         <is>
@@ -72260,7 +72256,7 @@
       </c>
       <c r="T668" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM</t>
+          <t xml:space="preserve">GTG </t>
         </is>
       </c>
       <c r="U668" t="inlineStr">
@@ -72289,11 +72285,11 @@
     </row>
     <row r="669">
       <c r="A669" t="n">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
@@ -72303,7 +72299,7 @@
       </c>
       <c r="D669" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E669" t="inlineStr">
@@ -72343,7 +72339,7 @@
         </is>
       </c>
       <c r="O669" t="n">
-        <v>17042622</v>
+        <v>16960096</v>
       </c>
       <c r="P669" t="inlineStr">
         <is>
@@ -72390,11 +72386,11 @@
     </row>
     <row r="670">
       <c r="A670" t="n">
-        <v>6628</v>
+        <v>6703</v>
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
@@ -72404,12 +72400,12 @@
       </c>
       <c r="D670" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F670" t="inlineStr">
@@ -72444,7 +72440,7 @@
         </is>
       </c>
       <c r="O670" t="n">
-        <v>16960096</v>
+        <v>17941235</v>
       </c>
       <c r="P670" t="inlineStr">
         <is>
@@ -72462,7 +72458,7 @@
       </c>
       <c r="T670" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
+          <t>LIMA MOTA</t>
         </is>
       </c>
       <c r="U670" t="inlineStr">
@@ -72491,11 +72487,11 @@
     </row>
     <row r="671">
       <c r="A671" t="n">
-        <v>6703</v>
+        <v>6704</v>
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
+          <t>TECNO COM INFORMATICA LTDA</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
@@ -72505,7 +72501,7 @@
       </c>
       <c r="D671" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E671" t="inlineStr">
@@ -72545,7 +72541,7 @@
         </is>
       </c>
       <c r="O671" t="n">
-        <v>17941235</v>
+        <v>17952464</v>
       </c>
       <c r="P671" t="inlineStr">
         <is>
@@ -72563,7 +72559,7 @@
       </c>
       <c r="T671" t="inlineStr">
         <is>
-          <t>LIMA MOTA</t>
+          <t>TECNO COM</t>
         </is>
       </c>
       <c r="U671" t="inlineStr">
@@ -72592,11 +72588,11 @@
     </row>
     <row r="672">
       <c r="A672" t="n">
-        <v>6704</v>
+        <v>6705</v>
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>TECNO COM INFORMATICA LTDA</t>
+          <t>NARCIZO ALVES CORDEIRO</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
@@ -72606,7 +72602,7 @@
       </c>
       <c r="D672" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E672" t="inlineStr">
@@ -72646,7 +72642,7 @@
         </is>
       </c>
       <c r="O672" t="n">
-        <v>17952464</v>
+        <v>17952644</v>
       </c>
       <c r="P672" t="inlineStr">
         <is>
@@ -72693,11 +72689,11 @@
     </row>
     <row r="673">
       <c r="A673" t="n">
-        <v>6705</v>
+        <v>6779</v>
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>NARCIZO ALVES CORDEIRO</t>
+          <t>CORDEIRO E CIA LTDA</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
@@ -72747,7 +72743,7 @@
         </is>
       </c>
       <c r="O673" t="n">
-        <v>17952644</v>
+        <v>18056819</v>
       </c>
       <c r="P673" t="inlineStr">
         <is>
@@ -72768,11 +72764,7 @@
           <t>TECNO COM</t>
         </is>
       </c>
-      <c r="U673" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+      <c r="U673" t="inlineStr"/>
       <c r="V673" t="inlineStr"/>
       <c r="W673" t="inlineStr"/>
       <c r="X673" t="inlineStr"/>
@@ -72794,11 +72786,11 @@
     </row>
     <row r="674">
       <c r="A674" t="n">
-        <v>6779</v>
+        <v>6885</v>
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>CORDEIRO E CIA LTDA</t>
+          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
@@ -72848,7 +72840,7 @@
         </is>
       </c>
       <c r="O674" t="n">
-        <v>18056819</v>
+        <v>18128855</v>
       </c>
       <c r="P674" t="inlineStr">
         <is>
@@ -72866,7 +72858,7 @@
       </c>
       <c r="T674" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U674" t="inlineStr"/>
@@ -72891,11 +72883,11 @@
     </row>
     <row r="675">
       <c r="A675" t="n">
-        <v>6885</v>
+        <v>6945</v>
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
+          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
@@ -72910,7 +72902,7 @@
       </c>
       <c r="E675" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F675" t="inlineStr">
@@ -72945,11 +72937,11 @@
         </is>
       </c>
       <c r="O675" t="n">
-        <v>18128855</v>
+        <v>18164563</v>
       </c>
       <c r="P675" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="Q675" t="inlineStr">
@@ -72963,7 +72955,7 @@
       </c>
       <c r="T675" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>BRASIL DISTRIBUIDORA</t>
         </is>
       </c>
       <c r="U675" t="inlineStr"/>
@@ -72988,11 +72980,11 @@
     </row>
     <row r="676">
       <c r="A676" t="n">
-        <v>6945</v>
+        <v>6949</v>
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
+          <t>TEC GRUA LOCAÇÃO E COMERCIO DE EQUIPAMENTOS PARA CONSTRUÇÃO LTDA</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
@@ -73002,17 +72994,17 @@
       </c>
       <c r="D676" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F676" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Reynaldo Santos</t>
         </is>
       </c>
       <c r="G676" t="n">
@@ -73042,11 +73034,11 @@
         </is>
       </c>
       <c r="O676" t="n">
-        <v>18164563</v>
+        <v>18178197</v>
       </c>
       <c r="P676" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="Q676" t="inlineStr">
@@ -73060,7 +73052,7 @@
       </c>
       <c r="T676" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA</t>
+          <t>TEC GRUA</t>
         </is>
       </c>
       <c r="U676" t="inlineStr"/>
@@ -73085,11 +73077,11 @@
     </row>
     <row r="677">
       <c r="A677" t="n">
-        <v>6949</v>
+        <v>6962</v>
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>TEC GRUA LOCAÇÃO E COMERCIO DE EQUIPAMENTOS PARA CONSTRUÇÃO LTDA</t>
+          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
@@ -73139,11 +73131,11 @@
         </is>
       </c>
       <c r="O677" t="n">
-        <v>18178197</v>
+        <v>18188786</v>
       </c>
       <c r="P677" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="Q677" t="inlineStr">
@@ -73157,7 +73149,7 @@
       </c>
       <c r="T677" t="inlineStr">
         <is>
-          <t>TEC GRUA</t>
+          <t>PROMOTORAS GYN</t>
         </is>
       </c>
       <c r="U677" t="inlineStr"/>
@@ -73182,11 +73174,11 @@
     </row>
     <row r="678">
       <c r="A678" t="n">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
+          <t>PROMOTORAS GYN LTDA</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
@@ -73236,7 +73228,7 @@
         </is>
       </c>
       <c r="O678" t="n">
-        <v>18188786</v>
+        <v>18188692</v>
       </c>
       <c r="P678" t="inlineStr">
         <is>
@@ -73279,11 +73271,11 @@
     </row>
     <row r="679">
       <c r="A679" t="n">
-        <v>6963</v>
+        <v>6224</v>
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
@@ -73303,11 +73295,11 @@
       </c>
       <c r="F679" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G679" t="n">
-        <v>9088</v>
+        <v>6813</v>
       </c>
       <c r="H679" t="n">
         <v>0</v>
@@ -73319,7 +73311,7 @@
       </c>
       <c r="J679" t="inlineStr">
         <is>
-          <t>Conferência Consulta Cx Postal - 2º Quinzena</t>
+          <t>DEC - Conferência 2º Quinzena</t>
         </is>
       </c>
       <c r="K679" t="inlineStr"/>
@@ -73333,7 +73325,7 @@
         </is>
       </c>
       <c r="O679" t="n">
-        <v>18188692</v>
+        <v>17688928</v>
       </c>
       <c r="P679" t="inlineStr">
         <is>
@@ -73351,10 +73343,14 @@
       </c>
       <c r="T679" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN</t>
-        </is>
-      </c>
-      <c r="U679" t="inlineStr"/>
+          <t>SUPER MAIS DO GOIÁS</t>
+        </is>
+      </c>
+      <c r="U679" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V679" t="inlineStr"/>
       <c r="W679" t="inlineStr"/>
       <c r="X679" t="inlineStr"/>
@@ -73376,11 +73372,11 @@
     </row>
     <row r="680">
       <c r="A680" t="n">
-        <v>6224</v>
+        <v>6548</v>
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>GOIAS SILAGEM LTDA</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
@@ -73400,7 +73396,7 @@
       </c>
       <c r="F680" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G680" t="n">
@@ -73430,11 +73426,11 @@
         </is>
       </c>
       <c r="O680" t="n">
-        <v>17688928</v>
+        <v>17222761</v>
       </c>
       <c r="P680" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="Q680" t="inlineStr">
@@ -73448,7 +73444,7 @@
       </c>
       <c r="T680" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>GOIAS SILAGEM</t>
         </is>
       </c>
       <c r="U680" t="inlineStr">
@@ -73477,11 +73473,11 @@
     </row>
     <row r="681">
       <c r="A681" t="n">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM LTDA</t>
+          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
@@ -73496,7 +73492,7 @@
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F681" t="inlineStr">
@@ -73531,7 +73527,7 @@
         </is>
       </c>
       <c r="O681" t="n">
-        <v>17222761</v>
+        <v>17042467</v>
       </c>
       <c r="P681" t="inlineStr">
         <is>
@@ -73549,7 +73545,7 @@
       </c>
       <c r="T681" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM</t>
+          <t xml:space="preserve">GTG </t>
         </is>
       </c>
       <c r="U681" t="inlineStr">
@@ -73578,11 +73574,11 @@
     </row>
     <row r="682">
       <c r="A682" t="n">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
@@ -73592,7 +73588,7 @@
       </c>
       <c r="D682" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E682" t="inlineStr">
@@ -73632,7 +73628,7 @@
         </is>
       </c>
       <c r="O682" t="n">
-        <v>17042467</v>
+        <v>16960011</v>
       </c>
       <c r="P682" t="inlineStr">
         <is>
@@ -73679,11 +73675,11 @@
     </row>
     <row r="683">
       <c r="A683" t="n">
-        <v>6628</v>
+        <v>6703</v>
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
@@ -73693,12 +73689,12 @@
       </c>
       <c r="D683" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F683" t="inlineStr">
@@ -73733,7 +73729,7 @@
         </is>
       </c>
       <c r="O683" t="n">
-        <v>16960011</v>
+        <v>17941195</v>
       </c>
       <c r="P683" t="inlineStr">
         <is>
@@ -73751,7 +73747,7 @@
       </c>
       <c r="T683" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
+          <t>LIMA MOTA</t>
         </is>
       </c>
       <c r="U683" t="inlineStr">
@@ -73780,11 +73776,11 @@
     </row>
     <row r="684">
       <c r="A684" t="n">
-        <v>6703</v>
+        <v>6704</v>
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
+          <t>TECNO COM INFORMATICA LTDA</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
@@ -73794,7 +73790,7 @@
       </c>
       <c r="D684" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E684" t="inlineStr">
@@ -73834,7 +73830,7 @@
         </is>
       </c>
       <c r="O684" t="n">
-        <v>17941195</v>
+        <v>17952409</v>
       </c>
       <c r="P684" t="inlineStr">
         <is>
@@ -73852,7 +73848,7 @@
       </c>
       <c r="T684" t="inlineStr">
         <is>
-          <t>LIMA MOTA</t>
+          <t>TECNO COM</t>
         </is>
       </c>
       <c r="U684" t="inlineStr">
@@ -73881,11 +73877,11 @@
     </row>
     <row r="685">
       <c r="A685" t="n">
-        <v>6704</v>
+        <v>6705</v>
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>TECNO COM INFORMATICA LTDA</t>
+          <t>NARCIZO ALVES CORDEIRO</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
@@ -73895,7 +73891,7 @@
       </c>
       <c r="D685" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E685" t="inlineStr">
@@ -73935,7 +73931,7 @@
         </is>
       </c>
       <c r="O685" t="n">
-        <v>17952409</v>
+        <v>17952589</v>
       </c>
       <c r="P685" t="inlineStr">
         <is>
@@ -73982,11 +73978,11 @@
     </row>
     <row r="686">
       <c r="A686" t="n">
-        <v>6705</v>
+        <v>6779</v>
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>NARCIZO ALVES CORDEIRO</t>
+          <t>CORDEIRO E CIA LTDA</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
@@ -74036,7 +74032,7 @@
         </is>
       </c>
       <c r="O686" t="n">
-        <v>17952589</v>
+        <v>18056758</v>
       </c>
       <c r="P686" t="inlineStr">
         <is>
@@ -74057,11 +74053,7 @@
           <t>TECNO COM</t>
         </is>
       </c>
-      <c r="U686" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+      <c r="U686" t="inlineStr"/>
       <c r="V686" t="inlineStr"/>
       <c r="W686" t="inlineStr"/>
       <c r="X686" t="inlineStr"/>
@@ -74083,11 +74075,11 @@
     </row>
     <row r="687">
       <c r="A687" t="n">
-        <v>6779</v>
+        <v>6885</v>
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>CORDEIRO E CIA LTDA</t>
+          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
@@ -74137,7 +74129,7 @@
         </is>
       </c>
       <c r="O687" t="n">
-        <v>18056758</v>
+        <v>18128800</v>
       </c>
       <c r="P687" t="inlineStr">
         <is>
@@ -74155,7 +74147,7 @@
       </c>
       <c r="T687" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U687" t="inlineStr"/>
@@ -74180,11 +74172,11 @@
     </row>
     <row r="688">
       <c r="A688" t="n">
-        <v>6885</v>
+        <v>6945</v>
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
+          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
@@ -74199,7 +74191,7 @@
       </c>
       <c r="E688" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F688" t="inlineStr">
@@ -74234,11 +74226,11 @@
         </is>
       </c>
       <c r="O688" t="n">
-        <v>18128800</v>
+        <v>18164528</v>
       </c>
       <c r="P688" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="Q688" t="inlineStr">
@@ -74252,7 +74244,7 @@
       </c>
       <c r="T688" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>BRASIL DISTRIBUIDORA</t>
         </is>
       </c>
       <c r="U688" t="inlineStr"/>
@@ -74277,11 +74269,11 @@
     </row>
     <row r="689">
       <c r="A689" t="n">
-        <v>6945</v>
+        <v>6949</v>
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
+          <t>TEC GRUA LOCAÇÃO E COMERCIO DE EQUIPAMENTOS PARA CONSTRUÇÃO LTDA</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
@@ -74291,17 +74283,17 @@
       </c>
       <c r="D689" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F689" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Reynaldo Santos</t>
         </is>
       </c>
       <c r="G689" t="n">
@@ -74331,11 +74323,11 @@
         </is>
       </c>
       <c r="O689" t="n">
-        <v>18164528</v>
+        <v>18178167</v>
       </c>
       <c r="P689" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="Q689" t="inlineStr">
@@ -74349,7 +74341,7 @@
       </c>
       <c r="T689" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA</t>
+          <t>TEC GRUA</t>
         </is>
       </c>
       <c r="U689" t="inlineStr"/>
@@ -74374,11 +74366,11 @@
     </row>
     <row r="690">
       <c r="A690" t="n">
-        <v>6949</v>
+        <v>6962</v>
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>TEC GRUA LOCAÇÃO E COMERCIO DE EQUIPAMENTOS PARA CONSTRUÇÃO LTDA</t>
+          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
@@ -74428,11 +74420,11 @@
         </is>
       </c>
       <c r="O690" t="n">
-        <v>18178167</v>
+        <v>18188751</v>
       </c>
       <c r="P690" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="Q690" t="inlineStr">
@@ -74446,7 +74438,7 @@
       </c>
       <c r="T690" t="inlineStr">
         <is>
-          <t>TEC GRUA</t>
+          <t>PROMOTORAS GYN</t>
         </is>
       </c>
       <c r="U690" t="inlineStr"/>
@@ -74471,11 +74463,11 @@
     </row>
     <row r="691">
       <c r="A691" t="n">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
+          <t>PROMOTORAS GYN LTDA</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
@@ -74525,7 +74517,7 @@
         </is>
       </c>
       <c r="O691" t="n">
-        <v>18188751</v>
+        <v>18188657</v>
       </c>
       <c r="P691" t="inlineStr">
         <is>
@@ -74568,11 +74560,11 @@
     </row>
     <row r="692">
       <c r="A692" t="n">
-        <v>6963</v>
+        <v>5417</v>
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN LTDA</t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
@@ -74592,11 +74584,11 @@
       </c>
       <c r="F692" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G692" t="n">
-        <v>6813</v>
+        <v>957</v>
       </c>
       <c r="H692" t="n">
         <v>0</v>
@@ -74608,25 +74600,25 @@
       </c>
       <c r="J692" t="inlineStr">
         <is>
-          <t>DEC - Conferência 2º Quinzena</t>
+          <t>Definição do Lucro Trimestral</t>
         </is>
       </c>
       <c r="K692" t="inlineStr"/>
       <c r="L692" s="1" t="n">
-        <v>46220</v>
+        <v>46233</v>
       </c>
       <c r="M692" t="inlineStr"/>
       <c r="N692" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
       <c r="O692" t="n">
-        <v>18188657</v>
+        <v>17398899</v>
       </c>
       <c r="P692" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="Q692" t="inlineStr">
@@ -74636,14 +74628,18 @@
       </c>
       <c r="R692" t="inlineStr"/>
       <c r="S692" t="n">
-        <v>-3</v>
+        <v>-16</v>
       </c>
       <c r="T692" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN</t>
-        </is>
-      </c>
-      <c r="U692" t="inlineStr"/>
+          <t>NOSSO NOVO SUPERMERCADO</t>
+        </is>
+      </c>
+      <c r="U692" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V692" t="inlineStr"/>
       <c r="W692" t="inlineStr"/>
       <c r="X692" t="inlineStr"/>
@@ -74658,18 +74654,18 @@
       <c r="AE692" t="inlineStr"/>
       <c r="AF692" t="inlineStr">
         <is>
-          <t>Obrigação Acessória</t>
+          <t>Tarefa</t>
         </is>
       </c>
       <c r="AG692" t="inlineStr"/>
     </row>
     <row r="693">
       <c r="A693" t="n">
-        <v>5417</v>
+        <v>5617</v>
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
@@ -74689,7 +74685,7 @@
       </c>
       <c r="F693" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G693" t="n">
@@ -74719,7 +74715,7 @@
         </is>
       </c>
       <c r="O693" t="n">
-        <v>17398899</v>
+        <v>17407535</v>
       </c>
       <c r="P693" t="inlineStr">
         <is>
@@ -74737,7 +74733,7 @@
       </c>
       <c r="T693" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U693" t="inlineStr">
@@ -74766,11 +74762,11 @@
     </row>
     <row r="694">
       <c r="A694" t="n">
-        <v>5617</v>
+        <v>6627</v>
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
@@ -74785,7 +74781,7 @@
       </c>
       <c r="E694" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F694" t="inlineStr">
@@ -74820,7 +74816,7 @@
         </is>
       </c>
       <c r="O694" t="n">
-        <v>17407535</v>
+        <v>17042325</v>
       </c>
       <c r="P694" t="inlineStr">
         <is>
@@ -74838,7 +74834,7 @@
       </c>
       <c r="T694" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t xml:space="preserve">GTG </t>
         </is>
       </c>
       <c r="U694" t="inlineStr">
@@ -74867,11 +74863,11 @@
     </row>
     <row r="695">
       <c r="A695" t="n">
-        <v>6627</v>
+        <v>6359</v>
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
+          <t>MACHADO PRESTACAO DE SERVICOS LTDA</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
@@ -74881,12 +74877,12 @@
       </c>
       <c r="D695" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E695" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F695" t="inlineStr">
@@ -74895,19 +74891,19 @@
         </is>
       </c>
       <c r="G695" t="n">
-        <v>957</v>
+        <v>1662</v>
       </c>
       <c r="H695" t="n">
         <v>0</v>
       </c>
       <c r="I695" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="J695" t="inlineStr">
         <is>
-          <t>Definição do Lucro Trimestral</t>
+          <t>Devolução de Documentos</t>
         </is>
       </c>
       <c r="K695" t="inlineStr"/>
@@ -74921,32 +74917,26 @@
         </is>
       </c>
       <c r="O695" t="n">
-        <v>17042325</v>
-      </c>
-      <c r="P695" t="inlineStr">
-        <is>
-          <t>Sergio Fernandes</t>
-        </is>
-      </c>
+        <v>17108122</v>
+      </c>
+      <c r="P695" t="inlineStr"/>
       <c r="Q695" t="inlineStr">
         <is>
-          <t>Em Aberto</t>
-        </is>
-      </c>
-      <c r="R695" t="inlineStr"/>
+          <t>Baixado</t>
+        </is>
+      </c>
+      <c r="R695" s="1" t="n">
+        <v>46209.66158305555</v>
+      </c>
       <c r="S695" t="n">
         <v>-16</v>
       </c>
       <c r="T695" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
-        </is>
-      </c>
-      <c r="U695" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>MACHADO</t>
+        </is>
+      </c>
+      <c r="U695" t="inlineStr"/>
       <c r="V695" t="inlineStr"/>
       <c r="W695" t="inlineStr"/>
       <c r="X695" t="inlineStr"/>
@@ -74954,7 +74944,11 @@
       <c r="Z695" t="n">
         <v>0</v>
       </c>
-      <c r="AA695" t="inlineStr"/>
+      <c r="AA695" t="inlineStr">
+        <is>
+          <t>Isabella Nascimento</t>
+        </is>
+      </c>
       <c r="AB695" t="inlineStr"/>
       <c r="AC695" t="inlineStr"/>
       <c r="AD695" t="inlineStr"/>
@@ -74968,11 +74962,11 @@
     </row>
     <row r="696">
       <c r="A696" t="n">
-        <v>6359</v>
+        <v>6628</v>
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>MACHADO PRESTACAO DE SERVICOS LTDA</t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
@@ -74987,7 +74981,7 @@
       </c>
       <c r="E696" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F696" t="inlineStr">
@@ -74996,7 +74990,7 @@
         </is>
       </c>
       <c r="G696" t="n">
-        <v>1662</v>
+        <v>1650</v>
       </c>
       <c r="H696" t="n">
         <v>0</v>
@@ -75008,12 +75002,12 @@
       </c>
       <c r="J696" t="inlineStr">
         <is>
-          <t>Devolução de Documentos</t>
+          <t>Fechamento Mensal</t>
         </is>
       </c>
       <c r="K696" t="inlineStr"/>
       <c r="L696" s="1" t="n">
-        <v>46233</v>
+        <v>46231</v>
       </c>
       <c r="M696" t="inlineStr"/>
       <c r="N696" t="inlineStr">
@@ -75022,26 +75016,34 @@
         </is>
       </c>
       <c r="O696" t="n">
-        <v>17108122</v>
-      </c>
-      <c r="P696" t="inlineStr"/>
+        <v>16959972</v>
+      </c>
+      <c r="P696" t="inlineStr">
+        <is>
+          <t>Nathalia Lourenco</t>
+        </is>
+      </c>
       <c r="Q696" t="inlineStr">
         <is>
           <t>Baixado</t>
         </is>
       </c>
       <c r="R696" s="1" t="n">
-        <v>46209.66158305555</v>
+        <v>46203.00285659722</v>
       </c>
       <c r="S696" t="n">
-        <v>-16</v>
+        <v>-14</v>
       </c>
       <c r="T696" t="inlineStr">
         <is>
-          <t>MACHADO</t>
-        </is>
-      </c>
-      <c r="U696" t="inlineStr"/>
+          <t xml:space="preserve">GTG </t>
+        </is>
+      </c>
+      <c r="U696" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V696" t="inlineStr"/>
       <c r="W696" t="inlineStr"/>
       <c r="X696" t="inlineStr"/>
@@ -75051,7 +75053,7 @@
       </c>
       <c r="AA696" t="inlineStr">
         <is>
-          <t>Isabella Nascimento</t>
+          <t>ex-funcionario</t>
         </is>
       </c>
       <c r="AB696" t="inlineStr"/>
@@ -75063,15 +75065,19 @@
           <t>Tarefa</t>
         </is>
       </c>
-      <c r="AG696" t="inlineStr"/>
+      <c r="AG696" t="inlineStr">
+        <is>
+          <t>Isabella Nascimento</t>
+        </is>
+      </c>
     </row>
     <row r="697">
       <c r="A697" t="n">
-        <v>6628</v>
+        <v>6945</v>
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
@@ -75121,11 +75127,11 @@
         </is>
       </c>
       <c r="O697" t="n">
-        <v>16959972</v>
+        <v>18163665</v>
       </c>
       <c r="P697" t="inlineStr">
         <is>
-          <t>Nathalia Lourenco</t>
+          <t>Laisa Rocha</t>
         </is>
       </c>
       <c r="Q697" t="inlineStr">
@@ -75134,21 +75140,17 @@
         </is>
       </c>
       <c r="R697" s="1" t="n">
-        <v>46203.00285659722</v>
+        <v>46203.00296711805</v>
       </c>
       <c r="S697" t="n">
         <v>-14</v>
       </c>
       <c r="T697" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
-        </is>
-      </c>
-      <c r="U697" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>BRASIL DISTRIBUIDORA</t>
+        </is>
+      </c>
+      <c r="U697" t="inlineStr"/>
       <c r="V697" t="inlineStr"/>
       <c r="W697" t="inlineStr"/>
       <c r="X697" t="inlineStr"/>
@@ -75178,11 +75180,11 @@
     </row>
     <row r="698">
       <c r="A698" t="n">
-        <v>6945</v>
+        <v>6704</v>
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
+          <t>TECNO COM INFORMATICA LTDA</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
@@ -75192,12 +75194,12 @@
       </c>
       <c r="D698" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E698" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F698" t="inlineStr">
@@ -75206,24 +75208,24 @@
         </is>
       </c>
       <c r="G698" t="n">
-        <v>1650</v>
+        <v>7868</v>
       </c>
       <c r="H698" t="n">
         <v>0</v>
       </c>
       <c r="I698" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL INDUSTRIA</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="J698" t="inlineStr">
         <is>
-          <t>Fechamento Mensal</t>
+          <t xml:space="preserve">Envio do Razão Conta - Valores à Classificar </t>
         </is>
       </c>
       <c r="K698" t="inlineStr"/>
       <c r="L698" s="1" t="n">
-        <v>46231</v>
+        <v>46230</v>
       </c>
       <c r="M698" t="inlineStr"/>
       <c r="N698" t="inlineStr">
@@ -75232,11 +75234,11 @@
         </is>
       </c>
       <c r="O698" t="n">
-        <v>18163665</v>
+        <v>17955419</v>
       </c>
       <c r="P698" t="inlineStr">
         <is>
-          <t>Laisa Rocha</t>
+          <t>Paulo Silva</t>
         </is>
       </c>
       <c r="Q698" t="inlineStr">
@@ -75245,17 +75247,21 @@
         </is>
       </c>
       <c r="R698" s="1" t="n">
-        <v>46203.00296711805</v>
+        <v>46204.72937350695</v>
       </c>
       <c r="S698" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="T698" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA</t>
-        </is>
-      </c>
-      <c r="U698" t="inlineStr"/>
+          <t>TECNO COM</t>
+        </is>
+      </c>
+      <c r="U698" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V698" t="inlineStr"/>
       <c r="W698" t="inlineStr"/>
       <c r="X698" t="inlineStr"/>
@@ -75265,7 +75271,7 @@
       </c>
       <c r="AA698" t="inlineStr">
         <is>
-          <t>ex-funcionario</t>
+          <t>Paulo Silva</t>
         </is>
       </c>
       <c r="AB698" t="inlineStr"/>
@@ -75279,17 +75285,17 @@
       </c>
       <c r="AG698" t="inlineStr">
         <is>
-          <t>Isabella Nascimento</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="n">
-        <v>6704</v>
+        <v>5417</v>
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>TECNO COM INFORMATICA LTDA</t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
@@ -75309,11 +75315,11 @@
       </c>
       <c r="F699" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G699" t="n">
-        <v>7868</v>
+        <v>11276</v>
       </c>
       <c r="H699" t="n">
         <v>0</v>
@@ -75325,25 +75331,25 @@
       </c>
       <c r="J699" t="inlineStr">
         <is>
-          <t xml:space="preserve">Envio do Razão Conta - Valores à Classificar </t>
+          <t>Fed - DIRBI</t>
         </is>
       </c>
       <c r="K699" t="inlineStr"/>
       <c r="L699" s="1" t="n">
-        <v>46230</v>
+        <v>46223</v>
       </c>
       <c r="M699" t="inlineStr"/>
       <c r="N699" t="inlineStr">
         <is>
-          <t>06/2026</t>
+          <t>05/2026</t>
         </is>
       </c>
       <c r="O699" t="n">
-        <v>17955419</v>
+        <v>17399421</v>
       </c>
       <c r="P699" t="inlineStr">
         <is>
-          <t>Paulo Silva</t>
+          <t>Eveny Silva</t>
         </is>
       </c>
       <c r="Q699" t="inlineStr">
@@ -75352,14 +75358,14 @@
         </is>
       </c>
       <c r="R699" s="1" t="n">
-        <v>46204.72937350695</v>
+        <v>46206.41464283565</v>
       </c>
       <c r="S699" t="n">
-        <v>-13</v>
+        <v>-6</v>
       </c>
       <c r="T699" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>NOSSO NOVO SUPERMERCADO</t>
         </is>
       </c>
       <c r="U699" t="inlineStr">
@@ -75376,7 +75382,7 @@
       </c>
       <c r="AA699" t="inlineStr">
         <is>
-          <t>Paulo Silva</t>
+          <t>Eveny Silva</t>
         </is>
       </c>
       <c r="AB699" t="inlineStr"/>
@@ -75390,17 +75396,17 @@
       </c>
       <c r="AG699" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Karina Santos</t>
         </is>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="n">
-        <v>5417</v>
+        <v>5617</v>
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
@@ -75420,7 +75426,7 @@
       </c>
       <c r="F700" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G700" t="n">
@@ -75450,11 +75456,11 @@
         </is>
       </c>
       <c r="O700" t="n">
-        <v>17399421</v>
+        <v>17407942</v>
       </c>
       <c r="P700" t="inlineStr">
         <is>
-          <t>Eveny Silva</t>
+          <t>Jackson Silva</t>
         </is>
       </c>
       <c r="Q700" t="inlineStr">
@@ -75463,14 +75469,14 @@
         </is>
       </c>
       <c r="R700" s="1" t="n">
-        <v>46206.41464283565</v>
+        <v>46206.70573774305</v>
       </c>
       <c r="S700" t="n">
         <v>-6</v>
       </c>
       <c r="T700" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U700" t="inlineStr">
@@ -75487,7 +75493,7 @@
       </c>
       <c r="AA700" t="inlineStr">
         <is>
-          <t>Eveny Silva</t>
+          <t>Gustavo Vettorazzi</t>
         </is>
       </c>
       <c r="AB700" t="inlineStr"/>
@@ -75501,17 +75507,17 @@
       </c>
       <c r="AG700" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="n">
-        <v>5617</v>
+        <v>6224</v>
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
@@ -75531,7 +75537,7 @@
       </c>
       <c r="F701" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G701" t="n">
@@ -75561,7 +75567,7 @@
         </is>
       </c>
       <c r="O701" t="n">
-        <v>17407942</v>
+        <v>18179997</v>
       </c>
       <c r="P701" t="inlineStr">
         <is>
@@ -75574,7 +75580,7 @@
         </is>
       </c>
       <c r="R701" s="1" t="n">
-        <v>46206.70573774305</v>
+        <v>46206.70573846065</v>
       </c>
       <c r="S701" t="n">
         <v>-6</v>
@@ -75618,11 +75624,11 @@
     </row>
     <row r="702">
       <c r="A702" t="n">
-        <v>6224</v>
+        <v>6486</v>
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>PC GAMER GOIANIA LTDA</t>
         </is>
       </c>
       <c r="C702" t="inlineStr">
@@ -75642,7 +75648,7 @@
       </c>
       <c r="F702" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G702" t="n">
@@ -75672,11 +75678,11 @@
         </is>
       </c>
       <c r="O702" t="n">
-        <v>18179997</v>
+        <v>18152555</v>
       </c>
       <c r="P702" t="inlineStr">
         <is>
-          <t>Jackson Silva</t>
+          <t>Nathany Barreto</t>
         </is>
       </c>
       <c r="Q702" t="inlineStr">
@@ -75685,14 +75691,14 @@
         </is>
       </c>
       <c r="R702" s="1" t="n">
-        <v>46206.70573846065</v>
+        <v>46211.41697137732</v>
       </c>
       <c r="S702" t="n">
         <v>-6</v>
       </c>
       <c r="T702" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>PC GAMER</t>
         </is>
       </c>
       <c r="U702" t="inlineStr">
@@ -75709,7 +75715,7 @@
       </c>
       <c r="AA702" t="inlineStr">
         <is>
-          <t>Gustavo Vettorazzi</t>
+          <t>Karina Santos</t>
         </is>
       </c>
       <c r="AB702" t="inlineStr"/>
@@ -75723,17 +75729,17 @@
       </c>
       <c r="AG702" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Karina Santos</t>
         </is>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="n">
-        <v>6486</v>
+        <v>6278</v>
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>PC GAMER GOIANIA LTDA</t>
+          <t>EMPORIO DOS FRIOS LTDA</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
@@ -75743,7 +75749,7 @@
       </c>
       <c r="D703" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Real - Anual</t>
         </is>
       </c>
       <c r="E703" t="inlineStr">
@@ -75757,10 +75763,10 @@
         </is>
       </c>
       <c r="G703" t="n">
-        <v>11276</v>
+        <v>1628</v>
       </c>
       <c r="H703" t="n">
-        <v>0</v>
+        <v>1581</v>
       </c>
       <c r="I703" t="inlineStr">
         <is>
@@ -75769,7 +75775,7 @@
       </c>
       <c r="J703" t="inlineStr">
         <is>
-          <t>Fed - DIRBI</t>
+          <t>Outras Receitas</t>
         </is>
       </c>
       <c r="K703" t="inlineStr"/>
@@ -75779,15 +75785,15 @@
       <c r="M703" t="inlineStr"/>
       <c r="N703" t="inlineStr">
         <is>
-          <t>05/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
       <c r="O703" t="n">
-        <v>18152555</v>
+        <v>17539752</v>
       </c>
       <c r="P703" t="inlineStr">
         <is>
-          <t>Nathany Barreto</t>
+          <t>Isabela Lemos</t>
         </is>
       </c>
       <c r="Q703" t="inlineStr">
@@ -75796,14 +75802,14 @@
         </is>
       </c>
       <c r="R703" s="1" t="n">
-        <v>46211.41697137732</v>
+        <v>46203.3758668287</v>
       </c>
       <c r="S703" t="n">
         <v>-6</v>
       </c>
       <c r="T703" t="inlineStr">
         <is>
-          <t>PC GAMER</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U703" t="inlineStr">
@@ -75820,7 +75826,7 @@
       </c>
       <c r="AA703" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Isabela Lemos</t>
         </is>
       </c>
       <c r="AB703" t="inlineStr"/>
@@ -75834,17 +75840,17 @@
       </c>
       <c r="AG703" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="n">
-        <v>6278</v>
+        <v>6279</v>
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS LTDA</t>
+          <t>DIENNYFER DA S PEREIRA</t>
         </is>
       </c>
       <c r="C704" t="inlineStr">
@@ -75854,7 +75860,7 @@
       </c>
       <c r="D704" t="inlineStr">
         <is>
-          <t>Federal - Lucro Real - Anual</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E704" t="inlineStr">
@@ -75864,7 +75870,7 @@
       </c>
       <c r="F704" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G704" t="n">
@@ -75894,7 +75900,7 @@
         </is>
       </c>
       <c r="O704" t="n">
-        <v>17539752</v>
+        <v>17645955</v>
       </c>
       <c r="P704" t="inlineStr">
         <is>
@@ -75907,7 +75913,7 @@
         </is>
       </c>
       <c r="R704" s="1" t="n">
-        <v>46203.3758668287</v>
+        <v>46203.37586737268</v>
       </c>
       <c r="S704" t="n">
         <v>-6</v>
@@ -75951,11 +75957,11 @@
     </row>
     <row r="705">
       <c r="A705" t="n">
-        <v>6279</v>
+        <v>6404</v>
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>DIENNYFER DA S PEREIRA</t>
+          <t>SOLAR INVESTIMENTOS LTDA</t>
         </is>
       </c>
       <c r="C705" t="inlineStr">
@@ -75975,7 +75981,7 @@
       </c>
       <c r="F705" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G705" t="n">
@@ -76005,7 +76011,7 @@
         </is>
       </c>
       <c r="O705" t="n">
-        <v>17645955</v>
+        <v>16962139</v>
       </c>
       <c r="P705" t="inlineStr">
         <is>
@@ -76018,14 +76024,14 @@
         </is>
       </c>
       <c r="R705" s="1" t="n">
-        <v>46203.37586737268</v>
+        <v>46203.37586936342</v>
       </c>
       <c r="S705" t="n">
         <v>-6</v>
       </c>
       <c r="T705" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>SOLAR INVESTIMENTOS</t>
         </is>
       </c>
       <c r="U705" t="inlineStr">
@@ -76062,11 +76068,11 @@
     </row>
     <row r="706">
       <c r="A706" t="n">
-        <v>6404</v>
+        <v>6704</v>
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS LTDA</t>
+          <t>TECNO COM INFORMATICA LTDA</t>
         </is>
       </c>
       <c r="C706" t="inlineStr">
@@ -76076,7 +76082,7 @@
       </c>
       <c r="D706" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E706" t="inlineStr">
@@ -76116,11 +76122,11 @@
         </is>
       </c>
       <c r="O706" t="n">
-        <v>16962139</v>
+        <v>17955382</v>
       </c>
       <c r="P706" t="inlineStr">
         <is>
-          <t>Isabela Lemos</t>
+          <t>Paulo Silva</t>
         </is>
       </c>
       <c r="Q706" t="inlineStr">
@@ -76129,14 +76135,14 @@
         </is>
       </c>
       <c r="R706" s="1" t="n">
-        <v>46203.37586936342</v>
+        <v>46205.45020773148</v>
       </c>
       <c r="S706" t="n">
         <v>-6</v>
       </c>
       <c r="T706" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS</t>
+          <t>TECNO COM</t>
         </is>
       </c>
       <c r="U706" t="inlineStr">
@@ -76153,7 +76159,7 @@
       </c>
       <c r="AA706" t="inlineStr">
         <is>
-          <t>Isabela Lemos</t>
+          <t>Paulo Silva</t>
         </is>
       </c>
       <c r="AB706" t="inlineStr"/>
@@ -76173,11 +76179,11 @@
     </row>
     <row r="707">
       <c r="A707" t="n">
-        <v>6704</v>
+        <v>6705</v>
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>TECNO COM INFORMATICA LTDA</t>
+          <t>NARCIZO ALVES CORDEIRO</t>
         </is>
       </c>
       <c r="C707" t="inlineStr">
@@ -76187,7 +76193,7 @@
       </c>
       <c r="D707" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E707" t="inlineStr">
@@ -76227,7 +76233,7 @@
         </is>
       </c>
       <c r="O707" t="n">
-        <v>17955382</v>
+        <v>17955236</v>
       </c>
       <c r="P707" t="inlineStr">
         <is>
@@ -76240,7 +76246,7 @@
         </is>
       </c>
       <c r="R707" s="1" t="n">
-        <v>46205.45020773148</v>
+        <v>46205.45020809027</v>
       </c>
       <c r="S707" t="n">
         <v>-6</v>
@@ -76284,11 +76290,11 @@
     </row>
     <row r="708">
       <c r="A708" t="n">
-        <v>6705</v>
+        <v>6779</v>
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>NARCIZO ALVES CORDEIRO</t>
+          <t>CORDEIRO E CIA LTDA</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
@@ -76338,7 +76344,7 @@
         </is>
       </c>
       <c r="O708" t="n">
-        <v>17955236</v>
+        <v>18056727</v>
       </c>
       <c r="P708" t="inlineStr">
         <is>
@@ -76351,7 +76357,7 @@
         </is>
       </c>
       <c r="R708" s="1" t="n">
-        <v>46205.45020809027</v>
+        <v>46205.45020880787</v>
       </c>
       <c r="S708" t="n">
         <v>-6</v>
@@ -76361,11 +76367,7 @@
           <t>TECNO COM</t>
         </is>
       </c>
-      <c r="U708" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+      <c r="U708" t="inlineStr"/>
       <c r="V708" t="inlineStr"/>
       <c r="W708" t="inlineStr"/>
       <c r="X708" t="inlineStr"/>
@@ -76395,11 +76397,11 @@
     </row>
     <row r="709">
       <c r="A709" t="n">
-        <v>6779</v>
+        <v>6885</v>
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>CORDEIRO E CIA LTDA</t>
+          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
         </is>
       </c>
       <c r="C709" t="inlineStr">
@@ -76449,11 +76451,11 @@
         </is>
       </c>
       <c r="O709" t="n">
-        <v>18056727</v>
+        <v>18128696</v>
       </c>
       <c r="P709" t="inlineStr">
         <is>
-          <t>Paulo Silva</t>
+          <t>Isabela Lemos</t>
         </is>
       </c>
       <c r="Q709" t="inlineStr">
@@ -76462,14 +76464,14 @@
         </is>
       </c>
       <c r="R709" s="1" t="n">
-        <v>46205.45020880787</v>
+        <v>46203.37587081019</v>
       </c>
       <c r="S709" t="n">
         <v>-6</v>
       </c>
       <c r="T709" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U709" t="inlineStr"/>
@@ -76482,7 +76484,7 @@
       </c>
       <c r="AA709" t="inlineStr">
         <is>
-          <t>Paulo Silva</t>
+          <t>Isabela Lemos</t>
         </is>
       </c>
       <c r="AB709" t="inlineStr"/>
@@ -76530,37 +76532,37 @@
         </is>
       </c>
       <c r="G710" t="n">
-        <v>1628</v>
+        <v>5885</v>
       </c>
       <c r="H710" t="n">
-        <v>1581</v>
+        <v>5784</v>
       </c>
       <c r="I710" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="J710" t="inlineStr">
         <is>
-          <t>Outras Receitas</t>
+          <t>Adiantamento Salarial (20)</t>
         </is>
       </c>
       <c r="K710" t="inlineStr"/>
       <c r="L710" s="1" t="n">
-        <v>46223</v>
+        <v>46220</v>
       </c>
       <c r="M710" t="inlineStr"/>
       <c r="N710" t="inlineStr">
         <is>
-          <t>06/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
       <c r="O710" t="n">
-        <v>18128696</v>
+        <v>18157292</v>
       </c>
       <c r="P710" t="inlineStr">
         <is>
-          <t>Isabela Lemos</t>
+          <t>Vitor Guedes</t>
         </is>
       </c>
       <c r="Q710" t="inlineStr">
@@ -76569,10 +76571,10 @@
         </is>
       </c>
       <c r="R710" s="1" t="n">
-        <v>46203.37587081019</v>
+        <v>46216.44618675926</v>
       </c>
       <c r="S710" t="n">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="T710" t="inlineStr">
         <is>
@@ -76589,7 +76591,7 @@
       </c>
       <c r="AA710" t="inlineStr">
         <is>
-          <t>Isabela Lemos</t>
+          <t>Vitor Guedes</t>
         </is>
       </c>
       <c r="AB710" t="inlineStr"/>
@@ -76598,22 +76600,22 @@
       <c r="AE710" t="inlineStr"/>
       <c r="AF710" t="inlineStr">
         <is>
-          <t>Tarefa</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="AG710" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>David Bragança</t>
         </is>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="n">
-        <v>6885</v>
+        <v>6703</v>
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
+          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
@@ -76623,7 +76625,7 @@
       </c>
       <c r="D711" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E711" t="inlineStr">
@@ -76637,10 +76639,10 @@
         </is>
       </c>
       <c r="G711" t="n">
-        <v>5885</v>
+        <v>6395</v>
       </c>
       <c r="H711" t="n">
-        <v>5784</v>
+        <v>5792</v>
       </c>
       <c r="I711" t="inlineStr">
         <is>
@@ -76649,25 +76651,25 @@
       </c>
       <c r="J711" t="inlineStr">
         <is>
-          <t>Adiantamento Salarial (20)</t>
+          <t>Cartão de Ponto</t>
         </is>
       </c>
       <c r="K711" t="inlineStr"/>
       <c r="L711" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="M711" t="inlineStr"/>
       <c r="N711" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
       <c r="O711" t="n">
-        <v>18157292</v>
+        <v>18105118</v>
       </c>
       <c r="P711" t="inlineStr">
         <is>
-          <t>Vitor Guedes</t>
+          <t>Ana Marcelino</t>
         </is>
       </c>
       <c r="Q711" t="inlineStr">
@@ -76676,17 +76678,21 @@
         </is>
       </c>
       <c r="R711" s="1" t="n">
-        <v>46216.44618675926</v>
+        <v>46206.62907918981</v>
       </c>
       <c r="S711" t="n">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="T711" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
-        </is>
-      </c>
-      <c r="U711" t="inlineStr"/>
+          <t>LIMA MOTA</t>
+        </is>
+      </c>
+      <c r="U711" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V711" t="inlineStr"/>
       <c r="W711" t="inlineStr"/>
       <c r="X711" t="inlineStr"/>
@@ -76696,7 +76702,7 @@
       </c>
       <c r="AA711" t="inlineStr">
         <is>
-          <t>Vitor Guedes</t>
+          <t>Elaine Assis</t>
         </is>
       </c>
       <c r="AB711" t="inlineStr"/>
@@ -76705,22 +76711,22 @@
       <c r="AE711" t="inlineStr"/>
       <c r="AF711" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Tarefa</t>
         </is>
       </c>
       <c r="AG711" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="n">
-        <v>6703</v>
+        <v>6945</v>
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
+          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
@@ -76730,12 +76736,12 @@
       </c>
       <c r="D712" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F712" t="inlineStr">
@@ -76744,10 +76750,10 @@
         </is>
       </c>
       <c r="G712" t="n">
-        <v>6395</v>
+        <v>6348</v>
       </c>
       <c r="H712" t="n">
-        <v>5792</v>
+        <v>0</v>
       </c>
       <c r="I712" t="inlineStr">
         <is>
@@ -76756,7 +76762,7 @@
       </c>
       <c r="J712" t="inlineStr">
         <is>
-          <t>Cartão de Ponto</t>
+          <t>RESCISÃO - RESCISÃO</t>
         </is>
       </c>
       <c r="K712" t="inlineStr"/>
@@ -76770,11 +76776,11 @@
         </is>
       </c>
       <c r="O712" t="n">
-        <v>18105118</v>
+        <v>18186112</v>
       </c>
       <c r="P712" t="inlineStr">
         <is>
-          <t>Ana Marcelino</t>
+          <t>Santos Karina</t>
         </is>
       </c>
       <c r="Q712" t="inlineStr">
@@ -76783,22 +76789,22 @@
         </is>
       </c>
       <c r="R712" s="1" t="n">
-        <v>46206.62907918981</v>
+        <v>46206.44786171296</v>
       </c>
       <c r="S712" t="n">
         <v>-6</v>
       </c>
       <c r="T712" t="inlineStr">
         <is>
-          <t>LIMA MOTA</t>
-        </is>
-      </c>
-      <c r="U712" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="V712" t="inlineStr"/>
+          <t>BRASIL DISTRIBUIDORA</t>
+        </is>
+      </c>
+      <c r="U712" t="inlineStr"/>
+      <c r="V712" t="inlineStr">
+        <is>
+          <t>63 - Isaak Pinheiro Dias, Pedido de demissão - Aviso Trabalhado - pagamento em 22/07/2026. - Data Comentário: 16/06/2026 13:28</t>
+        </is>
+      </c>
       <c r="W712" t="inlineStr"/>
       <c r="X712" t="inlineStr"/>
       <c r="Y712" t="inlineStr"/>
@@ -76807,7 +76813,7 @@
       </c>
       <c r="AA712" t="inlineStr">
         <is>
-          <t>Elaine Assis</t>
+          <t>Santos Karina</t>
         </is>
       </c>
       <c r="AB712" t="inlineStr"/>
@@ -76816,22 +76822,22 @@
       <c r="AE712" t="inlineStr"/>
       <c r="AF712" t="inlineStr">
         <is>
-          <t>Tarefa</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="AG712" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>Leandro Matos</t>
         </is>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="n">
-        <v>6945</v>
+        <v>6627</v>
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
+          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
@@ -76841,7 +76847,7 @@
       </c>
       <c r="D713" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E713" t="inlineStr">
@@ -76855,19 +76861,19 @@
         </is>
       </c>
       <c r="G713" t="n">
-        <v>6348</v>
+        <v>11550</v>
       </c>
       <c r="H713" t="n">
-        <v>0</v>
+        <v>1862</v>
       </c>
       <c r="I713" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J713" t="inlineStr">
         <is>
-          <t>RESCISÃO - RESCISÃO</t>
+          <t>Bloco K</t>
         </is>
       </c>
       <c r="K713" t="inlineStr"/>
@@ -76881,11 +76887,11 @@
         </is>
       </c>
       <c r="O713" t="n">
-        <v>18186112</v>
+        <v>18048491</v>
       </c>
       <c r="P713" t="inlineStr">
         <is>
-          <t>Santos Karina</t>
+          <t>Denis Reis</t>
         </is>
       </c>
       <c r="Q713" t="inlineStr">
@@ -76894,22 +76900,22 @@
         </is>
       </c>
       <c r="R713" s="1" t="n">
-        <v>46206.44786171296</v>
+        <v>46203.71390146991</v>
       </c>
       <c r="S713" t="n">
         <v>-6</v>
       </c>
       <c r="T713" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA</t>
-        </is>
-      </c>
-      <c r="U713" t="inlineStr"/>
-      <c r="V713" t="inlineStr">
-        <is>
-          <t>63 - Isaak Pinheiro Dias, Pedido de demissão - Aviso Trabalhado - pagamento em 22/07/2026. - Data Comentário: 16/06/2026 13:28</t>
-        </is>
-      </c>
+          <t xml:space="preserve">GTG </t>
+        </is>
+      </c>
+      <c r="U713" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V713" t="inlineStr"/>
       <c r="W713" t="inlineStr"/>
       <c r="X713" t="inlineStr"/>
       <c r="Y713" t="inlineStr"/>
@@ -76918,7 +76924,7 @@
       </c>
       <c r="AA713" t="inlineStr">
         <is>
-          <t>Santos Karina</t>
+          <t>Denis Reis</t>
         </is>
       </c>
       <c r="AB713" t="inlineStr"/>
@@ -76927,22 +76933,22 @@
       <c r="AE713" t="inlineStr"/>
       <c r="AF713" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Tarefa</t>
         </is>
       </c>
       <c r="AG713" t="inlineStr">
         <is>
-          <t>Leandro Matos</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
     </row>
     <row r="714">
       <c r="A714" t="n">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
@@ -76952,7 +76958,7 @@
       </c>
       <c r="D714" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E714" t="inlineStr">
@@ -76966,10 +76972,10 @@
         </is>
       </c>
       <c r="G714" t="n">
-        <v>11550</v>
+        <v>1862</v>
       </c>
       <c r="H714" t="n">
-        <v>1862</v>
+        <v>0</v>
       </c>
       <c r="I714" t="inlineStr">
         <is>
@@ -76978,12 +76984,12 @@
       </c>
       <c r="J714" t="inlineStr">
         <is>
-          <t>Bloco K</t>
+          <t>Fechamento Mensal</t>
         </is>
       </c>
       <c r="K714" t="inlineStr"/>
       <c r="L714" s="1" t="n">
-        <v>46223</v>
+        <v>46219</v>
       </c>
       <c r="M714" t="inlineStr"/>
       <c r="N714" t="inlineStr">
@@ -76992,11 +76998,11 @@
         </is>
       </c>
       <c r="O714" t="n">
-        <v>18048491</v>
+        <v>18047770</v>
       </c>
       <c r="P714" t="inlineStr">
         <is>
-          <t>Denis Reis</t>
+          <t>Fernando Bastos</t>
         </is>
       </c>
       <c r="Q714" t="inlineStr">
@@ -77005,10 +77011,10 @@
         </is>
       </c>
       <c r="R714" s="1" t="n">
-        <v>46203.71390146991</v>
+        <v>46203.00370568287</v>
       </c>
       <c r="S714" t="n">
-        <v>-6</v>
+        <v>-2</v>
       </c>
       <c r="T714" t="inlineStr">
         <is>
@@ -77029,7 +77035,7 @@
       </c>
       <c r="AA714" t="inlineStr">
         <is>
-          <t>Denis Reis</t>
+          <t>ex-funcionario</t>
         </is>
       </c>
       <c r="AB714" t="inlineStr"/>
@@ -77049,11 +77055,11 @@
     </row>
     <row r="715">
       <c r="A715" t="n">
-        <v>6628</v>
+        <v>6548</v>
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>GOIAS SILAGEM LTDA</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
@@ -77063,12 +77069,12 @@
       </c>
       <c r="D715" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F715" t="inlineStr">
@@ -77077,7 +77083,7 @@
         </is>
       </c>
       <c r="G715" t="n">
-        <v>1862</v>
+        <v>7026</v>
       </c>
       <c r="H715" t="n">
         <v>0</v>
@@ -77089,12 +77095,12 @@
       </c>
       <c r="J715" t="inlineStr">
         <is>
-          <t>Fechamento Mensal</t>
+          <t>Movimento - Sistema de Análise</t>
         </is>
       </c>
       <c r="K715" t="inlineStr"/>
       <c r="L715" s="1" t="n">
-        <v>46219</v>
+        <v>46226</v>
       </c>
       <c r="M715" t="inlineStr"/>
       <c r="N715" t="inlineStr">
@@ -77103,11 +77109,11 @@
         </is>
       </c>
       <c r="O715" t="n">
-        <v>18047770</v>
+        <v>18094897</v>
       </c>
       <c r="P715" t="inlineStr">
         <is>
-          <t>Fernando Bastos</t>
+          <t>Cristiana Grizostomo</t>
         </is>
       </c>
       <c r="Q715" t="inlineStr">
@@ -77116,14 +77122,14 @@
         </is>
       </c>
       <c r="R715" s="1" t="n">
-        <v>46203.00370568287</v>
+        <v>46217.71423630787</v>
       </c>
       <c r="S715" t="n">
-        <v>-2</v>
+        <v>-9</v>
       </c>
       <c r="T715" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
+          <t>GOIAS SILAGEM</t>
         </is>
       </c>
       <c r="U715" t="inlineStr">
@@ -77131,7 +77137,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V715" t="inlineStr"/>
+      <c r="V715" t="inlineStr">
+        <is>
+          <t>Baixado via API integração MGC x Sistema de Analise Fiscal em 14/07/2026 17:12:12. - Data Comentário: 14/07/2026 17:07</t>
+        </is>
+      </c>
       <c r="W715" t="inlineStr"/>
       <c r="X715" t="inlineStr"/>
       <c r="Y715" t="inlineStr"/>

--- a/dados/base/goias.xlsx
+++ b/dados/base/goias.xlsx
@@ -1027,11 +1027,11 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5417</v>
+        <v>6279</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>DIENNYFER DA S PEREIRA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1074,22 +1074,18 @@
       <c r="L6" s="1" t="n">
         <v>46218</v>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>15/07/2026</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>17399054</v>
+        <v>18205115</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Mikael Teixeira</t>
+          <t>Vitor Guedes</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1103,7 +1099,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1113,8 +1109,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 15/07/2026 
-em processamento - Data Comentário: 14/07/2026 18:00</t>
+          <t>8. Serviços Suspensos. - Data Comentário: 14/07/2026 17:43</t>
         </is>
       </c>
       <c r="W6" t="inlineStr"/>
@@ -1133,15 +1128,19 @@
           <t>Imposto</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>David Bragança</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6279</v>
+        <v>6548</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DIENNYFER DA S PEREIRA</t>
+          <t>GOIAS SILAGEM LTDA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1151,7 +1150,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1161,7 +1160,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1184,18 +1183,22 @@
       <c r="L7" s="1" t="n">
         <v>46218</v>
       </c>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>15/07/2026</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>18205115</v>
+        <v>17222615</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vitor Guedes</t>
+          <t>Daniel Moraes</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1209,7 +1212,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>GOIAS SILAGEM</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1219,7 +1222,8 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>8. Serviços Suspensos. - Data Comentário: 14/07/2026 17:43</t>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 15/07/2026 
+Previsão pra finalizar em 15/07/2026 - Data Comentário: 13/07/2026 09:06</t>
         </is>
       </c>
       <c r="W7" t="inlineStr"/>
@@ -1246,11 +1250,11 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>6548</v>
+        <v>6885</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM LTDA</t>
+          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1260,7 +1264,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1293,22 +1297,18 @@
       <c r="L8" s="1" t="n">
         <v>46218</v>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>15/07/2026</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>17222615</v>
+        <v>18157267</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Daniel Moraes</t>
+          <t>Vitor Guedes</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1322,18 +1322,13 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>EMPORIO DOS FRIOS</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 15/07/2026 
-Previsão pra finalizar em 15/07/2026 - Data Comentário: 13/07/2026 09:06</t>
+          <t>8. Serviços Suspensos. - Data Comentário: 14/07/2026 17:40</t>
         </is>
       </c>
       <c r="W8" t="inlineStr"/>
@@ -1360,11 +1355,11 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>6885</v>
+        <v>5617</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1374,7 +1369,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1388,19 +1383,19 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>5867</v>
+        <v>7884</v>
       </c>
       <c r="H9" t="n">
-        <v>5786</v>
+        <v>9114</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>GFD - FGTS Digital Mensal</t>
+          <t>Log/Envio de Inconsistência (Mensal)</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1414,11 +1409,11 @@
         </is>
       </c>
       <c r="O9" t="n">
-        <v>18157267</v>
+        <v>18120594</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Vitor Guedes</t>
+          <t>Cristina Leite</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1432,13 +1427,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr"/>
+          <t>SUPER MAIS DO GOIÁS</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>8. Serviços Suspensos. - Data Comentário: 14/07/2026 17:40</t>
+          <t>Atraso do Cliente, cobrança ativa, GC e GM ciente do atraso - Data Comentário: 10/07/2026 10:31</t>
         </is>
       </c>
       <c r="W9" t="inlineStr"/>
@@ -1454,12 +1453,12 @@
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Tarefa</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
     </row>
@@ -1493,10 +1492,10 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>7884</v>
+        <v>11303</v>
       </c>
       <c r="H10" t="n">
-        <v>9114</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1505,7 +1504,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Log/Envio de Inconsistência (Mensal)</t>
+          <t>Retorno do Check-List Fiscal</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1519,7 +1518,7 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>18120594</v>
+        <v>17407963</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -1545,11 +1544,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Atraso do Cliente, cobrança ativa, GC e GM ciente do atraso - Data Comentário: 10/07/2026 10:31</t>
-        </is>
-      </c>
+      <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr"/>
@@ -1574,11 +1569,11 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>5617</v>
+        <v>6949</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>TEC GRUA LOCAÇÃO E COMERCIO DE EQUIPAMENTOS PARA CONSTRUÇÃO LTDA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1598,70 +1593,77 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Reynaldo Santos</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>11303</v>
+        <v>11615</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Retorno do Check-List Fiscal</t>
+          <t>Envio de ATA de Implantação - CTB I</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" s="1" t="n">
-        <v>46218</v>
-      </c>
-      <c r="M11" t="inlineStr"/>
+        <v>46206</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>17407963</v>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Cristina Leite</t>
-        </is>
-      </c>
+        <v>18166586</v>
+      </c>
+      <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Em Aberto</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr"/>
+          <t>Baixado</t>
+        </is>
+      </c>
+      <c r="R11" s="1" t="n">
+        <v>46206.43215109954</v>
+      </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr"/>
+          <t>TEC GRUA</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 26/06/2026 
+Aguardando agendamento das implantações - Data Comentário: 18/06/2026 17:44</t>
+        </is>
+      </c>
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="n">
         <v>0</v>
       </c>
-      <c r="AA11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Erika Santana</t>
+        </is>
+      </c>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr"/>
@@ -1671,19 +1673,15 @@
           <t>Tarefa</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>Ricardo Fischer</t>
-        </is>
-      </c>
+      <c r="AG11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>6949</v>
+        <v>6962</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TEC GRUA LOCAÇÃO E COMERCIO DE EQUIPAMENTOS PARA CONSTRUÇÃO LTDA</t>
+          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1726,18 +1724,14 @@
       <c r="L12" s="1" t="n">
         <v>46206</v>
       </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>26/06/2026</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>18166586</v>
+        <v>18186559</v>
       </c>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr">
@@ -1746,21 +1740,20 @@
         </is>
       </c>
       <c r="R12" s="1" t="n">
-        <v>46206.43215109954</v>
+        <v>46206.43205978009</v>
       </c>
       <c r="S12" t="n">
         <v>12</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>TEC GRUA</t>
+          <t>PROMOTORAS GYN</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 26/06/2026 
-Aguardando agendamento das implantações - Data Comentário: 18/06/2026 17:44</t>
+          <t>Rotina Para Criar Tarefas Dos Clientes Novos - CodCliente: 6962; Tarefa Incluida: 11615; Vencimento: 17/06/2026 00:00:00; UsuarioResponsavel: erikas - Data Comentário: 17/06/2026 11:09</t>
         </is>
       </c>
       <c r="W12" t="inlineStr"/>
@@ -1787,11 +1780,11 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
+          <t>PROMOTORAS GYN LTDA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1841,7 +1834,7 @@
         </is>
       </c>
       <c r="O13" t="n">
-        <v>18186559</v>
+        <v>18186560</v>
       </c>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr">
@@ -1850,7 +1843,7 @@
         </is>
       </c>
       <c r="R13" s="1" t="n">
-        <v>46206.43205978009</v>
+        <v>46206.43206049768</v>
       </c>
       <c r="S13" t="n">
         <v>12</v>
@@ -1863,7 +1856,7 @@
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr">
         <is>
-          <t>Rotina Para Criar Tarefas Dos Clientes Novos - CodCliente: 6962; Tarefa Incluida: 11615; Vencimento: 17/06/2026 00:00:00; UsuarioResponsavel: erikas - Data Comentário: 17/06/2026 11:09</t>
+          <t>Rotina Para Criar Tarefas Dos Clientes Novos - CodCliente: 6963; Tarefa Incluida: 11615; Vencimento: 17/06/2026 00:00:00; UsuarioResponsavel: erikas - Data Comentário: 17/06/2026 11:09</t>
         </is>
       </c>
       <c r="W13" t="inlineStr"/>
@@ -1890,11 +1883,11 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>6963</v>
+        <v>6548</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN LTDA</t>
+          <t>GOIAS SILAGEM LTDA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1914,11 +1907,11 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>11615</v>
+        <v>11299</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1930,12 +1923,12 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Envio de ATA de Implantação - CTB I</t>
+          <t>Retorno do Check-List</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" s="1" t="n">
-        <v>46206</v>
+        <v>46218</v>
       </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
@@ -1944,31 +1937,35 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>18186560</v>
-      </c>
-      <c r="P14" t="inlineStr"/>
+        <v>17968039</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Thais Souza</t>
+        </is>
+      </c>
       <c r="Q14" t="inlineStr">
         <is>
           <t>Baixado</t>
         </is>
       </c>
       <c r="R14" s="1" t="n">
-        <v>46206.43206049768</v>
+        <v>46204.75352534722</v>
       </c>
       <c r="S14" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Rotina Para Criar Tarefas Dos Clientes Novos - CodCliente: 6963; Tarefa Incluida: 11615; Vencimento: 17/06/2026 00:00:00; UsuarioResponsavel: erikas - Data Comentário: 17/06/2026 11:09</t>
-        </is>
-      </c>
+          <t>GOIAS SILAGEM</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr"/>
@@ -1977,7 +1974,7 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>Erika Santana</t>
+          <t>Juan Rodrigues</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr"/>
@@ -1989,15 +1986,19 @@
           <t>Tarefa</t>
         </is>
       </c>
-      <c r="AG14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>Erika Santana</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM LTDA</t>
+          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2012,7 +2013,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2047,11 +2048,11 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>17968039</v>
+        <v>17042639</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Thais Souza</t>
+          <t>Nathalia Lourenco</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -2060,14 +2061,14 @@
         </is>
       </c>
       <c r="R15" s="1" t="n">
-        <v>46204.75352534722</v>
+        <v>46204.75352809028</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM</t>
+          <t xml:space="preserve">GTG </t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2098,17 +2099,17 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>Erika Santana</t>
+          <t>Isabella Nascimento</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2118,7 +2119,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2158,7 +2159,7 @@
         </is>
       </c>
       <c r="O16" t="n">
-        <v>17042639</v>
+        <v>16960108</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
@@ -2171,7 +2172,7 @@
         </is>
       </c>
       <c r="R16" s="1" t="n">
-        <v>46204.75352809028</v>
+        <v>46204.7535284375</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -2215,11 +2216,11 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>6628</v>
+        <v>6945</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2269,11 +2270,11 @@
         </is>
       </c>
       <c r="O17" t="n">
-        <v>16960108</v>
+        <v>18163697</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Nathalia Lourenco</t>
+          <t>Laisa Rocha</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -2282,21 +2283,17 @@
         </is>
       </c>
       <c r="R17" s="1" t="n">
-        <v>46204.7535284375</v>
+        <v>46204.7535334838</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>BRASIL DISTRIBUIDORA</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr"/>
@@ -2326,11 +2323,11 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>6945</v>
+        <v>6962</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
+          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2340,17 +2337,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Reynaldo Santos</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2380,11 +2377,11 @@
         </is>
       </c>
       <c r="O18" t="n">
-        <v>18163697</v>
+        <v>18187976</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Laisa Rocha</t>
+          <t>Mirian Lima</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -2393,14 +2390,14 @@
         </is>
       </c>
       <c r="R18" s="1" t="n">
-        <v>46204.7535334838</v>
+        <v>46204.75353387732</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA</t>
+          <t>PROMOTORAS GYN</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2433,11 +2430,11 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
+          <t>PROMOTORAS GYN LTDA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2487,7 +2484,7 @@
         </is>
       </c>
       <c r="O19" t="n">
-        <v>18187976</v>
+        <v>18187914</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
@@ -2500,7 +2497,7 @@
         </is>
       </c>
       <c r="R19" s="1" t="n">
-        <v>46204.75353387732</v>
+        <v>46204.75353515046</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -2540,11 +2537,11 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>6963</v>
+        <v>5417</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN LTDA</t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2564,18 +2561,18 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>11299</v>
+        <v>11297</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL INDUSTRIA</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2594,11 +2591,11 @@
         </is>
       </c>
       <c r="O20" t="n">
-        <v>18187914</v>
+        <v>17399442</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Mirian Lima</t>
+          <t>Eveny Silva</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -2607,17 +2604,21 @@
         </is>
       </c>
       <c r="R20" s="1" t="n">
-        <v>46204.75353515046</v>
+        <v>46204.75350494213</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr"/>
+          <t>NOSSO NOVO SUPERMERCADO</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr"/>
@@ -2641,17 +2642,17 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>Isabella Nascimento</t>
+          <t>Karina Santos</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>5417</v>
+        <v>5617</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2671,7 +2672,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2701,11 +2702,11 @@
         </is>
       </c>
       <c r="O21" t="n">
-        <v>17399442</v>
+        <v>17407953</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Eveny Silva</t>
+          <t>Jackson Silva</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -2714,14 +2715,14 @@
         </is>
       </c>
       <c r="R21" s="1" t="n">
-        <v>46204.75350494213</v>
+        <v>46204.75351072917</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2752,17 +2753,17 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>5617</v>
+        <v>6224</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2782,7 +2783,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -2812,7 +2813,7 @@
         </is>
       </c>
       <c r="O22" t="n">
-        <v>17407953</v>
+        <v>17689061</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
@@ -2825,7 +2826,7 @@
         </is>
       </c>
       <c r="R22" s="1" t="n">
-        <v>46204.75351072917</v>
+        <v>46204.75352068287</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -2869,11 +2870,11 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>6224</v>
+        <v>6278</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>EMPORIO DOS FRIOS LTDA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2883,7 +2884,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Real - Anual</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2893,7 +2894,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -2923,11 +2924,11 @@
         </is>
       </c>
       <c r="O23" t="n">
-        <v>17689061</v>
+        <v>17539888</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Jackson Silva</t>
+          <t>Isabela Lemos</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -2936,14 +2937,14 @@
         </is>
       </c>
       <c r="R23" s="1" t="n">
-        <v>46204.75352068287</v>
+        <v>46204.75352175926</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2974,17 +2975,17 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>6278</v>
+        <v>6704</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS LTDA</t>
+          <t>TECNO COM INFORMATICA LTDA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2994,7 +2995,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Federal - Lucro Real - Anual</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -3034,11 +3035,11 @@
         </is>
       </c>
       <c r="O24" t="n">
-        <v>17539888</v>
+        <v>17955432</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Isabela Lemos</t>
+          <t>Paulo Silva</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -3047,14 +3048,14 @@
         </is>
       </c>
       <c r="R24" s="1" t="n">
-        <v>46204.75352175926</v>
+        <v>46204.75353024306</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>TECNO COM</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3091,11 +3092,11 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>6704</v>
+        <v>6705</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>TECNO COM INFORMATICA LTDA</t>
+          <t>NARCIZO ALVES CORDEIRO</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3105,7 +3106,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -3145,7 +3146,7 @@
         </is>
       </c>
       <c r="O25" t="n">
-        <v>17955432</v>
+        <v>17955272</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
@@ -3158,7 +3159,7 @@
         </is>
       </c>
       <c r="R25" s="1" t="n">
-        <v>46204.75353024306</v>
+        <v>46204.7535309838</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -3202,11 +3203,11 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>6705</v>
+        <v>6779</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>NARCIZO ALVES CORDEIRO</t>
+          <t>CORDEIRO E CIA LTDA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3256,7 +3257,7 @@
         </is>
       </c>
       <c r="O26" t="n">
-        <v>17955272</v>
+        <v>18056830</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
@@ -3269,7 +3270,7 @@
         </is>
       </c>
       <c r="R26" s="1" t="n">
-        <v>46204.7535309838</v>
+        <v>46204.75353240741</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -3279,11 +3280,7 @@
           <t>TECNO COM</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+      <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr"/>
       <c r="X26" t="inlineStr"/>
@@ -3313,11 +3310,11 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>6779</v>
+        <v>6885</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CORDEIRO E CIA LTDA</t>
+          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3367,11 +3364,11 @@
         </is>
       </c>
       <c r="O27" t="n">
-        <v>18056830</v>
+        <v>18128901</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Paulo Silva</t>
+          <t>Isabela Lemos</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -3380,14 +3377,14 @@
         </is>
       </c>
       <c r="R27" s="1" t="n">
-        <v>46204.75353240741</v>
+        <v>46204.75353278935</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U27" t="inlineStr"/>
@@ -3420,11 +3417,11 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>6885</v>
+        <v>6628</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3439,7 +3436,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3448,57 +3445,61 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>11297</v>
+        <v>11817</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Retorno do Check-List</t>
+          <t>Alteração dados cadastrais</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" s="1" t="n">
-        <v>46218</v>
+        <v>46205</v>
       </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
-          <t>06/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
       <c r="O28" t="n">
-        <v>18128901</v>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>Isabela Lemos</t>
-        </is>
-      </c>
+        <v>18199226</v>
+      </c>
+      <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr">
         <is>
           <t>Baixado</t>
         </is>
       </c>
       <c r="R28" s="1" t="n">
-        <v>46204.75353278935</v>
+        <v>46205.599529375</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
+          <t xml:space="preserve">GTG </t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Aplicação de promoção. - Data Comentário: 02/07/2026 11:13</t>
+        </is>
+      </c>
       <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr"/>
       <c r="Y28" t="inlineStr"/>
@@ -3507,7 +3508,7 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>Juan Rodrigues</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr"/>
@@ -3519,19 +3520,15 @@
           <t>Tarefa</t>
         </is>
       </c>
-      <c r="AG28" t="inlineStr">
-        <is>
-          <t>Fernanda Araujo</t>
-        </is>
-      </c>
+      <c r="AG28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>6628</v>
+        <v>6962</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3541,21 +3538,21 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Reynaldo Santos</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>11817</v>
+        <v>9791</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -3567,47 +3564,48 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Alteração dados cadastrais</t>
+          <t>Aplicação de Modelo - Pendente</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" s="1" t="n">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
       <c r="O29" t="n">
-        <v>18199226</v>
-      </c>
-      <c r="P29" t="inlineStr"/>
+        <v>18186541</v>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Mauricio Lermen</t>
+        </is>
+      </c>
       <c r="Q29" t="inlineStr">
         <is>
           <t>Baixado</t>
         </is>
       </c>
       <c r="R29" s="1" t="n">
-        <v>46205.599529375</v>
+        <v>46218.65692637731</v>
       </c>
       <c r="S29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>PROMOTORAS GYN</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr">
         <is>
-          <t>Aplicação de promoção. - Data Comentário: 02/07/2026 11:13</t>
+          <t>Sem informações para a realização da tarefa  
+Empresa de implantação, sem docs ou procurações. - Data Comentário: 24/06/2026 15:43</t>
         </is>
       </c>
       <c r="W29" t="inlineStr"/>
@@ -3618,7 +3616,7 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Mauricio Lermen</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr"/>
@@ -3634,11 +3632,11 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
+          <t>PROMOTORAS GYN LTDA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3688,7 +3686,7 @@
         </is>
       </c>
       <c r="O30" t="n">
-        <v>18186541</v>
+        <v>18186542</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
@@ -3701,7 +3699,7 @@
         </is>
       </c>
       <c r="R30" s="1" t="n">
-        <v>46218.65692637731</v>
+        <v>46218.6569265625</v>
       </c>
       <c r="S30" t="n">
         <v>12</v>
@@ -3742,11 +3740,11 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>6963</v>
+        <v>5417</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN LTDA</t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3766,11 +3764,11 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>9791</v>
+        <v>11815</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -3782,50 +3780,45 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Aplicação de Modelo - Pendente</t>
+          <t>Cálculo de férias individuais</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" s="1" t="n">
-        <v>46206</v>
+        <v>46204</v>
       </c>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
-          <t>06/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
       <c r="O31" t="n">
-        <v>18186542</v>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>Mauricio Lermen</t>
-        </is>
-      </c>
+        <v>18196299</v>
+      </c>
+      <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr">
         <is>
           <t>Baixado</t>
         </is>
       </c>
       <c r="R31" s="1" t="n">
-        <v>46218.6569265625</v>
+        <v>46204.71542079861</v>
       </c>
       <c r="S31" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>Sem informações para a realização da tarefa  
-Empresa de implantação, sem docs ou procurações. - Data Comentário: 24/06/2026 15:43</t>
-        </is>
-      </c>
+          <t>NOSSO NOVO SUPERMERCADO</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr"/>
       <c r="Y31" t="inlineStr"/>
@@ -3834,7 +3827,7 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>Mauricio Lermen</t>
+          <t>Mikael Teixeira</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr"/>
@@ -3904,7 +3897,7 @@
         </is>
       </c>
       <c r="O32" t="n">
-        <v>18196299</v>
+        <v>18196300</v>
       </c>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr">
@@ -3913,7 +3906,7 @@
         </is>
       </c>
       <c r="R32" s="1" t="n">
-        <v>46204.71542079861</v>
+        <v>46204.71542134259</v>
       </c>
       <c r="S32" t="n">
         <v>14</v>
@@ -3953,11 +3946,11 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>5417</v>
+        <v>6779</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>CORDEIRO E CIA LTDA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3967,7 +3960,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3977,7 +3970,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4007,7 +4000,7 @@
         </is>
       </c>
       <c r="O33" t="n">
-        <v>18196300</v>
+        <v>18195927</v>
       </c>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr">
@@ -4016,22 +4009,22 @@
         </is>
       </c>
       <c r="R33" s="1" t="n">
-        <v>46204.71542134259</v>
+        <v>46204.48446469908</v>
       </c>
       <c r="S33" t="n">
         <v>14</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr"/>
+          <t>TECNO COM</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Férias de 02/07/2026 a 10/07/2026. - Data Comentário: 01/07/2026 11:26</t>
+        </is>
+      </c>
       <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr"/>
       <c r="Y33" t="inlineStr"/>
@@ -4040,7 +4033,7 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>Mikael Teixeira</t>
+          <t>Kaique Souza</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr"/>
@@ -4056,11 +4049,11 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>6779</v>
+        <v>5417</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CORDEIRO E CIA LTDA</t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4070,7 +4063,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -4080,14 +4073,14 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>11815</v>
+        <v>5800</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>5776</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -4096,43 +4089,55 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Cálculo de férias individuais</t>
+          <t>CCT Lançamento Sd.508</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" s="1" t="n">
-        <v>46204</v>
-      </c>
-      <c r="M34" t="inlineStr"/>
+        <v>46205</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>00/2026</t>
         </is>
       </c>
       <c r="O34" t="n">
-        <v>18195927</v>
-      </c>
-      <c r="P34" t="inlineStr"/>
+        <v>17399013</v>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Mikael Teixeira</t>
+        </is>
+      </c>
       <c r="Q34" t="inlineStr">
         <is>
           <t>Baixado</t>
         </is>
       </c>
       <c r="R34" s="1" t="n">
-        <v>46204.48446469908</v>
+        <v>46205.75412240741</v>
       </c>
       <c r="S34" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr"/>
+          <t>NOSSO NOVO SUPERMERCADO</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>Férias de 02/07/2026 a 10/07/2026. - Data Comentário: 01/07/2026 11:26</t>
+          <t>2. Folha Processada aguardando OK do cliente para finalização   Previsão para conclusão dia 02/07/2026 - Data Comentário: 30/06/2026 15:03</t>
         </is>
       </c>
       <c r="W34" t="inlineStr"/>
@@ -4143,7 +4148,7 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>Kaique Souza</t>
+          <t>Mikael Teixeira</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr"/>
@@ -4159,11 +4164,11 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>5417</v>
+        <v>6224</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4183,14 +4188,14 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>5800</v>
+        <v>5859</v>
       </c>
       <c r="H35" t="n">
-        <v>5776</v>
+        <v>5786</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -4199,29 +4204,25 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>CCT Lançamento Sd.508</t>
+          <t>Contribuição Assistencial</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" s="1" t="n">
-        <v>46205</v>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>02/07/2026</t>
-        </is>
-      </c>
+        <v>46206</v>
+      </c>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
-          <t>00/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
       <c r="O35" t="n">
-        <v>17399013</v>
+        <v>17688763</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Mikael Teixeira</t>
+          <t>Tania Luz</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -4230,14 +4231,14 @@
         </is>
       </c>
       <c r="R35" s="1" t="n">
-        <v>46205.75412240741</v>
+        <v>46205.75458568287</v>
       </c>
       <c r="S35" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4245,11 +4246,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>2. Folha Processada aguardando OK do cliente para finalização   Previsão para conclusão dia 02/07/2026 - Data Comentário: 30/06/2026 15:03</t>
-        </is>
-      </c>
+      <c r="V35" t="inlineStr"/>
       <c r="W35" t="inlineStr"/>
       <c r="X35" t="inlineStr"/>
       <c r="Y35" t="inlineStr"/>
@@ -4258,7 +4255,7 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>Mikael Teixeira</t>
+          <t>Tania Luz</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr"/>
@@ -4267,18 +4264,22 @@
       <c r="AE35" t="inlineStr"/>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>Tarefa</t>
-        </is>
-      </c>
-      <c r="AG35" t="inlineStr"/>
+          <t>Imposto</t>
+        </is>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>Edivaldo Veiga</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>6224</v>
+        <v>6628</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -4288,17 +4289,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4328,11 +4329,11 @@
         </is>
       </c>
       <c r="O36" t="n">
-        <v>17688763</v>
+        <v>18052438</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Tania Luz</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -4341,14 +4342,14 @@
         </is>
       </c>
       <c r="R36" s="1" t="n">
-        <v>46205.75458568287</v>
+        <v>46206.44903752315</v>
       </c>
       <c r="S36" t="n">
         <v>12</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t xml:space="preserve">GTG </t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4365,7 +4366,7 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>Tania Luz</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr"/>
@@ -4379,17 +4380,17 @@
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>David Bragança</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>6628</v>
+        <v>6779</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>CORDEIRO E CIA LTDA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -4404,7 +4405,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -4439,34 +4440,26 @@
         </is>
       </c>
       <c r="O37" t="n">
-        <v>18052438</v>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>Jakeline Silva</t>
-        </is>
-      </c>
+        <v>18090166</v>
+      </c>
+      <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr">
         <is>
           <t>Baixado</t>
         </is>
       </c>
       <c r="R37" s="1" t="n">
-        <v>46206.44903752315</v>
+        <v>46199.48727971065</v>
       </c>
       <c r="S37" t="n">
         <v>12</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>TECNO COM</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr"/>
       <c r="X37" t="inlineStr"/>
@@ -4476,7 +4469,7 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Kaique Souza</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr"/>
@@ -4488,19 +4481,15 @@
           <t>Imposto</t>
         </is>
       </c>
-      <c r="AG37" t="inlineStr">
-        <is>
-          <t>David Bragança</t>
-        </is>
-      </c>
+      <c r="AG37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>6779</v>
+        <v>6885</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CORDEIRO E CIA LTDA</t>
+          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4550,23 +4539,27 @@
         </is>
       </c>
       <c r="O38" t="n">
-        <v>18090166</v>
-      </c>
-      <c r="P38" t="inlineStr"/>
+        <v>18157259</v>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Vitor Guedes</t>
+        </is>
+      </c>
       <c r="Q38" t="inlineStr">
         <is>
           <t>Baixado</t>
         </is>
       </c>
       <c r="R38" s="1" t="n">
-        <v>46199.48727971065</v>
+        <v>46205.69236453703</v>
       </c>
       <c r="S38" t="n">
         <v>12</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U38" t="inlineStr"/>
@@ -4579,7 +4572,7 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>Kaique Souza</t>
+          <t>Vitor Guedes</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr"/>
@@ -4591,15 +4584,19 @@
           <t>Imposto</t>
         </is>
       </c>
-      <c r="AG38" t="inlineStr"/>
+      <c r="AG38" t="inlineStr">
+        <is>
+          <t>David Bragança</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>6885</v>
+        <v>6945</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
+          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -4614,7 +4611,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4642,18 +4639,22 @@
       <c r="L39" s="1" t="n">
         <v>46206</v>
       </c>
-      <c r="M39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O39" t="n">
-        <v>18157259</v>
+        <v>18179094</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Vitor Guedes</t>
+          <t>Santos Karina</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -4662,18 +4663,23 @@
         </is>
       </c>
       <c r="R39" s="1" t="n">
-        <v>46205.69236453703</v>
+        <v>46209.43008613426</v>
       </c>
       <c r="S39" t="n">
         <v>12</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>BRASIL DISTRIBUIDORA</t>
         </is>
       </c>
       <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr"/>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 07/07/2026 
+cliente em implantação, em andamento - Data Comentário: 03/07/2026 17:19</t>
+        </is>
+      </c>
       <c r="W39" t="inlineStr"/>
       <c r="X39" t="inlineStr"/>
       <c r="Y39" t="inlineStr"/>
@@ -4682,7 +4688,7 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>Vitor Guedes</t>
+          <t>Santos Karina</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr"/>
@@ -4696,17 +4702,17 @@
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Leandro Matos</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>6945</v>
+        <v>6486</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
+          <t>PC GAMER GOIANIA LTDA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -4716,12 +4722,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -4730,10 +4736,10 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>5859</v>
+        <v>11542</v>
       </c>
       <c r="H40" t="n">
-        <v>5786</v>
+        <v>0</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -4742,29 +4748,25 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Contribuição Assistencial</t>
+          <t>Envio Arq. eConsignado Cliente</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" s="1" t="n">
-        <v>46206</v>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>07/07/2026</t>
-        </is>
-      </c>
+        <v>46204</v>
+      </c>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>06/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
       <c r="O40" t="n">
-        <v>18179094</v>
+        <v>16976370</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Santos Karina</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -4773,23 +4775,22 @@
         </is>
       </c>
       <c r="R40" s="1" t="n">
-        <v>46209.43008613426</v>
+        <v>46204.5600265625</v>
       </c>
       <c r="S40" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 07/07/2026 
-cliente em implantação, em andamento - Data Comentário: 03/07/2026 17:19</t>
-        </is>
-      </c>
+          <t>PC GAMER</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr"/>
       <c r="W40" t="inlineStr"/>
       <c r="X40" t="inlineStr"/>
       <c r="Y40" t="inlineStr"/>
@@ -4798,7 +4799,7 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>Santos Karina</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr"/>
@@ -4807,22 +4808,22 @@
       <c r="AE40" t="inlineStr"/>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Obrigação Acessória</t>
         </is>
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>Leandro Matos</t>
+          <t>David Bragança</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>6486</v>
+        <v>6548</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PC GAMER GOIANIA LTDA</t>
+          <t>GOIAS SILAGEM LTDA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -4872,11 +4873,11 @@
         </is>
       </c>
       <c r="O41" t="n">
-        <v>16976370</v>
+        <v>17222966</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Daniel Moraes</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -4885,14 +4886,14 @@
         </is>
       </c>
       <c r="R41" s="1" t="n">
-        <v>46204.5600265625</v>
+        <v>46196.71390480324</v>
       </c>
       <c r="S41" t="n">
         <v>14</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>PC GAMER</t>
+          <t>GOIAS SILAGEM</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4909,7 +4910,7 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Evellin Bispo</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr"/>
@@ -4929,11 +4930,11 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>6548</v>
+        <v>6703</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM LTDA</t>
+          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -4943,7 +4944,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4983,11 +4984,11 @@
         </is>
       </c>
       <c r="O42" t="n">
-        <v>17222966</v>
+        <v>18077183</v>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Daniel Moraes</t>
+          <t>Ana Marcelino</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -4996,14 +4997,14 @@
         </is>
       </c>
       <c r="R42" s="1" t="n">
-        <v>46196.71390480324</v>
+        <v>46198.70825575232</v>
       </c>
       <c r="S42" t="n">
         <v>14</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM</t>
+          <t>LIMA MOTA</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -5020,7 +5021,7 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>Evellin Bispo</t>
+          <t>Elaine Assis</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr"/>
@@ -5034,17 +5035,17 @@
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>6703</v>
+        <v>6779</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
+          <t>CORDEIRO E CIA LTDA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -5054,7 +5055,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -5094,11 +5095,11 @@
         </is>
       </c>
       <c r="O43" t="n">
-        <v>18077183</v>
+        <v>18090270</v>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Ana Marcelino</t>
+          <t>Kaique Souza</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
@@ -5107,21 +5108,17 @@
         </is>
       </c>
       <c r="R43" s="1" t="n">
-        <v>46198.70825575232</v>
+        <v>46196.59280127315</v>
       </c>
       <c r="S43" t="n">
         <v>14</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>LIMA MOTA</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>TECNO COM</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr"/>
       <c r="V43" t="inlineStr"/>
       <c r="W43" t="inlineStr"/>
       <c r="X43" t="inlineStr"/>
@@ -5131,7 +5128,7 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>Elaine Assis</t>
+          <t>Kaique Souza</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr"/>
@@ -5151,11 +5148,11 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>6779</v>
+        <v>6949</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CORDEIRO E CIA LTDA</t>
+          <t>TEC GRUA LOCAÇÃO E COMERCIO DE EQUIPAMENTOS PARA CONSTRUÇÃO LTDA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -5165,7 +5162,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -5175,7 +5172,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Reynaldo Santos</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5205,11 +5202,11 @@
         </is>
       </c>
       <c r="O44" t="n">
-        <v>18090270</v>
+        <v>18190469</v>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Kaique Souza</t>
+          <t>Gabriela Peres</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -5218,14 +5215,14 @@
         </is>
       </c>
       <c r="R44" s="1" t="n">
-        <v>46196.59280127315</v>
+        <v>46204.41370118056</v>
       </c>
       <c r="S44" t="n">
         <v>14</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>TEC GRUA</t>
         </is>
       </c>
       <c r="U44" t="inlineStr"/>
@@ -5238,7 +5235,7 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>Kaique Souza</t>
+          <t>Santos Karina</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr"/>
@@ -5252,17 +5249,17 @@
       </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>Leandro Matos</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>6949</v>
+        <v>5417</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>TEC GRUA LOCAÇÃO E COMERCIO DE EQUIPAMENTOS PARA CONSTRUÇÃO LTDA</t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -5282,11 +5279,11 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>11542</v>
+        <v>9746</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -5298,25 +5295,29 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Envio Arq. eConsignado Cliente</t>
+          <t>eSocial – Fechamento Mensal</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" s="1" t="n">
-        <v>46204</v>
-      </c>
-      <c r="M45" t="inlineStr"/>
+        <v>46213</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
       <c r="O45" t="n">
-        <v>18190469</v>
+        <v>17399401</v>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Gabriela Peres</t>
+          <t>Mikael Teixeira</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -5325,18 +5326,27 @@
         </is>
       </c>
       <c r="R45" s="1" t="n">
-        <v>46204.41370118056</v>
+        <v>46213.6834903125</v>
       </c>
       <c r="S45" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>TEC GRUA</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr"/>
+          <t>NOSSO NOVO SUPERMERCADO</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 10/07/2026 
+está com diferenças de valores entre sistema x esocial, estamos regularizando - Data Comentário: 08/07/2026 17:11</t>
+        </is>
+      </c>
       <c r="W45" t="inlineStr"/>
       <c r="X45" t="inlineStr"/>
       <c r="Y45" t="inlineStr"/>
@@ -5345,7 +5355,7 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>Santos Karina</t>
+          <t>Mikael Teixeira</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr"/>
@@ -5354,22 +5364,18 @@
       <c r="AE45" t="inlineStr"/>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>Obrigação Acessória</t>
-        </is>
-      </c>
-      <c r="AG45" t="inlineStr">
-        <is>
-          <t>Leandro Matos</t>
-        </is>
-      </c>
+          <t>Tarefa</t>
+        </is>
+      </c>
+      <c r="AG45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>5417</v>
+        <v>5617</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -5389,7 +5395,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5412,22 +5418,18 @@
       <c r="L46" s="1" t="n">
         <v>46213</v>
       </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>10/07/2026</t>
-        </is>
-      </c>
+      <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O46" t="n">
-        <v>17399401</v>
+        <v>17407922</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Mikael Teixeira</t>
+          <t>Tania Luz</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -5436,14 +5438,14 @@
         </is>
       </c>
       <c r="R46" s="1" t="n">
-        <v>46213.6834903125</v>
+        <v>46217.3946746875</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5453,8 +5455,7 @@
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 10/07/2026 
-está com diferenças de valores entre sistema x esocial, estamos regularizando - Data Comentário: 08/07/2026 17:11</t>
+          <t>8. Serviços Suspensos. - Data Comentário: 08/07/2026 10:25</t>
         </is>
       </c>
       <c r="W46" t="inlineStr"/>
@@ -5465,7 +5466,7 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>Mikael Teixeira</t>
+          <t>Gabriel Amaral</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr"/>
@@ -5477,15 +5478,19 @@
           <t>Tarefa</t>
         </is>
       </c>
-      <c r="AG46" t="inlineStr"/>
+      <c r="AG46" t="inlineStr">
+        <is>
+          <t>Edivaldo Veiga</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>5617</v>
+        <v>6224</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -5505,7 +5510,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -5535,7 +5540,7 @@
         </is>
       </c>
       <c r="O47" t="n">
-        <v>17407922</v>
+        <v>17689040</v>
       </c>
       <c r="P47" t="inlineStr">
         <is>
@@ -5548,7 +5553,7 @@
         </is>
       </c>
       <c r="R47" s="1" t="n">
-        <v>46217.3946746875</v>
+        <v>46217.39654822917</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5596,11 +5601,11 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>6224</v>
+        <v>6404</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>SOLAR INVESTIMENTOS LTDA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -5610,7 +5615,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -5620,7 +5625,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -5643,18 +5648,22 @@
       <c r="L48" s="1" t="n">
         <v>46213</v>
       </c>
-      <c r="M48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O48" t="n">
-        <v>17689040</v>
+        <v>16962422</v>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Tania Luz</t>
+          <t>Jhenifer Tenorio</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -5663,14 +5672,14 @@
         </is>
       </c>
       <c r="R48" s="1" t="n">
-        <v>46217.39654822917</v>
+        <v>46209.71247704861</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>SOLAR INVESTIMENTOS</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5680,7 +5689,7 @@
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>8. Serviços Suspensos. - Data Comentário: 08/07/2026 10:25</t>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 08/07/2026 - Data Comentário: 06/07/2026 12:40</t>
         </is>
       </c>
       <c r="W48" t="inlineStr"/>
@@ -5691,7 +5700,7 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>Gabriel Amaral</t>
+          <t>Jhenifer Tenorio</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr"/>
@@ -5705,17 +5714,17 @@
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>6404</v>
+        <v>6486</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS LTDA</t>
+          <t>PC GAMER GOIANIA LTDA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -5725,7 +5734,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5769,11 +5778,11 @@
         </is>
       </c>
       <c r="O49" t="n">
-        <v>16962422</v>
+        <v>16976298</v>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Jhenifer Tenorio</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -5782,14 +5791,14 @@
         </is>
       </c>
       <c r="R49" s="1" t="n">
-        <v>46209.71247704861</v>
+        <v>46209.71499087963</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS</t>
+          <t>PC GAMER</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5799,7 +5808,8 @@
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 08/07/2026 - Data Comentário: 06/07/2026 12:40</t>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 08/07/2026 
+PREVISÃO DE FINALIZAÇÃO: 08/07/2026 - Data Comentário: 06/07/2026 10:43</t>
         </is>
       </c>
       <c r="W49" t="inlineStr"/>
@@ -5810,7 +5820,7 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>Jhenifer Tenorio</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr"/>
@@ -5824,17 +5834,17 @@
       </c>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>David Bragança</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>6486</v>
+        <v>6548</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>PC GAMER GOIANIA LTDA</t>
+          <t>GOIAS SILAGEM LTDA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -5888,11 +5898,11 @@
         </is>
       </c>
       <c r="O50" t="n">
-        <v>16976298</v>
+        <v>17222913</v>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Daniel Moraes</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
@@ -5901,14 +5911,14 @@
         </is>
       </c>
       <c r="R50" s="1" t="n">
-        <v>46209.71499087963</v>
+        <v>46211.48251296296</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>PC GAMER</t>
+          <t>GOIAS SILAGEM</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5919,7 +5929,7 @@
       <c r="V50" t="inlineStr">
         <is>
           <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 08/07/2026 
-PREVISÃO DE FINALIZAÇÃO: 08/07/2026 - Data Comentário: 06/07/2026 10:43</t>
+Previsão de conclusão em 08/07/2026. - Data Comentário: 07/07/2026 16:47</t>
         </is>
       </c>
       <c r="W50" t="inlineStr"/>
@@ -5930,7 +5940,7 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Daniel Moraes</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr"/>
@@ -5950,11 +5960,11 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM LTDA</t>
+          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -5969,7 +5979,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -6008,11 +6018,11 @@
         </is>
       </c>
       <c r="O51" t="n">
-        <v>17222913</v>
+        <v>18068609</v>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Daniel Moraes</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
@@ -6021,14 +6031,14 @@
         </is>
       </c>
       <c r="R51" s="1" t="n">
-        <v>46211.48251296296</v>
+        <v>46210.47222041667</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM</t>
+          <t xml:space="preserve">GTG </t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -6039,7 +6049,7 @@
       <c r="V51" t="inlineStr">
         <is>
           <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 08/07/2026 
-Previsão de conclusão em 08/07/2026. - Data Comentário: 07/07/2026 16:47</t>
+PREVISÃO DE FINALIZAÇÃO: 08/07/2026 - Data Comentário: 06/07/2026 10:43</t>
         </is>
       </c>
       <c r="W51" t="inlineStr"/>
@@ -6050,7 +6060,7 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>Daniel Moraes</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr"/>
@@ -6070,11 +6080,11 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -6084,7 +6094,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -6128,7 +6138,7 @@
         </is>
       </c>
       <c r="O52" t="n">
-        <v>18068609</v>
+        <v>18052528</v>
       </c>
       <c r="P52" t="inlineStr">
         <is>
@@ -6141,7 +6151,7 @@
         </is>
       </c>
       <c r="R52" s="1" t="n">
-        <v>46210.47222041667</v>
+        <v>46211.58264625</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6158,8 +6168,8 @@
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 08/07/2026 
-PREVISÃO DE FINALIZAÇÃO: 08/07/2026 - Data Comentário: 06/07/2026 10:43</t>
+          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 08/07/2026 
+EMPRESA SOLICITOU REABERTURA DA FOLHA PARA ALTERAÇÃO NO COLABORADOR TSN : Maycon Gomes da Silva. AGUARDANDO FECHAMENTO ESOCIAL PARA BAIXA. - Data Comentário: 08/07/2026 09:12</t>
         </is>
       </c>
       <c r="W52" t="inlineStr"/>
@@ -6190,11 +6200,11 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>6628</v>
+        <v>6703</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -6204,12 +6214,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -6239,7 +6249,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -6248,11 +6258,11 @@
         </is>
       </c>
       <c r="O53" t="n">
-        <v>18052528</v>
+        <v>18077161</v>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Ana Marcelino</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
@@ -6261,14 +6271,14 @@
         </is>
       </c>
       <c r="R53" s="1" t="n">
-        <v>46211.58264625</v>
+        <v>46210.48132625</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
+          <t>LIMA MOTA</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6278,8 +6288,8 @@
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 08/07/2026 
-EMPRESA SOLICITOU REABERTURA DA FOLHA PARA ALTERAÇÃO NO COLABORADOR TSN : Maycon Gomes da Silva. AGUARDANDO FECHAMENTO ESOCIAL PARA BAIXA. - Data Comentário: 08/07/2026 09:12</t>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 07/07/2026 
+Previsão de conclusão 07/07/2026. - Data Comentário: 07/07/2026 10:22</t>
         </is>
       </c>
       <c r="W53" t="inlineStr"/>
@@ -6290,7 +6300,7 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Elaine Assis</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr"/>
@@ -6304,17 +6314,17 @@
       </c>
       <c r="AG53" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>6703</v>
+        <v>6779</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
+          <t>CORDEIRO E CIA LTDA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -6324,7 +6334,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -6359,7 +6369,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -6368,11 +6378,11 @@
         </is>
       </c>
       <c r="O54" t="n">
-        <v>18077161</v>
+        <v>18090248</v>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Ana Marcelino</t>
+          <t>Kaique Souza</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
@@ -6381,25 +6391,21 @@
         </is>
       </c>
       <c r="R54" s="1" t="n">
-        <v>46210.48132625</v>
+        <v>46210.45896016204</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>LIMA MOTA</t>
-        </is>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>TECNO COM</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr"/>
       <c r="V54" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 07/07/2026 
-Previsão de conclusão 07/07/2026. - Data Comentário: 07/07/2026 10:22</t>
+          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 10/07/2026 
+ESocial será baixado no vencimento para evitar retificações por solicitações do cliente. - Data Comentário: 03/07/2026 14:17</t>
         </is>
       </c>
       <c r="W54" t="inlineStr"/>
@@ -6410,7 +6416,7 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>Elaine Assis</t>
+          <t>Kaique Souza</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr"/>
@@ -6430,11 +6436,11 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>6779</v>
+        <v>6885</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CORDEIRO E CIA LTDA</t>
+          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -6479,7 +6485,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -6488,11 +6494,11 @@
         </is>
       </c>
       <c r="O55" t="n">
-        <v>18090248</v>
+        <v>18157325</v>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Kaique Souza</t>
+          <t>Vitor Guedes</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
@@ -6501,21 +6507,21 @@
         </is>
       </c>
       <c r="R55" s="1" t="n">
-        <v>46210.45896016204</v>
+        <v>46210.72289299768</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U55" t="inlineStr"/>
       <c r="V55" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 10/07/2026 
-ESocial será baixado no vencimento para evitar retificações por solicitações do cliente. - Data Comentário: 03/07/2026 14:17</t>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 07/07/2026 
+PREVISÃO DE CONCLUSÃO: 07/07/2026 - Data Comentário: 07/07/2026 13:13</t>
         </is>
       </c>
       <c r="W55" t="inlineStr"/>
@@ -6526,7 +6532,7 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>Kaique Souza</t>
+          <t>Vitor Guedes</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr"/>
@@ -6540,17 +6546,17 @@
       </c>
       <c r="AG55" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>David Bragança</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>6885</v>
+        <v>6945</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
+          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -6565,7 +6571,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -6595,7 +6601,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -6604,11 +6610,11 @@
         </is>
       </c>
       <c r="O56" t="n">
-        <v>18157325</v>
+        <v>18179152</v>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Vitor Guedes</t>
+          <t>Santos Karina</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
@@ -6617,21 +6623,21 @@
         </is>
       </c>
       <c r="R56" s="1" t="n">
-        <v>46210.72289299768</v>
+        <v>46216.74133621528</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>BRASIL DISTRIBUIDORA</t>
         </is>
       </c>
       <c r="U56" t="inlineStr"/>
       <c r="V56" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 07/07/2026 
-PREVISÃO DE CONCLUSÃO: 07/07/2026 - Data Comentário: 07/07/2026 13:13</t>
+          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 13/07/2026 
+Empresa Implantação em processamento. - Data Comentário: 10/07/2026 17:01</t>
         </is>
       </c>
       <c r="W56" t="inlineStr"/>
@@ -6642,7 +6648,7 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>Vitor Guedes</t>
+          <t>Santos Karina</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr"/>
@@ -6656,17 +6662,17 @@
       </c>
       <c r="AG56" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Leandro Matos</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>6945</v>
+        <v>6279</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
+          <t>DIENNYFER DA S PEREIRA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -6676,21 +6682,21 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>9746</v>
+        <v>10905</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -6702,7 +6708,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>eSocial – Fechamento Mensal</t>
+          <t>eSocial - Fechamento SM</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -6711,7 +6717,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -6720,34 +6726,34 @@
         </is>
       </c>
       <c r="O57" t="n">
-        <v>18179152</v>
-      </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>Santos Karina</t>
-        </is>
-      </c>
+        <v>18195935</v>
+      </c>
+      <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr">
         <is>
           <t>Baixado</t>
         </is>
       </c>
       <c r="R57" s="1" t="n">
-        <v>46216.74133621528</v>
+        <v>46211.59005767361</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA</t>
-        </is>
-      </c>
-      <c r="U57" t="inlineStr"/>
+          <t>EMPORIO DOS FRIOS</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 13/07/2026 
-Empresa Implantação em processamento. - Data Comentário: 10/07/2026 17:01</t>
+          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 10/07/2026 
+Chamado aberto para a Controladoria para realização da baixa - nº 80915. - Data Comentário: 08/07/2026 13:52</t>
         </is>
       </c>
       <c r="W57" t="inlineStr"/>
@@ -6758,7 +6764,7 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>Santos Karina</t>
+          <t>Gabriel Amaral</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr"/>
@@ -6767,22 +6773,18 @@
       <c r="AE57" t="inlineStr"/>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>Tarefa</t>
-        </is>
-      </c>
-      <c r="AG57" t="inlineStr">
-        <is>
-          <t>Leandro Matos</t>
-        </is>
-      </c>
+          <t>Obrigação Acessória</t>
+        </is>
+      </c>
+      <c r="AG57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>6279</v>
+        <v>5417</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>DIENNYFER DA S PEREIRA</t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -6792,7 +6794,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -6802,14 +6804,14 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>10905</v>
+        <v>5905</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>5784</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -6818,16 +6820,16 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>eSocial - Fechamento SM</t>
+          <t>Folha Mensal/Pró-Labore</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" s="1" t="n">
-        <v>46213</v>
+        <v>46206</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -6836,23 +6838,27 @@
         </is>
       </c>
       <c r="O58" t="n">
-        <v>18195935</v>
-      </c>
-      <c r="P58" t="inlineStr"/>
+        <v>17399094</v>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Mikael Teixeira</t>
+        </is>
+      </c>
       <c r="Q58" t="inlineStr">
         <is>
           <t>Baixado</t>
         </is>
       </c>
       <c r="R58" s="1" t="n">
-        <v>46211.59005767361</v>
+        <v>46206.54816894676</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>NOSSO NOVO SUPERMERCADO</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6862,8 +6868,7 @@
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 10/07/2026 
-Chamado aberto para a Controladoria para realização da baixa - nº 80915. - Data Comentário: 08/07/2026 13:52</t>
+          <t>3. Folha, Aguardando Resumo p/ Processamento   Previsão para conclusão dia 03/07/2026 - Data Comentário: 30/06/2026 15:48</t>
         </is>
       </c>
       <c r="W58" t="inlineStr"/>
@@ -6874,7 +6879,7 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>Gabriel Amaral</t>
+          <t>Mikael Teixeira</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr"/>
@@ -6890,11 +6895,11 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>5417</v>
+        <v>5617</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -6914,7 +6919,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -6937,22 +6942,18 @@
       <c r="L59" s="1" t="n">
         <v>46206</v>
       </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
+      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O59" t="n">
-        <v>17399094</v>
+        <v>17407675</v>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Mikael Teixeira</t>
+          <t>Tania Luz</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
@@ -6961,14 +6962,14 @@
         </is>
       </c>
       <c r="R59" s="1" t="n">
-        <v>46206.54816894676</v>
+        <v>46217.39487814814</v>
       </c>
       <c r="S59" t="n">
         <v>12</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6978,7 +6979,7 @@
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>3. Folha, Aguardando Resumo p/ Processamento   Previsão para conclusão dia 03/07/2026 - Data Comentário: 30/06/2026 15:48</t>
+          <t>8. Serviços Suspensos. - Data Comentário: 08/07/2026 10:25</t>
         </is>
       </c>
       <c r="W59" t="inlineStr"/>
@@ -6989,7 +6990,7 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>Mikael Teixeira</t>
+          <t>Gabriel Amaral</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr"/>
@@ -7001,15 +7002,19 @@
           <t>Obrigação Acessória</t>
         </is>
       </c>
-      <c r="AG59" t="inlineStr"/>
+      <c r="AG59" t="inlineStr">
+        <is>
+          <t>Edivaldo Veiga</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>5617</v>
+        <v>6224</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -7029,7 +7034,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7059,7 +7064,7 @@
         </is>
       </c>
       <c r="O60" t="n">
-        <v>17407675</v>
+        <v>17688813</v>
       </c>
       <c r="P60" t="inlineStr">
         <is>
@@ -7072,7 +7077,7 @@
         </is>
       </c>
       <c r="R60" s="1" t="n">
-        <v>46217.39487814814</v>
+        <v>46217.39640148148</v>
       </c>
       <c r="S60" t="n">
         <v>12</v>
@@ -7120,11 +7125,11 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>6224</v>
+        <v>6486</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>PC GAMER GOIANIA LTDA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -7144,7 +7149,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7167,18 +7172,22 @@
       <c r="L61" s="1" t="n">
         <v>46206</v>
       </c>
-      <c r="M61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O61" t="n">
-        <v>17688813</v>
+        <v>16976084</v>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Tania Luz</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
@@ -7187,14 +7196,14 @@
         </is>
       </c>
       <c r="R61" s="1" t="n">
-        <v>46217.39640148148</v>
+        <v>46206.55861924768</v>
       </c>
       <c r="S61" t="n">
         <v>12</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>PC GAMER</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -7204,7 +7213,7 @@
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>8. Serviços Suspensos. - Data Comentário: 08/07/2026 10:25</t>
+          <t>2. Folha Processada aguardando OK do cliente para finalização   Previsão para conclusão dia 03/07/2026 - Data Comentário: 02/07/2026 15:13</t>
         </is>
       </c>
       <c r="W61" t="inlineStr"/>
@@ -7215,7 +7224,7 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>Gabriel Amaral</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr"/>
@@ -7229,17 +7238,17 @@
       </c>
       <c r="AG61" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>David Bragança</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>6486</v>
+        <v>6627</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>PC GAMER GOIANIA LTDA</t>
+          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -7254,7 +7263,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -7293,7 +7302,7 @@
         </is>
       </c>
       <c r="O62" t="n">
-        <v>16976084</v>
+        <v>18068575</v>
       </c>
       <c r="P62" t="inlineStr">
         <is>
@@ -7306,14 +7315,14 @@
         </is>
       </c>
       <c r="R62" s="1" t="n">
-        <v>46206.55861924768</v>
+        <v>46206.67165491898</v>
       </c>
       <c r="S62" t="n">
         <v>12</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>PC GAMER</t>
+          <t xml:space="preserve">GTG </t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7323,7 +7332,7 @@
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2. Folha Processada aguardando OK do cliente para finalização   Previsão para conclusão dia 03/07/2026 - Data Comentário: 02/07/2026 15:13</t>
+          <t>2. Folha Processada aguardando OK do cliente para finalização  Previsão para conclusão dia 03/07/2026 - Data Comentário: 03/07/2026 09:21</t>
         </is>
       </c>
       <c r="W62" t="inlineStr"/>
@@ -7354,11 +7363,11 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -7368,7 +7377,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -7412,7 +7421,7 @@
         </is>
       </c>
       <c r="O63" t="n">
-        <v>18068575</v>
+        <v>18052494</v>
       </c>
       <c r="P63" t="inlineStr">
         <is>
@@ -7425,7 +7434,7 @@
         </is>
       </c>
       <c r="R63" s="1" t="n">
-        <v>46206.67165491898</v>
+        <v>46206.67202474537</v>
       </c>
       <c r="S63" t="n">
         <v>12</v>
@@ -7473,11 +7482,11 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>6628</v>
+        <v>6703</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -7487,12 +7496,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -7531,11 +7540,11 @@
         </is>
       </c>
       <c r="O64" t="n">
-        <v>18052494</v>
+        <v>18077130</v>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Ana Marcelino</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
@@ -7544,14 +7553,14 @@
         </is>
       </c>
       <c r="R64" s="1" t="n">
-        <v>46206.67202474537</v>
+        <v>46206.62892094907</v>
       </c>
       <c r="S64" t="n">
         <v>12</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
+          <t>LIMA MOTA</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7561,7 +7570,7 @@
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2. Folha Processada aguardando OK do cliente para finalização  Previsão para conclusão dia 03/07/2026 - Data Comentário: 03/07/2026 09:21</t>
+          <t>2. Folha Processada aguardando OK do cliente para finalização   Previsão para conclusão dia 03/07/2026 - Data Comentário: 02/07/2026 17:14</t>
         </is>
       </c>
       <c r="W64" t="inlineStr"/>
@@ -7572,7 +7581,7 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Elaine Assis</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr"/>
@@ -7586,17 +7595,17 @@
       </c>
       <c r="AG64" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>6703</v>
+        <v>6779</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
+          <t>CORDEIRO E CIA LTDA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -7606,7 +7615,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -7641,7 +7650,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -7650,11 +7659,11 @@
         </is>
       </c>
       <c r="O65" t="n">
-        <v>18077130</v>
+        <v>18090217</v>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Ana Marcelino</t>
+          <t>Kaique Souza</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
@@ -7663,24 +7672,20 @@
         </is>
       </c>
       <c r="R65" s="1" t="n">
-        <v>46206.62892094907</v>
+        <v>46206.64427289352</v>
       </c>
       <c r="S65" t="n">
         <v>12</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>LIMA MOTA</t>
-        </is>
-      </c>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>TECNO COM</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr"/>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2. Folha Processada aguardando OK do cliente para finalização   Previsão para conclusão dia 03/07/2026 - Data Comentário: 02/07/2026 17:14</t>
+          <t>2. Folha Processada aguardando OK do cliente para finalização   Previsão para conclusão dia 06/07/2026 - Data Comentário: 03/07/2026 14:18</t>
         </is>
       </c>
       <c r="W65" t="inlineStr"/>
@@ -7691,7 +7696,7 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>Elaine Assis</t>
+          <t>Kaique Souza</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr"/>
@@ -7711,11 +7716,11 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>6779</v>
+        <v>6885</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CORDEIRO E CIA LTDA</t>
+          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -7760,7 +7765,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -7769,11 +7774,11 @@
         </is>
       </c>
       <c r="O66" t="n">
-        <v>18090217</v>
+        <v>18157300</v>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Kaique Souza</t>
+          <t>Vitor Guedes</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
@@ -7782,20 +7787,20 @@
         </is>
       </c>
       <c r="R66" s="1" t="n">
-        <v>46206.64427289352</v>
+        <v>46205.6924828125</v>
       </c>
       <c r="S66" t="n">
         <v>12</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U66" t="inlineStr"/>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2. Folha Processada aguardando OK do cliente para finalização   Previsão para conclusão dia 06/07/2026 - Data Comentário: 03/07/2026 14:18</t>
+          <t>2. Folha Processada aguardando OK do cliente para finalização   Previsão para conclusão dia 02/07/2026 - Data Comentário: 02/07/2026 10:31</t>
         </is>
       </c>
       <c r="W66" t="inlineStr"/>
@@ -7806,7 +7811,7 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>Kaique Souza</t>
+          <t>Vitor Guedes</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr"/>
@@ -7820,17 +7825,17 @@
       </c>
       <c r="AG66" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>David Bragança</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>6885</v>
+        <v>6945</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
+          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -7845,7 +7850,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -7875,7 +7880,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -7884,11 +7889,11 @@
         </is>
       </c>
       <c r="O67" t="n">
-        <v>18157300</v>
+        <v>18179130</v>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Vitor Guedes</t>
+          <t>Santos Karina</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
@@ -7897,20 +7902,20 @@
         </is>
       </c>
       <c r="R67" s="1" t="n">
-        <v>46205.6924828125</v>
+        <v>46206.69765491898</v>
       </c>
       <c r="S67" t="n">
         <v>12</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>BRASIL DISTRIBUIDORA</t>
         </is>
       </c>
       <c r="U67" t="inlineStr"/>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2. Folha Processada aguardando OK do cliente para finalização   Previsão para conclusão dia 02/07/2026 - Data Comentário: 02/07/2026 10:31</t>
+          <t>2. Folha Processada aguardando OK do cliente para finalização   Previsão para conclusão dia 03/07/2026 - Data Comentário: 03/07/2026 16:19</t>
         </is>
       </c>
       <c r="W67" t="inlineStr"/>
@@ -7921,7 +7926,7 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>Vitor Guedes</t>
+          <t>Santos Karina</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr"/>
@@ -7935,17 +7940,17 @@
       </c>
       <c r="AG67" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Leandro Matos</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>6945</v>
+        <v>5417</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -7955,21 +7960,21 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>5905</v>
+        <v>5853</v>
       </c>
       <c r="H68" t="n">
         <v>5784</v>
@@ -7981,29 +7986,25 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Folha Mensal/Pró-Labore</t>
+          <t>FOPAG Impressão PDF</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
       <c r="L68" s="1" t="n">
-        <v>46206</v>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
+        <v>46210</v>
+      </c>
+      <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O68" t="n">
-        <v>18179130</v>
+        <v>17399034</v>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Santos Karina</t>
+          <t>Mikael Teixeira</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
@@ -8012,22 +8013,22 @@
         </is>
       </c>
       <c r="R68" s="1" t="n">
-        <v>46206.69765491898</v>
+        <v>46206.65603582176</v>
       </c>
       <c r="S68" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA</t>
-        </is>
-      </c>
-      <c r="U68" t="inlineStr"/>
-      <c r="V68" t="inlineStr">
-        <is>
-          <t>2. Folha Processada aguardando OK do cliente para finalização   Previsão para conclusão dia 03/07/2026 - Data Comentário: 03/07/2026 16:19</t>
-        </is>
-      </c>
+          <t>NOSSO NOVO SUPERMERCADO</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr"/>
       <c r="W68" t="inlineStr"/>
       <c r="X68" t="inlineStr"/>
       <c r="Y68" t="inlineStr"/>
@@ -8036,7 +8037,7 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>Santos Karina</t>
+          <t>Mikael Teixeira</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr"/>
@@ -8045,22 +8046,18 @@
       <c r="AE68" t="inlineStr"/>
       <c r="AF68" t="inlineStr">
         <is>
-          <t>Obrigação Acessória</t>
-        </is>
-      </c>
-      <c r="AG68" t="inlineStr">
-        <is>
-          <t>Leandro Matos</t>
-        </is>
-      </c>
+          <t>Tarefa</t>
+        </is>
+      </c>
+      <c r="AG68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>5417</v>
+        <v>5617</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -8080,7 +8077,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8110,11 +8107,11 @@
         </is>
       </c>
       <c r="O69" t="n">
-        <v>17399034</v>
+        <v>17407635</v>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Mikael Teixeira</t>
+          <t>Tania Luz</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
@@ -8123,14 +8120,14 @@
         </is>
       </c>
       <c r="R69" s="1" t="n">
-        <v>46206.65603582176</v>
+        <v>46217.39498159722</v>
       </c>
       <c r="S69" t="n">
         <v>8</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -8138,7 +8135,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V69" t="inlineStr"/>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>8. Serviços Suspensos. - Data Comentário: 03/07/2026 08:40</t>
+        </is>
+      </c>
       <c r="W69" t="inlineStr"/>
       <c r="X69" t="inlineStr"/>
       <c r="Y69" t="inlineStr"/>
@@ -8147,7 +8148,7 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>Mikael Teixeira</t>
+          <t>Gabriel Amaral</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr"/>
@@ -8159,15 +8160,19 @@
           <t>Tarefa</t>
         </is>
       </c>
-      <c r="AG69" t="inlineStr"/>
+      <c r="AG69" t="inlineStr">
+        <is>
+          <t>Edivaldo Veiga</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>5617</v>
+        <v>6224</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -8187,7 +8192,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8217,7 +8222,7 @@
         </is>
       </c>
       <c r="O70" t="n">
-        <v>17407635</v>
+        <v>17688753</v>
       </c>
       <c r="P70" t="inlineStr">
         <is>
@@ -8230,7 +8235,7 @@
         </is>
       </c>
       <c r="R70" s="1" t="n">
-        <v>46217.39498159722</v>
+        <v>46217.39632554398</v>
       </c>
       <c r="S70" t="n">
         <v>8</v>
@@ -8247,7 +8252,7 @@
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>8. Serviços Suspensos. - Data Comentário: 03/07/2026 08:40</t>
+          <t>8. Serviços Suspensos. - Data Comentário: 03/07/2026 08:39</t>
         </is>
       </c>
       <c r="W70" t="inlineStr"/>
@@ -8278,11 +8283,11 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>6224</v>
+        <v>6486</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>PC GAMER GOIANIA LTDA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -8302,7 +8307,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8332,11 +8337,11 @@
         </is>
       </c>
       <c r="O71" t="n">
-        <v>17688753</v>
+        <v>16976044</v>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Tania Luz</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
@@ -8345,14 +8350,14 @@
         </is>
       </c>
       <c r="R71" s="1" t="n">
-        <v>46217.39632554398</v>
+        <v>46209.41001810185</v>
       </c>
       <c r="S71" t="n">
         <v>8</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>PC GAMER</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -8360,11 +8365,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V71" t="inlineStr">
-        <is>
-          <t>8. Serviços Suspensos. - Data Comentário: 03/07/2026 08:39</t>
-        </is>
-      </c>
+      <c r="V71" t="inlineStr"/>
       <c r="W71" t="inlineStr"/>
       <c r="X71" t="inlineStr"/>
       <c r="Y71" t="inlineStr"/>
@@ -8373,7 +8374,7 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>Gabriel Amaral</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr"/>
@@ -8387,17 +8388,17 @@
       </c>
       <c r="AG71" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>David Bragança</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>6486</v>
+        <v>6627</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>PC GAMER GOIANIA LTDA</t>
+          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -8412,7 +8413,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -8447,7 +8448,7 @@
         </is>
       </c>
       <c r="O72" t="n">
-        <v>16976044</v>
+        <v>18068508</v>
       </c>
       <c r="P72" t="inlineStr">
         <is>
@@ -8460,14 +8461,14 @@
         </is>
       </c>
       <c r="R72" s="1" t="n">
-        <v>46209.41001810185</v>
+        <v>46209.41001846065</v>
       </c>
       <c r="S72" t="n">
         <v>8</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>PC GAMER</t>
+          <t xml:space="preserve">GTG </t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -8504,11 +8505,11 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -8518,7 +8519,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -8558,7 +8559,7 @@
         </is>
       </c>
       <c r="O73" t="n">
-        <v>18068508</v>
+        <v>18052427</v>
       </c>
       <c r="P73" t="inlineStr">
         <is>
@@ -8571,7 +8572,7 @@
         </is>
       </c>
       <c r="R73" s="1" t="n">
-        <v>46209.41001846065</v>
+        <v>46209.41001900463</v>
       </c>
       <c r="S73" t="n">
         <v>8</v>
@@ -8615,11 +8616,11 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>6628</v>
+        <v>6703</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -8629,12 +8630,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -8669,11 +8670,11 @@
         </is>
       </c>
       <c r="O74" t="n">
-        <v>18052427</v>
+        <v>18077089</v>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Ana Marcelino</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
@@ -8682,14 +8683,14 @@
         </is>
       </c>
       <c r="R74" s="1" t="n">
-        <v>46209.41001900463</v>
+        <v>46206.62881552083</v>
       </c>
       <c r="S74" t="n">
         <v>8</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
+          <t>LIMA MOTA</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -8706,7 +8707,7 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Elaine Assis</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr"/>
@@ -8720,17 +8721,17 @@
       </c>
       <c r="AG74" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>6703</v>
+        <v>6779</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
+          <t>CORDEIRO E CIA LTDA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -8740,7 +8741,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -8773,18 +8774,22 @@
       <c r="L75" s="1" t="n">
         <v>46210</v>
       </c>
-      <c r="M75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
       <c r="N75" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O75" t="n">
-        <v>18077089</v>
+        <v>18090156</v>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Ana Marcelino</t>
+          <t>Kaique Souza</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
@@ -8793,22 +8798,22 @@
         </is>
       </c>
       <c r="R75" s="1" t="n">
-        <v>46206.62881552083</v>
+        <v>46206.64398119213</v>
       </c>
       <c r="S75" t="n">
         <v>8</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>LIMA MOTA</t>
-        </is>
-      </c>
-      <c r="U75" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="V75" t="inlineStr"/>
+          <t>TECNO COM</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr"/>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>2. Folha Processada aguardando OK do cliente para finalização   Previsão para conclusão dia 06/07/2026 - Data Comentário: 03/07/2026 14:17</t>
+        </is>
+      </c>
       <c r="W75" t="inlineStr"/>
       <c r="X75" t="inlineStr"/>
       <c r="Y75" t="inlineStr"/>
@@ -8817,7 +8822,7 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>Elaine Assis</t>
+          <t>Kaique Souza</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr"/>
@@ -8837,11 +8842,11 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>6779</v>
+        <v>6885</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>CORDEIRO E CIA LTDA</t>
+          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -8884,22 +8889,18 @@
       <c r="L76" s="1" t="n">
         <v>46210</v>
       </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>06/07/2026</t>
-        </is>
-      </c>
+      <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O76" t="n">
-        <v>18090156</v>
+        <v>18157251</v>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Kaique Souza</t>
+          <t>Vitor Guedes</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
@@ -8908,22 +8909,18 @@
         </is>
       </c>
       <c r="R76" s="1" t="n">
-        <v>46206.64398119213</v>
+        <v>46209.55182975694</v>
       </c>
       <c r="S76" t="n">
         <v>8</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U76" t="inlineStr"/>
-      <c r="V76" t="inlineStr">
-        <is>
-          <t>2. Folha Processada aguardando OK do cliente para finalização   Previsão para conclusão dia 06/07/2026 - Data Comentário: 03/07/2026 14:17</t>
-        </is>
-      </c>
+      <c r="V76" t="inlineStr"/>
       <c r="W76" t="inlineStr"/>
       <c r="X76" t="inlineStr"/>
       <c r="Y76" t="inlineStr"/>
@@ -8932,7 +8929,7 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>Kaique Souza</t>
+          <t>Vitor Guedes</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr"/>
@@ -8946,17 +8943,17 @@
       </c>
       <c r="AG76" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>David Bragança</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>6885</v>
+        <v>6945</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
+          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -8971,7 +8968,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -9006,11 +9003,11 @@
         </is>
       </c>
       <c r="O77" t="n">
-        <v>18157251</v>
+        <v>18179087</v>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Vitor Guedes</t>
+          <t>Santos Karina</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
@@ -9019,14 +9016,14 @@
         </is>
       </c>
       <c r="R77" s="1" t="n">
-        <v>46209.55182975694</v>
+        <v>46211.39936383102</v>
       </c>
       <c r="S77" t="n">
         <v>8</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>BRASIL DISTRIBUIDORA</t>
         </is>
       </c>
       <c r="U77" t="inlineStr"/>
@@ -9039,7 +9036,7 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>Vitor Guedes</t>
+          <t>Santos Karina</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr"/>
@@ -9053,17 +9050,17 @@
       </c>
       <c r="AG77" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Leandro Matos</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>6945</v>
+        <v>5417</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -9073,24 +9070,24 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>5853</v>
+        <v>5867</v>
       </c>
       <c r="H78" t="n">
-        <v>5784</v>
+        <v>5786</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -9099,25 +9096,29 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>FOPAG Impressão PDF</t>
+          <t>GFD - FGTS Digital Mensal</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
       <c r="L78" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="M78" t="inlineStr"/>
+        <v>46218</v>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>15/07/2026</t>
+        </is>
+      </c>
       <c r="N78" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O78" t="n">
-        <v>18179087</v>
+        <v>17399054</v>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Santos Karina</t>
+          <t>Mikael Teixeira</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
@@ -9126,18 +9127,27 @@
         </is>
       </c>
       <c r="R78" s="1" t="n">
-        <v>46211.39936383102</v>
+        <v>46218.71253230324</v>
       </c>
       <c r="S78" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA</t>
-        </is>
-      </c>
-      <c r="U78" t="inlineStr"/>
-      <c r="V78" t="inlineStr"/>
+          <t>NOSSO NOVO SUPERMERCADO</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 15/07/2026 
+em processamento - Data Comentário: 14/07/2026 18:00</t>
+        </is>
+      </c>
       <c r="W78" t="inlineStr"/>
       <c r="X78" t="inlineStr"/>
       <c r="Y78" t="inlineStr"/>
@@ -9146,7 +9156,7 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>Santos Karina</t>
+          <t>Mikael Teixeira</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr"/>
@@ -9155,14 +9165,10 @@
       <c r="AE78" t="inlineStr"/>
       <c r="AF78" t="inlineStr">
         <is>
-          <t>Tarefa</t>
-        </is>
-      </c>
-      <c r="AG78" t="inlineStr">
-        <is>
-          <t>Leandro Matos</t>
-        </is>
-      </c>
+          <t>Imposto</t>
+        </is>
+      </c>
+      <c r="AG78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">

--- a/dados/base/goias.xlsx
+++ b/dados/base/goias.xlsx
@@ -43011,7 +43011,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V386" t="inlineStr"/>
+      <c r="V386" t="inlineStr">
+        <is>
+          <t>Imposto enviado via SCI Report - Data Comentário: 16/07/2026 11:35</t>
+        </is>
+      </c>
       <c r="W386" t="inlineStr"/>
       <c r="X386" t="inlineStr"/>
       <c r="Y386" t="inlineStr"/>
@@ -64444,11 +64448,11 @@
     </row>
     <row r="591">
       <c r="A591" t="n">
-        <v>6279</v>
+        <v>6486</v>
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>DIENNYFER DA S PEREIRA</t>
+          <t>PC GAMER GOIANIA LTDA</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
@@ -64458,7 +64462,7 @@
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E591" t="inlineStr">
@@ -64468,7 +64472,7 @@
       </c>
       <c r="F591" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G591" t="n">
@@ -64498,7 +64502,7 @@
         </is>
       </c>
       <c r="O591" t="n">
-        <v>17646092</v>
+        <v>16976225</v>
       </c>
       <c r="P591" t="inlineStr">
         <is>
@@ -64516,7 +64520,7 @@
       </c>
       <c r="T591" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>PC GAMER</t>
         </is>
       </c>
       <c r="U591" t="inlineStr">
@@ -64524,7 +64528,13 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V591" t="inlineStr"/>
+      <c r="V591" t="inlineStr">
+        <is>
+          <t>Integração com Sistema de Análise 
+ICMS liberado, aguardo a validação do SPED Contribuições. 
+Data Simulação: 06/07/2026 18:42:09 - Data Comentário: 06/07/2026 19:12</t>
+        </is>
+      </c>
       <c r="W591" t="inlineStr"/>
       <c r="X591" t="inlineStr"/>
       <c r="Y591" t="inlineStr"/>
@@ -64549,11 +64559,11 @@
     </row>
     <row r="592">
       <c r="A592" t="n">
-        <v>6486</v>
+        <v>6627</v>
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>PC GAMER GOIANIA LTDA</t>
+          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
@@ -64568,7 +64578,7 @@
       </c>
       <c r="E592" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F592" t="inlineStr">
@@ -64577,24 +64587,24 @@
         </is>
       </c>
       <c r="G592" t="n">
-        <v>7025</v>
+        <v>946</v>
       </c>
       <c r="H592" t="n">
         <v>0</v>
       </c>
       <c r="I592" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="J592" t="inlineStr">
         <is>
-          <t>Movimento - Sistema de Análise</t>
+          <t>Confirm Rec - ICMS RPA</t>
         </is>
       </c>
       <c r="K592" t="inlineStr"/>
       <c r="L592" s="1" t="n">
-        <v>46226</v>
+        <v>46223</v>
       </c>
       <c r="M592" t="inlineStr"/>
       <c r="N592" t="inlineStr">
@@ -64603,11 +64613,11 @@
         </is>
       </c>
       <c r="O592" t="n">
-        <v>16976225</v>
+        <v>17042267</v>
       </c>
       <c r="P592" t="inlineStr">
         <is>
-          <t>Cristina Leite</t>
+          <t>Victoria Virgens</t>
         </is>
       </c>
       <c r="Q592" t="inlineStr">
@@ -64617,11 +64627,11 @@
       </c>
       <c r="R592" t="inlineStr"/>
       <c r="S592" t="n">
-        <v>-7</v>
+        <v>-4</v>
       </c>
       <c r="T592" t="inlineStr">
         <is>
-          <t>PC GAMER</t>
+          <t xml:space="preserve">GTG </t>
         </is>
       </c>
       <c r="U592" t="inlineStr">
@@ -64629,13 +64639,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V592" t="inlineStr">
-        <is>
-          <t>Integração com Sistema de Análise 
-ICMS liberado, aguardo a validação do SPED Contribuições. 
-Data Simulação: 06/07/2026 18:42:09 - Data Comentário: 06/07/2026 19:12</t>
-        </is>
-      </c>
+      <c r="V592" t="inlineStr"/>
       <c r="W592" t="inlineStr"/>
       <c r="X592" t="inlineStr"/>
       <c r="Y592" t="inlineStr"/>
@@ -64649,22 +64653,18 @@
       <c r="AE592" t="inlineStr"/>
       <c r="AF592" t="inlineStr">
         <is>
-          <t>Tarefa</t>
-        </is>
-      </c>
-      <c r="AG592" t="inlineStr">
-        <is>
-          <t>Ricardo Fischer</t>
-        </is>
-      </c>
+          <t>Imposto</t>
+        </is>
+      </c>
+      <c r="AG592" t="inlineStr"/>
     </row>
     <row r="593">
       <c r="A593" t="n">
-        <v>6627</v>
+        <v>6885</v>
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
+          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
@@ -64674,12 +64674,12 @@
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E593" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F593" t="inlineStr">
@@ -64688,7 +64688,7 @@
         </is>
       </c>
       <c r="G593" t="n">
-        <v>946</v>
+        <v>953</v>
       </c>
       <c r="H593" t="n">
         <v>0</v>
@@ -64700,12 +64700,12 @@
       </c>
       <c r="J593" t="inlineStr">
         <is>
-          <t>Confirm Rec - ICMS RPA</t>
+          <t>Confirm Rec - PIS/COFINS</t>
         </is>
       </c>
       <c r="K593" t="inlineStr"/>
       <c r="L593" s="1" t="n">
-        <v>46223</v>
+        <v>46227</v>
       </c>
       <c r="M593" t="inlineStr"/>
       <c r="N593" t="inlineStr">
@@ -64714,7 +64714,7 @@
         </is>
       </c>
       <c r="O593" t="n">
-        <v>17042267</v>
+        <v>18128666</v>
       </c>
       <c r="P593" t="inlineStr">
         <is>
@@ -64728,18 +64728,14 @@
       </c>
       <c r="R593" t="inlineStr"/>
       <c r="S593" t="n">
-        <v>-4</v>
+        <v>-8</v>
       </c>
       <c r="T593" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
-        </is>
-      </c>
-      <c r="U593" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>EMPORIO DOS FRIOS</t>
+        </is>
+      </c>
+      <c r="U593" t="inlineStr"/>
       <c r="V593" t="inlineStr"/>
       <c r="W593" t="inlineStr"/>
       <c r="X593" t="inlineStr"/>
@@ -64761,11 +64757,11 @@
     </row>
     <row r="594">
       <c r="A594" t="n">
-        <v>6885</v>
+        <v>5417</v>
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
@@ -64775,7 +64771,7 @@
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E594" t="inlineStr">
@@ -64785,11 +64781,11 @@
       </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G594" t="n">
-        <v>953</v>
+        <v>7022</v>
       </c>
       <c r="H594" t="n">
         <v>0</v>
@@ -64801,12 +64797,12 @@
       </c>
       <c r="J594" t="inlineStr">
         <is>
-          <t>Confirm Rec - PIS/COFINS</t>
+          <t xml:space="preserve">Confirm. Rec - Impostos DCTF WEB </t>
         </is>
       </c>
       <c r="K594" t="inlineStr"/>
       <c r="L594" s="1" t="n">
-        <v>46227</v>
+        <v>46223</v>
       </c>
       <c r="M594" t="inlineStr"/>
       <c r="N594" t="inlineStr">
@@ -64815,7 +64811,7 @@
         </is>
       </c>
       <c r="O594" t="n">
-        <v>18128666</v>
+        <v>17399268</v>
       </c>
       <c r="P594" t="inlineStr">
         <is>
@@ -64829,15 +64825,23 @@
       </c>
       <c r="R594" t="inlineStr"/>
       <c r="S594" t="n">
-        <v>-8</v>
+        <v>-4</v>
       </c>
       <c r="T594" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
-        </is>
-      </c>
-      <c r="U594" t="inlineStr"/>
-      <c r="V594" t="inlineStr"/>
+          <t>NOSSO NOVO SUPERMERCADO</t>
+        </is>
+      </c>
+      <c r="U594" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V594" t="inlineStr">
+        <is>
+          <t>Reaberto via Rotina Configuração Após Baixa de tarefa [7051] sendo a ultima baixa feita [7051]-15/07/2026 15:20:21.. - Data Comentário: 15/07/2026 15:19</t>
+        </is>
+      </c>
       <c r="W594" t="inlineStr"/>
       <c r="X594" t="inlineStr"/>
       <c r="Y594" t="inlineStr"/>
@@ -64858,11 +64862,11 @@
     </row>
     <row r="595">
       <c r="A595" t="n">
-        <v>5417</v>
+        <v>6627</v>
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
@@ -64877,12 +64881,12 @@
       </c>
       <c r="E595" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G595" t="n">
@@ -64912,7 +64916,7 @@
         </is>
       </c>
       <c r="O595" t="n">
-        <v>17399268</v>
+        <v>17042501</v>
       </c>
       <c r="P595" t="inlineStr">
         <is>
@@ -64930,7 +64934,7 @@
       </c>
       <c r="T595" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
+          <t xml:space="preserve">GTG </t>
         </is>
       </c>
       <c r="U595" t="inlineStr">
@@ -64940,7 +64944,7 @@
       </c>
       <c r="V595" t="inlineStr">
         <is>
-          <t>Reaberto via Rotina Configuração Após Baixa de tarefa [7051] sendo a ultima baixa feita [7051]-15/07/2026 15:20:21.. - Data Comentário: 15/07/2026 15:19</t>
+          <t>Reaberto via Rotina Configuração Após Baixa de tarefa [7237] sendo a ultima baixa feita [7237]-15/07/2026 17:43:38.. - Data Comentário: 15/07/2026 17:42</t>
         </is>
       </c>
       <c r="W595" t="inlineStr"/>
@@ -64963,11 +64967,11 @@
     </row>
     <row r="596">
       <c r="A596" t="n">
-        <v>6627</v>
+        <v>6705</v>
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
+          <t>NARCIZO ALVES CORDEIRO</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
@@ -64977,12 +64981,12 @@
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E596" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F596" t="inlineStr">
@@ -65017,7 +65021,7 @@
         </is>
       </c>
       <c r="O596" t="n">
-        <v>17042501</v>
+        <v>17952599</v>
       </c>
       <c r="P596" t="inlineStr">
         <is>
@@ -65035,7 +65039,7 @@
       </c>
       <c r="T596" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
+          <t>TECNO COM</t>
         </is>
       </c>
       <c r="U596" t="inlineStr">
@@ -65045,7 +65049,7 @@
       </c>
       <c r="V596" t="inlineStr">
         <is>
-          <t>Reaberto via Rotina Configuração Após Baixa de tarefa [7237] sendo a ultima baixa feita [7237]-15/07/2026 17:43:38.. - Data Comentário: 15/07/2026 17:42</t>
+          <t>Reaberto via Rotina Configuração Após Baixa de tarefa [7051] sendo a ultima baixa feita [7051]-15/07/2026 19:04:36.. - Data Comentário: 15/07/2026 19:03</t>
         </is>
       </c>
       <c r="W596" t="inlineStr"/>
@@ -65068,11 +65072,11 @@
     </row>
     <row r="597">
       <c r="A597" t="n">
-        <v>6705</v>
+        <v>5417</v>
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>NARCIZO ALVES CORDEIRO</t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
@@ -65082,7 +65086,7 @@
       </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E597" t="inlineStr">
@@ -65092,11 +65096,11 @@
       </c>
       <c r="F597" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G597" t="n">
-        <v>7022</v>
+        <v>9086</v>
       </c>
       <c r="H597" t="n">
         <v>0</v>
@@ -65108,21 +65112,21 @@
       </c>
       <c r="J597" t="inlineStr">
         <is>
-          <t xml:space="preserve">Confirm. Rec - Impostos DCTF WEB </t>
+          <t>Consulta Cx Postal - 2º Quinzena</t>
         </is>
       </c>
       <c r="K597" t="inlineStr"/>
       <c r="L597" s="1" t="n">
-        <v>46223</v>
+        <v>46220</v>
       </c>
       <c r="M597" t="inlineStr"/>
       <c r="N597" t="inlineStr">
         <is>
-          <t>06/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
       <c r="O597" t="n">
-        <v>17952599</v>
+        <v>17399361</v>
       </c>
       <c r="P597" t="inlineStr">
         <is>
@@ -65136,11 +65140,11 @@
       </c>
       <c r="R597" t="inlineStr"/>
       <c r="S597" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="T597" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>NOSSO NOVO SUPERMERCADO</t>
         </is>
       </c>
       <c r="U597" t="inlineStr">
@@ -65148,11 +65152,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V597" t="inlineStr">
-        <is>
-          <t>Reaberto via Rotina Configuração Após Baixa de tarefa [7051] sendo a ultima baixa feita [7051]-15/07/2026 19:04:36.. - Data Comentário: 15/07/2026 19:03</t>
-        </is>
-      </c>
+      <c r="V597" t="inlineStr"/>
       <c r="W597" t="inlineStr"/>
       <c r="X597" t="inlineStr"/>
       <c r="Y597" t="inlineStr"/>
@@ -65166,18 +65166,18 @@
       <c r="AE597" t="inlineStr"/>
       <c r="AF597" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Obrigação Acessória</t>
         </is>
       </c>
       <c r="AG597" t="inlineStr"/>
     </row>
     <row r="598">
       <c r="A598" t="n">
-        <v>5417</v>
+        <v>5617</v>
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
@@ -65197,7 +65197,7 @@
       </c>
       <c r="F598" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G598" t="n">
@@ -65227,7 +65227,7 @@
         </is>
       </c>
       <c r="O598" t="n">
-        <v>17399361</v>
+        <v>17407882</v>
       </c>
       <c r="P598" t="inlineStr">
         <is>
@@ -65245,7 +65245,7 @@
       </c>
       <c r="T598" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U598" t="inlineStr">
@@ -65274,11 +65274,11 @@
     </row>
     <row r="599">
       <c r="A599" t="n">
-        <v>5617</v>
+        <v>6224</v>
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
@@ -65298,7 +65298,7 @@
       </c>
       <c r="F599" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G599" t="n">
@@ -65328,7 +65328,7 @@
         </is>
       </c>
       <c r="O599" t="n">
-        <v>17407882</v>
+        <v>17689000</v>
       </c>
       <c r="P599" t="inlineStr">
         <is>
@@ -65375,11 +65375,11 @@
     </row>
     <row r="600">
       <c r="A600" t="n">
-        <v>6224</v>
+        <v>6278</v>
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>EMPORIO DOS FRIOS LTDA</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
@@ -65389,7 +65389,7 @@
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Real - Anual</t>
         </is>
       </c>
       <c r="E600" t="inlineStr">
@@ -65399,7 +65399,7 @@
       </c>
       <c r="F600" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G600" t="n">
@@ -65429,7 +65429,7 @@
         </is>
       </c>
       <c r="O600" t="n">
-        <v>17689000</v>
+        <v>17539858</v>
       </c>
       <c r="P600" t="inlineStr">
         <is>
@@ -65447,7 +65447,7 @@
       </c>
       <c r="T600" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U600" t="inlineStr">
@@ -65476,11 +65476,11 @@
     </row>
     <row r="601">
       <c r="A601" t="n">
-        <v>6278</v>
+        <v>6279</v>
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS LTDA</t>
+          <t>DIENNYFER DA S PEREIRA</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
@@ -65490,7 +65490,7 @@
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>Federal - Lucro Real - Anual</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E601" t="inlineStr">
@@ -65500,7 +65500,7 @@
       </c>
       <c r="F601" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G601" t="n">
@@ -65530,7 +65530,7 @@
         </is>
       </c>
       <c r="O601" t="n">
-        <v>17539858</v>
+        <v>17646135</v>
       </c>
       <c r="P601" t="inlineStr">
         <is>
@@ -65577,11 +65577,11 @@
     </row>
     <row r="602">
       <c r="A602" t="n">
-        <v>6279</v>
+        <v>6404</v>
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>DIENNYFER DA S PEREIRA</t>
+          <t>SOLAR INVESTIMENTOS LTDA</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
@@ -65601,7 +65601,7 @@
       </c>
       <c r="F602" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G602" t="n">
@@ -65631,7 +65631,7 @@
         </is>
       </c>
       <c r="O602" t="n">
-        <v>17646135</v>
+        <v>16962378</v>
       </c>
       <c r="P602" t="inlineStr">
         <is>
@@ -65649,7 +65649,7 @@
       </c>
       <c r="T602" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>SOLAR INVESTIMENTOS</t>
         </is>
       </c>
       <c r="U602" t="inlineStr">
@@ -65678,11 +65678,11 @@
     </row>
     <row r="603">
       <c r="A603" t="n">
-        <v>6404</v>
+        <v>6486</v>
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS LTDA</t>
+          <t>PC GAMER GOIANIA LTDA</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
@@ -65692,7 +65692,7 @@
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E603" t="inlineStr">
@@ -65732,7 +65732,7 @@
         </is>
       </c>
       <c r="O603" t="n">
-        <v>16962378</v>
+        <v>16976268</v>
       </c>
       <c r="P603" t="inlineStr">
         <is>
@@ -65750,7 +65750,7 @@
       </c>
       <c r="T603" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS</t>
+          <t>PC GAMER</t>
         </is>
       </c>
       <c r="U603" t="inlineStr">
@@ -65779,11 +65779,11 @@
     </row>
     <row r="604">
       <c r="A604" t="n">
-        <v>6486</v>
+        <v>6548</v>
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>PC GAMER GOIANIA LTDA</t>
+          <t>GOIAS SILAGEM LTDA</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
@@ -65833,7 +65833,7 @@
         </is>
       </c>
       <c r="O604" t="n">
-        <v>16976268</v>
+        <v>17222863</v>
       </c>
       <c r="P604" t="inlineStr">
         <is>
@@ -65851,7 +65851,7 @@
       </c>
       <c r="T604" t="inlineStr">
         <is>
-          <t>PC GAMER</t>
+          <t>GOIAS SILAGEM</t>
         </is>
       </c>
       <c r="U604" t="inlineStr">
@@ -65880,11 +65880,11 @@
     </row>
     <row r="605">
       <c r="A605" t="n">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM LTDA</t>
+          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
@@ -65899,7 +65899,7 @@
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F605" t="inlineStr">
@@ -65934,7 +65934,7 @@
         </is>
       </c>
       <c r="O605" t="n">
-        <v>17222863</v>
+        <v>17042583</v>
       </c>
       <c r="P605" t="inlineStr">
         <is>
@@ -65952,7 +65952,7 @@
       </c>
       <c r="T605" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM</t>
+          <t xml:space="preserve">GTG </t>
         </is>
       </c>
       <c r="U605" t="inlineStr">
@@ -65981,11 +65981,11 @@
     </row>
     <row r="606">
       <c r="A606" t="n">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
@@ -65995,7 +65995,7 @@
       </c>
       <c r="D606" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E606" t="inlineStr">
@@ -66035,7 +66035,7 @@
         </is>
       </c>
       <c r="O606" t="n">
-        <v>17042583</v>
+        <v>16960072</v>
       </c>
       <c r="P606" t="inlineStr">
         <is>
@@ -66082,11 +66082,11 @@
     </row>
     <row r="607">
       <c r="A607" t="n">
-        <v>6628</v>
+        <v>6703</v>
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
@@ -66096,12 +66096,12 @@
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E607" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F607" t="inlineStr">
@@ -66136,7 +66136,7 @@
         </is>
       </c>
       <c r="O607" t="n">
-        <v>16960072</v>
+        <v>17941215</v>
       </c>
       <c r="P607" t="inlineStr">
         <is>
@@ -66154,7 +66154,7 @@
       </c>
       <c r="T607" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
+          <t>LIMA MOTA</t>
         </is>
       </c>
       <c r="U607" t="inlineStr">
@@ -66183,11 +66183,11 @@
     </row>
     <row r="608">
       <c r="A608" t="n">
-        <v>6703</v>
+        <v>6704</v>
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
+          <t>TECNO COM INFORMATICA LTDA</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
@@ -66197,7 +66197,7 @@
       </c>
       <c r="D608" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E608" t="inlineStr">
@@ -66237,7 +66237,7 @@
         </is>
       </c>
       <c r="O608" t="n">
-        <v>17941215</v>
+        <v>17952442</v>
       </c>
       <c r="P608" t="inlineStr">
         <is>
@@ -66255,7 +66255,7 @@
       </c>
       <c r="T608" t="inlineStr">
         <is>
-          <t>LIMA MOTA</t>
+          <t>TECNO COM</t>
         </is>
       </c>
       <c r="U608" t="inlineStr">
@@ -66284,11 +66284,11 @@
     </row>
     <row r="609">
       <c r="A609" t="n">
-        <v>6704</v>
+        <v>6705</v>
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>TECNO COM INFORMATICA LTDA</t>
+          <t>NARCIZO ALVES CORDEIRO</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
@@ -66298,7 +66298,7 @@
       </c>
       <c r="D609" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E609" t="inlineStr">
@@ -66338,7 +66338,7 @@
         </is>
       </c>
       <c r="O609" t="n">
-        <v>17952442</v>
+        <v>17952622</v>
       </c>
       <c r="P609" t="inlineStr">
         <is>
@@ -66385,11 +66385,11 @@
     </row>
     <row r="610">
       <c r="A610" t="n">
-        <v>6705</v>
+        <v>6779</v>
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>NARCIZO ALVES CORDEIRO</t>
+          <t>CORDEIRO E CIA LTDA</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
@@ -66439,7 +66439,7 @@
         </is>
       </c>
       <c r="O610" t="n">
-        <v>17952622</v>
+        <v>18056799</v>
       </c>
       <c r="P610" t="inlineStr">
         <is>
@@ -66460,11 +66460,7 @@
           <t>TECNO COM</t>
         </is>
       </c>
-      <c r="U610" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+      <c r="U610" t="inlineStr"/>
       <c r="V610" t="inlineStr"/>
       <c r="W610" t="inlineStr"/>
       <c r="X610" t="inlineStr"/>
@@ -66486,11 +66482,11 @@
     </row>
     <row r="611">
       <c r="A611" t="n">
-        <v>6779</v>
+        <v>6885</v>
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>CORDEIRO E CIA LTDA</t>
+          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
@@ -66540,7 +66536,7 @@
         </is>
       </c>
       <c r="O611" t="n">
-        <v>18056799</v>
+        <v>18128837</v>
       </c>
       <c r="P611" t="inlineStr">
         <is>
@@ -66558,7 +66554,7 @@
       </c>
       <c r="T611" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U611" t="inlineStr"/>
@@ -66583,11 +66579,11 @@
     </row>
     <row r="612">
       <c r="A612" t="n">
-        <v>6885</v>
+        <v>6945</v>
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
+          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
@@ -66602,7 +66598,7 @@
       </c>
       <c r="E612" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F612" t="inlineStr">
@@ -66637,7 +66633,7 @@
         </is>
       </c>
       <c r="O612" t="n">
-        <v>18128837</v>
+        <v>18164549</v>
       </c>
       <c r="P612" t="inlineStr">
         <is>
@@ -66655,7 +66651,7 @@
       </c>
       <c r="T612" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>BRASIL DISTRIBUIDORA</t>
         </is>
       </c>
       <c r="U612" t="inlineStr"/>
@@ -66680,11 +66676,11 @@
     </row>
     <row r="613">
       <c r="A613" t="n">
-        <v>6945</v>
+        <v>6949</v>
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
+          <t>TEC GRUA LOCAÇÃO E COMERCIO DE EQUIPAMENTOS PARA CONSTRUÇÃO LTDA</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
@@ -66694,17 +66690,17 @@
       </c>
       <c r="D613" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E613" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F613" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Reynaldo Santos</t>
         </is>
       </c>
       <c r="G613" t="n">
@@ -66734,7 +66730,7 @@
         </is>
       </c>
       <c r="O613" t="n">
-        <v>18164549</v>
+        <v>18178185</v>
       </c>
       <c r="P613" t="inlineStr">
         <is>
@@ -66752,7 +66748,7 @@
       </c>
       <c r="T613" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA</t>
+          <t>TEC GRUA</t>
         </is>
       </c>
       <c r="U613" t="inlineStr"/>
@@ -66777,11 +66773,11 @@
     </row>
     <row r="614">
       <c r="A614" t="n">
-        <v>6949</v>
+        <v>6962</v>
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>TEC GRUA LOCAÇÃO E COMERCIO DE EQUIPAMENTOS PARA CONSTRUÇÃO LTDA</t>
+          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
@@ -66831,7 +66827,7 @@
         </is>
       </c>
       <c r="O614" t="n">
-        <v>18178185</v>
+        <v>18188772</v>
       </c>
       <c r="P614" t="inlineStr">
         <is>
@@ -66849,7 +66845,7 @@
       </c>
       <c r="T614" t="inlineStr">
         <is>
-          <t>TEC GRUA</t>
+          <t>PROMOTORAS GYN</t>
         </is>
       </c>
       <c r="U614" t="inlineStr"/>
@@ -66874,11 +66870,11 @@
     </row>
     <row r="615">
       <c r="A615" t="n">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
+          <t>PROMOTORAS GYN LTDA</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
@@ -66928,7 +66924,7 @@
         </is>
       </c>
       <c r="O615" t="n">
-        <v>18188772</v>
+        <v>18188678</v>
       </c>
       <c r="P615" t="inlineStr">
         <is>
@@ -66971,11 +66967,11 @@
     </row>
     <row r="616">
       <c r="A616" t="n">
-        <v>6963</v>
+        <v>5417</v>
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN LTDA</t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
@@ -66995,11 +66991,11 @@
       </c>
       <c r="F616" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G616" t="n">
-        <v>9086</v>
+        <v>943</v>
       </c>
       <c r="H616" t="n">
         <v>0</v>
@@ -67011,21 +67007,21 @@
       </c>
       <c r="J616" t="inlineStr">
         <is>
-          <t>Consulta Cx Postal - 2º Quinzena</t>
+          <t>Inclusão de Ata de Reunião</t>
         </is>
       </c>
       <c r="K616" t="inlineStr"/>
       <c r="L616" s="1" t="n">
-        <v>46220</v>
+        <v>46233</v>
       </c>
       <c r="M616" t="inlineStr"/>
       <c r="N616" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
       <c r="O616" t="n">
-        <v>18188678</v>
+        <v>17398857</v>
       </c>
       <c r="P616" t="inlineStr">
         <is>
@@ -67039,14 +67035,18 @@
       </c>
       <c r="R616" t="inlineStr"/>
       <c r="S616" t="n">
-        <v>-1</v>
+        <v>-14</v>
       </c>
       <c r="T616" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN</t>
-        </is>
-      </c>
-      <c r="U616" t="inlineStr"/>
+          <t>NOSSO NOVO SUPERMERCADO</t>
+        </is>
+      </c>
+      <c r="U616" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V616" t="inlineStr"/>
       <c r="W616" t="inlineStr"/>
       <c r="X616" t="inlineStr"/>
@@ -67061,18 +67061,18 @@
       <c r="AE616" t="inlineStr"/>
       <c r="AF616" t="inlineStr">
         <is>
-          <t>Obrigação Acessória</t>
+          <t>Tarefa</t>
         </is>
       </c>
       <c r="AG616" t="inlineStr"/>
     </row>
     <row r="617">
       <c r="A617" t="n">
-        <v>5417</v>
+        <v>5617</v>
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
@@ -67092,7 +67092,7 @@
       </c>
       <c r="F617" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G617" t="n">
@@ -67122,7 +67122,7 @@
         </is>
       </c>
       <c r="O617" t="n">
-        <v>17398857</v>
+        <v>17407517</v>
       </c>
       <c r="P617" t="inlineStr">
         <is>
@@ -67140,7 +67140,7 @@
       </c>
       <c r="T617" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U617" t="inlineStr">
@@ -67169,11 +67169,11 @@
     </row>
     <row r="618">
       <c r="A618" t="n">
-        <v>5617</v>
+        <v>6224</v>
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
@@ -67193,7 +67193,7 @@
       </c>
       <c r="F618" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G618" t="n">
@@ -67223,7 +67223,7 @@
         </is>
       </c>
       <c r="O618" t="n">
-        <v>17407517</v>
+        <v>17688603</v>
       </c>
       <c r="P618" t="inlineStr">
         <is>
@@ -67270,11 +67270,11 @@
     </row>
     <row r="619">
       <c r="A619" t="n">
-        <v>6224</v>
+        <v>6278</v>
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>EMPORIO DOS FRIOS LTDA</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
@@ -67284,7 +67284,7 @@
       </c>
       <c r="D619" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Real - Anual</t>
         </is>
       </c>
       <c r="E619" t="inlineStr">
@@ -67294,7 +67294,7 @@
       </c>
       <c r="F619" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G619" t="n">
@@ -67324,7 +67324,7 @@
         </is>
       </c>
       <c r="O619" t="n">
-        <v>17688603</v>
+        <v>17539698</v>
       </c>
       <c r="P619" t="inlineStr">
         <is>
@@ -67342,7 +67342,7 @@
       </c>
       <c r="T619" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U619" t="inlineStr">
@@ -67371,11 +67371,11 @@
     </row>
     <row r="620">
       <c r="A620" t="n">
-        <v>6278</v>
+        <v>6279</v>
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS LTDA</t>
+          <t>DIENNYFER DA S PEREIRA</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
@@ -67385,7 +67385,7 @@
       </c>
       <c r="D620" t="inlineStr">
         <is>
-          <t>Federal - Lucro Real - Anual</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E620" t="inlineStr">
@@ -67395,7 +67395,7 @@
       </c>
       <c r="F620" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G620" t="n">
@@ -67425,7 +67425,7 @@
         </is>
       </c>
       <c r="O620" t="n">
-        <v>17539698</v>
+        <v>17645913</v>
       </c>
       <c r="P620" t="inlineStr">
         <is>
@@ -67472,11 +67472,11 @@
     </row>
     <row r="621">
       <c r="A621" t="n">
-        <v>6279</v>
+        <v>6486</v>
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>DIENNYFER DA S PEREIRA</t>
+          <t>PC GAMER GOIANIA LTDA</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
@@ -67486,7 +67486,7 @@
       </c>
       <c r="D621" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E621" t="inlineStr">
@@ -67496,7 +67496,7 @@
       </c>
       <c r="F621" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G621" t="n">
@@ -67526,7 +67526,7 @@
         </is>
       </c>
       <c r="O621" t="n">
-        <v>17645913</v>
+        <v>16975888</v>
       </c>
       <c r="P621" t="inlineStr">
         <is>
@@ -67544,7 +67544,7 @@
       </c>
       <c r="T621" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>PC GAMER</t>
         </is>
       </c>
       <c r="U621" t="inlineStr">
@@ -67573,11 +67573,11 @@
     </row>
     <row r="622">
       <c r="A622" t="n">
-        <v>6486</v>
+        <v>6703</v>
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>PC GAMER GOIANIA LTDA</t>
+          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
@@ -67587,7 +67587,7 @@
       </c>
       <c r="D622" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E622" t="inlineStr">
@@ -67627,7 +67627,7 @@
         </is>
       </c>
       <c r="O622" t="n">
-        <v>16975888</v>
+        <v>17941120</v>
       </c>
       <c r="P622" t="inlineStr">
         <is>
@@ -67645,7 +67645,7 @@
       </c>
       <c r="T622" t="inlineStr">
         <is>
-          <t>PC GAMER</t>
+          <t>LIMA MOTA</t>
         </is>
       </c>
       <c r="U622" t="inlineStr">
@@ -67674,11 +67674,11 @@
     </row>
     <row r="623">
       <c r="A623" t="n">
-        <v>6703</v>
+        <v>6704</v>
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
+          <t>TECNO COM INFORMATICA LTDA</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
@@ -67688,7 +67688,7 @@
       </c>
       <c r="D623" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E623" t="inlineStr">
@@ -67728,7 +67728,7 @@
         </is>
       </c>
       <c r="O623" t="n">
-        <v>17941120</v>
+        <v>17952312</v>
       </c>
       <c r="P623" t="inlineStr">
         <is>
@@ -67746,7 +67746,7 @@
       </c>
       <c r="T623" t="inlineStr">
         <is>
-          <t>LIMA MOTA</t>
+          <t>TECNO COM</t>
         </is>
       </c>
       <c r="U623" t="inlineStr">
@@ -67775,11 +67775,11 @@
     </row>
     <row r="624">
       <c r="A624" t="n">
-        <v>6704</v>
+        <v>6705</v>
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>TECNO COM INFORMATICA LTDA</t>
+          <t>NARCIZO ALVES CORDEIRO</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
@@ -67789,7 +67789,7 @@
       </c>
       <c r="D624" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E624" t="inlineStr">
@@ -67829,7 +67829,7 @@
         </is>
       </c>
       <c r="O624" t="n">
-        <v>17952312</v>
+        <v>17952511</v>
       </c>
       <c r="P624" t="inlineStr">
         <is>
@@ -67876,11 +67876,11 @@
     </row>
     <row r="625">
       <c r="A625" t="n">
-        <v>6705</v>
+        <v>6885</v>
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>NARCIZO ALVES CORDEIRO</t>
+          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
@@ -67930,7 +67930,7 @@
         </is>
       </c>
       <c r="O625" t="n">
-        <v>17952511</v>
+        <v>18128630</v>
       </c>
       <c r="P625" t="inlineStr">
         <is>
@@ -67948,14 +67948,10 @@
       </c>
       <c r="T625" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
-        </is>
-      </c>
-      <c r="U625" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>EMPORIO DOS FRIOS</t>
+        </is>
+      </c>
+      <c r="U625" t="inlineStr"/>
       <c r="V625" t="inlineStr"/>
       <c r="W625" t="inlineStr"/>
       <c r="X625" t="inlineStr"/>
@@ -67977,11 +67973,11 @@
     </row>
     <row r="626">
       <c r="A626" t="n">
-        <v>6885</v>
+        <v>6962</v>
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
+          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
@@ -67991,7 +67987,7 @@
       </c>
       <c r="D626" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E626" t="inlineStr">
@@ -68001,7 +67997,7 @@
       </c>
       <c r="F626" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Reynaldo Santos</t>
         </is>
       </c>
       <c r="G626" t="n">
@@ -68031,7 +68027,7 @@
         </is>
       </c>
       <c r="O626" t="n">
-        <v>18128630</v>
+        <v>18188708</v>
       </c>
       <c r="P626" t="inlineStr">
         <is>
@@ -68049,7 +68045,7 @@
       </c>
       <c r="T626" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>PROMOTORAS GYN</t>
         </is>
       </c>
       <c r="U626" t="inlineStr"/>
@@ -68074,11 +68070,11 @@
     </row>
     <row r="627">
       <c r="A627" t="n">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
+          <t>PROMOTORAS GYN LTDA</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
@@ -68128,7 +68124,7 @@
         </is>
       </c>
       <c r="O627" t="n">
-        <v>18188708</v>
+        <v>18188614</v>
       </c>
       <c r="P627" t="inlineStr">
         <is>
@@ -68171,11 +68167,11 @@
     </row>
     <row r="628">
       <c r="A628" t="n">
-        <v>6963</v>
+        <v>5417</v>
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN LTDA</t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
@@ -68195,41 +68191,41 @@
       </c>
       <c r="F628" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G628" t="n">
-        <v>943</v>
+        <v>9088</v>
       </c>
       <c r="H628" t="n">
         <v>0</v>
       </c>
       <c r="I628" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="J628" t="inlineStr">
         <is>
-          <t>Inclusão de Ata de Reunião</t>
+          <t>Conferência Consulta Cx Postal - 2º Quinzena</t>
         </is>
       </c>
       <c r="K628" t="inlineStr"/>
       <c r="L628" s="1" t="n">
-        <v>46233</v>
+        <v>46220</v>
       </c>
       <c r="M628" t="inlineStr"/>
       <c r="N628" t="inlineStr">
         <is>
-          <t>06/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
       <c r="O628" t="n">
-        <v>18188614</v>
+        <v>17399381</v>
       </c>
       <c r="P628" t="inlineStr">
         <is>
-          <t>Victoria Virgens</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="Q628" t="inlineStr">
@@ -68239,14 +68235,18 @@
       </c>
       <c r="R628" t="inlineStr"/>
       <c r="S628" t="n">
-        <v>-14</v>
+        <v>-1</v>
       </c>
       <c r="T628" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN</t>
-        </is>
-      </c>
-      <c r="U628" t="inlineStr"/>
+          <t>NOSSO NOVO SUPERMERCADO</t>
+        </is>
+      </c>
+      <c r="U628" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V628" t="inlineStr"/>
       <c r="W628" t="inlineStr"/>
       <c r="X628" t="inlineStr"/>
@@ -68261,18 +68261,18 @@
       <c r="AE628" t="inlineStr"/>
       <c r="AF628" t="inlineStr">
         <is>
-          <t>Tarefa</t>
+          <t>Obrigação Acessória</t>
         </is>
       </c>
       <c r="AG628" t="inlineStr"/>
     </row>
     <row r="629">
       <c r="A629" t="n">
-        <v>5417</v>
+        <v>5617</v>
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
@@ -68292,7 +68292,7 @@
       </c>
       <c r="F629" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G629" t="n">
@@ -68322,7 +68322,7 @@
         </is>
       </c>
       <c r="O629" t="n">
-        <v>17399381</v>
+        <v>17407902</v>
       </c>
       <c r="P629" t="inlineStr">
         <is>
@@ -68340,7 +68340,7 @@
       </c>
       <c r="T629" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U629" t="inlineStr">
@@ -68369,11 +68369,11 @@
     </row>
     <row r="630">
       <c r="A630" t="n">
-        <v>5617</v>
+        <v>6224</v>
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
@@ -68393,7 +68393,7 @@
       </c>
       <c r="F630" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G630" t="n">
@@ -68423,11 +68423,11 @@
         </is>
       </c>
       <c r="O630" t="n">
-        <v>17407902</v>
+        <v>17689020</v>
       </c>
       <c r="P630" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="Q630" t="inlineStr">
@@ -68470,11 +68470,11 @@
     </row>
     <row r="631">
       <c r="A631" t="n">
-        <v>6224</v>
+        <v>6278</v>
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>EMPORIO DOS FRIOS LTDA</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
@@ -68484,7 +68484,7 @@
       </c>
       <c r="D631" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Real - Anual</t>
         </is>
       </c>
       <c r="E631" t="inlineStr">
@@ -68494,7 +68494,7 @@
       </c>
       <c r="F631" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G631" t="n">
@@ -68524,11 +68524,11 @@
         </is>
       </c>
       <c r="O631" t="n">
-        <v>17689020</v>
+        <v>17539878</v>
       </c>
       <c r="P631" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="Q631" t="inlineStr">
@@ -68542,7 +68542,7 @@
       </c>
       <c r="T631" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U631" t="inlineStr">
@@ -68571,11 +68571,11 @@
     </row>
     <row r="632">
       <c r="A632" t="n">
-        <v>6278</v>
+        <v>6279</v>
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS LTDA</t>
+          <t>DIENNYFER DA S PEREIRA</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
@@ -68585,7 +68585,7 @@
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>Federal - Lucro Real - Anual</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E632" t="inlineStr">
@@ -68595,7 +68595,7 @@
       </c>
       <c r="F632" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G632" t="n">
@@ -68625,7 +68625,7 @@
         </is>
       </c>
       <c r="O632" t="n">
-        <v>17539878</v>
+        <v>17646155</v>
       </c>
       <c r="P632" t="inlineStr">
         <is>
@@ -68672,11 +68672,11 @@
     </row>
     <row r="633">
       <c r="A633" t="n">
-        <v>6279</v>
+        <v>6404</v>
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>DIENNYFER DA S PEREIRA</t>
+          <t>SOLAR INVESTIMENTOS LTDA</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
@@ -68696,7 +68696,7 @@
       </c>
       <c r="F633" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G633" t="n">
@@ -68726,11 +68726,11 @@
         </is>
       </c>
       <c r="O633" t="n">
-        <v>17646155</v>
+        <v>16962398</v>
       </c>
       <c r="P633" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="Q633" t="inlineStr">
@@ -68744,7 +68744,7 @@
       </c>
       <c r="T633" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>SOLAR INVESTIMENTOS</t>
         </is>
       </c>
       <c r="U633" t="inlineStr">
@@ -68773,11 +68773,11 @@
     </row>
     <row r="634">
       <c r="A634" t="n">
-        <v>6404</v>
+        <v>6486</v>
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS LTDA</t>
+          <t>PC GAMER GOIANIA LTDA</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
@@ -68787,7 +68787,7 @@
       </c>
       <c r="D634" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E634" t="inlineStr">
@@ -68827,7 +68827,7 @@
         </is>
       </c>
       <c r="O634" t="n">
-        <v>16962398</v>
+        <v>16976288</v>
       </c>
       <c r="P634" t="inlineStr">
         <is>
@@ -68845,7 +68845,7 @@
       </c>
       <c r="T634" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS</t>
+          <t>PC GAMER</t>
         </is>
       </c>
       <c r="U634" t="inlineStr">
@@ -68874,11 +68874,11 @@
     </row>
     <row r="635">
       <c r="A635" t="n">
-        <v>6486</v>
+        <v>6548</v>
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>PC GAMER GOIANIA LTDA</t>
+          <t>GOIAS SILAGEM LTDA</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
@@ -68928,11 +68928,11 @@
         </is>
       </c>
       <c r="O635" t="n">
-        <v>16976288</v>
+        <v>17222895</v>
       </c>
       <c r="P635" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="Q635" t="inlineStr">
@@ -68946,7 +68946,7 @@
       </c>
       <c r="T635" t="inlineStr">
         <is>
-          <t>PC GAMER</t>
+          <t>GOIAS SILAGEM</t>
         </is>
       </c>
       <c r="U635" t="inlineStr">
@@ -68975,11 +68975,11 @@
     </row>
     <row r="636">
       <c r="A636" t="n">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM LTDA</t>
+          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
@@ -68994,7 +68994,7 @@
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F636" t="inlineStr">
@@ -69029,7 +69029,7 @@
         </is>
       </c>
       <c r="O636" t="n">
-        <v>17222895</v>
+        <v>17042622</v>
       </c>
       <c r="P636" t="inlineStr">
         <is>
@@ -69047,7 +69047,7 @@
       </c>
       <c r="T636" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM</t>
+          <t xml:space="preserve">GTG </t>
         </is>
       </c>
       <c r="U636" t="inlineStr">
@@ -69076,11 +69076,11 @@
     </row>
     <row r="637">
       <c r="A637" t="n">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
@@ -69090,7 +69090,7 @@
       </c>
       <c r="D637" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E637" t="inlineStr">
@@ -69130,7 +69130,7 @@
         </is>
       </c>
       <c r="O637" t="n">
-        <v>17042622</v>
+        <v>16960096</v>
       </c>
       <c r="P637" t="inlineStr">
         <is>
@@ -69177,11 +69177,11 @@
     </row>
     <row r="638">
       <c r="A638" t="n">
-        <v>6628</v>
+        <v>6703</v>
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
@@ -69191,12 +69191,12 @@
       </c>
       <c r="D638" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E638" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F638" t="inlineStr">
@@ -69231,7 +69231,7 @@
         </is>
       </c>
       <c r="O638" t="n">
-        <v>16960096</v>
+        <v>17941235</v>
       </c>
       <c r="P638" t="inlineStr">
         <is>
@@ -69249,7 +69249,7 @@
       </c>
       <c r="T638" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
+          <t>LIMA MOTA</t>
         </is>
       </c>
       <c r="U638" t="inlineStr">
@@ -69278,11 +69278,11 @@
     </row>
     <row r="639">
       <c r="A639" t="n">
-        <v>6703</v>
+        <v>6704</v>
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
+          <t>TECNO COM INFORMATICA LTDA</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
@@ -69292,7 +69292,7 @@
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E639" t="inlineStr">
@@ -69332,7 +69332,7 @@
         </is>
       </c>
       <c r="O639" t="n">
-        <v>17941235</v>
+        <v>17952464</v>
       </c>
       <c r="P639" t="inlineStr">
         <is>
@@ -69350,7 +69350,7 @@
       </c>
       <c r="T639" t="inlineStr">
         <is>
-          <t>LIMA MOTA</t>
+          <t>TECNO COM</t>
         </is>
       </c>
       <c r="U639" t="inlineStr">
@@ -69379,11 +69379,11 @@
     </row>
     <row r="640">
       <c r="A640" t="n">
-        <v>6704</v>
+        <v>6705</v>
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>TECNO COM INFORMATICA LTDA</t>
+          <t>NARCIZO ALVES CORDEIRO</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
@@ -69393,7 +69393,7 @@
       </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E640" t="inlineStr">
@@ -69433,7 +69433,7 @@
         </is>
       </c>
       <c r="O640" t="n">
-        <v>17952464</v>
+        <v>17952644</v>
       </c>
       <c r="P640" t="inlineStr">
         <is>
@@ -69480,11 +69480,11 @@
     </row>
     <row r="641">
       <c r="A641" t="n">
-        <v>6705</v>
+        <v>6779</v>
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>NARCIZO ALVES CORDEIRO</t>
+          <t>CORDEIRO E CIA LTDA</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
@@ -69534,7 +69534,7 @@
         </is>
       </c>
       <c r="O641" t="n">
-        <v>17952644</v>
+        <v>18056819</v>
       </c>
       <c r="P641" t="inlineStr">
         <is>
@@ -69555,11 +69555,7 @@
           <t>TECNO COM</t>
         </is>
       </c>
-      <c r="U641" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+      <c r="U641" t="inlineStr"/>
       <c r="V641" t="inlineStr"/>
       <c r="W641" t="inlineStr"/>
       <c r="X641" t="inlineStr"/>
@@ -69581,11 +69577,11 @@
     </row>
     <row r="642">
       <c r="A642" t="n">
-        <v>6779</v>
+        <v>6885</v>
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>CORDEIRO E CIA LTDA</t>
+          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
@@ -69635,7 +69631,7 @@
         </is>
       </c>
       <c r="O642" t="n">
-        <v>18056819</v>
+        <v>18128855</v>
       </c>
       <c r="P642" t="inlineStr">
         <is>
@@ -69653,7 +69649,7 @@
       </c>
       <c r="T642" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U642" t="inlineStr"/>
@@ -69678,11 +69674,11 @@
     </row>
     <row r="643">
       <c r="A643" t="n">
-        <v>6885</v>
+        <v>6945</v>
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
+          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
@@ -69697,7 +69693,7 @@
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F643" t="inlineStr">
@@ -69732,11 +69728,11 @@
         </is>
       </c>
       <c r="O643" t="n">
-        <v>18128855</v>
+        <v>18164563</v>
       </c>
       <c r="P643" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="Q643" t="inlineStr">
@@ -69750,7 +69746,7 @@
       </c>
       <c r="T643" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>BRASIL DISTRIBUIDORA</t>
         </is>
       </c>
       <c r="U643" t="inlineStr"/>
@@ -69775,11 +69771,11 @@
     </row>
     <row r="644">
       <c r="A644" t="n">
-        <v>6945</v>
+        <v>6949</v>
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
+          <t>TEC GRUA LOCAÇÃO E COMERCIO DE EQUIPAMENTOS PARA CONSTRUÇÃO LTDA</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
@@ -69789,17 +69785,17 @@
       </c>
       <c r="D644" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F644" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Reynaldo Santos</t>
         </is>
       </c>
       <c r="G644" t="n">
@@ -69829,11 +69825,11 @@
         </is>
       </c>
       <c r="O644" t="n">
-        <v>18164563</v>
+        <v>18178197</v>
       </c>
       <c r="P644" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="Q644" t="inlineStr">
@@ -69847,7 +69843,7 @@
       </c>
       <c r="T644" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA</t>
+          <t>TEC GRUA</t>
         </is>
       </c>
       <c r="U644" t="inlineStr"/>
@@ -69872,11 +69868,11 @@
     </row>
     <row r="645">
       <c r="A645" t="n">
-        <v>6949</v>
+        <v>6962</v>
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>TEC GRUA LOCAÇÃO E COMERCIO DE EQUIPAMENTOS PARA CONSTRUÇÃO LTDA</t>
+          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
@@ -69926,11 +69922,11 @@
         </is>
       </c>
       <c r="O645" t="n">
-        <v>18178197</v>
+        <v>18188786</v>
       </c>
       <c r="P645" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="Q645" t="inlineStr">
@@ -69944,7 +69940,7 @@
       </c>
       <c r="T645" t="inlineStr">
         <is>
-          <t>TEC GRUA</t>
+          <t>PROMOTORAS GYN</t>
         </is>
       </c>
       <c r="U645" t="inlineStr"/>
@@ -69969,11 +69965,11 @@
     </row>
     <row r="646">
       <c r="A646" t="n">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
+          <t>PROMOTORAS GYN LTDA</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
@@ -70023,7 +70019,7 @@
         </is>
       </c>
       <c r="O646" t="n">
-        <v>18188786</v>
+        <v>18188692</v>
       </c>
       <c r="P646" t="inlineStr">
         <is>
@@ -70066,11 +70062,11 @@
     </row>
     <row r="647">
       <c r="A647" t="n">
-        <v>6963</v>
+        <v>5417</v>
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN LTDA</t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
@@ -70090,11 +70086,11 @@
       </c>
       <c r="F647" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G647" t="n">
-        <v>9088</v>
+        <v>957</v>
       </c>
       <c r="H647" t="n">
         <v>0</v>
@@ -70106,25 +70102,25 @@
       </c>
       <c r="J647" t="inlineStr">
         <is>
-          <t>Conferência Consulta Cx Postal - 2º Quinzena</t>
+          <t>Definição do Lucro Trimestral</t>
         </is>
       </c>
       <c r="K647" t="inlineStr"/>
       <c r="L647" s="1" t="n">
-        <v>46220</v>
+        <v>46233</v>
       </c>
       <c r="M647" t="inlineStr"/>
       <c r="N647" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
       <c r="O647" t="n">
-        <v>18188692</v>
+        <v>17398899</v>
       </c>
       <c r="P647" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="Q647" t="inlineStr">
@@ -70134,14 +70130,18 @@
       </c>
       <c r="R647" t="inlineStr"/>
       <c r="S647" t="n">
-        <v>-1</v>
+        <v>-14</v>
       </c>
       <c r="T647" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN</t>
-        </is>
-      </c>
-      <c r="U647" t="inlineStr"/>
+          <t>NOSSO NOVO SUPERMERCADO</t>
+        </is>
+      </c>
+      <c r="U647" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V647" t="inlineStr"/>
       <c r="W647" t="inlineStr"/>
       <c r="X647" t="inlineStr"/>
@@ -70156,18 +70156,18 @@
       <c r="AE647" t="inlineStr"/>
       <c r="AF647" t="inlineStr">
         <is>
-          <t>Obrigação Acessória</t>
+          <t>Tarefa</t>
         </is>
       </c>
       <c r="AG647" t="inlineStr"/>
     </row>
     <row r="648">
       <c r="A648" t="n">
-        <v>5417</v>
+        <v>5617</v>
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
@@ -70187,7 +70187,7 @@
       </c>
       <c r="F648" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G648" t="n">
@@ -70217,7 +70217,7 @@
         </is>
       </c>
       <c r="O648" t="n">
-        <v>17398899</v>
+        <v>17407535</v>
       </c>
       <c r="P648" t="inlineStr">
         <is>
@@ -70235,7 +70235,7 @@
       </c>
       <c r="T648" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U648" t="inlineStr">
@@ -70264,11 +70264,11 @@
     </row>
     <row r="649">
       <c r="A649" t="n">
-        <v>5617</v>
+        <v>6627</v>
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
@@ -70283,7 +70283,7 @@
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F649" t="inlineStr">
@@ -70318,7 +70318,7 @@
         </is>
       </c>
       <c r="O649" t="n">
-        <v>17407535</v>
+        <v>17042325</v>
       </c>
       <c r="P649" t="inlineStr">
         <is>
@@ -70336,7 +70336,7 @@
       </c>
       <c r="T649" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t xml:space="preserve">GTG </t>
         </is>
       </c>
       <c r="U649" t="inlineStr">
@@ -70365,11 +70365,11 @@
     </row>
     <row r="650">
       <c r="A650" t="n">
-        <v>6627</v>
+        <v>6279</v>
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
+          <t>DIENNYFER DA S PEREIRA</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
@@ -70379,21 +70379,21 @@
       </c>
       <c r="D650" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E650" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F650" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G650" t="n">
-        <v>957</v>
+        <v>7027</v>
       </c>
       <c r="H650" t="n">
         <v>0</v>
@@ -70405,12 +70405,12 @@
       </c>
       <c r="J650" t="inlineStr">
         <is>
-          <t>Definição do Lucro Trimestral</t>
+          <t>Movimento - Sistema de Análise</t>
         </is>
       </c>
       <c r="K650" t="inlineStr"/>
       <c r="L650" s="1" t="n">
-        <v>46233</v>
+        <v>46227</v>
       </c>
       <c r="M650" t="inlineStr"/>
       <c r="N650" t="inlineStr">
@@ -70419,7 +70419,7 @@
         </is>
       </c>
       <c r="O650" t="n">
-        <v>17042325</v>
+        <v>17646102</v>
       </c>
       <c r="P650" t="inlineStr">
         <is>
@@ -70433,11 +70433,11 @@
       </c>
       <c r="R650" t="inlineStr"/>
       <c r="S650" t="n">
-        <v>-14</v>
+        <v>-8</v>
       </c>
       <c r="T650" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U650" t="inlineStr">
@@ -70445,7 +70445,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V650" t="inlineStr"/>
+      <c r="V650" t="inlineStr">
+        <is>
+          <t>Reaberto via API integração MGC x Sistema de Analise Fiscal em 16/07/2026 11:07:36. - Data Comentário: 16/07/2026 11:04</t>
+        </is>
+      </c>
       <c r="W650" t="inlineStr"/>
       <c r="X650" t="inlineStr"/>
       <c r="Y650" t="inlineStr"/>
@@ -76073,11 +76077,11 @@
     </row>
     <row r="701">
       <c r="A701" t="n">
-        <v>6404</v>
+        <v>6279</v>
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS LTDA</t>
+          <t>DIENNYFER DA S PEREIRA</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
@@ -76097,7 +76101,7 @@
       </c>
       <c r="F701" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G701" t="n">
@@ -76127,7 +76131,7 @@
         </is>
       </c>
       <c r="O701" t="n">
-        <v>16962336</v>
+        <v>17646092</v>
       </c>
       <c r="P701" t="inlineStr">
         <is>
@@ -76140,14 +76144,14 @@
         </is>
       </c>
       <c r="R701" s="1" t="n">
-        <v>46210.75621153935</v>
+        <v>46219.46361605324</v>
       </c>
       <c r="S701" t="n">
         <v>-7</v>
       </c>
       <c r="T701" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U701" t="inlineStr">
@@ -76157,7 +76161,7 @@
       </c>
       <c r="V701" t="inlineStr">
         <is>
-          <t>Baixado via API integração MGC x Sistema de Analise Fiscal em 07/07/2026 18:06:44. - Data Comentário: 07/07/2026 18:05</t>
+          <t>Baixado via API integração MGC x Sistema de Analise Fiscal em 16/07/2026 11:08:58. - Data Comentário: 16/07/2026 11:04</t>
         </is>
       </c>
       <c r="W701" t="inlineStr"/>
@@ -76188,11 +76192,11 @@
     </row>
     <row r="702">
       <c r="A702" t="n">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>SOLAR INVESTIMENTOS LTDA</t>
         </is>
       </c>
       <c r="C702" t="inlineStr">
@@ -76202,7 +76206,7 @@
       </c>
       <c r="D702" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E702" t="inlineStr">
@@ -76212,11 +76216,11 @@
       </c>
       <c r="F702" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G702" t="n">
-        <v>1793</v>
+        <v>7025</v>
       </c>
       <c r="H702" t="n">
         <v>0</v>
@@ -76228,25 +76232,21 @@
       </c>
       <c r="J702" t="inlineStr">
         <is>
-          <t>Mun - ISS Serv. Tomados</t>
+          <t>Movimento - Sistema de Análise</t>
         </is>
       </c>
       <c r="K702" t="inlineStr"/>
       <c r="L702" s="1" t="n">
-        <v>46220</v>
-      </c>
-      <c r="M702" t="inlineStr">
-        <is>
-          <t>08/07/2026</t>
-        </is>
-      </c>
+        <v>46226</v>
+      </c>
+      <c r="M702" t="inlineStr"/>
       <c r="N702" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O702" t="n">
-        <v>17398943</v>
+        <v>16962336</v>
       </c>
       <c r="P702" t="inlineStr">
         <is>
@@ -76259,14 +76259,14 @@
         </is>
       </c>
       <c r="R702" s="1" t="n">
-        <v>46213.36370773148</v>
+        <v>46210.75621153935</v>
       </c>
       <c r="S702" t="n">
-        <v>-1</v>
+        <v>-7</v>
       </c>
       <c r="T702" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
+          <t>SOLAR INVESTIMENTOS</t>
         </is>
       </c>
       <c r="U702" t="inlineStr">
@@ -76276,7 +76276,7 @@
       </c>
       <c r="V702" t="inlineStr">
         <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 08/07/2026 - Data Comentário: 06/07/2026 15:51</t>
+          <t>Baixado via API integração MGC x Sistema de Analise Fiscal em 07/07/2026 18:06:44. - Data Comentário: 07/07/2026 18:05</t>
         </is>
       </c>
       <c r="W702" t="inlineStr"/>
@@ -76287,7 +76287,7 @@
       </c>
       <c r="AA702" t="inlineStr">
         <is>
-          <t>Cristina Leite</t>
+          <t>ex-funcionario</t>
         </is>
       </c>
       <c r="AB702" t="inlineStr"/>
@@ -76296,7 +76296,7 @@
       <c r="AE702" t="inlineStr"/>
       <c r="AF702" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Tarefa</t>
         </is>
       </c>
       <c r="AG702" t="inlineStr">
@@ -76307,11 +76307,11 @@
     </row>
     <row r="703">
       <c r="A703" t="n">
-        <v>6628</v>
+        <v>5417</v>
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
@@ -76321,51 +76321,55 @@
       </c>
       <c r="D703" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E703" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F703" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G703" t="n">
-        <v>945</v>
+        <v>1793</v>
       </c>
       <c r="H703" t="n">
         <v>0</v>
       </c>
       <c r="I703" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J703" t="inlineStr">
         <is>
-          <t>Confirm Rec - DAS</t>
+          <t>Mun - ISS Serv. Tomados</t>
         </is>
       </c>
       <c r="K703" t="inlineStr"/>
       <c r="L703" s="1" t="n">
-        <v>46223</v>
-      </c>
-      <c r="M703" t="inlineStr"/>
+        <v>46220</v>
+      </c>
+      <c r="M703" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
       <c r="N703" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O703" t="n">
-        <v>16959936</v>
+        <v>17398943</v>
       </c>
       <c r="P703" t="inlineStr">
         <is>
-          <t>Victoria Virgens</t>
+          <t>Cristina Leite</t>
         </is>
       </c>
       <c r="Q703" t="inlineStr">
@@ -76374,14 +76378,14 @@
         </is>
       </c>
       <c r="R703" s="1" t="n">
-        <v>46204.04179737269</v>
+        <v>46213.36370773148</v>
       </c>
       <c r="S703" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="T703" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
+          <t>NOSSO NOVO SUPERMERCADO</t>
         </is>
       </c>
       <c r="U703" t="inlineStr">
@@ -76391,7 +76395,7 @@
       </c>
       <c r="V703" t="inlineStr">
         <is>
-          <t>Baixado via Rotina Configuração Após Baixa de tarefa, tarefas estão pedentes:[1879]. - Data Comentário: 01/07/2026 00:59</t>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 08/07/2026 - Data Comentário: 06/07/2026 15:51</t>
         </is>
       </c>
       <c r="W703" t="inlineStr"/>
@@ -76402,7 +76406,7 @@
       </c>
       <c r="AA703" t="inlineStr">
         <is>
-          <t>ex-funcionario</t>
+          <t>Cristina Leite</t>
         </is>
       </c>
       <c r="AB703" t="inlineStr"/>
@@ -76414,15 +76418,19 @@
           <t>Imposto</t>
         </is>
       </c>
-      <c r="AG703" t="inlineStr"/>
+      <c r="AG703" t="inlineStr">
+        <is>
+          <t>Ricardo Fischer</t>
+        </is>
+      </c>
     </row>
     <row r="704">
       <c r="A704" t="n">
-        <v>6705</v>
+        <v>6628</v>
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>NARCIZO ALVES CORDEIRO</t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C704" t="inlineStr">
@@ -76437,7 +76445,7 @@
       </c>
       <c r="E704" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F704" t="inlineStr">
@@ -76472,7 +76480,7 @@
         </is>
       </c>
       <c r="O704" t="n">
-        <v>17952522</v>
+        <v>16959936</v>
       </c>
       <c r="P704" t="inlineStr">
         <is>
@@ -76485,14 +76493,14 @@
         </is>
       </c>
       <c r="R704" s="1" t="n">
-        <v>46218.72615659722</v>
+        <v>46204.04179737269</v>
       </c>
       <c r="S704" t="n">
         <v>-4</v>
       </c>
       <c r="T704" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t xml:space="preserve">GTG </t>
         </is>
       </c>
       <c r="U704" t="inlineStr">
@@ -76502,7 +76510,7 @@
       </c>
       <c r="V704" t="inlineStr">
         <is>
-          <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1805] sendo a ultima baixa feita [1805]-14/07/2026 10:55:51.. - Data Comentário: 14/07/2026 10:54</t>
+          <t>Baixado via Rotina Configuração Após Baixa de tarefa, tarefas estão pedentes:[1879]. - Data Comentário: 01/07/2026 00:59</t>
         </is>
       </c>
       <c r="W704" t="inlineStr"/>
@@ -76513,7 +76521,7 @@
       </c>
       <c r="AA704" t="inlineStr">
         <is>
-          <t>Victoria Virgens</t>
+          <t>ex-funcionario</t>
         </is>
       </c>
       <c r="AB704" t="inlineStr"/>
@@ -76529,11 +76537,11 @@
     </row>
     <row r="705">
       <c r="A705" t="n">
-        <v>6779</v>
+        <v>6705</v>
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>CORDEIRO E CIA LTDA</t>
+          <t>NARCIZO ALVES CORDEIRO</t>
         </is>
       </c>
       <c r="C705" t="inlineStr">
@@ -76583,7 +76591,7 @@
         </is>
       </c>
       <c r="O705" t="n">
-        <v>18056693</v>
+        <v>17952522</v>
       </c>
       <c r="P705" t="inlineStr">
         <is>
@@ -76596,7 +76604,7 @@
         </is>
       </c>
       <c r="R705" s="1" t="n">
-        <v>46218.7261571412</v>
+        <v>46218.72615659722</v>
       </c>
       <c r="S705" t="n">
         <v>-4</v>
@@ -76606,10 +76614,14 @@
           <t>TECNO COM</t>
         </is>
       </c>
-      <c r="U705" t="inlineStr"/>
+      <c r="U705" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V705" t="inlineStr">
         <is>
-          <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1805] sendo a ultima baixa feita [1805]-14/07/2026 10:55:52.. - Data Comentário: 14/07/2026 10:54</t>
+          <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1805] sendo a ultima baixa feita [1805]-14/07/2026 10:55:51.. - Data Comentário: 14/07/2026 10:54</t>
         </is>
       </c>
       <c r="W705" t="inlineStr"/>
@@ -76636,11 +76648,11 @@
     </row>
     <row r="706">
       <c r="A706" t="n">
-        <v>6885</v>
+        <v>6779</v>
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
+          <t>CORDEIRO E CIA LTDA</t>
         </is>
       </c>
       <c r="C706" t="inlineStr">
@@ -76690,7 +76702,7 @@
         </is>
       </c>
       <c r="O706" t="n">
-        <v>18128639</v>
+        <v>18056693</v>
       </c>
       <c r="P706" t="inlineStr">
         <is>
@@ -76703,20 +76715,20 @@
         </is>
       </c>
       <c r="R706" s="1" t="n">
-        <v>46218.72455349537</v>
+        <v>46218.7261571412</v>
       </c>
       <c r="S706" t="n">
         <v>-4</v>
       </c>
       <c r="T706" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>TECNO COM</t>
         </is>
       </c>
       <c r="U706" t="inlineStr"/>
       <c r="V706" t="inlineStr">
         <is>
-          <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1805] sendo a ultima baixa feita [1805]-14/07/2026 09:05:39.. - Data Comentário: 14/07/2026 09:04</t>
+          <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1805] sendo a ultima baixa feita [1805]-14/07/2026 10:55:52.. - Data Comentário: 14/07/2026 10:54</t>
         </is>
       </c>
       <c r="W706" t="inlineStr"/>
@@ -76743,11 +76755,11 @@
     </row>
     <row r="707">
       <c r="A707" t="n">
-        <v>6945</v>
+        <v>6885</v>
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
+          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
         </is>
       </c>
       <c r="C707" t="inlineStr">
@@ -76762,7 +76774,7 @@
       </c>
       <c r="E707" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F707" t="inlineStr">
@@ -76797,7 +76809,7 @@
         </is>
       </c>
       <c r="O707" t="n">
-        <v>18164485</v>
+        <v>18128639</v>
       </c>
       <c r="P707" t="inlineStr">
         <is>
@@ -76810,18 +76822,22 @@
         </is>
       </c>
       <c r="R707" s="1" t="n">
-        <v>46210.80007584491</v>
+        <v>46218.72455349537</v>
       </c>
       <c r="S707" t="n">
         <v>-4</v>
       </c>
       <c r="T707" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U707" t="inlineStr"/>
-      <c r="V707" t="inlineStr"/>
+      <c r="V707" t="inlineStr">
+        <is>
+          <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1805] sendo a ultima baixa feita [1805]-14/07/2026 09:05:39.. - Data Comentário: 14/07/2026 09:04</t>
+        </is>
+      </c>
       <c r="W707" t="inlineStr"/>
       <c r="X707" t="inlineStr"/>
       <c r="Y707" t="inlineStr"/>
@@ -76846,11 +76862,11 @@
     </row>
     <row r="708">
       <c r="A708" t="n">
-        <v>5417</v>
+        <v>6945</v>
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
@@ -76860,21 +76876,21 @@
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E708" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F708" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G708" t="n">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="H708" t="n">
         <v>0</v>
@@ -76886,7 +76902,7 @@
       </c>
       <c r="J708" t="inlineStr">
         <is>
-          <t>Confirm Rec - ICMS RPA</t>
+          <t>Confirm Rec - DAS</t>
         </is>
       </c>
       <c r="K708" t="inlineStr"/>
@@ -76900,7 +76916,7 @@
         </is>
       </c>
       <c r="O708" t="n">
-        <v>17398867</v>
+        <v>18164485</v>
       </c>
       <c r="P708" t="inlineStr">
         <is>
@@ -76913,26 +76929,18 @@
         </is>
       </c>
       <c r="R708" s="1" t="n">
-        <v>46204.16684155093</v>
+        <v>46210.80007584491</v>
       </c>
       <c r="S708" t="n">
         <v>-4</v>
       </c>
       <c r="T708" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
-        </is>
-      </c>
-      <c r="U708" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="V708" t="inlineStr">
-        <is>
-          <t>Baixado via Rotina Configuração Após Baixa de tarefa, tarefas estão pedentes:[11286]. - Data Comentário: 01/07/2026 03:59</t>
-        </is>
-      </c>
+          <t>BRASIL DISTRIBUIDORA</t>
+        </is>
+      </c>
+      <c r="U708" t="inlineStr"/>
+      <c r="V708" t="inlineStr"/>
       <c r="W708" t="inlineStr"/>
       <c r="X708" t="inlineStr"/>
       <c r="Y708" t="inlineStr"/>
@@ -76941,7 +76949,7 @@
       </c>
       <c r="AA708" t="inlineStr">
         <is>
-          <t>ex-funcionario</t>
+          <t>Victoria Virgens</t>
         </is>
       </c>
       <c r="AB708" t="inlineStr"/>
@@ -76957,11 +76965,11 @@
     </row>
     <row r="709">
       <c r="A709" t="n">
-        <v>6278</v>
+        <v>5417</v>
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS LTDA</t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C709" t="inlineStr">
@@ -76971,7 +76979,7 @@
       </c>
       <c r="D709" t="inlineStr">
         <is>
-          <t>Federal - Lucro Real - Anual</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E709" t="inlineStr">
@@ -76981,7 +76989,7 @@
       </c>
       <c r="F709" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G709" t="n">
@@ -77011,7 +77019,7 @@
         </is>
       </c>
       <c r="O709" t="n">
-        <v>17539708</v>
+        <v>17398867</v>
       </c>
       <c r="P709" t="inlineStr">
         <is>
@@ -77024,14 +77032,14 @@
         </is>
       </c>
       <c r="R709" s="1" t="n">
-        <v>46023.15052158565</v>
+        <v>46204.16684155093</v>
       </c>
       <c r="S709" t="n">
         <v>-4</v>
       </c>
       <c r="T709" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>NOSSO NOVO SUPERMERCADO</t>
         </is>
       </c>
       <c r="U709" t="inlineStr">
@@ -77039,7 +77047,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V709" t="inlineStr"/>
+      <c r="V709" t="inlineStr">
+        <is>
+          <t>Baixado via Rotina Configuração Após Baixa de tarefa, tarefas estão pedentes:[11286]. - Data Comentário: 01/07/2026 03:59</t>
+        </is>
+      </c>
       <c r="W709" t="inlineStr"/>
       <c r="X709" t="inlineStr"/>
       <c r="Y709" t="inlineStr"/>
@@ -77064,11 +77076,11 @@
     </row>
     <row r="710">
       <c r="A710" t="n">
-        <v>6404</v>
+        <v>6278</v>
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS LTDA</t>
+          <t>EMPORIO DOS FRIOS LTDA</t>
         </is>
       </c>
       <c r="C710" t="inlineStr">
@@ -77078,7 +77090,7 @@
       </c>
       <c r="D710" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - Lucro Real - Anual</t>
         </is>
       </c>
       <c r="E710" t="inlineStr">
@@ -77118,7 +77130,7 @@
         </is>
       </c>
       <c r="O710" t="n">
-        <v>16962091</v>
+        <v>17539708</v>
       </c>
       <c r="P710" t="inlineStr">
         <is>
@@ -77131,14 +77143,14 @@
         </is>
       </c>
       <c r="R710" s="1" t="n">
-        <v>46204.12510590278</v>
+        <v>46023.15052158565</v>
       </c>
       <c r="S710" t="n">
         <v>-4</v>
       </c>
       <c r="T710" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U710" t="inlineStr">
@@ -77146,11 +77158,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V710" t="inlineStr">
-        <is>
-          <t>Baixado via Rotina Configuração Após Baixa de tarefa, tarefas estão pedentes:[11286]. - Data Comentário: 01/07/2026 02:59</t>
-        </is>
-      </c>
+      <c r="V710" t="inlineStr"/>
       <c r="W710" t="inlineStr"/>
       <c r="X710" t="inlineStr"/>
       <c r="Y710" t="inlineStr"/>
@@ -77175,11 +77183,11 @@
     </row>
     <row r="711">
       <c r="A711" t="n">
-        <v>6703</v>
+        <v>6404</v>
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
+          <t>SOLAR INVESTIMENTOS LTDA</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
@@ -77229,7 +77237,7 @@
         </is>
       </c>
       <c r="O711" t="n">
-        <v>17941130</v>
+        <v>16962091</v>
       </c>
       <c r="P711" t="inlineStr">
         <is>
@@ -77242,14 +77250,14 @@
         </is>
       </c>
       <c r="R711" s="1" t="n">
-        <v>46204.37521674769</v>
+        <v>46204.12510590278</v>
       </c>
       <c r="S711" t="n">
         <v>-4</v>
       </c>
       <c r="T711" t="inlineStr">
         <is>
-          <t>LIMA MOTA</t>
+          <t>SOLAR INVESTIMENTOS</t>
         </is>
       </c>
       <c r="U711" t="inlineStr">
@@ -77259,7 +77267,7 @@
       </c>
       <c r="V711" t="inlineStr">
         <is>
-          <t>Baixado via Rotina Configuração Após Baixa de tarefa, tarefas estão pedentes:[1802]. - Data Comentário: 01/07/2026 08:59</t>
+          <t>Baixado via Rotina Configuração Após Baixa de tarefa, tarefas estão pedentes:[11286]. - Data Comentário: 01/07/2026 02:59</t>
         </is>
       </c>
       <c r="W711" t="inlineStr"/>
@@ -77286,11 +77294,11 @@
     </row>
     <row r="712">
       <c r="A712" t="n">
-        <v>6704</v>
+        <v>6703</v>
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>TECNO COM INFORMATICA LTDA</t>
+          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
@@ -77300,7 +77308,7 @@
       </c>
       <c r="D712" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E712" t="inlineStr">
@@ -77340,7 +77348,7 @@
         </is>
       </c>
       <c r="O712" t="n">
-        <v>17952323</v>
+        <v>17941130</v>
       </c>
       <c r="P712" t="inlineStr">
         <is>
@@ -77353,14 +77361,14 @@
         </is>
       </c>
       <c r="R712" s="1" t="n">
-        <v>46057.39078310185</v>
+        <v>46204.37521674769</v>
       </c>
       <c r="S712" t="n">
         <v>-4</v>
       </c>
       <c r="T712" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>LIMA MOTA</t>
         </is>
       </c>
       <c r="U712" t="inlineStr">
@@ -77368,7 +77376,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V712" t="inlineStr"/>
+      <c r="V712" t="inlineStr">
+        <is>
+          <t>Baixado via Rotina Configuração Após Baixa de tarefa, tarefas estão pedentes:[1802]. - Data Comentário: 01/07/2026 08:59</t>
+        </is>
+      </c>
       <c r="W712" t="inlineStr"/>
       <c r="X712" t="inlineStr"/>
       <c r="Y712" t="inlineStr"/>
@@ -77393,11 +77405,11 @@
     </row>
     <row r="713">
       <c r="A713" t="n">
-        <v>6885</v>
+        <v>6704</v>
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
+          <t>TECNO COM INFORMATICA LTDA</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
@@ -77407,7 +77419,7 @@
       </c>
       <c r="D713" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E713" t="inlineStr">
@@ -77447,7 +77459,7 @@
         </is>
       </c>
       <c r="O713" t="n">
-        <v>18128648</v>
+        <v>17952323</v>
       </c>
       <c r="P713" t="inlineStr">
         <is>
@@ -77460,17 +77472,21 @@
         </is>
       </c>
       <c r="R713" s="1" t="n">
-        <v>46216.49331971065</v>
+        <v>46057.39078310185</v>
       </c>
       <c r="S713" t="n">
         <v>-4</v>
       </c>
       <c r="T713" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
-        </is>
-      </c>
-      <c r="U713" t="inlineStr"/>
+          <t>TECNO COM</t>
+        </is>
+      </c>
+      <c r="U713" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V713" t="inlineStr"/>
       <c r="W713" t="inlineStr"/>
       <c r="X713" t="inlineStr"/>
@@ -77480,7 +77496,7 @@
       </c>
       <c r="AA713" t="inlineStr">
         <is>
-          <t>Victoria Virgens</t>
+          <t>ex-funcionario</t>
         </is>
       </c>
       <c r="AB713" t="inlineStr"/>
@@ -77496,11 +77512,11 @@
     </row>
     <row r="714">
       <c r="A714" t="n">
-        <v>6945</v>
+        <v>6885</v>
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
+          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
@@ -77515,7 +77531,7 @@
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F714" t="inlineStr">
@@ -77550,7 +77566,7 @@
         </is>
       </c>
       <c r="O714" t="n">
-        <v>18164492</v>
+        <v>18128648</v>
       </c>
       <c r="P714" t="inlineStr">
         <is>
@@ -77563,14 +77579,14 @@
         </is>
       </c>
       <c r="R714" s="1" t="n">
-        <v>46216.49332078703</v>
+        <v>46216.49331971065</v>
       </c>
       <c r="S714" t="n">
         <v>-4</v>
       </c>
       <c r="T714" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U714" t="inlineStr"/>
@@ -77599,11 +77615,11 @@
     </row>
     <row r="715">
       <c r="A715" t="n">
-        <v>5417</v>
+        <v>6945</v>
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
@@ -77613,21 +77629,21 @@
       </c>
       <c r="D715" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G715" t="n">
-        <v>949</v>
+        <v>946</v>
       </c>
       <c r="H715" t="n">
         <v>0</v>
@@ -77639,12 +77655,12 @@
       </c>
       <c r="J715" t="inlineStr">
         <is>
-          <t>Confirm Rec - IRPJ/CSLL (CTB)</t>
+          <t>Confirm Rec - ICMS RPA</t>
         </is>
       </c>
       <c r="K715" t="inlineStr"/>
       <c r="L715" s="1" t="n">
-        <v>46233</v>
+        <v>46223</v>
       </c>
       <c r="M715" t="inlineStr"/>
       <c r="N715" t="inlineStr">
@@ -77653,7 +77669,7 @@
         </is>
       </c>
       <c r="O715" t="n">
-        <v>17398875</v>
+        <v>18164492</v>
       </c>
       <c r="P715" t="inlineStr">
         <is>
@@ -77666,26 +77682,18 @@
         </is>
       </c>
       <c r="R715" s="1" t="n">
-        <v>46204.29183217593</v>
+        <v>46216.49332078703</v>
       </c>
       <c r="S715" t="n">
-        <v>-14</v>
+        <v>-4</v>
       </c>
       <c r="T715" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
-        </is>
-      </c>
-      <c r="U715" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="V715" t="inlineStr">
-        <is>
-          <t>Baixado via Rotina Configuração Após Baixa de tarefa, tarefas estão pedentes:[1582]. - Data Comentário: 01/07/2026 06:59</t>
-        </is>
-      </c>
+          <t>BRASIL DISTRIBUIDORA</t>
+        </is>
+      </c>
+      <c r="U715" t="inlineStr"/>
+      <c r="V715" t="inlineStr"/>
       <c r="W715" t="inlineStr"/>
       <c r="X715" t="inlineStr"/>
       <c r="Y715" t="inlineStr"/>
@@ -77694,7 +77702,7 @@
       </c>
       <c r="AA715" t="inlineStr">
         <is>
-          <t>ex-funcionario</t>
+          <t>Victoria Virgens</t>
         </is>
       </c>
       <c r="AB715" t="inlineStr"/>
@@ -77710,11 +77718,11 @@
     </row>
     <row r="716">
       <c r="A716" t="n">
-        <v>6278</v>
+        <v>5417</v>
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS LTDA</t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
@@ -77724,7 +77732,7 @@
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>Federal - Lucro Real - Anual</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E716" t="inlineStr">
@@ -77734,7 +77742,7 @@
       </c>
       <c r="F716" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G716" t="n">
@@ -77764,7 +77772,7 @@
         </is>
       </c>
       <c r="O716" t="n">
-        <v>17539716</v>
+        <v>17398875</v>
       </c>
       <c r="P716" t="inlineStr">
         <is>
@@ -77777,14 +77785,14 @@
         </is>
       </c>
       <c r="R716" s="1" t="n">
-        <v>46204.33341168981</v>
+        <v>46204.29183217593</v>
       </c>
       <c r="S716" t="n">
         <v>-14</v>
       </c>
       <c r="T716" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>NOSSO NOVO SUPERMERCADO</t>
         </is>
       </c>
       <c r="U716" t="inlineStr">
@@ -77794,7 +77802,7 @@
       </c>
       <c r="V716" t="inlineStr">
         <is>
-          <t>Baixado via Rotina Configuração Após Baixa de tarefa, tarefas estão pedentes:[1582]. - Data Comentário: 01/07/2026 07:59</t>
+          <t>Baixado via Rotina Configuração Após Baixa de tarefa, tarefas estão pedentes:[1582]. - Data Comentário: 01/07/2026 06:59</t>
         </is>
       </c>
       <c r="W716" t="inlineStr"/>
@@ -77821,11 +77829,11 @@
     </row>
     <row r="717">
       <c r="A717" t="n">
-        <v>6627</v>
+        <v>6278</v>
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
+          <t>EMPORIO DOS FRIOS LTDA</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
@@ -77835,12 +77843,12 @@
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Real - Anual</t>
         </is>
       </c>
       <c r="E717" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F717" t="inlineStr">
@@ -77875,7 +77883,7 @@
         </is>
       </c>
       <c r="O717" t="n">
-        <v>17042295</v>
+        <v>17539716</v>
       </c>
       <c r="P717" t="inlineStr">
         <is>
@@ -77888,14 +77896,14 @@
         </is>
       </c>
       <c r="R717" s="1" t="n">
-        <v>46204.25011258102</v>
+        <v>46204.33341168981</v>
       </c>
       <c r="S717" t="n">
         <v>-14</v>
       </c>
       <c r="T717" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U717" t="inlineStr">
@@ -77905,7 +77913,7 @@
       </c>
       <c r="V717" t="inlineStr">
         <is>
-          <t>Baixado via Rotina Configuração Após Baixa de tarefa, tarefas estão pedentes:[1651]. - Data Comentário: 01/07/2026 05:59</t>
+          <t>Baixado via Rotina Configuração Após Baixa de tarefa, tarefas estão pedentes:[1582]. - Data Comentário: 01/07/2026 07:59</t>
         </is>
       </c>
       <c r="W717" t="inlineStr"/>
@@ -77932,11 +77940,11 @@
     </row>
     <row r="718">
       <c r="A718" t="n">
-        <v>6704</v>
+        <v>6627</v>
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>TECNO COM INFORMATICA LTDA</t>
+          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
@@ -77951,7 +77959,7 @@
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F718" t="inlineStr">
@@ -77986,7 +77994,7 @@
         </is>
       </c>
       <c r="O718" t="n">
-        <v>17952331</v>
+        <v>17042295</v>
       </c>
       <c r="P718" t="inlineStr">
         <is>
@@ -77999,14 +78007,14 @@
         </is>
       </c>
       <c r="R718" s="1" t="n">
-        <v>46204.37522271991</v>
+        <v>46204.25011258102</v>
       </c>
       <c r="S718" t="n">
         <v>-14</v>
       </c>
       <c r="T718" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t xml:space="preserve">GTG </t>
         </is>
       </c>
       <c r="U718" t="inlineStr">
@@ -78016,7 +78024,7 @@
       </c>
       <c r="V718" t="inlineStr">
         <is>
-          <t>Baixado via Rotina Configuração Após Baixa de tarefa, tarefas estão pedentes:[1582]. - Data Comentário: 01/07/2026 08:59</t>
+          <t>Baixado via Rotina Configuração Após Baixa de tarefa, tarefas estão pedentes:[1651]. - Data Comentário: 01/07/2026 05:59</t>
         </is>
       </c>
       <c r="W718" t="inlineStr"/>
@@ -78043,11 +78051,11 @@
     </row>
     <row r="719">
       <c r="A719" t="n">
-        <v>6404</v>
+        <v>6704</v>
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS LTDA</t>
+          <t>TECNO COM INFORMATICA LTDA</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
@@ -78057,7 +78065,7 @@
       </c>
       <c r="D719" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E719" t="inlineStr">
@@ -78071,7 +78079,7 @@
         </is>
       </c>
       <c r="G719" t="n">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="H719" t="n">
         <v>0</v>
@@ -78083,7 +78091,7 @@
       </c>
       <c r="J719" t="inlineStr">
         <is>
-          <t>Confirm Rec - IRPJ/CSLL (EF)</t>
+          <t>Confirm Rec - IRPJ/CSLL (CTB)</t>
         </is>
       </c>
       <c r="K719" t="inlineStr"/>
@@ -78097,7 +78105,7 @@
         </is>
       </c>
       <c r="O719" t="n">
-        <v>16962099</v>
+        <v>17952331</v>
       </c>
       <c r="P719" t="inlineStr">
         <is>
@@ -78110,14 +78118,14 @@
         </is>
       </c>
       <c r="R719" s="1" t="n">
-        <v>46204.25009074074</v>
+        <v>46204.37522271991</v>
       </c>
       <c r="S719" t="n">
         <v>-14</v>
       </c>
       <c r="T719" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS</t>
+          <t>TECNO COM</t>
         </is>
       </c>
       <c r="U719" t="inlineStr">
@@ -78127,7 +78135,7 @@
       </c>
       <c r="V719" t="inlineStr">
         <is>
-          <t>Baixado via Rotina Configuração Após Baixa de tarefa, tarefas estão pedentes:[1810]. - Data Comentário: 01/07/2026 05:59</t>
+          <t>Baixado via Rotina Configuração Após Baixa de tarefa, tarefas estão pedentes:[1582]. - Data Comentário: 01/07/2026 08:59</t>
         </is>
       </c>
       <c r="W719" t="inlineStr"/>
@@ -78154,11 +78162,11 @@
     </row>
     <row r="720">
       <c r="A720" t="n">
-        <v>6703</v>
+        <v>6404</v>
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
+          <t>SOLAR INVESTIMENTOS LTDA</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
@@ -78208,7 +78216,7 @@
         </is>
       </c>
       <c r="O720" t="n">
-        <v>17941138</v>
+        <v>16962099</v>
       </c>
       <c r="P720" t="inlineStr">
         <is>
@@ -78221,14 +78229,14 @@
         </is>
       </c>
       <c r="R720" s="1" t="n">
-        <v>46204.37521859954</v>
+        <v>46204.25009074074</v>
       </c>
       <c r="S720" t="n">
         <v>-14</v>
       </c>
       <c r="T720" t="inlineStr">
         <is>
-          <t>LIMA MOTA</t>
+          <t>SOLAR INVESTIMENTOS</t>
         </is>
       </c>
       <c r="U720" t="inlineStr">
@@ -78238,7 +78246,7 @@
       </c>
       <c r="V720" t="inlineStr">
         <is>
-          <t>Baixado via Rotina Configuração Após Baixa de tarefa, tarefas estão pedentes:[1810]. - Data Comentário: 01/07/2026 08:59</t>
+          <t>Baixado via Rotina Configuração Após Baixa de tarefa, tarefas estão pedentes:[1810]. - Data Comentário: 01/07/2026 05:59</t>
         </is>
       </c>
       <c r="W720" t="inlineStr"/>
@@ -78265,11 +78273,11 @@
     </row>
     <row r="721">
       <c r="A721" t="n">
-        <v>5417</v>
+        <v>6703</v>
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
@@ -78279,7 +78287,7 @@
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E721" t="inlineStr">
@@ -78289,11 +78297,11 @@
       </c>
       <c r="F721" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G721" t="n">
-        <v>953</v>
+        <v>948</v>
       </c>
       <c r="H721" t="n">
         <v>0</v>
@@ -78305,12 +78313,12 @@
       </c>
       <c r="J721" t="inlineStr">
         <is>
-          <t>Confirm Rec - PIS/COFINS</t>
+          <t>Confirm Rec - IRPJ/CSLL (EF)</t>
         </is>
       </c>
       <c r="K721" t="inlineStr"/>
       <c r="L721" s="1" t="n">
-        <v>46227</v>
+        <v>46233</v>
       </c>
       <c r="M721" t="inlineStr"/>
       <c r="N721" t="inlineStr">
@@ -78319,7 +78327,7 @@
         </is>
       </c>
       <c r="O721" t="n">
-        <v>17398881</v>
+        <v>17941138</v>
       </c>
       <c r="P721" t="inlineStr">
         <is>
@@ -78332,14 +78340,14 @@
         </is>
       </c>
       <c r="R721" s="1" t="n">
-        <v>46204.41730355324</v>
+        <v>46204.37521859954</v>
       </c>
       <c r="S721" t="n">
-        <v>-8</v>
+        <v>-14</v>
       </c>
       <c r="T721" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
+          <t>LIMA MOTA</t>
         </is>
       </c>
       <c r="U721" t="inlineStr">
@@ -78349,7 +78357,7 @@
       </c>
       <c r="V721" t="inlineStr">
         <is>
-          <t>Baixado via Rotina Configuração Após Baixa de tarefa, tarefas estão pedentes:[1808]. - Data Comentário: 01/07/2026 10:00</t>
+          <t>Baixado via Rotina Configuração Após Baixa de tarefa, tarefas estão pedentes:[1810]. - Data Comentário: 01/07/2026 08:59</t>
         </is>
       </c>
       <c r="W721" t="inlineStr"/>
@@ -78376,11 +78384,11 @@
     </row>
     <row r="722">
       <c r="A722" t="n">
-        <v>6278</v>
+        <v>5417</v>
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS LTDA</t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
@@ -78390,7 +78398,7 @@
       </c>
       <c r="D722" t="inlineStr">
         <is>
-          <t>Federal - Lucro Real - Anual</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E722" t="inlineStr">
@@ -78400,7 +78408,7 @@
       </c>
       <c r="F722" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G722" t="n">
@@ -78430,7 +78438,7 @@
         </is>
       </c>
       <c r="O722" t="n">
-        <v>17539722</v>
+        <v>17398881</v>
       </c>
       <c r="P722" t="inlineStr">
         <is>
@@ -78443,14 +78451,14 @@
         </is>
       </c>
       <c r="R722" s="1" t="n">
-        <v>46023.15053034722</v>
+        <v>46204.41730355324</v>
       </c>
       <c r="S722" t="n">
         <v>-8</v>
       </c>
       <c r="T722" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>NOSSO NOVO SUPERMERCADO</t>
         </is>
       </c>
       <c r="U722" t="inlineStr">
@@ -78458,7 +78466,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V722" t="inlineStr"/>
+      <c r="V722" t="inlineStr">
+        <is>
+          <t>Baixado via Rotina Configuração Após Baixa de tarefa, tarefas estão pedentes:[1808]. - Data Comentário: 01/07/2026 10:00</t>
+        </is>
+      </c>
       <c r="W722" t="inlineStr"/>
       <c r="X722" t="inlineStr"/>
       <c r="Y722" t="inlineStr"/>
@@ -78483,11 +78495,11 @@
     </row>
     <row r="723">
       <c r="A723" t="n">
-        <v>6404</v>
+        <v>6278</v>
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS LTDA</t>
+          <t>EMPORIO DOS FRIOS LTDA</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
@@ -78497,7 +78509,7 @@
       </c>
       <c r="D723" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - Lucro Real - Anual</t>
         </is>
       </c>
       <c r="E723" t="inlineStr">
@@ -78537,7 +78549,7 @@
         </is>
       </c>
       <c r="O723" t="n">
-        <v>16962105</v>
+        <v>17539722</v>
       </c>
       <c r="P723" t="inlineStr">
         <is>
@@ -78550,14 +78562,14 @@
         </is>
       </c>
       <c r="R723" s="1" t="n">
-        <v>46204.41680613426</v>
+        <v>46023.15053034722</v>
       </c>
       <c r="S723" t="n">
         <v>-8</v>
       </c>
       <c r="T723" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U723" t="inlineStr">
@@ -78565,11 +78577,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V723" t="inlineStr">
-        <is>
-          <t>Baixado via Rotina Configuração Após Baixa de tarefa, tarefas estão pedentes:[1807]. - Data Comentário: 01/07/2026 09:59</t>
-        </is>
-      </c>
+      <c r="V723" t="inlineStr"/>
       <c r="W723" t="inlineStr"/>
       <c r="X723" t="inlineStr"/>
       <c r="Y723" t="inlineStr"/>
@@ -78594,11 +78602,11 @@
     </row>
     <row r="724">
       <c r="A724" t="n">
-        <v>6627</v>
+        <v>6404</v>
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
+          <t>SOLAR INVESTIMENTOS LTDA</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
@@ -78608,12 +78616,12 @@
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E724" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F724" t="inlineStr">
@@ -78648,7 +78656,7 @@
         </is>
       </c>
       <c r="O724" t="n">
-        <v>17042311</v>
+        <v>16962105</v>
       </c>
       <c r="P724" t="inlineStr">
         <is>
@@ -78661,14 +78669,14 @@
         </is>
       </c>
       <c r="R724" s="1" t="n">
-        <v>46204.41687068287</v>
+        <v>46204.41680613426</v>
       </c>
       <c r="S724" t="n">
         <v>-8</v>
       </c>
       <c r="T724" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
+          <t>SOLAR INVESTIMENTOS</t>
         </is>
       </c>
       <c r="U724" t="inlineStr">
@@ -78678,7 +78686,7 @@
       </c>
       <c r="V724" t="inlineStr">
         <is>
-          <t>Baixado via Rotina Configuração Após Baixa de tarefa, tarefas estão pedentes:[1882]. - Data Comentário: 01/07/2026 09:59</t>
+          <t>Baixado via Rotina Configuração Após Baixa de tarefa, tarefas estão pedentes:[1807]. - Data Comentário: 01/07/2026 09:59</t>
         </is>
       </c>
       <c r="W724" t="inlineStr"/>
@@ -78705,11 +78713,11 @@
     </row>
     <row r="725">
       <c r="A725" t="n">
-        <v>6703</v>
+        <v>6627</v>
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
+          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
@@ -78719,12 +78727,12 @@
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E725" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F725" t="inlineStr">
@@ -78759,7 +78767,7 @@
         </is>
       </c>
       <c r="O725" t="n">
-        <v>17941164</v>
+        <v>17042311</v>
       </c>
       <c r="P725" t="inlineStr">
         <is>
@@ -78772,14 +78780,14 @@
         </is>
       </c>
       <c r="R725" s="1" t="n">
-        <v>46204.41788634259</v>
+        <v>46204.41687068287</v>
       </c>
       <c r="S725" t="n">
         <v>-8</v>
       </c>
       <c r="T725" t="inlineStr">
         <is>
-          <t>LIMA MOTA</t>
+          <t xml:space="preserve">GTG </t>
         </is>
       </c>
       <c r="U725" t="inlineStr">
@@ -78789,7 +78797,7 @@
       </c>
       <c r="V725" t="inlineStr">
         <is>
-          <t>Baixado via Rotina Configuração Após Baixa de tarefa, tarefas estão pedentes:[1807]. - Data Comentário: 01/07/2026 10:00</t>
+          <t>Baixado via Rotina Configuração Após Baixa de tarefa, tarefas estão pedentes:[1882]. - Data Comentário: 01/07/2026 09:59</t>
         </is>
       </c>
       <c r="W725" t="inlineStr"/>
@@ -78816,11 +78824,11 @@
     </row>
     <row r="726">
       <c r="A726" t="n">
-        <v>6704</v>
+        <v>6703</v>
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>TECNO COM INFORMATICA LTDA</t>
+          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
@@ -78830,7 +78838,7 @@
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E726" t="inlineStr">
@@ -78870,7 +78878,7 @@
         </is>
       </c>
       <c r="O726" t="n">
-        <v>17952360</v>
+        <v>17941164</v>
       </c>
       <c r="P726" t="inlineStr">
         <is>
@@ -78883,14 +78891,14 @@
         </is>
       </c>
       <c r="R726" s="1" t="n">
-        <v>46057.3907997338</v>
+        <v>46204.41788634259</v>
       </c>
       <c r="S726" t="n">
         <v>-8</v>
       </c>
       <c r="T726" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>LIMA MOTA</t>
         </is>
       </c>
       <c r="U726" t="inlineStr">
@@ -78898,7 +78906,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V726" t="inlineStr"/>
+      <c r="V726" t="inlineStr">
+        <is>
+          <t>Baixado via Rotina Configuração Após Baixa de tarefa, tarefas estão pedentes:[1807]. - Data Comentário: 01/07/2026 10:00</t>
+        </is>
+      </c>
       <c r="W726" t="inlineStr"/>
       <c r="X726" t="inlineStr"/>
       <c r="Y726" t="inlineStr"/>
@@ -78923,11 +78935,11 @@
     </row>
     <row r="727">
       <c r="A727" t="n">
-        <v>6962</v>
+        <v>6704</v>
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
+          <t>TECNO COM INFORMATICA LTDA</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
@@ -78947,7 +78959,7 @@
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G727" t="n">
@@ -78977,26 +78989,34 @@
         </is>
       </c>
       <c r="O727" t="n">
-        <v>18188729</v>
-      </c>
-      <c r="P727" t="inlineStr"/>
+        <v>17952360</v>
+      </c>
+      <c r="P727" t="inlineStr">
+        <is>
+          <t>Victoria Virgens</t>
+        </is>
+      </c>
       <c r="Q727" t="inlineStr">
         <is>
           <t>Baixado</t>
         </is>
       </c>
       <c r="R727" s="1" t="n">
-        <v>46192.56685792824</v>
+        <v>46057.3907997338</v>
       </c>
       <c r="S727" t="n">
         <v>-8</v>
       </c>
       <c r="T727" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN</t>
-        </is>
-      </c>
-      <c r="U727" t="inlineStr"/>
+          <t>TECNO COM</t>
+        </is>
+      </c>
+      <c r="U727" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V727" t="inlineStr"/>
       <c r="W727" t="inlineStr"/>
       <c r="X727" t="inlineStr"/>
@@ -79022,11 +79042,11 @@
     </row>
     <row r="728">
       <c r="A728" t="n">
-        <v>6963</v>
+        <v>6962</v>
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN LTDA</t>
+          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
         </is>
       </c>
       <c r="C728" t="inlineStr">
@@ -79076,7 +79096,7 @@
         </is>
       </c>
       <c r="O728" t="n">
-        <v>18188635</v>
+        <v>18188729</v>
       </c>
       <c r="P728" t="inlineStr"/>
       <c r="Q728" t="inlineStr">
@@ -79085,7 +79105,7 @@
         </is>
       </c>
       <c r="R728" s="1" t="n">
-        <v>46192.56339828703</v>
+        <v>46192.56685792824</v>
       </c>
       <c r="S728" t="n">
         <v>-8</v>
@@ -79121,11 +79141,11 @@
     </row>
     <row r="729">
       <c r="A729" t="n">
-        <v>6278</v>
+        <v>6963</v>
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS LTDA</t>
+          <t>PROMOTORAS GYN LTDA</t>
         </is>
       </c>
       <c r="C729" t="inlineStr">
@@ -79135,7 +79155,7 @@
       </c>
       <c r="D729" t="inlineStr">
         <is>
-          <t>Federal - Lucro Real - Anual</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E729" t="inlineStr">
@@ -79145,11 +79165,11 @@
       </c>
       <c r="F729" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Reynaldo Santos</t>
         </is>
       </c>
       <c r="G729" t="n">
-        <v>7022</v>
+        <v>953</v>
       </c>
       <c r="H729" t="n">
         <v>0</v>
@@ -79161,12 +79181,12 @@
       </c>
       <c r="J729" t="inlineStr">
         <is>
-          <t xml:space="preserve">Confirm. Rec - Impostos DCTF WEB </t>
+          <t>Confirm Rec - PIS/COFINS</t>
         </is>
       </c>
       <c r="K729" t="inlineStr"/>
       <c r="L729" s="1" t="n">
-        <v>46223</v>
+        <v>46227</v>
       </c>
       <c r="M729" t="inlineStr"/>
       <c r="N729" t="inlineStr">
@@ -79175,39 +79195,27 @@
         </is>
       </c>
       <c r="O729" t="n">
-        <v>17539776</v>
-      </c>
-      <c r="P729" t="inlineStr">
-        <is>
-          <t>Victoria Virgens</t>
-        </is>
-      </c>
+        <v>18188635</v>
+      </c>
+      <c r="P729" t="inlineStr"/>
       <c r="Q729" t="inlineStr">
         <is>
           <t>Baixado</t>
         </is>
       </c>
       <c r="R729" s="1" t="n">
-        <v>46204.41751620371</v>
+        <v>46192.56339828703</v>
       </c>
       <c r="S729" t="n">
-        <v>-4</v>
+        <v>-8</v>
       </c>
       <c r="T729" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
-        </is>
-      </c>
-      <c r="U729" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="V729" t="inlineStr">
-        <is>
-          <t>Baixado via Rotina Configuração Após Baixa de tarefa, tarefas estão pedentes:[7051]. - Data Comentário: 01/07/2026 10:00</t>
-        </is>
-      </c>
+          <t>PROMOTORAS GYN</t>
+        </is>
+      </c>
+      <c r="U729" t="inlineStr"/>
+      <c r="V729" t="inlineStr"/>
       <c r="W729" t="inlineStr"/>
       <c r="X729" t="inlineStr"/>
       <c r="Y729" t="inlineStr"/>
@@ -79232,11 +79240,11 @@
     </row>
     <row r="730">
       <c r="A730" t="n">
-        <v>6704</v>
+        <v>6278</v>
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>TECNO COM INFORMATICA LTDA</t>
+          <t>EMPORIO DOS FRIOS LTDA</t>
         </is>
       </c>
       <c r="C730" t="inlineStr">
@@ -79246,7 +79254,7 @@
       </c>
       <c r="D730" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Real - Anual</t>
         </is>
       </c>
       <c r="E730" t="inlineStr">
@@ -79286,7 +79294,7 @@
         </is>
       </c>
       <c r="O730" t="n">
-        <v>17952419</v>
+        <v>17539776</v>
       </c>
       <c r="P730" t="inlineStr">
         <is>
@@ -79299,14 +79307,14 @@
         </is>
       </c>
       <c r="R730" s="1" t="n">
-        <v>46204.41788753472</v>
+        <v>46204.41751620371</v>
       </c>
       <c r="S730" t="n">
         <v>-4</v>
       </c>
       <c r="T730" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U730" t="inlineStr">
@@ -79343,11 +79351,11 @@
     </row>
     <row r="731">
       <c r="A731" t="n">
-        <v>6945</v>
+        <v>6704</v>
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
+          <t>TECNO COM INFORMATICA LTDA</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
@@ -79357,12 +79365,12 @@
       </c>
       <c r="D731" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E731" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F731" t="inlineStr">
@@ -79397,27 +79405,39 @@
         </is>
       </c>
       <c r="O731" t="n">
-        <v>18164534</v>
-      </c>
-      <c r="P731" t="inlineStr"/>
+        <v>17952419</v>
+      </c>
+      <c r="P731" t="inlineStr">
+        <is>
+          <t>Victoria Virgens</t>
+        </is>
+      </c>
       <c r="Q731" t="inlineStr">
         <is>
           <t>Baixado</t>
         </is>
       </c>
       <c r="R731" s="1" t="n">
-        <v>46168.72822039352</v>
+        <v>46204.41788753472</v>
       </c>
       <c r="S731" t="n">
         <v>-4</v>
       </c>
       <c r="T731" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA</t>
-        </is>
-      </c>
-      <c r="U731" t="inlineStr"/>
-      <c r="V731" t="inlineStr"/>
+          <t>TECNO COM</t>
+        </is>
+      </c>
+      <c r="U731" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V731" t="inlineStr">
+        <is>
+          <t>Baixado via Rotina Configuração Após Baixa de tarefa, tarefas estão pedentes:[7051]. - Data Comentário: 01/07/2026 10:00</t>
+        </is>
+      </c>
       <c r="W731" t="inlineStr"/>
       <c r="X731" t="inlineStr"/>
       <c r="Y731" t="inlineStr"/>
@@ -79442,11 +79462,11 @@
     </row>
     <row r="732">
       <c r="A732" t="n">
-        <v>6962</v>
+        <v>6945</v>
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
+          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
@@ -79456,17 +79476,17 @@
       </c>
       <c r="D732" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E732" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F732" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G732" t="n">
@@ -79496,7 +79516,7 @@
         </is>
       </c>
       <c r="O732" t="n">
-        <v>18188757</v>
+        <v>18164534</v>
       </c>
       <c r="P732" t="inlineStr"/>
       <c r="Q732" t="inlineStr">
@@ -79505,14 +79525,14 @@
         </is>
       </c>
       <c r="R732" s="1" t="n">
-        <v>46192.56687770833</v>
+        <v>46168.72822039352</v>
       </c>
       <c r="S732" t="n">
         <v>-4</v>
       </c>
       <c r="T732" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN</t>
+          <t>BRASIL DISTRIBUIDORA</t>
         </is>
       </c>
       <c r="U732" t="inlineStr"/>
@@ -79541,11 +79561,11 @@
     </row>
     <row r="733">
       <c r="A733" t="n">
-        <v>6963</v>
+        <v>6962</v>
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN LTDA</t>
+          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
@@ -79595,7 +79615,7 @@
         </is>
       </c>
       <c r="O733" t="n">
-        <v>18188663</v>
+        <v>18188757</v>
       </c>
       <c r="P733" t="inlineStr"/>
       <c r="Q733" t="inlineStr">
@@ -79604,7 +79624,7 @@
         </is>
       </c>
       <c r="R733" s="1" t="n">
-        <v>46192.56342578704</v>
+        <v>46192.56687770833</v>
       </c>
       <c r="S733" t="n">
         <v>-4</v>
@@ -79640,11 +79660,11 @@
     </row>
     <row r="734">
       <c r="A734" t="n">
-        <v>5417</v>
+        <v>6963</v>
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>PROMOTORAS GYN LTDA</t>
         </is>
       </c>
       <c r="C734" t="inlineStr">
@@ -79664,11 +79684,11 @@
       </c>
       <c r="F734" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Reynaldo Santos</t>
         </is>
       </c>
       <c r="G734" t="n">
-        <v>940</v>
+        <v>7022</v>
       </c>
       <c r="H734" t="n">
         <v>0</v>
@@ -79680,48 +79700,40 @@
       </c>
       <c r="J734" t="inlineStr">
         <is>
-          <t>DEC - Consulta 2º Quinzena</t>
+          <t xml:space="preserve">Confirm. Rec - Impostos DCTF WEB </t>
         </is>
       </c>
       <c r="K734" t="inlineStr"/>
       <c r="L734" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="M734" t="inlineStr"/>
       <c r="N734" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
       <c r="O734" t="n">
-        <v>17398838</v>
-      </c>
-      <c r="P734" t="inlineStr">
-        <is>
-          <t>Victoria Virgens</t>
-        </is>
-      </c>
+        <v>18188663</v>
+      </c>
+      <c r="P734" t="inlineStr"/>
       <c r="Q734" t="inlineStr">
         <is>
           <t>Baixado</t>
         </is>
       </c>
       <c r="R734" s="1" t="n">
-        <v>46213.75219915509</v>
+        <v>46192.56342578704</v>
       </c>
       <c r="S734" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="T734" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
-        </is>
-      </c>
-      <c r="U734" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>PROMOTORAS GYN</t>
+        </is>
+      </c>
+      <c r="U734" t="inlineStr"/>
       <c r="V734" t="inlineStr"/>
       <c r="W734" t="inlineStr"/>
       <c r="X734" t="inlineStr"/>
@@ -79740,18 +79752,18 @@
       <c r="AE734" t="inlineStr"/>
       <c r="AF734" t="inlineStr">
         <is>
-          <t>Obrigação Acessória</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="AG734" t="inlineStr"/>
     </row>
     <row r="735">
       <c r="A735" t="n">
-        <v>5617</v>
+        <v>5417</v>
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
@@ -79771,7 +79783,7 @@
       </c>
       <c r="F735" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G735" t="n">
@@ -79801,7 +79813,7 @@
         </is>
       </c>
       <c r="O735" t="n">
-        <v>17407498</v>
+        <v>17398838</v>
       </c>
       <c r="P735" t="inlineStr">
         <is>
@@ -79814,14 +79826,14 @@
         </is>
       </c>
       <c r="R735" s="1" t="n">
-        <v>46213.75220699074</v>
+        <v>46213.75219915509</v>
       </c>
       <c r="S735" t="n">
         <v>-1</v>
       </c>
       <c r="T735" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>NOSSO NOVO SUPERMERCADO</t>
         </is>
       </c>
       <c r="U735" t="inlineStr">
@@ -79854,11 +79866,11 @@
     </row>
     <row r="736">
       <c r="A736" t="n">
-        <v>6224</v>
+        <v>5617</v>
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C736" t="inlineStr">
@@ -79878,7 +79890,7 @@
       </c>
       <c r="F736" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G736" t="n">
@@ -79908,7 +79920,7 @@
         </is>
       </c>
       <c r="O736" t="n">
-        <v>17688584</v>
+        <v>17407498</v>
       </c>
       <c r="P736" t="inlineStr">
         <is>
@@ -79921,7 +79933,7 @@
         </is>
       </c>
       <c r="R736" s="1" t="n">
-        <v>46218.50235163194</v>
+        <v>46213.75220699074</v>
       </c>
       <c r="S736" t="n">
         <v>-1</v>
@@ -79961,11 +79973,11 @@
     </row>
     <row r="737">
       <c r="A737" t="n">
-        <v>6404</v>
+        <v>6224</v>
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C737" t="inlineStr">
@@ -79975,7 +79987,7 @@
       </c>
       <c r="D737" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E737" t="inlineStr">
@@ -79985,7 +79997,7 @@
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G737" t="n">
@@ -80015,7 +80027,7 @@
         </is>
       </c>
       <c r="O737" t="n">
-        <v>16962072</v>
+        <v>17688584</v>
       </c>
       <c r="P737" t="inlineStr">
         <is>
@@ -80028,14 +80040,14 @@
         </is>
       </c>
       <c r="R737" s="1" t="n">
-        <v>46213.75224594907</v>
+        <v>46218.50235163194</v>
       </c>
       <c r="S737" t="n">
         <v>-1</v>
       </c>
       <c r="T737" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U737" t="inlineStr">
@@ -80068,11 +80080,11 @@
     </row>
     <row r="738">
       <c r="A738" t="n">
-        <v>6486</v>
+        <v>6404</v>
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>PC GAMER GOIANIA LTDA</t>
+          <t>SOLAR INVESTIMENTOS LTDA</t>
         </is>
       </c>
       <c r="C738" t="inlineStr">
@@ -80082,7 +80094,7 @@
       </c>
       <c r="D738" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E738" t="inlineStr">
@@ -80122,7 +80134,7 @@
         </is>
       </c>
       <c r="O738" t="n">
-        <v>16975869</v>
+        <v>16962072</v>
       </c>
       <c r="P738" t="inlineStr">
         <is>
@@ -80135,14 +80147,14 @@
         </is>
       </c>
       <c r="R738" s="1" t="n">
-        <v>46213.75225217592</v>
+        <v>46213.75224594907</v>
       </c>
       <c r="S738" t="n">
         <v>-1</v>
       </c>
       <c r="T738" t="inlineStr">
         <is>
-          <t>PC GAMER</t>
+          <t>SOLAR INVESTIMENTOS</t>
         </is>
       </c>
       <c r="U738" t="inlineStr">
@@ -80175,11 +80187,11 @@
     </row>
     <row r="739">
       <c r="A739" t="n">
-        <v>6548</v>
+        <v>6486</v>
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM LTDA</t>
+          <t>PC GAMER GOIANIA LTDA</t>
         </is>
       </c>
       <c r="C739" t="inlineStr">
@@ -80229,7 +80241,7 @@
         </is>
       </c>
       <c r="O739" t="n">
-        <v>17222364</v>
+        <v>16975869</v>
       </c>
       <c r="P739" t="inlineStr">
         <is>
@@ -80242,14 +80254,14 @@
         </is>
       </c>
       <c r="R739" s="1" t="n">
-        <v>46218.50280594907</v>
+        <v>46213.75225217592</v>
       </c>
       <c r="S739" t="n">
         <v>-1</v>
       </c>
       <c r="T739" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM</t>
+          <t>PC GAMER</t>
         </is>
       </c>
       <c r="U739" t="inlineStr">
@@ -80282,11 +80294,11 @@
     </row>
     <row r="740">
       <c r="A740" t="n">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
+          <t>GOIAS SILAGEM LTDA</t>
         </is>
       </c>
       <c r="C740" t="inlineStr">
@@ -80301,7 +80313,7 @@
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F740" t="inlineStr">
@@ -80336,7 +80348,7 @@
         </is>
       </c>
       <c r="O740" t="n">
-        <v>17042219</v>
+        <v>17222364</v>
       </c>
       <c r="P740" t="inlineStr">
         <is>
@@ -80349,14 +80361,14 @@
         </is>
       </c>
       <c r="R740" s="1" t="n">
-        <v>46218.50287827546</v>
+        <v>46218.50280594907</v>
       </c>
       <c r="S740" t="n">
         <v>-1</v>
       </c>
       <c r="T740" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
+          <t>GOIAS SILAGEM</t>
         </is>
       </c>
       <c r="U740" t="inlineStr">
@@ -80389,11 +80401,11 @@
     </row>
     <row r="741">
       <c r="A741" t="n">
-        <v>6628</v>
+        <v>6627</v>
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C741" t="inlineStr">
@@ -80403,7 +80415,7 @@
       </c>
       <c r="D741" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E741" t="inlineStr">
@@ -80443,7 +80455,7 @@
         </is>
       </c>
       <c r="O741" t="n">
-        <v>16959924</v>
+        <v>17042219</v>
       </c>
       <c r="P741" t="inlineStr">
         <is>
@@ -80456,7 +80468,7 @@
         </is>
       </c>
       <c r="R741" s="1" t="n">
-        <v>46218.50288813657</v>
+        <v>46218.50287827546</v>
       </c>
       <c r="S741" t="n">
         <v>-1</v>
@@ -80496,11 +80508,11 @@
     </row>
     <row r="742">
       <c r="A742" t="n">
-        <v>6703</v>
+        <v>6628</v>
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C742" t="inlineStr">
@@ -80510,12 +80522,12 @@
       </c>
       <c r="D742" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E742" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F742" t="inlineStr">
@@ -80550,7 +80562,7 @@
         </is>
       </c>
       <c r="O742" t="n">
-        <v>17941110</v>
+        <v>16959924</v>
       </c>
       <c r="P742" t="inlineStr">
         <is>
@@ -80563,14 +80575,14 @@
         </is>
       </c>
       <c r="R742" s="1" t="n">
-        <v>46218.50294193287</v>
+        <v>46218.50288813657</v>
       </c>
       <c r="S742" t="n">
         <v>-1</v>
       </c>
       <c r="T742" t="inlineStr">
         <is>
-          <t>LIMA MOTA</t>
+          <t xml:space="preserve">GTG </t>
         </is>
       </c>
       <c r="U742" t="inlineStr">
@@ -80603,11 +80615,11 @@
     </row>
     <row r="743">
       <c r="A743" t="n">
-        <v>6704</v>
+        <v>6703</v>
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>TECNO COM INFORMATICA LTDA</t>
+          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C743" t="inlineStr">
@@ -80617,7 +80629,7 @@
       </c>
       <c r="D743" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E743" t="inlineStr">
@@ -80657,7 +80669,7 @@
         </is>
       </c>
       <c r="O743" t="n">
-        <v>17952290</v>
+        <v>17941110</v>
       </c>
       <c r="P743" t="inlineStr">
         <is>
@@ -80670,14 +80682,14 @@
         </is>
       </c>
       <c r="R743" s="1" t="n">
-        <v>46218.50295059028</v>
+        <v>46218.50294193287</v>
       </c>
       <c r="S743" t="n">
         <v>-1</v>
       </c>
       <c r="T743" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>LIMA MOTA</t>
         </is>
       </c>
       <c r="U743" t="inlineStr">
@@ -80710,11 +80722,11 @@
     </row>
     <row r="744">
       <c r="A744" t="n">
-        <v>6705</v>
+        <v>6704</v>
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>NARCIZO ALVES CORDEIRO</t>
+          <t>TECNO COM INFORMATICA LTDA</t>
         </is>
       </c>
       <c r="C744" t="inlineStr">
@@ -80724,7 +80736,7 @@
       </c>
       <c r="D744" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E744" t="inlineStr">
@@ -80764,7 +80776,7 @@
         </is>
       </c>
       <c r="O744" t="n">
-        <v>17952489</v>
+        <v>17952290</v>
       </c>
       <c r="P744" t="inlineStr">
         <is>
@@ -80777,7 +80789,7 @@
         </is>
       </c>
       <c r="R744" s="1" t="n">
-        <v>46218.50295923611</v>
+        <v>46218.50295059028</v>
       </c>
       <c r="S744" t="n">
         <v>-1</v>
@@ -80817,11 +80829,11 @@
     </row>
     <row r="745">
       <c r="A745" t="n">
-        <v>6779</v>
+        <v>6705</v>
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>CORDEIRO E CIA LTDA</t>
+          <t>NARCIZO ALVES CORDEIRO</t>
         </is>
       </c>
       <c r="C745" t="inlineStr">
@@ -80871,7 +80883,7 @@
         </is>
       </c>
       <c r="O745" t="n">
-        <v>18056683</v>
+        <v>17952489</v>
       </c>
       <c r="P745" t="inlineStr">
         <is>
@@ -80884,7 +80896,7 @@
         </is>
       </c>
       <c r="R745" s="1" t="n">
-        <v>46218.50296706019</v>
+        <v>46218.50295923611</v>
       </c>
       <c r="S745" t="n">
         <v>-1</v>
@@ -80894,7 +80906,11 @@
           <t>TECNO COM</t>
         </is>
       </c>
-      <c r="U745" t="inlineStr"/>
+      <c r="U745" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V745" t="inlineStr"/>
       <c r="W745" t="inlineStr"/>
       <c r="X745" t="inlineStr"/>
@@ -80920,11 +80936,11 @@
     </row>
     <row r="746">
       <c r="A746" t="n">
-        <v>6885</v>
+        <v>6779</v>
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
+          <t>CORDEIRO E CIA LTDA</t>
         </is>
       </c>
       <c r="C746" t="inlineStr">
@@ -80974,7 +80990,7 @@
         </is>
       </c>
       <c r="O746" t="n">
-        <v>18128612</v>
+        <v>18056683</v>
       </c>
       <c r="P746" t="inlineStr">
         <is>
@@ -80987,14 +81003,14 @@
         </is>
       </c>
       <c r="R746" s="1" t="n">
-        <v>46218.50304079861</v>
+        <v>46218.50296706019</v>
       </c>
       <c r="S746" t="n">
         <v>-1</v>
       </c>
       <c r="T746" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>TECNO COM</t>
         </is>
       </c>
       <c r="U746" t="inlineStr"/>
@@ -81023,11 +81039,11 @@
     </row>
     <row r="747">
       <c r="A747" t="n">
-        <v>6945</v>
+        <v>6885</v>
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
+          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
         </is>
       </c>
       <c r="C747" t="inlineStr">
@@ -81042,7 +81058,7 @@
       </c>
       <c r="E747" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F747" t="inlineStr">
@@ -81077,7 +81093,7 @@
         </is>
       </c>
       <c r="O747" t="n">
-        <v>18164471</v>
+        <v>18128612</v>
       </c>
       <c r="P747" t="inlineStr">
         <is>
@@ -81090,14 +81106,14 @@
         </is>
       </c>
       <c r="R747" s="1" t="n">
-        <v>46218.50313505787</v>
+        <v>46218.50304079861</v>
       </c>
       <c r="S747" t="n">
         <v>-1</v>
       </c>
       <c r="T747" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U747" t="inlineStr"/>
@@ -81126,11 +81142,11 @@
     </row>
     <row r="748">
       <c r="A748" t="n">
-        <v>6949</v>
+        <v>6945</v>
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>TEC GRUA LOCAÇÃO E COMERCIO DE EQUIPAMENTOS PARA CONSTRUÇÃO LTDA</t>
+          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
         </is>
       </c>
       <c r="C748" t="inlineStr">
@@ -81140,17 +81156,17 @@
       </c>
       <c r="D748" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E748" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F748" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G748" t="n">
@@ -81180,7 +81196,7 @@
         </is>
       </c>
       <c r="O748" t="n">
-        <v>18178118</v>
+        <v>18164471</v>
       </c>
       <c r="P748" t="inlineStr">
         <is>
@@ -81193,14 +81209,14 @@
         </is>
       </c>
       <c r="R748" s="1" t="n">
-        <v>46218.50315884259</v>
+        <v>46218.50313505787</v>
       </c>
       <c r="S748" t="n">
         <v>-1</v>
       </c>
       <c r="T748" t="inlineStr">
         <is>
-          <t>TEC GRUA</t>
+          <t>BRASIL DISTRIBUIDORA</t>
         </is>
       </c>
       <c r="U748" t="inlineStr"/>
@@ -81229,11 +81245,11 @@
     </row>
     <row r="749">
       <c r="A749" t="n">
-        <v>6962</v>
+        <v>6949</v>
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
+          <t>TEC GRUA LOCAÇÃO E COMERCIO DE EQUIPAMENTOS PARA CONSTRUÇÃO LTDA</t>
         </is>
       </c>
       <c r="C749" t="inlineStr">
@@ -81283,7 +81299,7 @@
         </is>
       </c>
       <c r="O749" t="n">
-        <v>18188701</v>
+        <v>18178118</v>
       </c>
       <c r="P749" t="inlineStr">
         <is>
@@ -81296,14 +81312,14 @@
         </is>
       </c>
       <c r="R749" s="1" t="n">
-        <v>46218.50316710648</v>
+        <v>46218.50315884259</v>
       </c>
       <c r="S749" t="n">
         <v>-1</v>
       </c>
       <c r="T749" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN</t>
+          <t>TEC GRUA</t>
         </is>
       </c>
       <c r="U749" t="inlineStr"/>
@@ -81332,11 +81348,11 @@
     </row>
     <row r="750">
       <c r="A750" t="n">
-        <v>6963</v>
+        <v>6962</v>
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN LTDA</t>
+          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
         </is>
       </c>
       <c r="C750" t="inlineStr">
@@ -81386,7 +81402,7 @@
         </is>
       </c>
       <c r="O750" t="n">
-        <v>18188607</v>
+        <v>18188701</v>
       </c>
       <c r="P750" t="inlineStr">
         <is>
@@ -81399,7 +81415,7 @@
         </is>
       </c>
       <c r="R750" s="1" t="n">
-        <v>46218.50317474537</v>
+        <v>46218.50316710648</v>
       </c>
       <c r="S750" t="n">
         <v>-1</v>
@@ -81435,11 +81451,11 @@
     </row>
     <row r="751">
       <c r="A751" t="n">
-        <v>5417</v>
+        <v>6963</v>
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>PROMOTORAS GYN LTDA</t>
         </is>
       </c>
       <c r="C751" t="inlineStr">
@@ -81459,23 +81475,23 @@
       </c>
       <c r="F751" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Reynaldo Santos</t>
         </is>
       </c>
       <c r="G751" t="n">
-        <v>6813</v>
+        <v>940</v>
       </c>
       <c r="H751" t="n">
         <v>0</v>
       </c>
       <c r="I751" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="J751" t="inlineStr">
         <is>
-          <t>DEC - Conferência 2º Quinzena</t>
+          <t>DEC - Consulta 2º Quinzena</t>
         </is>
       </c>
       <c r="K751" t="inlineStr"/>
@@ -81489,11 +81505,11 @@
         </is>
       </c>
       <c r="O751" t="n">
-        <v>17399239</v>
+        <v>18188607</v>
       </c>
       <c r="P751" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Victoria Virgens</t>
         </is>
       </c>
       <c r="Q751" t="inlineStr">
@@ -81502,21 +81518,17 @@
         </is>
       </c>
       <c r="R751" s="1" t="n">
-        <v>46213.75219873842</v>
+        <v>46218.50317474537</v>
       </c>
       <c r="S751" t="n">
         <v>-1</v>
       </c>
       <c r="T751" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
-        </is>
-      </c>
-      <c r="U751" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>PROMOTORAS GYN</t>
+        </is>
+      </c>
+      <c r="U751" t="inlineStr"/>
       <c r="V751" t="inlineStr"/>
       <c r="W751" t="inlineStr"/>
       <c r="X751" t="inlineStr"/>
@@ -81542,11 +81554,11 @@
     </row>
     <row r="752">
       <c r="A752" t="n">
-        <v>5617</v>
+        <v>5417</v>
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C752" t="inlineStr">
@@ -81566,7 +81578,7 @@
       </c>
       <c r="F752" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G752" t="n">
@@ -81596,7 +81608,7 @@
         </is>
       </c>
       <c r="O752" t="n">
-        <v>17407800</v>
+        <v>17399239</v>
       </c>
       <c r="P752" t="inlineStr">
         <is>
@@ -81609,14 +81621,14 @@
         </is>
       </c>
       <c r="R752" s="1" t="n">
-        <v>46213.75220643519</v>
+        <v>46213.75219873842</v>
       </c>
       <c r="S752" t="n">
         <v>-1</v>
       </c>
       <c r="T752" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>NOSSO NOVO SUPERMERCADO</t>
         </is>
       </c>
       <c r="U752" t="inlineStr">
@@ -81649,11 +81661,11 @@
     </row>
     <row r="753">
       <c r="A753" t="n">
-        <v>6224</v>
+        <v>5617</v>
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C753" t="inlineStr">
@@ -81673,7 +81685,7 @@
       </c>
       <c r="F753" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G753" t="n">
@@ -81703,11 +81715,11 @@
         </is>
       </c>
       <c r="O753" t="n">
-        <v>17688928</v>
+        <v>17407800</v>
       </c>
       <c r="P753" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="Q753" t="inlineStr">
@@ -81716,7 +81728,7 @@
         </is>
       </c>
       <c r="R753" s="1" t="n">
-        <v>46218.50235228009</v>
+        <v>46213.75220643519</v>
       </c>
       <c r="S753" t="n">
         <v>-1</v>
@@ -81756,11 +81768,11 @@
     </row>
     <row r="754">
       <c r="A754" t="n">
-        <v>6404</v>
+        <v>6224</v>
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C754" t="inlineStr">
@@ -81770,7 +81782,7 @@
       </c>
       <c r="D754" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E754" t="inlineStr">
@@ -81780,7 +81792,7 @@
       </c>
       <c r="F754" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G754" t="n">
@@ -81810,7 +81822,7 @@
         </is>
       </c>
       <c r="O754" t="n">
-        <v>16962317</v>
+        <v>17688928</v>
       </c>
       <c r="P754" t="inlineStr">
         <is>
@@ -81823,14 +81835,14 @@
         </is>
       </c>
       <c r="R754" s="1" t="n">
-        <v>46213.75224560185</v>
+        <v>46218.50235228009</v>
       </c>
       <c r="S754" t="n">
         <v>-1</v>
       </c>
       <c r="T754" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U754" t="inlineStr">
@@ -81863,11 +81875,11 @@
     </row>
     <row r="755">
       <c r="A755" t="n">
-        <v>6486</v>
+        <v>6404</v>
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>PC GAMER GOIANIA LTDA</t>
+          <t>SOLAR INVESTIMENTOS LTDA</t>
         </is>
       </c>
       <c r="C755" t="inlineStr">
@@ -81877,7 +81889,7 @@
       </c>
       <c r="D755" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E755" t="inlineStr">
@@ -81917,7 +81929,7 @@
         </is>
       </c>
       <c r="O755" t="n">
-        <v>16976196</v>
+        <v>16962317</v>
       </c>
       <c r="P755" t="inlineStr">
         <is>
@@ -81930,14 +81942,14 @@
         </is>
       </c>
       <c r="R755" s="1" t="n">
-        <v>46213.75225246528</v>
+        <v>46213.75224560185</v>
       </c>
       <c r="S755" t="n">
         <v>-1</v>
       </c>
       <c r="T755" t="inlineStr">
         <is>
-          <t>PC GAMER</t>
+          <t>SOLAR INVESTIMENTOS</t>
         </is>
       </c>
       <c r="U755" t="inlineStr">
@@ -81970,11 +81982,11 @@
     </row>
     <row r="756">
       <c r="A756" t="n">
-        <v>6548</v>
+        <v>6486</v>
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM LTDA</t>
+          <t>PC GAMER GOIANIA LTDA</t>
         </is>
       </c>
       <c r="C756" t="inlineStr">
@@ -82024,11 +82036,11 @@
         </is>
       </c>
       <c r="O756" t="n">
-        <v>17222761</v>
+        <v>16976196</v>
       </c>
       <c r="P756" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="Q756" t="inlineStr">
@@ -82037,14 +82049,14 @@
         </is>
       </c>
       <c r="R756" s="1" t="n">
-        <v>46218.502805625</v>
+        <v>46213.75225246528</v>
       </c>
       <c r="S756" t="n">
         <v>-1</v>
       </c>
       <c r="T756" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM</t>
+          <t>PC GAMER</t>
         </is>
       </c>
       <c r="U756" t="inlineStr">
@@ -82077,11 +82089,11 @@
     </row>
     <row r="757">
       <c r="A757" t="n">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
+          <t>GOIAS SILAGEM LTDA</t>
         </is>
       </c>
       <c r="C757" t="inlineStr">
@@ -82096,7 +82108,7 @@
       </c>
       <c r="E757" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F757" t="inlineStr">
@@ -82131,7 +82143,7 @@
         </is>
       </c>
       <c r="O757" t="n">
-        <v>17042467</v>
+        <v>17222761</v>
       </c>
       <c r="P757" t="inlineStr">
         <is>
@@ -82144,14 +82156,14 @@
         </is>
       </c>
       <c r="R757" s="1" t="n">
-        <v>46218.50287733796</v>
+        <v>46218.502805625</v>
       </c>
       <c r="S757" t="n">
         <v>-1</v>
       </c>
       <c r="T757" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
+          <t>GOIAS SILAGEM</t>
         </is>
       </c>
       <c r="U757" t="inlineStr">
@@ -82184,11 +82196,11 @@
     </row>
     <row r="758">
       <c r="A758" t="n">
-        <v>6628</v>
+        <v>6627</v>
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C758" t="inlineStr">
@@ -82198,7 +82210,7 @@
       </c>
       <c r="D758" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E758" t="inlineStr">
@@ -82238,7 +82250,7 @@
         </is>
       </c>
       <c r="O758" t="n">
-        <v>16960011</v>
+        <v>17042467</v>
       </c>
       <c r="P758" t="inlineStr">
         <is>
@@ -82251,7 +82263,7 @@
         </is>
       </c>
       <c r="R758" s="1" t="n">
-        <v>46218.50288734954</v>
+        <v>46218.50287733796</v>
       </c>
       <c r="S758" t="n">
         <v>-1</v>
@@ -82291,11 +82303,11 @@
     </row>
     <row r="759">
       <c r="A759" t="n">
-        <v>6703</v>
+        <v>6628</v>
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C759" t="inlineStr">
@@ -82305,12 +82317,12 @@
       </c>
       <c r="D759" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E759" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F759" t="inlineStr">
@@ -82345,7 +82357,7 @@
         </is>
       </c>
       <c r="O759" t="n">
-        <v>17941195</v>
+        <v>16960011</v>
       </c>
       <c r="P759" t="inlineStr">
         <is>
@@ -82358,14 +82370,14 @@
         </is>
       </c>
       <c r="R759" s="1" t="n">
-        <v>46218.50294237269</v>
+        <v>46218.50288734954</v>
       </c>
       <c r="S759" t="n">
         <v>-1</v>
       </c>
       <c r="T759" t="inlineStr">
         <is>
-          <t>LIMA MOTA</t>
+          <t xml:space="preserve">GTG </t>
         </is>
       </c>
       <c r="U759" t="inlineStr">
@@ -82398,11 +82410,11 @@
     </row>
     <row r="760">
       <c r="A760" t="n">
-        <v>6704</v>
+        <v>6703</v>
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>TECNO COM INFORMATICA LTDA</t>
+          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C760" t="inlineStr">
@@ -82412,7 +82424,7 @@
       </c>
       <c r="D760" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E760" t="inlineStr">
@@ -82452,7 +82464,7 @@
         </is>
       </c>
       <c r="O760" t="n">
-        <v>17952409</v>
+        <v>17941195</v>
       </c>
       <c r="P760" t="inlineStr">
         <is>
@@ -82465,14 +82477,14 @@
         </is>
       </c>
       <c r="R760" s="1" t="n">
-        <v>46218.50295001157</v>
+        <v>46218.50294237269</v>
       </c>
       <c r="S760" t="n">
         <v>-1</v>
       </c>
       <c r="T760" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>LIMA MOTA</t>
         </is>
       </c>
       <c r="U760" t="inlineStr">
@@ -82505,11 +82517,11 @@
     </row>
     <row r="761">
       <c r="A761" t="n">
-        <v>6705</v>
+        <v>6704</v>
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>NARCIZO ALVES CORDEIRO</t>
+          <t>TECNO COM INFORMATICA LTDA</t>
         </is>
       </c>
       <c r="C761" t="inlineStr">
@@ -82519,7 +82531,7 @@
       </c>
       <c r="D761" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E761" t="inlineStr">
@@ -82559,7 +82571,7 @@
         </is>
       </c>
       <c r="O761" t="n">
-        <v>17952589</v>
+        <v>17952409</v>
       </c>
       <c r="P761" t="inlineStr">
         <is>
@@ -82572,7 +82584,7 @@
         </is>
       </c>
       <c r="R761" s="1" t="n">
-        <v>46218.50295900463</v>
+        <v>46218.50295001157</v>
       </c>
       <c r="S761" t="n">
         <v>-1</v>
@@ -82612,11 +82624,11 @@
     </row>
     <row r="762">
       <c r="A762" t="n">
-        <v>6779</v>
+        <v>6705</v>
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>CORDEIRO E CIA LTDA</t>
+          <t>NARCIZO ALVES CORDEIRO</t>
         </is>
       </c>
       <c r="C762" t="inlineStr">
@@ -82666,7 +82678,7 @@
         </is>
       </c>
       <c r="O762" t="n">
-        <v>18056758</v>
+        <v>17952589</v>
       </c>
       <c r="P762" t="inlineStr">
         <is>
@@ -82679,7 +82691,7 @@
         </is>
       </c>
       <c r="R762" s="1" t="n">
-        <v>46218.50296666667</v>
+        <v>46218.50295900463</v>
       </c>
       <c r="S762" t="n">
         <v>-1</v>
@@ -82689,7 +82701,11 @@
           <t>TECNO COM</t>
         </is>
       </c>
-      <c r="U762" t="inlineStr"/>
+      <c r="U762" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V762" t="inlineStr"/>
       <c r="W762" t="inlineStr"/>
       <c r="X762" t="inlineStr"/>
@@ -82715,11 +82731,11 @@
     </row>
     <row r="763">
       <c r="A763" t="n">
-        <v>6885</v>
+        <v>6779</v>
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
+          <t>CORDEIRO E CIA LTDA</t>
         </is>
       </c>
       <c r="C763" t="inlineStr">
@@ -82769,7 +82785,7 @@
         </is>
       </c>
       <c r="O763" t="n">
-        <v>18128800</v>
+        <v>18056758</v>
       </c>
       <c r="P763" t="inlineStr">
         <is>
@@ -82782,14 +82798,14 @@
         </is>
       </c>
       <c r="R763" s="1" t="n">
-        <v>46218.50304114584</v>
+        <v>46218.50296666667</v>
       </c>
       <c r="S763" t="n">
         <v>-1</v>
       </c>
       <c r="T763" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>TECNO COM</t>
         </is>
       </c>
       <c r="U763" t="inlineStr"/>
@@ -82818,11 +82834,11 @@
     </row>
     <row r="764">
       <c r="A764" t="n">
-        <v>6945</v>
+        <v>6885</v>
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
+          <t xml:space="preserve">EMPORIO MENDANHA LTDA </t>
         </is>
       </c>
       <c r="C764" t="inlineStr">
@@ -82837,7 +82853,7 @@
       </c>
       <c r="E764" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F764" t="inlineStr">
@@ -82872,11 +82888,11 @@
         </is>
       </c>
       <c r="O764" t="n">
-        <v>18164528</v>
+        <v>18128800</v>
       </c>
       <c r="P764" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="Q764" t="inlineStr">
@@ -82885,14 +82901,14 @@
         </is>
       </c>
       <c r="R764" s="1" t="n">
-        <v>46218.50313549768</v>
+        <v>46218.50304114584</v>
       </c>
       <c r="S764" t="n">
         <v>-1</v>
       </c>
       <c r="T764" t="inlineStr">
         <is>
-          <t>BRASIL DISTRIBUIDORA</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U764" t="inlineStr"/>
@@ -82921,11 +82937,11 @@
     </row>
     <row r="765">
       <c r="A765" t="n">
-        <v>6949</v>
+        <v>6945</v>
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>TEC GRUA LOCAÇÃO E COMERCIO DE EQUIPAMENTOS PARA CONSTRUÇÃO LTDA</t>
+          <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
         </is>
       </c>
       <c r="C765" t="inlineStr">
@@ -82935,17 +82951,17 @@
       </c>
       <c r="D765" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E765" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F765" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G765" t="n">
@@ -82975,11 +82991,11 @@
         </is>
       </c>
       <c r="O765" t="n">
-        <v>18178167</v>
+        <v>18164528</v>
       </c>
       <c r="P765" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="Q765" t="inlineStr">
@@ -82988,14 +83004,14 @@
         </is>
       </c>
       <c r="R765" s="1" t="n">
-        <v>46218.50315827546</v>
+        <v>46218.50313549768</v>
       </c>
       <c r="S765" t="n">
         <v>-1</v>
       </c>
       <c r="T765" t="inlineStr">
         <is>
-          <t>TEC GRUA</t>
+          <t>BRASIL DISTRIBUIDORA</t>
         </is>
       </c>
       <c r="U765" t="inlineStr"/>
@@ -83024,11 +83040,11 @@
     </row>
     <row r="766">
       <c r="A766" t="n">
-        <v>6962</v>
+        <v>6949</v>
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
+          <t>TEC GRUA LOCAÇÃO E COMERCIO DE EQUIPAMENTOS PARA CONSTRUÇÃO LTDA</t>
         </is>
       </c>
       <c r="C766" t="inlineStr">
@@ -83078,11 +83094,11 @@
         </is>
       </c>
       <c r="O766" t="n">
-        <v>18188751</v>
+        <v>18178167</v>
       </c>
       <c r="P766" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="Q766" t="inlineStr">
@@ -83091,14 +83107,14 @@
         </is>
       </c>
       <c r="R766" s="1" t="n">
-        <v>46218.50316729167</v>
+        <v>46218.50315827546</v>
       </c>
       <c r="S766" t="n">
         <v>-1</v>
       </c>
       <c r="T766" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN</t>
+          <t>TEC GRUA</t>
         </is>
       </c>
       <c r="U766" t="inlineStr"/>
@@ -83127,11 +83143,11 @@
     </row>
     <row r="767">
       <c r="A767" t="n">
-        <v>6963</v>
+        <v>6962</v>
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN LTDA</t>
+          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
         </is>
       </c>
       <c r="C767" t="inlineStr">
@@ -83181,7 +83197,7 @@
         </is>
       </c>
       <c r="O767" t="n">
-        <v>18188657</v>
+        <v>18188751</v>
       </c>
       <c r="P767" t="inlineStr">
         <is>
@@ -83194,7 +83210,7 @@
         </is>
       </c>
       <c r="R767" s="1" t="n">
-        <v>46218.50317447916</v>
+        <v>46218.50316729167</v>
       </c>
       <c r="S767" t="n">
         <v>-1</v>
@@ -83230,11 +83246,11 @@
     </row>
     <row r="768">
       <c r="A768" t="n">
-        <v>6279</v>
+        <v>6963</v>
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>DIENNYFER DA S PEREIRA</t>
+          <t>PROMOTORAS GYN LTDA</t>
         </is>
       </c>
       <c r="C768" t="inlineStr">
@@ -83244,7 +83260,7 @@
       </c>
       <c r="D768" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E768" t="inlineStr">
@@ -83254,11 +83270,11 @@
       </c>
       <c r="F768" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Reynaldo Santos</t>
         </is>
       </c>
       <c r="G768" t="n">
-        <v>11001</v>
+        <v>6813</v>
       </c>
       <c r="H768" t="n">
         <v>0</v>
@@ -83270,25 +83286,25 @@
       </c>
       <c r="J768" t="inlineStr">
         <is>
-          <t>Movimento - Analise de Balanço Lucro Presumido</t>
+          <t>DEC - Conferência 2º Quinzena</t>
         </is>
       </c>
       <c r="K768" t="inlineStr"/>
       <c r="L768" s="1" t="n">
-        <v>46230</v>
+        <v>46220</v>
       </c>
       <c r="M768" t="inlineStr"/>
       <c r="N768" t="inlineStr">
         <is>
-          <t>06/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
       <c r="O768" t="n">
-        <v>18076051</v>
+        <v>18188657</v>
       </c>
       <c r="P768" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="Q768" t="inlineStr">
@@ -83297,26 +83313,18 @@
         </is>
       </c>
       <c r="R768" s="1" t="n">
-        <v>46174.04914510417</v>
+        <v>46218.50317447916</v>
       </c>
       <c r="S768" t="n">
-        <v>-11</v>
+        <v>-1</v>
       </c>
       <c r="T768" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
-        </is>
-      </c>
-      <c r="U768" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="V768" t="inlineStr">
-        <is>
-          <t>Baixado via rotina MGC x Analise Balanço em 01/06/2026 01:10:46. - Data Comentário: 01/06/2026 01:10</t>
-        </is>
-      </c>
+          <t>PROMOTORAS GYN</t>
+        </is>
+      </c>
+      <c r="U768" t="inlineStr"/>
+      <c r="V768" t="inlineStr"/>
       <c r="W768" t="inlineStr"/>
       <c r="X768" t="inlineStr"/>
       <c r="Y768" t="inlineStr"/>
@@ -83334,18 +83342,18 @@
       <c r="AE768" t="inlineStr"/>
       <c r="AF768" t="inlineStr">
         <is>
-          <t>Tarefa</t>
+          <t>Obrigação Acessória</t>
         </is>
       </c>
       <c r="AG768" t="inlineStr"/>
     </row>
     <row r="769">
       <c r="A769" t="n">
-        <v>6404</v>
+        <v>6279</v>
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS LTDA</t>
+          <t>DIENNYFER DA S PEREIRA</t>
         </is>
       </c>
       <c r="C769" t="inlineStr">
@@ -83365,7 +83373,7 @@
       </c>
       <c r="F769" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G769" t="n">
@@ -83395,11 +83403,11 @@
         </is>
       </c>
       <c r="O769" t="n">
-        <v>16962452</v>
+        <v>18076051</v>
       </c>
       <c r="P769" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="Q769" t="inlineStr">
@@ -83408,14 +83416,14 @@
         </is>
       </c>
       <c r="R769" s="1" t="n">
-        <v>46174.04916258102</v>
+        <v>46174.04914510417</v>
       </c>
       <c r="S769" t="n">
         <v>-11</v>
       </c>
       <c r="T769" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U769" t="inlineStr">
@@ -83425,7 +83433,7 @@
       </c>
       <c r="V769" t="inlineStr">
         <is>
-          <t>Baixado via rotina MGC x Analise Balanço em 01/06/2026 01:10:47. - Data Comentário: 01/06/2026 01:10</t>
+          <t>Baixado via rotina MGC x Analise Balanço em 01/06/2026 01:10:46. - Data Comentário: 01/06/2026 01:10</t>
         </is>
       </c>
       <c r="W769" t="inlineStr"/>
@@ -83452,11 +83460,11 @@
     </row>
     <row r="770">
       <c r="A770" t="n">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>SOLAR INVESTIMENTOS LTDA</t>
         </is>
       </c>
       <c r="C770" t="inlineStr">
@@ -83466,7 +83474,7 @@
       </c>
       <c r="D770" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E770" t="inlineStr">
@@ -83476,11 +83484,11 @@
       </c>
       <c r="F770" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G770" t="n">
-        <v>7877</v>
+        <v>11001</v>
       </c>
       <c r="H770" t="n">
         <v>0</v>
@@ -83492,7 +83500,7 @@
       </c>
       <c r="J770" t="inlineStr">
         <is>
-          <t>Movimento - Analise de Balanço Lucro Real</t>
+          <t>Movimento - Analise de Balanço Lucro Presumido</t>
         </is>
       </c>
       <c r="K770" t="inlineStr"/>
@@ -83506,11 +83514,11 @@
         </is>
       </c>
       <c r="O770" t="n">
-        <v>17399328</v>
+        <v>16962452</v>
       </c>
       <c r="P770" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="Q770" t="inlineStr">
@@ -83519,14 +83527,14 @@
         </is>
       </c>
       <c r="R770" s="1" t="n">
-        <v>46174.04899652778</v>
+        <v>46174.04916258102</v>
       </c>
       <c r="S770" t="n">
         <v>-11</v>
       </c>
       <c r="T770" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
+          <t>SOLAR INVESTIMENTOS</t>
         </is>
       </c>
       <c r="U770" t="inlineStr">
@@ -83536,7 +83544,7 @@
       </c>
       <c r="V770" t="inlineStr">
         <is>
-          <t>Baixado via rotina MGC x Analise Balanço em 01/06/2026 01:10:33. - Data Comentário: 01/06/2026 01:09</t>
+          <t>Baixado via rotina MGC x Analise Balanço em 01/06/2026 01:10:47. - Data Comentário: 01/06/2026 01:10</t>
         </is>
       </c>
       <c r="W770" t="inlineStr"/>
@@ -83563,11 +83571,11 @@
     </row>
     <row r="771">
       <c r="A771" t="n">
-        <v>5617</v>
+        <v>5417</v>
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C771" t="inlineStr">
@@ -83587,7 +83595,7 @@
       </c>
       <c r="F771" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G771" t="n">
@@ -83617,7 +83625,7 @@
         </is>
       </c>
       <c r="O771" t="n">
-        <v>18076498</v>
+        <v>17399328</v>
       </c>
       <c r="P771" t="inlineStr">
         <is>
@@ -83630,14 +83638,14 @@
         </is>
       </c>
       <c r="R771" s="1" t="n">
-        <v>46174.04886894676</v>
+        <v>46174.04899652778</v>
       </c>
       <c r="S771" t="n">
         <v>-11</v>
       </c>
       <c r="T771" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>NOSSO NOVO SUPERMERCADO</t>
         </is>
       </c>
       <c r="U771" t="inlineStr">
@@ -83647,7 +83655,7 @@
       </c>
       <c r="V771" t="inlineStr">
         <is>
-          <t>Baixado via rotina MGC x Analise Balanço em 01/06/2026 01:10:22. - Data Comentário: 01/06/2026 01:09</t>
+          <t>Baixado via rotina MGC x Analise Balanço em 01/06/2026 01:10:33. - Data Comentário: 01/06/2026 01:09</t>
         </is>
       </c>
       <c r="W771" t="inlineStr"/>
@@ -83674,11 +83682,11 @@
     </row>
     <row r="772">
       <c r="A772" t="n">
-        <v>6224</v>
+        <v>5617</v>
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C772" t="inlineStr">
@@ -83698,7 +83706,7 @@
       </c>
       <c r="F772" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G772" t="n">
@@ -83728,11 +83736,11 @@
         </is>
       </c>
       <c r="O772" t="n">
-        <v>18076568</v>
+        <v>18076498</v>
       </c>
       <c r="P772" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="Q772" t="inlineStr">
@@ -83741,7 +83749,7 @@
         </is>
       </c>
       <c r="R772" s="1" t="n">
-        <v>46174.04901342592</v>
+        <v>46174.04886894676</v>
       </c>
       <c r="S772" t="n">
         <v>-11</v>
@@ -83758,7 +83766,7 @@
       </c>
       <c r="V772" t="inlineStr">
         <is>
-          <t>Baixado via rotina MGC x Analise Balanço em 01/06/2026 01:10:34. - Data Comentário: 01/06/2026 01:09</t>
+          <t>Baixado via rotina MGC x Analise Balanço em 01/06/2026 01:10:22. - Data Comentário: 01/06/2026 01:09</t>
         </is>
       </c>
       <c r="W772" t="inlineStr"/>
@@ -83785,11 +83793,11 @@
     </row>
     <row r="773">
       <c r="A773" t="n">
-        <v>6278</v>
+        <v>6224</v>
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C773" t="inlineStr">
@@ -83799,7 +83807,7 @@
       </c>
       <c r="D773" t="inlineStr">
         <is>
-          <t>Federal - Lucro Real - Anual</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E773" t="inlineStr">
@@ -83809,7 +83817,7 @@
       </c>
       <c r="F773" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G773" t="n">
@@ -83839,11 +83847,11 @@
         </is>
       </c>
       <c r="O773" t="n">
-        <v>17539836</v>
+        <v>18076568</v>
       </c>
       <c r="P773" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="Q773" t="inlineStr">
@@ -83852,14 +83860,14 @@
         </is>
       </c>
       <c r="R773" s="1" t="n">
-        <v>46174.04899452546</v>
+        <v>46174.04901342592</v>
       </c>
       <c r="S773" t="n">
         <v>-11</v>
       </c>
       <c r="T773" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U773" t="inlineStr">
@@ -83869,7 +83877,7 @@
       </c>
       <c r="V773" t="inlineStr">
         <is>
-          <t>Baixado via rotina MGC x Analise Balanço em 01/06/2026 01:10:33. - Data Comentário: 01/06/2026 01:09</t>
+          <t>Baixado via rotina MGC x Analise Balanço em 01/06/2026 01:10:34. - Data Comentário: 01/06/2026 01:09</t>
         </is>
       </c>
       <c r="W773" t="inlineStr"/>
@@ -83896,11 +83904,11 @@
     </row>
     <row r="774">
       <c r="A774" t="n">
-        <v>6486</v>
+        <v>6278</v>
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>PC GAMER GOIANIA LTDA</t>
+          <t>EMPORIO DOS FRIOS LTDA</t>
         </is>
       </c>
       <c r="C774" t="inlineStr">
@@ -83910,7 +83918,7 @@
       </c>
       <c r="D774" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Real - Anual</t>
         </is>
       </c>
       <c r="E774" t="inlineStr">
@@ -83924,7 +83932,7 @@
         </is>
       </c>
       <c r="G774" t="n">
-        <v>9774</v>
+        <v>7877</v>
       </c>
       <c r="H774" t="n">
         <v>0</v>
@@ -83936,7 +83944,7 @@
       </c>
       <c r="J774" t="inlineStr">
         <is>
-          <t>Movimento - Analise de Balanço Simples Nacional</t>
+          <t>Movimento - Analise de Balanço Lucro Real</t>
         </is>
       </c>
       <c r="K774" t="inlineStr"/>
@@ -83950,11 +83958,11 @@
         </is>
       </c>
       <c r="O774" t="n">
-        <v>16976319</v>
+        <v>17539836</v>
       </c>
       <c r="P774" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="Q774" t="inlineStr">
@@ -83963,14 +83971,14 @@
         </is>
       </c>
       <c r="R774" s="1" t="n">
-        <v>46174.04894753472</v>
+        <v>46174.04899452546</v>
       </c>
       <c r="S774" t="n">
         <v>-11</v>
       </c>
       <c r="T774" t="inlineStr">
         <is>
-          <t>PC GAMER</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U774" t="inlineStr">
@@ -83980,7 +83988,7 @@
       </c>
       <c r="V774" t="inlineStr">
         <is>
-          <t>Baixado via rotina MGC x Analise Balanço em 01/06/2026 01:10:29. - Data Comentário: 01/06/2026 01:09</t>
+          <t>Baixado via rotina MGC x Analise Balanço em 01/06/2026 01:10:33. - Data Comentário: 01/06/2026 01:09</t>
         </is>
       </c>
       <c r="W774" t="inlineStr"/>
@@ -84007,11 +84015,11 @@
     </row>
     <row r="775">
       <c r="A775" t="n">
-        <v>5417</v>
+        <v>6486</v>
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>PC GAMER GOIANIA LTDA</t>
         </is>
       </c>
       <c r="C775" t="inlineStr">
@@ -84031,11 +84039,11 @@
       </c>
       <c r="F775" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G775" t="n">
-        <v>7027</v>
+        <v>9774</v>
       </c>
       <c r="H775" t="n">
         <v>0</v>
@@ -84047,12 +84055,12 @@
       </c>
       <c r="J775" t="inlineStr">
         <is>
-          <t>Movimento - Sistema de Análise</t>
+          <t>Movimento - Analise de Balanço Simples Nacional</t>
         </is>
       </c>
       <c r="K775" t="inlineStr"/>
       <c r="L775" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="M775" t="inlineStr"/>
       <c r="N775" t="inlineStr">
@@ -84061,11 +84069,11 @@
         </is>
       </c>
       <c r="O775" t="n">
-        <v>17399288</v>
+        <v>16976319</v>
       </c>
       <c r="P775" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="Q775" t="inlineStr">
@@ -84074,14 +84082,14 @@
         </is>
       </c>
       <c r="R775" s="1" t="n">
-        <v>46217.56402731482</v>
+        <v>46174.04894753472</v>
       </c>
       <c r="S775" t="n">
-        <v>-8</v>
+        <v>-11</v>
       </c>
       <c r="T775" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
+          <t>PC GAMER</t>
         </is>
       </c>
       <c r="U775" t="inlineStr">
@@ -84091,7 +84099,7 @@
       </c>
       <c r="V775" t="inlineStr">
         <is>
-          <t>Baixado via API integração MGC x Sistema de Analise Fiscal em 14/07/2026 13:32:04. - Data Comentário: 14/07/2026 13:31</t>
+          <t>Baixado via rotina MGC x Analise Balanço em 01/06/2026 01:10:29. - Data Comentário: 01/06/2026 01:09</t>
         </is>
       </c>
       <c r="W775" t="inlineStr"/>
@@ -84118,11 +84126,11 @@
     </row>
     <row r="776">
       <c r="A776" t="n">
-        <v>5617</v>
+        <v>5417</v>
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C776" t="inlineStr">
@@ -84142,7 +84150,7 @@
       </c>
       <c r="F776" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G776" t="n">
@@ -84172,7 +84180,7 @@
         </is>
       </c>
       <c r="O776" t="n">
-        <v>17407829</v>
+        <v>17399288</v>
       </c>
       <c r="P776" t="inlineStr">
         <is>
@@ -84185,14 +84193,14 @@
         </is>
       </c>
       <c r="R776" s="1" t="n">
-        <v>46174.0003128125</v>
+        <v>46217.56402731482</v>
       </c>
       <c r="S776" t="n">
         <v>-8</v>
       </c>
       <c r="T776" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>NOSSO NOVO SUPERMERCADO</t>
         </is>
       </c>
       <c r="U776" t="inlineStr">
@@ -84200,7 +84208,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V776" t="inlineStr"/>
+      <c r="V776" t="inlineStr">
+        <is>
+          <t>Baixado via API integração MGC x Sistema de Analise Fiscal em 14/07/2026 13:32:04. - Data Comentário: 14/07/2026 13:31</t>
+        </is>
+      </c>
       <c r="W776" t="inlineStr"/>
       <c r="X776" t="inlineStr"/>
       <c r="Y776" t="inlineStr"/>
@@ -84225,11 +84237,11 @@
     </row>
     <row r="777">
       <c r="A777" t="n">
-        <v>6224</v>
+        <v>5617</v>
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C777" t="inlineStr">
@@ -84249,7 +84261,7 @@
       </c>
       <c r="F777" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G777" t="n">
@@ -84279,9 +84291,13 @@
         </is>
       </c>
       <c r="O777" t="n">
-        <v>17688957</v>
-      </c>
-      <c r="P777" t="inlineStr"/>
+        <v>17407829</v>
+      </c>
+      <c r="P777" t="inlineStr">
+        <is>
+          <t>Sergio Fernandes</t>
+        </is>
+      </c>
       <c r="Q777" t="inlineStr">
         <is>
           <t>Baixado</t>
@@ -84328,11 +84344,11 @@
     </row>
     <row r="778">
       <c r="A778" t="n">
-        <v>6278</v>
+        <v>6224</v>
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C778" t="inlineStr">
@@ -84342,7 +84358,7 @@
       </c>
       <c r="D778" t="inlineStr">
         <is>
-          <t>Federal - Lucro Real - Anual</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E778" t="inlineStr">
@@ -84352,7 +84368,7 @@
       </c>
       <c r="F778" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G778" t="n">
@@ -84382,27 +84398,23 @@
         </is>
       </c>
       <c r="O778" t="n">
-        <v>17539796</v>
-      </c>
-      <c r="P778" t="inlineStr">
-        <is>
-          <t>Sergio Fernandes</t>
-        </is>
-      </c>
+        <v>17688957</v>
+      </c>
+      <c r="P778" t="inlineStr"/>
       <c r="Q778" t="inlineStr">
         <is>
           <t>Baixado</t>
         </is>
       </c>
       <c r="R778" s="1" t="n">
-        <v>46219.41349725694</v>
+        <v>46174.0003128125</v>
       </c>
       <c r="S778" t="n">
         <v>-8</v>
       </c>
       <c r="T778" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U778" t="inlineStr">
@@ -84410,13 +84422,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V778" t="inlineStr">
-        <is>
-          <t>Integração com Sistema de Análise 
-ICMS liberado, aguardo a validação do SPED Contribuições. 
-Data Simulação: 16/07/2026 09:55:26 - Data Comentário: 16/07/2026 10:06</t>
-        </is>
-      </c>
+      <c r="V778" t="inlineStr"/>
       <c r="W778" t="inlineStr"/>
       <c r="X778" t="inlineStr"/>
       <c r="Y778" t="inlineStr"/>
@@ -84441,11 +84447,11 @@
     </row>
     <row r="779">
       <c r="A779" t="n">
-        <v>6279</v>
+        <v>6278</v>
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>DIENNYFER DA S PEREIRA</t>
+          <t>EMPORIO DOS FRIOS LTDA</t>
         </is>
       </c>
       <c r="C779" t="inlineStr">
@@ -84455,7 +84461,7 @@
       </c>
       <c r="D779" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - Lucro Real - Anual</t>
         </is>
       </c>
       <c r="E779" t="inlineStr">
@@ -84465,7 +84471,7 @@
       </c>
       <c r="F779" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G779" t="n">
@@ -84495,7 +84501,7 @@
         </is>
       </c>
       <c r="O779" t="n">
-        <v>17646102</v>
+        <v>17539796</v>
       </c>
       <c r="P779" t="inlineStr">
         <is>
@@ -84508,7 +84514,7 @@
         </is>
       </c>
       <c r="R779" s="1" t="n">
-        <v>46174.0003128125</v>
+        <v>46219.41349725694</v>
       </c>
       <c r="S779" t="n">
         <v>-8</v>
@@ -84523,7 +84529,13 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V779" t="inlineStr"/>
+      <c r="V779" t="inlineStr">
+        <is>
+          <t>Integração com Sistema de Análise 
+ICMS liberado, aguardo a validação do SPED Contribuições. 
+Data Simulação: 16/07/2026 09:55:26 - Data Comentário: 16/07/2026 10:06</t>
+        </is>
+      </c>
       <c r="W779" t="inlineStr"/>
       <c r="X779" t="inlineStr"/>
       <c r="Y779" t="inlineStr"/>

--- a/dados/base/goias.xlsx
+++ b/dados/base/goias.xlsx
@@ -55461,11 +55461,11 @@
     </row>
     <row r="512">
       <c r="A512" t="n">
-        <v>6486</v>
+        <v>6628</v>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>PC GAMER GOIANIA LTDA</t>
+          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
@@ -55475,12 +55475,12 @@
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - SN</t>
         </is>
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F512" t="inlineStr">
@@ -55506,7 +55506,7 @@
       </c>
       <c r="K512" t="inlineStr"/>
       <c r="L512" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="M512" t="inlineStr"/>
       <c r="N512" t="inlineStr">
@@ -55515,7 +55515,7 @@
         </is>
       </c>
       <c r="O512" t="n">
-        <v>18204785</v>
+        <v>18205144</v>
       </c>
       <c r="P512" t="inlineStr">
         <is>
@@ -55529,11 +55529,11 @@
       </c>
       <c r="R512" t="inlineStr"/>
       <c r="S512" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="T512" t="inlineStr">
         <is>
-          <t>PC GAMER</t>
+          <t xml:space="preserve">GTG </t>
         </is>
       </c>
       <c r="U512" t="inlineStr">
@@ -55543,9 +55543,9 @@
       </c>
       <c r="V512" t="inlineStr">
         <is>
-          <t>•	PEDIDO DE DEMISSÃO COM DESCONTO DO AVISO PRÉVIO
-Comunicado – 13/07/2026
-Pagamento e Entrega dos documentos até 23/07/2026 - Data Comentário: 14/07/2026 09:48</t>
+          <t>•	DISPENSA ANTECIPADA DO CONTRATO DE EXPERIÊNCIA
+Comunicado – 14/07/2026
+Pagamento e Entrega dos documentos até 24/07/2026 - Data Comentário: 14/07/2026 18:12</t>
         </is>
       </c>
       <c r="W512" t="inlineStr"/>
@@ -55572,11 +55572,11 @@
     </row>
     <row r="513">
       <c r="A513" t="n">
-        <v>6628</v>
+        <v>6548</v>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>TSN TECHNICAL SERVICE NETWORK LTDA</t>
+          <t>GOIAS SILAGEM LTDA</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
@@ -55586,12 +55586,12 @@
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>Federal - SN</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F513" t="inlineStr">
@@ -55600,37 +55600,37 @@
         </is>
       </c>
       <c r="G513" t="n">
-        <v>6348</v>
+        <v>1913</v>
       </c>
       <c r="H513" t="n">
-        <v>0</v>
+        <v>1862</v>
       </c>
       <c r="I513" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J513" t="inlineStr">
         <is>
-          <t>RESCISÃO - RESCISÃO</t>
+          <t>Depreciação</t>
         </is>
       </c>
       <c r="K513" t="inlineStr"/>
       <c r="L513" s="1" t="n">
-        <v>46226</v>
+        <v>46224</v>
       </c>
       <c r="M513" t="inlineStr"/>
       <c r="N513" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
       <c r="O513" t="n">
-        <v>18205144</v>
+        <v>17988577</v>
       </c>
       <c r="P513" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Cristiana Grizostomo</t>
         </is>
       </c>
       <c r="Q513" t="inlineStr">
@@ -55640,11 +55640,11 @@
       </c>
       <c r="R513" t="inlineStr"/>
       <c r="S513" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="T513" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
+          <t>GOIAS SILAGEM</t>
         </is>
       </c>
       <c r="U513" t="inlineStr">
@@ -55652,13 +55652,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V513" t="inlineStr">
-        <is>
-          <t>•	DISPENSA ANTECIPADA DO CONTRATO DE EXPERIÊNCIA
-Comunicado – 14/07/2026
-Pagamento e Entrega dos documentos até 24/07/2026 - Data Comentário: 14/07/2026 18:12</t>
-        </is>
-      </c>
+      <c r="V513" t="inlineStr"/>
       <c r="W513" t="inlineStr"/>
       <c r="X513" t="inlineStr"/>
       <c r="Y513" t="inlineStr"/>
@@ -55672,22 +55666,22 @@
       <c r="AE513" t="inlineStr"/>
       <c r="AF513" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Tarefa</t>
         </is>
       </c>
       <c r="AG513" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="n">
-        <v>6949</v>
+        <v>6962</v>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>TEC GRUA LOCAÇÃO E COMERCIO DE EQUIPAMENTOS PARA CONSTRUÇÃO LTDA</t>
+          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
@@ -55711,37 +55705,37 @@
         </is>
       </c>
       <c r="G514" t="n">
-        <v>6348</v>
+        <v>1913</v>
       </c>
       <c r="H514" t="n">
-        <v>0</v>
+        <v>1862</v>
       </c>
       <c r="I514" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J514" t="inlineStr">
         <is>
-          <t>RESCISÃO - RESCISÃO</t>
+          <t>Depreciação</t>
         </is>
       </c>
       <c r="K514" t="inlineStr"/>
       <c r="L514" s="1" t="n">
-        <v>46220</v>
+        <v>46224</v>
       </c>
       <c r="M514" t="inlineStr"/>
       <c r="N514" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
       <c r="O514" t="n">
-        <v>18204635</v>
+        <v>18186965</v>
       </c>
       <c r="P514" t="inlineStr">
         <is>
-          <t>Gabriela Peres</t>
+          <t>Denis Reis</t>
         </is>
       </c>
       <c r="Q514" t="inlineStr">
@@ -55751,19 +55745,15 @@
       </c>
       <c r="R514" t="inlineStr"/>
       <c r="S514" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="T514" t="inlineStr">
         <is>
-          <t>TEC GRUA</t>
+          <t>PROMOTORAS GYN</t>
         </is>
       </c>
       <c r="U514" t="inlineStr"/>
-      <c r="V514" t="inlineStr">
-        <is>
-          <t>Pedido de demissão - Desconto de Aviso em 10/07/2026 - Pgto 20/07/2026 - Data Comentário: 13/07/2026 17:57</t>
-        </is>
-      </c>
+      <c r="V514" t="inlineStr"/>
       <c r="W514" t="inlineStr"/>
       <c r="X514" t="inlineStr"/>
       <c r="Y514" t="inlineStr"/>
@@ -55777,22 +55767,22 @@
       <c r="AE514" t="inlineStr"/>
       <c r="AF514" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Tarefa</t>
         </is>
       </c>
       <c r="AG514" t="inlineStr">
         <is>
-          <t>Leandro Matos</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="n">
-        <v>6548</v>
+        <v>6963</v>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM LTDA</t>
+          <t>PROMOTORAS GYN LTDA</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
@@ -55812,7 +55802,7 @@
       </c>
       <c r="F515" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Reynaldo Santos</t>
         </is>
       </c>
       <c r="G515" t="n">
@@ -55842,11 +55832,11 @@
         </is>
       </c>
       <c r="O515" t="n">
-        <v>17988577</v>
+        <v>18187231</v>
       </c>
       <c r="P515" t="inlineStr">
         <is>
-          <t>Cristiana Grizostomo</t>
+          <t>Denis Reis</t>
         </is>
       </c>
       <c r="Q515" t="inlineStr">
@@ -55860,14 +55850,10 @@
       </c>
       <c r="T515" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM</t>
-        </is>
-      </c>
-      <c r="U515" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>PROMOTORAS GYN</t>
+        </is>
+      </c>
+      <c r="U515" t="inlineStr"/>
       <c r="V515" t="inlineStr"/>
       <c r="W515" t="inlineStr"/>
       <c r="X515" t="inlineStr"/>
@@ -55893,11 +55879,11 @@
     </row>
     <row r="516">
       <c r="A516" t="n">
-        <v>6962</v>
+        <v>6949</v>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
+          <t>TEC GRUA LOCAÇÃO E COMERCIO DE EQUIPAMENTOS PARA CONSTRUÇÃO LTDA</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
@@ -55921,10 +55907,10 @@
         </is>
       </c>
       <c r="G516" t="n">
-        <v>1913</v>
+        <v>11617</v>
       </c>
       <c r="H516" t="n">
-        <v>1862</v>
+        <v>0</v>
       </c>
       <c r="I516" t="inlineStr">
         <is>
@@ -55933,25 +55919,29 @@
       </c>
       <c r="J516" t="inlineStr">
         <is>
-          <t>Depreciação</t>
+          <t>Envio de ATA de Implantação - EF I</t>
         </is>
       </c>
       <c r="K516" t="inlineStr"/>
       <c r="L516" s="1" t="n">
-        <v>46224</v>
-      </c>
-      <c r="M516" t="inlineStr"/>
+        <v>46220</v>
+      </c>
+      <c r="M516" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
       <c r="N516" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O516" t="n">
-        <v>18186965</v>
+        <v>18166588</v>
       </c>
       <c r="P516" t="inlineStr">
         <is>
-          <t>Denis Reis</t>
+          <t>Priscila Volpe</t>
         </is>
       </c>
       <c r="Q516" t="inlineStr">
@@ -55961,15 +55951,20 @@
       </c>
       <c r="R516" t="inlineStr"/>
       <c r="S516" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="T516" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN</t>
+          <t>TEC GRUA</t>
         </is>
       </c>
       <c r="U516" t="inlineStr"/>
-      <c r="V516" t="inlineStr"/>
+      <c r="V516" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 31/07/2026 
+ainda não foi realizado as implantações - Data Comentário: 01/07/2026 13:38</t>
+        </is>
+      </c>
       <c r="W516" t="inlineStr"/>
       <c r="X516" t="inlineStr"/>
       <c r="Y516" t="inlineStr"/>
@@ -55994,11 +55989,11 @@
     </row>
     <row r="517">
       <c r="A517" t="n">
-        <v>6963</v>
+        <v>6962</v>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN LTDA</t>
+          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
@@ -56022,10 +56017,10 @@
         </is>
       </c>
       <c r="G517" t="n">
-        <v>1913</v>
+        <v>11617</v>
       </c>
       <c r="H517" t="n">
-        <v>1862</v>
+        <v>0</v>
       </c>
       <c r="I517" t="inlineStr">
         <is>
@@ -56034,25 +56029,29 @@
       </c>
       <c r="J517" t="inlineStr">
         <is>
-          <t>Depreciação</t>
+          <t>Envio de ATA de Implantação - EF I</t>
         </is>
       </c>
       <c r="K517" t="inlineStr"/>
       <c r="L517" s="1" t="n">
-        <v>46224</v>
-      </c>
-      <c r="M517" t="inlineStr"/>
+        <v>46220</v>
+      </c>
+      <c r="M517" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
       <c r="N517" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O517" t="n">
-        <v>18187231</v>
+        <v>18186565</v>
       </c>
       <c r="P517" t="inlineStr">
         <is>
-          <t>Denis Reis</t>
+          <t>Priscila Volpe</t>
         </is>
       </c>
       <c r="Q517" t="inlineStr">
@@ -56062,7 +56061,7 @@
       </c>
       <c r="R517" t="inlineStr"/>
       <c r="S517" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="T517" t="inlineStr">
         <is>
@@ -56070,7 +56069,12 @@
         </is>
       </c>
       <c r="U517" t="inlineStr"/>
-      <c r="V517" t="inlineStr"/>
+      <c r="V517" t="inlineStr">
+        <is>
+          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 31/07/2026 
+ainda não foi realizado as implantações - Data Comentário: 01/07/2026 13:38</t>
+        </is>
+      </c>
       <c r="W517" t="inlineStr"/>
       <c r="X517" t="inlineStr"/>
       <c r="Y517" t="inlineStr"/>
@@ -56095,11 +56099,11 @@
     </row>
     <row r="518">
       <c r="A518" t="n">
-        <v>6949</v>
+        <v>6963</v>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>TEC GRUA LOCAÇÃO E COMERCIO DE EQUIPAMENTOS PARA CONSTRUÇÃO LTDA</t>
+          <t>PROMOTORAS GYN LTDA</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
@@ -56153,7 +56157,7 @@
         </is>
       </c>
       <c r="O518" t="n">
-        <v>18166588</v>
+        <v>18186566</v>
       </c>
       <c r="P518" t="inlineStr">
         <is>
@@ -56171,7 +56175,7 @@
       </c>
       <c r="T518" t="inlineStr">
         <is>
-          <t>TEC GRUA</t>
+          <t>PROMOTORAS GYN</t>
         </is>
       </c>
       <c r="U518" t="inlineStr"/>
@@ -56205,11 +56209,11 @@
     </row>
     <row r="519">
       <c r="A519" t="n">
-        <v>6962</v>
+        <v>6627</v>
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
+          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
@@ -56224,16 +56228,16 @@
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F519" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G519" t="n">
-        <v>11617</v>
+        <v>1882</v>
       </c>
       <c r="H519" t="n">
         <v>0</v>
@@ -56245,29 +56249,25 @@
       </c>
       <c r="J519" t="inlineStr">
         <is>
-          <t>Envio de ATA de Implantação - EF I</t>
+          <t>Fed - PIS/COFINS Não Cumul/Mon - 5856</t>
         </is>
       </c>
       <c r="K519" t="inlineStr"/>
       <c r="L519" s="1" t="n">
-        <v>46220</v>
-      </c>
-      <c r="M519" t="inlineStr">
-        <is>
-          <t>31/07/2026</t>
-        </is>
-      </c>
+        <v>46225</v>
+      </c>
+      <c r="M519" t="inlineStr"/>
       <c r="N519" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O519" t="n">
-        <v>18186565</v>
+        <v>17968388</v>
       </c>
       <c r="P519" t="inlineStr">
         <is>
-          <t>Priscila Volpe</t>
+          <t>Denis Reis</t>
         </is>
       </c>
       <c r="Q519" t="inlineStr">
@@ -56277,20 +56277,19 @@
       </c>
       <c r="R519" t="inlineStr"/>
       <c r="S519" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="T519" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN</t>
-        </is>
-      </c>
-      <c r="U519" t="inlineStr"/>
-      <c r="V519" t="inlineStr">
-        <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 31/07/2026 
-ainda não foi realizado as implantações - Data Comentário: 01/07/2026 13:38</t>
-        </is>
-      </c>
+          <t xml:space="preserve">GTG </t>
+        </is>
+      </c>
+      <c r="U519" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V519" t="inlineStr"/>
       <c r="W519" t="inlineStr"/>
       <c r="X519" t="inlineStr"/>
       <c r="Y519" t="inlineStr"/>
@@ -56304,7 +56303,7 @@
       <c r="AE519" t="inlineStr"/>
       <c r="AF519" t="inlineStr">
         <is>
-          <t>Tarefa</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="AG519" t="inlineStr">
@@ -56315,11 +56314,11 @@
     </row>
     <row r="520">
       <c r="A520" t="n">
-        <v>6963</v>
+        <v>6962</v>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN LTDA</t>
+          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
@@ -56343,7 +56342,7 @@
         </is>
       </c>
       <c r="G520" t="n">
-        <v>11617</v>
+        <v>1882</v>
       </c>
       <c r="H520" t="n">
         <v>0</v>
@@ -56355,29 +56354,25 @@
       </c>
       <c r="J520" t="inlineStr">
         <is>
-          <t>Envio de ATA de Implantação - EF I</t>
+          <t>Fed - PIS/COFINS Não Cumul/Mon - 5856</t>
         </is>
       </c>
       <c r="K520" t="inlineStr"/>
       <c r="L520" s="1" t="n">
-        <v>46220</v>
-      </c>
-      <c r="M520" t="inlineStr">
-        <is>
-          <t>31/07/2026</t>
-        </is>
-      </c>
+        <v>46225</v>
+      </c>
+      <c r="M520" t="inlineStr"/>
       <c r="N520" t="inlineStr">
         <is>
           <t>06/2026</t>
         </is>
       </c>
       <c r="O520" t="n">
-        <v>18186566</v>
+        <v>18186958</v>
       </c>
       <c r="P520" t="inlineStr">
         <is>
-          <t>Priscila Volpe</t>
+          <t>Denis Reis</t>
         </is>
       </c>
       <c r="Q520" t="inlineStr">
@@ -56387,7 +56382,7 @@
       </c>
       <c r="R520" t="inlineStr"/>
       <c r="S520" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="T520" t="inlineStr">
         <is>
@@ -56395,12 +56390,7 @@
         </is>
       </c>
       <c r="U520" t="inlineStr"/>
-      <c r="V520" t="inlineStr">
-        <is>
-          <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 31/07/2026 
-ainda não foi realizado as implantações - Data Comentário: 01/07/2026 13:38</t>
-        </is>
-      </c>
+      <c r="V520" t="inlineStr"/>
       <c r="W520" t="inlineStr"/>
       <c r="X520" t="inlineStr"/>
       <c r="Y520" t="inlineStr"/>
@@ -56414,7 +56404,7 @@
       <c r="AE520" t="inlineStr"/>
       <c r="AF520" t="inlineStr">
         <is>
-          <t>Tarefa</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="AG520" t="inlineStr">
@@ -56425,11 +56415,11 @@
     </row>
     <row r="521">
       <c r="A521" t="n">
-        <v>6627</v>
+        <v>6963</v>
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
+          <t>PROMOTORAS GYN LTDA</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
@@ -56444,12 +56434,12 @@
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F521" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Reynaldo Santos</t>
         </is>
       </c>
       <c r="G521" t="n">
@@ -56479,7 +56469,7 @@
         </is>
       </c>
       <c r="O521" t="n">
-        <v>17968388</v>
+        <v>18187224</v>
       </c>
       <c r="P521" t="inlineStr">
         <is>
@@ -56497,14 +56487,10 @@
       </c>
       <c r="T521" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
-        </is>
-      </c>
-      <c r="U521" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>PROMOTORAS GYN</t>
+        </is>
+      </c>
+      <c r="U521" t="inlineStr"/>
       <c r="V521" t="inlineStr"/>
       <c r="W521" t="inlineStr"/>
       <c r="X521" t="inlineStr"/>
@@ -56530,11 +56516,11 @@
     </row>
     <row r="522">
       <c r="A522" t="n">
-        <v>6962</v>
+        <v>6627</v>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
+          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
@@ -56549,16 +56535,16 @@
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="F522" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G522" t="n">
-        <v>1882</v>
+        <v>7026</v>
       </c>
       <c r="H522" t="n">
         <v>0</v>
@@ -56570,12 +56556,12 @@
       </c>
       <c r="J522" t="inlineStr">
         <is>
-          <t>Fed - PIS/COFINS Não Cumul/Mon - 5856</t>
+          <t>Movimento - Sistema de Análise</t>
         </is>
       </c>
       <c r="K522" t="inlineStr"/>
       <c r="L522" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="M522" t="inlineStr"/>
       <c r="N522" t="inlineStr">
@@ -56584,7 +56570,7 @@
         </is>
       </c>
       <c r="O522" t="n">
-        <v>18186958</v>
+        <v>18048471</v>
       </c>
       <c r="P522" t="inlineStr">
         <is>
@@ -56598,15 +56584,25 @@
       </c>
       <c r="R522" t="inlineStr"/>
       <c r="S522" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="T522" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN</t>
-        </is>
-      </c>
-      <c r="U522" t="inlineStr"/>
-      <c r="V522" t="inlineStr"/>
+          <t xml:space="preserve">GTG </t>
+        </is>
+      </c>
+      <c r="U522" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V522" t="inlineStr">
+        <is>
+          <t>Integração com Sistema de Análise 
+ICMS LIBERADO - PIS E COFINS não esta batendo com a apuração, verificar e subir novamente.
+Data Simulação: 16/07/2026 18:33:08 - Data Comentário: 16/07/2026 19:05</t>
+        </is>
+      </c>
       <c r="W522" t="inlineStr"/>
       <c r="X522" t="inlineStr"/>
       <c r="Y522" t="inlineStr"/>
@@ -56620,7 +56616,7 @@
       <c r="AE522" t="inlineStr"/>
       <c r="AF522" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Tarefa</t>
         </is>
       </c>
       <c r="AG522" t="inlineStr">
@@ -56631,11 +56627,11 @@
     </row>
     <row r="523">
       <c r="A523" t="n">
-        <v>6963</v>
+        <v>6548</v>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN LTDA</t>
+          <t>GOIAS SILAGEM LTDA</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
@@ -56655,14 +56651,14 @@
       </c>
       <c r="F523" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G523" t="n">
-        <v>1882</v>
+        <v>1914</v>
       </c>
       <c r="H523" t="n">
-        <v>0</v>
+        <v>1862</v>
       </c>
       <c r="I523" t="inlineStr">
         <is>
@@ -56671,12 +56667,12 @@
       </c>
       <c r="J523" t="inlineStr">
         <is>
-          <t>Fed - PIS/COFINS Não Cumul/Mon - 5856</t>
+          <t>Receitas Financeiras ( Aplicação Financeira )</t>
         </is>
       </c>
       <c r="K523" t="inlineStr"/>
       <c r="L523" s="1" t="n">
-        <v>46225</v>
+        <v>46224</v>
       </c>
       <c r="M523" t="inlineStr"/>
       <c r="N523" t="inlineStr">
@@ -56685,11 +56681,11 @@
         </is>
       </c>
       <c r="O523" t="n">
-        <v>18187224</v>
+        <v>17988589</v>
       </c>
       <c r="P523" t="inlineStr">
         <is>
-          <t>Denis Reis</t>
+          <t>Cristiana Grizostomo</t>
         </is>
       </c>
       <c r="Q523" t="inlineStr">
@@ -56699,14 +56695,18 @@
       </c>
       <c r="R523" t="inlineStr"/>
       <c r="S523" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="T523" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN</t>
-        </is>
-      </c>
-      <c r="U523" t="inlineStr"/>
+          <t>GOIAS SILAGEM</t>
+        </is>
+      </c>
+      <c r="U523" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V523" t="inlineStr"/>
       <c r="W523" t="inlineStr"/>
       <c r="X523" t="inlineStr"/>
@@ -56721,7 +56721,7 @@
       <c r="AE523" t="inlineStr"/>
       <c r="AF523" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Tarefa</t>
         </is>
       </c>
       <c r="AG523" t="inlineStr">
@@ -56732,11 +56732,11 @@
     </row>
     <row r="524">
       <c r="A524" t="n">
-        <v>6627</v>
+        <v>6962</v>
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
+          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
@@ -56751,19 +56751,19 @@
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="F524" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Reynaldo Santos</t>
         </is>
       </c>
       <c r="G524" t="n">
-        <v>7026</v>
+        <v>1914</v>
       </c>
       <c r="H524" t="n">
-        <v>0</v>
+        <v>1862</v>
       </c>
       <c r="I524" t="inlineStr">
         <is>
@@ -56772,12 +56772,12 @@
       </c>
       <c r="J524" t="inlineStr">
         <is>
-          <t>Movimento - Sistema de Análise</t>
+          <t>Receitas Financeiras ( Aplicação Financeira )</t>
         </is>
       </c>
       <c r="K524" t="inlineStr"/>
       <c r="L524" s="1" t="n">
-        <v>46226</v>
+        <v>46224</v>
       </c>
       <c r="M524" t="inlineStr"/>
       <c r="N524" t="inlineStr">
@@ -56786,7 +56786,7 @@
         </is>
       </c>
       <c r="O524" t="n">
-        <v>18048471</v>
+        <v>18186972</v>
       </c>
       <c r="P524" t="inlineStr">
         <is>
@@ -56800,25 +56800,15 @@
       </c>
       <c r="R524" t="inlineStr"/>
       <c r="S524" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="T524" t="inlineStr">
         <is>
-          <t xml:space="preserve">GTG </t>
-        </is>
-      </c>
-      <c r="U524" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="V524" t="inlineStr">
-        <is>
-          <t>Integração com Sistema de Análise 
-ICMS LIBERADO - PIS E COFINS não esta batendo com a apuração, verificar e subir novamente.
-Data Simulação: 16/07/2026 18:33:08 - Data Comentário: 16/07/2026 19:05</t>
-        </is>
-      </c>
+          <t>PROMOTORAS GYN</t>
+        </is>
+      </c>
+      <c r="U524" t="inlineStr"/>
+      <c r="V524" t="inlineStr"/>
       <c r="W524" t="inlineStr"/>
       <c r="X524" t="inlineStr"/>
       <c r="Y524" t="inlineStr"/>
@@ -56843,11 +56833,11 @@
     </row>
     <row r="525">
       <c r="A525" t="n">
-        <v>6548</v>
+        <v>6963</v>
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM LTDA</t>
+          <t>PROMOTORAS GYN LTDA</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
@@ -56867,7 +56857,7 @@
       </c>
       <c r="F525" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Reynaldo Santos</t>
         </is>
       </c>
       <c r="G525" t="n">
@@ -56897,11 +56887,11 @@
         </is>
       </c>
       <c r="O525" t="n">
-        <v>17988589</v>
+        <v>18187238</v>
       </c>
       <c r="P525" t="inlineStr">
         <is>
-          <t>Cristiana Grizostomo</t>
+          <t>Denis Reis</t>
         </is>
       </c>
       <c r="Q525" t="inlineStr">
@@ -56915,14 +56905,10 @@
       </c>
       <c r="T525" t="inlineStr">
         <is>
-          <t>GOIAS SILAGEM</t>
-        </is>
-      </c>
-      <c r="U525" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>PROMOTORAS GYN</t>
+        </is>
+      </c>
+      <c r="U525" t="inlineStr"/>
       <c r="V525" t="inlineStr"/>
       <c r="W525" t="inlineStr"/>
       <c r="X525" t="inlineStr"/>
@@ -56948,11 +56934,11 @@
     </row>
     <row r="526">
       <c r="A526" t="n">
-        <v>6962</v>
+        <v>6704</v>
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>INOVAR CONSULTORIA EM VAREJO LTDA</t>
+          <t>TECNO COM INFORMATICA LTDA</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
@@ -56972,28 +56958,28 @@
       </c>
       <c r="F526" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G526" t="n">
-        <v>1914</v>
+        <v>1802</v>
       </c>
       <c r="H526" t="n">
-        <v>1862</v>
+        <v>0</v>
       </c>
       <c r="I526" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J526" t="inlineStr">
         <is>
-          <t>Receitas Financeiras ( Aplicação Financeira )</t>
+          <t>Est - ICMS RPA - CÓD. 046-2</t>
         </is>
       </c>
       <c r="K526" t="inlineStr"/>
       <c r="L526" s="1" t="n">
-        <v>46224</v>
+        <v>46220</v>
       </c>
       <c r="M526" t="inlineStr"/>
       <c r="N526" t="inlineStr">
@@ -57002,11 +56988,11 @@
         </is>
       </c>
       <c r="O526" t="n">
-        <v>18186972</v>
+        <v>18085196</v>
       </c>
       <c r="P526" t="inlineStr">
         <is>
-          <t>Denis Reis</t>
+          <t>Cristina Leite</t>
         </is>
       </c>
       <c r="Q526" t="inlineStr">
@@ -57016,14 +57002,18 @@
       </c>
       <c r="R526" t="inlineStr"/>
       <c r="S526" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="T526" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN</t>
-        </is>
-      </c>
-      <c r="U526" t="inlineStr"/>
+          <t>TECNO COM</t>
+        </is>
+      </c>
+      <c r="U526" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V526" t="inlineStr"/>
       <c r="W526" t="inlineStr"/>
       <c r="X526" t="inlineStr"/>
@@ -57038,22 +57028,22 @@
       <c r="AE526" t="inlineStr"/>
       <c r="AF526" t="inlineStr">
         <is>
-          <t>Tarefa</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="AG526" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="n">
-        <v>6963</v>
+        <v>6404</v>
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN LTDA</t>
+          <t>SOLAR INVESTIMENTOS LTDA</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
@@ -57063,7 +57053,7 @@
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E527" t="inlineStr">
@@ -57073,28 +57063,28 @@
       </c>
       <c r="F527" t="inlineStr">
         <is>
-          <t>Reynaldo Santos</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G527" t="n">
-        <v>1914</v>
+        <v>1810</v>
       </c>
       <c r="H527" t="n">
-        <v>1862</v>
+        <v>0</v>
       </c>
       <c r="I527" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J527" t="inlineStr">
         <is>
-          <t>Receitas Financeiras ( Aplicação Financeira )</t>
+          <t>Fed - IRPJ/CSLL</t>
         </is>
       </c>
       <c r="K527" t="inlineStr"/>
       <c r="L527" s="1" t="n">
-        <v>46224</v>
+        <v>46230</v>
       </c>
       <c r="M527" t="inlineStr"/>
       <c r="N527" t="inlineStr">
@@ -57103,11 +57093,11 @@
         </is>
       </c>
       <c r="O527" t="n">
-        <v>18187238</v>
+        <v>16962177</v>
       </c>
       <c r="P527" t="inlineStr">
         <is>
-          <t>Denis Reis</t>
+          <t>Cristina Leite</t>
         </is>
       </c>
       <c r="Q527" t="inlineStr">
@@ -57117,14 +57107,18 @@
       </c>
       <c r="R527" t="inlineStr"/>
       <c r="S527" t="n">
-        <v>-4</v>
+        <v>-10</v>
       </c>
       <c r="T527" t="inlineStr">
         <is>
-          <t>PROMOTORAS GYN</t>
-        </is>
-      </c>
-      <c r="U527" t="inlineStr"/>
+          <t>SOLAR INVESTIMENTOS</t>
+        </is>
+      </c>
+      <c r="U527" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="V527" t="inlineStr"/>
       <c r="W527" t="inlineStr"/>
       <c r="X527" t="inlineStr"/>
@@ -57139,22 +57133,22 @@
       <c r="AE527" t="inlineStr"/>
       <c r="AF527" t="inlineStr">
         <is>
-          <t>Tarefa</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="AG527" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="n">
-        <v>6704</v>
+        <v>6703</v>
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>TECNO COM INFORMATICA LTDA</t>
+          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
@@ -57164,7 +57158,7 @@
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E528" t="inlineStr">
@@ -57178,7 +57172,7 @@
         </is>
       </c>
       <c r="G528" t="n">
-        <v>1802</v>
+        <v>1810</v>
       </c>
       <c r="H528" t="n">
         <v>0</v>
@@ -57190,12 +57184,12 @@
       </c>
       <c r="J528" t="inlineStr">
         <is>
-          <t>Est - ICMS RPA - CÓD. 046-2</t>
+          <t>Fed - IRPJ/CSLL</t>
         </is>
       </c>
       <c r="K528" t="inlineStr"/>
       <c r="L528" s="1" t="n">
-        <v>46220</v>
+        <v>46230</v>
       </c>
       <c r="M528" t="inlineStr"/>
       <c r="N528" t="inlineStr">
@@ -57204,7 +57198,7 @@
         </is>
       </c>
       <c r="O528" t="n">
-        <v>18085196</v>
+        <v>17948812</v>
       </c>
       <c r="P528" t="inlineStr">
         <is>
@@ -57218,11 +57212,11 @@
       </c>
       <c r="R528" t="inlineStr"/>
       <c r="S528" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="T528" t="inlineStr">
         <is>
-          <t>TECNO COM</t>
+          <t>LIMA MOTA</t>
         </is>
       </c>
       <c r="U528" t="inlineStr">
@@ -57255,11 +57249,11 @@
     </row>
     <row r="529">
       <c r="A529" t="n">
-        <v>6404</v>
+        <v>5617</v>
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS LTDA</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
@@ -57269,7 +57263,7 @@
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E529" t="inlineStr">
@@ -57283,7 +57277,7 @@
         </is>
       </c>
       <c r="G529" t="n">
-        <v>1810</v>
+        <v>6762</v>
       </c>
       <c r="H529" t="n">
         <v>0</v>
@@ -57295,12 +57289,12 @@
       </c>
       <c r="J529" t="inlineStr">
         <is>
-          <t>Fed - IRPJ/CSLL</t>
+          <t>Fed - IRRF s/ Aluguel - 3208</t>
         </is>
       </c>
       <c r="K529" t="inlineStr"/>
       <c r="L529" s="1" t="n">
-        <v>46230</v>
+        <v>46220</v>
       </c>
       <c r="M529" t="inlineStr"/>
       <c r="N529" t="inlineStr">
@@ -57309,7 +57303,7 @@
         </is>
       </c>
       <c r="O529" t="n">
-        <v>16962177</v>
+        <v>17407769</v>
       </c>
       <c r="P529" t="inlineStr">
         <is>
@@ -57323,11 +57317,11 @@
       </c>
       <c r="R529" t="inlineStr"/>
       <c r="S529" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="T529" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U529" t="inlineStr">
@@ -57360,11 +57354,11 @@
     </row>
     <row r="530">
       <c r="A530" t="n">
-        <v>6703</v>
+        <v>6224</v>
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
@@ -57374,7 +57368,7 @@
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E530" t="inlineStr">
@@ -57384,11 +57378,11 @@
       </c>
       <c r="F530" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G530" t="n">
-        <v>1810</v>
+        <v>6762</v>
       </c>
       <c r="H530" t="n">
         <v>0</v>
@@ -57400,12 +57394,12 @@
       </c>
       <c r="J530" t="inlineStr">
         <is>
-          <t>Fed - IRPJ/CSLL</t>
+          <t>Fed - IRRF s/ Aluguel - 3208</t>
         </is>
       </c>
       <c r="K530" t="inlineStr"/>
       <c r="L530" s="1" t="n">
-        <v>46230</v>
+        <v>46220</v>
       </c>
       <c r="M530" t="inlineStr"/>
       <c r="N530" t="inlineStr">
@@ -57414,7 +57408,7 @@
         </is>
       </c>
       <c r="O530" t="n">
-        <v>17948812</v>
+        <v>17688897</v>
       </c>
       <c r="P530" t="inlineStr">
         <is>
@@ -57428,11 +57422,11 @@
       </c>
       <c r="R530" t="inlineStr"/>
       <c r="S530" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="T530" t="inlineStr">
         <is>
-          <t>LIMA MOTA</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U530" t="inlineStr">
@@ -57465,11 +57459,11 @@
     </row>
     <row r="531">
       <c r="A531" t="n">
-        <v>5617</v>
+        <v>6279</v>
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>DIENNYFER DA S PEREIRA</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
@@ -57479,7 +57473,7 @@
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E531" t="inlineStr">
@@ -57489,11 +57483,11 @@
       </c>
       <c r="F531" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G531" t="n">
-        <v>6762</v>
+        <v>1807</v>
       </c>
       <c r="H531" t="n">
         <v>0</v>
@@ -57505,12 +57499,12 @@
       </c>
       <c r="J531" t="inlineStr">
         <is>
-          <t>Fed - IRRF s/ Aluguel - 3208</t>
+          <t>Fed - PIS/COFINS Cumulativo - 2172</t>
         </is>
       </c>
       <c r="K531" t="inlineStr"/>
       <c r="L531" s="1" t="n">
-        <v>46220</v>
+        <v>46225</v>
       </c>
       <c r="M531" t="inlineStr"/>
       <c r="N531" t="inlineStr">
@@ -57519,7 +57513,7 @@
         </is>
       </c>
       <c r="O531" t="n">
-        <v>17407769</v>
+        <v>18087644</v>
       </c>
       <c r="P531" t="inlineStr">
         <is>
@@ -57533,11 +57527,11 @@
       </c>
       <c r="R531" t="inlineStr"/>
       <c r="S531" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="T531" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U531" t="inlineStr">
@@ -57545,7 +57539,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V531" t="inlineStr"/>
+      <c r="V531" t="inlineStr">
+        <is>
+          <t>Imposto enviado via SCI Report - Data Comentário: 17/07/2026 08:13</t>
+        </is>
+      </c>
       <c r="W531" t="inlineStr"/>
       <c r="X531" t="inlineStr"/>
       <c r="Y531" t="inlineStr"/>
@@ -57570,11 +57568,11 @@
     </row>
     <row r="532">
       <c r="A532" t="n">
-        <v>6224</v>
+        <v>6404</v>
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>SOLAR INVESTIMENTOS LTDA</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
@@ -57584,7 +57582,7 @@
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Presumido</t>
         </is>
       </c>
       <c r="E532" t="inlineStr">
@@ -57594,11 +57592,11 @@
       </c>
       <c r="F532" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G532" t="n">
-        <v>6762</v>
+        <v>1807</v>
       </c>
       <c r="H532" t="n">
         <v>0</v>
@@ -57610,12 +57608,12 @@
       </c>
       <c r="J532" t="inlineStr">
         <is>
-          <t>Fed - IRRF s/ Aluguel - 3208</t>
+          <t>Fed - PIS/COFINS Cumulativo - 2172</t>
         </is>
       </c>
       <c r="K532" t="inlineStr"/>
       <c r="L532" s="1" t="n">
-        <v>46220</v>
+        <v>46225</v>
       </c>
       <c r="M532" t="inlineStr"/>
       <c r="N532" t="inlineStr">
@@ -57624,7 +57622,7 @@
         </is>
       </c>
       <c r="O532" t="n">
-        <v>17688897</v>
+        <v>16962169</v>
       </c>
       <c r="P532" t="inlineStr">
         <is>
@@ -57638,11 +57636,11 @@
       </c>
       <c r="R532" t="inlineStr"/>
       <c r="S532" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="T532" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>SOLAR INVESTIMENTOS</t>
         </is>
       </c>
       <c r="U532" t="inlineStr">
@@ -57675,11 +57673,11 @@
     </row>
     <row r="533">
       <c r="A533" t="n">
-        <v>6279</v>
+        <v>6703</v>
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>DIENNYFER DA S PEREIRA</t>
+          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
@@ -57699,7 +57697,7 @@
       </c>
       <c r="F533" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G533" t="n">
@@ -57729,7 +57727,7 @@
         </is>
       </c>
       <c r="O533" t="n">
-        <v>18087644</v>
+        <v>17948804</v>
       </c>
       <c r="P533" t="inlineStr">
         <is>
@@ -57747,7 +57745,7 @@
       </c>
       <c r="T533" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>LIMA MOTA</t>
         </is>
       </c>
       <c r="U533" t="inlineStr">
@@ -57784,11 +57782,11 @@
     </row>
     <row r="534">
       <c r="A534" t="n">
-        <v>6404</v>
+        <v>5417</v>
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS LTDA</t>
+          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
@@ -57798,7 +57796,7 @@
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E534" t="inlineStr">
@@ -57808,11 +57806,11 @@
       </c>
       <c r="F534" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="G534" t="n">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="H534" t="n">
         <v>0</v>
@@ -57824,7 +57822,7 @@
       </c>
       <c r="J534" t="inlineStr">
         <is>
-          <t>Fed - PIS/COFINS Cumulativo - 2172</t>
+          <t>Fed - PIS/COFINS Não Cumul/Mon - 5856</t>
         </is>
       </c>
       <c r="K534" t="inlineStr"/>
@@ -57838,7 +57836,7 @@
         </is>
       </c>
       <c r="O534" t="n">
-        <v>16962169</v>
+        <v>17398963</v>
       </c>
       <c r="P534" t="inlineStr">
         <is>
@@ -57856,7 +57854,7 @@
       </c>
       <c r="T534" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS</t>
+          <t>NOSSO NOVO SUPERMERCADO</t>
         </is>
       </c>
       <c r="U534" t="inlineStr">
@@ -57864,7 +57862,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V534" t="inlineStr"/>
+      <c r="V534" t="inlineStr">
+        <is>
+          <t>Imposto enviado via SCI Report - Data Comentário: 16/07/2026 18:38</t>
+        </is>
+      </c>
       <c r="W534" t="inlineStr"/>
       <c r="X534" t="inlineStr"/>
       <c r="Y534" t="inlineStr"/>
@@ -57889,11 +57891,11 @@
     </row>
     <row r="535">
       <c r="A535" t="n">
-        <v>6703</v>
+        <v>5617</v>
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>LIMA MOTA LOCAÇÕES, SERVIÇOS E COMERCIO LTDA</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
@@ -57903,7 +57905,7 @@
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t>Federal - Lucro Presumido</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E535" t="inlineStr">
@@ -57917,7 +57919,7 @@
         </is>
       </c>
       <c r="G535" t="n">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="H535" t="n">
         <v>0</v>
@@ -57929,7 +57931,7 @@
       </c>
       <c r="J535" t="inlineStr">
         <is>
-          <t>Fed - PIS/COFINS Cumulativo - 2172</t>
+          <t>Fed - PIS/COFINS Não Cumul/Mon - 5856</t>
         </is>
       </c>
       <c r="K535" t="inlineStr"/>
@@ -57943,7 +57945,7 @@
         </is>
       </c>
       <c r="O535" t="n">
-        <v>17948804</v>
+        <v>17407599</v>
       </c>
       <c r="P535" t="inlineStr">
         <is>
@@ -57961,7 +57963,7 @@
       </c>
       <c r="T535" t="inlineStr">
         <is>
-          <t>LIMA MOTA</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U535" t="inlineStr">
@@ -57969,11 +57971,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V535" t="inlineStr">
-        <is>
-          <t>Imposto enviado via SCI Report - Data Comentário: 17/07/2026 08:13</t>
-        </is>
-      </c>
+      <c r="V535" t="inlineStr"/>
       <c r="W535" t="inlineStr"/>
       <c r="X535" t="inlineStr"/>
       <c r="Y535" t="inlineStr"/>
@@ -57998,11 +57996,11 @@
     </row>
     <row r="536">
       <c r="A536" t="n">
-        <v>5417</v>
+        <v>6224</v>
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>COMERCIAL DE ALIMENTOS ALLEGRA LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
@@ -58022,7 +58020,7 @@
       </c>
       <c r="F536" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Sem Master</t>
         </is>
       </c>
       <c r="G536" t="n">
@@ -58052,7 +58050,7 @@
         </is>
       </c>
       <c r="O536" t="n">
-        <v>17398963</v>
+        <v>17688691</v>
       </c>
       <c r="P536" t="inlineStr">
         <is>
@@ -58070,7 +58068,7 @@
       </c>
       <c r="T536" t="inlineStr">
         <is>
-          <t>NOSSO NOVO SUPERMERCADO</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U536" t="inlineStr">
@@ -58078,11 +58076,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V536" t="inlineStr">
-        <is>
-          <t>Imposto enviado via SCI Report - Data Comentário: 16/07/2026 18:38</t>
-        </is>
-      </c>
+      <c r="V536" t="inlineStr"/>
       <c r="W536" t="inlineStr"/>
       <c r="X536" t="inlineStr"/>
       <c r="Y536" t="inlineStr"/>
@@ -58107,11 +58101,11 @@
     </row>
     <row r="537">
       <c r="A537" t="n">
-        <v>5617</v>
+        <v>6278</v>
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
+          <t>EMPORIO DOS FRIOS LTDA</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
@@ -58121,7 +58115,7 @@
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>Federal - L Real -Trimestral</t>
+          <t>Federal - Lucro Real - Anual</t>
         </is>
       </c>
       <c r="E537" t="inlineStr">
@@ -58161,7 +58155,7 @@
         </is>
       </c>
       <c r="O537" t="n">
-        <v>17407599</v>
+        <v>17148704</v>
       </c>
       <c r="P537" t="inlineStr">
         <is>
@@ -58179,7 +58173,7 @@
       </c>
       <c r="T537" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>EMPORIO DOS FRIOS</t>
         </is>
       </c>
       <c r="U537" t="inlineStr">
@@ -58212,11 +58206,11 @@
     </row>
     <row r="538">
       <c r="A538" t="n">
-        <v>6224</v>
+        <v>6704</v>
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>TECNO COM INFORMATICA LTDA</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
@@ -58236,7 +58230,7 @@
       </c>
       <c r="F538" t="inlineStr">
         <is>
-          <t>Sem Master</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="G538" t="n">
@@ -58266,7 +58260,7 @@
         </is>
       </c>
       <c r="O538" t="n">
-        <v>17688691</v>
+        <v>18085207</v>
       </c>
       <c r="P538" t="inlineStr">
         <is>
@@ -58284,7 +58278,7 @@
       </c>
       <c r="T538" t="inlineStr">
         <is>
-          <t>SUPER MAIS DO GOIÁS</t>
+          <t>TECNO COM</t>
         </is>
       </c>
       <c r="U538" t="inlineStr">
@@ -58317,11 +58311,11 @@
     </row>
     <row r="539">
       <c r="A539" t="n">
-        <v>6278</v>
+        <v>5617</v>
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS LTDA</t>
+          <t>SUPERMERCADO PRECO BAIXO TODO DIA LTDA</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
@@ -58331,7 +58325,7 @@
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>Federal - Lucro Real - Anual</t>
+          <t>Federal - L Real -Trimestral</t>
         </is>
       </c>
       <c r="E539" t="inlineStr">
@@ -58345,7 +58339,7 @@
         </is>
       </c>
       <c r="G539" t="n">
-        <v>1808</v>
+        <v>7025</v>
       </c>
       <c r="H539" t="n">
         <v>0</v>
@@ -58357,12 +58351,12 @@
       </c>
       <c r="J539" t="inlineStr">
         <is>
-          <t>Fed - PIS/COFINS Não Cumul/Mon - 5856</t>
+          <t>Movimento - Sistema de Análise</t>
         </is>
       </c>
       <c r="K539" t="inlineStr"/>
       <c r="L539" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="M539" t="inlineStr"/>
       <c r="N539" t="inlineStr">
@@ -58371,7 +58365,7 @@
         </is>
       </c>
       <c r="O539" t="n">
-        <v>17148704</v>
+        <v>17407819</v>
       </c>
       <c r="P539" t="inlineStr">
         <is>
@@ -58385,11 +58379,11 @@
       </c>
       <c r="R539" t="inlineStr"/>
       <c r="S539" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="T539" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS</t>
+          <t>SUPER MAIS DO GOIÁS</t>
         </is>
       </c>
       <c r="U539" t="inlineStr">
@@ -58397,7 +58391,13 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V539" t="inlineStr"/>
+      <c r="V539" t="inlineStr">
+        <is>
+          <t>Integração com Sistema de Análise 
+ICMS liberado, aguardo a validação do SPED Contribuições. 
+Data Simulação: 16/07/2026 16:40:46 - Data Comentário: 16/07/2026 17:06</t>
+        </is>
+      </c>
       <c r="W539" t="inlineStr"/>
       <c r="X539"